--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -9221,31 +9221,31 @@
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>聯詠(3034)</t>
         </is>
       </c>
       <c r="E244" s="14" t="n">
-        <v>331</v>
+        <v>6</v>
       </c>
       <c r="F244" s="14" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="G244" s="14" t="n">
-        <v>9022</v>
+        <v>290</v>
       </c>
       <c r="H244" s="14" t="n">
-        <v>1942</v>
+        <v>2691</v>
       </c>
       <c r="I244" s="14" t="n">
-        <v>7080</v>
+        <v>-2401</v>
       </c>
       <c r="J244" s="15" t="n">
-        <v>272.57</v>
+        <v>483.5</v>
       </c>
       <c r="K244" s="15" t="n">
-        <v>277.4</v>
-      </c>
-      <c r="L244" s="16">
+        <v>480.52</v>
+      </c>
+      <c r="L244" s="17">
         <f>F244*(K244-J244)</f>
         <v/>
       </c>
@@ -9253,31 +9253,31 @@
     <row r="245" ht="16.5" customHeight="1">
       <c r="D245" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>精材(3374)</t>
         </is>
       </c>
       <c r="E245" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F245" s="14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G245" s="14" t="n">
-        <v>4972</v>
+        <v>135</v>
       </c>
       <c r="H245" s="14" t="n">
-        <v>8305</v>
+        <v>897</v>
       </c>
       <c r="I245" s="14" t="n">
-        <v>-3333</v>
+        <v>-762</v>
       </c>
       <c r="J245" s="15" t="n">
-        <v>0</v>
+        <v>224.67</v>
       </c>
       <c r="K245" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L245" s="16">
+        <v>218.85</v>
+      </c>
+      <c r="L245" s="17">
         <f>F245*(K245-J245)</f>
         <v/>
       </c>
@@ -9285,31 +9285,31 @@
     <row r="246" ht="16.5" customHeight="1">
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>金像電(2368)</t>
+          <t>大聯大(3702)</t>
         </is>
       </c>
       <c r="E246" s="14" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F246" s="14" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G246" s="14" t="n">
-        <v>4565</v>
+        <v>11</v>
       </c>
       <c r="H246" s="14" t="n">
-        <v>7876</v>
+        <v>347</v>
       </c>
       <c r="I246" s="14" t="n">
-        <v>-3311</v>
+        <v>-336</v>
       </c>
       <c r="J246" s="15" t="n">
-        <v>1383.36</v>
+        <v>109</v>
       </c>
       <c r="K246" s="15" t="n">
-        <v>1312.58</v>
-      </c>
-      <c r="L246" s="17">
+        <v>111.97</v>
+      </c>
+      <c r="L246" s="16">
         <f>F246*(K246-J246)</f>
         <v/>
       </c>
@@ -9317,29 +9317,29 @@
     <row r="247" ht="16.5" customHeight="1">
       <c r="D247" s="13" t="inlineStr">
         <is>
-          <t>頎邦(6147)</t>
+          <t>藥華藥(6446)</t>
         </is>
       </c>
       <c r="E247" s="14" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="F247" s="14" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G247" s="14" t="n">
-        <v>4442</v>
+        <v>3</v>
       </c>
       <c r="H247" s="14" t="n">
-        <v>801</v>
+        <v>299</v>
       </c>
       <c r="I247" s="14" t="n">
-        <v>3641</v>
+        <v>-296</v>
       </c>
       <c r="J247" s="15" t="n">
-        <v>189.02</v>
+        <v>0</v>
       </c>
       <c r="K247" s="15" t="n">
-        <v>190.74</v>
+        <v>0</v>
       </c>
       <c r="L247" s="16">
         <f>F247*(K247-J247)</f>
@@ -9349,29 +9349,29 @@
     <row r="248" ht="16.5" customHeight="1">
       <c r="D248" s="13" t="inlineStr">
         <is>
-          <t>南茂(8150)</t>
+          <t>川湖(2059)</t>
         </is>
       </c>
       <c r="E248" s="14" t="n">
-        <v>449</v>
+        <v>0</v>
       </c>
       <c r="F248" s="14" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="G248" s="14" t="n">
-        <v>4190</v>
+        <v>0</v>
       </c>
       <c r="H248" s="14" t="n">
-        <v>2489</v>
+        <v>289</v>
       </c>
       <c r="I248" s="14" t="n">
-        <v>1701</v>
+        <v>-289</v>
       </c>
       <c r="J248" s="15" t="n">
-        <v>93.31</v>
+        <v>0</v>
       </c>
       <c r="K248" s="15" t="n">
-        <v>93.93000000000001</v>
+        <v>0</v>
       </c>
       <c r="L248" s="16">
         <f>F248*(K248-J248)</f>
@@ -9381,23 +9381,23 @@
     <row r="249" ht="16.5" customHeight="1">
       <c r="D249" s="13" t="inlineStr">
         <is>
-          <t>健策(3653)</t>
+          <t>鑫聯大投控(3709)</t>
         </is>
       </c>
       <c r="E249" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F249" s="14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G249" s="14" t="n">
-        <v>3691</v>
+        <v>0</v>
       </c>
       <c r="H249" s="14" t="n">
-        <v>766</v>
+        <v>0</v>
       </c>
       <c r="I249" s="14" t="n">
-        <v>2925</v>
+        <v>0</v>
       </c>
       <c r="J249" s="15" t="n">
         <v>0</v>
@@ -9411,132 +9411,48 @@
       </c>
     </row>
     <row r="250" ht="16.5" customHeight="1">
-      <c r="D250" s="13" t="inlineStr">
-        <is>
-          <t>台燿(6274)</t>
-        </is>
-      </c>
-      <c r="E250" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F250" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" s="14" t="n">
-        <v>3448</v>
-      </c>
-      <c r="H250" s="14" t="n">
-        <v>3996</v>
-      </c>
-      <c r="I250" s="14" t="n">
-        <v>-548</v>
-      </c>
-      <c r="J250" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K250" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L250" s="16">
-        <f>F250*(K250-J250)</f>
-        <v/>
-      </c>
+      <c r="D250" s="13" t="n"/>
+      <c r="E250" s="14" t="n"/>
+      <c r="F250" s="14" t="n"/>
+      <c r="G250" s="14" t="n"/>
+      <c r="H250" s="14" t="n"/>
+      <c r="I250" s="14" t="n"/>
+      <c r="J250" s="15" t="n"/>
+      <c r="K250" s="15" t="n"/>
+      <c r="L250" s="16" t="n"/>
     </row>
     <row r="251" ht="16.5" customHeight="1">
-      <c r="D251" s="13" t="inlineStr">
-        <is>
-          <t>鴻海(2317)</t>
-        </is>
-      </c>
-      <c r="E251" s="14" t="n">
-        <v>130</v>
-      </c>
-      <c r="F251" s="14" t="n">
-        <v>329</v>
-      </c>
-      <c r="G251" s="14" t="n">
-        <v>3255</v>
-      </c>
-      <c r="H251" s="14" t="n">
-        <v>8272</v>
-      </c>
-      <c r="I251" s="14" t="n">
-        <v>-5017</v>
-      </c>
-      <c r="J251" s="15" t="n">
-        <v>250.37</v>
-      </c>
-      <c r="K251" s="15" t="n">
-        <v>251.42</v>
-      </c>
-      <c r="L251" s="16">
-        <f>F251*(K251-J251)</f>
-        <v/>
-      </c>
+      <c r="D251" s="13" t="n"/>
+      <c r="E251" s="14" t="n"/>
+      <c r="F251" s="14" t="n"/>
+      <c r="G251" s="14" t="n"/>
+      <c r="H251" s="14" t="n"/>
+      <c r="I251" s="14" t="n"/>
+      <c r="J251" s="15" t="n"/>
+      <c r="K251" s="15" t="n"/>
+      <c r="L251" s="16" t="n"/>
     </row>
     <row r="252" ht="16.5" customHeight="1">
-      <c r="D252" s="13" t="inlineStr">
-        <is>
-          <t>台達電(2308)</t>
-        </is>
-      </c>
-      <c r="E252" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F252" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" s="14" t="n">
-        <v>2319</v>
-      </c>
-      <c r="H252" s="14" t="n">
-        <v>3769</v>
-      </c>
-      <c r="I252" s="14" t="n">
-        <v>-1450</v>
-      </c>
-      <c r="J252" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K252" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L252" s="16">
-        <f>F252*(K252-J252)</f>
-        <v/>
-      </c>
+      <c r="D252" s="13" t="n"/>
+      <c r="E252" s="14" t="n"/>
+      <c r="F252" s="14" t="n"/>
+      <c r="G252" s="14" t="n"/>
+      <c r="H252" s="14" t="n"/>
+      <c r="I252" s="14" t="n"/>
+      <c r="J252" s="15" t="n"/>
+      <c r="K252" s="15" t="n"/>
+      <c r="L252" s="16" t="n"/>
     </row>
     <row r="253" ht="16.5" customHeight="1">
-      <c r="D253" s="13" t="inlineStr">
-        <is>
-          <t>凌航(3135)</t>
-        </is>
-      </c>
-      <c r="E253" s="14" t="n">
-        <v>121</v>
-      </c>
-      <c r="F253" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G253" s="14" t="n">
-        <v>1992</v>
-      </c>
-      <c r="H253" s="14" t="n">
-        <v>35</v>
-      </c>
-      <c r="I253" s="14" t="n">
-        <v>1957</v>
-      </c>
-      <c r="J253" s="15" t="n">
-        <v>164.6</v>
-      </c>
-      <c r="K253" s="15" t="n">
-        <v>177</v>
-      </c>
-      <c r="L253" s="16">
-        <f>F253*(K253-J253)</f>
-        <v/>
-      </c>
+      <c r="D253" s="13" t="n"/>
+      <c r="E253" s="14" t="n"/>
+      <c r="F253" s="14" t="n"/>
+      <c r="G253" s="14" t="n"/>
+      <c r="H253" s="14" t="n"/>
+      <c r="I253" s="14" t="n"/>
+      <c r="J253" s="15" t="n"/>
+      <c r="K253" s="15" t="n"/>
+      <c r="L253" s="16" t="n"/>
     </row>
     <row r="254" ht="16.5" customHeight="1">
       <c r="B254" s="12" t="inlineStr">
@@ -9608,29 +9524,29 @@
       </c>
       <c r="D255" s="13" t="inlineStr">
         <is>
-          <t>奇鋐(3017)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E255" s="14" t="n">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="F255" s="14" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G255" s="14" t="n">
-        <v>88499</v>
+        <v>20788</v>
       </c>
       <c r="H255" s="14" t="n">
-        <v>4655</v>
+        <v>4492</v>
       </c>
       <c r="I255" s="14" t="n">
-        <v>83844</v>
+        <v>16296</v>
       </c>
       <c r="J255" s="15" t="n">
-        <v>2444.73</v>
+        <v>0</v>
       </c>
       <c r="K255" s="15" t="n">
-        <v>2450</v>
+        <v>0</v>
       </c>
       <c r="L255" s="16">
         <f>F255*(K255-J255)</f>
@@ -9640,31 +9556,31 @@
     <row r="256" ht="16.5" customHeight="1">
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>國巨*(2327)</t>
+          <t>藥華藥(6446)</t>
         </is>
       </c>
       <c r="E256" s="14" t="n">
-        <v>2002</v>
+        <v>0</v>
       </c>
       <c r="F256" s="14" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="G256" s="14" t="n">
-        <v>78307</v>
+        <v>16507</v>
       </c>
       <c r="H256" s="14" t="n">
-        <v>11826</v>
+        <v>0</v>
       </c>
       <c r="I256" s="14" t="n">
-        <v>66481</v>
+        <v>16507</v>
       </c>
       <c r="J256" s="15" t="n">
-        <v>391.14</v>
+        <v>0</v>
       </c>
       <c r="K256" s="15" t="n">
-        <v>386.48</v>
-      </c>
-      <c r="L256" s="17">
+        <v>0</v>
+      </c>
+      <c r="L256" s="16">
         <f>F256*(K256-J256)</f>
         <v/>
       </c>
@@ -9672,29 +9588,29 @@
     <row r="257" ht="16.5" customHeight="1">
       <c r="D257" s="13" t="inlineStr">
         <is>
-          <t>台達電(2308)</t>
+          <t>譜瑞-KY(4966)</t>
         </is>
       </c>
       <c r="E257" s="14" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="F257" s="14" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G257" s="14" t="n">
-        <v>71681</v>
+        <v>13920</v>
       </c>
       <c r="H257" s="14" t="n">
-        <v>16586</v>
+        <v>5423</v>
       </c>
       <c r="I257" s="14" t="n">
-        <v>55095</v>
+        <v>8497</v>
       </c>
       <c r="J257" s="15" t="n">
-        <v>2205.56</v>
+        <v>0</v>
       </c>
       <c r="K257" s="15" t="n">
-        <v>2211.52</v>
+        <v>0</v>
       </c>
       <c r="L257" s="16">
         <f>F257*(K257-J257)</f>
@@ -9704,29 +9620,29 @@
     <row r="258" ht="16.5" customHeight="1">
       <c r="D258" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>禾伸堂(3026)</t>
         </is>
       </c>
       <c r="E258" s="14" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="F258" s="14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G258" s="14" t="n">
-        <v>70843</v>
+        <v>13906</v>
       </c>
       <c r="H258" s="14" t="n">
-        <v>77034</v>
+        <v>1968</v>
       </c>
       <c r="I258" s="14" t="n">
-        <v>-6191</v>
+        <v>11938</v>
       </c>
       <c r="J258" s="15" t="n">
-        <v>0</v>
+        <v>327.98</v>
       </c>
       <c r="K258" s="15" t="n">
-        <v>0</v>
+        <v>328.02</v>
       </c>
       <c r="L258" s="16">
         <f>F258*(K258-J258)</f>
@@ -9736,7 +9652,7 @@
     <row r="259" ht="16.5" customHeight="1">
       <c r="D259" s="13" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>瑞昱(2379)</t>
         </is>
       </c>
       <c r="E259" s="14" t="n">
@@ -9746,13 +9662,13 @@
         <v>0</v>
       </c>
       <c r="G259" s="14" t="n">
-        <v>53012</v>
+        <v>525</v>
       </c>
       <c r="H259" s="14" t="n">
-        <v>36856</v>
+        <v>14802</v>
       </c>
       <c r="I259" s="14" t="n">
-        <v>16156</v>
+        <v>-14277</v>
       </c>
       <c r="J259" s="15" t="n">
         <v>0</v>
@@ -9766,164 +9682,59 @@
       </c>
     </row>
     <row r="260" ht="16.5" customHeight="1">
-      <c r="D260" s="13" t="inlineStr">
-        <is>
-          <t>健策(3653)</t>
-        </is>
-      </c>
-      <c r="E260" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F260" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G260" s="14" t="n">
-        <v>46345</v>
-      </c>
-      <c r="H260" s="14" t="n">
-        <v>92411</v>
-      </c>
-      <c r="I260" s="14" t="n">
-        <v>-46066</v>
-      </c>
-      <c r="J260" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K260" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L260" s="16">
-        <f>F260*(K260-J260)</f>
-        <v/>
-      </c>
+      <c r="D260" s="13" t="n"/>
+      <c r="E260" s="14" t="n"/>
+      <c r="F260" s="14" t="n"/>
+      <c r="G260" s="14" t="n"/>
+      <c r="H260" s="14" t="n"/>
+      <c r="I260" s="14" t="n"/>
+      <c r="J260" s="15" t="n"/>
+      <c r="K260" s="15" t="n"/>
+      <c r="L260" s="16" t="n"/>
     </row>
     <row r="261" ht="16.5" customHeight="1">
-      <c r="D261" s="13" t="inlineStr">
-        <is>
-          <t>旺矽(6223)</t>
-        </is>
-      </c>
-      <c r="E261" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F261" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G261" s="14" t="n">
-        <v>34010</v>
-      </c>
-      <c r="H261" s="14" t="n">
-        <v>1033</v>
-      </c>
-      <c r="I261" s="14" t="n">
-        <v>32977</v>
-      </c>
-      <c r="J261" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K261" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L261" s="16">
-        <f>F261*(K261-J261)</f>
-        <v/>
-      </c>
+      <c r="D261" s="13" t="n"/>
+      <c r="E261" s="14" t="n"/>
+      <c r="F261" s="14" t="n"/>
+      <c r="G261" s="14" t="n"/>
+      <c r="H261" s="14" t="n"/>
+      <c r="I261" s="14" t="n"/>
+      <c r="J261" s="15" t="n"/>
+      <c r="K261" s="15" t="n"/>
+      <c r="L261" s="16" t="n"/>
     </row>
     <row r="262" ht="16.5" customHeight="1">
-      <c r="D262" s="13" t="inlineStr">
-        <is>
-          <t>國泰20年美債(00687B)</t>
-        </is>
-      </c>
-      <c r="E262" s="14" t="n">
-        <v>10384</v>
-      </c>
-      <c r="F262" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" s="14" t="n">
-        <v>28856</v>
-      </c>
-      <c r="H262" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I262" s="14" t="n">
-        <v>28856</v>
-      </c>
-      <c r="J262" s="15" t="n">
-        <v>27.79</v>
-      </c>
-      <c r="K262" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L262" s="16">
-        <f>F262*(K262-J262)</f>
-        <v/>
-      </c>
+      <c r="D262" s="13" t="n"/>
+      <c r="E262" s="14" t="n"/>
+      <c r="F262" s="14" t="n"/>
+      <c r="G262" s="14" t="n"/>
+      <c r="H262" s="14" t="n"/>
+      <c r="I262" s="14" t="n"/>
+      <c r="J262" s="15" t="n"/>
+      <c r="K262" s="15" t="n"/>
+      <c r="L262" s="16" t="n"/>
     </row>
     <row r="263" ht="16.5" customHeight="1">
-      <c r="D263" s="13" t="inlineStr">
-        <is>
-          <t>金像電(2368)</t>
-        </is>
-      </c>
-      <c r="E263" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F263" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G263" s="14" t="n">
-        <v>27565</v>
-      </c>
-      <c r="H263" s="14" t="n">
-        <v>17028</v>
-      </c>
-      <c r="I263" s="14" t="n">
-        <v>10537</v>
-      </c>
-      <c r="J263" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K263" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L263" s="16">
-        <f>F263*(K263-J263)</f>
-        <v/>
-      </c>
+      <c r="D263" s="13" t="n"/>
+      <c r="E263" s="14" t="n"/>
+      <c r="F263" s="14" t="n"/>
+      <c r="G263" s="14" t="n"/>
+      <c r="H263" s="14" t="n"/>
+      <c r="I263" s="14" t="n"/>
+      <c r="J263" s="15" t="n"/>
+      <c r="K263" s="15" t="n"/>
+      <c r="L263" s="16" t="n"/>
     </row>
     <row r="264" ht="16.5" customHeight="1">
-      <c r="D264" s="13" t="inlineStr">
-        <is>
-          <t>緯穎(6669)</t>
-        </is>
-      </c>
-      <c r="E264" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F264" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G264" s="14" t="n">
-        <v>24978</v>
-      </c>
-      <c r="H264" s="14" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I264" s="14" t="n">
-        <v>21378</v>
-      </c>
-      <c r="J264" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K264" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L264" s="16">
-        <f>F264*(K264-J264)</f>
-        <v/>
-      </c>
+      <c r="D264" s="13" t="n"/>
+      <c r="E264" s="14" t="n"/>
+      <c r="F264" s="14" t="n"/>
+      <c r="G264" s="14" t="n"/>
+      <c r="H264" s="14" t="n"/>
+      <c r="I264" s="14" t="n"/>
+      <c r="J264" s="15" t="n"/>
+      <c r="K264" s="15" t="n"/>
+      <c r="L264" s="16" t="n"/>
     </row>
     <row r="265" ht="16.5" customHeight="1">
       <c r="B265" s="12" t="inlineStr">
@@ -9995,31 +9806,31 @@
       </c>
       <c r="D266" s="13" t="inlineStr">
         <is>
-          <t>日月光投控(3711)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E266" s="14" t="n">
-        <v>3591</v>
+        <v>651</v>
       </c>
       <c r="F266" s="14" t="n">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="G266" s="14" t="n">
-        <v>187294</v>
+        <v>91466</v>
       </c>
       <c r="H266" s="14" t="n">
-        <v>7086</v>
+        <v>30812</v>
       </c>
       <c r="I266" s="14" t="n">
-        <v>180208</v>
+        <v>60654</v>
       </c>
       <c r="J266" s="15" t="n">
-        <v>521.5599999999999</v>
+        <v>1405.01</v>
       </c>
       <c r="K266" s="15" t="n">
-        <v>521.01</v>
-      </c>
-      <c r="L266" s="17">
+        <v>1413.39</v>
+      </c>
+      <c r="L266" s="16">
         <f>F266*(K266-J266)</f>
         <v/>
       </c>
@@ -10027,29 +9838,29 @@
     <row r="267" ht="16.5" customHeight="1">
       <c r="D267" s="13" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>禾伸堂(3026)</t>
         </is>
       </c>
       <c r="E267" s="14" t="n">
-        <v>678</v>
+        <v>2469</v>
       </c>
       <c r="F267" s="14" t="n">
-        <v>135</v>
+        <v>1271</v>
       </c>
       <c r="G267" s="14" t="n">
-        <v>163707</v>
+        <v>81401</v>
       </c>
       <c r="H267" s="14" t="n">
-        <v>32083</v>
+        <v>41516</v>
       </c>
       <c r="I267" s="14" t="n">
-        <v>131624</v>
+        <v>39885</v>
       </c>
       <c r="J267" s="15" t="n">
-        <v>2414.56</v>
+        <v>329.69</v>
       </c>
       <c r="K267" s="15" t="n">
-        <v>2376.54</v>
+        <v>326.64</v>
       </c>
       <c r="L267" s="17">
         <f>F267*(K267-J267)</f>
@@ -10059,31 +9870,31 @@
     <row r="268" ht="16.5" customHeight="1">
       <c r="D268" s="13" t="inlineStr">
         <is>
-          <t>勤誠(8210)</t>
+          <t>聯詠(3034)</t>
         </is>
       </c>
       <c r="E268" s="14" t="n">
-        <v>651</v>
+        <v>1567</v>
       </c>
       <c r="F268" s="14" t="n">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="G268" s="14" t="n">
-        <v>91466</v>
+        <v>77938</v>
       </c>
       <c r="H268" s="14" t="n">
-        <v>30812</v>
+        <v>8404</v>
       </c>
       <c r="I268" s="14" t="n">
-        <v>60654</v>
+        <v>69534</v>
       </c>
       <c r="J268" s="15" t="n">
-        <v>1405.01</v>
+        <v>497.37</v>
       </c>
       <c r="K268" s="15" t="n">
-        <v>1413.39</v>
-      </c>
-      <c r="L268" s="16">
+        <v>488.59</v>
+      </c>
+      <c r="L268" s="17">
         <f>F268*(K268-J268)</f>
         <v/>
       </c>
@@ -10091,29 +9902,29 @@
     <row r="269" ht="16.5" customHeight="1">
       <c r="D269" s="13" t="inlineStr">
         <is>
-          <t>華通(2313)</t>
+          <t>順德(2351)</t>
         </is>
       </c>
       <c r="E269" s="14" t="n">
-        <v>3310</v>
+        <v>3538</v>
       </c>
       <c r="F269" s="14" t="n">
-        <v>223</v>
+        <v>605</v>
       </c>
       <c r="G269" s="14" t="n">
-        <v>83245</v>
+        <v>64704</v>
       </c>
       <c r="H269" s="14" t="n">
-        <v>5570</v>
+        <v>10895</v>
       </c>
       <c r="I269" s="14" t="n">
-        <v>77675</v>
+        <v>53809</v>
       </c>
       <c r="J269" s="15" t="n">
-        <v>251.49</v>
+        <v>182.88</v>
       </c>
       <c r="K269" s="15" t="n">
-        <v>249.76</v>
+        <v>180.08</v>
       </c>
       <c r="L269" s="17">
         <f>F269*(K269-J269)</f>
@@ -10123,29 +9934,29 @@
     <row r="270" ht="16.5" customHeight="1">
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>禾伸堂(3026)</t>
+          <t>瑞昱(2379)</t>
         </is>
       </c>
       <c r="E270" s="14" t="n">
-        <v>2469</v>
+        <v>1071</v>
       </c>
       <c r="F270" s="14" t="n">
-        <v>1271</v>
+        <v>183</v>
       </c>
       <c r="G270" s="14" t="n">
-        <v>81401</v>
+        <v>63286</v>
       </c>
       <c r="H270" s="14" t="n">
-        <v>41516</v>
+        <v>10759</v>
       </c>
       <c r="I270" s="14" t="n">
-        <v>39885</v>
+        <v>52527</v>
       </c>
       <c r="J270" s="15" t="n">
-        <v>329.69</v>
+        <v>590.91</v>
       </c>
       <c r="K270" s="15" t="n">
-        <v>326.64</v>
+        <v>587.9299999999999</v>
       </c>
       <c r="L270" s="17">
         <f>F270*(K270-J270)</f>
@@ -10155,31 +9966,31 @@
     <row r="271" ht="16.5" customHeight="1">
       <c r="D271" s="13" t="inlineStr">
         <is>
-          <t>致茂(2360)</t>
+          <t>台表科(6278)</t>
         </is>
       </c>
       <c r="E271" s="14" t="n">
-        <v>0</v>
+        <v>2172</v>
       </c>
       <c r="F271" s="14" t="n">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="G271" s="14" t="n">
-        <v>79890</v>
+        <v>43595</v>
       </c>
       <c r="H271" s="14" t="n">
-        <v>7982</v>
+        <v>18953</v>
       </c>
       <c r="I271" s="14" t="n">
-        <v>71908</v>
+        <v>24642</v>
       </c>
       <c r="J271" s="15" t="n">
-        <v>0</v>
+        <v>200.72</v>
       </c>
       <c r="K271" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L271" s="16">
+        <v>189.34</v>
+      </c>
+      <c r="L271" s="17">
         <f>F271*(K271-J271)</f>
         <v/>
       </c>
@@ -10187,29 +9998,29 @@
     <row r="272" ht="16.5" customHeight="1">
       <c r="D272" s="13" t="inlineStr">
         <is>
-          <t>聯詠(3034)</t>
+          <t>盟立(2464)</t>
         </is>
       </c>
       <c r="E272" s="14" t="n">
-        <v>1567</v>
+        <v>3380</v>
       </c>
       <c r="F272" s="14" t="n">
-        <v>172</v>
+        <v>2851</v>
       </c>
       <c r="G272" s="14" t="n">
-        <v>77938</v>
+        <v>41015</v>
       </c>
       <c r="H272" s="14" t="n">
-        <v>8404</v>
+        <v>33680</v>
       </c>
       <c r="I272" s="14" t="n">
-        <v>69534</v>
+        <v>7335</v>
       </c>
       <c r="J272" s="15" t="n">
-        <v>497.37</v>
+        <v>121.35</v>
       </c>
       <c r="K272" s="15" t="n">
-        <v>488.59</v>
+        <v>118.13</v>
       </c>
       <c r="L272" s="17">
         <f>F272*(K272-J272)</f>
@@ -10219,31 +10030,31 @@
     <row r="273" ht="16.5" customHeight="1">
       <c r="D273" s="13" t="inlineStr">
         <is>
-          <t>順德(2351)</t>
+          <t>川湖(2059)</t>
         </is>
       </c>
       <c r="E273" s="14" t="n">
-        <v>3538</v>
+        <v>0</v>
       </c>
       <c r="F273" s="14" t="n">
-        <v>605</v>
+        <v>0</v>
       </c>
       <c r="G273" s="14" t="n">
-        <v>64704</v>
+        <v>35696</v>
       </c>
       <c r="H273" s="14" t="n">
-        <v>10895</v>
+        <v>70242</v>
       </c>
       <c r="I273" s="14" t="n">
-        <v>53809</v>
+        <v>-34546</v>
       </c>
       <c r="J273" s="15" t="n">
-        <v>182.88</v>
+        <v>0</v>
       </c>
       <c r="K273" s="15" t="n">
-        <v>180.08</v>
-      </c>
-      <c r="L273" s="17">
+        <v>0</v>
+      </c>
+      <c r="L273" s="16">
         <f>F273*(K273-J273)</f>
         <v/>
       </c>
@@ -10251,31 +10062,31 @@
     <row r="274" ht="16.5" customHeight="1">
       <c r="D274" s="13" t="inlineStr">
         <is>
-          <t>緯穎(6669)</t>
+          <t>立隆電(2472)</t>
         </is>
       </c>
       <c r="E274" s="14" t="n">
-        <v>0</v>
+        <v>1121</v>
       </c>
       <c r="F274" s="14" t="n">
-        <v>0</v>
+        <v>546</v>
       </c>
       <c r="G274" s="14" t="n">
-        <v>64420</v>
+        <v>24752</v>
       </c>
       <c r="H274" s="14" t="n">
-        <v>50030</v>
+        <v>11632</v>
       </c>
       <c r="I274" s="14" t="n">
-        <v>14390</v>
+        <v>13120</v>
       </c>
       <c r="J274" s="15" t="n">
-        <v>0</v>
+        <v>220.81</v>
       </c>
       <c r="K274" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L274" s="16">
+        <v>213.04</v>
+      </c>
+      <c r="L274" s="17">
         <f>F274*(K274-J274)</f>
         <v/>
       </c>
@@ -10283,31 +10094,31 @@
     <row r="275" ht="16.5" customHeight="1">
       <c r="D275" s="13" t="inlineStr">
         <is>
-          <t>瑞昱(2379)</t>
+          <t>新應材(4749)</t>
         </is>
       </c>
       <c r="E275" s="14" t="n">
-        <v>1071</v>
+        <v>0</v>
       </c>
       <c r="F275" s="14" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="G275" s="14" t="n">
-        <v>63286</v>
+        <v>22393</v>
       </c>
       <c r="H275" s="14" t="n">
-        <v>10759</v>
+        <v>2043</v>
       </c>
       <c r="I275" s="14" t="n">
-        <v>52527</v>
+        <v>20350</v>
       </c>
       <c r="J275" s="15" t="n">
-        <v>590.91</v>
+        <v>0</v>
       </c>
       <c r="K275" s="15" t="n">
-        <v>587.9299999999999</v>
-      </c>
-      <c r="L275" s="17">
+        <v>0</v>
+      </c>
+      <c r="L275" s="16">
         <f>F275*(K275-J275)</f>
         <v/>
       </c>
@@ -13508,29 +13319,29 @@
       </c>
       <c r="D365" s="13" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>川湖(2059)</t>
         </is>
       </c>
       <c r="E365" s="14" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="F365" s="14" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="G365" s="14" t="n">
-        <v>6120</v>
+        <v>5320</v>
       </c>
       <c r="H365" s="14" t="n">
-        <v>3414</v>
+        <v>10589</v>
       </c>
       <c r="I365" s="14" t="n">
-        <v>2706</v>
+        <v>-5269</v>
       </c>
       <c r="J365" s="15" t="n">
-        <v>276.93</v>
+        <v>0</v>
       </c>
       <c r="K365" s="15" t="n">
-        <v>279.8</v>
+        <v>0</v>
       </c>
       <c r="L365" s="16">
         <f>F365*(K365-J365)</f>
@@ -13540,7 +13351,7 @@
     <row r="366" ht="16.5" customHeight="1">
       <c r="D366" s="13" t="inlineStr">
         <is>
-          <t>川湖(2059)</t>
+          <t>新應材(4749)</t>
         </is>
       </c>
       <c r="E366" s="14" t="n">
@@ -13550,13 +13361,13 @@
         <v>0</v>
       </c>
       <c r="G366" s="14" t="n">
-        <v>5320</v>
+        <v>4001</v>
       </c>
       <c r="H366" s="14" t="n">
-        <v>10589</v>
+        <v>1244</v>
       </c>
       <c r="I366" s="14" t="n">
-        <v>-5269</v>
+        <v>2757</v>
       </c>
       <c r="J366" s="15" t="n">
         <v>0</v>
@@ -13572,31 +13383,31 @@
     <row r="367" ht="16.5" customHeight="1">
       <c r="D367" s="13" t="inlineStr">
         <is>
-          <t>鴻海(2317)</t>
+          <t>文曄(3036)</t>
         </is>
       </c>
       <c r="E367" s="14" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="F367" s="14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G367" s="14" t="n">
-        <v>4331</v>
+        <v>3992</v>
       </c>
       <c r="H367" s="14" t="n">
-        <v>4936</v>
+        <v>568</v>
       </c>
       <c r="I367" s="14" t="n">
-        <v>-605</v>
+        <v>3424</v>
       </c>
       <c r="J367" s="15" t="n">
-        <v>0</v>
+        <v>240.5</v>
       </c>
       <c r="K367" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L367" s="16">
+        <v>236.58</v>
+      </c>
+      <c r="L367" s="17">
         <f>F367*(K367-J367)</f>
         <v/>
       </c>
@@ -13604,31 +13415,31 @@
     <row r="368" ht="16.5" customHeight="1">
       <c r="D368" s="13" t="inlineStr">
         <is>
-          <t>新應材(4749)</t>
+          <t>驊訊(6237)</t>
         </is>
       </c>
       <c r="E368" s="14" t="n">
-        <v>0</v>
+        <v>522</v>
       </c>
       <c r="F368" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G368" s="14" t="n">
-        <v>4001</v>
+        <v>2278</v>
       </c>
       <c r="H368" s="14" t="n">
-        <v>1244</v>
+        <v>9</v>
       </c>
       <c r="I368" s="14" t="n">
-        <v>2757</v>
+        <v>2269</v>
       </c>
       <c r="J368" s="15" t="n">
-        <v>0</v>
+        <v>43.65</v>
       </c>
       <c r="K368" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L368" s="16">
+        <v>43.5</v>
+      </c>
+      <c r="L368" s="17">
         <f>F368*(K368-J368)</f>
         <v/>
       </c>
@@ -13636,7 +13447,7 @@
     <row r="369" ht="16.5" customHeight="1">
       <c r="D369" s="13" t="inlineStr">
         <is>
-          <t>AES-KY(6781)</t>
+          <t>瑞昱(2379)</t>
         </is>
       </c>
       <c r="E369" s="14" t="n">
@@ -13646,13 +13457,13 @@
         <v>0</v>
       </c>
       <c r="G369" s="14" t="n">
-        <v>4001</v>
+        <v>1942</v>
       </c>
       <c r="H369" s="14" t="n">
-        <v>1153</v>
+        <v>1224</v>
       </c>
       <c r="I369" s="14" t="n">
-        <v>2848</v>
+        <v>718</v>
       </c>
       <c r="J369" s="15" t="n">
         <v>0</v>
@@ -13668,29 +13479,29 @@
     <row r="370" ht="16.5" customHeight="1">
       <c r="D370" s="13" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>盟立(2464)</t>
         </is>
       </c>
       <c r="E370" s="14" t="n">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="F370" s="14" t="n">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="G370" s="14" t="n">
-        <v>3992</v>
+        <v>1778</v>
       </c>
       <c r="H370" s="14" t="n">
-        <v>568</v>
+        <v>1271</v>
       </c>
       <c r="I370" s="14" t="n">
-        <v>3424</v>
+        <v>507</v>
       </c>
       <c r="J370" s="15" t="n">
-        <v>240.5</v>
+        <v>120.97</v>
       </c>
       <c r="K370" s="15" t="n">
-        <v>236.58</v>
+        <v>119.91</v>
       </c>
       <c r="L370" s="17">
         <f>F370*(K370-J370)</f>
@@ -13700,7 +13511,7 @@
     <row r="371" ht="16.5" customHeight="1">
       <c r="D371" s="13" t="inlineStr">
         <is>
-          <t>環球晶(6488)</t>
+          <t>精材(3374)</t>
         </is>
       </c>
       <c r="E371" s="14" t="n">
@@ -13710,13 +13521,13 @@
         <v>0</v>
       </c>
       <c r="G371" s="14" t="n">
-        <v>3353</v>
+        <v>1558</v>
       </c>
       <c r="H371" s="14" t="n">
-        <v>2398</v>
+        <v>2036</v>
       </c>
       <c r="I371" s="14" t="n">
-        <v>955</v>
+        <v>-478</v>
       </c>
       <c r="J371" s="15" t="n">
         <v>0</v>
@@ -13732,31 +13543,31 @@
     <row r="372" ht="16.5" customHeight="1">
       <c r="D372" s="13" t="inlineStr">
         <is>
-          <t>主動統一台股增長(00981A)</t>
+          <t>鈺鎧(5228)</t>
         </is>
       </c>
       <c r="E372" s="14" t="n">
-        <v>1145</v>
+        <v>292</v>
       </c>
       <c r="F372" s="14" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="G372" s="14" t="n">
-        <v>3338</v>
+        <v>1166</v>
       </c>
       <c r="H372" s="14" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="I372" s="14" t="n">
-        <v>2768</v>
+        <v>1166</v>
       </c>
       <c r="J372" s="15" t="n">
-        <v>29.16</v>
+        <v>39.95</v>
       </c>
       <c r="K372" s="15" t="n">
-        <v>28.94</v>
-      </c>
-      <c r="L372" s="17">
+        <v>0</v>
+      </c>
+      <c r="L372" s="16">
         <f>F372*(K372-J372)</f>
         <v/>
       </c>
@@ -13764,31 +13575,31 @@
     <row r="373" ht="16.5" customHeight="1">
       <c r="D373" s="13" t="inlineStr">
         <is>
-          <t>啟��(6285)</t>
+          <t>普萊德(6263)</t>
         </is>
       </c>
       <c r="E373" s="14" t="n">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="F373" s="14" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G373" s="14" t="n">
-        <v>3264</v>
+        <v>1130</v>
       </c>
       <c r="H373" s="14" t="n">
-        <v>876</v>
+        <v>53</v>
       </c>
       <c r="I373" s="14" t="n">
-        <v>2388</v>
+        <v>1077</v>
       </c>
       <c r="J373" s="15" t="n">
-        <v>261.1</v>
+        <v>152.7</v>
       </c>
       <c r="K373" s="15" t="n">
-        <v>257.56</v>
-      </c>
-      <c r="L373" s="17">
+        <v>175.67</v>
+      </c>
+      <c r="L373" s="16">
         <f>F373*(K373-J373)</f>
         <v/>
       </c>
@@ -13796,26 +13607,26 @@
     <row r="374" ht="16.5" customHeight="1">
       <c r="D374" s="13" t="inlineStr">
         <is>
-          <t>金居(8358)</t>
+          <t>現觀科(6906)</t>
         </is>
       </c>
       <c r="E374" s="14" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F374" s="14" t="n">
         <v>0</v>
       </c>
       <c r="G374" s="14" t="n">
-        <v>2753</v>
+        <v>501</v>
       </c>
       <c r="H374" s="14" t="n">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="I374" s="14" t="n">
-        <v>1572</v>
+        <v>501</v>
       </c>
       <c r="J374" s="15" t="n">
-        <v>0</v>
+        <v>67.7</v>
       </c>
       <c r="K374" s="15" t="n">
         <v>0</v>
@@ -13905,31 +13716,31 @@
       </c>
       <c r="D376" s="13" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>順德(2351)</t>
         </is>
       </c>
       <c r="E376" s="14" t="n">
-        <v>403</v>
+        <v>242</v>
       </c>
       <c r="F376" s="14" t="n">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="G376" s="14" t="n">
-        <v>11003</v>
+        <v>4340</v>
       </c>
       <c r="H376" s="14" t="n">
-        <v>2440</v>
+        <v>370</v>
       </c>
       <c r="I376" s="14" t="n">
-        <v>8563</v>
+        <v>3970</v>
       </c>
       <c r="J376" s="15" t="n">
-        <v>273.04</v>
+        <v>179.36</v>
       </c>
       <c r="K376" s="15" t="n">
-        <v>277.28</v>
-      </c>
-      <c r="L376" s="16">
+        <v>175.95</v>
+      </c>
+      <c r="L376" s="17">
         <f>F376*(K376-J376)</f>
         <v/>
       </c>
@@ -13937,31 +13748,31 @@
     <row r="377" ht="16.5" customHeight="1">
       <c r="D377" s="13" t="inlineStr">
         <is>
-          <t>金居(8358)</t>
+          <t>信昌電(6173)</t>
         </is>
       </c>
       <c r="E377" s="14" t="n">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F377" s="14" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="G377" s="14" t="n">
-        <v>9796</v>
+        <v>2440</v>
       </c>
       <c r="H377" s="14" t="n">
-        <v>4385</v>
+        <v>13</v>
       </c>
       <c r="I377" s="14" t="n">
-        <v>5411</v>
+        <v>2427</v>
       </c>
       <c r="J377" s="15" t="n">
-        <v>473.25</v>
+        <v>122</v>
       </c>
       <c r="K377" s="15" t="n">
-        <v>471.51</v>
-      </c>
-      <c r="L377" s="17">
+        <v>132</v>
+      </c>
+      <c r="L377" s="16">
         <f>F377*(K377-J377)</f>
         <v/>
       </c>
@@ -13969,7 +13780,7 @@
     <row r="378" ht="16.5" customHeight="1">
       <c r="D378" s="13" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E378" s="14" t="n">
@@ -13979,13 +13790,13 @@
         <v>0</v>
       </c>
       <c r="G378" s="14" t="n">
-        <v>9450</v>
+        <v>833</v>
       </c>
       <c r="H378" s="14" t="n">
-        <v>1669</v>
+        <v>1530</v>
       </c>
       <c r="I378" s="14" t="n">
-        <v>7781</v>
+        <v>-697</v>
       </c>
       <c r="J378" s="15" t="n">
         <v>0</v>
@@ -14001,31 +13812,31 @@
     <row r="379" ht="16.5" customHeight="1">
       <c r="D379" s="13" t="inlineStr">
         <is>
-          <t>南茂(8150)</t>
+          <t>聯詠(3034)</t>
         </is>
       </c>
       <c r="E379" s="14" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="F379" s="14" t="n">
-        <v>664</v>
+        <v>0</v>
       </c>
       <c r="G379" s="14" t="n">
-        <v>4858</v>
+        <v>0</v>
       </c>
       <c r="H379" s="14" t="n">
-        <v>5935</v>
+        <v>892</v>
       </c>
       <c r="I379" s="14" t="n">
-        <v>-1077</v>
+        <v>-892</v>
       </c>
       <c r="J379" s="15" t="n">
-        <v>96.95999999999999</v>
+        <v>0</v>
       </c>
       <c r="K379" s="15" t="n">
-        <v>89.38</v>
-      </c>
-      <c r="L379" s="17">
+        <v>0</v>
+      </c>
+      <c r="L379" s="16">
         <f>F379*(K379-J379)</f>
         <v/>
       </c>
@@ -14033,29 +13844,29 @@
     <row r="380" ht="16.5" customHeight="1">
       <c r="D380" s="13" t="inlineStr">
         <is>
-          <t>采鈺(6789)</t>
+          <t>全友(2305)</t>
         </is>
       </c>
       <c r="E380" s="14" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F380" s="14" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="G380" s="14" t="n">
-        <v>4508</v>
+        <v>0</v>
       </c>
       <c r="H380" s="14" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="I380" s="14" t="n">
-        <v>4366</v>
+        <v>0</v>
       </c>
       <c r="J380" s="15" t="n">
-        <v>601.09</v>
+        <v>0</v>
       </c>
       <c r="K380" s="15" t="n">
-        <v>710.5</v>
+        <v>0</v>
       </c>
       <c r="L380" s="16">
         <f>F380*(K380-J380)</f>
@@ -14063,164 +13874,59 @@
       </c>
     </row>
     <row r="381" ht="16.5" customHeight="1">
-      <c r="D381" s="13" t="inlineStr">
-        <is>
-          <t>順德(2351)</t>
-        </is>
-      </c>
-      <c r="E381" s="14" t="n">
-        <v>242</v>
-      </c>
-      <c r="F381" s="14" t="n">
-        <v>21</v>
-      </c>
-      <c r="G381" s="14" t="n">
-        <v>4340</v>
-      </c>
-      <c r="H381" s="14" t="n">
-        <v>370</v>
-      </c>
-      <c r="I381" s="14" t="n">
-        <v>3970</v>
-      </c>
-      <c r="J381" s="15" t="n">
-        <v>179.36</v>
-      </c>
-      <c r="K381" s="15" t="n">
-        <v>175.95</v>
-      </c>
-      <c r="L381" s="17">
-        <f>F381*(K381-J381)</f>
-        <v/>
-      </c>
+      <c r="D381" s="13" t="n"/>
+      <c r="E381" s="14" t="n"/>
+      <c r="F381" s="14" t="n"/>
+      <c r="G381" s="14" t="n"/>
+      <c r="H381" s="14" t="n"/>
+      <c r="I381" s="14" t="n"/>
+      <c r="J381" s="15" t="n"/>
+      <c r="K381" s="15" t="n"/>
+      <c r="L381" s="16" t="n"/>
     </row>
     <row r="382" ht="16.5" customHeight="1">
-      <c r="D382" s="13" t="inlineStr">
-        <is>
-          <t>頎邦(6147)</t>
-        </is>
-      </c>
-      <c r="E382" s="14" t="n">
-        <v>233</v>
-      </c>
-      <c r="F382" s="14" t="n">
-        <v>114</v>
-      </c>
-      <c r="G382" s="14" t="n">
-        <v>4307</v>
-      </c>
-      <c r="H382" s="14" t="n">
-        <v>2225</v>
-      </c>
-      <c r="I382" s="14" t="n">
-        <v>2082</v>
-      </c>
-      <c r="J382" s="15" t="n">
-        <v>184.85</v>
-      </c>
-      <c r="K382" s="15" t="n">
-        <v>195.21</v>
-      </c>
-      <c r="L382" s="16">
-        <f>F382*(K382-J382)</f>
-        <v/>
-      </c>
+      <c r="D382" s="13" t="n"/>
+      <c r="E382" s="14" t="n"/>
+      <c r="F382" s="14" t="n"/>
+      <c r="G382" s="14" t="n"/>
+      <c r="H382" s="14" t="n"/>
+      <c r="I382" s="14" t="n"/>
+      <c r="J382" s="15" t="n"/>
+      <c r="K382" s="15" t="n"/>
+      <c r="L382" s="16" t="n"/>
     </row>
     <row r="383" ht="16.5" customHeight="1">
-      <c r="D383" s="13" t="inlineStr">
-        <is>
-          <t>蔚華科(3055)</t>
-        </is>
-      </c>
-      <c r="E383" s="14" t="n">
-        <v>447</v>
-      </c>
-      <c r="F383" s="14" t="n">
-        <v>197</v>
-      </c>
-      <c r="G383" s="14" t="n">
-        <v>3953</v>
-      </c>
-      <c r="H383" s="14" t="n">
-        <v>1757</v>
-      </c>
-      <c r="I383" s="14" t="n">
-        <v>2196</v>
-      </c>
-      <c r="J383" s="15" t="n">
-        <v>88.44</v>
-      </c>
-      <c r="K383" s="15" t="n">
-        <v>89.17</v>
-      </c>
-      <c r="L383" s="16">
-        <f>F383*(K383-J383)</f>
-        <v/>
-      </c>
+      <c r="D383" s="13" t="n"/>
+      <c r="E383" s="14" t="n"/>
+      <c r="F383" s="14" t="n"/>
+      <c r="G383" s="14" t="n"/>
+      <c r="H383" s="14" t="n"/>
+      <c r="I383" s="14" t="n"/>
+      <c r="J383" s="15" t="n"/>
+      <c r="K383" s="15" t="n"/>
+      <c r="L383" s="16" t="n"/>
     </row>
     <row r="384" ht="16.5" customHeight="1">
-      <c r="D384" s="13" t="inlineStr">
-        <is>
-          <t>聯電(2303)</t>
-        </is>
-      </c>
-      <c r="E384" s="14" t="n">
-        <v>405</v>
-      </c>
-      <c r="F384" s="14" t="n">
-        <v>257</v>
-      </c>
-      <c r="G384" s="14" t="n">
-        <v>3801</v>
-      </c>
-      <c r="H384" s="14" t="n">
-        <v>2449</v>
-      </c>
-      <c r="I384" s="14" t="n">
-        <v>1352</v>
-      </c>
-      <c r="J384" s="15" t="n">
-        <v>93.84999999999999</v>
-      </c>
-      <c r="K384" s="15" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="L384" s="16">
-        <f>F384*(K384-J384)</f>
-        <v/>
-      </c>
+      <c r="D384" s="13" t="n"/>
+      <c r="E384" s="14" t="n"/>
+      <c r="F384" s="14" t="n"/>
+      <c r="G384" s="14" t="n"/>
+      <c r="H384" s="14" t="n"/>
+      <c r="I384" s="14" t="n"/>
+      <c r="J384" s="15" t="n"/>
+      <c r="K384" s="15" t="n"/>
+      <c r="L384" s="16" t="n"/>
     </row>
     <row r="385" ht="16.5" customHeight="1">
-      <c r="D385" s="13" t="inlineStr">
-        <is>
-          <t>啟��(6285)</t>
-        </is>
-      </c>
-      <c r="E385" s="14" t="n">
-        <v>134</v>
-      </c>
-      <c r="F385" s="14" t="n">
-        <v>280</v>
-      </c>
-      <c r="G385" s="14" t="n">
-        <v>3441</v>
-      </c>
-      <c r="H385" s="14" t="n">
-        <v>7012</v>
-      </c>
-      <c r="I385" s="14" t="n">
-        <v>-3571</v>
-      </c>
-      <c r="J385" s="15" t="n">
-        <v>256.79</v>
-      </c>
-      <c r="K385" s="15" t="n">
-        <v>250.41</v>
-      </c>
-      <c r="L385" s="17">
-        <f>F385*(K385-J385)</f>
-        <v/>
-      </c>
+      <c r="D385" s="13" t="n"/>
+      <c r="E385" s="14" t="n"/>
+      <c r="F385" s="14" t="n"/>
+      <c r="G385" s="14" t="n"/>
+      <c r="H385" s="14" t="n"/>
+      <c r="I385" s="14" t="n"/>
+      <c r="J385" s="15" t="n"/>
+      <c r="K385" s="15" t="n"/>
+      <c r="L385" s="16" t="n"/>
     </row>
     <row r="386" ht="16.5" customHeight="1">
       <c r="B386" s="12" t="inlineStr">
@@ -14292,29 +13998,29 @@
       </c>
       <c r="D387" s="13" t="inlineStr">
         <is>
-          <t>華邦電(2344)</t>
+          <t>盟立(2464)</t>
         </is>
       </c>
       <c r="E387" s="14" t="n">
-        <v>1742</v>
+        <v>571</v>
       </c>
       <c r="F387" s="14" t="n">
-        <v>558</v>
+        <v>530</v>
       </c>
       <c r="G387" s="14" t="n">
-        <v>18858</v>
+        <v>6812</v>
       </c>
       <c r="H387" s="14" t="n">
-        <v>5988</v>
+        <v>6230</v>
       </c>
       <c r="I387" s="14" t="n">
-        <v>12870</v>
+        <v>582</v>
       </c>
       <c r="J387" s="15" t="n">
-        <v>108.26</v>
+        <v>119.3</v>
       </c>
       <c r="K387" s="15" t="n">
-        <v>107.32</v>
+        <v>117.54</v>
       </c>
       <c r="L387" s="17">
         <f>F387*(K387-J387)</f>
@@ -14324,7 +14030,7 @@
     <row r="388" ht="16.5" customHeight="1">
       <c r="D388" s="13" t="inlineStr">
         <is>
-          <t>健策(3653)</t>
+          <t>新應材(4749)</t>
         </is>
       </c>
       <c r="E388" s="14" t="n">
@@ -14334,13 +14040,13 @@
         <v>0</v>
       </c>
       <c r="G388" s="14" t="n">
-        <v>13612</v>
+        <v>2749</v>
       </c>
       <c r="H388" s="14" t="n">
-        <v>500</v>
+        <v>685</v>
       </c>
       <c r="I388" s="14" t="n">
-        <v>13112</v>
+        <v>2064</v>
       </c>
       <c r="J388" s="15" t="n">
         <v>0</v>
@@ -14356,7 +14062,7 @@
     <row r="389" ht="16.5" customHeight="1">
       <c r="D389" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>禾伸堂(3026)</t>
         </is>
       </c>
       <c r="E389" s="14" t="n">
@@ -14366,13 +14072,13 @@
         <v>0</v>
       </c>
       <c r="G389" s="14" t="n">
-        <v>8933</v>
+        <v>1495</v>
       </c>
       <c r="H389" s="14" t="n">
-        <v>2243</v>
+        <v>2740</v>
       </c>
       <c r="I389" s="14" t="n">
-        <v>6690</v>
+        <v>-1245</v>
       </c>
       <c r="J389" s="15" t="n">
         <v>0</v>
@@ -14388,31 +14094,31 @@
     <row r="390" ht="16.5" customHeight="1">
       <c r="D390" s="13" t="inlineStr">
         <is>
-          <t>盟立(2464)</t>
+          <t>台表科(6278)</t>
         </is>
       </c>
       <c r="E390" s="14" t="n">
-        <v>571</v>
+        <v>75</v>
       </c>
       <c r="F390" s="14" t="n">
-        <v>530</v>
+        <v>9</v>
       </c>
       <c r="G390" s="14" t="n">
-        <v>6812</v>
+        <v>1488</v>
       </c>
       <c r="H390" s="14" t="n">
-        <v>6230</v>
+        <v>180</v>
       </c>
       <c r="I390" s="14" t="n">
-        <v>582</v>
+        <v>1308</v>
       </c>
       <c r="J390" s="15" t="n">
-        <v>119.3</v>
+        <v>198.41</v>
       </c>
       <c r="K390" s="15" t="n">
-        <v>117.54</v>
-      </c>
-      <c r="L390" s="17">
+        <v>199.78</v>
+      </c>
+      <c r="L390" s="16">
         <f>F390*(K390-J390)</f>
         <v/>
       </c>
@@ -14420,31 +14126,31 @@
     <row r="391" ht="16.5" customHeight="1">
       <c r="D391" s="13" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>信昌電(6173)</t>
         </is>
       </c>
       <c r="E391" s="14" t="n">
-        <v>234</v>
+        <v>74</v>
       </c>
       <c r="F391" s="14" t="n">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="G391" s="14" t="n">
-        <v>6470</v>
+        <v>899</v>
       </c>
       <c r="H391" s="14" t="n">
-        <v>5042</v>
+        <v>1917</v>
       </c>
       <c r="I391" s="14" t="n">
-        <v>1428</v>
+        <v>-1018</v>
       </c>
       <c r="J391" s="15" t="n">
-        <v>276.49</v>
+        <v>121.53</v>
       </c>
       <c r="K391" s="15" t="n">
-        <v>272.51</v>
-      </c>
-      <c r="L391" s="17">
+        <v>122.11</v>
+      </c>
+      <c r="L391" s="16">
         <f>F391*(K391-J391)</f>
         <v/>
       </c>
@@ -14452,31 +14158,31 @@
     <row r="392" ht="16.5" customHeight="1">
       <c r="D392" s="13" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>鑫聯大投控(3709)</t>
         </is>
       </c>
       <c r="E392" s="14" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F392" s="14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G392" s="14" t="n">
-        <v>6028</v>
+        <v>779</v>
       </c>
       <c r="H392" s="14" t="n">
-        <v>8303</v>
+        <v>238</v>
       </c>
       <c r="I392" s="14" t="n">
-        <v>-2275</v>
+        <v>541</v>
       </c>
       <c r="J392" s="15" t="n">
-        <v>0</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="K392" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L392" s="16">
+        <v>91.42</v>
+      </c>
+      <c r="L392" s="17">
         <f>F392*(K392-J392)</f>
         <v/>
       </c>
@@ -14484,31 +14190,31 @@
     <row r="393" ht="16.5" customHeight="1">
       <c r="D393" s="13" t="inlineStr">
         <is>
-          <t>凌航(3135)</t>
+          <t>聯詠(3034)</t>
         </is>
       </c>
       <c r="E393" s="14" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="F393" s="14" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="G393" s="14" t="n">
-        <v>4464</v>
+        <v>661</v>
       </c>
       <c r="H393" s="14" t="n">
-        <v>2048</v>
+        <v>2118</v>
       </c>
       <c r="I393" s="14" t="n">
-        <v>2416</v>
+        <v>-1457</v>
       </c>
       <c r="J393" s="15" t="n">
-        <v>167.8</v>
+        <v>0</v>
       </c>
       <c r="K393" s="15" t="n">
-        <v>165.19</v>
-      </c>
-      <c r="L393" s="17">
+        <v>0</v>
+      </c>
+      <c r="L393" s="16">
         <f>F393*(K393-J393)</f>
         <v/>
       </c>
@@ -14516,98 +14222,56 @@
     <row r="394" ht="16.5" customHeight="1">
       <c r="D394" s="13" t="inlineStr">
         <is>
-          <t>旺宏(2337)</t>
+          <t>川湖(2059)</t>
         </is>
       </c>
       <c r="E394" s="14" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="F394" s="14" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="G394" s="14" t="n">
-        <v>4135</v>
+        <v>0</v>
       </c>
       <c r="H394" s="14" t="n">
-        <v>2679</v>
+        <v>707</v>
       </c>
       <c r="I394" s="14" t="n">
-        <v>1456</v>
+        <v>-707</v>
       </c>
       <c r="J394" s="15" t="n">
-        <v>153.14</v>
+        <v>0</v>
       </c>
       <c r="K394" s="15" t="n">
-        <v>153.07</v>
-      </c>
-      <c r="L394" s="17">
+        <v>0</v>
+      </c>
+      <c r="L394" s="16">
         <f>F394*(K394-J394)</f>
         <v/>
       </c>
     </row>
     <row r="395" ht="16.5" customHeight="1">
-      <c r="D395" s="13" t="inlineStr">
-        <is>
-          <t>光洋科(1785)</t>
-        </is>
-      </c>
-      <c r="E395" s="14" t="n">
-        <v>209</v>
-      </c>
-      <c r="F395" s="14" t="n">
-        <v>132</v>
-      </c>
-      <c r="G395" s="14" t="n">
-        <v>3501</v>
-      </c>
-      <c r="H395" s="14" t="n">
-        <v>2254</v>
-      </c>
-      <c r="I395" s="14" t="n">
-        <v>1247</v>
-      </c>
-      <c r="J395" s="15" t="n">
-        <v>167.51</v>
-      </c>
-      <c r="K395" s="15" t="n">
-        <v>170.77</v>
-      </c>
-      <c r="L395" s="16">
-        <f>F395*(K395-J395)</f>
-        <v/>
-      </c>
+      <c r="D395" s="13" t="n"/>
+      <c r="E395" s="14" t="n"/>
+      <c r="F395" s="14" t="n"/>
+      <c r="G395" s="14" t="n"/>
+      <c r="H395" s="14" t="n"/>
+      <c r="I395" s="14" t="n"/>
+      <c r="J395" s="15" t="n"/>
+      <c r="K395" s="15" t="n"/>
+      <c r="L395" s="16" t="n"/>
     </row>
     <row r="396" ht="16.5" customHeight="1">
-      <c r="D396" s="13" t="inlineStr">
-        <is>
-          <t>智邦(2345)</t>
-        </is>
-      </c>
-      <c r="E396" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F396" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G396" s="14" t="n">
-        <v>3272</v>
-      </c>
-      <c r="H396" s="14" t="n">
-        <v>2184</v>
-      </c>
-      <c r="I396" s="14" t="n">
-        <v>1088</v>
-      </c>
-      <c r="J396" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K396" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L396" s="16">
-        <f>F396*(K396-J396)</f>
-        <v/>
-      </c>
+      <c r="D396" s="13" t="n"/>
+      <c r="E396" s="14" t="n"/>
+      <c r="F396" s="14" t="n"/>
+      <c r="G396" s="14" t="n"/>
+      <c r="H396" s="14" t="n"/>
+      <c r="I396" s="14" t="n"/>
+      <c r="J396" s="15" t="n"/>
+      <c r="K396" s="15" t="n"/>
+      <c r="L396" s="16" t="n"/>
     </row>
     <row r="397" ht="16.5" customHeight="1">
       <c r="B397" s="12" t="inlineStr">
@@ -14679,29 +14343,29 @@
       </c>
       <c r="D398" s="13" t="inlineStr">
         <is>
-          <t>世界(5347)</t>
+          <t>盟立(2464)</t>
         </is>
       </c>
       <c r="E398" s="14" t="n">
-        <v>765</v>
+        <v>181</v>
       </c>
       <c r="F398" s="14" t="n">
-        <v>28</v>
+        <v>237</v>
       </c>
       <c r="G398" s="14" t="n">
-        <v>12853</v>
+        <v>2125</v>
       </c>
       <c r="H398" s="14" t="n">
-        <v>485</v>
+        <v>2807</v>
       </c>
       <c r="I398" s="14" t="n">
-        <v>12368</v>
+        <v>-682</v>
       </c>
       <c r="J398" s="15" t="n">
-        <v>168.02</v>
+        <v>117.39</v>
       </c>
       <c r="K398" s="15" t="n">
-        <v>173.21</v>
+        <v>118.45</v>
       </c>
       <c r="L398" s="16">
         <f>F398*(K398-J398)</f>
@@ -14711,7 +14375,7 @@
     <row r="399" ht="16.5" customHeight="1">
       <c r="D399" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>台表科(6278)</t>
         </is>
       </c>
       <c r="E399" s="14" t="n">
@@ -14721,13 +14385,13 @@
         <v>0</v>
       </c>
       <c r="G399" s="14" t="n">
-        <v>5033</v>
+        <v>375</v>
       </c>
       <c r="H399" s="14" t="n">
-        <v>2084</v>
+        <v>72</v>
       </c>
       <c r="I399" s="14" t="n">
-        <v>2949</v>
+        <v>303</v>
       </c>
       <c r="J399" s="15" t="n">
         <v>0</v>
@@ -14743,29 +14407,29 @@
     <row r="400" ht="16.5" customHeight="1">
       <c r="D400" s="13" t="inlineStr">
         <is>
-          <t>晶豪科(3006)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E400" s="14" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="F400" s="14" t="n">
-        <v>298</v>
+        <v>0</v>
       </c>
       <c r="G400" s="14" t="n">
-        <v>4817</v>
+        <v>278</v>
       </c>
       <c r="H400" s="14" t="n">
-        <v>6188</v>
+        <v>857</v>
       </c>
       <c r="I400" s="14" t="n">
-        <v>-1371</v>
+        <v>-579</v>
       </c>
       <c r="J400" s="15" t="n">
-        <v>203.26</v>
+        <v>0</v>
       </c>
       <c r="K400" s="15" t="n">
-        <v>207.67</v>
+        <v>0</v>
       </c>
       <c r="L400" s="16">
         <f>F400*(K400-J400)</f>
@@ -14775,29 +14439,29 @@
     <row r="401" ht="16.5" customHeight="1">
       <c r="D401" s="13" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>精材(3374)</t>
         </is>
       </c>
       <c r="E401" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F401" s="14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G401" s="14" t="n">
-        <v>4036</v>
+        <v>237</v>
       </c>
       <c r="H401" s="14" t="n">
-        <v>3713</v>
+        <v>1119</v>
       </c>
       <c r="I401" s="14" t="n">
-        <v>323</v>
+        <v>-882</v>
       </c>
       <c r="J401" s="15" t="n">
-        <v>0</v>
+        <v>215.45</v>
       </c>
       <c r="K401" s="15" t="n">
-        <v>0</v>
+        <v>223.72</v>
       </c>
       <c r="L401" s="16">
         <f>F401*(K401-J401)</f>
@@ -14807,194 +14471,89 @@
     <row r="402" ht="16.5" customHeight="1">
       <c r="D402" s="13" t="inlineStr">
         <is>
-          <t>旺宏(2337)</t>
+          <t>新應材(4749)</t>
         </is>
       </c>
       <c r="E402" s="14" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="F402" s="14" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="G402" s="14" t="n">
-        <v>3059</v>
+        <v>204</v>
       </c>
       <c r="H402" s="14" t="n">
-        <v>1206</v>
+        <v>823</v>
       </c>
       <c r="I402" s="14" t="n">
-        <v>1853</v>
+        <v>-619</v>
       </c>
       <c r="J402" s="15" t="n">
-        <v>154.49</v>
+        <v>0</v>
       </c>
       <c r="K402" s="15" t="n">
-        <v>152.65</v>
-      </c>
-      <c r="L402" s="17">
+        <v>0</v>
+      </c>
+      <c r="L402" s="16">
         <f>F402*(K402-J402)</f>
         <v/>
       </c>
     </row>
     <row r="403" ht="16.5" customHeight="1">
-      <c r="D403" s="13" t="inlineStr">
-        <is>
-          <t>國巨*(2327)</t>
-        </is>
-      </c>
-      <c r="E403" s="14" t="n">
-        <v>69</v>
-      </c>
-      <c r="F403" s="14" t="n">
-        <v>580</v>
-      </c>
-      <c r="G403" s="14" t="n">
-        <v>2660</v>
-      </c>
-      <c r="H403" s="14" t="n">
-        <v>22537</v>
-      </c>
-      <c r="I403" s="14" t="n">
-        <v>-19877</v>
-      </c>
-      <c r="J403" s="15" t="n">
-        <v>385.54</v>
-      </c>
-      <c r="K403" s="15" t="n">
-        <v>388.56</v>
-      </c>
-      <c r="L403" s="16">
-        <f>F403*(K403-J403)</f>
-        <v/>
-      </c>
+      <c r="D403" s="13" t="n"/>
+      <c r="E403" s="14" t="n"/>
+      <c r="F403" s="14" t="n"/>
+      <c r="G403" s="14" t="n"/>
+      <c r="H403" s="14" t="n"/>
+      <c r="I403" s="14" t="n"/>
+      <c r="J403" s="15" t="n"/>
+      <c r="K403" s="15" t="n"/>
+      <c r="L403" s="16" t="n"/>
     </row>
     <row r="404" ht="16.5" customHeight="1">
-      <c r="D404" s="13" t="inlineStr">
-        <is>
-          <t>盟立(2464)</t>
-        </is>
-      </c>
-      <c r="E404" s="14" t="n">
-        <v>181</v>
-      </c>
-      <c r="F404" s="14" t="n">
-        <v>237</v>
-      </c>
-      <c r="G404" s="14" t="n">
-        <v>2125</v>
-      </c>
-      <c r="H404" s="14" t="n">
-        <v>2807</v>
-      </c>
-      <c r="I404" s="14" t="n">
-        <v>-682</v>
-      </c>
-      <c r="J404" s="15" t="n">
-        <v>117.39</v>
-      </c>
-      <c r="K404" s="15" t="n">
-        <v>118.45</v>
-      </c>
-      <c r="L404" s="16">
-        <f>F404*(K404-J404)</f>
-        <v/>
-      </c>
+      <c r="D404" s="13" t="n"/>
+      <c r="E404" s="14" t="n"/>
+      <c r="F404" s="14" t="n"/>
+      <c r="G404" s="14" t="n"/>
+      <c r="H404" s="14" t="n"/>
+      <c r="I404" s="14" t="n"/>
+      <c r="J404" s="15" t="n"/>
+      <c r="K404" s="15" t="n"/>
+      <c r="L404" s="16" t="n"/>
     </row>
     <row r="405" ht="16.5" customHeight="1">
-      <c r="D405" s="13" t="inlineStr">
-        <is>
-          <t>台光電(2383)</t>
-        </is>
-      </c>
-      <c r="E405" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F405" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G405" s="14" t="n">
-        <v>2001</v>
-      </c>
-      <c r="H405" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="I405" s="14" t="n">
-        <v>1991</v>
-      </c>
-      <c r="J405" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K405" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L405" s="16">
-        <f>F405*(K405-J405)</f>
-        <v/>
-      </c>
+      <c r="D405" s="13" t="n"/>
+      <c r="E405" s="14" t="n"/>
+      <c r="F405" s="14" t="n"/>
+      <c r="G405" s="14" t="n"/>
+      <c r="H405" s="14" t="n"/>
+      <c r="I405" s="14" t="n"/>
+      <c r="J405" s="15" t="n"/>
+      <c r="K405" s="15" t="n"/>
+      <c r="L405" s="16" t="n"/>
     </row>
     <row r="406" ht="16.5" customHeight="1">
-      <c r="D406" s="13" t="inlineStr">
-        <is>
-          <t>群聯(8299)</t>
-        </is>
-      </c>
-      <c r="E406" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F406" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G406" s="14" t="n">
-        <v>1957</v>
-      </c>
-      <c r="H406" s="14" t="n">
-        <v>2559</v>
-      </c>
-      <c r="I406" s="14" t="n">
-        <v>-602</v>
-      </c>
-      <c r="J406" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K406" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L406" s="16">
-        <f>F406*(K406-J406)</f>
-        <v/>
-      </c>
+      <c r="D406" s="13" t="n"/>
+      <c r="E406" s="14" t="n"/>
+      <c r="F406" s="14" t="n"/>
+      <c r="G406" s="14" t="n"/>
+      <c r="H406" s="14" t="n"/>
+      <c r="I406" s="14" t="n"/>
+      <c r="J406" s="15" t="n"/>
+      <c r="K406" s="15" t="n"/>
+      <c r="L406" s="16" t="n"/>
     </row>
     <row r="407" ht="16.5" customHeight="1">
-      <c r="D407" s="13" t="inlineStr">
-        <is>
-          <t>力積電(6770)</t>
-        </is>
-      </c>
-      <c r="E407" s="14" t="n">
-        <v>286</v>
-      </c>
-      <c r="F407" s="14" t="n">
-        <v>3226</v>
-      </c>
-      <c r="G407" s="14" t="n">
-        <v>1787</v>
-      </c>
-      <c r="H407" s="14" t="n">
-        <v>19752</v>
-      </c>
-      <c r="I407" s="14" t="n">
-        <v>-17965</v>
-      </c>
-      <c r="J407" s="15" t="n">
-        <v>62.48</v>
-      </c>
-      <c r="K407" s="15" t="n">
-        <v>61.23</v>
-      </c>
-      <c r="L407" s="17">
-        <f>F407*(K407-J407)</f>
-        <v/>
-      </c>
+      <c r="D407" s="13" t="n"/>
+      <c r="E407" s="14" t="n"/>
+      <c r="F407" s="14" t="n"/>
+      <c r="G407" s="14" t="n"/>
+      <c r="H407" s="14" t="n"/>
+      <c r="I407" s="14" t="n"/>
+      <c r="J407" s="15" t="n"/>
+      <c r="K407" s="15" t="n"/>
+      <c r="L407" s="16" t="n"/>
     </row>
     <row r="408" ht="16.5" customHeight="1">
       <c r="A408" s="12" t="inlineStr">
@@ -15108,29 +14667,29 @@
     <row r="410" ht="16.5" customHeight="1">
       <c r="D410" s="13" t="inlineStr">
         <is>
-          <t>正文(4906)</t>
+          <t>大聯大(3702)</t>
         </is>
       </c>
       <c r="E410" s="14" t="n">
-        <v>7647</v>
+        <v>2806</v>
       </c>
       <c r="F410" s="14" t="n">
-        <v>9603</v>
+        <v>24</v>
       </c>
       <c r="G410" s="14" t="n">
-        <v>32519</v>
+        <v>31816</v>
       </c>
       <c r="H410" s="14" t="n">
-        <v>40580</v>
+        <v>267</v>
       </c>
       <c r="I410" s="14" t="n">
-        <v>-8061</v>
+        <v>31549</v>
       </c>
       <c r="J410" s="15" t="n">
-        <v>42.52</v>
+        <v>113.39</v>
       </c>
       <c r="K410" s="15" t="n">
-        <v>42.26</v>
+        <v>111.25</v>
       </c>
       <c r="L410" s="17">
         <f>F410*(K410-J410)</f>
@@ -15140,29 +14699,29 @@
     <row r="411" ht="16.5" customHeight="1">
       <c r="D411" s="13" t="inlineStr">
         <is>
-          <t>大聯大(3702)</t>
+          <t>瑞昱(2379)</t>
         </is>
       </c>
       <c r="E411" s="14" t="n">
-        <v>2806</v>
+        <v>497</v>
       </c>
       <c r="F411" s="14" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G411" s="14" t="n">
-        <v>31816</v>
+        <v>29423</v>
       </c>
       <c r="H411" s="14" t="n">
-        <v>267</v>
+        <v>987</v>
       </c>
       <c r="I411" s="14" t="n">
-        <v>31549</v>
+        <v>28436</v>
       </c>
       <c r="J411" s="15" t="n">
-        <v>113.39</v>
+        <v>592.01</v>
       </c>
       <c r="K411" s="15" t="n">
-        <v>111.25</v>
+        <v>580.41</v>
       </c>
       <c r="L411" s="17">
         <f>F411*(K411-J411)</f>
@@ -15172,29 +14731,29 @@
     <row r="412" ht="16.5" customHeight="1">
       <c r="D412" s="13" t="inlineStr">
         <is>
-          <t>瑞昱(2379)</t>
+          <t>台表科(6278)</t>
         </is>
       </c>
       <c r="E412" s="14" t="n">
-        <v>497</v>
+        <v>605</v>
       </c>
       <c r="F412" s="14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G412" s="14" t="n">
-        <v>29423</v>
+        <v>12122</v>
       </c>
       <c r="H412" s="14" t="n">
-        <v>987</v>
+        <v>391</v>
       </c>
       <c r="I412" s="14" t="n">
-        <v>28436</v>
+        <v>11731</v>
       </c>
       <c r="J412" s="15" t="n">
-        <v>592.01</v>
+        <v>200.36</v>
       </c>
       <c r="K412" s="15" t="n">
-        <v>580.41</v>
+        <v>195.3</v>
       </c>
       <c r="L412" s="17">
         <f>F412*(K412-J412)</f>
@@ -15204,31 +14763,31 @@
     <row r="413" ht="16.5" customHeight="1">
       <c r="D413" s="13" t="inlineStr">
         <is>
-          <t>台表科(6278)</t>
+          <t>全宇昕(6651)</t>
         </is>
       </c>
       <c r="E413" s="14" t="n">
-        <v>605</v>
+        <v>779</v>
       </c>
       <c r="F413" s="14" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G413" s="14" t="n">
-        <v>12122</v>
+        <v>9464</v>
       </c>
       <c r="H413" s="14" t="n">
-        <v>391</v>
+        <v>24</v>
       </c>
       <c r="I413" s="14" t="n">
-        <v>11731</v>
+        <v>9440</v>
       </c>
       <c r="J413" s="15" t="n">
-        <v>200.36</v>
+        <v>121.49</v>
       </c>
       <c r="K413" s="15" t="n">
-        <v>195.3</v>
-      </c>
-      <c r="L413" s="17">
+        <v>122.5</v>
+      </c>
+      <c r="L413" s="16">
         <f>F413*(K413-J413)</f>
         <v/>
       </c>
@@ -15236,31 +14795,31 @@
     <row r="414" ht="16.5" customHeight="1">
       <c r="D414" s="13" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>天二科技(6834)</t>
         </is>
       </c>
       <c r="E414" s="14" t="n">
-        <v>0</v>
+        <v>846</v>
       </c>
       <c r="F414" s="14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G414" s="14" t="n">
-        <v>10676</v>
+        <v>4069</v>
       </c>
       <c r="H414" s="14" t="n">
-        <v>1538</v>
+        <v>62</v>
       </c>
       <c r="I414" s="14" t="n">
-        <v>9138</v>
+        <v>4007</v>
       </c>
       <c r="J414" s="15" t="n">
-        <v>0</v>
+        <v>48.1</v>
       </c>
       <c r="K414" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L414" s="16">
+        <v>48</v>
+      </c>
+      <c r="L414" s="17">
         <f>F414*(K414-J414)</f>
         <v/>
       </c>
@@ -15268,29 +14827,29 @@
     <row r="415" ht="16.5" customHeight="1">
       <c r="D415" s="13" t="inlineStr">
         <is>
-          <t>全宇昕(6651)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E415" s="14" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="F415" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G415" s="14" t="n">
-        <v>9464</v>
+        <v>2853</v>
       </c>
       <c r="H415" s="14" t="n">
-        <v>24</v>
+        <v>1280</v>
       </c>
       <c r="I415" s="14" t="n">
-        <v>9440</v>
+        <v>1573</v>
       </c>
       <c r="J415" s="15" t="n">
-        <v>121.49</v>
+        <v>0</v>
       </c>
       <c r="K415" s="15" t="n">
-        <v>122.5</v>
+        <v>0</v>
       </c>
       <c r="L415" s="16">
         <f>F415*(K415-J415)</f>
@@ -15300,31 +14859,31 @@
     <row r="416" ht="16.5" customHeight="1">
       <c r="D416" s="13" t="inlineStr">
         <is>
-          <t>亞力(1514)</t>
+          <t>新應材(4749)</t>
         </is>
       </c>
       <c r="E416" s="14" t="n">
-        <v>532</v>
+        <v>0</v>
       </c>
       <c r="F416" s="14" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G416" s="14" t="n">
-        <v>6915</v>
+        <v>2765</v>
       </c>
       <c r="H416" s="14" t="n">
-        <v>425</v>
+        <v>629</v>
       </c>
       <c r="I416" s="14" t="n">
-        <v>6490</v>
+        <v>2136</v>
       </c>
       <c r="J416" s="15" t="n">
-        <v>129.98</v>
+        <v>0</v>
       </c>
       <c r="K416" s="15" t="n">
-        <v>125</v>
-      </c>
-      <c r="L416" s="17">
+        <v>0</v>
+      </c>
+      <c r="L416" s="16">
         <f>F416*(K416-J416)</f>
         <v/>
       </c>
@@ -15332,31 +14891,31 @@
     <row r="417" ht="16.5" customHeight="1">
       <c r="D417" s="13" t="inlineStr">
         <is>
-          <t>主動統一台股增長(00981A)</t>
+          <t>文曄(3036)</t>
         </is>
       </c>
       <c r="E417" s="14" t="n">
-        <v>1738</v>
+        <v>51</v>
       </c>
       <c r="F417" s="14" t="n">
-        <v>1506</v>
+        <v>1</v>
       </c>
       <c r="G417" s="14" t="n">
-        <v>5028</v>
+        <v>1227</v>
       </c>
       <c r="H417" s="14" t="n">
-        <v>4355</v>
+        <v>24</v>
       </c>
       <c r="I417" s="14" t="n">
-        <v>673</v>
+        <v>1203</v>
       </c>
       <c r="J417" s="15" t="n">
-        <v>28.93</v>
+        <v>240.51</v>
       </c>
       <c r="K417" s="15" t="n">
-        <v>28.92</v>
-      </c>
-      <c r="L417" s="17">
+        <v>241</v>
+      </c>
+      <c r="L417" s="16">
         <f>F417*(K417-J417)</f>
         <v/>
       </c>
@@ -15364,7 +14923,7 @@
     <row r="418" ht="16.5" customHeight="1">
       <c r="D418" s="13" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>川湖(2059)</t>
         </is>
       </c>
       <c r="E418" s="14" t="n">
@@ -15374,13 +14933,13 @@
         <v>0</v>
       </c>
       <c r="G418" s="14" t="n">
-        <v>4892</v>
+        <v>532</v>
       </c>
       <c r="H418" s="14" t="n">
-        <v>3748</v>
+        <v>3726</v>
       </c>
       <c r="I418" s="14" t="n">
-        <v>1144</v>
+        <v>-3194</v>
       </c>
       <c r="J418" s="15" t="n">
         <v>0</v>
@@ -15463,7 +15022,7 @@
       </c>
       <c r="D420" s="13" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>新應材(4749)</t>
         </is>
       </c>
       <c r="E420" s="14" t="n">
@@ -15473,13 +15032,13 @@
         <v>0</v>
       </c>
       <c r="G420" s="14" t="n">
-        <v>11326</v>
+        <v>5508</v>
       </c>
       <c r="H420" s="14" t="n">
-        <v>940</v>
+        <v>5975</v>
       </c>
       <c r="I420" s="14" t="n">
-        <v>10386</v>
+        <v>-467</v>
       </c>
       <c r="J420" s="15" t="n">
         <v>0</v>
@@ -15495,7 +15054,7 @@
     <row r="421" ht="16.5" customHeight="1">
       <c r="D421" s="13" t="inlineStr">
         <is>
-          <t>欣興(3037)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E421" s="14" t="n">
@@ -15505,13 +15064,13 @@
         <v>0</v>
       </c>
       <c r="G421" s="14" t="n">
-        <v>5522</v>
+        <v>2544</v>
       </c>
       <c r="H421" s="14" t="n">
-        <v>3449</v>
+        <v>1144</v>
       </c>
       <c r="I421" s="14" t="n">
-        <v>2073</v>
+        <v>1400</v>
       </c>
       <c r="J421" s="15" t="n">
         <v>0</v>
@@ -15527,31 +15086,31 @@
     <row r="422" ht="16.5" customHeight="1">
       <c r="D422" s="13" t="inlineStr">
         <is>
-          <t>新應材(4749)</t>
+          <t>大聯大(3702)</t>
         </is>
       </c>
       <c r="E422" s="14" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="F422" s="14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G422" s="14" t="n">
-        <v>5508</v>
+        <v>2338</v>
       </c>
       <c r="H422" s="14" t="n">
-        <v>5975</v>
+        <v>145</v>
       </c>
       <c r="I422" s="14" t="n">
-        <v>-467</v>
+        <v>2193</v>
       </c>
       <c r="J422" s="15" t="n">
-        <v>0</v>
+        <v>113.5</v>
       </c>
       <c r="K422" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L422" s="16">
+        <v>111.85</v>
+      </c>
+      <c r="L422" s="17">
         <f>F422*(K422-J422)</f>
         <v/>
       </c>
@@ -15559,29 +15118,29 @@
     <row r="423" ht="16.5" customHeight="1">
       <c r="D423" s="13" t="inlineStr">
         <is>
-          <t>國巨*(2327)</t>
+          <t>聯詠(3034)</t>
         </is>
       </c>
       <c r="E423" s="14" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="F423" s="14" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G423" s="14" t="n">
-        <v>5295</v>
+        <v>2289</v>
       </c>
       <c r="H423" s="14" t="n">
-        <v>2691</v>
+        <v>683</v>
       </c>
       <c r="I423" s="14" t="n">
-        <v>2604</v>
+        <v>1606</v>
       </c>
       <c r="J423" s="15" t="n">
-        <v>386.52</v>
+        <v>0</v>
       </c>
       <c r="K423" s="15" t="n">
-        <v>389.97</v>
+        <v>0</v>
       </c>
       <c r="L423" s="16">
         <f>F423*(K423-J423)</f>
@@ -15591,7 +15150,7 @@
     <row r="424" ht="16.5" customHeight="1">
       <c r="D424" s="13" t="inlineStr">
         <is>
-          <t>南電(8046)</t>
+          <t>藥華藥(6446)</t>
         </is>
       </c>
       <c r="E424" s="14" t="n">
@@ -15601,13 +15160,13 @@
         <v>0</v>
       </c>
       <c r="G424" s="14" t="n">
-        <v>3861</v>
+        <v>1940</v>
       </c>
       <c r="H424" s="14" t="n">
-        <v>3096</v>
+        <v>690</v>
       </c>
       <c r="I424" s="14" t="n">
-        <v>765</v>
+        <v>1250</v>
       </c>
       <c r="J424" s="15" t="n">
         <v>0</v>
@@ -15623,29 +15182,29 @@
     <row r="425" ht="16.5" customHeight="1">
       <c r="D425" s="13" t="inlineStr">
         <is>
-          <t>主動統一台股增長(00981A)</t>
+          <t>譜瑞-KY(4966)</t>
         </is>
       </c>
       <c r="E425" s="14" t="n">
-        <v>1201</v>
+        <v>0</v>
       </c>
       <c r="F425" s="14" t="n">
-        <v>725</v>
+        <v>0</v>
       </c>
       <c r="G425" s="14" t="n">
-        <v>3476</v>
+        <v>1737</v>
       </c>
       <c r="H425" s="14" t="n">
-        <v>2103</v>
+        <v>213</v>
       </c>
       <c r="I425" s="14" t="n">
-        <v>1373</v>
+        <v>1524</v>
       </c>
       <c r="J425" s="15" t="n">
-        <v>28.94</v>
+        <v>0</v>
       </c>
       <c r="K425" s="15" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L425" s="16">
         <f>F425*(K425-J425)</f>
@@ -15655,7 +15214,7 @@
     <row r="426" ht="16.5" customHeight="1">
       <c r="D426" s="13" t="inlineStr">
         <is>
-          <t>達發(6526)</t>
+          <t>立隆電(2472)</t>
         </is>
       </c>
       <c r="E426" s="14" t="n">
@@ -15665,13 +15224,13 @@
         <v>0</v>
       </c>
       <c r="G426" s="14" t="n">
-        <v>3442</v>
+        <v>1233</v>
       </c>
       <c r="H426" s="14" t="n">
-        <v>234</v>
+        <v>414</v>
       </c>
       <c r="I426" s="14" t="n">
-        <v>3208</v>
+        <v>819</v>
       </c>
       <c r="J426" s="15" t="n">
         <v>0</v>
@@ -15687,7 +15246,7 @@
     <row r="427" ht="16.5" customHeight="1">
       <c r="D427" s="13" t="inlineStr">
         <is>
-          <t>聯鈞(3450)</t>
+          <t>川湖(2059)</t>
         </is>
       </c>
       <c r="E427" s="14" t="n">
@@ -15697,13 +15256,13 @@
         <v>0</v>
       </c>
       <c r="G427" s="14" t="n">
-        <v>3323</v>
+        <v>1056</v>
       </c>
       <c r="H427" s="14" t="n">
-        <v>4394</v>
+        <v>103</v>
       </c>
       <c r="I427" s="14" t="n">
-        <v>-1071</v>
+        <v>953</v>
       </c>
       <c r="J427" s="15" t="n">
         <v>0</v>
@@ -15719,66 +15278,45 @@
     <row r="428" ht="16.5" customHeight="1">
       <c r="D428" s="13" t="inlineStr">
         <is>
-          <t>玉山金(2884)</t>
+          <t>禾伸堂(3026)</t>
         </is>
       </c>
       <c r="E428" s="14" t="n">
-        <v>978</v>
+        <v>0</v>
       </c>
       <c r="F428" s="14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G428" s="14" t="n">
-        <v>3169</v>
+        <v>345</v>
       </c>
       <c r="H428" s="14" t="n">
-        <v>19</v>
+        <v>875</v>
       </c>
       <c r="I428" s="14" t="n">
-        <v>3150</v>
+        <v>-530</v>
       </c>
       <c r="J428" s="15" t="n">
-        <v>32.41</v>
+        <v>0</v>
       </c>
       <c r="K428" s="15" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="L428" s="17">
+        <v>0</v>
+      </c>
+      <c r="L428" s="16">
         <f>F428*(K428-J428)</f>
         <v/>
       </c>
     </row>
     <row r="429" ht="16.5" customHeight="1">
-      <c r="D429" s="13" t="inlineStr">
-        <is>
-          <t>智邦(2345)</t>
-        </is>
-      </c>
-      <c r="E429" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F429" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G429" s="14" t="n">
-        <v>3163</v>
-      </c>
-      <c r="H429" s="14" t="n">
-        <v>489</v>
-      </c>
-      <c r="I429" s="14" t="n">
-        <v>2674</v>
-      </c>
-      <c r="J429" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K429" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L429" s="16">
-        <f>F429*(K429-J429)</f>
-        <v/>
-      </c>
+      <c r="D429" s="13" t="n"/>
+      <c r="E429" s="14" t="n"/>
+      <c r="F429" s="14" t="n"/>
+      <c r="G429" s="14" t="n"/>
+      <c r="H429" s="14" t="n"/>
+      <c r="I429" s="14" t="n"/>
+      <c r="J429" s="15" t="n"/>
+      <c r="K429" s="15" t="n"/>
+      <c r="L429" s="16" t="n"/>
     </row>
     <row r="430" ht="16.5" customHeight="1">
       <c r="A430" s="12" t="inlineStr">

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="E4" s="14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G4" s="14" t="n">
         <v>14676</v>
@@ -741,12 +741,12 @@
         <v>-9895</v>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0</v>
+        <v>6380.83</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="16">
+        <v>6300.21</v>
+      </c>
+      <c r="L4" s="17">
         <f>F4*(K4-J4)</f>
         <v/>
       </c>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="E15" s="14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>9942</v>
@@ -1128,10 +1128,10 @@
         <v>6064</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0</v>
+        <v>2259.55</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0</v>
+        <v>2281.12</v>
       </c>
       <c r="L15" s="16">
         <f>F15*(K15-J15)</f>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="E17" s="14" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>6855</v>
@@ -1192,10 +1192,10 @@
         <v>-622</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0</v>
+        <v>535.55</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>0</v>
+        <v>537.89</v>
       </c>
       <c r="L17" s="16">
         <f>F17*(K17-J17)</f>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="E19" s="14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>5988</v>
@@ -1256,10 +1256,10 @@
         <v>4520</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0</v>
+        <v>1761.18</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0</v>
+        <v>1835.25</v>
       </c>
       <c r="L19" s="16">
         <f>F19*(K19-J19)</f>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="E24" s="14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F24" s="14" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>1590</v>
       </c>
       <c r="J24" s="15" t="n">
-        <v>0</v>
+        <v>2304.43</v>
       </c>
       <c r="K24" s="15" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="E25" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F25" s="14" t="n">
         <v>0</v>
@@ -1483,7 +1483,7 @@
         <v>1572</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>0</v>
+        <v>5241.67</v>
       </c>
       <c r="K25" s="15" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="E27" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F27" s="14" t="n">
         <v>0</v>
@@ -1547,7 +1547,7 @@
         <v>1133</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0</v>
+        <v>2309</v>
       </c>
       <c r="K27" s="15" t="n">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="E29" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="14" t="n">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>1063</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>0</v>
+        <v>5355</v>
       </c>
       <c r="K29" s="15" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="E31" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" s="14" t="n">
         <v>0</v>
@@ -1675,7 +1675,7 @@
         <v>782</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>0</v>
+        <v>3934.5</v>
       </c>
       <c r="K31" s="15" t="n">
         <v>0</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E32" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F32" s="14" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>777</v>
       </c>
       <c r="J32" s="15" t="n">
-        <v>0</v>
+        <v>2601.67</v>
       </c>
       <c r="K32" s="15" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="E44" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>4209</v>
@@ -2136,12 +2136,12 @@
         <v>2356</v>
       </c>
       <c r="J44" s="15" t="n">
-        <v>0</v>
+        <v>3826.36</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="16">
+        <v>3706.4</v>
+      </c>
+      <c r="L44" s="17">
         <f>F44*(K44-J44)</f>
         <v/>
       </c>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="E47" s="14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>4369</v>
@@ -2267,10 +2267,10 @@
         <v>3014</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>0</v>
+        <v>2184.45</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>0</v>
+        <v>2258.5</v>
       </c>
       <c r="L47" s="16">
         <f>F47*(K47-J47)</f>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="E49" s="14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>2802</v>
@@ -2331,10 +2331,10 @@
         <v>2283</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>0</v>
+        <v>4003</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>0</v>
+        <v>5191</v>
       </c>
       <c r="L49" s="16">
         <f>F49*(K49-J49)</f>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="E52" s="14" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="G52" s="14" t="n">
         <v>2416</v>
@@ -2427,12 +2427,12 @@
         <v>-353</v>
       </c>
       <c r="J52" s="15" t="n">
-        <v>0</v>
+        <v>215.7</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="16">
+        <v>214.67</v>
+      </c>
+      <c r="L52" s="17">
         <f>F52*(K52-J52)</f>
         <v/>
       </c>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="E54" s="14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>2170</v>
@@ -2491,12 +2491,12 @@
         <v>644</v>
       </c>
       <c r="J54" s="15" t="n">
-        <v>0</v>
+        <v>394.51</v>
       </c>
       <c r="K54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="16">
+        <v>391.21</v>
+      </c>
+      <c r="L54" s="17">
         <f>F54*(K54-J54)</f>
         <v/>
       </c>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="E62" s="14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="14" t="n">
         <v>13802</v>
@@ -2782,10 +2782,10 @@
         <v>12566</v>
       </c>
       <c r="J62" s="15" t="n">
-        <v>0</v>
+        <v>5750.83</v>
       </c>
       <c r="K62" s="15" t="n">
-        <v>0</v>
+        <v>6180.5</v>
       </c>
       <c r="L62" s="16">
         <f>F62*(K62-J62)</f>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="E73" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G73" s="14" t="n">
         <v>7636</v>
@@ -3169,10 +3169,10 @@
         <v>1250</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>0</v>
+        <v>6362.92</v>
       </c>
       <c r="K73" s="15" t="n">
-        <v>0</v>
+        <v>6386.3</v>
       </c>
       <c r="L73" s="16">
         <f>F73*(K73-J73)</f>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="E75" s="14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" s="14" t="n">
         <v>5405</v>
@@ -3233,10 +3233,10 @@
         <v>4918</v>
       </c>
       <c r="J75" s="15" t="n">
-        <v>0</v>
+        <v>3860.57</v>
       </c>
       <c r="K75" s="15" t="n">
-        <v>0</v>
+        <v>4868</v>
       </c>
       <c r="L75" s="16">
         <f>F75*(K75-J75)</f>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="E79" s="14" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G79" s="14" t="n">
         <v>54376</v>
@@ -3406,12 +3406,12 @@
         <v>52195</v>
       </c>
       <c r="J79" s="15" t="n">
-        <v>0</v>
+        <v>5723.84</v>
       </c>
       <c r="K79" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="16">
+        <v>5453</v>
+      </c>
+      <c r="L79" s="17">
         <f>F79*(K79-J79)</f>
         <v/>
       </c>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="E84" s="14" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G84" s="14" t="n">
         <v>12446</v>
@@ -3566,10 +3566,10 @@
         <v>8127</v>
       </c>
       <c r="J84" s="15" t="n">
-        <v>0</v>
+        <v>2222.5</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0</v>
+        <v>2273.37</v>
       </c>
       <c r="L84" s="16">
         <f>F84*(K84-J84)</f>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="E88" s="14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G88" s="14" t="n">
         <v>8955</v>
@@ -3694,12 +3694,12 @@
         <v>5803</v>
       </c>
       <c r="J88" s="15" t="n">
-        <v>0</v>
+        <v>5267.41</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="16">
+        <v>5253.17</v>
+      </c>
+      <c r="L88" s="17">
         <f>F88*(K88-J88)</f>
         <v/>
       </c>
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="E91" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G91" s="14" t="n">
         <v>3376</v>
@@ -3825,10 +3825,10 @@
         <v>-5434</v>
       </c>
       <c r="J91" s="15" t="n">
-        <v>0</v>
+        <v>5626</v>
       </c>
       <c r="K91" s="15" t="n">
-        <v>0</v>
+        <v>5873.47</v>
       </c>
       <c r="L91" s="16">
         <f>F91*(K91-J91)</f>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="E93" s="14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G93" s="14" t="n">
         <v>3003</v>
@@ -3889,12 +3889,12 @@
         <v>-4604</v>
       </c>
       <c r="J93" s="15" t="n">
-        <v>0</v>
+        <v>2309.77</v>
       </c>
       <c r="K93" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="16">
+        <v>2237.26</v>
+      </c>
+      <c r="L93" s="17">
         <f>F93*(K93-J93)</f>
         <v/>
       </c>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="E94" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F94" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G94" s="14" t="n">
         <v>1935</v>
@@ -3921,10 +3921,10 @@
         <v>374</v>
       </c>
       <c r="J94" s="15" t="n">
-        <v>0</v>
+        <v>3870.2</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0</v>
+        <v>3903.5</v>
       </c>
       <c r="L94" s="16">
         <f>F94*(K94-J94)</f>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="E95" s="14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F95" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G95" s="14" t="n">
         <v>1875</v>
@@ -3953,10 +3953,10 @@
         <v>1675</v>
       </c>
       <c r="J95" s="15" t="n">
-        <v>0</v>
+        <v>852.23</v>
       </c>
       <c r="K95" s="15" t="n">
-        <v>0</v>
+        <v>1001.5</v>
       </c>
       <c r="L95" s="16">
         <f>F95*(K95-J95)</f>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="E96" s="14" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F96" s="14" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G96" s="14" t="n">
         <v>1798</v>
@@ -3985,12 +3985,12 @@
         <v>490</v>
       </c>
       <c r="J96" s="15" t="n">
-        <v>0</v>
+        <v>243.01</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="16">
+        <v>242.3</v>
+      </c>
+      <c r="L96" s="17">
         <f>F96*(K96-J96)</f>
         <v/>
       </c>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="E97" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F97" s="14" t="n">
         <v>0</v>
@@ -4017,7 +4017,7 @@
         <v>1620</v>
       </c>
       <c r="J97" s="15" t="n">
-        <v>0</v>
+        <v>5443.67</v>
       </c>
       <c r="K97" s="15" t="n">
         <v>0</v>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="E99" s="14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G99" s="14" t="n">
         <v>1231</v>
@@ -4081,10 +4081,10 @@
         <v>452</v>
       </c>
       <c r="J99" s="15" t="n">
-        <v>0</v>
+        <v>1538.75</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>0</v>
+        <v>1557.6</v>
       </c>
       <c r="L99" s="16">
         <f>F99*(K99-J99)</f>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="E102" s="14" t="n">
-        <v>0</v>
+        <v>1101</v>
       </c>
       <c r="F102" s="14" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="G102" s="14" t="n">
         <v>33149</v>
@@ -4212,10 +4212,10 @@
         <v>-2621</v>
       </c>
       <c r="J102" s="15" t="n">
-        <v>0</v>
+        <v>301.08</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0</v>
+        <v>301.09</v>
       </c>
       <c r="L102" s="16">
         <f>F102*(K102-J102)</f>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="E105" s="14" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F105" s="14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G105" s="14" t="n">
         <v>10744</v>
@@ -4308,12 +4308,12 @@
         <v>9349</v>
       </c>
       <c r="J105" s="15" t="n">
-        <v>0</v>
+        <v>1821.1</v>
       </c>
       <c r="K105" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="16">
+        <v>1743.75</v>
+      </c>
+      <c r="L105" s="17">
         <f>F105*(K105-J105)</f>
         <v/>
       </c>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="E106" s="14" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="F106" s="14" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="G106" s="14" t="n">
         <v>8283</v>
@@ -4340,12 +4340,12 @@
         <v>2046</v>
       </c>
       <c r="J106" s="15" t="n">
-        <v>0</v>
+        <v>462.72</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="16">
+        <v>462</v>
+      </c>
+      <c r="L106" s="17">
         <f>F106*(K106-J106)</f>
         <v/>
       </c>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="E107" s="14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F107" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G107" s="14" t="n">
         <v>7556</v>
@@ -4372,12 +4372,12 @@
         <v>3338</v>
       </c>
       <c r="J107" s="15" t="n">
-        <v>0</v>
+        <v>3976.58</v>
       </c>
       <c r="K107" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="16">
+        <v>3835</v>
+      </c>
+      <c r="L107" s="17">
         <f>F107*(K107-J107)</f>
         <v/>
       </c>
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="E109" s="14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F109" s="14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G109" s="14" t="n">
         <v>6626</v>
@@ -4436,10 +4436,10 @@
         <v>-3693</v>
       </c>
       <c r="J109" s="15" t="n">
-        <v>0</v>
+        <v>3897.88</v>
       </c>
       <c r="K109" s="15" t="n">
-        <v>0</v>
+        <v>3968.81</v>
       </c>
       <c r="L109" s="16">
         <f>F109*(K109-J109)</f>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="E110" s="14" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F110" s="14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G110" s="14" t="n">
         <v>6278</v>
@@ -4468,12 +4468,12 @@
         <v>1519</v>
       </c>
       <c r="J110" s="15" t="n">
-        <v>0</v>
+        <v>1184.62</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="16">
+        <v>1160.73</v>
+      </c>
+      <c r="L110" s="17">
         <f>F110*(K110-J110)</f>
         <v/>
       </c>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="E117" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F117" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G117" s="14" t="n">
         <v>2182</v>
@@ -4727,12 +4727,12 @@
         <v>1588</v>
       </c>
       <c r="J117" s="15" t="n">
-        <v>0</v>
+        <v>3637.33</v>
       </c>
       <c r="K117" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="16">
+        <v>2967.5</v>
+      </c>
+      <c r="L117" s="17">
         <f>F117*(K117-J117)</f>
         <v/>
       </c>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="E118" s="14" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F118" s="14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G118" s="14" t="n">
         <v>1324</v>
@@ -4759,12 +4759,12 @@
         <v>315</v>
       </c>
       <c r="J118" s="15" t="n">
-        <v>0</v>
+        <v>426.94</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="16">
+        <v>420.5</v>
+      </c>
+      <c r="L118" s="17">
         <f>F118*(K118-J118)</f>
         <v/>
       </c>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="E123" s="14" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F123" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G123" s="14" t="n">
         <v>8137</v>
@@ -4954,10 +4954,10 @@
         <v>7152</v>
       </c>
       <c r="J123" s="15" t="n">
-        <v>0</v>
+        <v>2260.17</v>
       </c>
       <c r="K123" s="15" t="n">
-        <v>0</v>
+        <v>2463</v>
       </c>
       <c r="L123" s="16">
         <f>F123*(K123-J123)</f>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="E126" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F126" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G126" s="14" t="n">
         <v>4250</v>
@@ -5050,12 +5050,12 @@
         <v>3483</v>
       </c>
       <c r="J126" s="15" t="n">
-        <v>0</v>
+        <v>3863.91</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="16">
+        <v>3835</v>
+      </c>
+      <c r="L126" s="17">
         <f>F126*(K126-J126)</f>
         <v/>
       </c>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="E128" s="14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F128" s="14" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="G128" s="14" t="n">
         <v>2890</v>
@@ -5114,10 +5114,10 @@
         <v>-1367</v>
       </c>
       <c r="J128" s="15" t="n">
-        <v>0</v>
+        <v>412.93</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0</v>
+        <v>413.26</v>
       </c>
       <c r="L128" s="16">
         <f>F128*(K128-J128)</f>
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="E129" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F129" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G129" s="14" t="n">
         <v>2710</v>
@@ -5146,10 +5146,10 @@
         <v>408</v>
       </c>
       <c r="J129" s="15" t="n">
-        <v>0</v>
+        <v>4517.33</v>
       </c>
       <c r="K129" s="15" t="n">
-        <v>0</v>
+        <v>4604.4</v>
       </c>
       <c r="L129" s="16">
         <f>F129*(K129-J129)</f>
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="E130" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F130" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G130" s="14" t="n">
         <v>2595</v>
@@ -5178,10 +5178,10 @@
         <v>2018</v>
       </c>
       <c r="J130" s="15" t="n">
-        <v>0</v>
+        <v>2595.3</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0</v>
+        <v>2885</v>
       </c>
       <c r="L130" s="16">
         <f>F130*(K130-J130)</f>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="E132" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F132" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G132" s="14" t="n">
         <v>2472</v>
@@ -5242,12 +5242,12 @@
         <v>1238</v>
       </c>
       <c r="J132" s="15" t="n">
-        <v>0</v>
+        <v>6180</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="16">
+        <v>6172</v>
+      </c>
+      <c r="L132" s="17">
         <f>F132*(K132-J132)</f>
         <v/>
       </c>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="E137" s="14" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="F137" s="14" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G137" s="14" t="n">
         <v>35424</v>
@@ -5437,10 +5437,10 @@
         <v>21611</v>
       </c>
       <c r="J137" s="15" t="n">
-        <v>0</v>
+        <v>2585.69</v>
       </c>
       <c r="K137" s="15" t="n">
-        <v>0</v>
+        <v>2606.28</v>
       </c>
       <c r="L137" s="16">
         <f>F137*(K137-J137)</f>
@@ -5486,10 +5486,10 @@
         </is>
       </c>
       <c r="E139" s="14" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F139" s="14" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="G139" s="14" t="n">
         <v>26807</v>
@@ -5501,12 +5501,12 @@
         <v>-41768</v>
       </c>
       <c r="J139" s="15" t="n">
-        <v>0</v>
+        <v>2233.91</v>
       </c>
       <c r="K139" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="16">
+        <v>2233.72</v>
+      </c>
+      <c r="L139" s="17">
         <f>F139*(K139-J139)</f>
         <v/>
       </c>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="E141" s="14" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F141" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" s="14" t="n">
         <v>24789</v>
@@ -5565,10 +5565,10 @@
         <v>24232</v>
       </c>
       <c r="J141" s="15" t="n">
-        <v>0</v>
+        <v>5388.85</v>
       </c>
       <c r="K141" s="15" t="n">
-        <v>0</v>
+        <v>5566</v>
       </c>
       <c r="L141" s="16">
         <f>F141*(K141-J141)</f>
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="E143" s="14" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F143" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G143" s="14" t="n">
         <v>21815</v>
@@ -5629,10 +5629,10 @@
         <v>18464</v>
       </c>
       <c r="J143" s="15" t="n">
-        <v>0</v>
+        <v>5453.65</v>
       </c>
       <c r="K143" s="15" t="n">
-        <v>0</v>
+        <v>5585.17</v>
       </c>
       <c r="L143" s="16">
         <f>F143*(K143-J143)</f>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="E150" s="14" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F150" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G150" s="14" t="n">
         <v>46181</v>
@@ -5898,12 +5898,12 @@
         <v>43669</v>
       </c>
       <c r="J150" s="15" t="n">
-        <v>0</v>
+        <v>6414.08</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="16">
+        <v>6279</v>
+      </c>
+      <c r="L150" s="17">
         <f>F150*(K150-J150)</f>
         <v/>
       </c>
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="E151" s="14" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="F151" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G151" s="14" t="n">
         <v>44810</v>
@@ -5930,10 +5930,10 @@
         <v>41265</v>
       </c>
       <c r="J151" s="15" t="n">
-        <v>0</v>
+        <v>2836.04</v>
       </c>
       <c r="K151" s="15" t="n">
-        <v>0</v>
+        <v>2953.92</v>
       </c>
       <c r="L151" s="16">
         <f>F151*(K151-J151)</f>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="E159" s="14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F159" s="14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G159" s="14" t="n">
         <v>14722</v>
@@ -6221,10 +6221,10 @@
         <v>6726</v>
       </c>
       <c r="J159" s="15" t="n">
-        <v>0</v>
+        <v>4907.2</v>
       </c>
       <c r="K159" s="15" t="n">
-        <v>0</v>
+        <v>4997.56</v>
       </c>
       <c r="L159" s="16">
         <f>F159*(K159-J159)</f>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="E160" s="14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F160" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G160" s="14" t="n">
         <v>12663</v>
@@ -6253,10 +6253,10 @@
         <v>10907</v>
       </c>
       <c r="J160" s="15" t="n">
-        <v>0</v>
+        <v>5756.05</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>0</v>
+        <v>5852.67</v>
       </c>
       <c r="L160" s="16">
         <f>F160*(K160-J160)</f>
@@ -6270,10 +6270,10 @@
         </is>
       </c>
       <c r="E161" s="14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F161" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G161" s="14" t="n">
         <v>12332</v>
@@ -6285,12 +6285,12 @@
         <v>10938</v>
       </c>
       <c r="J161" s="15" t="n">
-        <v>0</v>
+        <v>5361.7</v>
       </c>
       <c r="K161" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" s="16">
+        <v>4648.33</v>
+      </c>
+      <c r="L161" s="17">
         <f>F161*(K161-J161)</f>
         <v/>
       </c>
@@ -6657,10 +6657,10 @@
         </is>
       </c>
       <c r="E172" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F172" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G172" s="14" t="n">
         <v>7636</v>
@@ -6672,10 +6672,10 @@
         <v>1250</v>
       </c>
       <c r="J172" s="15" t="n">
-        <v>0</v>
+        <v>6362.92</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>0</v>
+        <v>6386.3</v>
       </c>
       <c r="L172" s="16">
         <f>F172*(K172-J172)</f>
@@ -6721,10 +6721,10 @@
         </is>
       </c>
       <c r="E174" s="14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F174" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G174" s="14" t="n">
         <v>5405</v>
@@ -6736,10 +6736,10 @@
         <v>4918</v>
       </c>
       <c r="J174" s="15" t="n">
-        <v>0</v>
+        <v>3860.57</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>0</v>
+        <v>4868</v>
       </c>
       <c r="L174" s="16">
         <f>F174*(K174-J174)</f>
@@ -7076,10 +7076,10 @@
         </is>
       </c>
       <c r="E184" s="14" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="F184" s="14" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="G184" s="14" t="n">
         <v>5811</v>
@@ -7091,12 +7091,12 @@
         <v>1435</v>
       </c>
       <c r="J184" s="15" t="n">
-        <v>0</v>
+        <v>251.58</v>
       </c>
       <c r="K184" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L184" s="16">
+        <v>251.52</v>
+      </c>
+      <c r="L184" s="17">
         <f>F184*(K184-J184)</f>
         <v/>
       </c>
@@ -7303,10 +7303,10 @@
         </is>
       </c>
       <c r="E190" s="14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F190" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G190" s="14" t="n">
         <v>11130</v>
@@ -7318,12 +7318,12 @@
         <v>8896</v>
       </c>
       <c r="J190" s="15" t="n">
-        <v>0</v>
+        <v>5857.84</v>
       </c>
       <c r="K190" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L190" s="16">
+        <v>5586.25</v>
+      </c>
+      <c r="L190" s="17">
         <f>F190*(K190-J190)</f>
         <v/>
       </c>
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="E192" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F192" s="14" t="n">
         <v>0</v>
@@ -7382,7 +7382,7 @@
         <v>6391</v>
       </c>
       <c r="J192" s="15" t="n">
-        <v>0</v>
+        <v>6392.9</v>
       </c>
       <c r="K192" s="15" t="n">
         <v>0</v>
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="E193" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F193" s="14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G193" s="14" t="n">
         <v>5840</v>
@@ -7414,10 +7414,10 @@
         <v>2058</v>
       </c>
       <c r="J193" s="15" t="n">
-        <v>0</v>
+        <v>5309</v>
       </c>
       <c r="K193" s="15" t="n">
-        <v>0</v>
+        <v>5402.86</v>
       </c>
       <c r="L193" s="16">
         <f>F193*(K193-J193)</f>
@@ -7559,10 +7559,10 @@
         </is>
       </c>
       <c r="E198" s="14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F198" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G198" s="14" t="n">
         <v>2574</v>
@@ -7574,10 +7574,10 @@
         <v>1885</v>
       </c>
       <c r="J198" s="15" t="n">
-        <v>0</v>
+        <v>677.39</v>
       </c>
       <c r="K198" s="15" t="n">
-        <v>0</v>
+        <v>689.3</v>
       </c>
       <c r="L198" s="16">
         <f>F198*(K198-J198)</f>
@@ -7796,10 +7796,10 @@
         </is>
       </c>
       <c r="E204" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F204" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G204" s="14" t="n">
         <v>5681</v>
@@ -7811,10 +7811,10 @@
         <v>4604</v>
       </c>
       <c r="J204" s="15" t="n">
-        <v>0</v>
+        <v>5164.55</v>
       </c>
       <c r="K204" s="15" t="n">
-        <v>0</v>
+        <v>5384.5</v>
       </c>
       <c r="L204" s="16">
         <f>F204*(K204-J204)</f>
@@ -7860,10 +7860,10 @@
         </is>
       </c>
       <c r="E206" s="14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F206" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" s="14" t="n">
         <v>3471</v>
@@ -7875,10 +7875,10 @@
         <v>3193</v>
       </c>
       <c r="J206" s="15" t="n">
-        <v>0</v>
+        <v>2670</v>
       </c>
       <c r="K206" s="15" t="n">
-        <v>0</v>
+        <v>2782</v>
       </c>
       <c r="L206" s="16">
         <f>F206*(K206-J206)</f>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="E207" s="14" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="F207" s="14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G207" s="14" t="n">
         <v>1980</v>
@@ -7907,10 +7907,10 @@
         <v>279</v>
       </c>
       <c r="J207" s="15" t="n">
-        <v>0</v>
+        <v>241.52</v>
       </c>
       <c r="K207" s="15" t="n">
-        <v>0</v>
+        <v>242.97</v>
       </c>
       <c r="L207" s="16">
         <f>F207*(K207-J207)</f>
@@ -8119,10 +8119,10 @@
         </is>
       </c>
       <c r="E213" s="14" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="F213" s="14" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="G213" s="14" t="n">
         <v>15547</v>
@@ -8134,12 +8134,12 @@
         <v>2060</v>
       </c>
       <c r="J213" s="15" t="n">
-        <v>0</v>
+        <v>673.04</v>
       </c>
       <c r="K213" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L213" s="16">
+        <v>671</v>
+      </c>
+      <c r="L213" s="17">
         <f>F213*(K213-J213)</f>
         <v/>
       </c>
@@ -8151,10 +8151,10 @@
         </is>
       </c>
       <c r="E214" s="14" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F214" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G214" s="14" t="n">
         <v>14003</v>
@@ -8166,10 +8166,10 @@
         <v>13126</v>
       </c>
       <c r="J214" s="15" t="n">
-        <v>0</v>
+        <v>2857.71</v>
       </c>
       <c r="K214" s="15" t="n">
-        <v>0</v>
+        <v>2924.67</v>
       </c>
       <c r="L214" s="16">
         <f>F214*(K214-J214)</f>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="E215" s="14" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F215" s="14" t="n">
         <v>0</v>
@@ -8198,7 +8198,7 @@
         <v>13902</v>
       </c>
       <c r="J215" s="15" t="n">
-        <v>0</v>
+        <v>2254.11</v>
       </c>
       <c r="K215" s="15" t="n">
         <v>0</v>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="E219" s="14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F219" s="14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G219" s="14" t="n">
         <v>8891</v>
@@ -8326,12 +8326,12 @@
         <v>1443</v>
       </c>
       <c r="J219" s="15" t="n">
-        <v>0</v>
+        <v>4041.36</v>
       </c>
       <c r="K219" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L219" s="16">
+        <v>3920.26</v>
+      </c>
+      <c r="L219" s="17">
         <f>F219*(K219-J219)</f>
         <v/>
       </c>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="E220" s="14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F220" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G220" s="14" t="n">
         <v>8756</v>
@@ -8358,10 +8358,10 @@
         <v>8221</v>
       </c>
       <c r="J220" s="15" t="n">
-        <v>0</v>
+        <v>2575.26</v>
       </c>
       <c r="K220" s="15" t="n">
-        <v>0</v>
+        <v>2675.5</v>
       </c>
       <c r="L220" s="16">
         <f>F220*(K220-J220)</f>
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="E224" s="14" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F224" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G224" s="14" t="n">
         <v>4850</v>
@@ -8521,10 +8521,10 @@
         <v>4053</v>
       </c>
       <c r="J224" s="15" t="n">
-        <v>0</v>
+        <v>1310.7</v>
       </c>
       <c r="K224" s="15" t="n">
-        <v>0</v>
+        <v>1328.67</v>
       </c>
       <c r="L224" s="16">
         <f>F224*(K224-J224)</f>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="E225" s="14" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="F225" s="14" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="G225" s="14" t="n">
         <v>4581</v>
@@ -8553,12 +8553,12 @@
         <v>989</v>
       </c>
       <c r="J225" s="15" t="n">
-        <v>0</v>
+        <v>234.92</v>
       </c>
       <c r="K225" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L225" s="16">
+        <v>234.77</v>
+      </c>
+      <c r="L225" s="17">
         <f>F225*(K225-J225)</f>
         <v/>
       </c>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="E226" s="14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F226" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G226" s="14" t="n">
         <v>4417</v>
@@ -8585,10 +8585,10 @@
         <v>3873</v>
       </c>
       <c r="J226" s="15" t="n">
-        <v>0</v>
+        <v>2208.6</v>
       </c>
       <c r="K226" s="15" t="n">
-        <v>0</v>
+        <v>2718.5</v>
       </c>
       <c r="L226" s="16">
         <f>F226*(K226-J226)</f>
@@ -8602,10 +8602,10 @@
         </is>
       </c>
       <c r="E227" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F227" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G227" s="14" t="n">
         <v>3749</v>
@@ -8617,12 +8617,12 @@
         <v>1947</v>
       </c>
       <c r="J227" s="15" t="n">
-        <v>0</v>
+        <v>3749.1</v>
       </c>
       <c r="K227" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L227" s="16">
+        <v>3603.8</v>
+      </c>
+      <c r="L227" s="17">
         <f>F227*(K227-J227)</f>
         <v/>
       </c>
@@ -8829,10 +8829,10 @@
         </is>
       </c>
       <c r="E233" s="14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F233" s="14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G233" s="14" t="n">
         <v>4132</v>
@@ -8844,12 +8844,12 @@
         <v>-1501</v>
       </c>
       <c r="J233" s="15" t="n">
-        <v>0</v>
+        <v>2582.81</v>
       </c>
       <c r="K233" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L233" s="16">
+        <v>2560.59</v>
+      </c>
+      <c r="L233" s="17">
         <f>F233*(K233-J233)</f>
         <v/>
       </c>
@@ -8925,7 +8925,7 @@
         </is>
       </c>
       <c r="E236" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F236" s="14" t="n">
         <v>0</v>
@@ -8940,7 +8940,7 @@
         <v>2780</v>
       </c>
       <c r="J236" s="15" t="n">
-        <v>0</v>
+        <v>2826.4</v>
       </c>
       <c r="K236" s="15" t="n">
         <v>0</v>
@@ -8957,10 +8957,10 @@
         </is>
       </c>
       <c r="E237" s="14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F237" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G237" s="14" t="n">
         <v>2322</v>
@@ -8972,10 +8972,10 @@
         <v>-533</v>
       </c>
       <c r="J237" s="15" t="n">
-        <v>0</v>
+        <v>2579.67</v>
       </c>
       <c r="K237" s="15" t="n">
-        <v>0</v>
+        <v>2595.18</v>
       </c>
       <c r="L237" s="16">
         <f>F237*(K237-J237)</f>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="E238" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F238" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G238" s="14" t="n">
         <v>2315</v>
@@ -9004,12 +9004,12 @@
         <v>1259</v>
       </c>
       <c r="J238" s="15" t="n">
-        <v>0</v>
+        <v>3857.83</v>
       </c>
       <c r="K238" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L238" s="16">
+        <v>3521.67</v>
+      </c>
+      <c r="L238" s="17">
         <f>F238*(K238-J238)</f>
         <v/>
       </c>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="E239" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F239" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G239" s="14" t="n">
         <v>2156</v>
@@ -9036,12 +9036,12 @@
         <v>-185</v>
       </c>
       <c r="J239" s="15" t="n">
-        <v>0</v>
+        <v>4311.6</v>
       </c>
       <c r="K239" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L239" s="16">
+        <v>3901.83</v>
+      </c>
+      <c r="L239" s="17">
         <f>F239*(K239-J239)</f>
         <v/>
       </c>
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="E241" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F241" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G241" s="14" t="n">
         <v>2093</v>
@@ -9100,10 +9100,10 @@
         <v>-542</v>
       </c>
       <c r="J241" s="15" t="n">
-        <v>0</v>
+        <v>5231.75</v>
       </c>
       <c r="K241" s="15" t="n">
-        <v>0</v>
+        <v>5270</v>
       </c>
       <c r="L241" s="16">
         <f>F241*(K241-J241)</f>
@@ -9117,10 +9117,10 @@
         </is>
       </c>
       <c r="E242" s="14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F242" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G242" s="14" t="n">
         <v>2029</v>
@@ -9132,12 +9132,12 @@
         <v>1599</v>
       </c>
       <c r="J242" s="15" t="n">
-        <v>0</v>
+        <v>2254</v>
       </c>
       <c r="K242" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L242" s="16">
+        <v>2148.5</v>
+      </c>
+      <c r="L242" s="17">
         <f>F242*(K242-J242)</f>
         <v/>
       </c>
@@ -9222,31 +9222,31 @@
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>奇鈦科(3430)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E244" s="14" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F244" s="14" t="n">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="G244" s="14" t="n">
-        <v>83</v>
+        <v>915</v>
       </c>
       <c r="H244" s="14" t="n">
-        <v>1805</v>
+        <v>1226</v>
       </c>
       <c r="I244" s="14" t="n">
-        <v>-1722</v>
+        <v>-311</v>
       </c>
       <c r="J244" s="15" t="n">
-        <v>166.4</v>
+        <v>508.11</v>
       </c>
       <c r="K244" s="15" t="n">
-        <v>164.13</v>
-      </c>
-      <c r="L244" s="17">
+        <v>510.71</v>
+      </c>
+      <c r="L244" s="16">
         <f>F244*(K244-J244)</f>
         <v/>
       </c>
@@ -9254,31 +9254,31 @@
     <row r="245" ht="16.5" customHeight="1">
       <c r="D245" s="13" t="inlineStr">
         <is>
-          <t>中美晶(5483)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E245" s="14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F245" s="14" t="n">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="G245" s="14" t="n">
-        <v>32</v>
+        <v>428</v>
       </c>
       <c r="H245" s="14" t="n">
-        <v>311</v>
+        <v>9021</v>
       </c>
       <c r="I245" s="14" t="n">
-        <v>-279</v>
+        <v>-8593</v>
       </c>
       <c r="J245" s="15" t="n">
-        <v>0</v>
+        <v>305.71</v>
       </c>
       <c r="K245" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L245" s="16">
+        <v>298.71</v>
+      </c>
+      <c r="L245" s="17">
         <f>F245*(K245-J245)</f>
         <v/>
       </c>
@@ -9286,31 +9286,31 @@
     <row r="246" ht="16.5" customHeight="1">
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>昇達科(3491)</t>
+          <t>健策(3653)</t>
         </is>
       </c>
       <c r="E246" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F246" s="14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G246" s="14" t="n">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="H246" s="14" t="n">
-        <v>567</v>
+        <v>3073</v>
       </c>
       <c r="I246" s="14" t="n">
-        <v>-567</v>
+        <v>-2674</v>
       </c>
       <c r="J246" s="15" t="n">
-        <v>0</v>
+        <v>3990</v>
       </c>
       <c r="K246" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L246" s="16">
+        <v>3841.12</v>
+      </c>
+      <c r="L246" s="17">
         <f>F246*(K246-J246)</f>
         <v/>
       </c>
@@ -9318,29 +9318,29 @@
     <row r="247" ht="16.5" customHeight="1">
       <c r="D247" s="13" t="inlineStr">
         <is>
-          <t>宜鼎(5289)</t>
+          <t>晶豪科(3006)</t>
         </is>
       </c>
       <c r="E247" s="14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F247" s="14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G247" s="14" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="H247" s="14" t="n">
-        <v>1070</v>
+        <v>717</v>
       </c>
       <c r="I247" s="14" t="n">
-        <v>-1070</v>
+        <v>-323</v>
       </c>
       <c r="J247" s="15" t="n">
-        <v>0</v>
+        <v>218.83</v>
       </c>
       <c r="K247" s="15" t="n">
-        <v>0</v>
+        <v>224.06</v>
       </c>
       <c r="L247" s="16">
         <f>F247*(K247-J247)</f>
@@ -9350,89 +9350,194 @@
     <row r="248" ht="16.5" customHeight="1">
       <c r="D248" s="13" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>昶昕(8438)</t>
         </is>
       </c>
       <c r="E248" s="14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F248" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G248" s="14" t="n">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="H248" s="14" t="n">
-        <v>564</v>
+        <v>39</v>
       </c>
       <c r="I248" s="14" t="n">
-        <v>-564</v>
+        <v>297</v>
       </c>
       <c r="J248" s="15" t="n">
-        <v>0</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="K248" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L248" s="16">
+        <v>98</v>
+      </c>
+      <c r="L248" s="17">
         <f>F248*(K248-J248)</f>
         <v/>
       </c>
     </row>
     <row r="249" ht="16.5" customHeight="1">
-      <c r="D249" s="13" t="n"/>
-      <c r="E249" s="14" t="n"/>
-      <c r="F249" s="14" t="n"/>
-      <c r="G249" s="14" t="n"/>
-      <c r="H249" s="14" t="n"/>
-      <c r="I249" s="14" t="n"/>
-      <c r="J249" s="15" t="n"/>
-      <c r="K249" s="15" t="n"/>
-      <c r="L249" s="16" t="n"/>
+      <c r="D249" s="13" t="inlineStr">
+        <is>
+          <t>辛耘(3583)</t>
+        </is>
+      </c>
+      <c r="E249" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F249" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G249" s="14" t="n">
+        <v>209</v>
+      </c>
+      <c r="H249" s="14" t="n">
+        <v>935</v>
+      </c>
+      <c r="I249" s="14" t="n">
+        <v>-726</v>
+      </c>
+      <c r="J249" s="15" t="n">
+        <v>1043.5</v>
+      </c>
+      <c r="K249" s="15" t="n">
+        <v>849.91</v>
+      </c>
+      <c r="L249" s="17">
+        <f>F249*(K249-J249)</f>
+        <v/>
+      </c>
     </row>
     <row r="250" ht="16.5" customHeight="1">
-      <c r="D250" s="13" t="n"/>
-      <c r="E250" s="14" t="n"/>
-      <c r="F250" s="14" t="n"/>
-      <c r="G250" s="14" t="n"/>
-      <c r="H250" s="14" t="n"/>
-      <c r="I250" s="14" t="n"/>
-      <c r="J250" s="15" t="n"/>
-      <c r="K250" s="15" t="n"/>
-      <c r="L250" s="16" t="n"/>
+      <c r="D250" s="13" t="inlineStr">
+        <is>
+          <t>華邦電(2344)</t>
+        </is>
+      </c>
+      <c r="E250" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F250" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="G250" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="H250" s="14" t="n">
+        <v>1207</v>
+      </c>
+      <c r="I250" s="14" t="n">
+        <v>-1115</v>
+      </c>
+      <c r="J250" s="15" t="n">
+        <v>115.12</v>
+      </c>
+      <c r="K250" s="15" t="n">
+        <v>117.17</v>
+      </c>
+      <c r="L250" s="16">
+        <f>F250*(K250-J250)</f>
+        <v/>
+      </c>
     </row>
     <row r="251" ht="16.5" customHeight="1">
-      <c r="D251" s="13" t="n"/>
-      <c r="E251" s="14" t="n"/>
-      <c r="F251" s="14" t="n"/>
-      <c r="G251" s="14" t="n"/>
-      <c r="H251" s="14" t="n"/>
-      <c r="I251" s="14" t="n"/>
-      <c r="J251" s="15" t="n"/>
-      <c r="K251" s="15" t="n"/>
-      <c r="L251" s="16" t="n"/>
+      <c r="D251" s="13" t="inlineStr">
+        <is>
+          <t>奇鈦科(3430)</t>
+        </is>
+      </c>
+      <c r="E251" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F251" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="G251" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="H251" s="14" t="n">
+        <v>1805</v>
+      </c>
+      <c r="I251" s="14" t="n">
+        <v>-1722</v>
+      </c>
+      <c r="J251" s="15" t="n">
+        <v>166.4</v>
+      </c>
+      <c r="K251" s="15" t="n">
+        <v>164.13</v>
+      </c>
+      <c r="L251" s="17">
+        <f>F251*(K251-J251)</f>
+        <v/>
+      </c>
     </row>
     <row r="252" ht="16.5" customHeight="1">
-      <c r="D252" s="13" t="n"/>
-      <c r="E252" s="14" t="n"/>
-      <c r="F252" s="14" t="n"/>
-      <c r="G252" s="14" t="n"/>
-      <c r="H252" s="14" t="n"/>
-      <c r="I252" s="14" t="n"/>
-      <c r="J252" s="15" t="n"/>
-      <c r="K252" s="15" t="n"/>
-      <c r="L252" s="16" t="n"/>
+      <c r="D252" s="13" t="inlineStr">
+        <is>
+          <t>群創(3481)</t>
+        </is>
+      </c>
+      <c r="E252" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="F252" s="14" t="n">
+        <v>341</v>
+      </c>
+      <c r="G252" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="H252" s="14" t="n">
+        <v>1098</v>
+      </c>
+      <c r="I252" s="14" t="n">
+        <v>-1016</v>
+      </c>
+      <c r="J252" s="15" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="K252" s="15" t="n">
+        <v>32.21</v>
+      </c>
+      <c r="L252" s="16">
+        <f>F252*(K252-J252)</f>
+        <v/>
+      </c>
     </row>
     <row r="253" ht="16.5" customHeight="1">
-      <c r="D253" s="13" t="n"/>
-      <c r="E253" s="14" t="n"/>
-      <c r="F253" s="14" t="n"/>
-      <c r="G253" s="14" t="n"/>
-      <c r="H253" s="14" t="n"/>
-      <c r="I253" s="14" t="n"/>
-      <c r="J253" s="15" t="n"/>
-      <c r="K253" s="15" t="n"/>
-      <c r="L253" s="16" t="n"/>
+      <c r="D253" s="13" t="inlineStr">
+        <is>
+          <t>康舒(6282)</t>
+        </is>
+      </c>
+      <c r="E253" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="F253" s="14" t="n">
+        <v>148</v>
+      </c>
+      <c r="G253" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="H253" s="14" t="n">
+        <v>817</v>
+      </c>
+      <c r="I253" s="14" t="n">
+        <v>-749</v>
+      </c>
+      <c r="J253" s="15" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="K253" s="15" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="L253" s="16">
+        <f>F253*(K253-J253)</f>
+        <v/>
+      </c>
     </row>
     <row r="254" ht="16.5" customHeight="1">
       <c r="B254" s="12" t="inlineStr">
@@ -9504,31 +9609,31 @@
       </c>
       <c r="D255" s="13" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E255" s="14" t="n">
-        <v>2622</v>
+        <v>30730</v>
       </c>
       <c r="F255" s="14" t="n">
-        <v>110</v>
+        <v>212</v>
       </c>
       <c r="G255" s="14" t="n">
-        <v>69330</v>
+        <v>360984</v>
       </c>
       <c r="H255" s="14" t="n">
-        <v>2909</v>
+        <v>2439</v>
       </c>
       <c r="I255" s="14" t="n">
-        <v>66421</v>
+        <v>358545</v>
       </c>
       <c r="J255" s="15" t="n">
-        <v>264.42</v>
+        <v>117.47</v>
       </c>
       <c r="K255" s="15" t="n">
-        <v>264.44</v>
-      </c>
-      <c r="L255" s="16">
+        <v>115.05</v>
+      </c>
+      <c r="L255" s="17">
         <f>F255*(K255-J255)</f>
         <v/>
       </c>
@@ -9536,29 +9641,29 @@
     <row r="256" ht="16.5" customHeight="1">
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>川湖(2059)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E256" s="14" t="n">
-        <v>0</v>
+        <v>101621</v>
       </c>
       <c r="F256" s="14" t="n">
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="G256" s="14" t="n">
-        <v>31003</v>
+        <v>328208</v>
       </c>
       <c r="H256" s="14" t="n">
-        <v>1636</v>
+        <v>1773</v>
       </c>
       <c r="I256" s="14" t="n">
-        <v>29367</v>
+        <v>326435</v>
       </c>
       <c r="J256" s="15" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="K256" s="15" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="L256" s="16">
         <f>F256*(K256-J256)</f>
@@ -9568,29 +9673,29 @@
     <row r="257" ht="16.5" customHeight="1">
       <c r="D257" s="13" t="inlineStr">
         <is>
-          <t>昇達科(3491)</t>
+          <t>文曄(3036)</t>
         </is>
       </c>
       <c r="E257" s="14" t="n">
-        <v>0</v>
+        <v>2622</v>
       </c>
       <c r="F257" s="14" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G257" s="14" t="n">
-        <v>28492</v>
+        <v>69330</v>
       </c>
       <c r="H257" s="14" t="n">
-        <v>11444</v>
+        <v>2909</v>
       </c>
       <c r="I257" s="14" t="n">
-        <v>17048</v>
+        <v>66421</v>
       </c>
       <c r="J257" s="15" t="n">
-        <v>0</v>
+        <v>264.42</v>
       </c>
       <c r="K257" s="15" t="n">
-        <v>0</v>
+        <v>264.44</v>
       </c>
       <c r="L257" s="16">
         <f>F257*(K257-J257)</f>
@@ -9600,31 +9705,31 @@
     <row r="258" ht="16.5" customHeight="1">
       <c r="D258" s="13" t="inlineStr">
         <is>
-          <t>中美晶(5483)</t>
+          <t>創意(3443)</t>
         </is>
       </c>
       <c r="E258" s="14" t="n">
-        <v>1782</v>
+        <v>64</v>
       </c>
       <c r="F258" s="14" t="n">
-        <v>336</v>
+        <v>40</v>
       </c>
       <c r="G258" s="14" t="n">
-        <v>27885</v>
+        <v>36820</v>
       </c>
       <c r="H258" s="14" t="n">
-        <v>5400</v>
+        <v>22808</v>
       </c>
       <c r="I258" s="14" t="n">
-        <v>22485</v>
+        <v>14012</v>
       </c>
       <c r="J258" s="15" t="n">
-        <v>156.48</v>
+        <v>5753.09</v>
       </c>
       <c r="K258" s="15" t="n">
-        <v>160.73</v>
-      </c>
-      <c r="L258" s="16">
+        <v>5701.88</v>
+      </c>
+      <c r="L258" s="17">
         <f>F258*(K258-J258)</f>
         <v/>
       </c>
@@ -9632,29 +9737,29 @@
     <row r="259" ht="16.5" customHeight="1">
       <c r="D259" s="13" t="inlineStr">
         <is>
-          <t>勤誠(8210)</t>
+          <t>昇達科(3491)</t>
         </is>
       </c>
       <c r="E259" s="14" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="F259" s="14" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G259" s="14" t="n">
-        <v>25941</v>
+        <v>28492</v>
       </c>
       <c r="H259" s="14" t="n">
-        <v>17216</v>
+        <v>11444</v>
       </c>
       <c r="I259" s="14" t="n">
-        <v>8725</v>
+        <v>17048</v>
       </c>
       <c r="J259" s="15" t="n">
-        <v>0</v>
+        <v>1814.78</v>
       </c>
       <c r="K259" s="15" t="n">
-        <v>0</v>
+        <v>1816.59</v>
       </c>
       <c r="L259" s="16">
         <f>F259*(K259-J259)</f>
@@ -9664,31 +9769,31 @@
     <row r="260" ht="16.5" customHeight="1">
       <c r="D260" s="13" t="inlineStr">
         <is>
-          <t>禾伸堂(3026)</t>
+          <t>中美晶(5483)</t>
         </is>
       </c>
       <c r="E260" s="14" t="n">
-        <v>505</v>
+        <v>1782</v>
       </c>
       <c r="F260" s="14" t="n">
-        <v>121</v>
+        <v>336</v>
       </c>
       <c r="G260" s="14" t="n">
-        <v>17181</v>
+        <v>27885</v>
       </c>
       <c r="H260" s="14" t="n">
-        <v>4020</v>
+        <v>5400</v>
       </c>
       <c r="I260" s="14" t="n">
-        <v>13161</v>
+        <v>22485</v>
       </c>
       <c r="J260" s="15" t="n">
-        <v>340.21</v>
+        <v>156.48</v>
       </c>
       <c r="K260" s="15" t="n">
-        <v>332.25</v>
-      </c>
-      <c r="L260" s="17">
+        <v>160.73</v>
+      </c>
+      <c r="L260" s="16">
         <f>F260*(K260-J260)</f>
         <v/>
       </c>
@@ -9696,29 +9801,29 @@
     <row r="261" ht="16.5" customHeight="1">
       <c r="D261" s="13" t="inlineStr">
         <is>
-          <t>台表科(6278)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E261" s="14" t="n">
-        <v>584</v>
+        <v>167</v>
       </c>
       <c r="F261" s="14" t="n">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="G261" s="14" t="n">
-        <v>12458</v>
+        <v>25941</v>
       </c>
       <c r="H261" s="14" t="n">
-        <v>1215</v>
+        <v>17216</v>
       </c>
       <c r="I261" s="14" t="n">
-        <v>11243</v>
+        <v>8725</v>
       </c>
       <c r="J261" s="15" t="n">
-        <v>213.33</v>
+        <v>1553.35</v>
       </c>
       <c r="K261" s="15" t="n">
-        <v>209.47</v>
+        <v>1550.99</v>
       </c>
       <c r="L261" s="17">
         <f>F261*(K261-J261)</f>
@@ -9728,29 +9833,29 @@
     <row r="262" ht="16.5" customHeight="1">
       <c r="D262" s="13" t="inlineStr">
         <is>
-          <t>瑞昱(2379)</t>
+          <t>健策(3653)</t>
         </is>
       </c>
       <c r="E262" s="14" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F262" s="14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G262" s="14" t="n">
-        <v>1543</v>
+        <v>21220</v>
       </c>
       <c r="H262" s="14" t="n">
-        <v>11576</v>
+        <v>7245</v>
       </c>
       <c r="I262" s="14" t="n">
-        <v>-10033</v>
+        <v>13975</v>
       </c>
       <c r="J262" s="15" t="n">
-        <v>0</v>
+        <v>4003.68</v>
       </c>
       <c r="K262" s="15" t="n">
-        <v>0</v>
+        <v>4025.17</v>
       </c>
       <c r="L262" s="16">
         <f>F262*(K262-J262)</f>
@@ -9760,31 +9865,31 @@
     <row r="263" ht="16.5" customHeight="1">
       <c r="D263" s="13" t="inlineStr">
         <is>
-          <t>聯詠(3034)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E263" s="14" t="n">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="F263" s="14" t="n">
-        <v>0</v>
+        <v>4259</v>
       </c>
       <c r="G263" s="14" t="n">
-        <v>108</v>
+        <v>17015</v>
       </c>
       <c r="H263" s="14" t="n">
-        <v>10836</v>
+        <v>127950</v>
       </c>
       <c r="I263" s="14" t="n">
-        <v>-10728</v>
+        <v>-110935</v>
       </c>
       <c r="J263" s="15" t="n">
-        <v>0</v>
+        <v>300.62</v>
       </c>
       <c r="K263" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L263" s="16">
+        <v>300.42</v>
+      </c>
+      <c r="L263" s="17">
         <f>F263*(K263-J263)</f>
         <v/>
       </c>
@@ -9792,31 +9897,31 @@
     <row r="264" ht="16.5" customHeight="1">
       <c r="D264" s="13" t="inlineStr">
         <is>
-          <t>大聯大(3702)</t>
+          <t>中砂(1560)</t>
         </is>
       </c>
       <c r="E264" s="14" t="n">
-        <v>446</v>
+        <v>93</v>
       </c>
       <c r="F264" s="14" t="n">
-        <v>7</v>
+        <v>745</v>
       </c>
       <c r="G264" s="14" t="n">
-        <v>0</v>
+        <v>5850</v>
       </c>
       <c r="H264" s="14" t="n">
-        <v>0</v>
+        <v>46853</v>
       </c>
       <c r="I264" s="14" t="n">
-        <v>0</v>
+        <v>-41003</v>
       </c>
       <c r="J264" s="15" t="n">
-        <v>0</v>
+        <v>629</v>
       </c>
       <c r="K264" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L264" s="16">
+        <v>628.9</v>
+      </c>
+      <c r="L264" s="17">
         <f>F264*(K264-J264)</f>
         <v/>
       </c>
@@ -9891,31 +9996,31 @@
       </c>
       <c r="D266" s="13" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E266" s="14" t="n">
-        <v>0</v>
+        <v>7837</v>
       </c>
       <c r="F266" s="14" t="n">
-        <v>0</v>
+        <v>1573</v>
       </c>
       <c r="G266" s="14" t="n">
-        <v>72645</v>
+        <v>235855</v>
       </c>
       <c r="H266" s="14" t="n">
-        <v>5632</v>
+        <v>47190</v>
       </c>
       <c r="I266" s="14" t="n">
-        <v>67013</v>
+        <v>188665</v>
       </c>
       <c r="J266" s="15" t="n">
-        <v>0</v>
+        <v>300.95</v>
       </c>
       <c r="K266" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L266" s="16">
+        <v>300</v>
+      </c>
+      <c r="L266" s="17">
         <f>F266*(K266-J266)</f>
         <v/>
       </c>
@@ -9923,29 +10028,29 @@
     <row r="267" ht="16.5" customHeight="1">
       <c r="D267" s="13" t="inlineStr">
         <is>
-          <t>中美晶(5483)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E267" s="14" t="n">
-        <v>3667</v>
+        <v>39161</v>
       </c>
       <c r="F267" s="14" t="n">
-        <v>279</v>
+        <v>719</v>
       </c>
       <c r="G267" s="14" t="n">
-        <v>59828</v>
+        <v>126131</v>
       </c>
       <c r="H267" s="14" t="n">
-        <v>4330</v>
+        <v>2297</v>
       </c>
       <c r="I267" s="14" t="n">
-        <v>55498</v>
+        <v>123834</v>
       </c>
       <c r="J267" s="15" t="n">
-        <v>163.15</v>
+        <v>32.21</v>
       </c>
       <c r="K267" s="15" t="n">
-        <v>155.19</v>
+        <v>31.94</v>
       </c>
       <c r="L267" s="17">
         <f>F267*(K267-J267)</f>
@@ -9955,31 +10060,31 @@
     <row r="268" ht="16.5" customHeight="1">
       <c r="D268" s="13" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E268" s="14" t="n">
-        <v>2115</v>
+        <v>272</v>
       </c>
       <c r="F268" s="14" t="n">
-        <v>709</v>
+        <v>21</v>
       </c>
       <c r="G268" s="14" t="n">
-        <v>55936</v>
+        <v>72645</v>
       </c>
       <c r="H268" s="14" t="n">
-        <v>18665</v>
+        <v>5632</v>
       </c>
       <c r="I268" s="14" t="n">
-        <v>37271</v>
+        <v>67013</v>
       </c>
       <c r="J268" s="15" t="n">
-        <v>264.47</v>
+        <v>2670.76</v>
       </c>
       <c r="K268" s="15" t="n">
-        <v>263.26</v>
-      </c>
-      <c r="L268" s="17">
+        <v>2681.81</v>
+      </c>
+      <c r="L268" s="16">
         <f>F268*(K268-J268)</f>
         <v/>
       </c>
@@ -9987,31 +10092,31 @@
     <row r="269" ht="16.5" customHeight="1">
       <c r="D269" s="13" t="inlineStr">
         <is>
-          <t>宜鼎(5289)</t>
+          <t>晶豪科(3006)</t>
         </is>
       </c>
       <c r="E269" s="14" t="n">
-        <v>0</v>
+        <v>2883</v>
       </c>
       <c r="F269" s="14" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="G269" s="14" t="n">
-        <v>49285</v>
+        <v>63762</v>
       </c>
       <c r="H269" s="14" t="n">
-        <v>13014</v>
+        <v>3288</v>
       </c>
       <c r="I269" s="14" t="n">
-        <v>36271</v>
+        <v>60474</v>
       </c>
       <c r="J269" s="15" t="n">
-        <v>0</v>
+        <v>221.17</v>
       </c>
       <c r="K269" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L269" s="16">
+        <v>214.9</v>
+      </c>
+      <c r="L269" s="17">
         <f>F269*(K269-J269)</f>
         <v/>
       </c>
@@ -10019,31 +10124,31 @@
     <row r="270" ht="16.5" customHeight="1">
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>譜瑞-KY(4966)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E270" s="14" t="n">
-        <v>0</v>
+        <v>5209</v>
       </c>
       <c r="F270" s="14" t="n">
-        <v>0</v>
+        <v>2192</v>
       </c>
       <c r="G270" s="14" t="n">
-        <v>42887</v>
+        <v>61080</v>
       </c>
       <c r="H270" s="14" t="n">
-        <v>1470</v>
+        <v>25317</v>
       </c>
       <c r="I270" s="14" t="n">
-        <v>41417</v>
+        <v>35763</v>
       </c>
       <c r="J270" s="15" t="n">
-        <v>0</v>
+        <v>117.26</v>
       </c>
       <c r="K270" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L270" s="16">
+        <v>115.5</v>
+      </c>
+      <c r="L270" s="17">
         <f>F270*(K270-J270)</f>
         <v/>
       </c>
@@ -10051,29 +10156,29 @@
     <row r="271" ht="16.5" customHeight="1">
       <c r="D271" s="13" t="inlineStr">
         <is>
-          <t>台表科(6278)</t>
+          <t>中美晶(5483)</t>
         </is>
       </c>
       <c r="E271" s="14" t="n">
-        <v>1082</v>
+        <v>3667</v>
       </c>
       <c r="F271" s="14" t="n">
-        <v>2284</v>
+        <v>279</v>
       </c>
       <c r="G271" s="14" t="n">
-        <v>23254</v>
+        <v>59828</v>
       </c>
       <c r="H271" s="14" t="n">
-        <v>46088</v>
+        <v>4330</v>
       </c>
       <c r="I271" s="14" t="n">
-        <v>-22834</v>
+        <v>55498</v>
       </c>
       <c r="J271" s="15" t="n">
-        <v>214.92</v>
+        <v>163.15</v>
       </c>
       <c r="K271" s="15" t="n">
-        <v>201.79</v>
+        <v>155.19</v>
       </c>
       <c r="L271" s="17">
         <f>F271*(K271-J271)</f>
@@ -10083,31 +10188,31 @@
     <row r="272" ht="16.5" customHeight="1">
       <c r="D272" s="13" t="inlineStr">
         <is>
-          <t>勤誠(8210)</t>
+          <t>文曄(3036)</t>
         </is>
       </c>
       <c r="E272" s="14" t="n">
-        <v>0</v>
+        <v>2115</v>
       </c>
       <c r="F272" s="14" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="G272" s="14" t="n">
-        <v>20648</v>
+        <v>55936</v>
       </c>
       <c r="H272" s="14" t="n">
-        <v>654</v>
+        <v>18665</v>
       </c>
       <c r="I272" s="14" t="n">
-        <v>19994</v>
+        <v>37271</v>
       </c>
       <c r="J272" s="15" t="n">
-        <v>0</v>
+        <v>264.47</v>
       </c>
       <c r="K272" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L272" s="16">
+        <v>263.26</v>
+      </c>
+      <c r="L272" s="17">
         <f>F272*(K272-J272)</f>
         <v/>
       </c>
@@ -10115,29 +10220,29 @@
     <row r="273" ht="16.5" customHeight="1">
       <c r="D273" s="13" t="inlineStr">
         <is>
-          <t>聯詠(3034)</t>
+          <t>宜鼎(5289)</t>
         </is>
       </c>
       <c r="E273" s="14" t="n">
-        <v>51</v>
+        <v>280</v>
       </c>
       <c r="F273" s="14" t="n">
-        <v>839</v>
+        <v>74</v>
       </c>
       <c r="G273" s="14" t="n">
-        <v>2553</v>
+        <v>49285</v>
       </c>
       <c r="H273" s="14" t="n">
-        <v>41775</v>
+        <v>13014</v>
       </c>
       <c r="I273" s="14" t="n">
-        <v>-39222</v>
+        <v>36271</v>
       </c>
       <c r="J273" s="15" t="n">
-        <v>500.53</v>
+        <v>1760.19</v>
       </c>
       <c r="K273" s="15" t="n">
-        <v>497.91</v>
+        <v>1758.7</v>
       </c>
       <c r="L273" s="17">
         <f>F273*(K273-J273)</f>
@@ -10147,29 +10252,29 @@
     <row r="274" ht="16.5" customHeight="1">
       <c r="D274" s="13" t="inlineStr">
         <is>
-          <t>順德(2351)</t>
+          <t>譜瑞-KY(4966)</t>
         </is>
       </c>
       <c r="E274" s="14" t="n">
-        <v>117</v>
+        <v>584</v>
       </c>
       <c r="F274" s="14" t="n">
-        <v>2013</v>
+        <v>20</v>
       </c>
       <c r="G274" s="14" t="n">
-        <v>2166</v>
+        <v>42887</v>
       </c>
       <c r="H274" s="14" t="n">
-        <v>37540</v>
+        <v>1470</v>
       </c>
       <c r="I274" s="14" t="n">
-        <v>-35374</v>
+        <v>41417</v>
       </c>
       <c r="J274" s="15" t="n">
-        <v>185.1</v>
+        <v>734.37</v>
       </c>
       <c r="K274" s="15" t="n">
-        <v>186.49</v>
+        <v>735.1</v>
       </c>
       <c r="L274" s="16">
         <f>F274*(K274-J274)</f>
@@ -10179,29 +10284,29 @@
     <row r="275" ht="16.5" customHeight="1">
       <c r="D275" s="13" t="inlineStr">
         <is>
-          <t>立隆電(2472)</t>
+          <t>強茂(2481)</t>
         </is>
       </c>
       <c r="E275" s="14" t="n">
-        <v>51</v>
+        <v>3172</v>
       </c>
       <c r="F275" s="14" t="n">
-        <v>821</v>
+        <v>22</v>
       </c>
       <c r="G275" s="14" t="n">
-        <v>1134</v>
+        <v>34554</v>
       </c>
       <c r="H275" s="14" t="n">
-        <v>17660</v>
+        <v>233</v>
       </c>
       <c r="I275" s="14" t="n">
-        <v>-16526</v>
+        <v>34321</v>
       </c>
       <c r="J275" s="15" t="n">
-        <v>222.35</v>
+        <v>108.93</v>
       </c>
       <c r="K275" s="15" t="n">
-        <v>215.1</v>
+        <v>105.86</v>
       </c>
       <c r="L275" s="17">
         <f>F275*(K275-J275)</f>
@@ -10324,10 +10429,10 @@
         </is>
       </c>
       <c r="E278" s="14" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F278" s="14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G278" s="14" t="n">
         <v>13793</v>
@@ -10339,12 +10444,12 @@
         <v>10705</v>
       </c>
       <c r="J278" s="15" t="n">
-        <v>0</v>
+        <v>2224.61</v>
       </c>
       <c r="K278" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L278" s="16">
+        <v>2205.93</v>
+      </c>
+      <c r="L278" s="17">
         <f>F278*(K278-J278)</f>
         <v/>
       </c>
@@ -10753,10 +10858,10 @@
         </is>
       </c>
       <c r="E290" s="14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F290" s="14" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G290" s="14" t="n">
         <v>14676</v>
@@ -10768,12 +10873,12 @@
         <v>-9895</v>
       </c>
       <c r="J290" s="15" t="n">
-        <v>0</v>
+        <v>6380.83</v>
       </c>
       <c r="K290" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L290" s="16">
+        <v>6300.21</v>
+      </c>
+      <c r="L290" s="17">
         <f>F290*(K290-J290)</f>
         <v/>
       </c>
@@ -11108,10 +11213,10 @@
         </is>
       </c>
       <c r="E300" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F300" s="14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G300" s="14" t="n">
         <v>3376</v>
@@ -11123,10 +11228,10 @@
         <v>-5434</v>
       </c>
       <c r="J300" s="15" t="n">
-        <v>0</v>
+        <v>5626</v>
       </c>
       <c r="K300" s="15" t="n">
-        <v>0</v>
+        <v>5873.47</v>
       </c>
       <c r="L300" s="16">
         <f>F300*(K300-J300)</f>
@@ -11172,10 +11277,10 @@
         </is>
       </c>
       <c r="E302" s="14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F302" s="14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G302" s="14" t="n">
         <v>3003</v>
@@ -11187,12 +11292,12 @@
         <v>-4604</v>
       </c>
       <c r="J302" s="15" t="n">
-        <v>0</v>
+        <v>2309.77</v>
       </c>
       <c r="K302" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L302" s="16">
+        <v>2237.26</v>
+      </c>
+      <c r="L302" s="17">
         <f>F302*(K302-J302)</f>
         <v/>
       </c>
@@ -11204,10 +11309,10 @@
         </is>
       </c>
       <c r="E303" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F303" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G303" s="14" t="n">
         <v>1935</v>
@@ -11219,10 +11324,10 @@
         <v>374</v>
       </c>
       <c r="J303" s="15" t="n">
-        <v>0</v>
+        <v>3870.2</v>
       </c>
       <c r="K303" s="15" t="n">
-        <v>0</v>
+        <v>3903.5</v>
       </c>
       <c r="L303" s="16">
         <f>F303*(K303-J303)</f>
@@ -11236,10 +11341,10 @@
         </is>
       </c>
       <c r="E304" s="14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F304" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G304" s="14" t="n">
         <v>1875</v>
@@ -11251,10 +11356,10 @@
         <v>1675</v>
       </c>
       <c r="J304" s="15" t="n">
-        <v>0</v>
+        <v>852.23</v>
       </c>
       <c r="K304" s="15" t="n">
-        <v>0</v>
+        <v>1001.5</v>
       </c>
       <c r="L304" s="16">
         <f>F304*(K304-J304)</f>
@@ -11268,10 +11373,10 @@
         </is>
       </c>
       <c r="E305" s="14" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F305" s="14" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G305" s="14" t="n">
         <v>1798</v>
@@ -11283,12 +11388,12 @@
         <v>490</v>
       </c>
       <c r="J305" s="15" t="n">
-        <v>0</v>
+        <v>243.01</v>
       </c>
       <c r="K305" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L305" s="16">
+        <v>242.3</v>
+      </c>
+      <c r="L305" s="17">
         <f>F305*(K305-J305)</f>
         <v/>
       </c>
@@ -11300,7 +11405,7 @@
         </is>
       </c>
       <c r="E306" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F306" s="14" t="n">
         <v>0</v>
@@ -11315,7 +11420,7 @@
         <v>1620</v>
       </c>
       <c r="J306" s="15" t="n">
-        <v>0</v>
+        <v>5443.67</v>
       </c>
       <c r="K306" s="15" t="n">
         <v>0</v>
@@ -11364,10 +11469,10 @@
         </is>
       </c>
       <c r="E308" s="14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F308" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G308" s="14" t="n">
         <v>1231</v>
@@ -11379,10 +11484,10 @@
         <v>452</v>
       </c>
       <c r="J308" s="15" t="n">
-        <v>0</v>
+        <v>1538.75</v>
       </c>
       <c r="K308" s="15" t="n">
-        <v>0</v>
+        <v>1557.6</v>
       </c>
       <c r="L308" s="16">
         <f>F308*(K308-J308)</f>
@@ -11463,10 +11568,10 @@
         </is>
       </c>
       <c r="E310" s="14" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F310" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G310" s="14" t="n">
         <v>9463</v>
@@ -11478,12 +11583,12 @@
         <v>8842</v>
       </c>
       <c r="J310" s="15" t="n">
-        <v>0</v>
+        <v>2253.17</v>
       </c>
       <c r="K310" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L310" s="16">
+        <v>2070.67</v>
+      </c>
+      <c r="L310" s="17">
         <f>F310*(K310-J310)</f>
         <v/>
       </c>
@@ -11559,10 +11664,10 @@
         </is>
       </c>
       <c r="E313" s="14" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F313" s="14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G313" s="14" t="n">
         <v>3839</v>
@@ -11574,12 +11679,12 @@
         <v>2232</v>
       </c>
       <c r="J313" s="15" t="n">
-        <v>0</v>
+        <v>673.49</v>
       </c>
       <c r="K313" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L313" s="16">
+        <v>669.62</v>
+      </c>
+      <c r="L313" s="17">
         <f>F313*(K313-J313)</f>
         <v/>
       </c>
@@ -11623,10 +11728,10 @@
         </is>
       </c>
       <c r="E315" s="14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F315" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G315" s="14" t="n">
         <v>2814</v>
@@ -11638,10 +11743,10 @@
         <v>2282</v>
       </c>
       <c r="J315" s="15" t="n">
-        <v>0</v>
+        <v>4019.43</v>
       </c>
       <c r="K315" s="15" t="n">
-        <v>0</v>
+        <v>5315</v>
       </c>
       <c r="L315" s="16">
         <f>F315*(K315-J315)</f>
@@ -11719,10 +11824,10 @@
         </is>
       </c>
       <c r="E318" s="14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F318" s="14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G318" s="14" t="n">
         <v>2166</v>
@@ -11734,10 +11839,10 @@
         <v>509</v>
       </c>
       <c r="J318" s="15" t="n">
-        <v>0</v>
+        <v>902.46</v>
       </c>
       <c r="K318" s="15" t="n">
-        <v>0</v>
+        <v>920.61</v>
       </c>
       <c r="L318" s="16">
         <f>F318*(K318-J318)</f>
@@ -11850,10 +11955,10 @@
         </is>
       </c>
       <c r="E321" s="14" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F321" s="14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G321" s="14" t="n">
         <v>16529</v>
@@ -11865,10 +11970,10 @@
         <v>13416</v>
       </c>
       <c r="J321" s="15" t="n">
-        <v>0</v>
+        <v>3843.91</v>
       </c>
       <c r="K321" s="15" t="n">
-        <v>0</v>
+        <v>3890.75</v>
       </c>
       <c r="L321" s="16">
         <f>F321*(K321-J321)</f>
@@ -11882,10 +11987,10 @@
         </is>
       </c>
       <c r="E322" s="14" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F322" s="14" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G322" s="14" t="n">
         <v>15862</v>
@@ -11897,10 +12002,10 @@
         <v>1772</v>
       </c>
       <c r="J322" s="15" t="n">
-        <v>0</v>
+        <v>2234.03</v>
       </c>
       <c r="K322" s="15" t="n">
-        <v>0</v>
+        <v>2236.56</v>
       </c>
       <c r="L322" s="16">
         <f>F322*(K322-J322)</f>
@@ -12010,10 +12115,10 @@
         </is>
       </c>
       <c r="E326" s="14" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F326" s="14" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G326" s="14" t="n">
         <v>6063</v>
@@ -12025,12 +12130,12 @@
         <v>1000</v>
       </c>
       <c r="J326" s="15" t="n">
-        <v>0</v>
+        <v>1837.3</v>
       </c>
       <c r="K326" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L326" s="16">
+        <v>1808.25</v>
+      </c>
+      <c r="L326" s="17">
         <f>F326*(K326-J326)</f>
         <v/>
       </c>
@@ -12042,10 +12147,10 @@
         </is>
       </c>
       <c r="E327" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F327" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G327" s="14" t="n">
         <v>5885</v>
@@ -12057,10 +12162,10 @@
         <v>2570</v>
       </c>
       <c r="J327" s="15" t="n">
-        <v>0</v>
+        <v>5349.91</v>
       </c>
       <c r="K327" s="15" t="n">
-        <v>0</v>
+        <v>5524.67</v>
       </c>
       <c r="L327" s="16">
         <f>F327*(K327-J327)</f>
@@ -12269,10 +12374,10 @@
         </is>
       </c>
       <c r="E333" s="14" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="F333" s="14" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G333" s="14" t="n">
         <v>4938</v>
@@ -12284,12 +12389,12 @@
         <v>1207</v>
       </c>
       <c r="J333" s="15" t="n">
-        <v>0</v>
+        <v>461.49</v>
       </c>
       <c r="K333" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L333" s="16">
+        <v>460.57</v>
+      </c>
+      <c r="L333" s="17">
         <f>F333*(K333-J333)</f>
         <v/>
       </c>
@@ -12429,10 +12534,10 @@
         </is>
       </c>
       <c r="E338" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F338" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G338" s="14" t="n">
         <v>2516</v>
@@ -12444,12 +12549,12 @@
         <v>1532</v>
       </c>
       <c r="J338" s="15" t="n">
-        <v>0</v>
+        <v>5031.8</v>
       </c>
       <c r="K338" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L338" s="16">
+        <v>4917.5</v>
+      </c>
+      <c r="L338" s="17">
         <f>F338*(K338-J338)</f>
         <v/>
       </c>
@@ -12521,29 +12626,29 @@
     <row r="341" ht="16.5" customHeight="1">
       <c r="D341" s="13" t="inlineStr">
         <is>
-          <t>華通(2313)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E341" s="14" t="n">
-        <v>82</v>
+        <v>633</v>
       </c>
       <c r="F341" s="14" t="n">
-        <v>41</v>
+        <v>570</v>
       </c>
       <c r="G341" s="14" t="n">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="H341" s="14" t="n">
-        <v>1030</v>
+        <v>1841</v>
       </c>
       <c r="I341" s="14" t="n">
-        <v>1000</v>
+        <v>204</v>
       </c>
       <c r="J341" s="15" t="n">
-        <v>247.59</v>
+        <v>32.3</v>
       </c>
       <c r="K341" s="15" t="n">
-        <v>251.27</v>
+        <v>32.3</v>
       </c>
       <c r="L341" s="16">
         <f>F341*(K341-J341)</f>
@@ -12848,10 +12953,10 @@
         </is>
       </c>
       <c r="E350" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F350" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G350" s="14" t="n">
         <v>1698</v>
@@ -12863,12 +12968,12 @@
         <v>-494</v>
       </c>
       <c r="J350" s="15" t="n">
-        <v>0</v>
+        <v>5661.33</v>
       </c>
       <c r="K350" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L350" s="16">
+        <v>5478.75</v>
+      </c>
+      <c r="L350" s="17">
         <f>F350*(K350-J350)</f>
         <v/>
       </c>
@@ -12880,10 +12985,10 @@
         </is>
       </c>
       <c r="E351" s="14" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F351" s="14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G351" s="14" t="n">
         <v>1544</v>
@@ -12895,12 +13000,12 @@
         <v>374</v>
       </c>
       <c r="J351" s="15" t="n">
-        <v>0</v>
+        <v>395.85</v>
       </c>
       <c r="K351" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L351" s="16">
+        <v>389.83</v>
+      </c>
+      <c r="L351" s="17">
         <f>F351*(K351-J351)</f>
         <v/>
       </c>
@@ -13043,10 +13148,10 @@
         </is>
       </c>
       <c r="E355" s="14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F355" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G355" s="14" t="n">
         <v>5758</v>
@@ -13058,10 +13163,10 @@
         <v>4813</v>
       </c>
       <c r="J355" s="15" t="n">
-        <v>0</v>
+        <v>2214.81</v>
       </c>
       <c r="K355" s="15" t="n">
-        <v>0</v>
+        <v>2363.5</v>
       </c>
       <c r="L355" s="16">
         <f>F355*(K355-J355)</f>
@@ -13139,10 +13244,10 @@
         </is>
       </c>
       <c r="E358" s="14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F358" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G358" s="14" t="n">
         <v>1749</v>
@@ -13154,10 +13259,10 @@
         <v>1643</v>
       </c>
       <c r="J358" s="15" t="n">
-        <v>0</v>
+        <v>920.63</v>
       </c>
       <c r="K358" s="15" t="n">
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="L358" s="16">
         <f>F358*(K358-J358)</f>
@@ -13203,10 +13308,10 @@
         </is>
       </c>
       <c r="E360" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F360" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G360" s="14" t="n">
         <v>1387</v>
@@ -13218,10 +13323,10 @@
         <v>304</v>
       </c>
       <c r="J360" s="15" t="n">
-        <v>0</v>
+        <v>4622.67</v>
       </c>
       <c r="K360" s="15" t="n">
-        <v>0</v>
+        <v>5415.5</v>
       </c>
       <c r="L360" s="16">
         <f>F360*(K360-J360)</f>
@@ -13299,10 +13404,10 @@
         </is>
       </c>
       <c r="E363" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F363" s="14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G363" s="14" t="n">
         <v>1227</v>
@@ -13314,12 +13419,12 @@
         <v>-1555</v>
       </c>
       <c r="J363" s="15" t="n">
-        <v>0</v>
+        <v>4091.33</v>
       </c>
       <c r="K363" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L363" s="16">
+        <v>3974.14</v>
+      </c>
+      <c r="L363" s="17">
         <f>F363*(K363-J363)</f>
         <v/>
       </c>
@@ -13468,29 +13573,29 @@
     <row r="367" ht="16.5" customHeight="1">
       <c r="D367" s="13" t="inlineStr">
         <is>
-          <t>宜鼎(5289)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E367" s="14" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="F367" s="14" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="G367" s="14" t="n">
-        <v>3489</v>
+        <v>5223</v>
       </c>
       <c r="H367" s="14" t="n">
-        <v>4715</v>
+        <v>5877</v>
       </c>
       <c r="I367" s="14" t="n">
-        <v>-1226</v>
+        <v>-654</v>
       </c>
       <c r="J367" s="15" t="n">
-        <v>0</v>
+        <v>300.16</v>
       </c>
       <c r="K367" s="15" t="n">
-        <v>0</v>
+        <v>301.36</v>
       </c>
       <c r="L367" s="16">
         <f>F367*(K367-J367)</f>
@@ -13500,31 +13605,31 @@
     <row r="368" ht="16.5" customHeight="1">
       <c r="D368" s="13" t="inlineStr">
         <is>
-          <t>家登(3680)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E368" s="14" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="F368" s="14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G368" s="14" t="n">
-        <v>1154</v>
+        <v>3874</v>
       </c>
       <c r="H368" s="14" t="n">
-        <v>559</v>
+        <v>826</v>
       </c>
       <c r="I368" s="14" t="n">
-        <v>595</v>
+        <v>3048</v>
       </c>
       <c r="J368" s="15" t="n">
-        <v>0</v>
+        <v>490.38</v>
       </c>
       <c r="K368" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L368" s="16">
+        <v>486.06</v>
+      </c>
+      <c r="L368" s="17">
         <f>F368*(K368-J368)</f>
         <v/>
       </c>
@@ -13532,29 +13637,29 @@
     <row r="369" ht="16.5" customHeight="1">
       <c r="D369" s="13" t="inlineStr">
         <is>
-          <t>普萊德(6263)</t>
+          <t>宜鼎(5289)</t>
         </is>
       </c>
       <c r="E369" s="14" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F369" s="14" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="G369" s="14" t="n">
-        <v>1008</v>
+        <v>3489</v>
       </c>
       <c r="H369" s="14" t="n">
-        <v>50</v>
+        <v>4715</v>
       </c>
       <c r="I369" s="14" t="n">
-        <v>958</v>
+        <v>-1226</v>
       </c>
       <c r="J369" s="15" t="n">
-        <v>168</v>
+        <v>1744.65</v>
       </c>
       <c r="K369" s="15" t="n">
-        <v>168</v>
+        <v>1746.41</v>
       </c>
       <c r="L369" s="16">
         <f>F369*(K369-J369)</f>
@@ -13564,29 +13669,29 @@
     <row r="370" ht="16.5" customHeight="1">
       <c r="D370" s="13" t="inlineStr">
         <is>
-          <t>聯詠(3034)</t>
+          <t>鴻勁(7769)</t>
         </is>
       </c>
       <c r="E370" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F370" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G370" s="14" t="n">
-        <v>939</v>
+        <v>2954</v>
       </c>
       <c r="H370" s="14" t="n">
-        <v>60</v>
+        <v>3480</v>
       </c>
       <c r="I370" s="14" t="n">
-        <v>879</v>
+        <v>-526</v>
       </c>
       <c r="J370" s="15" t="n">
-        <v>0</v>
+        <v>5907.4</v>
       </c>
       <c r="K370" s="15" t="n">
-        <v>0</v>
+        <v>6959.6</v>
       </c>
       <c r="L370" s="16">
         <f>F370*(K370-J370)</f>
@@ -13596,29 +13701,29 @@
     <row r="371" ht="16.5" customHeight="1">
       <c r="D371" s="13" t="inlineStr">
         <is>
-          <t>信昌電(6173)</t>
+          <t>華新科(2492)</t>
         </is>
       </c>
       <c r="E371" s="14" t="n">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="F371" s="14" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G371" s="14" t="n">
-        <v>248</v>
+        <v>1529</v>
       </c>
       <c r="H371" s="14" t="n">
-        <v>847</v>
+        <v>1103</v>
       </c>
       <c r="I371" s="14" t="n">
-        <v>-599</v>
+        <v>426</v>
       </c>
       <c r="J371" s="15" t="n">
-        <v>124.05</v>
+        <v>171.82</v>
       </c>
       <c r="K371" s="15" t="n">
-        <v>126.39</v>
+        <v>172.3</v>
       </c>
       <c r="L371" s="16">
         <f>F371*(K371-J371)</f>
@@ -13628,31 +13733,31 @@
     <row r="372" ht="16.5" customHeight="1">
       <c r="D372" s="13" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>創見(2451)</t>
         </is>
       </c>
       <c r="E372" s="14" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="F372" s="14" t="n">
-        <v>176</v>
+        <v>59</v>
       </c>
       <c r="G372" s="14" t="n">
-        <v>48</v>
+        <v>1251</v>
       </c>
       <c r="H372" s="14" t="n">
-        <v>4586</v>
+        <v>2012</v>
       </c>
       <c r="I372" s="14" t="n">
-        <v>-4538</v>
+        <v>-761</v>
       </c>
       <c r="J372" s="15" t="n">
-        <v>239.5</v>
+        <v>347.58</v>
       </c>
       <c r="K372" s="15" t="n">
-        <v>260.56</v>
-      </c>
-      <c r="L372" s="16">
+        <v>340.93</v>
+      </c>
+      <c r="L372" s="17">
         <f>F372*(K372-J372)</f>
         <v/>
       </c>
@@ -13660,29 +13765,29 @@
     <row r="373" ht="16.5" customHeight="1">
       <c r="D373" s="13" t="inlineStr">
         <is>
-          <t>現觀科(6906)</t>
+          <t>康舒(6282)</t>
         </is>
       </c>
       <c r="E373" s="14" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="F373" s="14" t="n">
-        <v>74</v>
+        <v>261</v>
       </c>
       <c r="G373" s="14" t="n">
-        <v>0</v>
+        <v>1213</v>
       </c>
       <c r="H373" s="14" t="n">
-        <v>512</v>
+        <v>1446</v>
       </c>
       <c r="I373" s="14" t="n">
-        <v>-512</v>
+        <v>-233</v>
       </c>
       <c r="J373" s="15" t="n">
-        <v>0</v>
+        <v>55.4</v>
       </c>
       <c r="K373" s="15" t="n">
-        <v>69.23</v>
+        <v>55.4</v>
       </c>
       <c r="L373" s="16">
         <f>F373*(K373-J373)</f>
@@ -13690,15 +13795,36 @@
       </c>
     </row>
     <row r="374" ht="16.5" customHeight="1">
-      <c r="D374" s="13" t="n"/>
-      <c r="E374" s="14" t="n"/>
-      <c r="F374" s="14" t="n"/>
-      <c r="G374" s="14" t="n"/>
-      <c r="H374" s="14" t="n"/>
-      <c r="I374" s="14" t="n"/>
-      <c r="J374" s="15" t="n"/>
-      <c r="K374" s="15" t="n"/>
-      <c r="L374" s="16" t="n"/>
+      <c r="D374" s="13" t="inlineStr">
+        <is>
+          <t>家登(3680)</t>
+        </is>
+      </c>
+      <c r="E374" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F374" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G374" s="14" t="n">
+        <v>1154</v>
+      </c>
+      <c r="H374" s="14" t="n">
+        <v>559</v>
+      </c>
+      <c r="I374" s="14" t="n">
+        <v>595</v>
+      </c>
+      <c r="J374" s="15" t="n">
+        <v>607.42</v>
+      </c>
+      <c r="K374" s="15" t="n">
+        <v>621</v>
+      </c>
+      <c r="L374" s="16">
+        <f>F374*(K374-J374)</f>
+        <v/>
+      </c>
     </row>
     <row r="375" ht="16.5" customHeight="1">
       <c r="A375" s="12" t="inlineStr">
@@ -13780,29 +13906,29 @@
       </c>
       <c r="D376" s="13" t="inlineStr">
         <is>
-          <t>昇達科(3491)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E376" s="14" t="n">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="F376" s="14" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="G376" s="14" t="n">
-        <v>5416</v>
+        <v>23143</v>
       </c>
       <c r="H376" s="14" t="n">
-        <v>2224</v>
+        <v>19256</v>
       </c>
       <c r="I376" s="14" t="n">
-        <v>3192</v>
+        <v>3887</v>
       </c>
       <c r="J376" s="15" t="n">
-        <v>0</v>
+        <v>298.62</v>
       </c>
       <c r="K376" s="15" t="n">
-        <v>0</v>
+        <v>300.88</v>
       </c>
       <c r="L376" s="16">
         <f>F376*(K376-J376)</f>
@@ -13812,29 +13938,29 @@
     <row r="377" ht="16.5" customHeight="1">
       <c r="D377" s="13" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E377" s="14" t="n">
-        <v>201</v>
+        <v>6122</v>
       </c>
       <c r="F377" s="14" t="n">
-        <v>110</v>
+        <v>617</v>
       </c>
       <c r="G377" s="14" t="n">
-        <v>5316</v>
+        <v>19702</v>
       </c>
       <c r="H377" s="14" t="n">
-        <v>2906</v>
+        <v>1973</v>
       </c>
       <c r="I377" s="14" t="n">
-        <v>2410</v>
+        <v>17729</v>
       </c>
       <c r="J377" s="15" t="n">
-        <v>264.5</v>
+        <v>32.18</v>
       </c>
       <c r="K377" s="15" t="n">
-        <v>264.22</v>
+        <v>31.98</v>
       </c>
       <c r="L377" s="17">
         <f>F377*(K377-J377)</f>
@@ -13844,29 +13970,29 @@
     <row r="378" ht="16.5" customHeight="1">
       <c r="D378" s="13" t="inlineStr">
         <is>
-          <t>順德(2351)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E378" s="14" t="n">
-        <v>150</v>
+        <v>748</v>
       </c>
       <c r="F378" s="14" t="n">
-        <v>58</v>
+        <v>686</v>
       </c>
       <c r="G378" s="14" t="n">
-        <v>2775</v>
+        <v>8646</v>
       </c>
       <c r="H378" s="14" t="n">
-        <v>1106</v>
+        <v>7930</v>
       </c>
       <c r="I378" s="14" t="n">
-        <v>1669</v>
+        <v>716</v>
       </c>
       <c r="J378" s="15" t="n">
-        <v>185</v>
+        <v>115.59</v>
       </c>
       <c r="K378" s="15" t="n">
-        <v>190.71</v>
+        <v>115.6</v>
       </c>
       <c r="L378" s="16">
         <f>F378*(K378-J378)</f>
@@ -13876,29 +14002,29 @@
     <row r="379" ht="16.5" customHeight="1">
       <c r="D379" s="13" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>昇達科(3491)</t>
         </is>
       </c>
       <c r="E379" s="14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F379" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G379" s="14" t="n">
-        <v>1629</v>
+        <v>5416</v>
       </c>
       <c r="H379" s="14" t="n">
-        <v>277</v>
+        <v>2224</v>
       </c>
       <c r="I379" s="14" t="n">
-        <v>1352</v>
+        <v>3192</v>
       </c>
       <c r="J379" s="15" t="n">
-        <v>0</v>
+        <v>1805.47</v>
       </c>
       <c r="K379" s="15" t="n">
-        <v>0</v>
+        <v>1853.58</v>
       </c>
       <c r="L379" s="16">
         <f>F379*(K379-J379)</f>
@@ -13908,31 +14034,31 @@
     <row r="380" ht="16.5" customHeight="1">
       <c r="D380" s="13" t="inlineStr">
         <is>
-          <t>統新(6426)</t>
+          <t>文曄(3036)</t>
         </is>
       </c>
       <c r="E380" s="14" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="F380" s="14" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G380" s="14" t="n">
-        <v>803</v>
+        <v>5316</v>
       </c>
       <c r="H380" s="14" t="n">
-        <v>78</v>
+        <v>2906</v>
       </c>
       <c r="I380" s="14" t="n">
-        <v>725</v>
+        <v>2410</v>
       </c>
       <c r="J380" s="15" t="n">
-        <v>0</v>
+        <v>264.5</v>
       </c>
       <c r="K380" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L380" s="16">
+        <v>264.22</v>
+      </c>
+      <c r="L380" s="17">
         <f>F380*(K380-J380)</f>
         <v/>
       </c>
@@ -13940,31 +14066,31 @@
     <row r="381" ht="16.5" customHeight="1">
       <c r="D381" s="13" t="inlineStr">
         <is>
-          <t>勤誠(8210)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E381" s="14" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F381" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G381" s="14" t="n">
-        <v>774</v>
+        <v>2650</v>
       </c>
       <c r="H381" s="14" t="n">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="I381" s="14" t="n">
-        <v>596</v>
+        <v>2405</v>
       </c>
       <c r="J381" s="15" t="n">
-        <v>0</v>
+        <v>490.67</v>
       </c>
       <c r="K381" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L381" s="16">
+        <v>490.6</v>
+      </c>
+      <c r="L381" s="17">
         <f>F381*(K381-J381)</f>
         <v/>
       </c>
@@ -13972,29 +14098,29 @@
     <row r="382" ht="16.5" customHeight="1">
       <c r="D382" s="13" t="inlineStr">
         <is>
-          <t>禾伸堂(3026)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E382" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F382" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G382" s="14" t="n">
-        <v>238</v>
+        <v>1629</v>
       </c>
       <c r="H382" s="14" t="n">
-        <v>590</v>
+        <v>277</v>
       </c>
       <c r="I382" s="14" t="n">
-        <v>-352</v>
+        <v>1352</v>
       </c>
       <c r="J382" s="15" t="n">
-        <v>0</v>
+        <v>2714.5</v>
       </c>
       <c r="K382" s="15" t="n">
-        <v>0</v>
+        <v>2771</v>
       </c>
       <c r="L382" s="16">
         <f>F382*(K382-J382)</f>
@@ -14004,29 +14130,29 @@
     <row r="383" ht="16.5" customHeight="1">
       <c r="D383" s="13" t="inlineStr">
         <is>
-          <t>德微(3675)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E383" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F383" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G383" s="14" t="n">
-        <v>121</v>
+        <v>774</v>
       </c>
       <c r="H383" s="14" t="n">
-        <v>553</v>
+        <v>178</v>
       </c>
       <c r="I383" s="14" t="n">
-        <v>-432</v>
+        <v>596</v>
       </c>
       <c r="J383" s="15" t="n">
-        <v>0</v>
+        <v>1548</v>
       </c>
       <c r="K383" s="15" t="n">
-        <v>0</v>
+        <v>1785</v>
       </c>
       <c r="L383" s="16">
         <f>F383*(K383-J383)</f>
@@ -14046,19 +14172,19 @@
         <v>16</v>
       </c>
       <c r="G384" s="14" t="n">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="H384" s="14" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I384" s="14" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="J384" s="15" t="n">
-        <v>0</v>
+        <v>80.3</v>
       </c>
       <c r="K384" s="15" t="n">
-        <v>0</v>
+        <v>80.31</v>
       </c>
       <c r="L384" s="16">
         <f>F384*(K384-J384)</f>
@@ -14068,31 +14194,31 @@
     <row r="385" ht="16.5" customHeight="1">
       <c r="D385" s="13" t="inlineStr">
         <is>
-          <t>閎康(3587)</t>
+          <t>昶昕(8438)</t>
         </is>
       </c>
       <c r="E385" s="14" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F385" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G385" s="14" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="H385" s="14" t="n">
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="I385" s="14" t="n">
-        <v>-420</v>
+        <v>345</v>
       </c>
       <c r="J385" s="15" t="n">
-        <v>0</v>
+        <v>98.7</v>
       </c>
       <c r="K385" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L385" s="16">
+        <v>98.5</v>
+      </c>
+      <c r="L385" s="17">
         <f>F385*(K385-J385)</f>
         <v/>
       </c>
@@ -14167,31 +14293,31 @@
       </c>
       <c r="D387" s="13" t="inlineStr">
         <is>
-          <t>昇達科(3491)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E387" s="14" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="F387" s="14" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="G387" s="14" t="n">
-        <v>6063</v>
+        <v>8642</v>
       </c>
       <c r="H387" s="14" t="n">
-        <v>5063</v>
+        <v>4991</v>
       </c>
       <c r="I387" s="14" t="n">
-        <v>1000</v>
+        <v>3651</v>
       </c>
       <c r="J387" s="15" t="n">
-        <v>0</v>
+        <v>301.1</v>
       </c>
       <c r="K387" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L387" s="16">
+        <v>300.68</v>
+      </c>
+      <c r="L387" s="17">
         <f>F387*(K387-J387)</f>
         <v/>
       </c>
@@ -14199,29 +14325,29 @@
     <row r="388" ht="16.5" customHeight="1">
       <c r="D388" s="13" t="inlineStr">
         <is>
-          <t>台半(5425)</t>
+          <t>昇達科(3491)</t>
         </is>
       </c>
       <c r="E388" s="14" t="n">
-        <v>486</v>
+        <v>33</v>
       </c>
       <c r="F388" s="14" t="n">
-        <v>317</v>
+        <v>28</v>
       </c>
       <c r="G388" s="14" t="n">
-        <v>3851</v>
+        <v>6063</v>
       </c>
       <c r="H388" s="14" t="n">
-        <v>2483</v>
+        <v>5063</v>
       </c>
       <c r="I388" s="14" t="n">
-        <v>1368</v>
+        <v>1000</v>
       </c>
       <c r="J388" s="15" t="n">
-        <v>79.25</v>
+        <v>1837.3</v>
       </c>
       <c r="K388" s="15" t="n">
-        <v>78.33</v>
+        <v>1808.25</v>
       </c>
       <c r="L388" s="17">
         <f>F388*(K388-J388)</f>
@@ -14231,31 +14357,31 @@
     <row r="389" ht="16.5" customHeight="1">
       <c r="D389" s="13" t="inlineStr">
         <is>
-          <t>聯詠(3034)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E389" s="14" t="n">
-        <v>0</v>
+        <v>1322</v>
       </c>
       <c r="F389" s="14" t="n">
-        <v>0</v>
+        <v>684</v>
       </c>
       <c r="G389" s="14" t="n">
-        <v>2254</v>
+        <v>4258</v>
       </c>
       <c r="H389" s="14" t="n">
-        <v>1275</v>
+        <v>2185</v>
       </c>
       <c r="I389" s="14" t="n">
-        <v>979</v>
+        <v>2073</v>
       </c>
       <c r="J389" s="15" t="n">
-        <v>0</v>
+        <v>32.21</v>
       </c>
       <c r="K389" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L389" s="16">
+        <v>31.94</v>
+      </c>
+      <c r="L389" s="17">
         <f>F389*(K389-J389)</f>
         <v/>
       </c>
@@ -14263,31 +14389,31 @@
     <row r="390" ht="16.5" customHeight="1">
       <c r="D390" s="13" t="inlineStr">
         <is>
-          <t>德微(3675)</t>
+          <t>台半(5425)</t>
         </is>
       </c>
       <c r="E390" s="14" t="n">
-        <v>45</v>
+        <v>486</v>
       </c>
       <c r="F390" s="14" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
       <c r="G390" s="14" t="n">
-        <v>1118</v>
+        <v>3851</v>
       </c>
       <c r="H390" s="14" t="n">
-        <v>25</v>
+        <v>2483</v>
       </c>
       <c r="I390" s="14" t="n">
-        <v>1093</v>
+        <v>1368</v>
       </c>
       <c r="J390" s="15" t="n">
-        <v>248.33</v>
+        <v>79.25</v>
       </c>
       <c r="K390" s="15" t="n">
-        <v>249</v>
-      </c>
-      <c r="L390" s="16">
+        <v>78.33</v>
+      </c>
+      <c r="L390" s="17">
         <f>F390*(K390-J390)</f>
         <v/>
       </c>
@@ -14295,29 +14421,29 @@
     <row r="391" ht="16.5" customHeight="1">
       <c r="D391" s="13" t="inlineStr">
         <is>
-          <t>台表科(6278)</t>
+          <t>矽力*-KY(6415)</t>
         </is>
       </c>
       <c r="E391" s="14" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="F391" s="14" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G391" s="14" t="n">
-        <v>582</v>
+        <v>3157</v>
       </c>
       <c r="H391" s="14" t="n">
-        <v>1577</v>
+        <v>1847</v>
       </c>
       <c r="I391" s="14" t="n">
-        <v>-995</v>
+        <v>1310</v>
       </c>
       <c r="J391" s="15" t="n">
-        <v>0</v>
+        <v>471.13</v>
       </c>
       <c r="K391" s="15" t="n">
-        <v>0</v>
+        <v>473.67</v>
       </c>
       <c r="L391" s="16">
         <f>F391*(K391-J391)</f>
@@ -14327,31 +14453,31 @@
     <row r="392" ht="16.5" customHeight="1">
       <c r="D392" s="13" t="inlineStr">
         <is>
-          <t>盟立(2464)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E392" s="14" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="F392" s="14" t="n">
-        <v>113</v>
+        <v>1272</v>
       </c>
       <c r="G392" s="14" t="n">
-        <v>349</v>
+        <v>1661</v>
       </c>
       <c r="H392" s="14" t="n">
-        <v>1340</v>
+        <v>14895</v>
       </c>
       <c r="I392" s="14" t="n">
-        <v>-991</v>
+        <v>-13234</v>
       </c>
       <c r="J392" s="15" t="n">
-        <v>120.34</v>
+        <v>114.57</v>
       </c>
       <c r="K392" s="15" t="n">
-        <v>118.58</v>
-      </c>
-      <c r="L392" s="17">
+        <v>117.1</v>
+      </c>
+      <c r="L392" s="16">
         <f>F392*(K392-J392)</f>
         <v/>
       </c>
@@ -14359,31 +14485,31 @@
     <row r="393" ht="16.5" customHeight="1">
       <c r="D393" s="13" t="inlineStr">
         <is>
-          <t>信昌電(6173)</t>
+          <t>德微(3675)</t>
         </is>
       </c>
       <c r="E393" s="14" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F393" s="14" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="G393" s="14" t="n">
-        <v>336</v>
+        <v>1118</v>
       </c>
       <c r="H393" s="14" t="n">
-        <v>1298</v>
+        <v>25</v>
       </c>
       <c r="I393" s="14" t="n">
-        <v>-962</v>
+        <v>1093</v>
       </c>
       <c r="J393" s="15" t="n">
-        <v>129.23</v>
+        <v>248.33</v>
       </c>
       <c r="K393" s="15" t="n">
-        <v>123.6</v>
-      </c>
-      <c r="L393" s="17">
+        <v>249</v>
+      </c>
+      <c r="L393" s="16">
         <f>F393*(K393-J393)</f>
         <v/>
       </c>
@@ -14391,31 +14517,31 @@
     <row r="394" ht="16.5" customHeight="1">
       <c r="D394" s="13" t="inlineStr">
         <is>
-          <t>譜瑞-KY(4966)</t>
+          <t>強茂(2481)</t>
         </is>
       </c>
       <c r="E394" s="14" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F394" s="14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G394" s="14" t="n">
-        <v>324</v>
+        <v>1074</v>
       </c>
       <c r="H394" s="14" t="n">
-        <v>870</v>
+        <v>305</v>
       </c>
       <c r="I394" s="14" t="n">
-        <v>-546</v>
+        <v>769</v>
       </c>
       <c r="J394" s="15" t="n">
-        <v>0</v>
+        <v>108.46</v>
       </c>
       <c r="K394" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L394" s="16">
+        <v>105.14</v>
+      </c>
+      <c r="L394" s="17">
         <f>F394*(K394-J394)</f>
         <v/>
       </c>
@@ -14423,31 +14549,31 @@
     <row r="395" ht="16.5" customHeight="1">
       <c r="D395" s="13" t="inlineStr">
         <is>
-          <t>榮剛(5009)</t>
+          <t>信昌電(6173)</t>
         </is>
       </c>
       <c r="E395" s="14" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F395" s="14" t="n">
-        <v>393</v>
+        <v>105</v>
       </c>
       <c r="G395" s="14" t="n">
-        <v>56</v>
+        <v>336</v>
       </c>
       <c r="H395" s="14" t="n">
-        <v>1575</v>
+        <v>1298</v>
       </c>
       <c r="I395" s="14" t="n">
-        <v>-1519</v>
+        <v>-962</v>
       </c>
       <c r="J395" s="15" t="n">
-        <v>39.71</v>
+        <v>129.23</v>
       </c>
       <c r="K395" s="15" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="L395" s="16">
+        <v>123.6</v>
+      </c>
+      <c r="L395" s="17">
         <f>F395*(K395-J395)</f>
         <v/>
       </c>
@@ -14455,31 +14581,31 @@
     <row r="396" ht="16.5" customHeight="1">
       <c r="D396" s="13" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>譜瑞-KY(4966)</t>
         </is>
       </c>
       <c r="E396" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F396" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G396" s="14" t="n">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="H396" s="14" t="n">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="I396" s="14" t="n">
-        <v>-814</v>
+        <v>-546</v>
       </c>
       <c r="J396" s="15" t="n">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="K396" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L396" s="16">
+        <v>725.33</v>
+      </c>
+      <c r="L396" s="17">
         <f>F396*(K396-J396)</f>
         <v/>
       </c>
@@ -14554,31 +14680,31 @@
       </c>
       <c r="D398" s="13" t="inlineStr">
         <is>
-          <t>盟立(2464)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E398" s="14" t="n">
-        <v>266</v>
+        <v>31</v>
       </c>
       <c r="F398" s="14" t="n">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="G398" s="14" t="n">
-        <v>3136</v>
+        <v>935</v>
       </c>
       <c r="H398" s="14" t="n">
-        <v>567</v>
+        <v>3820</v>
       </c>
       <c r="I398" s="14" t="n">
-        <v>2569</v>
+        <v>-2885</v>
       </c>
       <c r="J398" s="15" t="n">
-        <v>117.88</v>
+        <v>301.55</v>
       </c>
       <c r="K398" s="15" t="n">
-        <v>120.62</v>
-      </c>
-      <c r="L398" s="16">
+        <v>300.82</v>
+      </c>
+      <c r="L398" s="17">
         <f>F398*(K398-J398)</f>
         <v/>
       </c>
@@ -14586,29 +14712,29 @@
     <row r="399" ht="16.5" customHeight="1">
       <c r="D399" s="13" t="inlineStr">
         <is>
-          <t>禾伸堂(3026)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E399" s="14" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="F399" s="14" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="G399" s="14" t="n">
-        <v>572</v>
+        <v>817</v>
       </c>
       <c r="H399" s="14" t="n">
-        <v>171</v>
+        <v>2304</v>
       </c>
       <c r="I399" s="14" t="n">
-        <v>401</v>
+        <v>-1487</v>
       </c>
       <c r="J399" s="15" t="n">
-        <v>0</v>
+        <v>31.9</v>
       </c>
       <c r="K399" s="15" t="n">
-        <v>0</v>
+        <v>32.13</v>
       </c>
       <c r="L399" s="16">
         <f>F399*(K399-J399)</f>
@@ -14618,29 +14744,29 @@
     <row r="400" ht="16.5" customHeight="1">
       <c r="D400" s="13" t="inlineStr">
         <is>
-          <t>中美晶(5483)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E400" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F400" s="14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G400" s="14" t="n">
-        <v>33</v>
+        <v>583</v>
       </c>
       <c r="H400" s="14" t="n">
-        <v>358</v>
+        <v>1084</v>
       </c>
       <c r="I400" s="14" t="n">
-        <v>-325</v>
+        <v>-501</v>
       </c>
       <c r="J400" s="15" t="n">
-        <v>0</v>
+        <v>485.92</v>
       </c>
       <c r="K400" s="15" t="n">
-        <v>0</v>
+        <v>492.59</v>
       </c>
       <c r="L400" s="16">
         <f>F400*(K400-J400)</f>
@@ -14650,29 +14776,29 @@
     <row r="401" ht="16.5" customHeight="1">
       <c r="D401" s="13" t="inlineStr">
         <is>
-          <t>譜瑞-KY(4966)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E401" s="14" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F401" s="14" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="G401" s="14" t="n">
-        <v>6</v>
+        <v>529</v>
       </c>
       <c r="H401" s="14" t="n">
-        <v>511</v>
+        <v>1501</v>
       </c>
       <c r="I401" s="14" t="n">
-        <v>-505</v>
+        <v>-972</v>
       </c>
       <c r="J401" s="15" t="n">
-        <v>0</v>
+        <v>115.04</v>
       </c>
       <c r="K401" s="15" t="n">
-        <v>0</v>
+        <v>116.35</v>
       </c>
       <c r="L401" s="16">
         <f>F401*(K401-J401)</f>
@@ -14682,29 +14808,29 @@
     <row r="402" ht="16.5" customHeight="1">
       <c r="D402" s="13" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>楠梓電(2316)</t>
         </is>
       </c>
       <c r="E402" s="14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F402" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G402" s="14" t="n">
-        <v>3</v>
+        <v>481</v>
       </c>
       <c r="H402" s="14" t="n">
-        <v>610</v>
+        <v>25</v>
       </c>
       <c r="I402" s="14" t="n">
-        <v>-607</v>
+        <v>456</v>
       </c>
       <c r="J402" s="15" t="n">
-        <v>0</v>
+        <v>117.24</v>
       </c>
       <c r="K402" s="15" t="n">
-        <v>0</v>
+        <v>123.5</v>
       </c>
       <c r="L402" s="16">
         <f>F402*(K402-J402)</f>
@@ -14712,59 +14838,164 @@
       </c>
     </row>
     <row r="403" ht="16.5" customHeight="1">
-      <c r="D403" s="13" t="n"/>
-      <c r="E403" s="14" t="n"/>
-      <c r="F403" s="14" t="n"/>
-      <c r="G403" s="14" t="n"/>
-      <c r="H403" s="14" t="n"/>
-      <c r="I403" s="14" t="n"/>
-      <c r="J403" s="15" t="n"/>
-      <c r="K403" s="15" t="n"/>
-      <c r="L403" s="16" t="n"/>
+      <c r="D403" s="13" t="inlineStr">
+        <is>
+          <t>康舒(6282)</t>
+        </is>
+      </c>
+      <c r="E403" s="14" t="n">
+        <v>69</v>
+      </c>
+      <c r="F403" s="14" t="n">
+        <v>169</v>
+      </c>
+      <c r="G403" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="H403" s="14" t="n">
+        <v>924</v>
+      </c>
+      <c r="I403" s="14" t="n">
+        <v>-544</v>
+      </c>
+      <c r="J403" s="15" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="K403" s="15" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="L403" s="17">
+        <f>F403*(K403-J403)</f>
+        <v/>
+      </c>
     </row>
     <row r="404" ht="16.5" customHeight="1">
-      <c r="D404" s="13" t="n"/>
-      <c r="E404" s="14" t="n"/>
-      <c r="F404" s="14" t="n"/>
-      <c r="G404" s="14" t="n"/>
-      <c r="H404" s="14" t="n"/>
-      <c r="I404" s="14" t="n"/>
-      <c r="J404" s="15" t="n"/>
-      <c r="K404" s="15" t="n"/>
-      <c r="L404" s="16" t="n"/>
+      <c r="D404" s="13" t="inlineStr">
+        <is>
+          <t>晶豪科(3006)</t>
+        </is>
+      </c>
+      <c r="E404" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="F404" s="14" t="n">
+        <v>130</v>
+      </c>
+      <c r="G404" s="14" t="n">
+        <v>284</v>
+      </c>
+      <c r="H404" s="14" t="n">
+        <v>2816</v>
+      </c>
+      <c r="I404" s="14" t="n">
+        <v>-2532</v>
+      </c>
+      <c r="J404" s="15" t="n">
+        <v>218.69</v>
+      </c>
+      <c r="K404" s="15" t="n">
+        <v>216.63</v>
+      </c>
+      <c r="L404" s="17">
+        <f>F404*(K404-J404)</f>
+        <v/>
+      </c>
     </row>
     <row r="405" ht="16.5" customHeight="1">
-      <c r="D405" s="13" t="n"/>
-      <c r="E405" s="14" t="n"/>
-      <c r="F405" s="14" t="n"/>
-      <c r="G405" s="14" t="n"/>
-      <c r="H405" s="14" t="n"/>
-      <c r="I405" s="14" t="n"/>
-      <c r="J405" s="15" t="n"/>
-      <c r="K405" s="15" t="n"/>
-      <c r="L405" s="16" t="n"/>
+      <c r="D405" s="13" t="inlineStr">
+        <is>
+          <t>新唐(4919)</t>
+        </is>
+      </c>
+      <c r="E405" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F405" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G405" s="14" t="n">
+        <v>278</v>
+      </c>
+      <c r="H405" s="14" t="n">
+        <v>658</v>
+      </c>
+      <c r="I405" s="14" t="n">
+        <v>-380</v>
+      </c>
+      <c r="J405" s="15" t="n">
+        <v>185.07</v>
+      </c>
+      <c r="K405" s="15" t="n">
+        <v>182.69</v>
+      </c>
+      <c r="L405" s="17">
+        <f>F405*(K405-J405)</f>
+        <v/>
+      </c>
     </row>
     <row r="406" ht="16.5" customHeight="1">
-      <c r="D406" s="13" t="n"/>
-      <c r="E406" s="14" t="n"/>
-      <c r="F406" s="14" t="n"/>
-      <c r="G406" s="14" t="n"/>
-      <c r="H406" s="14" t="n"/>
-      <c r="I406" s="14" t="n"/>
-      <c r="J406" s="15" t="n"/>
-      <c r="K406" s="15" t="n"/>
-      <c r="L406" s="16" t="n"/>
+      <c r="D406" s="13" t="inlineStr">
+        <is>
+          <t>健策(3653)</t>
+        </is>
+      </c>
+      <c r="E406" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F406" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G406" s="14" t="n">
+        <v>130</v>
+      </c>
+      <c r="H406" s="14" t="n">
+        <v>1240</v>
+      </c>
+      <c r="I406" s="14" t="n">
+        <v>-1110</v>
+      </c>
+      <c r="J406" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K406" s="15" t="n">
+        <v>4135</v>
+      </c>
+      <c r="L406" s="16">
+        <f>F406*(K406-J406)</f>
+        <v/>
+      </c>
     </row>
     <row r="407" ht="16.5" customHeight="1">
-      <c r="D407" s="13" t="n"/>
-      <c r="E407" s="14" t="n"/>
-      <c r="F407" s="14" t="n"/>
-      <c r="G407" s="14" t="n"/>
-      <c r="H407" s="14" t="n"/>
-      <c r="I407" s="14" t="n"/>
-      <c r="J407" s="15" t="n"/>
-      <c r="K407" s="15" t="n"/>
-      <c r="L407" s="16" t="n"/>
+      <c r="D407" s="13" t="inlineStr">
+        <is>
+          <t>智原(3035)</t>
+        </is>
+      </c>
+      <c r="E407" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F407" s="14" t="n">
+        <v>87</v>
+      </c>
+      <c r="G407" s="14" t="n">
+        <v>118</v>
+      </c>
+      <c r="H407" s="14" t="n">
+        <v>1696</v>
+      </c>
+      <c r="I407" s="14" t="n">
+        <v>-1578</v>
+      </c>
+      <c r="J407" s="15" t="n">
+        <v>197.33</v>
+      </c>
+      <c r="K407" s="15" t="n">
+        <v>194.93</v>
+      </c>
+      <c r="L407" s="17">
+        <f>F407*(K407-J407)</f>
+        <v/>
+      </c>
     </row>
     <row r="408" ht="16.5" customHeight="1">
       <c r="A408" s="12" t="inlineStr">
@@ -14878,29 +15109,29 @@
     <row r="410" ht="16.5" customHeight="1">
       <c r="D410" s="13" t="inlineStr">
         <is>
-          <t>閎康(3587)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E410" s="14" t="n">
-        <v>343</v>
+        <v>491</v>
       </c>
       <c r="F410" s="14" t="n">
-        <v>204</v>
+        <v>30</v>
       </c>
       <c r="G410" s="14" t="n">
-        <v>12022</v>
+        <v>24686</v>
       </c>
       <c r="H410" s="14" t="n">
-        <v>7150</v>
+        <v>1445</v>
       </c>
       <c r="I410" s="14" t="n">
-        <v>4872</v>
+        <v>23241</v>
       </c>
       <c r="J410" s="15" t="n">
-        <v>350.5</v>
+        <v>502.76</v>
       </c>
       <c r="K410" s="15" t="n">
-        <v>350.48</v>
+        <v>481.7</v>
       </c>
       <c r="L410" s="17">
         <f>F410*(K410-J410)</f>
@@ -14910,29 +15141,29 @@
     <row r="411" ht="16.5" customHeight="1">
       <c r="D411" s="13" t="inlineStr">
         <is>
-          <t>陽程(3498)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E411" s="14" t="n">
-        <v>887</v>
+        <v>616</v>
       </c>
       <c r="F411" s="14" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="G411" s="14" t="n">
-        <v>9092</v>
+        <v>18509</v>
       </c>
       <c r="H411" s="14" t="n">
-        <v>0</v>
+        <v>4643</v>
       </c>
       <c r="I411" s="14" t="n">
-        <v>9092</v>
+        <v>13866</v>
       </c>
       <c r="J411" s="15" t="n">
-        <v>102.5</v>
+        <v>300.47</v>
       </c>
       <c r="K411" s="15" t="n">
-        <v>0</v>
+        <v>301.51</v>
       </c>
       <c r="L411" s="16">
         <f>F411*(K411-J411)</f>
@@ -14942,29 +15173,29 @@
     <row r="412" ht="16.5" customHeight="1">
       <c r="D412" s="13" t="inlineStr">
         <is>
-          <t>正淩(8147)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E412" s="14" t="n">
-        <v>493</v>
+        <v>1265</v>
       </c>
       <c r="F412" s="14" t="n">
-        <v>2</v>
+        <v>270</v>
       </c>
       <c r="G412" s="14" t="n">
-        <v>8356</v>
+        <v>14663</v>
       </c>
       <c r="H412" s="14" t="n">
-        <v>32</v>
+        <v>3110</v>
       </c>
       <c r="I412" s="14" t="n">
-        <v>8324</v>
+        <v>11553</v>
       </c>
       <c r="J412" s="15" t="n">
-        <v>169.5</v>
+        <v>115.91</v>
       </c>
       <c r="K412" s="15" t="n">
-        <v>160</v>
+        <v>115.2</v>
       </c>
       <c r="L412" s="17">
         <f>F412*(K412-J412)</f>
@@ -14974,29 +15205,29 @@
     <row r="413" ht="16.5" customHeight="1">
       <c r="D413" s="13" t="inlineStr">
         <is>
-          <t>大聯大(3702)</t>
+          <t>閎康(3587)</t>
         </is>
       </c>
       <c r="E413" s="14" t="n">
-        <v>730</v>
+        <v>343</v>
       </c>
       <c r="F413" s="14" t="n">
-        <v>3385</v>
+        <v>204</v>
       </c>
       <c r="G413" s="14" t="n">
-        <v>8345</v>
+        <v>12022</v>
       </c>
       <c r="H413" s="14" t="n">
-        <v>38484</v>
+        <v>7150</v>
       </c>
       <c r="I413" s="14" t="n">
-        <v>-30139</v>
+        <v>4872</v>
       </c>
       <c r="J413" s="15" t="n">
-        <v>114.31</v>
+        <v>350.5</v>
       </c>
       <c r="K413" s="15" t="n">
-        <v>113.69</v>
+        <v>350.48</v>
       </c>
       <c r="L413" s="17">
         <f>F413*(K413-J413)</f>
@@ -15006,29 +15237,29 @@
     <row r="414" ht="16.5" customHeight="1">
       <c r="D414" s="13" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E414" s="14" t="n">
-        <v>0</v>
+        <v>3355</v>
       </c>
       <c r="F414" s="14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G414" s="14" t="n">
-        <v>6994</v>
+        <v>10607</v>
       </c>
       <c r="H414" s="14" t="n">
-        <v>642</v>
+        <v>2899</v>
       </c>
       <c r="I414" s="14" t="n">
-        <v>6352</v>
+        <v>7708</v>
       </c>
       <c r="J414" s="15" t="n">
-        <v>0</v>
+        <v>31.62</v>
       </c>
       <c r="K414" s="15" t="n">
-        <v>0</v>
+        <v>32.21</v>
       </c>
       <c r="L414" s="16">
         <f>F414*(K414-J414)</f>
@@ -15038,29 +15269,29 @@
     <row r="415" ht="16.5" customHeight="1">
       <c r="D415" s="13" t="inlineStr">
         <is>
-          <t>元太(8069)</t>
+          <t>陽程(3498)</t>
         </is>
       </c>
       <c r="E415" s="14" t="n">
-        <v>201</v>
+        <v>887</v>
       </c>
       <c r="F415" s="14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G415" s="14" t="n">
-        <v>3578</v>
+        <v>9092</v>
       </c>
       <c r="H415" s="14" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I415" s="14" t="n">
-        <v>3418</v>
+        <v>9092</v>
       </c>
       <c r="J415" s="15" t="n">
-        <v>178</v>
+        <v>102.5</v>
       </c>
       <c r="K415" s="15" t="n">
-        <v>178.33</v>
+        <v>0</v>
       </c>
       <c r="L415" s="16">
         <f>F415*(K415-J415)</f>
@@ -15070,29 +15301,29 @@
     <row r="416" ht="16.5" customHeight="1">
       <c r="D416" s="13" t="inlineStr">
         <is>
-          <t>瑞昱(2379)</t>
+          <t>正淩(8147)</t>
         </is>
       </c>
       <c r="E416" s="14" t="n">
-        <v>56</v>
+        <v>493</v>
       </c>
       <c r="F416" s="14" t="n">
-        <v>464</v>
+        <v>2</v>
       </c>
       <c r="G416" s="14" t="n">
-        <v>3357</v>
+        <v>8356</v>
       </c>
       <c r="H416" s="14" t="n">
-        <v>27476</v>
+        <v>32</v>
       </c>
       <c r="I416" s="14" t="n">
-        <v>-24119</v>
+        <v>8324</v>
       </c>
       <c r="J416" s="15" t="n">
-        <v>599.45</v>
+        <v>169.5</v>
       </c>
       <c r="K416" s="15" t="n">
-        <v>592.16</v>
+        <v>160</v>
       </c>
       <c r="L416" s="17">
         <f>F416*(K416-J416)</f>
@@ -15102,29 +15333,29 @@
     <row r="417" ht="16.5" customHeight="1">
       <c r="D417" s="13" t="inlineStr">
         <is>
-          <t>宜鼎(5289)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E417" s="14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F417" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G417" s="14" t="n">
-        <v>2986</v>
+        <v>6994</v>
       </c>
       <c r="H417" s="14" t="n">
-        <v>1624</v>
+        <v>642</v>
       </c>
       <c r="I417" s="14" t="n">
-        <v>1362</v>
+        <v>6352</v>
       </c>
       <c r="J417" s="15" t="n">
-        <v>0</v>
+        <v>2689.92</v>
       </c>
       <c r="K417" s="15" t="n">
-        <v>0</v>
+        <v>3210.5</v>
       </c>
       <c r="L417" s="16">
         <f>F417*(K417-J417)</f>
@@ -15134,31 +15365,31 @@
     <row r="418" ht="16.5" customHeight="1">
       <c r="D418" s="13" t="inlineStr">
         <is>
-          <t>M31(6643)</t>
+          <t>強茂(2481)</t>
         </is>
       </c>
       <c r="E418" s="14" t="n">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="F418" s="14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G418" s="14" t="n">
-        <v>2732</v>
+        <v>5533</v>
       </c>
       <c r="H418" s="14" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="I418" s="14" t="n">
-        <v>2732</v>
+        <v>5295</v>
       </c>
       <c r="J418" s="15" t="n">
-        <v>0</v>
+        <v>108.91</v>
       </c>
       <c r="K418" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L418" s="16">
+        <v>108.09</v>
+      </c>
+      <c r="L418" s="17">
         <f>F418*(K418-J418)</f>
         <v/>
       </c>
@@ -15233,29 +15464,29 @@
       </c>
       <c r="D420" s="13" t="inlineStr">
         <is>
-          <t>國精化(4722)</t>
+          <t>創意(3443)</t>
         </is>
       </c>
       <c r="E420" s="14" t="n">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="F420" s="14" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="G420" s="14" t="n">
-        <v>3308</v>
+        <v>11814</v>
       </c>
       <c r="H420" s="14" t="n">
-        <v>1314</v>
+        <v>6136</v>
       </c>
       <c r="I420" s="14" t="n">
-        <v>1994</v>
+        <v>5678</v>
       </c>
       <c r="J420" s="15" t="n">
-        <v>239.73</v>
+        <v>5625.81</v>
       </c>
       <c r="K420" s="15" t="n">
-        <v>238.98</v>
+        <v>5578.64</v>
       </c>
       <c r="L420" s="17">
         <f>F420*(K420-J420)</f>
@@ -15265,29 +15496,29 @@
     <row r="421" ht="16.5" customHeight="1">
       <c r="D421" s="13" t="inlineStr">
         <is>
-          <t>立隆電(2472)</t>
+          <t>智原(3035)</t>
         </is>
       </c>
       <c r="E421" s="14" t="n">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="F421" s="14" t="n">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="G421" s="14" t="n">
-        <v>2149</v>
+        <v>3434</v>
       </c>
       <c r="H421" s="14" t="n">
-        <v>513</v>
+        <v>1792</v>
       </c>
       <c r="I421" s="14" t="n">
-        <v>1636</v>
+        <v>1642</v>
       </c>
       <c r="J421" s="15" t="n">
-        <v>223.83</v>
+        <v>194.04</v>
       </c>
       <c r="K421" s="15" t="n">
-        <v>223.17</v>
+        <v>190.67</v>
       </c>
       <c r="L421" s="17">
         <f>F421*(K421-J421)</f>
@@ -15297,26 +15528,26 @@
     <row r="422" ht="16.5" customHeight="1">
       <c r="D422" s="13" t="inlineStr">
         <is>
-          <t>藥華藥(6446)</t>
+          <t>世芯-KY(3661)</t>
         </is>
       </c>
       <c r="E422" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F422" s="14" t="n">
         <v>0</v>
       </c>
       <c r="G422" s="14" t="n">
-        <v>1634</v>
+        <v>2663</v>
       </c>
       <c r="H422" s="14" t="n">
-        <v>2546</v>
+        <v>67</v>
       </c>
       <c r="I422" s="14" t="n">
-        <v>-912</v>
+        <v>2596</v>
       </c>
       <c r="J422" s="15" t="n">
-        <v>0</v>
+        <v>5326</v>
       </c>
       <c r="K422" s="15" t="n">
         <v>0</v>
@@ -15329,31 +15560,31 @@
     <row r="423" ht="16.5" customHeight="1">
       <c r="D423" s="13" t="inlineStr">
         <is>
-          <t>勤誠(8210)</t>
+          <t>康舒(6282)</t>
         </is>
       </c>
       <c r="E423" s="14" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="F423" s="14" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G423" s="14" t="n">
-        <v>1631</v>
+        <v>2359</v>
       </c>
       <c r="H423" s="14" t="n">
-        <v>3438</v>
+        <v>637</v>
       </c>
       <c r="I423" s="14" t="n">
-        <v>-1807</v>
+        <v>1722</v>
       </c>
       <c r="J423" s="15" t="n">
-        <v>0</v>
+        <v>55.37</v>
       </c>
       <c r="K423" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L423" s="16">
+        <v>54.93</v>
+      </c>
+      <c r="L423" s="17">
         <f>F423*(K423-J423)</f>
         <v/>
       </c>
@@ -15361,31 +15592,31 @@
     <row r="424" ht="16.5" customHeight="1">
       <c r="D424" s="13" t="inlineStr">
         <is>
-          <t>中美晶(5483)</t>
+          <t>創見(2451)</t>
         </is>
       </c>
       <c r="E424" s="14" t="n">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="F424" s="14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G424" s="14" t="n">
-        <v>1566</v>
+        <v>1786</v>
       </c>
       <c r="H424" s="14" t="n">
-        <v>376</v>
+        <v>860</v>
       </c>
       <c r="I424" s="14" t="n">
-        <v>1190</v>
+        <v>926</v>
       </c>
       <c r="J424" s="15" t="n">
-        <v>161.39</v>
+        <v>343.4</v>
       </c>
       <c r="K424" s="15" t="n">
-        <v>156.46</v>
-      </c>
-      <c r="L424" s="17">
+        <v>343.84</v>
+      </c>
+      <c r="L424" s="16">
         <f>F424*(K424-J424)</f>
         <v/>
       </c>
@@ -15393,29 +15624,29 @@
     <row r="425" ht="16.5" customHeight="1">
       <c r="D425" s="13" t="inlineStr">
         <is>
-          <t>振樺電(8114)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E425" s="14" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="F425" s="14" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G425" s="14" t="n">
-        <v>1330</v>
+        <v>1631</v>
       </c>
       <c r="H425" s="14" t="n">
-        <v>65</v>
+        <v>3438</v>
       </c>
       <c r="I425" s="14" t="n">
-        <v>1265</v>
+        <v>-1807</v>
       </c>
       <c r="J425" s="15" t="n">
-        <v>218</v>
+        <v>1630.8</v>
       </c>
       <c r="K425" s="15" t="n">
-        <v>216.33</v>
+        <v>1562.77</v>
       </c>
       <c r="L425" s="17">
         <f>F425*(K425-J425)</f>
@@ -15425,29 +15656,29 @@
     <row r="426" ht="16.5" customHeight="1">
       <c r="D426" s="13" t="inlineStr">
         <is>
-          <t>川湖(2059)</t>
+          <t>中砂(1560)</t>
         </is>
       </c>
       <c r="E426" s="14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F426" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G426" s="14" t="n">
-        <v>1289</v>
+        <v>1576</v>
       </c>
       <c r="H426" s="14" t="n">
-        <v>2170</v>
+        <v>126</v>
       </c>
       <c r="I426" s="14" t="n">
-        <v>-881</v>
+        <v>1450</v>
       </c>
       <c r="J426" s="15" t="n">
-        <v>0</v>
+        <v>630.52</v>
       </c>
       <c r="K426" s="15" t="n">
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="L426" s="16">
         <f>F426*(K426-J426)</f>
@@ -15457,31 +15688,31 @@
     <row r="427" ht="16.5" customHeight="1">
       <c r="D427" s="13" t="inlineStr">
         <is>
-          <t>譜瑞-KY(4966)</t>
+          <t>中美晶(5483)</t>
         </is>
       </c>
       <c r="E427" s="14" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F427" s="14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G427" s="14" t="n">
-        <v>429</v>
+        <v>1566</v>
       </c>
       <c r="H427" s="14" t="n">
-        <v>2742</v>
+        <v>376</v>
       </c>
       <c r="I427" s="14" t="n">
-        <v>-2313</v>
+        <v>1190</v>
       </c>
       <c r="J427" s="15" t="n">
-        <v>0</v>
+        <v>161.39</v>
       </c>
       <c r="K427" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L427" s="16">
+        <v>156.46</v>
+      </c>
+      <c r="L427" s="17">
         <f>F427*(K427-J427)</f>
         <v/>
       </c>
@@ -15489,29 +15720,29 @@
     <row r="428" ht="16.5" customHeight="1">
       <c r="D428" s="13" t="inlineStr">
         <is>
-          <t>聯詠(3034)</t>
+          <t>志聖(2467)</t>
         </is>
       </c>
       <c r="E428" s="14" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F428" s="14" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="G428" s="14" t="n">
-        <v>170</v>
+        <v>1352</v>
       </c>
       <c r="H428" s="14" t="n">
-        <v>3166</v>
+        <v>289</v>
       </c>
       <c r="I428" s="14" t="n">
-        <v>-2996</v>
+        <v>1063</v>
       </c>
       <c r="J428" s="15" t="n">
-        <v>565.67</v>
+        <v>588</v>
       </c>
       <c r="K428" s="15" t="n">
-        <v>494.67</v>
+        <v>577.8</v>
       </c>
       <c r="L428" s="17">
         <f>F428*(K428-J428)</f>
@@ -15521,31 +15752,31 @@
     <row r="429" ht="16.5" customHeight="1">
       <c r="D429" s="13" t="inlineStr">
         <is>
-          <t>大聯大(3702)</t>
+          <t>振樺電(8114)</t>
         </is>
       </c>
       <c r="E429" s="14" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="F429" s="14" t="n">
-        <v>215</v>
+        <v>3</v>
       </c>
       <c r="G429" s="14" t="n">
-        <v>138</v>
+        <v>1330</v>
       </c>
       <c r="H429" s="14" t="n">
-        <v>2477</v>
+        <v>65</v>
       </c>
       <c r="I429" s="14" t="n">
-        <v>-2339</v>
+        <v>1265</v>
       </c>
       <c r="J429" s="15" t="n">
-        <v>114.92</v>
+        <v>218</v>
       </c>
       <c r="K429" s="15" t="n">
-        <v>115.21</v>
-      </c>
-      <c r="L429" s="16">
+        <v>216.33</v>
+      </c>
+      <c r="L429" s="17">
         <f>F429*(K429-J429)</f>
         <v/>
       </c>
@@ -15666,10 +15897,10 @@
         </is>
       </c>
       <c r="E432" s="14" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="F432" s="14" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G432" s="14" t="n">
         <v>8248</v>
@@ -15681,12 +15912,12 @@
         <v>-1306</v>
       </c>
       <c r="J432" s="15" t="n">
-        <v>0</v>
+        <v>299.91</v>
       </c>
       <c r="K432" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L432" s="16">
+        <v>299.5</v>
+      </c>
+      <c r="L432" s="17">
         <f>F432*(K432-J432)</f>
         <v/>
       </c>
@@ -15730,10 +15961,10 @@
         </is>
       </c>
       <c r="E434" s="14" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="F434" s="14" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="G434" s="14" t="n">
         <v>4248</v>
@@ -15745,12 +15976,12 @@
         <v>-701</v>
       </c>
       <c r="J434" s="15" t="n">
-        <v>0</v>
+        <v>159.69</v>
       </c>
       <c r="K434" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L434" s="16">
+        <v>159.64</v>
+      </c>
+      <c r="L434" s="17">
         <f>F434*(K434-J434)</f>
         <v/>
       </c>
@@ -15794,10 +16025,10 @@
         </is>
       </c>
       <c r="E436" s="14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F436" s="14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G436" s="14" t="n">
         <v>3389</v>
@@ -15809,10 +16040,10 @@
         <v>2153</v>
       </c>
       <c r="J436" s="15" t="n">
-        <v>0</v>
+        <v>677.74</v>
       </c>
       <c r="K436" s="15" t="n">
-        <v>0</v>
+        <v>686.5599999999999</v>
       </c>
       <c r="L436" s="16">
         <f>F436*(K436-J436)</f>
@@ -15826,10 +16057,10 @@
         </is>
       </c>
       <c r="E437" s="14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F437" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G437" s="14" t="n">
         <v>3002</v>
@@ -15841,12 +16072,12 @@
         <v>504</v>
       </c>
       <c r="J437" s="15" t="n">
-        <v>0</v>
+        <v>4288.57</v>
       </c>
       <c r="K437" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L437" s="16">
+        <v>4163.83</v>
+      </c>
+      <c r="L437" s="17">
         <f>F437*(K437-J437)</f>
         <v/>
       </c>
@@ -15858,10 +16089,10 @@
         </is>
       </c>
       <c r="E438" s="14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F438" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G438" s="14" t="n">
         <v>2964</v>
@@ -15873,12 +16104,12 @@
         <v>1531</v>
       </c>
       <c r="J438" s="15" t="n">
-        <v>0</v>
+        <v>3705.62</v>
       </c>
       <c r="K438" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L438" s="16">
+        <v>3581.75</v>
+      </c>
+      <c r="L438" s="17">
         <f>F438*(K438-J438)</f>
         <v/>
       </c>
@@ -15890,10 +16121,10 @@
         </is>
       </c>
       <c r="E439" s="14" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F439" s="14" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G439" s="14" t="n">
         <v>2584</v>
@@ -15905,12 +16136,12 @@
         <v>-707</v>
       </c>
       <c r="J439" s="15" t="n">
-        <v>0</v>
+        <v>527.24</v>
       </c>
       <c r="K439" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L439" s="16">
+        <v>522.41</v>
+      </c>
+      <c r="L439" s="17">
         <f>F439*(K439-J439)</f>
         <v/>
       </c>
@@ -15918,29 +16149,29 @@
     <row r="440" ht="16.5" customHeight="1">
       <c r="D440" s="13" t="inlineStr">
         <is>
-          <t>奇鋐(3017)</t>
+          <t>元大台灣50正2(00631L)</t>
         </is>
       </c>
       <c r="E440" s="14" t="n">
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="F440" s="14" t="n">
-        <v>0</v>
+        <v>663</v>
       </c>
       <c r="G440" s="14" t="n">
-        <v>2547</v>
+        <v>2580</v>
       </c>
       <c r="H440" s="14" t="n">
-        <v>4151</v>
+        <v>2165</v>
       </c>
       <c r="I440" s="14" t="n">
-        <v>-1604</v>
+        <v>415</v>
       </c>
       <c r="J440" s="15" t="n">
-        <v>0</v>
+        <v>32.66</v>
       </c>
       <c r="K440" s="15" t="n">
-        <v>0</v>
+        <v>32.66</v>
       </c>
       <c r="L440" s="16">
         <f>F440*(K440-J440)</f>
@@ -16095,10 +16326,10 @@
         </is>
       </c>
       <c r="E444" s="14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F444" s="14" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G444" s="14" t="n">
         <v>5034</v>
@@ -16110,12 +16341,12 @@
         <v>-9278</v>
       </c>
       <c r="J444" s="15" t="n">
-        <v>0</v>
+        <v>3871.92</v>
       </c>
       <c r="K444" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L444" s="16">
+        <v>3868.22</v>
+      </c>
+      <c r="L444" s="17">
         <f>F444*(K444-J444)</f>
         <v/>
       </c>
@@ -16159,10 +16390,10 @@
         </is>
       </c>
       <c r="E446" s="14" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="F446" s="14" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G446" s="14" t="n">
         <v>3455</v>
@@ -16174,12 +16405,12 @@
         <v>610</v>
       </c>
       <c r="J446" s="15" t="n">
-        <v>0</v>
+        <v>300.42</v>
       </c>
       <c r="K446" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L446" s="16">
+        <v>299.47</v>
+      </c>
+      <c r="L446" s="17">
         <f>F446*(K446-J446)</f>
         <v/>
       </c>
@@ -16255,10 +16486,10 @@
         </is>
       </c>
       <c r="E449" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F449" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G449" s="14" t="n">
         <v>2100</v>
@@ -16270,10 +16501,10 @@
         <v>1552</v>
       </c>
       <c r="J449" s="15" t="n">
-        <v>0</v>
+        <v>5249.75</v>
       </c>
       <c r="K449" s="15" t="n">
-        <v>0</v>
+        <v>5479</v>
       </c>
       <c r="L449" s="16">
         <f>F449*(K449-J449)</f>
@@ -16287,7 +16518,7 @@
         </is>
       </c>
       <c r="E450" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F450" s="14" t="n">
         <v>0</v>
@@ -16302,7 +16533,7 @@
         <v>1483</v>
       </c>
       <c r="J450" s="15" t="n">
-        <v>0</v>
+        <v>4126.25</v>
       </c>
       <c r="K450" s="15" t="n">
         <v>0</v>
@@ -16546,10 +16777,10 @@
         </is>
       </c>
       <c r="E457" s="14" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="F457" s="14" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G457" s="14" t="n">
         <v>3991</v>
@@ -16561,12 +16792,12 @@
         <v>1147</v>
       </c>
       <c r="J457" s="15" t="n">
-        <v>0</v>
+        <v>458.74</v>
       </c>
       <c r="K457" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L457" s="16">
+        <v>458.71</v>
+      </c>
+      <c r="L457" s="17">
         <f>F457*(K457-J457)</f>
         <v/>
       </c>
@@ -16610,10 +16841,10 @@
         </is>
       </c>
       <c r="E459" s="14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F459" s="14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G459" s="14" t="n">
         <v>3489</v>
@@ -16625,10 +16856,10 @@
         <v>1870</v>
       </c>
       <c r="J459" s="15" t="n">
-        <v>0</v>
+        <v>1341.92</v>
       </c>
       <c r="K459" s="15" t="n">
-        <v>0</v>
+        <v>1349.25</v>
       </c>
       <c r="L459" s="16">
         <f>F459*(K459-J459)</f>
@@ -16642,10 +16873,10 @@
         </is>
       </c>
       <c r="E460" s="14" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="F460" s="14" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="G460" s="14" t="n">
         <v>3262</v>
@@ -16657,12 +16888,12 @@
         <v>-2310</v>
       </c>
       <c r="J460" s="15" t="n">
-        <v>0</v>
+        <v>393.06</v>
       </c>
       <c r="K460" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L460" s="16">
+        <v>392.42</v>
+      </c>
+      <c r="L460" s="17">
         <f>F460*(K460-J460)</f>
         <v/>
       </c>
@@ -16706,10 +16937,10 @@
         </is>
       </c>
       <c r="E462" s="14" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F462" s="14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G462" s="14" t="n">
         <v>3158</v>
@@ -16721,10 +16952,10 @@
         <v>1255</v>
       </c>
       <c r="J462" s="15" t="n">
-        <v>0</v>
+        <v>902.26</v>
       </c>
       <c r="K462" s="15" t="n">
-        <v>0</v>
+        <v>906.1</v>
       </c>
       <c r="L462" s="16">
         <f>F462*(K462-J462)</f>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -1439,7 +1439,7 @@
         <v>7</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>1613</v>
@@ -1454,9 +1454,9 @@
         <v>2304.43</v>
       </c>
       <c r="K24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="16">
+        <v>226</v>
+      </c>
+      <c r="L24" s="17">
         <f>F24*(K24-J24)</f>
         <v/>
       </c>
@@ -1535,7 +1535,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>1154</v>
@@ -1550,9 +1550,9 @@
         <v>2309</v>
       </c>
       <c r="K27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="16">
+        <v>206</v>
+      </c>
+      <c r="L27" s="17">
         <f>F27*(K27-J27)</f>
         <v/>
       </c>
@@ -1599,7 +1599,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>1071</v>
@@ -1614,9 +1614,9 @@
         <v>5355</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="16">
+        <v>81</v>
+      </c>
+      <c r="L29" s="17">
         <f>F29*(K29-J29)</f>
         <v/>
       </c>
@@ -1663,7 +1663,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>787</v>
@@ -1678,9 +1678,9 @@
         <v>3934.5</v>
       </c>
       <c r="K31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="16">
+        <v>48</v>
+      </c>
+      <c r="L31" s="17">
         <f>F31*(K31-J31)</f>
         <v/>
       </c>
@@ -1695,7 +1695,7 @@
         <v>3</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>780</v>
@@ -1710,9 +1710,9 @@
         <v>2601.67</v>
       </c>
       <c r="K32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="16">
+        <v>26</v>
+      </c>
+      <c r="L32" s="17">
         <f>F32*(K32-J32)</f>
         <v/>
       </c>
@@ -3093,7 +3093,7 @@
         <v>124</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" s="14" t="n">
         <v>33108</v>
@@ -3108,9 +3108,9 @@
         <v>2670</v>
       </c>
       <c r="K71" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="16">
+        <v>48</v>
+      </c>
+      <c r="L71" s="17">
         <f>F71*(K71-J71)</f>
         <v/>
       </c>
@@ -4005,7 +4005,7 @@
         <v>3</v>
       </c>
       <c r="F97" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" s="14" t="n">
         <v>1633</v>
@@ -4020,9 +4020,9 @@
         <v>5443.67</v>
       </c>
       <c r="K97" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="16">
+        <v>133</v>
+      </c>
+      <c r="L97" s="17">
         <f>F97*(K97-J97)</f>
         <v/>
       </c>
@@ -6596,7 +6596,7 @@
         <v>124</v>
       </c>
       <c r="F170" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G170" s="14" t="n">
         <v>33108</v>
@@ -6611,9 +6611,9 @@
         <v>2670</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L170" s="16">
+        <v>48</v>
+      </c>
+      <c r="L170" s="17">
         <f>F170*(K170-J170)</f>
         <v/>
       </c>
@@ -7370,7 +7370,7 @@
         <v>10</v>
       </c>
       <c r="F192" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192" s="14" t="n">
         <v>6393</v>
@@ -7385,9 +7385,9 @@
         <v>6392.9</v>
       </c>
       <c r="K192" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" s="16">
+        <v>18</v>
+      </c>
+      <c r="L192" s="17">
         <f>F192*(K192-J192)</f>
         <v/>
       </c>
@@ -8186,7 +8186,7 @@
         <v>62</v>
       </c>
       <c r="F215" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G215" s="14" t="n">
         <v>13976</v>
@@ -8201,9 +8201,9 @@
         <v>2254.11</v>
       </c>
       <c r="K215" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L215" s="16">
+        <v>740</v>
+      </c>
+      <c r="L215" s="17">
         <f>F215*(K215-J215)</f>
         <v/>
       </c>
@@ -8733,7 +8733,7 @@
         <v>97</v>
       </c>
       <c r="F231" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G231" s="14" t="n">
         <v>2509</v>
@@ -8748,9 +8748,9 @@
         <v>258.66</v>
       </c>
       <c r="K231" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L231" s="16">
+        <v>10</v>
+      </c>
+      <c r="L231" s="17">
         <f>F231*(K231-J231)</f>
         <v/>
       </c>
@@ -8928,7 +8928,7 @@
         <v>10</v>
       </c>
       <c r="F236" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G236" s="14" t="n">
         <v>2826</v>
@@ -8943,9 +8943,9 @@
         <v>2826.4</v>
       </c>
       <c r="K236" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L236" s="16">
+        <v>463</v>
+      </c>
+      <c r="L236" s="17">
         <f>F236*(K236-J236)</f>
         <v/>
       </c>
@@ -11408,7 +11408,7 @@
         <v>3</v>
       </c>
       <c r="F306" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G306" s="14" t="n">
         <v>1633</v>
@@ -11423,9 +11423,9 @@
         <v>5443.67</v>
       </c>
       <c r="K306" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L306" s="16">
+        <v>133</v>
+      </c>
+      <c r="L306" s="17">
         <f>F306*(K306-J306)</f>
         <v/>
       </c>
@@ -13516,7 +13516,7 @@
         <v>38</v>
       </c>
       <c r="F365" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G365" s="14" t="n">
         <v>10121</v>
@@ -13531,9 +13531,9 @@
         <v>2663.47</v>
       </c>
       <c r="K365" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L365" s="16">
+        <v>1191</v>
+      </c>
+      <c r="L365" s="17">
         <f>F365*(K365-J365)</f>
         <v/>
       </c>
@@ -14940,7 +14940,7 @@
         </is>
       </c>
       <c r="E406" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F406" s="14" t="n">
         <v>3</v>
@@ -14955,7 +14955,7 @@
         <v>-1110</v>
       </c>
       <c r="J406" s="15" t="n">
-        <v>0</v>
+        <v>1303</v>
       </c>
       <c r="K406" s="15" t="n">
         <v>4135</v>
@@ -15269,29 +15269,29 @@
     <row r="415" ht="16.5" customHeight="1">
       <c r="D415" s="13" t="inlineStr">
         <is>
-          <t>陽程(3498)</t>
+          <t>蔚華科(3055)</t>
         </is>
       </c>
       <c r="E415" s="14" t="n">
-        <v>887</v>
+        <v>1010</v>
       </c>
       <c r="F415" s="14" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="G415" s="14" t="n">
-        <v>9092</v>
+        <v>10100</v>
       </c>
       <c r="H415" s="14" t="n">
-        <v>0</v>
+        <v>5040</v>
       </c>
       <c r="I415" s="14" t="n">
-        <v>9092</v>
+        <v>5060</v>
       </c>
       <c r="J415" s="15" t="n">
-        <v>102.5</v>
+        <v>100</v>
       </c>
       <c r="K415" s="15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L415" s="16">
         <f>F415*(K415-J415)</f>
@@ -15301,31 +15301,31 @@
     <row r="416" ht="16.5" customHeight="1">
       <c r="D416" s="13" t="inlineStr">
         <is>
-          <t>正淩(8147)</t>
+          <t>陽程(3498)</t>
         </is>
       </c>
       <c r="E416" s="14" t="n">
-        <v>493</v>
+        <v>887</v>
       </c>
       <c r="F416" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G416" s="14" t="n">
-        <v>8356</v>
+        <v>9092</v>
       </c>
       <c r="H416" s="14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I416" s="14" t="n">
-        <v>8324</v>
+        <v>9092</v>
       </c>
       <c r="J416" s="15" t="n">
-        <v>169.5</v>
+        <v>102.5</v>
       </c>
       <c r="K416" s="15" t="n">
-        <v>160</v>
-      </c>
-      <c r="L416" s="17">
+        <v>0</v>
+      </c>
+      <c r="L416" s="16">
         <f>F416*(K416-J416)</f>
         <v/>
       </c>
@@ -15333,31 +15333,31 @@
     <row r="417" ht="16.5" customHeight="1">
       <c r="D417" s="13" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>正淩(8147)</t>
         </is>
       </c>
       <c r="E417" s="14" t="n">
-        <v>26</v>
+        <v>493</v>
       </c>
       <c r="F417" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G417" s="14" t="n">
-        <v>6994</v>
+        <v>8356</v>
       </c>
       <c r="H417" s="14" t="n">
-        <v>642</v>
+        <v>32</v>
       </c>
       <c r="I417" s="14" t="n">
-        <v>6352</v>
+        <v>8324</v>
       </c>
       <c r="J417" s="15" t="n">
-        <v>2689.92</v>
+        <v>169.5</v>
       </c>
       <c r="K417" s="15" t="n">
-        <v>3210.5</v>
-      </c>
-      <c r="L417" s="16">
+        <v>160</v>
+      </c>
+      <c r="L417" s="17">
         <f>F417*(K417-J417)</f>
         <v/>
       </c>
@@ -15365,31 +15365,31 @@
     <row r="418" ht="16.5" customHeight="1">
       <c r="D418" s="13" t="inlineStr">
         <is>
-          <t>強茂(2481)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E418" s="14" t="n">
-        <v>508</v>
+        <v>26</v>
       </c>
       <c r="F418" s="14" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G418" s="14" t="n">
-        <v>5533</v>
+        <v>6994</v>
       </c>
       <c r="H418" s="14" t="n">
-        <v>238</v>
+        <v>642</v>
       </c>
       <c r="I418" s="14" t="n">
-        <v>5295</v>
+        <v>6352</v>
       </c>
       <c r="J418" s="15" t="n">
-        <v>108.91</v>
+        <v>2689.92</v>
       </c>
       <c r="K418" s="15" t="n">
-        <v>108.09</v>
-      </c>
-      <c r="L418" s="17">
+        <v>3210.5</v>
+      </c>
+      <c r="L418" s="16">
         <f>F418*(K418-J418)</f>
         <v/>
       </c>
@@ -15535,7 +15535,7 @@
         <v>5</v>
       </c>
       <c r="F422" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G422" s="14" t="n">
         <v>2663</v>
@@ -15550,9 +15550,9 @@
         <v>5326</v>
       </c>
       <c r="K422" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L422" s="16">
+        <v>672</v>
+      </c>
+      <c r="L422" s="17">
         <f>F422*(K422-J422)</f>
         <v/>
       </c>
@@ -16521,7 +16521,7 @@
         <v>4</v>
       </c>
       <c r="F450" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G450" s="14" t="n">
         <v>1650</v>
@@ -16536,9 +16536,9 @@
         <v>4126.25</v>
       </c>
       <c r="K450" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L450" s="16">
+        <v>1672</v>
+      </c>
+      <c r="L450" s="17">
         <f>F450*(K450-J450)</f>
         <v/>
       </c>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -4162,29 +4162,29 @@
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="E101" s="14" t="n">
-        <v>214</v>
+        <v>17287</v>
       </c>
       <c r="F101" s="14" t="n">
-        <v>20</v>
+        <v>16887</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>48192</v>
+        <v>180489</v>
       </c>
       <c r="H101" s="14" t="n">
-        <v>4397</v>
+        <v>176187</v>
       </c>
       <c r="I101" s="14" t="n">
-        <v>43795</v>
+        <v>4302</v>
       </c>
       <c r="J101" s="15" t="n">
-        <v>2251.97</v>
+        <v>104.41</v>
       </c>
       <c r="K101" s="15" t="n">
-        <v>2198.3</v>
+        <v>104.33</v>
       </c>
       <c r="L101" s="17">
         <f>F101*(K101-J101)</f>
@@ -4194,29 +4194,29 @@
     <row r="102" ht="16.5" customHeight="1">
       <c r="D102" s="13" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>台積電(2330)</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
-        <v>1033</v>
+        <v>347</v>
       </c>
       <c r="F102" s="14" t="n">
-        <v>1114</v>
+        <v>40</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>33149</v>
+        <v>78060</v>
       </c>
       <c r="H102" s="14" t="n">
-        <v>35770</v>
+        <v>9050</v>
       </c>
       <c r="I102" s="14" t="n">
-        <v>-2621</v>
+        <v>69010</v>
       </c>
       <c r="J102" s="15" t="n">
-        <v>320.9</v>
+        <v>2249.56</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>321.09</v>
+        <v>2262.5</v>
       </c>
       <c r="L102" s="16">
         <f>F102*(K102-J102)</f>
@@ -4226,31 +4226,31 @@
     <row r="103" ht="16.5" customHeight="1">
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>帆宣(6196)</t>
+          <t>大立光(3008)</t>
         </is>
       </c>
       <c r="E103" s="14" t="n">
-        <v>447</v>
+        <v>226</v>
       </c>
       <c r="F103" s="14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>19171</v>
+        <v>62914</v>
       </c>
       <c r="H103" s="14" t="n">
-        <v>428</v>
+        <v>6979</v>
       </c>
       <c r="I103" s="14" t="n">
-        <v>18743</v>
+        <v>55935</v>
       </c>
       <c r="J103" s="15" t="n">
-        <v>428.87</v>
+        <v>2783.81</v>
       </c>
       <c r="K103" s="15" t="n">
-        <v>427.5</v>
-      </c>
-      <c r="L103" s="17">
+        <v>2791.6</v>
+      </c>
+      <c r="L103" s="16">
         <f>F103*(K103-J103)</f>
         <v/>
       </c>
@@ -4258,31 +4258,31 @@
     <row r="104" ht="16.5" customHeight="1">
       <c r="D104" s="13" t="inlineStr">
         <is>
-          <t>中砂(1560)</t>
+          <t>鴻勁(7769)</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
-        <v>207</v>
+        <v>70</v>
       </c>
       <c r="F104" s="14" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>13018</v>
+        <v>48403</v>
       </c>
       <c r="H104" s="14" t="n">
-        <v>4326</v>
+        <v>1539</v>
       </c>
       <c r="I104" s="14" t="n">
-        <v>8692</v>
+        <v>46864</v>
       </c>
       <c r="J104" s="15" t="n">
-        <v>628.88</v>
+        <v>6914.66</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>626.9400000000001</v>
-      </c>
-      <c r="L104" s="17">
+        <v>7693</v>
+      </c>
+      <c r="L104" s="16">
         <f>F104*(K104-J104)</f>
         <v/>
       </c>
@@ -4290,29 +4290,29 @@
     <row r="105" ht="16.5" customHeight="1">
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>昇達科(3491)</t>
+          <t>聯亞(3081)</t>
         </is>
       </c>
       <c r="E105" s="14" t="n">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="F105" s="14" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>10744</v>
+        <v>42197</v>
       </c>
       <c r="H105" s="14" t="n">
-        <v>1395</v>
+        <v>10855</v>
       </c>
       <c r="I105" s="14" t="n">
-        <v>9349</v>
+        <v>31342</v>
       </c>
       <c r="J105" s="15" t="n">
-        <v>1761.39</v>
+        <v>3057.75</v>
       </c>
       <c r="K105" s="15" t="n">
-        <v>1743.75</v>
+        <v>3015.28</v>
       </c>
       <c r="L105" s="17">
         <f>F105*(K105-J105)</f>
@@ -4322,31 +4322,31 @@
     <row r="106" ht="16.5" customHeight="1">
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>金居(8358)</t>
+          <t>雙鴻(3324)</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
-        <v>174</v>
+        <v>309</v>
       </c>
       <c r="F106" s="14" t="n">
-        <v>131</v>
+        <v>3</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>8283</v>
+        <v>33156</v>
       </c>
       <c r="H106" s="14" t="n">
-        <v>6237</v>
+        <v>268</v>
       </c>
       <c r="I106" s="14" t="n">
-        <v>2046</v>
+        <v>32888</v>
       </c>
       <c r="J106" s="15" t="n">
-        <v>476.02</v>
+        <v>1073.01</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>476.11</v>
-      </c>
-      <c r="L106" s="16">
+        <v>891.67</v>
+      </c>
+      <c r="L106" s="17">
         <f>F106*(K106-J106)</f>
         <v/>
       </c>
@@ -4354,29 +4354,29 @@
     <row r="107" ht="16.5" customHeight="1">
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>欣興(3037)</t>
         </is>
       </c>
       <c r="E107" s="14" t="n">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="F107" s="14" t="n">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>7556</v>
+        <v>30868</v>
       </c>
       <c r="H107" s="14" t="n">
-        <v>4218</v>
+        <v>7142</v>
       </c>
       <c r="I107" s="14" t="n">
-        <v>3338</v>
+        <v>23726</v>
       </c>
       <c r="J107" s="15" t="n">
-        <v>3777.75</v>
+        <v>884.47</v>
       </c>
       <c r="K107" s="15" t="n">
-        <v>3835</v>
+        <v>903.99</v>
       </c>
       <c r="L107" s="16">
         <f>F107*(K107-J107)</f>
@@ -4386,29 +4386,29 @@
     <row r="108" ht="16.5" customHeight="1">
       <c r="D108" s="13" t="inlineStr">
         <is>
-          <t>智原(3035)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
-        <v>360</v>
+        <v>110</v>
       </c>
       <c r="F108" s="14" t="n">
-        <v>280</v>
+        <v>154</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>6967</v>
+        <v>29840</v>
       </c>
       <c r="H108" s="14" t="n">
-        <v>5454</v>
+        <v>41952</v>
       </c>
       <c r="I108" s="14" t="n">
-        <v>1513</v>
+        <v>-12112</v>
       </c>
       <c r="J108" s="15" t="n">
-        <v>193.53</v>
+        <v>2712.7</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>194.79</v>
+        <v>2724.16</v>
       </c>
       <c r="L108" s="16">
         <f>F108*(K108-J108)</f>
@@ -4418,31 +4418,31 @@
     <row r="109" ht="16.5" customHeight="1">
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>健策(3653)</t>
+          <t>臻鼎-KY(4958)</t>
         </is>
       </c>
       <c r="E109" s="14" t="n">
-        <v>17</v>
+        <v>611</v>
       </c>
       <c r="F109" s="14" t="n">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>6626</v>
+        <v>25239</v>
       </c>
       <c r="H109" s="14" t="n">
-        <v>10319</v>
+        <v>2436</v>
       </c>
       <c r="I109" s="14" t="n">
-        <v>-3693</v>
+        <v>22803</v>
       </c>
       <c r="J109" s="15" t="n">
-        <v>3897.88</v>
+        <v>413.08</v>
       </c>
       <c r="K109" s="15" t="n">
-        <v>3968.81</v>
-      </c>
-      <c r="L109" s="16">
+        <v>412.85</v>
+      </c>
+      <c r="L109" s="17">
         <f>F109*(K109-J109)</f>
         <v/>
       </c>
@@ -4450,31 +4450,31 @@
     <row r="110" ht="16.5" customHeight="1">
       <c r="D110" s="13" t="inlineStr">
         <is>
-          <t>新應材(4749)</t>
+          <t>聯發科(2454)</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F110" s="14" t="n">
-        <v>41</v>
+        <v>176</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>6278</v>
+        <v>19617</v>
       </c>
       <c r="H110" s="14" t="n">
-        <v>4759</v>
+        <v>67752</v>
       </c>
       <c r="I110" s="14" t="n">
-        <v>1519</v>
+        <v>-48135</v>
       </c>
       <c r="J110" s="15" t="n">
-        <v>1184.62</v>
+        <v>3846.41</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>1160.73</v>
-      </c>
-      <c r="L110" s="17">
+        <v>3849.52</v>
+      </c>
+      <c r="L110" s="16">
         <f>F110*(K110-J110)</f>
         <v/>
       </c>
@@ -4549,29 +4549,29 @@
       </c>
       <c r="D112" s="13" t="inlineStr">
         <is>
-          <t>宜鼎(5289)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
-        <v>143</v>
+        <v>2428</v>
       </c>
       <c r="F112" s="14" t="n">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>25062</v>
+        <v>25217</v>
       </c>
       <c r="H112" s="14" t="n">
-        <v>645</v>
+        <v>816</v>
       </c>
       <c r="I112" s="14" t="n">
-        <v>24417</v>
+        <v>24401</v>
       </c>
       <c r="J112" s="15" t="n">
-        <v>1752.59</v>
+        <v>103.86</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>1612</v>
+        <v>100.74</v>
       </c>
       <c r="L112" s="17">
         <f>F112*(K112-J112)</f>
@@ -4581,31 +4581,31 @@
     <row r="113" ht="16.5" customHeight="1">
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>華通(2313)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E113" s="14" t="n">
-        <v>466</v>
+        <v>2599</v>
       </c>
       <c r="F113" s="14" t="n">
-        <v>35</v>
+        <v>256</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>11621</v>
+        <v>9190</v>
       </c>
       <c r="H113" s="14" t="n">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="I113" s="14" t="n">
-        <v>10734</v>
+        <v>8297</v>
       </c>
       <c r="J113" s="15" t="n">
-        <v>249.38</v>
+        <v>35.36</v>
       </c>
       <c r="K113" s="15" t="n">
-        <v>253.49</v>
-      </c>
-      <c r="L113" s="16">
+        <v>34.88</v>
+      </c>
+      <c r="L113" s="17">
         <f>F113*(K113-J113)</f>
         <v/>
       </c>
@@ -4613,29 +4613,29 @@
     <row r="114" ht="16.5" customHeight="1">
       <c r="D114" s="13" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>華星光(4979)</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
-        <v>312</v>
+        <v>112</v>
       </c>
       <c r="F114" s="14" t="n">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>9366</v>
+        <v>7953</v>
       </c>
       <c r="H114" s="14" t="n">
-        <v>2478</v>
+        <v>558</v>
       </c>
       <c r="I114" s="14" t="n">
-        <v>6888</v>
+        <v>7395</v>
       </c>
       <c r="J114" s="15" t="n">
-        <v>300.18</v>
+        <v>710.12</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>298.58</v>
+        <v>697.25</v>
       </c>
       <c r="L114" s="17">
         <f>F114*(K114-J114)</f>
@@ -4645,29 +4645,29 @@
     <row r="115" ht="16.5" customHeight="1">
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>頎邦(6147)</t>
         </is>
       </c>
       <c r="E115" s="14" t="n">
-        <v>26</v>
+        <v>322</v>
       </c>
       <c r="F115" s="14" t="n">
-        <v>5</v>
+        <v>334</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>5856</v>
+        <v>6318</v>
       </c>
       <c r="H115" s="14" t="n">
-        <v>1133</v>
+        <v>6554</v>
       </c>
       <c r="I115" s="14" t="n">
-        <v>4723</v>
+        <v>-236</v>
       </c>
       <c r="J115" s="15" t="n">
-        <v>2252.23</v>
+        <v>196.22</v>
       </c>
       <c r="K115" s="15" t="n">
-        <v>2265.2</v>
+        <v>196.23</v>
       </c>
       <c r="L115" s="16">
         <f>F115*(K115-J115)</f>
@@ -4677,31 +4677,31 @@
     <row r="116" ht="16.5" customHeight="1">
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>上詮(3363)</t>
+          <t>主動統一升級50(00403A)</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
-        <v>32</v>
+        <v>4424</v>
       </c>
       <c r="F116" s="14" t="n">
-        <v>2</v>
+        <v>713</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>2722</v>
+        <v>4762</v>
       </c>
       <c r="H116" s="14" t="n">
-        <v>179</v>
+        <v>765</v>
       </c>
       <c r="I116" s="14" t="n">
-        <v>2543</v>
+        <v>3997</v>
       </c>
       <c r="J116" s="15" t="n">
-        <v>850.62</v>
+        <v>10.76</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>893.5</v>
-      </c>
-      <c r="L116" s="16">
+        <v>10.73</v>
+      </c>
+      <c r="L116" s="17">
         <f>F116*(K116-J116)</f>
         <v/>
       </c>
@@ -4709,29 +4709,29 @@
     <row r="117" ht="16.5" customHeight="1">
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E117" s="14" t="n">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="F117" s="14" t="n">
-        <v>2</v>
+        <v>417</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>2182</v>
+        <v>3301</v>
       </c>
       <c r="H117" s="14" t="n">
-        <v>594</v>
+        <v>13085</v>
       </c>
       <c r="I117" s="14" t="n">
-        <v>1588</v>
+        <v>-9784</v>
       </c>
       <c r="J117" s="15" t="n">
-        <v>3637.33</v>
+        <v>314.4</v>
       </c>
       <c r="K117" s="15" t="n">
-        <v>2967.5</v>
+        <v>313.79</v>
       </c>
       <c r="L117" s="17">
         <f>F117*(K117-J117)</f>
@@ -4741,29 +4741,29 @@
     <row r="118" ht="16.5" customHeight="1">
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>聯鈞(3450)</t>
+          <t>台積電(2330)</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F118" s="14" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>1324</v>
+        <v>2504</v>
       </c>
       <c r="H118" s="14" t="n">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="I118" s="14" t="n">
-        <v>315</v>
+        <v>1500</v>
       </c>
       <c r="J118" s="15" t="n">
-        <v>472.68</v>
+        <v>2275.91</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>480.57</v>
+        <v>2511</v>
       </c>
       <c r="L118" s="16">
         <f>F118*(K118-J118)</f>
@@ -4773,31 +4773,31 @@
     <row r="119" ht="16.5" customHeight="1">
       <c r="D119" s="13" t="inlineStr">
         <is>
-          <t>京元電子(2449)</t>
+          <t>台達電(2308)</t>
         </is>
       </c>
       <c r="E119" s="14" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F119" s="14" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>1298</v>
+        <v>1711</v>
       </c>
       <c r="H119" s="14" t="n">
-        <v>356</v>
+        <v>304</v>
       </c>
       <c r="I119" s="14" t="n">
-        <v>942</v>
+        <v>1407</v>
       </c>
       <c r="J119" s="15" t="n">
-        <v>301.91</v>
+        <v>2139</v>
       </c>
       <c r="K119" s="15" t="n">
-        <v>296.42</v>
-      </c>
-      <c r="L119" s="17">
+        <v>3035</v>
+      </c>
+      <c r="L119" s="16">
         <f>F119*(K119-J119)</f>
         <v/>
       </c>
@@ -4805,31 +4805,31 @@
     <row r="120" ht="16.5" customHeight="1">
       <c r="D120" s="13" t="inlineStr">
         <is>
-          <t>欣興(3037)</t>
+          <t>聯發科(2454)</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F120" s="14" t="n">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>1217</v>
+        <v>1502</v>
       </c>
       <c r="H120" s="14" t="n">
-        <v>11094</v>
+        <v>661</v>
       </c>
       <c r="I120" s="14" t="n">
-        <v>-9877</v>
+        <v>841</v>
       </c>
       <c r="J120" s="15" t="n">
-        <v>869.14</v>
+        <v>3755.75</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>880.52</v>
-      </c>
-      <c r="L120" s="16">
+        <v>3306</v>
+      </c>
+      <c r="L120" s="17">
         <f>F120*(K120-J120)</f>
         <v/>
       </c>
@@ -4837,29 +4837,29 @@
     <row r="121" ht="16.5" customHeight="1">
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>元大台灣50(0050)</t>
+          <t>穩懋(3105)</t>
         </is>
       </c>
       <c r="E121" s="14" t="n">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="F121" s="14" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>1054</v>
+        <v>1491</v>
       </c>
       <c r="H121" s="14" t="n">
-        <v>409</v>
+        <v>1132</v>
       </c>
       <c r="I121" s="14" t="n">
-        <v>645</v>
+        <v>359</v>
       </c>
       <c r="J121" s="15" t="n">
-        <v>96.72</v>
+        <v>514.28</v>
       </c>
       <c r="K121" s="15" t="n">
-        <v>97.33</v>
+        <v>514.6799999999999</v>
       </c>
       <c r="L121" s="16">
         <f>F121*(K121-J121)</f>
@@ -4936,31 +4936,31 @@
       </c>
       <c r="D123" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>聯發科(2454)</t>
         </is>
       </c>
       <c r="E123" s="14" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F123" s="14" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>8137</v>
+        <v>8428</v>
       </c>
       <c r="H123" s="14" t="n">
-        <v>985</v>
+        <v>3997</v>
       </c>
       <c r="I123" s="14" t="n">
-        <v>7152</v>
+        <v>4431</v>
       </c>
       <c r="J123" s="15" t="n">
-        <v>2260.17</v>
+        <v>3664.48</v>
       </c>
       <c r="K123" s="15" t="n">
-        <v>2463</v>
-      </c>
-      <c r="L123" s="16">
+        <v>3633.82</v>
+      </c>
+      <c r="L123" s="17">
         <f>F123*(K123-J123)</f>
         <v/>
       </c>
@@ -4968,29 +4968,29 @@
     <row r="124" ht="16.5" customHeight="1">
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>順德(2351)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
-        <v>379</v>
+        <v>22</v>
       </c>
       <c r="F124" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>7062</v>
+        <v>5874</v>
       </c>
       <c r="H124" s="14" t="n">
-        <v>206</v>
+        <v>3764</v>
       </c>
       <c r="I124" s="14" t="n">
-        <v>6856</v>
+        <v>2110</v>
       </c>
       <c r="J124" s="15" t="n">
-        <v>186.33</v>
+        <v>2670.05</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>187.36</v>
+        <v>2688.93</v>
       </c>
       <c r="L124" s="16">
         <f>F124*(K124-J124)</f>
@@ -5000,31 +5000,31 @@
     <row r="125" ht="16.5" customHeight="1">
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>聯詠(3034)</t>
+          <t>主動統一升級50(00403A)</t>
         </is>
       </c>
       <c r="E125" s="14" t="n">
-        <v>88</v>
+        <v>4747</v>
       </c>
       <c r="F125" s="14" t="n">
-        <v>16</v>
+        <v>2322</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>4340</v>
+        <v>5103</v>
       </c>
       <c r="H125" s="14" t="n">
-        <v>778</v>
+        <v>2498</v>
       </c>
       <c r="I125" s="14" t="n">
-        <v>3562</v>
+        <v>2605</v>
       </c>
       <c r="J125" s="15" t="n">
-        <v>493.2</v>
+        <v>10.75</v>
       </c>
       <c r="K125" s="15" t="n">
-        <v>486.5</v>
-      </c>
-      <c r="L125" s="17">
+        <v>10.76</v>
+      </c>
+      <c r="L125" s="16">
         <f>F125*(K125-J125)</f>
         <v/>
       </c>
@@ -5032,31 +5032,31 @@
     <row r="126" ht="16.5" customHeight="1">
       <c r="D126" s="13" t="inlineStr">
         <is>
-          <t>健策(3653)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="F126" s="14" t="n">
-        <v>2</v>
+        <v>151</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>4250</v>
+        <v>4128</v>
       </c>
       <c r="H126" s="14" t="n">
-        <v>767</v>
+        <v>4846</v>
       </c>
       <c r="I126" s="14" t="n">
-        <v>3483</v>
+        <v>-718</v>
       </c>
       <c r="J126" s="15" t="n">
-        <v>3863.91</v>
+        <v>320</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>3835</v>
-      </c>
-      <c r="L126" s="17">
+        <v>320.94</v>
+      </c>
+      <c r="L126" s="16">
         <f>F126*(K126-J126)</f>
         <v/>
       </c>
@@ -5064,29 +5064,29 @@
     <row r="127" ht="16.5" customHeight="1">
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>力積電(6770)</t>
+          <t>臻鼎-KY(4958)</t>
         </is>
       </c>
       <c r="E127" s="14" t="n">
-        <v>475</v>
+        <v>96</v>
       </c>
       <c r="F127" s="14" t="n">
-        <v>789</v>
+        <v>66</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>3022</v>
+        <v>3892</v>
       </c>
       <c r="H127" s="14" t="n">
-        <v>5116</v>
+        <v>2680</v>
       </c>
       <c r="I127" s="14" t="n">
-        <v>-2094</v>
+        <v>1212</v>
       </c>
       <c r="J127" s="15" t="n">
-        <v>63.61</v>
+        <v>405.38</v>
       </c>
       <c r="K127" s="15" t="n">
-        <v>64.84</v>
+        <v>406.09</v>
       </c>
       <c r="L127" s="16">
         <f>F127*(K127-J127)</f>
@@ -5096,31 +5096,31 @@
     <row r="128" ht="16.5" customHeight="1">
       <c r="D128" s="13" t="inlineStr">
         <is>
-          <t>臻鼎-KY(4958)</t>
+          <t>智邦(2345)</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="F128" s="14" t="n">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>2890</v>
+        <v>3707</v>
       </c>
       <c r="H128" s="14" t="n">
-        <v>4257</v>
+        <v>601</v>
       </c>
       <c r="I128" s="14" t="n">
-        <v>-1367</v>
+        <v>3106</v>
       </c>
       <c r="J128" s="15" t="n">
-        <v>407.11</v>
+        <v>2471.47</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>405.39</v>
-      </c>
-      <c r="L128" s="17">
+        <v>3005.5</v>
+      </c>
+      <c r="L128" s="16">
         <f>F128*(K128-J128)</f>
         <v/>
       </c>
@@ -5128,31 +5128,31 @@
     <row r="129" ht="16.5" customHeight="1">
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>力旺(3529)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E129" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="F129" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F129" s="14" t="n">
-        <v>6</v>
-      </c>
       <c r="G129" s="14" t="n">
-        <v>2710</v>
+        <v>3699</v>
       </c>
       <c r="H129" s="14" t="n">
-        <v>2302</v>
+        <v>361</v>
       </c>
       <c r="I129" s="14" t="n">
-        <v>408</v>
+        <v>3338</v>
       </c>
       <c r="J129" s="15" t="n">
-        <v>3872</v>
+        <v>499.85</v>
       </c>
       <c r="K129" s="15" t="n">
-        <v>3837</v>
-      </c>
-      <c r="L129" s="17">
+        <v>515.71</v>
+      </c>
+      <c r="L129" s="16">
         <f>F129*(K129-J129)</f>
         <v/>
       </c>
@@ -5160,29 +5160,29 @@
     <row r="130" ht="16.5" customHeight="1">
       <c r="D130" s="13" t="inlineStr">
         <is>
-          <t>奇鋐(3017)</t>
+          <t>台積電(2330)</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F130" s="14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>2595</v>
+        <v>3647</v>
       </c>
       <c r="H130" s="14" t="n">
-        <v>577</v>
+        <v>1878</v>
       </c>
       <c r="I130" s="14" t="n">
-        <v>2018</v>
+        <v>1769</v>
       </c>
       <c r="J130" s="15" t="n">
-        <v>2595.3</v>
+        <v>2279.5</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>2885</v>
+        <v>2347.62</v>
       </c>
       <c r="L130" s="16">
         <f>F130*(K130-J130)</f>
@@ -5192,29 +5192,29 @@
     <row r="131" ht="16.5" customHeight="1">
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>旺宏(2337)</t>
+          <t>創意(3443)</t>
         </is>
       </c>
       <c r="E131" s="14" t="n">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="F131" s="14" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>2475</v>
+        <v>3412</v>
       </c>
       <c r="H131" s="14" t="n">
-        <v>1595</v>
+        <v>10</v>
       </c>
       <c r="I131" s="14" t="n">
-        <v>880</v>
+        <v>3402</v>
       </c>
       <c r="J131" s="15" t="n">
-        <v>160.71</v>
+        <v>5686.83</v>
       </c>
       <c r="K131" s="15" t="n">
-        <v>159.47</v>
+        <v>95</v>
       </c>
       <c r="L131" s="17">
         <f>F131*(K131-J131)</f>
@@ -5224,31 +5224,31 @@
     <row r="132" ht="16.5" customHeight="1">
       <c r="D132" s="13" t="inlineStr">
         <is>
-          <t>鴻勁(7769)</t>
+          <t>台達電(2308)</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F132" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>2472</v>
+        <v>2984</v>
       </c>
       <c r="H132" s="14" t="n">
-        <v>1234</v>
+        <v>1398</v>
       </c>
       <c r="I132" s="14" t="n">
-        <v>1238</v>
+        <v>1586</v>
       </c>
       <c r="J132" s="15" t="n">
-        <v>6180</v>
+        <v>2131.43</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>6172</v>
-      </c>
-      <c r="L132" s="17">
+        <v>2330.17</v>
+      </c>
+      <c r="L132" s="16">
         <f>F132*(K132-J132)</f>
         <v/>
       </c>
@@ -5323,29 +5323,29 @@
       </c>
       <c r="D134" s="13" t="inlineStr">
         <is>
-          <t>群益台灣精選高息(00919)</t>
+          <t>台積電(2330)</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
-        <v>25742</v>
+        <v>2049</v>
       </c>
       <c r="F134" s="14" t="n">
-        <v>52</v>
+        <v>699</v>
       </c>
       <c r="G134" s="14" t="n">
-        <v>66091</v>
+        <v>462367</v>
       </c>
       <c r="H134" s="14" t="n">
-        <v>133</v>
+        <v>157137</v>
       </c>
       <c r="I134" s="14" t="n">
-        <v>65958</v>
+        <v>305230</v>
       </c>
       <c r="J134" s="15" t="n">
-        <v>25.67</v>
+        <v>2256.55</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>25.65</v>
+        <v>2248.02</v>
       </c>
       <c r="L134" s="17">
         <f>F134*(K134-J134)</f>
@@ -5355,29 +5355,29 @@
     <row r="135" ht="16.5" customHeight="1">
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>技嘉(2376)</t>
+          <t>群益台灣精選高息(00919)</t>
         </is>
       </c>
       <c r="E135" s="14" t="n">
-        <v>1739</v>
+        <v>39423</v>
       </c>
       <c r="F135" s="14" t="n">
-        <v>56</v>
+        <v>493</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>56538</v>
+        <v>101224</v>
       </c>
       <c r="H135" s="14" t="n">
-        <v>1826</v>
+        <v>1268</v>
       </c>
       <c r="I135" s="14" t="n">
-        <v>54712</v>
+        <v>99956</v>
       </c>
       <c r="J135" s="15" t="n">
-        <v>325.12</v>
+        <v>25.68</v>
       </c>
       <c r="K135" s="15" t="n">
-        <v>326.14</v>
+        <v>25.71</v>
       </c>
       <c r="L135" s="16">
         <f>F135*(K135-J135)</f>
@@ -5387,29 +5387,29 @@
     <row r="136" ht="16.5" customHeight="1">
       <c r="D136" s="13" t="inlineStr">
         <is>
-          <t>主動統一台股增長(00981A)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
-        <v>14578</v>
+        <v>320</v>
       </c>
       <c r="F136" s="14" t="n">
-        <v>7353</v>
+        <v>64</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>42955</v>
+        <v>87224</v>
       </c>
       <c r="H136" s="14" t="n">
-        <v>21742</v>
+        <v>17569</v>
       </c>
       <c r="I136" s="14" t="n">
-        <v>21213</v>
+        <v>69655</v>
       </c>
       <c r="J136" s="15" t="n">
-        <v>29.47</v>
+        <v>2725.76</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>29.57</v>
+        <v>2745.11</v>
       </c>
       <c r="L136" s="16">
         <f>F136*(K136-J136)</f>
@@ -5419,29 +5419,29 @@
     <row r="137" ht="16.5" customHeight="1">
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>智邦(2345)</t>
+          <t>奇鋐(3017)</t>
         </is>
       </c>
       <c r="E137" s="14" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="F137" s="14" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>35424</v>
+        <v>47805</v>
       </c>
       <c r="H137" s="14" t="n">
-        <v>13813</v>
+        <v>19810</v>
       </c>
       <c r="I137" s="14" t="n">
-        <v>21611</v>
+        <v>27995</v>
       </c>
       <c r="J137" s="15" t="n">
-        <v>2530.28</v>
+        <v>2516.03</v>
       </c>
       <c r="K137" s="15" t="n">
-        <v>2511.51</v>
+        <v>2507.57</v>
       </c>
       <c r="L137" s="17">
         <f>F137*(K137-J137)</f>
@@ -5451,31 +5451,31 @@
     <row r="138" ht="16.5" customHeight="1">
       <c r="D138" s="13" t="inlineStr">
         <is>
-          <t>元大台灣價值高息(00940)</t>
+          <t>華通(2313)</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
-        <v>28266</v>
+        <v>1824</v>
       </c>
       <c r="F138" s="14" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>31798</v>
+        <v>47309</v>
       </c>
       <c r="H138" s="14" t="n">
-        <v>152</v>
+        <v>3503</v>
       </c>
       <c r="I138" s="14" t="n">
-        <v>31646</v>
+        <v>43806</v>
       </c>
       <c r="J138" s="15" t="n">
-        <v>11.25</v>
+        <v>259.37</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="L138" s="16">
+        <v>257.54</v>
+      </c>
+      <c r="L138" s="17">
         <f>F138*(K138-J138)</f>
         <v/>
       </c>
@@ -5483,31 +5483,31 @@
     <row r="139" ht="16.5" customHeight="1">
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>復華台灣科技優息(00929)</t>
         </is>
       </c>
       <c r="E139" s="14" t="n">
-        <v>119</v>
+        <v>14091</v>
       </c>
       <c r="F139" s="14" t="n">
-        <v>304</v>
+        <v>214</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>26807</v>
+        <v>36671</v>
       </c>
       <c r="H139" s="14" t="n">
-        <v>68575</v>
+        <v>550</v>
       </c>
       <c r="I139" s="14" t="n">
-        <v>-41768</v>
+        <v>36121</v>
       </c>
       <c r="J139" s="15" t="n">
-        <v>2252.68</v>
+        <v>26.02</v>
       </c>
       <c r="K139" s="15" t="n">
-        <v>2255.76</v>
-      </c>
-      <c r="L139" s="16">
+        <v>25.68</v>
+      </c>
+      <c r="L139" s="17">
         <f>F139*(K139-J139)</f>
         <v/>
       </c>
@@ -5519,27 +5519,27 @@
         </is>
       </c>
       <c r="E140" s="14" t="n">
-        <v>9215</v>
+        <v>11574</v>
       </c>
       <c r="F140" s="14" t="n">
-        <v>25</v>
+        <v>1009</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>25984</v>
+        <v>32735</v>
       </c>
       <c r="H140" s="14" t="n">
-        <v>71</v>
+        <v>2834</v>
       </c>
       <c r="I140" s="14" t="n">
-        <v>25913</v>
+        <v>29901</v>
       </c>
       <c r="J140" s="15" t="n">
-        <v>28.2</v>
+        <v>28.28</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>28.32</v>
-      </c>
-      <c r="L140" s="16">
+        <v>28.09</v>
+      </c>
+      <c r="L140" s="17">
         <f>F140*(K140-J140)</f>
         <v/>
       </c>
@@ -5547,29 +5547,29 @@
     <row r="141" ht="16.5" customHeight="1">
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>緯穎(6669)</t>
+          <t>國巨*(2327)</t>
         </is>
       </c>
       <c r="E141" s="14" t="n">
-        <v>43</v>
+        <v>755</v>
       </c>
       <c r="F141" s="14" t="n">
-        <v>1</v>
+        <v>386</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>24789</v>
+        <v>31688</v>
       </c>
       <c r="H141" s="14" t="n">
-        <v>557</v>
+        <v>16179</v>
       </c>
       <c r="I141" s="14" t="n">
-        <v>24232</v>
+        <v>15509</v>
       </c>
       <c r="J141" s="15" t="n">
-        <v>5764.81</v>
+        <v>419.7</v>
       </c>
       <c r="K141" s="15" t="n">
-        <v>5566</v>
+        <v>419.14</v>
       </c>
       <c r="L141" s="17">
         <f>F141*(K141-J141)</f>
@@ -5579,29 +5579,29 @@
     <row r="142" ht="16.5" customHeight="1">
       <c r="D142" s="13" t="inlineStr">
         <is>
-          <t>旺宏(2337)</t>
+          <t>譜瑞-KY(4966)</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
-        <v>1367</v>
+        <v>348</v>
       </c>
       <c r="F142" s="14" t="n">
-        <v>274</v>
+        <v>67</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>21971</v>
+        <v>26479</v>
       </c>
       <c r="H142" s="14" t="n">
-        <v>4398</v>
+        <v>5088</v>
       </c>
       <c r="I142" s="14" t="n">
-        <v>17573</v>
+        <v>21391</v>
       </c>
       <c r="J142" s="15" t="n">
-        <v>160.73</v>
+        <v>760.89</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>160.52</v>
+        <v>759.36</v>
       </c>
       <c r="L142" s="17">
         <f>F142*(K142-J142)</f>
@@ -5611,31 +5611,31 @@
     <row r="143" ht="16.5" customHeight="1">
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>川湖(2059)</t>
+          <t>大華優利高填息30(00918)</t>
         </is>
       </c>
       <c r="E143" s="14" t="n">
-        <v>40</v>
+        <v>9988</v>
       </c>
       <c r="F143" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G143" s="14" t="n">
-        <v>21815</v>
+        <v>25505</v>
       </c>
       <c r="H143" s="14" t="n">
-        <v>3351</v>
+        <v>18</v>
       </c>
       <c r="I143" s="14" t="n">
-        <v>18464</v>
+        <v>25487</v>
       </c>
       <c r="J143" s="15" t="n">
-        <v>5453.65</v>
+        <v>25.54</v>
       </c>
       <c r="K143" s="15" t="n">
-        <v>5585.17</v>
-      </c>
-      <c r="L143" s="16">
+        <v>25.43</v>
+      </c>
+      <c r="L143" s="17">
         <f>F143*(K143-J143)</f>
         <v/>
       </c>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="E145" s="14" t="n">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F145" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G145" s="14" t="n">
         <v>197019</v>
@@ -5739,12 +5739,12 @@
         <v>191023</v>
       </c>
       <c r="J145" s="15" t="n">
-        <v>5794.67</v>
+        <v>5694.19</v>
       </c>
       <c r="K145" s="15" t="n">
-        <v>5995.7</v>
-      </c>
-      <c r="L145" s="16">
+        <v>5450.64</v>
+      </c>
+      <c r="L145" s="17">
         <f>F145*(K145-J145)</f>
         <v/>
       </c>
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="E146" s="14" t="n">
-        <v>452</v>
+        <v>555</v>
       </c>
       <c r="F146" s="14" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G146" s="14" t="n">
         <v>122734</v>
@@ -5771,12 +5771,12 @@
         <v>121584</v>
       </c>
       <c r="J146" s="15" t="n">
-        <v>2715.36</v>
+        <v>2211.43</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>328.43</v>
-      </c>
-      <c r="L146" s="17">
+        <v>2299</v>
+      </c>
+      <c r="L146" s="16">
         <f>F146*(K146-J146)</f>
         <v/>
       </c>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="E147" s="14" t="n">
-        <v>2800</v>
+        <v>3355</v>
       </c>
       <c r="F147" s="14" t="n">
-        <v>130</v>
+        <v>350</v>
       </c>
       <c r="G147" s="14" t="n">
         <v>105639</v>
@@ -5803,10 +5803,10 @@
         <v>94508</v>
       </c>
       <c r="J147" s="15" t="n">
-        <v>377.28</v>
+        <v>314.87</v>
       </c>
       <c r="K147" s="15" t="n">
-        <v>856.26</v>
+        <v>318.04</v>
       </c>
       <c r="L147" s="16">
         <f>F147*(K147-J147)</f>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="E148" s="14" t="n">
-        <v>265</v>
+        <v>934</v>
       </c>
       <c r="F148" s="14" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="G148" s="14" t="n">
         <v>71088</v>
@@ -5835,12 +5835,12 @@
         <v>67632</v>
       </c>
       <c r="J148" s="15" t="n">
-        <v>2682.58</v>
+        <v>761.12</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>6912.4</v>
-      </c>
-      <c r="L148" s="16">
+        <v>751.35</v>
+      </c>
+      <c r="L148" s="17">
         <f>F148*(K148-J148)</f>
         <v/>
       </c>
@@ -5848,31 +5848,31 @@
     <row r="149" ht="16.5" customHeight="1">
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>智邦(2345)</t>
+          <t>文曄(3036)</t>
         </is>
       </c>
       <c r="E149" s="14" t="n">
-        <v>259</v>
+        <v>1534</v>
       </c>
       <c r="F149" s="14" t="n">
-        <v>30</v>
+        <v>544</v>
       </c>
       <c r="G149" s="14" t="n">
-        <v>65398</v>
+        <v>42396</v>
       </c>
       <c r="H149" s="14" t="n">
-        <v>7575</v>
+        <v>14879</v>
       </c>
       <c r="I149" s="14" t="n">
-        <v>57823</v>
+        <v>27517</v>
       </c>
       <c r="J149" s="15" t="n">
-        <v>2525</v>
+        <v>276.38</v>
       </c>
       <c r="K149" s="15" t="n">
-        <v>2525</v>
-      </c>
-      <c r="L149" s="16">
+        <v>273.51</v>
+      </c>
+      <c r="L149" s="17">
         <f>F149*(K149-J149)</f>
         <v/>
       </c>
@@ -5880,31 +5880,31 @@
     <row r="150" ht="16.5" customHeight="1">
       <c r="D150" s="13" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>國巨*(2327)</t>
         </is>
       </c>
       <c r="E150" s="14" t="n">
-        <v>268</v>
+        <v>901</v>
       </c>
       <c r="F150" s="14" t="n">
-        <v>31</v>
+        <v>337</v>
       </c>
       <c r="G150" s="14" t="n">
-        <v>42396</v>
+        <v>38082</v>
       </c>
       <c r="H150" s="14" t="n">
-        <v>14879</v>
+        <v>14022</v>
       </c>
       <c r="I150" s="14" t="n">
-        <v>27517</v>
+        <v>24060</v>
       </c>
       <c r="J150" s="15" t="n">
-        <v>1581.94</v>
+        <v>422.67</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>4799.68</v>
-      </c>
-      <c r="L150" s="16">
+        <v>416.09</v>
+      </c>
+      <c r="L150" s="17">
         <f>F150*(K150-J150)</f>
         <v/>
       </c>
@@ -5912,29 +5912,29 @@
     <row r="151" ht="16.5" customHeight="1">
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>立隆電(2472)</t>
+          <t>元太(8069)</t>
         </is>
       </c>
       <c r="E151" s="14" t="n">
-        <v>1898</v>
+        <v>1928</v>
       </c>
       <c r="F151" s="14" t="n">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="G151" s="14" t="n">
-        <v>42325</v>
+        <v>37684</v>
       </c>
       <c r="H151" s="14" t="n">
-        <v>401</v>
+        <v>3264</v>
       </c>
       <c r="I151" s="14" t="n">
-        <v>41924</v>
+        <v>34420</v>
       </c>
       <c r="J151" s="15" t="n">
-        <v>223</v>
+        <v>195.45</v>
       </c>
       <c r="K151" s="15" t="n">
-        <v>223</v>
+        <v>195.47</v>
       </c>
       <c r="L151" s="16">
         <f>F151*(K151-J151)</f>
@@ -5944,31 +5944,31 @@
     <row r="152" ht="16.5" customHeight="1">
       <c r="D152" s="13" t="inlineStr">
         <is>
-          <t>國巨*(2327)</t>
+          <t>台積電(2330)</t>
         </is>
       </c>
       <c r="E152" s="14" t="n">
-        <v>6134</v>
+        <v>161</v>
       </c>
       <c r="F152" s="14" t="n">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="G152" s="14" t="n">
-        <v>38082</v>
+        <v>36253</v>
       </c>
       <c r="H152" s="14" t="n">
-        <v>14022</v>
+        <v>23388</v>
       </c>
       <c r="I152" s="14" t="n">
-        <v>24060</v>
+        <v>12865</v>
       </c>
       <c r="J152" s="15" t="n">
-        <v>62.08</v>
+        <v>2251.75</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>1894.91</v>
-      </c>
-      <c r="L152" s="16">
+        <v>2248.82</v>
+      </c>
+      <c r="L152" s="17">
         <f>F152*(K152-J152)</f>
         <v/>
       </c>
@@ -5976,29 +5976,29 @@
     <row r="153" ht="16.5" customHeight="1">
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>元太(8069)</t>
+          <t>聯發科(2454)</t>
         </is>
       </c>
       <c r="E153" s="14" t="n">
-        <v>1928</v>
+        <v>58</v>
       </c>
       <c r="F153" s="14" t="n">
-        <v>167</v>
+        <v>93</v>
       </c>
       <c r="G153" s="14" t="n">
-        <v>37684</v>
+        <v>21353</v>
       </c>
       <c r="H153" s="14" t="n">
-        <v>3264</v>
+        <v>34489</v>
       </c>
       <c r="I153" s="14" t="n">
-        <v>34420</v>
+        <v>-13136</v>
       </c>
       <c r="J153" s="15" t="n">
-        <v>195.45</v>
+        <v>3681.62</v>
       </c>
       <c r="K153" s="15" t="n">
-        <v>195.47</v>
+        <v>3708.54</v>
       </c>
       <c r="L153" s="16">
         <f>F153*(K153-J153)</f>
@@ -6008,31 +6008,31 @@
     <row r="154" ht="16.5" customHeight="1">
       <c r="D154" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>聯鈞(3450)</t>
         </is>
       </c>
       <c r="E154" s="14" t="n">
-        <v>161</v>
+        <v>418</v>
       </c>
       <c r="F154" s="14" t="n">
-        <v>104</v>
+        <v>249</v>
       </c>
       <c r="G154" s="14" t="n">
-        <v>36253</v>
+        <v>19568</v>
       </c>
       <c r="H154" s="14" t="n">
-        <v>23388</v>
+        <v>11664</v>
       </c>
       <c r="I154" s="14" t="n">
-        <v>12865</v>
+        <v>7904</v>
       </c>
       <c r="J154" s="15" t="n">
-        <v>2251.75</v>
+        <v>468.14</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>2248.82</v>
-      </c>
-      <c r="L154" s="17">
+        <v>468.43</v>
+      </c>
+      <c r="L154" s="16">
         <f>F154*(K154-J154)</f>
         <v/>
       </c>
@@ -6107,31 +6107,31 @@
       </c>
       <c r="D156" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E156" s="14" t="n">
-        <v>141</v>
+        <v>7376</v>
       </c>
       <c r="F156" s="14" t="n">
-        <v>26</v>
+        <v>8959</v>
       </c>
       <c r="G156" s="14" t="n">
-        <v>31734</v>
+        <v>231873</v>
       </c>
       <c r="H156" s="14" t="n">
-        <v>5799</v>
+        <v>281870</v>
       </c>
       <c r="I156" s="14" t="n">
-        <v>25935</v>
+        <v>-49997</v>
       </c>
       <c r="J156" s="15" t="n">
-        <v>2250.62</v>
+        <v>314.36</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>2230.5</v>
-      </c>
-      <c r="L156" s="17">
+        <v>314.62</v>
+      </c>
+      <c r="L156" s="16">
         <f>F156*(K156-J156)</f>
         <v/>
       </c>
@@ -6143,27 +6143,27 @@
         </is>
       </c>
       <c r="E157" s="14" t="n">
-        <v>2609</v>
+        <v>4685</v>
       </c>
       <c r="F157" s="14" t="n">
-        <v>580</v>
+        <v>782</v>
       </c>
       <c r="G157" s="14" t="n">
-        <v>30052</v>
+        <v>56372</v>
       </c>
       <c r="H157" s="14" t="n">
-        <v>6712</v>
+        <v>9387</v>
       </c>
       <c r="I157" s="14" t="n">
-        <v>23340</v>
+        <v>46985</v>
       </c>
       <c r="J157" s="15" t="n">
-        <v>115.19</v>
+        <v>120.33</v>
       </c>
       <c r="K157" s="15" t="n">
-        <v>115.72</v>
-      </c>
-      <c r="L157" s="16">
+        <v>120.04</v>
+      </c>
+      <c r="L157" s="17">
         <f>F157*(K157-J157)</f>
         <v/>
       </c>
@@ -6171,29 +6171,29 @@
     <row r="158" ht="16.5" customHeight="1">
       <c r="D158" s="13" t="inlineStr">
         <is>
-          <t>鴻海(2317)</t>
+          <t>元太(8069)</t>
         </is>
       </c>
       <c r="E158" s="14" t="n">
-        <v>806</v>
+        <v>1952</v>
       </c>
       <c r="F158" s="14" t="n">
-        <v>167</v>
+        <v>1385</v>
       </c>
       <c r="G158" s="14" t="n">
-        <v>20359</v>
+        <v>38152</v>
       </c>
       <c r="H158" s="14" t="n">
-        <v>4249</v>
+        <v>27075</v>
       </c>
       <c r="I158" s="14" t="n">
-        <v>16110</v>
+        <v>11077</v>
       </c>
       <c r="J158" s="15" t="n">
-        <v>252.59</v>
+        <v>195.45</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>254.45</v>
+        <v>195.49</v>
       </c>
       <c r="L158" s="16">
         <f>F158*(K158-J158)</f>
@@ -6203,31 +6203,31 @@
     <row r="159" ht="16.5" customHeight="1">
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>旺矽(6223)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E159" s="14" t="n">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="F159" s="14" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G159" s="14" t="n">
-        <v>14722</v>
+        <v>27063</v>
       </c>
       <c r="H159" s="14" t="n">
-        <v>7996</v>
+        <v>13739</v>
       </c>
       <c r="I159" s="14" t="n">
-        <v>6726</v>
+        <v>13324</v>
       </c>
       <c r="J159" s="15" t="n">
-        <v>5452.44</v>
+        <v>2733.66</v>
       </c>
       <c r="K159" s="15" t="n">
-        <v>5330.73</v>
-      </c>
-      <c r="L159" s="17">
+        <v>2747.76</v>
+      </c>
+      <c r="L159" s="16">
         <f>F159*(K159-J159)</f>
         <v/>
       </c>
@@ -6235,31 +6235,31 @@
     <row r="160" ht="16.5" customHeight="1">
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>創意(3443)</t>
+          <t>緯穎(6669)</t>
         </is>
       </c>
       <c r="E160" s="14" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F160" s="14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G160" s="14" t="n">
-        <v>12663</v>
+        <v>24258</v>
       </c>
       <c r="H160" s="14" t="n">
-        <v>1756</v>
+        <v>4407</v>
       </c>
       <c r="I160" s="14" t="n">
-        <v>10907</v>
+        <v>19851</v>
       </c>
       <c r="J160" s="15" t="n">
-        <v>5505.78</v>
+        <v>5775.71</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>5852.67</v>
-      </c>
-      <c r="L160" s="16">
+        <v>5508.38</v>
+      </c>
+      <c r="L160" s="17">
         <f>F160*(K160-J160)</f>
         <v/>
       </c>
@@ -6267,31 +6267,31 @@
     <row r="161" ht="16.5" customHeight="1">
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>緯穎(6669)</t>
+          <t>華碩(2357)</t>
         </is>
       </c>
       <c r="E161" s="14" t="n">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="F161" s="14" t="n">
-        <v>2</v>
+        <v>134</v>
       </c>
       <c r="G161" s="14" t="n">
-        <v>12332</v>
+        <v>22346</v>
       </c>
       <c r="H161" s="14" t="n">
-        <v>1394</v>
+        <v>9035</v>
       </c>
       <c r="I161" s="14" t="n">
-        <v>10938</v>
+        <v>13311</v>
       </c>
       <c r="J161" s="15" t="n">
-        <v>5872.33</v>
+        <v>679.2</v>
       </c>
       <c r="K161" s="15" t="n">
-        <v>6972.5</v>
-      </c>
-      <c r="L161" s="16">
+        <v>674.22</v>
+      </c>
+      <c r="L161" s="17">
         <f>F161*(K161-J161)</f>
         <v/>
       </c>
@@ -6299,31 +6299,31 @@
     <row r="162" ht="16.5" customHeight="1">
       <c r="D162" s="13" t="inlineStr">
         <is>
-          <t>元大台灣50(0050)</t>
+          <t>國巨*(2327)</t>
         </is>
       </c>
       <c r="E162" s="14" t="n">
-        <v>1233</v>
+        <v>537</v>
       </c>
       <c r="F162" s="14" t="n">
-        <v>819</v>
+        <v>256</v>
       </c>
       <c r="G162" s="14" t="n">
-        <v>11965</v>
+        <v>22063</v>
       </c>
       <c r="H162" s="14" t="n">
-        <v>7935</v>
+        <v>10637</v>
       </c>
       <c r="I162" s="14" t="n">
-        <v>4030</v>
+        <v>11426</v>
       </c>
       <c r="J162" s="15" t="n">
-        <v>97.04000000000001</v>
+        <v>410.85</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>96.89</v>
-      </c>
-      <c r="L162" s="17">
+        <v>415.51</v>
+      </c>
+      <c r="L162" s="16">
         <f>F162*(K162-J162)</f>
         <v/>
       </c>
@@ -6331,31 +6331,31 @@
     <row r="163" ht="16.5" customHeight="1">
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>金居(8358)</t>
+          <t>中華電(2412)</t>
         </is>
       </c>
       <c r="E163" s="14" t="n">
-        <v>234</v>
+        <v>1503</v>
       </c>
       <c r="F163" s="14" t="n">
-        <v>106</v>
+        <v>216</v>
       </c>
       <c r="G163" s="14" t="n">
-        <v>10908</v>
+        <v>20444</v>
       </c>
       <c r="H163" s="14" t="n">
-        <v>4901</v>
+        <v>2948</v>
       </c>
       <c r="I163" s="14" t="n">
-        <v>6007</v>
+        <v>17496</v>
       </c>
       <c r="J163" s="15" t="n">
-        <v>466.14</v>
+        <v>136.02</v>
       </c>
       <c r="K163" s="15" t="n">
-        <v>462.35</v>
-      </c>
-      <c r="L163" s="17">
+        <v>136.46</v>
+      </c>
+      <c r="L163" s="16">
         <f>F163*(K163-J163)</f>
         <v/>
       </c>
@@ -6363,31 +6363,31 @@
     <row r="164" ht="16.5" customHeight="1">
       <c r="D164" s="13" t="inlineStr">
         <is>
-          <t>富邦金(2881)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E164" s="14" t="n">
-        <v>1126</v>
+        <v>123</v>
       </c>
       <c r="F164" s="14" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G164" s="14" t="n">
-        <v>10806</v>
+        <v>19055</v>
       </c>
       <c r="H164" s="14" t="n">
-        <v>396</v>
+        <v>3387</v>
       </c>
       <c r="I164" s="14" t="n">
-        <v>10410</v>
+        <v>15668</v>
       </c>
       <c r="J164" s="15" t="n">
-        <v>95.97</v>
+        <v>1549.16</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>96.70999999999999</v>
-      </c>
-      <c r="L164" s="16">
+        <v>1539.45</v>
+      </c>
+      <c r="L164" s="17">
         <f>F164*(K164-J164)</f>
         <v/>
       </c>
@@ -6395,29 +6395,29 @@
     <row r="165" ht="16.5" customHeight="1">
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>中信金(2891)</t>
+          <t>世芯-KY(3661)</t>
         </is>
       </c>
       <c r="E165" s="14" t="n">
-        <v>1938</v>
+        <v>36</v>
       </c>
       <c r="F165" s="14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G165" s="14" t="n">
-        <v>10718</v>
+        <v>18903</v>
       </c>
       <c r="H165" s="14" t="n">
-        <v>50</v>
+        <v>1819</v>
       </c>
       <c r="I165" s="14" t="n">
-        <v>10668</v>
+        <v>17084</v>
       </c>
       <c r="J165" s="15" t="n">
-        <v>55.31</v>
+        <v>5250.94</v>
       </c>
       <c r="K165" s="15" t="n">
-        <v>55.33</v>
+        <v>6064.67</v>
       </c>
       <c r="L165" s="16">
         <f>F165*(K165-J165)</f>
@@ -6881,29 +6881,29 @@
       </c>
       <c r="D178" s="13" t="inlineStr">
         <is>
-          <t>華邦電(2344)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E178" s="14" t="n">
-        <v>3947</v>
+        <v>1768</v>
       </c>
       <c r="F178" s="14" t="n">
-        <v>310</v>
+        <v>486</v>
       </c>
       <c r="G178" s="14" t="n">
-        <v>45464</v>
+        <v>55796</v>
       </c>
       <c r="H178" s="14" t="n">
-        <v>3605</v>
+        <v>15375</v>
       </c>
       <c r="I178" s="14" t="n">
-        <v>41859</v>
+        <v>40421</v>
       </c>
       <c r="J178" s="15" t="n">
-        <v>115.19</v>
+        <v>315.59</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>116.28</v>
+        <v>316.36</v>
       </c>
       <c r="L178" s="16">
         <f>F178*(K178-J178)</f>
@@ -6913,29 +6913,29 @@
     <row r="179" ht="16.5" customHeight="1">
       <c r="D179" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E179" s="14" t="n">
-        <v>103</v>
+        <v>4446</v>
       </c>
       <c r="F179" s="14" t="n">
-        <v>36</v>
+        <v>268</v>
       </c>
       <c r="G179" s="14" t="n">
-        <v>23327</v>
+        <v>53924</v>
       </c>
       <c r="H179" s="14" t="n">
-        <v>8024</v>
+        <v>3222</v>
       </c>
       <c r="I179" s="14" t="n">
-        <v>15303</v>
+        <v>50702</v>
       </c>
       <c r="J179" s="15" t="n">
-        <v>2264.72</v>
+        <v>121.29</v>
       </c>
       <c r="K179" s="15" t="n">
-        <v>2228.89</v>
+        <v>120.23</v>
       </c>
       <c r="L179" s="17">
         <f>F179*(K179-J179)</f>
@@ -6945,29 +6945,29 @@
     <row r="180" ht="16.5" customHeight="1">
       <c r="D180" s="13" t="inlineStr">
         <is>
-          <t>嘉澤(3533)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E180" s="14" t="n">
-        <v>70</v>
+        <v>919</v>
       </c>
       <c r="F180" s="14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G180" s="14" t="n">
-        <v>19909</v>
+        <v>47166</v>
       </c>
       <c r="H180" s="14" t="n">
-        <v>974</v>
+        <v>673</v>
       </c>
       <c r="I180" s="14" t="n">
-        <v>18935</v>
+        <v>46493</v>
       </c>
       <c r="J180" s="15" t="n">
-        <v>2844.16</v>
+        <v>513.23</v>
       </c>
       <c r="K180" s="15" t="n">
-        <v>3247.33</v>
+        <v>517.85</v>
       </c>
       <c r="L180" s="16">
         <f>F180*(K180-J180)</f>
@@ -6977,31 +6977,31 @@
     <row r="181" ht="16.5" customHeight="1">
       <c r="D181" s="13" t="inlineStr">
         <is>
-          <t>新唐(4919)</t>
+          <t>華新科(2492)</t>
         </is>
       </c>
       <c r="E181" s="14" t="n">
-        <v>551</v>
+        <v>2171</v>
       </c>
       <c r="F181" s="14" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="G181" s="14" t="n">
-        <v>9970</v>
+        <v>39823</v>
       </c>
       <c r="H181" s="14" t="n">
-        <v>1213</v>
+        <v>796</v>
       </c>
       <c r="I181" s="14" t="n">
-        <v>8757</v>
+        <v>39027</v>
       </c>
       <c r="J181" s="15" t="n">
-        <v>180.95</v>
+        <v>183.43</v>
       </c>
       <c r="K181" s="15" t="n">
-        <v>178.43</v>
-      </c>
-      <c r="L181" s="17">
+        <v>185.21</v>
+      </c>
+      <c r="L181" s="16">
         <f>F181*(K181-J181)</f>
         <v/>
       </c>
@@ -7009,31 +7009,31 @@
     <row r="182" ht="16.5" customHeight="1">
       <c r="D182" s="13" t="inlineStr">
         <is>
-          <t>旺宏(2337)</t>
+          <t>主動統一升級50(00403A)</t>
         </is>
       </c>
       <c r="E182" s="14" t="n">
-        <v>480</v>
+        <v>14254</v>
       </c>
       <c r="F182" s="14" t="n">
-        <v>261</v>
+        <v>2577</v>
       </c>
       <c r="G182" s="14" t="n">
-        <v>7677</v>
+        <v>15298</v>
       </c>
       <c r="H182" s="14" t="n">
-        <v>4153</v>
+        <v>2792</v>
       </c>
       <c r="I182" s="14" t="n">
-        <v>3524</v>
+        <v>12506</v>
       </c>
       <c r="J182" s="15" t="n">
-        <v>159.94</v>
+        <v>10.73</v>
       </c>
       <c r="K182" s="15" t="n">
-        <v>159.11</v>
-      </c>
-      <c r="L182" s="17">
+        <v>10.84</v>
+      </c>
+      <c r="L182" s="16">
         <f>F182*(K182-J182)</f>
         <v/>
       </c>
@@ -7041,29 +7041,29 @@
     <row r="183" ht="16.5" customHeight="1">
       <c r="D183" s="13" t="inlineStr">
         <is>
-          <t>南亞(1303)</t>
+          <t>臺慶科(3357)</t>
         </is>
       </c>
       <c r="E183" s="14" t="n">
-        <v>667</v>
+        <v>524</v>
       </c>
       <c r="F183" s="14" t="n">
-        <v>141</v>
+        <v>31</v>
       </c>
       <c r="G183" s="14" t="n">
-        <v>6088</v>
+        <v>10106</v>
       </c>
       <c r="H183" s="14" t="n">
-        <v>1290</v>
+        <v>601</v>
       </c>
       <c r="I183" s="14" t="n">
-        <v>4798</v>
+        <v>9505</v>
       </c>
       <c r="J183" s="15" t="n">
-        <v>91.27</v>
+        <v>192.85</v>
       </c>
       <c r="K183" s="15" t="n">
-        <v>91.52</v>
+        <v>193.97</v>
       </c>
       <c r="L183" s="16">
         <f>F183*(K183-J183)</f>
@@ -7073,29 +7073,29 @@
     <row r="184" ht="16.5" customHeight="1">
       <c r="D184" s="13" t="inlineStr">
         <is>
-          <t>鴻海(2317)</t>
+          <t>台積電(2330)</t>
         </is>
       </c>
       <c r="E184" s="14" t="n">
-        <v>232</v>
+        <v>33</v>
       </c>
       <c r="F184" s="14" t="n">
-        <v>175</v>
+        <v>39</v>
       </c>
       <c r="G184" s="14" t="n">
-        <v>5811</v>
+        <v>7541</v>
       </c>
       <c r="H184" s="14" t="n">
-        <v>4376</v>
+        <v>8712</v>
       </c>
       <c r="I184" s="14" t="n">
-        <v>1435</v>
+        <v>-1171</v>
       </c>
       <c r="J184" s="15" t="n">
-        <v>250.49</v>
+        <v>2285.06</v>
       </c>
       <c r="K184" s="15" t="n">
-        <v>250.08</v>
+        <v>2233.95</v>
       </c>
       <c r="L184" s="17">
         <f>F184*(K184-J184)</f>
@@ -7105,31 +7105,31 @@
     <row r="185" ht="16.5" customHeight="1">
       <c r="D185" s="13" t="inlineStr">
         <is>
-          <t>緯創(3231)</t>
+          <t>臻鼎-KY(4958)</t>
         </is>
       </c>
       <c r="E185" s="14" t="n">
-        <v>397</v>
+        <v>142</v>
       </c>
       <c r="F185" s="14" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="G185" s="14" t="n">
-        <v>5563</v>
+        <v>5934</v>
       </c>
       <c r="H185" s="14" t="n">
-        <v>1394</v>
+        <v>2050</v>
       </c>
       <c r="I185" s="14" t="n">
-        <v>4169</v>
+        <v>3884</v>
       </c>
       <c r="J185" s="15" t="n">
-        <v>140.13</v>
+        <v>417.9</v>
       </c>
       <c r="K185" s="15" t="n">
-        <v>139.35</v>
-      </c>
-      <c r="L185" s="17">
+        <v>418.47</v>
+      </c>
+      <c r="L185" s="16">
         <f>F185*(K185-J185)</f>
         <v/>
       </c>
@@ -7137,31 +7137,31 @@
     <row r="186" ht="16.5" customHeight="1">
       <c r="D186" s="13" t="inlineStr">
         <is>
-          <t>楠梓電(2316)</t>
+          <t>國巨*(2327)</t>
         </is>
       </c>
       <c r="E186" s="14" t="n">
-        <v>393</v>
+        <v>124</v>
       </c>
       <c r="F186" s="14" t="n">
-        <v>11</v>
+        <v>148</v>
       </c>
       <c r="G186" s="14" t="n">
-        <v>4713</v>
+        <v>5200</v>
       </c>
       <c r="H186" s="14" t="n">
-        <v>135</v>
+        <v>6202</v>
       </c>
       <c r="I186" s="14" t="n">
-        <v>4578</v>
+        <v>-1002</v>
       </c>
       <c r="J186" s="15" t="n">
-        <v>119.91</v>
+        <v>419.39</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>123</v>
-      </c>
-      <c r="L186" s="16">
+        <v>419.07</v>
+      </c>
+      <c r="L186" s="17">
         <f>F186*(K186-J186)</f>
         <v/>
       </c>
@@ -7169,31 +7169,31 @@
     <row r="187" ht="16.5" customHeight="1">
       <c r="D187" s="13" t="inlineStr">
         <is>
-          <t>京元電子(2449)</t>
+          <t>華星光(4979)</t>
         </is>
       </c>
       <c r="E187" s="14" t="n">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="F187" s="14" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G187" s="14" t="n">
-        <v>4584</v>
+        <v>4984</v>
       </c>
       <c r="H187" s="14" t="n">
-        <v>1696</v>
+        <v>3998</v>
       </c>
       <c r="I187" s="14" t="n">
-        <v>2888</v>
+        <v>986</v>
       </c>
       <c r="J187" s="15" t="n">
-        <v>299.64</v>
+        <v>655.74</v>
       </c>
       <c r="K187" s="15" t="n">
-        <v>302.91</v>
-      </c>
-      <c r="L187" s="16">
+        <v>655.39</v>
+      </c>
+      <c r="L187" s="17">
         <f>F187*(K187-J187)</f>
         <v/>
       </c>
@@ -7268,29 +7268,29 @@
       </c>
       <c r="D189" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>緯穎(6669)</t>
         </is>
       </c>
       <c r="E189" s="14" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F189" s="14" t="n">
-        <v>274</v>
+        <v>1</v>
       </c>
       <c r="G189" s="14" t="n">
-        <v>15243</v>
+        <v>40346</v>
       </c>
       <c r="H189" s="14" t="n">
-        <v>61368</v>
+        <v>47</v>
       </c>
       <c r="I189" s="14" t="n">
-        <v>-46125</v>
+        <v>40299</v>
       </c>
       <c r="J189" s="15" t="n">
-        <v>2241.56</v>
+        <v>5682.48</v>
       </c>
       <c r="K189" s="15" t="n">
-        <v>2239.73</v>
+        <v>470</v>
       </c>
       <c r="L189" s="17">
         <f>F189*(K189-J189)</f>
@@ -7300,31 +7300,31 @@
     <row r="190" ht="16.5" customHeight="1">
       <c r="D190" s="13" t="inlineStr">
         <is>
-          <t>創意(3443)</t>
+          <t>世芯-KY(3661)</t>
         </is>
       </c>
       <c r="E190" s="14" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F190" s="14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G190" s="14" t="n">
-        <v>11130</v>
+        <v>8279</v>
       </c>
       <c r="H190" s="14" t="n">
-        <v>2234</v>
+        <v>3590</v>
       </c>
       <c r="I190" s="14" t="n">
-        <v>8896</v>
+        <v>4689</v>
       </c>
       <c r="J190" s="15" t="n">
-        <v>5564.95</v>
+        <v>5174.56</v>
       </c>
       <c r="K190" s="15" t="n">
-        <v>5586.25</v>
-      </c>
-      <c r="L190" s="16">
+        <v>5127.86</v>
+      </c>
+      <c r="L190" s="17">
         <f>F190*(K190-J190)</f>
         <v/>
       </c>
@@ -7332,31 +7332,31 @@
     <row r="191" ht="16.5" customHeight="1">
       <c r="D191" s="13" t="inlineStr">
         <is>
-          <t>景碩(3189)</t>
+          <t>台半(5425)</t>
         </is>
       </c>
       <c r="E191" s="14" t="n">
-        <v>212</v>
+        <v>953</v>
       </c>
       <c r="F191" s="14" t="n">
-        <v>6</v>
+        <v>174</v>
       </c>
       <c r="G191" s="14" t="n">
-        <v>10428</v>
+        <v>7748</v>
       </c>
       <c r="H191" s="14" t="n">
-        <v>273</v>
+        <v>1421</v>
       </c>
       <c r="I191" s="14" t="n">
-        <v>10155</v>
+        <v>6327</v>
       </c>
       <c r="J191" s="15" t="n">
-        <v>491.89</v>
+        <v>81.3</v>
       </c>
       <c r="K191" s="15" t="n">
-        <v>454.83</v>
-      </c>
-      <c r="L191" s="17">
+        <v>81.67</v>
+      </c>
+      <c r="L191" s="16">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -7364,29 +7364,29 @@
     <row r="192" ht="16.5" customHeight="1">
       <c r="D192" s="13" t="inlineStr">
         <is>
-          <t>鴻勁(7769)</t>
+          <t>啟��(6285)</t>
         </is>
       </c>
       <c r="E192" s="14" t="n">
-        <v>9</v>
+        <v>226</v>
       </c>
       <c r="F192" s="14" t="n">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="G192" s="14" t="n">
-        <v>6393</v>
+        <v>6328</v>
       </c>
       <c r="H192" s="14" t="n">
-        <v>2</v>
+        <v>3765</v>
       </c>
       <c r="I192" s="14" t="n">
-        <v>6391</v>
+        <v>2563</v>
       </c>
       <c r="J192" s="15" t="n">
-        <v>7103.22</v>
+        <v>280</v>
       </c>
       <c r="K192" s="15" t="n">
-        <v>18</v>
+        <v>270.89</v>
       </c>
       <c r="L192" s="17">
         <f>F192*(K192-J192)</f>
@@ -7396,31 +7396,31 @@
     <row r="193" ht="16.5" customHeight="1">
       <c r="D193" s="13" t="inlineStr">
         <is>
-          <t>世芯-KY(3661)</t>
+          <t>宜鼎(5289)</t>
         </is>
       </c>
       <c r="E193" s="14" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F193" s="14" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G193" s="14" t="n">
-        <v>5840</v>
+        <v>5292</v>
       </c>
       <c r="H193" s="14" t="n">
-        <v>3782</v>
+        <v>7358</v>
       </c>
       <c r="I193" s="14" t="n">
-        <v>2058</v>
+        <v>-2066</v>
       </c>
       <c r="J193" s="15" t="n">
-        <v>5309</v>
+        <v>1824.66</v>
       </c>
       <c r="K193" s="15" t="n">
-        <v>5402.86</v>
-      </c>
-      <c r="L193" s="16">
+        <v>1794.66</v>
+      </c>
+      <c r="L193" s="17">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -7428,31 +7428,31 @@
     <row r="194" ht="16.5" customHeight="1">
       <c r="D194" s="13" t="inlineStr">
         <is>
-          <t>順德(2351)</t>
+          <t>主動統一升級50(00403A)</t>
         </is>
       </c>
       <c r="E194" s="14" t="n">
-        <v>263</v>
+        <v>4919</v>
       </c>
       <c r="F194" s="14" t="n">
-        <v>3</v>
+        <v>1632</v>
       </c>
       <c r="G194" s="14" t="n">
-        <v>4903</v>
+        <v>5274</v>
       </c>
       <c r="H194" s="14" t="n">
-        <v>56</v>
+        <v>1757</v>
       </c>
       <c r="I194" s="14" t="n">
-        <v>4847</v>
+        <v>3517</v>
       </c>
       <c r="J194" s="15" t="n">
-        <v>186.41</v>
+        <v>10.72</v>
       </c>
       <c r="K194" s="15" t="n">
-        <v>185.33</v>
-      </c>
-      <c r="L194" s="17">
+        <v>10.77</v>
+      </c>
+      <c r="L194" s="16">
         <f>F194*(K194-J194)</f>
         <v/>
       </c>
@@ -7460,31 +7460,31 @@
     <row r="195" ht="16.5" customHeight="1">
       <c r="D195" s="13" t="inlineStr">
         <is>
-          <t>新唐(4919)</t>
+          <t>華新科(2492)</t>
         </is>
       </c>
       <c r="E195" s="14" t="n">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="F195" s="14" t="n">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="G195" s="14" t="n">
-        <v>3982</v>
+        <v>4802</v>
       </c>
       <c r="H195" s="14" t="n">
-        <v>737</v>
+        <v>1883</v>
       </c>
       <c r="I195" s="14" t="n">
-        <v>3245</v>
+        <v>2919</v>
       </c>
       <c r="J195" s="15" t="n">
-        <v>179.38</v>
+        <v>186.13</v>
       </c>
       <c r="K195" s="15" t="n">
-        <v>179.73</v>
-      </c>
-      <c r="L195" s="16">
+        <v>175.95</v>
+      </c>
+      <c r="L195" s="17">
         <f>F195*(K195-J195)</f>
         <v/>
       </c>
@@ -7492,31 +7492,31 @@
     <row r="196" ht="16.5" customHeight="1">
       <c r="D196" s="13" t="inlineStr">
         <is>
-          <t>力積電(6770)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E196" s="14" t="n">
-        <v>437</v>
+        <v>151</v>
       </c>
       <c r="F196" s="14" t="n">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="G196" s="14" t="n">
-        <v>2801</v>
+        <v>4734</v>
       </c>
       <c r="H196" s="14" t="n">
-        <v>1384</v>
+        <v>5958</v>
       </c>
       <c r="I196" s="14" t="n">
-        <v>1417</v>
+        <v>-1224</v>
       </c>
       <c r="J196" s="15" t="n">
-        <v>64.09999999999999</v>
+        <v>313.48</v>
       </c>
       <c r="K196" s="15" t="n">
-        <v>62.93</v>
-      </c>
-      <c r="L196" s="17">
+        <v>315.22</v>
+      </c>
+      <c r="L196" s="16">
         <f>F196*(K196-J196)</f>
         <v/>
       </c>
@@ -7524,31 +7524,31 @@
     <row r="197" ht="16.5" customHeight="1">
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>華邦電(2344)</t>
+          <t>新唐(4919)</t>
         </is>
       </c>
       <c r="E197" s="14" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F197" s="14" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="G197" s="14" t="n">
-        <v>2729</v>
+        <v>4511</v>
       </c>
       <c r="H197" s="14" t="n">
-        <v>1277</v>
+        <v>1313</v>
       </c>
       <c r="I197" s="14" t="n">
-        <v>1452</v>
+        <v>3198</v>
       </c>
       <c r="J197" s="15" t="n">
-        <v>114.66</v>
+        <v>188.74</v>
       </c>
       <c r="K197" s="15" t="n">
-        <v>116.13</v>
-      </c>
-      <c r="L197" s="16">
+        <v>187.53</v>
+      </c>
+      <c r="L197" s="17">
         <f>F197*(K197-J197)</f>
         <v/>
       </c>
@@ -7556,29 +7556,29 @@
     <row r="198" ht="16.5" customHeight="1">
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>華星光(4979)</t>
+          <t>京元電子(2449)</t>
         </is>
       </c>
       <c r="E198" s="14" t="n">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="F198" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G198" s="14" t="n">
-        <v>2574</v>
+        <v>3985</v>
       </c>
       <c r="H198" s="14" t="n">
-        <v>689</v>
+        <v>340</v>
       </c>
       <c r="I198" s="14" t="n">
-        <v>1885</v>
+        <v>3645</v>
       </c>
       <c r="J198" s="15" t="n">
-        <v>660.03</v>
+        <v>299.61</v>
       </c>
       <c r="K198" s="15" t="n">
-        <v>689.3</v>
+        <v>309.45</v>
       </c>
       <c r="L198" s="16">
         <f>F198*(K198-J198)</f>
@@ -7665,31 +7665,31 @@
       </c>
       <c r="D200" s="13" t="inlineStr">
         <is>
-          <t>晶豪科(3006)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E200" s="14" t="n">
-        <v>823</v>
+        <v>312</v>
       </c>
       <c r="F200" s="14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G200" s="14" t="n">
-        <v>17919</v>
+        <v>85960</v>
       </c>
       <c r="H200" s="14" t="n">
-        <v>68</v>
+        <v>2408</v>
       </c>
       <c r="I200" s="14" t="n">
-        <v>17851</v>
+        <v>83552</v>
       </c>
       <c r="J200" s="15" t="n">
-        <v>217.73</v>
+        <v>2755.13</v>
       </c>
       <c r="K200" s="15" t="n">
-        <v>225.33</v>
-      </c>
-      <c r="L200" s="16">
+        <v>2676</v>
+      </c>
+      <c r="L200" s="17">
         <f>F200*(K200-J200)</f>
         <v/>
       </c>
@@ -7697,31 +7697,31 @@
     <row r="201" ht="16.5" customHeight="1">
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>聯發科(2454)</t>
         </is>
       </c>
       <c r="E201" s="14" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="F201" s="14" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="G201" s="14" t="n">
-        <v>13109</v>
+        <v>7489</v>
       </c>
       <c r="H201" s="14" t="n">
-        <v>244</v>
+        <v>32964</v>
       </c>
       <c r="I201" s="14" t="n">
-        <v>12865</v>
+        <v>-25475</v>
       </c>
       <c r="J201" s="15" t="n">
-        <v>2260.14</v>
+        <v>3941.63</v>
       </c>
       <c r="K201" s="15" t="n">
-        <v>2442</v>
-      </c>
-      <c r="L201" s="16">
+        <v>3833.07</v>
+      </c>
+      <c r="L201" s="17">
         <f>F201*(K201-J201)</f>
         <v/>
       </c>
@@ -7729,29 +7729,29 @@
     <row r="202" ht="16.5" customHeight="1">
       <c r="D202" s="13" t="inlineStr">
         <is>
-          <t>世界(5347)</t>
+          <t>順德(2351)</t>
         </is>
       </c>
       <c r="E202" s="14" t="n">
-        <v>534</v>
+        <v>386</v>
       </c>
       <c r="F202" s="14" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G202" s="14" t="n">
-        <v>9359</v>
+        <v>6951</v>
       </c>
       <c r="H202" s="14" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="I202" s="14" t="n">
-        <v>8709</v>
+        <v>6951</v>
       </c>
       <c r="J202" s="15" t="n">
-        <v>175.27</v>
+        <v>180.09</v>
       </c>
       <c r="K202" s="15" t="n">
-        <v>175.65</v>
+        <v>0</v>
       </c>
       <c r="L202" s="16">
         <f>F202*(K202-J202)</f>
@@ -7761,31 +7761,31 @@
     <row r="203" ht="16.5" customHeight="1">
       <c r="D203" s="13" t="inlineStr">
         <is>
-          <t>良維(6290)</t>
+          <t>華星光(4979)</t>
         </is>
       </c>
       <c r="E203" s="14" t="n">
-        <v>235</v>
+        <v>51</v>
       </c>
       <c r="F203" s="14" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G203" s="14" t="n">
-        <v>6072</v>
+        <v>3356</v>
       </c>
       <c r="H203" s="14" t="n">
-        <v>590</v>
+        <v>1998</v>
       </c>
       <c r="I203" s="14" t="n">
-        <v>5482</v>
+        <v>1358</v>
       </c>
       <c r="J203" s="15" t="n">
-        <v>258.4</v>
+        <v>658.0599999999999</v>
       </c>
       <c r="K203" s="15" t="n">
-        <v>256.43</v>
-      </c>
-      <c r="L203" s="17">
+        <v>666.17</v>
+      </c>
+      <c r="L203" s="16">
         <f>F203*(K203-J203)</f>
         <v/>
       </c>
@@ -7793,31 +7793,31 @@
     <row r="204" ht="16.5" customHeight="1">
       <c r="D204" s="13" t="inlineStr">
         <is>
-          <t>緯穎(6669)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E204" s="14" t="n">
-        <v>10</v>
+        <v>259</v>
       </c>
       <c r="F204" s="14" t="n">
-        <v>2</v>
+        <v>387</v>
       </c>
       <c r="G204" s="14" t="n">
-        <v>5681</v>
+        <v>3078</v>
       </c>
       <c r="H204" s="14" t="n">
-        <v>1077</v>
+        <v>4622</v>
       </c>
       <c r="I204" s="14" t="n">
-        <v>4604</v>
+        <v>-1544</v>
       </c>
       <c r="J204" s="15" t="n">
-        <v>5681</v>
+        <v>118.84</v>
       </c>
       <c r="K204" s="15" t="n">
-        <v>5384.5</v>
-      </c>
-      <c r="L204" s="17">
+        <v>119.42</v>
+      </c>
+      <c r="L204" s="16">
         <f>F204*(K204-J204)</f>
         <v/>
       </c>
@@ -7825,31 +7825,31 @@
     <row r="205" ht="16.5" customHeight="1">
       <c r="D205" s="13" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>穩懋(3105)</t>
         </is>
       </c>
       <c r="E205" s="14" t="n">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="F205" s="14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G205" s="14" t="n">
-        <v>3960</v>
+        <v>2723</v>
       </c>
       <c r="H205" s="14" t="n">
-        <v>1442</v>
+        <v>2293</v>
       </c>
       <c r="I205" s="14" t="n">
-        <v>2518</v>
+        <v>430</v>
       </c>
       <c r="J205" s="15" t="n">
-        <v>297.77</v>
+        <v>513.79</v>
       </c>
       <c r="K205" s="15" t="n">
-        <v>300.52</v>
-      </c>
-      <c r="L205" s="16">
+        <v>509.49</v>
+      </c>
+      <c r="L205" s="17">
         <f>F205*(K205-J205)</f>
         <v/>
       </c>
@@ -7857,31 +7857,31 @@
     <row r="206" ht="16.5" customHeight="1">
       <c r="D206" s="13" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>旺宏(2337)</t>
         </is>
       </c>
       <c r="E206" s="14" t="n">
-        <v>13</v>
+        <v>175</v>
       </c>
       <c r="F206" s="14" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="G206" s="14" t="n">
-        <v>3471</v>
+        <v>2713</v>
       </c>
       <c r="H206" s="14" t="n">
-        <v>278</v>
+        <v>818</v>
       </c>
       <c r="I206" s="14" t="n">
-        <v>3193</v>
+        <v>1895</v>
       </c>
       <c r="J206" s="15" t="n">
-        <v>2670</v>
+        <v>155.02</v>
       </c>
       <c r="K206" s="15" t="n">
-        <v>2782</v>
-      </c>
-      <c r="L206" s="16">
+        <v>154.32</v>
+      </c>
+      <c r="L206" s="17">
         <f>F206*(K206-J206)</f>
         <v/>
       </c>
@@ -7889,31 +7889,31 @@
     <row r="207" ht="16.5" customHeight="1">
       <c r="D207" s="13" t="inlineStr">
         <is>
-          <t>華通(2313)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E207" s="14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F207" s="14" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G207" s="14" t="n">
-        <v>1980</v>
+        <v>2488</v>
       </c>
       <c r="H207" s="14" t="n">
-        <v>1701</v>
+        <v>1764</v>
       </c>
       <c r="I207" s="14" t="n">
-        <v>279</v>
+        <v>724</v>
       </c>
       <c r="J207" s="15" t="n">
-        <v>260.59</v>
+        <v>323.05</v>
       </c>
       <c r="K207" s="15" t="n">
-        <v>261.66</v>
-      </c>
-      <c r="L207" s="16">
+        <v>320.65</v>
+      </c>
+      <c r="L207" s="17">
         <f>F207*(K207-J207)</f>
         <v/>
       </c>
@@ -7921,29 +7921,29 @@
     <row r="208" ht="16.5" customHeight="1">
       <c r="D208" s="13" t="inlineStr">
         <is>
-          <t>旺宏(2337)</t>
+          <t>文曄(3036)</t>
         </is>
       </c>
       <c r="E208" s="14" t="n">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="F208" s="14" t="n">
-        <v>30</v>
+        <v>233</v>
       </c>
       <c r="G208" s="14" t="n">
-        <v>1756</v>
+        <v>2014</v>
       </c>
       <c r="H208" s="14" t="n">
-        <v>476</v>
+        <v>6272</v>
       </c>
       <c r="I208" s="14" t="n">
-        <v>1280</v>
+        <v>-4258</v>
       </c>
       <c r="J208" s="15" t="n">
-        <v>159.59</v>
+        <v>275.86</v>
       </c>
       <c r="K208" s="15" t="n">
-        <v>158.57</v>
+        <v>269.16</v>
       </c>
       <c r="L208" s="17">
         <f>F208*(K208-J208)</f>
@@ -7953,31 +7953,31 @@
     <row r="209" ht="16.5" customHeight="1">
       <c r="D209" s="13" t="inlineStr">
         <is>
-          <t>緯創(3231)</t>
+          <t>艾笛森(3591)</t>
         </is>
       </c>
       <c r="E209" s="14" t="n">
-        <v>110</v>
+        <v>756</v>
       </c>
       <c r="F209" s="14" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G209" s="14" t="n">
-        <v>1554</v>
+        <v>1840</v>
       </c>
       <c r="H209" s="14" t="n">
-        <v>278</v>
+        <v>39</v>
       </c>
       <c r="I209" s="14" t="n">
-        <v>1276</v>
+        <v>1801</v>
       </c>
       <c r="J209" s="15" t="n">
-        <v>141.31</v>
+        <v>24.33</v>
       </c>
       <c r="K209" s="15" t="n">
-        <v>138.9</v>
-      </c>
-      <c r="L209" s="17">
+        <v>24.5</v>
+      </c>
+      <c r="L209" s="16">
         <f>F209*(K209-J209)</f>
         <v/>
       </c>
@@ -8052,31 +8052,31 @@
       </c>
       <c r="D211" s="13" t="inlineStr">
         <is>
-          <t>新唐(4919)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E211" s="14" t="n">
-        <v>1412</v>
+        <v>3454</v>
       </c>
       <c r="F211" s="14" t="n">
-        <v>7</v>
+        <v>5661</v>
       </c>
       <c r="G211" s="14" t="n">
-        <v>25730</v>
+        <v>110557</v>
       </c>
       <c r="H211" s="14" t="n">
-        <v>129</v>
+        <v>179761</v>
       </c>
       <c r="I211" s="14" t="n">
-        <v>25601</v>
+        <v>-69204</v>
       </c>
       <c r="J211" s="15" t="n">
-        <v>182.23</v>
+        <v>320.08</v>
       </c>
       <c r="K211" s="15" t="n">
-        <v>184.86</v>
-      </c>
-      <c r="L211" s="16">
+        <v>317.54</v>
+      </c>
+      <c r="L211" s="17">
         <f>F211*(K211-J211)</f>
         <v/>
       </c>
@@ -8084,31 +8084,31 @@
     <row r="212" ht="16.5" customHeight="1">
       <c r="D212" s="13" t="inlineStr">
         <is>
-          <t>南亞(1303)</t>
+          <t>華通(2313)</t>
         </is>
       </c>
       <c r="E212" s="14" t="n">
-        <v>2795</v>
+        <v>973</v>
       </c>
       <c r="F212" s="14" t="n">
-        <v>1375</v>
+        <v>74</v>
       </c>
       <c r="G212" s="14" t="n">
-        <v>25579</v>
+        <v>25474</v>
       </c>
       <c r="H212" s="14" t="n">
-        <v>12552</v>
+        <v>1938</v>
       </c>
       <c r="I212" s="14" t="n">
-        <v>13027</v>
+        <v>23536</v>
       </c>
       <c r="J212" s="15" t="n">
-        <v>91.52</v>
+        <v>261.81</v>
       </c>
       <c r="K212" s="15" t="n">
-        <v>91.29000000000001</v>
-      </c>
-      <c r="L212" s="17">
+        <v>261.84</v>
+      </c>
+      <c r="L212" s="16">
         <f>F212*(K212-J212)</f>
         <v/>
       </c>
@@ -8116,31 +8116,31 @@
     <row r="213" ht="16.5" customHeight="1">
       <c r="D213" s="13" t="inlineStr">
         <is>
-          <t>華星光(4979)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E213" s="14" t="n">
-        <v>236</v>
+        <v>122</v>
       </c>
       <c r="F213" s="14" t="n">
-        <v>205</v>
+        <v>2</v>
       </c>
       <c r="G213" s="14" t="n">
-        <v>15547</v>
+        <v>18892</v>
       </c>
       <c r="H213" s="14" t="n">
-        <v>13487</v>
+        <v>335</v>
       </c>
       <c r="I213" s="14" t="n">
-        <v>2060</v>
+        <v>18557</v>
       </c>
       <c r="J213" s="15" t="n">
-        <v>658.78</v>
+        <v>1548.49</v>
       </c>
       <c r="K213" s="15" t="n">
-        <v>657.91</v>
-      </c>
-      <c r="L213" s="17">
+        <v>1673.5</v>
+      </c>
+      <c r="L213" s="16">
         <f>F213*(K213-J213)</f>
         <v/>
       </c>
@@ -8148,31 +8148,31 @@
     <row r="214" ht="16.5" customHeight="1">
       <c r="D214" s="13" t="inlineStr">
         <is>
-          <t>嘉澤(3533)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E214" s="14" t="n">
-        <v>50</v>
+        <v>285</v>
       </c>
       <c r="F214" s="14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G214" s="14" t="n">
-        <v>14003</v>
+        <v>14874</v>
       </c>
       <c r="H214" s="14" t="n">
-        <v>877</v>
+        <v>624</v>
       </c>
       <c r="I214" s="14" t="n">
-        <v>13126</v>
+        <v>14250</v>
       </c>
       <c r="J214" s="15" t="n">
-        <v>2800.56</v>
+        <v>521.88</v>
       </c>
       <c r="K214" s="15" t="n">
-        <v>2924.67</v>
-      </c>
-      <c r="L214" s="16">
+        <v>519.92</v>
+      </c>
+      <c r="L214" s="17">
         <f>F214*(K214-J214)</f>
         <v/>
       </c>
@@ -8180,31 +8180,31 @@
     <row r="215" ht="16.5" customHeight="1">
       <c r="D215" s="13" t="inlineStr">
         <is>
-          <t>雍智科技(6683)</t>
+          <t>鴻勁(7769)</t>
         </is>
       </c>
       <c r="E215" s="14" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="F215" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G215" s="14" t="n">
-        <v>13976</v>
+        <v>13811</v>
       </c>
       <c r="H215" s="14" t="n">
-        <v>74</v>
+        <v>1395</v>
       </c>
       <c r="I215" s="14" t="n">
-        <v>13902</v>
+        <v>12416</v>
       </c>
       <c r="J215" s="15" t="n">
-        <v>2368.73</v>
+        <v>6905.3</v>
       </c>
       <c r="K215" s="15" t="n">
-        <v>740</v>
-      </c>
-      <c r="L215" s="17">
+        <v>6976</v>
+      </c>
+      <c r="L215" s="16">
         <f>F215*(K215-J215)</f>
         <v/>
       </c>
@@ -8212,31 +8212,31 @@
     <row r="216" ht="16.5" customHeight="1">
       <c r="D216" s="13" t="inlineStr">
         <is>
-          <t>華碩(2357)</t>
+          <t>光洋科(1785)</t>
         </is>
       </c>
       <c r="E216" s="14" t="n">
-        <v>169</v>
+        <v>619</v>
       </c>
       <c r="F216" s="14" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G216" s="14" t="n">
-        <v>11690</v>
+        <v>9964</v>
       </c>
       <c r="H216" s="14" t="n">
-        <v>139</v>
+        <v>255</v>
       </c>
       <c r="I216" s="14" t="n">
-        <v>11551</v>
+        <v>9709</v>
       </c>
       <c r="J216" s="15" t="n">
-        <v>691.73</v>
+        <v>160.97</v>
       </c>
       <c r="K216" s="15" t="n">
-        <v>693</v>
-      </c>
-      <c r="L216" s="16">
+        <v>159.31</v>
+      </c>
+      <c r="L216" s="17">
         <f>F216*(K216-J216)</f>
         <v/>
       </c>
@@ -8244,31 +8244,31 @@
     <row r="217" ht="16.5" customHeight="1">
       <c r="D217" s="13" t="inlineStr">
         <is>
-          <t>凱基金(2883)</t>
+          <t>健策(3653)</t>
         </is>
       </c>
       <c r="E217" s="14" t="n">
-        <v>5005</v>
+        <v>22</v>
       </c>
       <c r="F217" s="14" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G217" s="14" t="n">
-        <v>11494</v>
+        <v>8755</v>
       </c>
       <c r="H217" s="14" t="n">
-        <v>0</v>
+        <v>12095</v>
       </c>
       <c r="I217" s="14" t="n">
-        <v>11494</v>
+        <v>-3340</v>
       </c>
       <c r="J217" s="15" t="n">
-        <v>22.97</v>
+        <v>3979.45</v>
       </c>
       <c r="K217" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L217" s="16">
+        <v>3901.55</v>
+      </c>
+      <c r="L217" s="17">
         <f>F217*(K217-J217)</f>
         <v/>
       </c>
@@ -8276,29 +8276,29 @@
     <row r="218" ht="16.5" customHeight="1">
       <c r="D218" s="13" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>元大台灣高息低波(00713)</t>
         </is>
       </c>
       <c r="E218" s="14" t="n">
-        <v>357</v>
+        <v>1570</v>
       </c>
       <c r="F218" s="14" t="n">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="G218" s="14" t="n">
-        <v>10700</v>
+        <v>8653</v>
       </c>
       <c r="H218" s="14" t="n">
-        <v>2715</v>
+        <v>39</v>
       </c>
       <c r="I218" s="14" t="n">
-        <v>7985</v>
+        <v>8614</v>
       </c>
       <c r="J218" s="15" t="n">
-        <v>299.72</v>
+        <v>55.11</v>
       </c>
       <c r="K218" s="15" t="n">
-        <v>301.71</v>
+        <v>55.71</v>
       </c>
       <c r="L218" s="16">
         <f>F218*(K218-J218)</f>
@@ -8308,31 +8308,31 @@
     <row r="219" ht="16.5" customHeight="1">
       <c r="D219" s="13" t="inlineStr">
         <is>
-          <t>健策(3653)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="E219" s="14" t="n">
-        <v>23</v>
+        <v>818</v>
       </c>
       <c r="F219" s="14" t="n">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="G219" s="14" t="n">
-        <v>8891</v>
+        <v>8297</v>
       </c>
       <c r="H219" s="14" t="n">
-        <v>7448</v>
+        <v>633</v>
       </c>
       <c r="I219" s="14" t="n">
-        <v>1443</v>
+        <v>7664</v>
       </c>
       <c r="J219" s="15" t="n">
-        <v>3865.65</v>
+        <v>101.44</v>
       </c>
       <c r="K219" s="15" t="n">
-        <v>3920.26</v>
-      </c>
-      <c r="L219" s="16">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="L219" s="17">
         <f>F219*(K219-J219)</f>
         <v/>
       </c>
@@ -8340,31 +8340,31 @@
     <row r="220" ht="16.5" customHeight="1">
       <c r="D220" s="13" t="inlineStr">
         <is>
-          <t>奇鋐(3017)</t>
+          <t>緯穎(6669)</t>
         </is>
       </c>
       <c r="E220" s="14" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F220" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G220" s="14" t="n">
-        <v>8756</v>
+        <v>6265</v>
       </c>
       <c r="H220" s="14" t="n">
-        <v>535</v>
+        <v>34</v>
       </c>
       <c r="I220" s="14" t="n">
-        <v>8221</v>
+        <v>6231</v>
       </c>
       <c r="J220" s="15" t="n">
-        <v>2501.69</v>
+        <v>5695.45</v>
       </c>
       <c r="K220" s="15" t="n">
-        <v>2675.5</v>
-      </c>
-      <c r="L220" s="16">
+        <v>336</v>
+      </c>
+      <c r="L220" s="17">
         <f>F220*(K220-J220)</f>
         <v/>
       </c>
@@ -8439,29 +8439,29 @@
       </c>
       <c r="D222" s="13" t="inlineStr">
         <is>
-          <t>聯鈞(3450)</t>
+          <t>上銀(2049)</t>
         </is>
       </c>
       <c r="E222" s="14" t="n">
-        <v>157</v>
+        <v>321</v>
       </c>
       <c r="F222" s="14" t="n">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="G222" s="14" t="n">
-        <v>6602</v>
+        <v>11858</v>
       </c>
       <c r="H222" s="14" t="n">
-        <v>4316</v>
+        <v>120</v>
       </c>
       <c r="I222" s="14" t="n">
-        <v>2286</v>
+        <v>11738</v>
       </c>
       <c r="J222" s="15" t="n">
-        <v>420.51</v>
+        <v>369.4</v>
       </c>
       <c r="K222" s="15" t="n">
-        <v>423.13</v>
+        <v>400.67</v>
       </c>
       <c r="L222" s="16">
         <f>F222*(K222-J222)</f>
@@ -8471,31 +8471,31 @@
     <row r="223" ht="16.5" customHeight="1">
       <c r="D223" s="13" t="inlineStr">
         <is>
-          <t>禾伸堂(3026)</t>
+          <t>和椿(6215)</t>
         </is>
       </c>
       <c r="E223" s="14" t="n">
-        <v>152</v>
+        <v>901</v>
       </c>
       <c r="F223" s="14" t="n">
-        <v>218</v>
+        <v>1</v>
       </c>
       <c r="G223" s="14" t="n">
-        <v>5044</v>
+        <v>11319</v>
       </c>
       <c r="H223" s="14" t="n">
-        <v>7282</v>
+        <v>12</v>
       </c>
       <c r="I223" s="14" t="n">
-        <v>-2238</v>
+        <v>11307</v>
       </c>
       <c r="J223" s="15" t="n">
-        <v>331.84</v>
+        <v>125.63</v>
       </c>
       <c r="K223" s="15" t="n">
-        <v>334.05</v>
-      </c>
-      <c r="L223" s="16">
+        <v>125</v>
+      </c>
+      <c r="L223" s="17">
         <f>F223*(K223-J223)</f>
         <v/>
       </c>
@@ -8503,29 +8503,29 @@
     <row r="224" ht="16.5" customHeight="1">
       <c r="D224" s="13" t="inlineStr">
         <is>
-          <t>AES-KY(6781)</t>
+          <t>國精化(4722)</t>
         </is>
       </c>
       <c r="E224" s="14" t="n">
-        <v>38</v>
+        <v>436</v>
       </c>
       <c r="F224" s="14" t="n">
-        <v>6</v>
+        <v>402</v>
       </c>
       <c r="G224" s="14" t="n">
-        <v>4850</v>
+        <v>11265</v>
       </c>
       <c r="H224" s="14" t="n">
-        <v>797</v>
+        <v>10386</v>
       </c>
       <c r="I224" s="14" t="n">
-        <v>4053</v>
+        <v>879</v>
       </c>
       <c r="J224" s="15" t="n">
-        <v>1276.21</v>
+        <v>258.36</v>
       </c>
       <c r="K224" s="15" t="n">
-        <v>1328.67</v>
+        <v>258.36</v>
       </c>
       <c r="L224" s="16">
         <f>F224*(K224-J224)</f>
@@ -8535,29 +8535,29 @@
     <row r="225" ht="16.5" customHeight="1">
       <c r="D225" s="13" t="inlineStr">
         <is>
-          <t>國精化(4722)</t>
+          <t>大銀微系統(4576)</t>
         </is>
       </c>
       <c r="E225" s="14" t="n">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="F225" s="14" t="n">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="G225" s="14" t="n">
-        <v>4581</v>
+        <v>6324</v>
       </c>
       <c r="H225" s="14" t="n">
-        <v>3592</v>
+        <v>1268</v>
       </c>
       <c r="I225" s="14" t="n">
-        <v>989</v>
+        <v>5056</v>
       </c>
       <c r="J225" s="15" t="n">
-        <v>258.81</v>
+        <v>256.03</v>
       </c>
       <c r="K225" s="15" t="n">
-        <v>258.42</v>
+        <v>253.5</v>
       </c>
       <c r="L225" s="17">
         <f>F225*(K225-J225)</f>
@@ -8567,29 +8567,29 @@
     <row r="226" ht="16.5" customHeight="1">
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>緯穎(6669)</t>
         </is>
       </c>
       <c r="E226" s="14" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F226" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G226" s="14" t="n">
-        <v>4417</v>
+        <v>6152</v>
       </c>
       <c r="H226" s="14" t="n">
-        <v>544</v>
+        <v>3499</v>
       </c>
       <c r="I226" s="14" t="n">
-        <v>3873</v>
+        <v>2653</v>
       </c>
       <c r="J226" s="15" t="n">
-        <v>2208.6</v>
+        <v>5592.73</v>
       </c>
       <c r="K226" s="15" t="n">
-        <v>2718.5</v>
+        <v>5832.33</v>
       </c>
       <c r="L226" s="16">
         <f>F226*(K226-J226)</f>
@@ -8599,29 +8599,29 @@
     <row r="227" ht="16.5" customHeight="1">
       <c r="D227" s="13" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>燿華(2367)</t>
         </is>
       </c>
       <c r="E227" s="14" t="n">
-        <v>10</v>
+        <v>912</v>
       </c>
       <c r="F227" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G227" s="14" t="n">
-        <v>3749</v>
+        <v>5875</v>
       </c>
       <c r="H227" s="14" t="n">
-        <v>1802</v>
+        <v>45</v>
       </c>
       <c r="I227" s="14" t="n">
-        <v>1947</v>
+        <v>5830</v>
       </c>
       <c r="J227" s="15" t="n">
-        <v>3749.1</v>
+        <v>64.42</v>
       </c>
       <c r="K227" s="15" t="n">
-        <v>3603.8</v>
+        <v>64</v>
       </c>
       <c r="L227" s="17">
         <f>F227*(K227-J227)</f>
@@ -8631,29 +8631,29 @@
     <row r="228" ht="16.5" customHeight="1">
       <c r="D228" s="13" t="inlineStr">
         <is>
-          <t>世界(5347)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E228" s="14" t="n">
-        <v>172</v>
+        <v>366</v>
       </c>
       <c r="F228" s="14" t="n">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="G228" s="14" t="n">
-        <v>2972</v>
+        <v>4387</v>
       </c>
       <c r="H228" s="14" t="n">
-        <v>506</v>
+        <v>883</v>
       </c>
       <c r="I228" s="14" t="n">
-        <v>2466</v>
+        <v>3504</v>
       </c>
       <c r="J228" s="15" t="n">
-        <v>172.82</v>
+        <v>119.86</v>
       </c>
       <c r="K228" s="15" t="n">
-        <v>174.38</v>
+        <v>120.97</v>
       </c>
       <c r="L228" s="16">
         <f>F228*(K228-J228)</f>
@@ -8663,29 +8663,29 @@
     <row r="229" ht="16.5" customHeight="1">
       <c r="D229" s="13" t="inlineStr">
         <is>
-          <t>新唐(4919)</t>
+          <t>華通(2313)</t>
         </is>
       </c>
       <c r="E229" s="14" t="n">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="F229" s="14" t="n">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="G229" s="14" t="n">
-        <v>2879</v>
+        <v>3917</v>
       </c>
       <c r="H229" s="14" t="n">
-        <v>1616</v>
+        <v>545</v>
       </c>
       <c r="I229" s="14" t="n">
-        <v>1263</v>
+        <v>3372</v>
       </c>
       <c r="J229" s="15" t="n">
-        <v>175.54</v>
+        <v>261.12</v>
       </c>
       <c r="K229" s="15" t="n">
-        <v>173.73</v>
+        <v>259.67</v>
       </c>
       <c r="L229" s="17">
         <f>F229*(K229-J229)</f>
@@ -8695,29 +8695,29 @@
     <row r="230" ht="16.5" customHeight="1">
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>光洋科(1785)</t>
+          <t>國巨*(2327)</t>
         </is>
       </c>
       <c r="E230" s="14" t="n">
-        <v>171</v>
+        <v>87</v>
       </c>
       <c r="F230" s="14" t="n">
-        <v>220</v>
+        <v>162</v>
       </c>
       <c r="G230" s="14" t="n">
-        <v>2800</v>
+        <v>3637</v>
       </c>
       <c r="H230" s="14" t="n">
-        <v>3558</v>
+        <v>6510</v>
       </c>
       <c r="I230" s="14" t="n">
-        <v>-758</v>
+        <v>-2873</v>
       </c>
       <c r="J230" s="15" t="n">
-        <v>163.74</v>
+        <v>418.01</v>
       </c>
       <c r="K230" s="15" t="n">
-        <v>161.71</v>
+        <v>401.88</v>
       </c>
       <c r="L230" s="17">
         <f>F230*(K230-J230)</f>
@@ -8727,31 +8727,31 @@
     <row r="231" ht="16.5" customHeight="1">
       <c r="D231" s="13" t="inlineStr">
         <is>
-          <t>統新(6426)</t>
+          <t>信昌電(6173)</t>
         </is>
       </c>
       <c r="E231" s="14" t="n">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="F231" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G231" s="14" t="n">
-        <v>2509</v>
+        <v>2793</v>
       </c>
       <c r="H231" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I231" s="14" t="n">
-        <v>2508</v>
+        <v>2793</v>
       </c>
       <c r="J231" s="15" t="n">
-        <v>258.66</v>
+        <v>147</v>
       </c>
       <c r="K231" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="L231" s="17">
+        <v>0</v>
+      </c>
+      <c r="L231" s="16">
         <f>F231*(K231-J231)</f>
         <v/>
       </c>
@@ -8826,31 +8826,31 @@
       </c>
       <c r="D233" s="13" t="inlineStr">
         <is>
-          <t>智邦(2345)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="E233" s="14" t="n">
-        <v>16</v>
+        <v>3042</v>
       </c>
       <c r="F233" s="14" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="G233" s="14" t="n">
-        <v>4132</v>
+        <v>30663</v>
       </c>
       <c r="H233" s="14" t="n">
-        <v>5633</v>
+        <v>635</v>
       </c>
       <c r="I233" s="14" t="n">
-        <v>-1501</v>
+        <v>30028</v>
       </c>
       <c r="J233" s="15" t="n">
-        <v>2582.81</v>
+        <v>100.8</v>
       </c>
       <c r="K233" s="15" t="n">
-        <v>2560.59</v>
-      </c>
-      <c r="L233" s="17">
+        <v>102.39</v>
+      </c>
+      <c r="L233" s="16">
         <f>F233*(K233-J233)</f>
         <v/>
       </c>
@@ -8858,29 +8858,29 @@
     <row r="234" ht="16.5" customHeight="1">
       <c r="D234" s="13" t="inlineStr">
         <is>
-          <t>華星光(4979)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E234" s="14" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F234" s="14" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G234" s="14" t="n">
-        <v>3384</v>
+        <v>3368</v>
       </c>
       <c r="H234" s="14" t="n">
-        <v>134</v>
+        <v>4102</v>
       </c>
       <c r="I234" s="14" t="n">
-        <v>3250</v>
+        <v>-734</v>
       </c>
       <c r="J234" s="15" t="n">
-        <v>676.74</v>
+        <v>2807</v>
       </c>
       <c r="K234" s="15" t="n">
-        <v>671.5</v>
+        <v>2734.8</v>
       </c>
       <c r="L234" s="17">
         <f>F234*(K234-J234)</f>
@@ -8890,31 +8890,31 @@
     <row r="235" ht="16.5" customHeight="1">
       <c r="D235" s="13" t="inlineStr">
         <is>
-          <t>宇瞻(8271)</t>
+          <t>華通(2313)</t>
         </is>
       </c>
       <c r="E235" s="14" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="F235" s="14" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G235" s="14" t="n">
-        <v>2876</v>
+        <v>3230</v>
       </c>
       <c r="H235" s="14" t="n">
-        <v>280</v>
+        <v>661</v>
       </c>
       <c r="I235" s="14" t="n">
-        <v>2596</v>
+        <v>2569</v>
       </c>
       <c r="J235" s="15" t="n">
-        <v>256.76</v>
+        <v>256.33</v>
       </c>
       <c r="K235" s="15" t="n">
-        <v>254.91</v>
-      </c>
-      <c r="L235" s="17">
+        <v>264.24</v>
+      </c>
+      <c r="L235" s="16">
         <f>F235*(K235-J235)</f>
         <v/>
       </c>
@@ -8922,29 +8922,29 @@
     <row r="236" ht="16.5" customHeight="1">
       <c r="D236" s="13" t="inlineStr">
         <is>
-          <t>聯亞(3081)</t>
+          <t>金居(8358)</t>
         </is>
       </c>
       <c r="E236" s="14" t="n">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="F236" s="14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G236" s="14" t="n">
-        <v>2826</v>
+        <v>3084</v>
       </c>
       <c r="H236" s="14" t="n">
-        <v>46</v>
+        <v>612</v>
       </c>
       <c r="I236" s="14" t="n">
-        <v>2780</v>
+        <v>2472</v>
       </c>
       <c r="J236" s="15" t="n">
-        <v>3140.44</v>
+        <v>489.54</v>
       </c>
       <c r="K236" s="15" t="n">
-        <v>463</v>
+        <v>470.46</v>
       </c>
       <c r="L236" s="17">
         <f>F236*(K236-J236)</f>
@@ -8954,29 +8954,29 @@
     <row r="237" ht="16.5" customHeight="1">
       <c r="D237" s="13" t="inlineStr">
         <is>
-          <t>奇鋐(3017)</t>
+          <t>華星光(4979)</t>
         </is>
       </c>
       <c r="E237" s="14" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="F237" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G237" s="14" t="n">
-        <v>2322</v>
+        <v>2868</v>
       </c>
       <c r="H237" s="14" t="n">
-        <v>2855</v>
+        <v>687</v>
       </c>
       <c r="I237" s="14" t="n">
-        <v>-533</v>
+        <v>2181</v>
       </c>
       <c r="J237" s="15" t="n">
-        <v>2579.67</v>
+        <v>667.09</v>
       </c>
       <c r="K237" s="15" t="n">
-        <v>2595.18</v>
+        <v>686.6</v>
       </c>
       <c r="L237" s="16">
         <f>F237*(K237-J237)</f>
@@ -8986,31 +8986,31 @@
     <row r="238" ht="16.5" customHeight="1">
       <c r="D238" s="13" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E238" s="14" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="F238" s="14" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G238" s="14" t="n">
-        <v>2315</v>
+        <v>2577</v>
       </c>
       <c r="H238" s="14" t="n">
-        <v>1056</v>
+        <v>1133</v>
       </c>
       <c r="I238" s="14" t="n">
-        <v>1259</v>
+        <v>1444</v>
       </c>
       <c r="J238" s="15" t="n">
-        <v>3857.83</v>
+        <v>314.22</v>
       </c>
       <c r="K238" s="15" t="n">
-        <v>3521.67</v>
-      </c>
-      <c r="L238" s="17">
+        <v>314.69</v>
+      </c>
+      <c r="L238" s="16">
         <f>F238*(K238-J238)</f>
         <v/>
       </c>
@@ -9018,31 +9018,31 @@
     <row r="239" ht="16.5" customHeight="1">
       <c r="D239" s="13" t="inlineStr">
         <is>
-          <t>健策(3653)</t>
+          <t>眾達-KY(4977)</t>
         </is>
       </c>
       <c r="E239" s="14" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="F239" s="14" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="G239" s="14" t="n">
-        <v>2156</v>
+        <v>1988</v>
       </c>
       <c r="H239" s="14" t="n">
-        <v>2341</v>
+        <v>1035</v>
       </c>
       <c r="I239" s="14" t="n">
-        <v>-185</v>
+        <v>953</v>
       </c>
       <c r="J239" s="15" t="n">
-        <v>4311.6</v>
+        <v>258.25</v>
       </c>
       <c r="K239" s="15" t="n">
-        <v>3901.83</v>
-      </c>
-      <c r="L239" s="17">
+        <v>258.65</v>
+      </c>
+      <c r="L239" s="16">
         <f>F239*(K239-J239)</f>
         <v/>
       </c>
@@ -9050,31 +9050,31 @@
     <row r="240" ht="16.5" customHeight="1">
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>一詮(2486)</t>
+          <t>創意(3443)</t>
         </is>
       </c>
       <c r="E240" s="14" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="F240" s="14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G240" s="14" t="n">
-        <v>2127</v>
+        <v>1890</v>
       </c>
       <c r="H240" s="14" t="n">
-        <v>145</v>
+        <v>1131</v>
       </c>
       <c r="I240" s="14" t="n">
-        <v>1982</v>
+        <v>759</v>
       </c>
       <c r="J240" s="15" t="n">
-        <v>283.6</v>
+        <v>6301.67</v>
       </c>
       <c r="K240" s="15" t="n">
-        <v>290.6</v>
-      </c>
-      <c r="L240" s="16">
+        <v>5655</v>
+      </c>
+      <c r="L240" s="17">
         <f>F240*(K240-J240)</f>
         <v/>
       </c>
@@ -9082,31 +9082,31 @@
     <row r="241" ht="16.5" customHeight="1">
       <c r="D241" s="13" t="inlineStr">
         <is>
-          <t>緯穎(6669)</t>
+          <t>光洋科(1785)</t>
         </is>
       </c>
       <c r="E241" s="14" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="F241" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G241" s="14" t="n">
-        <v>2093</v>
+        <v>1827</v>
       </c>
       <c r="H241" s="14" t="n">
-        <v>2635</v>
+        <v>16</v>
       </c>
       <c r="I241" s="14" t="n">
-        <v>-542</v>
+        <v>1811</v>
       </c>
       <c r="J241" s="15" t="n">
-        <v>5231.75</v>
+        <v>158.86</v>
       </c>
       <c r="K241" s="15" t="n">
-        <v>5270</v>
-      </c>
-      <c r="L241" s="16">
+        <v>157</v>
+      </c>
+      <c r="L241" s="17">
         <f>F241*(K241-J241)</f>
         <v/>
       </c>
@@ -9114,31 +9114,31 @@
     <row r="242" ht="16.5" customHeight="1">
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>精材(3374)</t>
         </is>
       </c>
       <c r="E242" s="14" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="F242" s="14" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="G242" s="14" t="n">
-        <v>2029</v>
+        <v>1814</v>
       </c>
       <c r="H242" s="14" t="n">
-        <v>430</v>
+        <v>2609</v>
       </c>
       <c r="I242" s="14" t="n">
-        <v>1599</v>
+        <v>-795</v>
       </c>
       <c r="J242" s="15" t="n">
-        <v>2254</v>
+        <v>255.54</v>
       </c>
       <c r="K242" s="15" t="n">
-        <v>2148.5</v>
-      </c>
-      <c r="L242" s="17">
+        <v>255.77</v>
+      </c>
+      <c r="L242" s="16">
         <f>F242*(K242-J242)</f>
         <v/>
       </c>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -9256,29 +9256,29 @@
     <row r="245" ht="16.5" customHeight="1">
       <c r="D245" s="13" t="inlineStr">
         <is>
-          <t>藥華藥(6446) ▲9.99%</t>
+          <t>麗正(2302) ▲9.94%</t>
         </is>
       </c>
       <c r="E245" s="14" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F245" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G245" s="14" t="n">
-        <v>305</v>
+        <v>133</v>
       </c>
       <c r="H245" s="14" t="n">
-        <v>648</v>
+        <v>16</v>
       </c>
       <c r="I245" s="14" t="n">
-        <v>-343</v>
+        <v>117</v>
       </c>
       <c r="J245" s="15" t="n">
-        <v>761.75</v>
+        <v>26</v>
       </c>
       <c r="K245" s="15" t="n">
-        <v>810</v>
+        <v>26</v>
       </c>
       <c r="L245" s="16">
         <f>F245*(K245-J245)</f>
@@ -9286,196 +9286,70 @@
       </c>
     </row>
     <row r="246" ht="16.5" customHeight="1">
-      <c r="D246" s="13" t="inlineStr">
-        <is>
-          <t>健鼎(3044) ▲9.98%</t>
-        </is>
-      </c>
-      <c r="E246" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F246" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="G246" s="14" t="n">
-        <v>156</v>
-      </c>
-      <c r="H246" s="14" t="n">
-        <v>470</v>
-      </c>
-      <c r="I246" s="14" t="n">
-        <v>-314</v>
-      </c>
-      <c r="J246" s="15" t="n">
-        <v>518.67</v>
-      </c>
-      <c r="K246" s="15" t="n">
-        <v>522.78</v>
-      </c>
-      <c r="L246" s="16">
-        <f>F246*(K246-J246)</f>
-        <v/>
-      </c>
+      <c r="D246" s="13" t="n"/>
+      <c r="E246" s="14" t="n"/>
+      <c r="F246" s="14" t="n"/>
+      <c r="G246" s="14" t="n"/>
+      <c r="H246" s="14" t="n"/>
+      <c r="I246" s="14" t="n"/>
+      <c r="J246" s="15" t="n"/>
+      <c r="K246" s="15" t="n"/>
+      <c r="L246" s="16" t="n"/>
     </row>
     <row r="247" ht="16.5" customHeight="1">
-      <c r="D247" s="13" t="inlineStr">
-        <is>
-          <t>麗正(2302) ▲9.94%</t>
-        </is>
-      </c>
-      <c r="E247" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="F247" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="G247" s="14" t="n">
-        <v>133</v>
-      </c>
-      <c r="H247" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="I247" s="14" t="n">
-        <v>117</v>
-      </c>
-      <c r="J247" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="K247" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="L247" s="16">
-        <f>F247*(K247-J247)</f>
-        <v/>
-      </c>
+      <c r="D247" s="13" t="n"/>
+      <c r="E247" s="14" t="n"/>
+      <c r="F247" s="14" t="n"/>
+      <c r="G247" s="14" t="n"/>
+      <c r="H247" s="14" t="n"/>
+      <c r="I247" s="14" t="n"/>
+      <c r="J247" s="15" t="n"/>
+      <c r="K247" s="15" t="n"/>
+      <c r="L247" s="16" t="n"/>
     </row>
     <row r="248" ht="16.5" customHeight="1">
-      <c r="D248" s="13" t="inlineStr">
-        <is>
-          <t>TPK-KY(3673) ▲9.9%</t>
-        </is>
-      </c>
-      <c r="E248" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="F248" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="G248" s="14" t="n">
-        <v>86</v>
-      </c>
-      <c r="H248" s="14" t="n">
-        <v>581</v>
-      </c>
-      <c r="I248" s="14" t="n">
-        <v>-495</v>
-      </c>
-      <c r="J248" s="15" t="n">
-        <v>61.79</v>
-      </c>
-      <c r="K248" s="15" t="n">
-        <v>64.54000000000001</v>
-      </c>
-      <c r="L248" s="16">
-        <f>F248*(K248-J248)</f>
-        <v/>
-      </c>
+      <c r="D248" s="13" t="n"/>
+      <c r="E248" s="14" t="n"/>
+      <c r="F248" s="14" t="n"/>
+      <c r="G248" s="14" t="n"/>
+      <c r="H248" s="14" t="n"/>
+      <c r="I248" s="14" t="n"/>
+      <c r="J248" s="15" t="n"/>
+      <c r="K248" s="15" t="n"/>
+      <c r="L248" s="16" t="n"/>
     </row>
     <row r="249" ht="16.5" customHeight="1">
-      <c r="D249" s="13" t="inlineStr">
-        <is>
-          <t>元太(8069) ▲9.97%</t>
-        </is>
-      </c>
-      <c r="E249" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F249" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="G249" s="14" t="n">
-        <v>42</v>
-      </c>
-      <c r="H249" s="14" t="n">
-        <v>235</v>
-      </c>
-      <c r="I249" s="14" t="n">
-        <v>-193</v>
-      </c>
-      <c r="J249" s="15" t="n">
-        <v>212</v>
-      </c>
-      <c r="K249" s="15" t="n">
-        <v>213.36</v>
-      </c>
-      <c r="L249" s="16">
-        <f>F249*(K249-J249)</f>
-        <v/>
-      </c>
+      <c r="D249" s="13" t="n"/>
+      <c r="E249" s="14" t="n"/>
+      <c r="F249" s="14" t="n"/>
+      <c r="G249" s="14" t="n"/>
+      <c r="H249" s="14" t="n"/>
+      <c r="I249" s="14" t="n"/>
+      <c r="J249" s="15" t="n"/>
+      <c r="K249" s="15" t="n"/>
+      <c r="L249" s="16" t="n"/>
     </row>
     <row r="250" ht="16.5" customHeight="1">
-      <c r="D250" s="13" t="inlineStr">
-        <is>
-          <t>邁科(6831) ▲9.9%</t>
-        </is>
-      </c>
-      <c r="E250" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F250" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="G250" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H250" s="14" t="n">
-        <v>423</v>
-      </c>
-      <c r="I250" s="14" t="n">
-        <v>-423</v>
-      </c>
-      <c r="J250" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K250" s="15" t="n">
-        <v>705.17</v>
-      </c>
-      <c r="L250" s="16">
-        <f>F250*(K250-J250)</f>
-        <v/>
-      </c>
+      <c r="D250" s="13" t="n"/>
+      <c r="E250" s="14" t="n"/>
+      <c r="F250" s="14" t="n"/>
+      <c r="G250" s="14" t="n"/>
+      <c r="H250" s="14" t="n"/>
+      <c r="I250" s="14" t="n"/>
+      <c r="J250" s="15" t="n"/>
+      <c r="K250" s="15" t="n"/>
+      <c r="L250" s="16" t="n"/>
     </row>
     <row r="251" ht="16.5" customHeight="1">
-      <c r="D251" s="13" t="inlineStr">
-        <is>
-          <t>安可(3615) ▲9.89%</t>
-        </is>
-      </c>
-      <c r="E251" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F251" s="14" t="n">
-        <v>27</v>
-      </c>
-      <c r="G251" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H251" s="14" t="n">
-        <v>98</v>
-      </c>
-      <c r="I251" s="14" t="n">
-        <v>-98</v>
-      </c>
-      <c r="J251" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K251" s="15" t="n">
-        <v>36.11</v>
-      </c>
-      <c r="L251" s="16">
-        <f>F251*(K251-J251)</f>
-        <v/>
-      </c>
+      <c r="D251" s="13" t="n"/>
+      <c r="E251" s="14" t="n"/>
+      <c r="F251" s="14" t="n"/>
+      <c r="G251" s="14" t="n"/>
+      <c r="H251" s="14" t="n"/>
+      <c r="I251" s="14" t="n"/>
+      <c r="J251" s="15" t="n"/>
+      <c r="K251" s="15" t="n"/>
+      <c r="L251" s="16" t="n"/>
     </row>
     <row r="252" ht="16.5" customHeight="1">
       <c r="D252" s="13" t="n"/>
@@ -9601,29 +9475,29 @@
     <row r="256" ht="16.5" customHeight="1">
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>印能科技(7734) ▲9.92%</t>
+          <t>健鼎(3044) ▲9.98%</t>
         </is>
       </c>
       <c r="E256" s="14" t="n">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="F256" s="14" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G256" s="14" t="n">
-        <v>5160</v>
+        <v>3733</v>
       </c>
       <c r="H256" s="14" t="n">
-        <v>16300</v>
+        <v>1428</v>
       </c>
       <c r="I256" s="14" t="n">
-        <v>-11140</v>
+        <v>2305</v>
       </c>
       <c r="J256" s="15" t="n">
-        <v>4299.58</v>
+        <v>525.79</v>
       </c>
       <c r="K256" s="15" t="n">
-        <v>4405.54</v>
+        <v>529</v>
       </c>
       <c r="L256" s="16">
         <f>F256*(K256-J256)</f>
@@ -9631,68 +9505,26 @@
       </c>
     </row>
     <row r="257" ht="16.5" customHeight="1">
-      <c r="D257" s="13" t="inlineStr">
-        <is>
-          <t>健鼎(3044) ▲9.98%</t>
-        </is>
-      </c>
-      <c r="E257" s="14" t="n">
-        <v>71</v>
-      </c>
-      <c r="F257" s="14" t="n">
-        <v>27</v>
-      </c>
-      <c r="G257" s="14" t="n">
-        <v>3733</v>
-      </c>
-      <c r="H257" s="14" t="n">
-        <v>1428</v>
-      </c>
-      <c r="I257" s="14" t="n">
-        <v>2305</v>
-      </c>
-      <c r="J257" s="15" t="n">
-        <v>525.79</v>
-      </c>
-      <c r="K257" s="15" t="n">
-        <v>529</v>
-      </c>
-      <c r="L257" s="16">
-        <f>F257*(K257-J257)</f>
-        <v/>
-      </c>
+      <c r="D257" s="13" t="n"/>
+      <c r="E257" s="14" t="n"/>
+      <c r="F257" s="14" t="n"/>
+      <c r="G257" s="14" t="n"/>
+      <c r="H257" s="14" t="n"/>
+      <c r="I257" s="14" t="n"/>
+      <c r="J257" s="15" t="n"/>
+      <c r="K257" s="15" t="n"/>
+      <c r="L257" s="16" t="n"/>
     </row>
     <row r="258" ht="16.5" customHeight="1">
-      <c r="D258" s="13" t="inlineStr">
-        <is>
-          <t>中探針(6217) ▲10.0%</t>
-        </is>
-      </c>
-      <c r="E258" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F258" s="14" t="n">
-        <v>161</v>
-      </c>
-      <c r="G258" s="14" t="n">
-        <v>99</v>
-      </c>
-      <c r="H258" s="14" t="n">
-        <v>5488</v>
-      </c>
-      <c r="I258" s="14" t="n">
-        <v>-5389</v>
-      </c>
-      <c r="J258" s="15" t="n">
-        <v>328.67</v>
-      </c>
-      <c r="K258" s="15" t="n">
-        <v>340.89</v>
-      </c>
-      <c r="L258" s="16">
-        <f>F258*(K258-J258)</f>
-        <v/>
-      </c>
+      <c r="D258" s="13" t="n"/>
+      <c r="E258" s="14" t="n"/>
+      <c r="F258" s="14" t="n"/>
+      <c r="G258" s="14" t="n"/>
+      <c r="H258" s="14" t="n"/>
+      <c r="I258" s="14" t="n"/>
+      <c r="J258" s="15" t="n"/>
+      <c r="K258" s="15" t="n"/>
+      <c r="L258" s="16" t="n"/>
     </row>
     <row r="259" ht="16.5" customHeight="1">
       <c r="D259" s="13" t="n"/>
@@ -10052,68 +9884,26 @@
       </c>
     </row>
     <row r="273" ht="16.5" customHeight="1">
-      <c r="D273" s="13" t="inlineStr">
-        <is>
-          <t>元太(8069) ▲9.97%</t>
-        </is>
-      </c>
-      <c r="E273" s="14" t="n">
-        <v>161</v>
-      </c>
-      <c r="F273" s="14" t="n">
-        <v>1550</v>
-      </c>
-      <c r="G273" s="14" t="n">
-        <v>3378</v>
-      </c>
-      <c r="H273" s="14" t="n">
-        <v>32293</v>
-      </c>
-      <c r="I273" s="14" t="n">
-        <v>-28915</v>
-      </c>
-      <c r="J273" s="15" t="n">
-        <v>209.83</v>
-      </c>
-      <c r="K273" s="15" t="n">
-        <v>208.34</v>
-      </c>
-      <c r="L273" s="17">
-        <f>F273*(K273-J273)</f>
-        <v/>
-      </c>
+      <c r="D273" s="13" t="n"/>
+      <c r="E273" s="14" t="n"/>
+      <c r="F273" s="14" t="n"/>
+      <c r="G273" s="14" t="n"/>
+      <c r="H273" s="14" t="n"/>
+      <c r="I273" s="14" t="n"/>
+      <c r="J273" s="15" t="n"/>
+      <c r="K273" s="15" t="n"/>
+      <c r="L273" s="16" t="n"/>
     </row>
     <row r="274" ht="16.5" customHeight="1">
-      <c r="D274" s="13" t="inlineStr">
-        <is>
-          <t>麗正(2302) ▲9.94%</t>
-        </is>
-      </c>
-      <c r="E274" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F274" s="14" t="n">
-        <v>1001</v>
-      </c>
-      <c r="G274" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H274" s="14" t="n">
-        <v>2603</v>
-      </c>
-      <c r="I274" s="14" t="n">
-        <v>-2598</v>
-      </c>
-      <c r="J274" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="K274" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="L274" s="16">
-        <f>F274*(K274-J274)</f>
-        <v/>
-      </c>
+      <c r="D274" s="13" t="n"/>
+      <c r="E274" s="14" t="n"/>
+      <c r="F274" s="14" t="n"/>
+      <c r="G274" s="14" t="n"/>
+      <c r="H274" s="14" t="n"/>
+      <c r="I274" s="14" t="n"/>
+      <c r="J274" s="15" t="n"/>
+      <c r="K274" s="15" t="n"/>
+      <c r="L274" s="16" t="n"/>
     </row>
     <row r="275" ht="16.5" customHeight="1">
       <c r="D275" s="13" t="n"/>
@@ -13418,29 +13208,29 @@
     <row r="368" ht="16.5" customHeight="1">
       <c r="D368" s="13" t="inlineStr">
         <is>
-          <t>旺宏(2337) ▲9.8%</t>
+          <t>亞帝歐(3516) ▲10.0%</t>
         </is>
       </c>
       <c r="E368" s="14" t="n">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="F368" s="14" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="G368" s="14" t="n">
-        <v>1244</v>
+        <v>855</v>
       </c>
       <c r="H368" s="14" t="n">
-        <v>1945</v>
+        <v>0</v>
       </c>
       <c r="I368" s="14" t="n">
-        <v>-701</v>
+        <v>855</v>
       </c>
       <c r="J368" s="15" t="n">
-        <v>157.41</v>
+        <v>23.1</v>
       </c>
       <c r="K368" s="15" t="n">
-        <v>159.45</v>
+        <v>0</v>
       </c>
       <c r="L368" s="16">
         <f>F368*(K368-J368)</f>
@@ -13450,29 +13240,29 @@
     <row r="369" ht="16.5" customHeight="1">
       <c r="D369" s="13" t="inlineStr">
         <is>
-          <t>亞帝歐(3516) ▲10.0%</t>
+          <t>中化生(1762) ▲10.0%</t>
         </is>
       </c>
       <c r="E369" s="14" t="n">
-        <v>370</v>
+        <v>114</v>
       </c>
       <c r="F369" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G369" s="14" t="n">
-        <v>855</v>
+        <v>433</v>
       </c>
       <c r="H369" s="14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I369" s="14" t="n">
-        <v>855</v>
+        <v>414</v>
       </c>
       <c r="J369" s="15" t="n">
-        <v>23.1</v>
+        <v>37.95</v>
       </c>
       <c r="K369" s="15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L369" s="16">
         <f>F369*(K369-J369)</f>
@@ -13482,29 +13272,29 @@
     <row r="370" ht="16.5" customHeight="1">
       <c r="D370" s="13" t="inlineStr">
         <is>
-          <t>中化生(1762) ▲10.0%</t>
+          <t>國邑*(6875) ▲10.0%</t>
         </is>
       </c>
       <c r="E370" s="14" t="n">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="F370" s="14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G370" s="14" t="n">
-        <v>433</v>
+        <v>149</v>
       </c>
       <c r="H370" s="14" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I370" s="14" t="n">
-        <v>414</v>
+        <v>149</v>
       </c>
       <c r="J370" s="15" t="n">
-        <v>37.95</v>
+        <v>40.16</v>
       </c>
       <c r="K370" s="15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L370" s="16">
         <f>F370*(K370-J370)</f>
@@ -13514,29 +13304,29 @@
     <row r="371" ht="16.5" customHeight="1">
       <c r="D371" s="13" t="inlineStr">
         <is>
-          <t>京晨科(6419) ▲9.97%</t>
+          <t>銘旺實(4432) ▲9.89%</t>
         </is>
       </c>
       <c r="E371" s="14" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="F371" s="14" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="G371" s="14" t="n">
-        <v>158</v>
+        <v>72</v>
       </c>
       <c r="H371" s="14" t="n">
-        <v>2253</v>
+        <v>0</v>
       </c>
       <c r="I371" s="14" t="n">
-        <v>-2095</v>
+        <v>72</v>
       </c>
       <c r="J371" s="15" t="n">
-        <v>157.9</v>
+        <v>15.54</v>
       </c>
       <c r="K371" s="15" t="n">
-        <v>164.44</v>
+        <v>0</v>
       </c>
       <c r="L371" s="16">
         <f>F371*(K371-J371)</f>
@@ -13544,100 +13334,37 @@
       </c>
     </row>
     <row r="372" ht="16.5" customHeight="1">
-      <c r="D372" s="13" t="inlineStr">
-        <is>
-          <t>國邑*(6875) ▲10.0%</t>
-        </is>
-      </c>
-      <c r="E372" s="14" t="n">
-        <v>37</v>
-      </c>
-      <c r="F372" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G372" s="14" t="n">
-        <v>149</v>
-      </c>
-      <c r="H372" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I372" s="14" t="n">
-        <v>149</v>
-      </c>
-      <c r="J372" s="15" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="K372" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L372" s="16">
-        <f>F372*(K372-J372)</f>
-        <v/>
-      </c>
+      <c r="D372" s="13" t="n"/>
+      <c r="E372" s="14" t="n"/>
+      <c r="F372" s="14" t="n"/>
+      <c r="G372" s="14" t="n"/>
+      <c r="H372" s="14" t="n"/>
+      <c r="I372" s="14" t="n"/>
+      <c r="J372" s="15" t="n"/>
+      <c r="K372" s="15" t="n"/>
+      <c r="L372" s="16" t="n"/>
     </row>
     <row r="373" ht="16.5" customHeight="1">
-      <c r="D373" s="13" t="inlineStr">
-        <is>
-          <t>銘旺實(4432) ▲9.89%</t>
-        </is>
-      </c>
-      <c r="E373" s="14" t="n">
-        <v>46</v>
-      </c>
-      <c r="F373" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G373" s="14" t="n">
-        <v>72</v>
-      </c>
-      <c r="H373" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I373" s="14" t="n">
-        <v>72</v>
-      </c>
-      <c r="J373" s="15" t="n">
-        <v>15.54</v>
-      </c>
-      <c r="K373" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L373" s="16">
-        <f>F373*(K373-J373)</f>
-        <v/>
-      </c>
+      <c r="D373" s="13" t="n"/>
+      <c r="E373" s="14" t="n"/>
+      <c r="F373" s="14" t="n"/>
+      <c r="G373" s="14" t="n"/>
+      <c r="H373" s="14" t="n"/>
+      <c r="I373" s="14" t="n"/>
+      <c r="J373" s="15" t="n"/>
+      <c r="K373" s="15" t="n"/>
+      <c r="L373" s="16" t="n"/>
     </row>
     <row r="374" ht="16.5" customHeight="1">
-      <c r="D374" s="13" t="inlineStr">
-        <is>
-          <t>麗正(2302) ▲9.94%</t>
-        </is>
-      </c>
-      <c r="E374" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F374" s="14" t="n">
-        <v>1507</v>
-      </c>
-      <c r="G374" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H374" s="14" t="n">
-        <v>3756</v>
-      </c>
-      <c r="I374" s="14" t="n">
-        <v>-3751</v>
-      </c>
-      <c r="J374" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="K374" s="15" t="n">
-        <v>24.93</v>
-      </c>
-      <c r="L374" s="16">
-        <f>F374*(K374-J374)</f>
-        <v/>
-      </c>
+      <c r="D374" s="13" t="n"/>
+      <c r="E374" s="14" t="n"/>
+      <c r="F374" s="14" t="n"/>
+      <c r="G374" s="14" t="n"/>
+      <c r="H374" s="14" t="n"/>
+      <c r="I374" s="14" t="n"/>
+      <c r="J374" s="15" t="n"/>
+      <c r="K374" s="15" t="n"/>
+      <c r="L374" s="16" t="n"/>
     </row>
     <row r="375" ht="16.5" customHeight="1">
       <c r="A375" s="12" t="inlineStr">
@@ -13717,132 +13444,48 @@
           <t>9B2n</t>
         </is>
       </c>
-      <c r="D376" s="13" t="inlineStr">
-        <is>
-          <t>元太(8069) ▲9.97%</t>
-        </is>
-      </c>
-      <c r="E376" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F376" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="G376" s="14" t="n">
-        <v>84</v>
-      </c>
-      <c r="H376" s="14" t="n">
-        <v>1463</v>
-      </c>
-      <c r="I376" s="14" t="n">
-        <v>-1379</v>
-      </c>
-      <c r="J376" s="15" t="n">
-        <v>209.5</v>
-      </c>
-      <c r="K376" s="15" t="n">
-        <v>208.96</v>
-      </c>
-      <c r="L376" s="17">
-        <f>F376*(K376-J376)</f>
-        <v/>
-      </c>
+      <c r="D376" s="13" t="n"/>
+      <c r="E376" s="14" t="n"/>
+      <c r="F376" s="14" t="n"/>
+      <c r="G376" s="14" t="n"/>
+      <c r="H376" s="14" t="n"/>
+      <c r="I376" s="14" t="n"/>
+      <c r="J376" s="15" t="n"/>
+      <c r="K376" s="15" t="n"/>
+      <c r="L376" s="16" t="n"/>
     </row>
     <row r="377" ht="16.5" customHeight="1">
-      <c r="D377" s="13" t="inlineStr">
-        <is>
-          <t>臺慶科(3357) ▲9.79%</t>
-        </is>
-      </c>
-      <c r="E377" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F377" s="14" t="n">
-        <v>33</v>
-      </c>
-      <c r="G377" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H377" s="14" t="n">
-        <v>698</v>
-      </c>
-      <c r="I377" s="14" t="n">
-        <v>-698</v>
-      </c>
-      <c r="J377" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K377" s="15" t="n">
-        <v>211.48</v>
-      </c>
-      <c r="L377" s="16">
-        <f>F377*(K377-J377)</f>
-        <v/>
-      </c>
+      <c r="D377" s="13" t="n"/>
+      <c r="E377" s="14" t="n"/>
+      <c r="F377" s="14" t="n"/>
+      <c r="G377" s="14" t="n"/>
+      <c r="H377" s="14" t="n"/>
+      <c r="I377" s="14" t="n"/>
+      <c r="J377" s="15" t="n"/>
+      <c r="K377" s="15" t="n"/>
+      <c r="L377" s="16" t="n"/>
     </row>
     <row r="378" ht="16.5" customHeight="1">
-      <c r="D378" s="13" t="inlineStr">
-        <is>
-          <t>中探針(6217) ▲10.0%</t>
-        </is>
-      </c>
-      <c r="E378" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F378" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="G378" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H378" s="14" t="n">
-        <v>692</v>
-      </c>
-      <c r="I378" s="14" t="n">
-        <v>-692</v>
-      </c>
-      <c r="J378" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K378" s="15" t="n">
-        <v>345.85</v>
-      </c>
-      <c r="L378" s="16">
-        <f>F378*(K378-J378)</f>
-        <v/>
-      </c>
+      <c r="D378" s="13" t="n"/>
+      <c r="E378" s="14" t="n"/>
+      <c r="F378" s="14" t="n"/>
+      <c r="G378" s="14" t="n"/>
+      <c r="H378" s="14" t="n"/>
+      <c r="I378" s="14" t="n"/>
+      <c r="J378" s="15" t="n"/>
+      <c r="K378" s="15" t="n"/>
+      <c r="L378" s="16" t="n"/>
     </row>
     <row r="379" ht="16.5" customHeight="1">
-      <c r="D379" s="13" t="inlineStr">
-        <is>
-          <t>聯德控股-KY(4912) ▲10.0%</t>
-        </is>
-      </c>
-      <c r="E379" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F379" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="G379" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H379" s="14" t="n">
-        <v>418</v>
-      </c>
-      <c r="I379" s="14" t="n">
-        <v>-418</v>
-      </c>
-      <c r="J379" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K379" s="15" t="n">
-        <v>104.5</v>
-      </c>
-      <c r="L379" s="16">
-        <f>F379*(K379-J379)</f>
-        <v/>
-      </c>
+      <c r="D379" s="13" t="n"/>
+      <c r="E379" s="14" t="n"/>
+      <c r="F379" s="14" t="n"/>
+      <c r="G379" s="14" t="n"/>
+      <c r="H379" s="14" t="n"/>
+      <c r="I379" s="14" t="n"/>
+      <c r="J379" s="15" t="n"/>
+      <c r="K379" s="15" t="n"/>
+      <c r="L379" s="16" t="n"/>
     </row>
     <row r="380" ht="16.5" customHeight="1">
       <c r="D380" s="13" t="n"/>
@@ -14076,29 +13719,29 @@
     <row r="390" ht="16.5" customHeight="1">
       <c r="D390" s="13" t="inlineStr">
         <is>
-          <t>元太(8069) ▲9.97%</t>
+          <t>麗正(2302) ▲9.94%</t>
         </is>
       </c>
       <c r="E390" s="14" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="F390" s="14" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="G390" s="14" t="n">
-        <v>636</v>
+        <v>242</v>
       </c>
       <c r="H390" s="14" t="n">
-        <v>1113</v>
+        <v>36</v>
       </c>
       <c r="I390" s="14" t="n">
-        <v>-477</v>
+        <v>206</v>
       </c>
       <c r="J390" s="15" t="n">
-        <v>212.07</v>
+        <v>26</v>
       </c>
       <c r="K390" s="15" t="n">
-        <v>214.06</v>
+        <v>26</v>
       </c>
       <c r="L390" s="16">
         <f>F390*(K390-J390)</f>
@@ -14106,100 +13749,37 @@
       </c>
     </row>
     <row r="391" ht="16.5" customHeight="1">
-      <c r="D391" s="13" t="inlineStr">
-        <is>
-          <t>健鼎(3044) ▲9.98%</t>
-        </is>
-      </c>
-      <c r="E391" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="F391" s="14" t="n">
-        <v>41</v>
-      </c>
-      <c r="G391" s="14" t="n">
-        <v>623</v>
-      </c>
-      <c r="H391" s="14" t="n">
-        <v>2168</v>
-      </c>
-      <c r="I391" s="14" t="n">
-        <v>-1545</v>
-      </c>
-      <c r="J391" s="15" t="n">
-        <v>518.92</v>
-      </c>
-      <c r="K391" s="15" t="n">
-        <v>528.8</v>
-      </c>
-      <c r="L391" s="16">
-        <f>F391*(K391-J391)</f>
-        <v/>
-      </c>
+      <c r="D391" s="13" t="n"/>
+      <c r="E391" s="14" t="n"/>
+      <c r="F391" s="14" t="n"/>
+      <c r="G391" s="14" t="n"/>
+      <c r="H391" s="14" t="n"/>
+      <c r="I391" s="14" t="n"/>
+      <c r="J391" s="15" t="n"/>
+      <c r="K391" s="15" t="n"/>
+      <c r="L391" s="16" t="n"/>
     </row>
     <row r="392" ht="16.5" customHeight="1">
-      <c r="D392" s="13" t="inlineStr">
-        <is>
-          <t>麗正(2302) ▲9.94%</t>
-        </is>
-      </c>
-      <c r="E392" s="14" t="n">
-        <v>93</v>
-      </c>
-      <c r="F392" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="G392" s="14" t="n">
-        <v>242</v>
-      </c>
-      <c r="H392" s="14" t="n">
-        <v>36</v>
-      </c>
-      <c r="I392" s="14" t="n">
-        <v>206</v>
-      </c>
-      <c r="J392" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="K392" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="L392" s="16">
-        <f>F392*(K392-J392)</f>
-        <v/>
-      </c>
+      <c r="D392" s="13" t="n"/>
+      <c r="E392" s="14" t="n"/>
+      <c r="F392" s="14" t="n"/>
+      <c r="G392" s="14" t="n"/>
+      <c r="H392" s="14" t="n"/>
+      <c r="I392" s="14" t="n"/>
+      <c r="J392" s="15" t="n"/>
+      <c r="K392" s="15" t="n"/>
+      <c r="L392" s="16" t="n"/>
     </row>
     <row r="393" ht="16.5" customHeight="1">
-      <c r="D393" s="13" t="inlineStr">
-        <is>
-          <t>印能科技(7734) ▲9.92%</t>
-        </is>
-      </c>
-      <c r="E393" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F393" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G393" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H393" s="14" t="n">
-        <v>542</v>
-      </c>
-      <c r="I393" s="14" t="n">
-        <v>-540</v>
-      </c>
-      <c r="J393" s="15" t="n">
-        <v>21</v>
-      </c>
-      <c r="K393" s="15" t="n">
-        <v>5419</v>
-      </c>
-      <c r="L393" s="16">
-        <f>F393*(K393-J393)</f>
-        <v/>
-      </c>
+      <c r="D393" s="13" t="n"/>
+      <c r="E393" s="14" t="n"/>
+      <c r="F393" s="14" t="n"/>
+      <c r="G393" s="14" t="n"/>
+      <c r="H393" s="14" t="n"/>
+      <c r="I393" s="14" t="n"/>
+      <c r="J393" s="15" t="n"/>
+      <c r="K393" s="15" t="n"/>
+      <c r="L393" s="16" t="n"/>
     </row>
     <row r="394" ht="16.5" customHeight="1">
       <c r="D394" s="13" t="n"/>
@@ -14304,29 +13884,29 @@
       </c>
       <c r="D398" s="13" t="inlineStr">
         <is>
-          <t>旺宏(2337) ▲9.8%</t>
+          <t>印能科技(7734) ▲9.92%</t>
         </is>
       </c>
       <c r="E398" s="14" t="n">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="F398" s="14" t="n">
-        <v>322</v>
+        <v>1</v>
       </c>
       <c r="G398" s="14" t="n">
-        <v>1738</v>
+        <v>836</v>
       </c>
       <c r="H398" s="14" t="n">
-        <v>5202</v>
+        <v>431</v>
       </c>
       <c r="I398" s="14" t="n">
-        <v>-3464</v>
+        <v>405</v>
       </c>
       <c r="J398" s="15" t="n">
-        <v>159.4</v>
+        <v>4180</v>
       </c>
       <c r="K398" s="15" t="n">
-        <v>161.56</v>
+        <v>4313</v>
       </c>
       <c r="L398" s="16">
         <f>F398*(K398-J398)</f>
@@ -14336,29 +13916,29 @@
     <row r="399" ht="16.5" customHeight="1">
       <c r="D399" s="13" t="inlineStr">
         <is>
-          <t>印能科技(7734) ▲9.92%</t>
+          <t>台汽電(8926) ▲9.88%</t>
         </is>
       </c>
       <c r="E399" s="14" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F399" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G399" s="14" t="n">
-        <v>836</v>
+        <v>284</v>
       </c>
       <c r="H399" s="14" t="n">
-        <v>431</v>
+        <v>6</v>
       </c>
       <c r="I399" s="14" t="n">
-        <v>405</v>
+        <v>278</v>
       </c>
       <c r="J399" s="15" t="n">
-        <v>4180</v>
+        <v>56.7</v>
       </c>
       <c r="K399" s="15" t="n">
-        <v>4313</v>
+        <v>57</v>
       </c>
       <c r="L399" s="16">
         <f>F399*(K399-J399)</f>
@@ -14366,100 +13946,37 @@
       </c>
     </row>
     <row r="400" ht="16.5" customHeight="1">
-      <c r="D400" s="13" t="inlineStr">
-        <is>
-          <t>微星(2377) ▲10.0%</t>
-        </is>
-      </c>
-      <c r="E400" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="F400" s="14" t="n">
-        <v>102</v>
-      </c>
-      <c r="G400" s="14" t="n">
-        <v>438</v>
-      </c>
-      <c r="H400" s="14" t="n">
-        <v>1168</v>
-      </c>
-      <c r="I400" s="14" t="n">
-        <v>-730</v>
-      </c>
-      <c r="J400" s="15" t="n">
-        <v>109.58</v>
-      </c>
-      <c r="K400" s="15" t="n">
-        <v>114.48</v>
-      </c>
-      <c r="L400" s="16">
-        <f>F400*(K400-J400)</f>
-        <v/>
-      </c>
+      <c r="D400" s="13" t="n"/>
+      <c r="E400" s="14" t="n"/>
+      <c r="F400" s="14" t="n"/>
+      <c r="G400" s="14" t="n"/>
+      <c r="H400" s="14" t="n"/>
+      <c r="I400" s="14" t="n"/>
+      <c r="J400" s="15" t="n"/>
+      <c r="K400" s="15" t="n"/>
+      <c r="L400" s="16" t="n"/>
     </row>
     <row r="401" ht="16.5" customHeight="1">
-      <c r="D401" s="13" t="inlineStr">
-        <is>
-          <t>台汽電(8926) ▲9.88%</t>
-        </is>
-      </c>
-      <c r="E401" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="F401" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G401" s="14" t="n">
-        <v>284</v>
-      </c>
-      <c r="H401" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="I401" s="14" t="n">
-        <v>278</v>
-      </c>
-      <c r="J401" s="15" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="K401" s="15" t="n">
-        <v>57</v>
-      </c>
-      <c r="L401" s="16">
-        <f>F401*(K401-J401)</f>
-        <v/>
-      </c>
+      <c r="D401" s="13" t="n"/>
+      <c r="E401" s="14" t="n"/>
+      <c r="F401" s="14" t="n"/>
+      <c r="G401" s="14" t="n"/>
+      <c r="H401" s="14" t="n"/>
+      <c r="I401" s="14" t="n"/>
+      <c r="J401" s="15" t="n"/>
+      <c r="K401" s="15" t="n"/>
+      <c r="L401" s="16" t="n"/>
     </row>
     <row r="402" ht="16.5" customHeight="1">
-      <c r="D402" s="13" t="inlineStr">
-        <is>
-          <t>元太(8069) ▲9.97%</t>
-        </is>
-      </c>
-      <c r="E402" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="F402" s="14" t="n">
-        <v>39</v>
-      </c>
-      <c r="G402" s="14" t="n">
-        <v>167</v>
-      </c>
-      <c r="H402" s="14" t="n">
-        <v>847</v>
-      </c>
-      <c r="I402" s="14" t="n">
-        <v>-680</v>
-      </c>
-      <c r="J402" s="15" t="n">
-        <v>208.62</v>
-      </c>
-      <c r="K402" s="15" t="n">
-        <v>217.23</v>
-      </c>
-      <c r="L402" s="16">
-        <f>F402*(K402-J402)</f>
-        <v/>
-      </c>
+      <c r="D402" s="13" t="n"/>
+      <c r="E402" s="14" t="n"/>
+      <c r="F402" s="14" t="n"/>
+      <c r="G402" s="14" t="n"/>
+      <c r="H402" s="14" t="n"/>
+      <c r="I402" s="14" t="n"/>
+      <c r="J402" s="15" t="n"/>
+      <c r="K402" s="15" t="n"/>
+      <c r="L402" s="16" t="n"/>
     </row>
     <row r="403" ht="16.5" customHeight="1">
       <c r="D403" s="13" t="n"/>
@@ -14756,31 +14273,31 @@
     <row r="414" ht="16.5" customHeight="1">
       <c r="D414" s="13" t="inlineStr">
         <is>
-          <t>微星(2377) ▲10.0%</t>
+          <t>大甲(2221) ▲9.91%</t>
         </is>
       </c>
       <c r="E414" s="14" t="n">
-        <v>163</v>
+        <v>272</v>
       </c>
       <c r="F414" s="14" t="n">
-        <v>3100</v>
+        <v>1</v>
       </c>
       <c r="G414" s="14" t="n">
-        <v>1850</v>
+        <v>1130</v>
       </c>
       <c r="H414" s="14" t="n">
-        <v>33836</v>
+        <v>4</v>
       </c>
       <c r="I414" s="14" t="n">
-        <v>-31986</v>
+        <v>1126</v>
       </c>
       <c r="J414" s="15" t="n">
-        <v>113.47</v>
+        <v>41.54</v>
       </c>
       <c r="K414" s="15" t="n">
-        <v>109.15</v>
-      </c>
-      <c r="L414" s="17">
+        <v>42</v>
+      </c>
+      <c r="L414" s="16">
         <f>F414*(K414-J414)</f>
         <v/>
       </c>
@@ -14788,31 +14305,31 @@
     <row r="415" ht="16.5" customHeight="1">
       <c r="D415" s="13" t="inlineStr">
         <is>
-          <t>元太(8069) ▲9.97%</t>
+          <t>健鼎(3044) ▲9.98%</t>
         </is>
       </c>
       <c r="E415" s="14" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="F415" s="14" t="n">
-        <v>868</v>
+        <v>3</v>
       </c>
       <c r="G415" s="14" t="n">
-        <v>1244</v>
+        <v>1089</v>
       </c>
       <c r="H415" s="14" t="n">
-        <v>18079</v>
+        <v>167</v>
       </c>
       <c r="I415" s="14" t="n">
-        <v>-16835</v>
+        <v>922</v>
       </c>
       <c r="J415" s="15" t="n">
-        <v>214.48</v>
+        <v>518.52</v>
       </c>
       <c r="K415" s="15" t="n">
-        <v>208.28</v>
-      </c>
-      <c r="L415" s="17">
+        <v>555.67</v>
+      </c>
+      <c r="L415" s="16">
         <f>F415*(K415-J415)</f>
         <v/>
       </c>
@@ -14820,29 +14337,29 @@
     <row r="416" ht="16.5" customHeight="1">
       <c r="D416" s="13" t="inlineStr">
         <is>
-          <t>大甲(2221) ▲9.91%</t>
+          <t>鑽石投資(6901) ▲9.67%</t>
         </is>
       </c>
       <c r="E416" s="14" t="n">
-        <v>272</v>
+        <v>647</v>
       </c>
       <c r="F416" s="14" t="n">
-        <v>1</v>
+        <v>539</v>
       </c>
       <c r="G416" s="14" t="n">
-        <v>1130</v>
+        <v>954</v>
       </c>
       <c r="H416" s="14" t="n">
-        <v>4</v>
+        <v>795</v>
       </c>
       <c r="I416" s="14" t="n">
-        <v>1126</v>
+        <v>159</v>
       </c>
       <c r="J416" s="15" t="n">
-        <v>41.54</v>
+        <v>14.75</v>
       </c>
       <c r="K416" s="15" t="n">
-        <v>42</v>
+        <v>14.75</v>
       </c>
       <c r="L416" s="16">
         <f>F416*(K416-J416)</f>
@@ -14852,31 +14369,31 @@
     <row r="417" ht="16.5" customHeight="1">
       <c r="D417" s="13" t="inlineStr">
         <is>
-          <t>健鼎(3044) ▲9.98%</t>
+          <t>凌華(6166) ▲9.85%</t>
         </is>
       </c>
       <c r="E417" s="14" t="n">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="F417" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G417" s="14" t="n">
-        <v>1089</v>
+        <v>774</v>
       </c>
       <c r="H417" s="14" t="n">
-        <v>167</v>
+        <v>63</v>
       </c>
       <c r="I417" s="14" t="n">
-        <v>922</v>
+        <v>711</v>
       </c>
       <c r="J417" s="15" t="n">
-        <v>518.52</v>
+        <v>110.51</v>
       </c>
       <c r="K417" s="15" t="n">
-        <v>555.67</v>
-      </c>
-      <c r="L417" s="16">
+        <v>104.5</v>
+      </c>
+      <c r="L417" s="17">
         <f>F417*(K417-J417)</f>
         <v/>
       </c>
@@ -14884,31 +14401,31 @@
     <row r="418" ht="16.5" customHeight="1">
       <c r="D418" s="13" t="inlineStr">
         <is>
-          <t>鑽石投資(6901) ▲9.67%</t>
+          <t>印能科技(7734) ▲9.92%</t>
         </is>
       </c>
       <c r="E418" s="14" t="n">
-        <v>647</v>
+        <v>1</v>
       </c>
       <c r="F418" s="14" t="n">
-        <v>539</v>
+        <v>1</v>
       </c>
       <c r="G418" s="14" t="n">
-        <v>954</v>
+        <v>455</v>
       </c>
       <c r="H418" s="14" t="n">
-        <v>795</v>
+        <v>6</v>
       </c>
       <c r="I418" s="14" t="n">
-        <v>159</v>
+        <v>449</v>
       </c>
       <c r="J418" s="15" t="n">
-        <v>14.75</v>
+        <v>4550</v>
       </c>
       <c r="K418" s="15" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="L418" s="16">
+        <v>65</v>
+      </c>
+      <c r="L418" s="17">
         <f>F418*(K418-J418)</f>
         <v/>
       </c>
@@ -14983,29 +14500,29 @@
       </c>
       <c r="D420" s="13" t="inlineStr">
         <is>
-          <t>旺宏(2337) ▲9.8%</t>
+          <t>藥華藥(6446) ▲9.99%</t>
         </is>
       </c>
       <c r="E420" s="14" t="n">
-        <v>287</v>
+        <v>50</v>
       </c>
       <c r="F420" s="14" t="n">
-        <v>362</v>
+        <v>9</v>
       </c>
       <c r="G420" s="14" t="n">
-        <v>4606</v>
+        <v>3869</v>
       </c>
       <c r="H420" s="14" t="n">
-        <v>5757</v>
+        <v>696</v>
       </c>
       <c r="I420" s="14" t="n">
-        <v>-1151</v>
+        <v>3173</v>
       </c>
       <c r="J420" s="15" t="n">
-        <v>160.49</v>
+        <v>773.74</v>
       </c>
       <c r="K420" s="15" t="n">
-        <v>159.04</v>
+        <v>773</v>
       </c>
       <c r="L420" s="17">
         <f>F420*(K420-J420)</f>
@@ -15015,29 +14532,29 @@
     <row r="421" ht="16.5" customHeight="1">
       <c r="D421" s="13" t="inlineStr">
         <is>
-          <t>藥華藥(6446) ▲9.99%</t>
+          <t>微星(2377) ▲10.0%</t>
         </is>
       </c>
       <c r="E421" s="14" t="n">
-        <v>50</v>
+        <v>280</v>
       </c>
       <c r="F421" s="14" t="n">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G421" s="14" t="n">
-        <v>3869</v>
+        <v>3170</v>
       </c>
       <c r="H421" s="14" t="n">
-        <v>696</v>
+        <v>1021</v>
       </c>
       <c r="I421" s="14" t="n">
-        <v>3173</v>
+        <v>2149</v>
       </c>
       <c r="J421" s="15" t="n">
-        <v>773.74</v>
+        <v>113.2</v>
       </c>
       <c r="K421" s="15" t="n">
-        <v>773</v>
+        <v>109.74</v>
       </c>
       <c r="L421" s="17">
         <f>F421*(K421-J421)</f>
@@ -15047,31 +14564,31 @@
     <row r="422" ht="16.5" customHeight="1">
       <c r="D422" s="13" t="inlineStr">
         <is>
-          <t>微星(2377) ▲10.0%</t>
+          <t>健鼎(3044) ▲9.98%</t>
         </is>
       </c>
       <c r="E422" s="14" t="n">
-        <v>280</v>
+        <v>36</v>
       </c>
       <c r="F422" s="14" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="G422" s="14" t="n">
-        <v>3170</v>
+        <v>1923</v>
       </c>
       <c r="H422" s="14" t="n">
-        <v>1021</v>
+        <v>216</v>
       </c>
       <c r="I422" s="14" t="n">
-        <v>2149</v>
+        <v>1707</v>
       </c>
       <c r="J422" s="15" t="n">
-        <v>113.2</v>
+        <v>534.28</v>
       </c>
       <c r="K422" s="15" t="n">
-        <v>109.74</v>
-      </c>
-      <c r="L422" s="17">
+        <v>539.75</v>
+      </c>
+      <c r="L422" s="16">
         <f>F422*(K422-J422)</f>
         <v/>
       </c>
@@ -15079,31 +14596,31 @@
     <row r="423" ht="16.5" customHeight="1">
       <c r="D423" s="13" t="inlineStr">
         <is>
-          <t>健鼎(3044) ▲9.98%</t>
+          <t>台汽電(8926) ▲9.88%</t>
         </is>
       </c>
       <c r="E423" s="14" t="n">
-        <v>36</v>
+        <v>205</v>
       </c>
       <c r="F423" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G423" s="14" t="n">
-        <v>1923</v>
+        <v>1162</v>
       </c>
       <c r="H423" s="14" t="n">
-        <v>216</v>
+        <v>17</v>
       </c>
       <c r="I423" s="14" t="n">
-        <v>1707</v>
+        <v>1145</v>
       </c>
       <c r="J423" s="15" t="n">
-        <v>534.28</v>
+        <v>56.7</v>
       </c>
       <c r="K423" s="15" t="n">
-        <v>539.75</v>
-      </c>
-      <c r="L423" s="16">
+        <v>56</v>
+      </c>
+      <c r="L423" s="17">
         <f>F423*(K423-J423)</f>
         <v/>
       </c>
@@ -15111,98 +14628,56 @@
     <row r="424" ht="16.5" customHeight="1">
       <c r="D424" s="13" t="inlineStr">
         <is>
-          <t>台汽電(8926) ▲9.88%</t>
+          <t>鈺邦(6449) ▲9.82%</t>
         </is>
       </c>
       <c r="E424" s="14" t="n">
-        <v>205</v>
+        <v>44</v>
       </c>
       <c r="F424" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G424" s="14" t="n">
-        <v>1162</v>
+        <v>942</v>
       </c>
       <c r="H424" s="14" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I424" s="14" t="n">
-        <v>1145</v>
+        <v>898</v>
       </c>
       <c r="J424" s="15" t="n">
-        <v>56.7</v>
+        <v>214.02</v>
       </c>
       <c r="K424" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="L424" s="17">
+        <v>222.5</v>
+      </c>
+      <c r="L424" s="16">
         <f>F424*(K424-J424)</f>
         <v/>
       </c>
     </row>
     <row r="425" ht="16.5" customHeight="1">
-      <c r="D425" s="13" t="inlineStr">
-        <is>
-          <t>鈺邦(6449) ▲9.82%</t>
-        </is>
-      </c>
-      <c r="E425" s="14" t="n">
-        <v>44</v>
-      </c>
-      <c r="F425" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G425" s="14" t="n">
-        <v>942</v>
-      </c>
-      <c r="H425" s="14" t="n">
-        <v>44</v>
-      </c>
-      <c r="I425" s="14" t="n">
-        <v>898</v>
-      </c>
-      <c r="J425" s="15" t="n">
-        <v>214.02</v>
-      </c>
-      <c r="K425" s="15" t="n">
-        <v>222.5</v>
-      </c>
-      <c r="L425" s="16">
-        <f>F425*(K425-J425)</f>
-        <v/>
-      </c>
+      <c r="D425" s="13" t="n"/>
+      <c r="E425" s="14" t="n"/>
+      <c r="F425" s="14" t="n"/>
+      <c r="G425" s="14" t="n"/>
+      <c r="H425" s="14" t="n"/>
+      <c r="I425" s="14" t="n"/>
+      <c r="J425" s="15" t="n"/>
+      <c r="K425" s="15" t="n"/>
+      <c r="L425" s="16" t="n"/>
     </row>
     <row r="426" ht="16.5" customHeight="1">
-      <c r="D426" s="13" t="inlineStr">
-        <is>
-          <t>印能科技(7734) ▲9.92%</t>
-        </is>
-      </c>
-      <c r="E426" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F426" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G426" s="14" t="n">
-        <v>444</v>
-      </c>
-      <c r="H426" s="14" t="n">
-        <v>1381</v>
-      </c>
-      <c r="I426" s="14" t="n">
-        <v>-937</v>
-      </c>
-      <c r="J426" s="15" t="n">
-        <v>4439</v>
-      </c>
-      <c r="K426" s="15" t="n">
-        <v>4603</v>
-      </c>
-      <c r="L426" s="16">
-        <f>F426*(K426-J426)</f>
-        <v/>
-      </c>
+      <c r="D426" s="13" t="n"/>
+      <c r="E426" s="14" t="n"/>
+      <c r="F426" s="14" t="n"/>
+      <c r="G426" s="14" t="n"/>
+      <c r="H426" s="14" t="n"/>
+      <c r="I426" s="14" t="n"/>
+      <c r="J426" s="15" t="n"/>
+      <c r="K426" s="15" t="n"/>
+      <c r="L426" s="16" t="n"/>
     </row>
     <row r="427" ht="16.5" customHeight="1">
       <c r="D427" s="13" t="n"/>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="E189" s="31" t="n">
-        <v>1776</v>
+        <v>1771</v>
       </c>
       <c r="F189" s="31" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G189" s="31" t="n">
         <v>23292</v>
@@ -8080,12 +8080,12 @@
         <v>21855</v>
       </c>
       <c r="J189" s="32" t="n">
-        <v>131.15</v>
+        <v>131.52</v>
       </c>
       <c r="K189" s="32" t="n">
-        <v>130.67</v>
-      </c>
-      <c r="L189" s="33">
+        <v>131.87</v>
+      </c>
+      <c r="L189" s="35">
         <f>F189*(K189-J189)</f>
         <v/>
       </c>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="E191" s="31" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F191" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G191" s="31" t="n">
         <v>5757</v>
@@ -8150,12 +8150,12 @@
         <v>4744</v>
       </c>
       <c r="J191" s="32" t="n">
-        <v>738.05</v>
+        <v>767.5700000000001</v>
       </c>
       <c r="K191" s="32" t="n">
-        <v>723.5</v>
-      </c>
-      <c r="L191" s="33">
+        <v>779.15</v>
+      </c>
+      <c r="L191" s="35">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -8170,10 +8170,10 @@
         </is>
       </c>
       <c r="E192" s="31" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F192" s="31" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G192" s="31" t="n">
         <v>4738</v>
@@ -8185,12 +8185,12 @@
         <v>2441</v>
       </c>
       <c r="J192" s="32" t="n">
-        <v>361.64</v>
+        <v>358.9</v>
       </c>
       <c r="K192" s="32" t="n">
-        <v>364.59</v>
-      </c>
-      <c r="L192" s="35">
+        <v>358.89</v>
+      </c>
+      <c r="L192" s="33">
         <f>F192*(K192-J192)</f>
         <v/>
       </c>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="E193" s="31" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F193" s="31" t="n">
         <v>23</v>
@@ -8220,12 +8220,12 @@
         <v>3857</v>
       </c>
       <c r="J193" s="32" t="n">
-        <v>140.27</v>
+        <v>141.7</v>
       </c>
       <c r="K193" s="32" t="n">
         <v>140.39</v>
       </c>
-      <c r="L193" s="35">
+      <c r="L193" s="33">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -8306,29 +8306,29 @@
       <c r="C196" s="34" t="n"/>
       <c r="D196" s="30" t="inlineStr">
         <is>
-          <t>友達(2409)</t>
+          <t>大綜(3147)</t>
         </is>
       </c>
       <c r="E196" s="31" t="n">
-        <v>1046</v>
+        <v>106</v>
       </c>
       <c r="F196" s="31" t="n">
-        <v>943</v>
+        <v>0</v>
       </c>
       <c r="G196" s="31" t="n">
-        <v>2835</v>
+        <v>3016</v>
       </c>
       <c r="H196" s="31" t="n">
-        <v>2556</v>
+        <v>0</v>
       </c>
       <c r="I196" s="31" t="n">
-        <v>279</v>
+        <v>3016</v>
       </c>
       <c r="J196" s="32" t="n">
-        <v>27.1</v>
+        <v>284.5</v>
       </c>
       <c r="K196" s="32" t="n">
-        <v>27.1</v>
+        <v>0</v>
       </c>
       <c r="L196" s="35">
         <f>F196*(K196-J196)</f>
@@ -8376,31 +8376,31 @@
       <c r="C198" s="34" t="n"/>
       <c r="D198" s="30" t="inlineStr">
         <is>
-          <t>群創(3481)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E198" s="31" t="n">
-        <v>442</v>
+        <v>158</v>
       </c>
       <c r="F198" s="31" t="n">
-        <v>320</v>
+        <v>47</v>
       </c>
       <c r="G198" s="31" t="n">
-        <v>2305</v>
+        <v>2560</v>
       </c>
       <c r="H198" s="31" t="n">
-        <v>1643</v>
+        <v>761</v>
       </c>
       <c r="I198" s="31" t="n">
-        <v>662</v>
+        <v>1799</v>
       </c>
       <c r="J198" s="32" t="n">
-        <v>52.15</v>
+        <v>162</v>
       </c>
       <c r="K198" s="32" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="L198" s="33">
+        <v>162</v>
+      </c>
+      <c r="L198" s="35">
         <f>F198*(K198-J198)</f>
         <v/>
       </c>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="E189" s="31" t="n">
-        <v>1771</v>
+        <v>1776</v>
       </c>
       <c r="F189" s="31" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G189" s="31" t="n">
         <v>23292</v>
@@ -8080,12 +8080,12 @@
         <v>21855</v>
       </c>
       <c r="J189" s="32" t="n">
-        <v>131.52</v>
+        <v>131.15</v>
       </c>
       <c r="K189" s="32" t="n">
-        <v>131.87</v>
-      </c>
-      <c r="L189" s="35">
+        <v>130.67</v>
+      </c>
+      <c r="L189" s="33">
         <f>F189*(K189-J189)</f>
         <v/>
       </c>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="E191" s="31" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F191" s="31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G191" s="31" t="n">
         <v>5757</v>
@@ -8150,12 +8150,12 @@
         <v>4744</v>
       </c>
       <c r="J191" s="32" t="n">
-        <v>767.5700000000001</v>
+        <v>738.05</v>
       </c>
       <c r="K191" s="32" t="n">
-        <v>779.15</v>
-      </c>
-      <c r="L191" s="35">
+        <v>723.5</v>
+      </c>
+      <c r="L191" s="33">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -8170,10 +8170,10 @@
         </is>
       </c>
       <c r="E192" s="31" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F192" s="31" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G192" s="31" t="n">
         <v>4738</v>
@@ -8185,12 +8185,12 @@
         <v>2441</v>
       </c>
       <c r="J192" s="32" t="n">
-        <v>358.9</v>
+        <v>361.64</v>
       </c>
       <c r="K192" s="32" t="n">
-        <v>358.89</v>
-      </c>
-      <c r="L192" s="33">
+        <v>364.59</v>
+      </c>
+      <c r="L192" s="35">
         <f>F192*(K192-J192)</f>
         <v/>
       </c>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="E193" s="31" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F193" s="31" t="n">
         <v>23</v>
@@ -8220,12 +8220,12 @@
         <v>3857</v>
       </c>
       <c r="J193" s="32" t="n">
-        <v>141.7</v>
+        <v>140.27</v>
       </c>
       <c r="K193" s="32" t="n">
         <v>140.39</v>
       </c>
-      <c r="L193" s="33">
+      <c r="L193" s="35">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -8306,29 +8306,29 @@
       <c r="C196" s="34" t="n"/>
       <c r="D196" s="30" t="inlineStr">
         <is>
-          <t>大綜(3147)</t>
+          <t>友達(2409)</t>
         </is>
       </c>
       <c r="E196" s="31" t="n">
-        <v>106</v>
+        <v>1046</v>
       </c>
       <c r="F196" s="31" t="n">
-        <v>0</v>
+        <v>943</v>
       </c>
       <c r="G196" s="31" t="n">
-        <v>3016</v>
+        <v>2835</v>
       </c>
       <c r="H196" s="31" t="n">
-        <v>0</v>
+        <v>2556</v>
       </c>
       <c r="I196" s="31" t="n">
-        <v>3016</v>
+        <v>279</v>
       </c>
       <c r="J196" s="32" t="n">
-        <v>284.5</v>
+        <v>27.1</v>
       </c>
       <c r="K196" s="32" t="n">
-        <v>0</v>
+        <v>27.1</v>
       </c>
       <c r="L196" s="35">
         <f>F196*(K196-J196)</f>
@@ -8376,31 +8376,31 @@
       <c r="C198" s="34" t="n"/>
       <c r="D198" s="30" t="inlineStr">
         <is>
-          <t>華邦電(2344)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E198" s="31" t="n">
-        <v>158</v>
+        <v>442</v>
       </c>
       <c r="F198" s="31" t="n">
-        <v>47</v>
+        <v>320</v>
       </c>
       <c r="G198" s="31" t="n">
-        <v>2560</v>
+        <v>2305</v>
       </c>
       <c r="H198" s="31" t="n">
-        <v>761</v>
+        <v>1643</v>
       </c>
       <c r="I198" s="31" t="n">
-        <v>1799</v>
+        <v>662</v>
       </c>
       <c r="J198" s="32" t="n">
-        <v>162</v>
+        <v>52.15</v>
       </c>
       <c r="K198" s="32" t="n">
-        <v>162</v>
-      </c>
-      <c r="L198" s="35">
+        <v>51.35</v>
+      </c>
+      <c r="L198" s="33">
         <f>F198*(K198-J198)</f>
         <v/>
       </c>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="E189" s="31" t="n">
-        <v>1771</v>
+        <v>1776</v>
       </c>
       <c r="F189" s="31" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G189" s="31" t="n">
         <v>23292</v>
@@ -8080,12 +8080,12 @@
         <v>21855</v>
       </c>
       <c r="J189" s="32" t="n">
-        <v>131.52</v>
+        <v>131.15</v>
       </c>
       <c r="K189" s="32" t="n">
-        <v>131.87</v>
-      </c>
-      <c r="L189" s="35">
+        <v>130.67</v>
+      </c>
+      <c r="L189" s="33">
         <f>F189*(K189-J189)</f>
         <v/>
       </c>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="E191" s="31" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F191" s="31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G191" s="31" t="n">
         <v>5757</v>
@@ -8150,12 +8150,12 @@
         <v>4744</v>
       </c>
       <c r="J191" s="32" t="n">
-        <v>767.5700000000001</v>
+        <v>738.05</v>
       </c>
       <c r="K191" s="32" t="n">
-        <v>779.15</v>
-      </c>
-      <c r="L191" s="35">
+        <v>723.5</v>
+      </c>
+      <c r="L191" s="33">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -8170,10 +8170,10 @@
         </is>
       </c>
       <c r="E192" s="31" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F192" s="31" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G192" s="31" t="n">
         <v>4738</v>
@@ -8185,12 +8185,12 @@
         <v>2441</v>
       </c>
       <c r="J192" s="32" t="n">
-        <v>358.9</v>
+        <v>361.64</v>
       </c>
       <c r="K192" s="32" t="n">
-        <v>358.89</v>
-      </c>
-      <c r="L192" s="33">
+        <v>364.59</v>
+      </c>
+      <c r="L192" s="35">
         <f>F192*(K192-J192)</f>
         <v/>
       </c>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="E193" s="31" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F193" s="31" t="n">
         <v>23</v>
@@ -8220,12 +8220,12 @@
         <v>3857</v>
       </c>
       <c r="J193" s="32" t="n">
-        <v>141.7</v>
+        <v>140.27</v>
       </c>
       <c r="K193" s="32" t="n">
         <v>140.39</v>
       </c>
-      <c r="L193" s="33">
+      <c r="L193" s="35">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -8306,29 +8306,29 @@
       <c r="C196" s="34" t="n"/>
       <c r="D196" s="30" t="inlineStr">
         <is>
-          <t>大綜(3147)</t>
+          <t>友達(2409)</t>
         </is>
       </c>
       <c r="E196" s="31" t="n">
-        <v>106</v>
+        <v>1046</v>
       </c>
       <c r="F196" s="31" t="n">
-        <v>0</v>
+        <v>943</v>
       </c>
       <c r="G196" s="31" t="n">
-        <v>3016</v>
+        <v>2835</v>
       </c>
       <c r="H196" s="31" t="n">
-        <v>0</v>
+        <v>2556</v>
       </c>
       <c r="I196" s="31" t="n">
-        <v>3016</v>
+        <v>279</v>
       </c>
       <c r="J196" s="32" t="n">
-        <v>284.5</v>
+        <v>27.1</v>
       </c>
       <c r="K196" s="32" t="n">
-        <v>0</v>
+        <v>27.1</v>
       </c>
       <c r="L196" s="35">
         <f>F196*(K196-J196)</f>
@@ -8376,31 +8376,31 @@
       <c r="C198" s="34" t="n"/>
       <c r="D198" s="30" t="inlineStr">
         <is>
-          <t>華邦電(2344)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E198" s="31" t="n">
-        <v>158</v>
+        <v>442</v>
       </c>
       <c r="F198" s="31" t="n">
-        <v>47</v>
+        <v>320</v>
       </c>
       <c r="G198" s="31" t="n">
-        <v>2560</v>
+        <v>2305</v>
       </c>
       <c r="H198" s="31" t="n">
-        <v>761</v>
+        <v>1643</v>
       </c>
       <c r="I198" s="31" t="n">
-        <v>1799</v>
+        <v>662</v>
       </c>
       <c r="J198" s="32" t="n">
-        <v>162</v>
+        <v>52.15</v>
       </c>
       <c r="K198" s="32" t="n">
-        <v>162</v>
-      </c>
-      <c r="L198" s="35">
+        <v>51.35</v>
+      </c>
+      <c r="L198" s="33">
         <f>F198*(K198-J198)</f>
         <v/>
       </c>
@@ -16507,29 +16507,29 @@
       <c r="C411" s="95" t="n"/>
       <c r="D411" s="91" t="inlineStr">
         <is>
-          <t>光聖(6442)</t>
+          <t>波若威(3163)</t>
         </is>
       </c>
       <c r="E411" s="92" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F411" s="92" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G411" s="92" t="n">
-        <v>5294</v>
+        <v>2487</v>
       </c>
       <c r="H411" s="92" t="n">
-        <v>2768</v>
+        <v>236</v>
       </c>
       <c r="I411" s="92" t="n">
-        <v>2526</v>
+        <v>2251</v>
       </c>
       <c r="J411" s="93" t="n">
-        <v>2036.27</v>
+        <v>1036.29</v>
       </c>
       <c r="K411" s="93" t="n">
-        <v>2129.23</v>
+        <v>1182</v>
       </c>
       <c r="L411" s="96">
         <f>F411*(K411-J411)</f>
@@ -16542,31 +16542,31 @@
       <c r="C412" s="95" t="n"/>
       <c r="D412" s="91" t="inlineStr">
         <is>
-          <t>上詮(3363)</t>
+          <t>聖暉*(5536)</t>
         </is>
       </c>
       <c r="E412" s="92" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="F412" s="92" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G412" s="92" t="n">
-        <v>4271</v>
+        <v>1607</v>
       </c>
       <c r="H412" s="92" t="n">
-        <v>2135</v>
+        <v>621</v>
       </c>
       <c r="I412" s="92" t="n">
-        <v>2136</v>
+        <v>986</v>
       </c>
       <c r="J412" s="93" t="n">
-        <v>908.72</v>
+        <v>1147.71</v>
       </c>
       <c r="K412" s="93" t="n">
-        <v>889.67</v>
-      </c>
-      <c r="L412" s="94">
+        <v>1241.8</v>
+      </c>
+      <c r="L412" s="96">
         <f>F412*(K412-J412)</f>
         <v/>
       </c>
@@ -16577,31 +16577,31 @@
       <c r="C413" s="95" t="n"/>
       <c r="D413" s="91" t="inlineStr">
         <is>
-          <t>台新新光金(2887)</t>
+          <t>佳必琪(6197)</t>
         </is>
       </c>
       <c r="E413" s="92" t="n">
-        <v>1179</v>
+        <v>36</v>
       </c>
       <c r="F413" s="92" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G413" s="92" t="n">
-        <v>3310</v>
+        <v>1184</v>
       </c>
       <c r="H413" s="92" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I413" s="92" t="n">
-        <v>3250</v>
+        <v>1120</v>
       </c>
       <c r="J413" s="93" t="n">
-        <v>28.08</v>
+        <v>329</v>
       </c>
       <c r="K413" s="93" t="n">
-        <v>28.38</v>
-      </c>
-      <c r="L413" s="96">
+        <v>322.5</v>
+      </c>
+      <c r="L413" s="94">
         <f>F413*(K413-J413)</f>
         <v/>
       </c>
@@ -16612,29 +16612,29 @@
       <c r="C414" s="95" t="n"/>
       <c r="D414" s="91" t="inlineStr">
         <is>
-          <t>聖暉*(5536)</t>
+          <t>遠雄(5522)</t>
         </is>
       </c>
       <c r="E414" s="92" t="n">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F414" s="92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G414" s="92" t="n">
-        <v>1607</v>
+        <v>869</v>
       </c>
       <c r="H414" s="92" t="n">
-        <v>621</v>
+        <v>0</v>
       </c>
       <c r="I414" s="92" t="n">
-        <v>986</v>
+        <v>869</v>
       </c>
       <c r="J414" s="93" t="n">
-        <v>1147.71</v>
+        <v>76.25</v>
       </c>
       <c r="K414" s="93" t="n">
-        <v>1241.8</v>
+        <v>0</v>
       </c>
       <c r="L414" s="96">
         <f>F414*(K414-J414)</f>
@@ -16647,31 +16647,31 @@
       <c r="C415" s="95" t="n"/>
       <c r="D415" s="91" t="inlineStr">
         <is>
-          <t>可成(2474)</t>
+          <t>兆利(3548)</t>
         </is>
       </c>
       <c r="E415" s="92" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F415" s="92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G415" s="92" t="n">
-        <v>1185</v>
+        <v>637</v>
       </c>
       <c r="H415" s="92" t="n">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="I415" s="92" t="n">
-        <v>1092</v>
+        <v>606</v>
       </c>
       <c r="J415" s="93" t="n">
-        <v>232.35</v>
+        <v>104.49</v>
       </c>
       <c r="K415" s="93" t="n">
-        <v>231.5</v>
-      </c>
-      <c r="L415" s="94">
+        <v>104.67</v>
+      </c>
+      <c r="L415" s="96">
         <f>F415*(K415-J415)</f>
         <v/>
       </c>
@@ -16682,29 +16682,29 @@
       <c r="C416" s="95" t="n"/>
       <c r="D416" s="91" t="inlineStr">
         <is>
-          <t>川湖(2059)</t>
+          <t>華盈(3520)</t>
         </is>
       </c>
       <c r="E416" s="92" t="n">
-        <v>2</v>
+        <v>163</v>
       </c>
       <c r="F416" s="92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G416" s="92" t="n">
-        <v>1139</v>
+        <v>278</v>
       </c>
       <c r="H416" s="92" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I416" s="92" t="n">
-        <v>1133</v>
+        <v>270</v>
       </c>
       <c r="J416" s="93" t="n">
-        <v>5695</v>
+        <v>17.05</v>
       </c>
       <c r="K416" s="93" t="n">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="L416" s="94">
         <f>F416*(K416-J416)</f>
@@ -16715,71 +16715,33 @@
       <c r="A417" s="95" t="n"/>
       <c r="B417" s="95" t="n"/>
       <c r="C417" s="95" t="n"/>
-      <c r="D417" s="91" t="inlineStr">
-        <is>
-          <t>長華*(8070)</t>
-        </is>
-      </c>
-      <c r="E417" s="92" t="n">
-        <v>179</v>
-      </c>
-      <c r="F417" s="92" t="n">
-        <v>5</v>
-      </c>
-      <c r="G417" s="92" t="n">
-        <v>1121</v>
-      </c>
-      <c r="H417" s="92" t="n">
-        <v>32</v>
-      </c>
-      <c r="I417" s="92" t="n">
-        <v>1089</v>
-      </c>
-      <c r="J417" s="93" t="n">
-        <v>62.61</v>
-      </c>
-      <c r="K417" s="93" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="L417" s="96">
-        <f>F417*(K417-J417)</f>
-        <v/>
-      </c>
+      <c r="D417" s="98" t="inlineStr">
+        <is>
+          <t>⚪ 今日漲停僅 8 檔</t>
+        </is>
+      </c>
+      <c r="E417" s="92" t="n"/>
+      <c r="F417" s="92" t="n"/>
+      <c r="G417" s="92" t="n"/>
+      <c r="H417" s="92" t="n"/>
+      <c r="I417" s="92" t="n"/>
+      <c r="J417" s="93" t="n"/>
+      <c r="K417" s="93" t="n"/>
+      <c r="L417" s="96" t="n"/>
     </row>
     <row r="418" ht="16.5" customHeight="1">
       <c r="A418" s="95" t="n"/>
       <c r="B418" s="95" t="n"/>
       <c r="C418" s="95" t="n"/>
-      <c r="D418" s="91" t="inlineStr">
-        <is>
-          <t>兆利(3548)</t>
-        </is>
-      </c>
-      <c r="E418" s="92" t="n">
-        <v>61</v>
-      </c>
-      <c r="F418" s="92" t="n">
-        <v>3</v>
-      </c>
-      <c r="G418" s="92" t="n">
-        <v>637</v>
-      </c>
-      <c r="H418" s="92" t="n">
-        <v>31</v>
-      </c>
-      <c r="I418" s="92" t="n">
-        <v>606</v>
-      </c>
-      <c r="J418" s="93" t="n">
-        <v>104.49</v>
-      </c>
-      <c r="K418" s="93" t="n">
-        <v>104.67</v>
-      </c>
-      <c r="L418" s="96">
-        <f>F418*(K418-J418)</f>
-        <v/>
-      </c>
+      <c r="D418" s="91" t="n"/>
+      <c r="E418" s="92" t="n"/>
+      <c r="F418" s="92" t="n"/>
+      <c r="G418" s="92" t="n"/>
+      <c r="H418" s="92" t="n"/>
+      <c r="I418" s="92" t="n"/>
+      <c r="J418" s="93" t="n"/>
+      <c r="K418" s="93" t="n"/>
+      <c r="L418" s="96" t="n"/>
     </row>
     <row r="419" ht="16.5" customHeight="1">
       <c r="A419" s="97" t="n"/>
@@ -16853,31 +16815,31 @@
       </c>
       <c r="D420" s="91" t="inlineStr">
         <is>
-          <t>訊芯-KY(6451)</t>
+          <t>科嶠(4542)</t>
         </is>
       </c>
       <c r="E420" s="92" t="n">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="F420" s="92" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G420" s="92" t="n">
-        <v>4736</v>
+        <v>3768</v>
       </c>
       <c r="H420" s="92" t="n">
-        <v>1103</v>
+        <v>179</v>
       </c>
       <c r="I420" s="92" t="n">
-        <v>3633</v>
+        <v>3589</v>
       </c>
       <c r="J420" s="93" t="n">
-        <v>686.38</v>
+        <v>275.05</v>
       </c>
       <c r="K420" s="93" t="n">
-        <v>689.62</v>
-      </c>
-      <c r="L420" s="96">
+        <v>255.86</v>
+      </c>
+      <c r="L420" s="94">
         <f>F420*(K420-J420)</f>
         <v/>
       </c>
@@ -16888,31 +16850,31 @@
       <c r="C421" s="95" t="n"/>
       <c r="D421" s="91" t="inlineStr">
         <is>
-          <t>川湖(2059)</t>
+          <t>金居(8358)</t>
         </is>
       </c>
       <c r="E421" s="92" t="n">
+        <v>22</v>
+      </c>
+      <c r="F421" s="92" t="n">
         <v>7</v>
       </c>
-      <c r="F421" s="92" t="n">
-        <v>1</v>
-      </c>
       <c r="G421" s="92" t="n">
-        <v>3773</v>
+        <v>1332</v>
       </c>
       <c r="H421" s="92" t="n">
-        <v>73</v>
+        <v>434</v>
       </c>
       <c r="I421" s="92" t="n">
-        <v>3700</v>
+        <v>898</v>
       </c>
       <c r="J421" s="93" t="n">
-        <v>5389.57</v>
+        <v>605.5</v>
       </c>
       <c r="K421" s="93" t="n">
-        <v>730</v>
-      </c>
-      <c r="L421" s="94">
+        <v>620</v>
+      </c>
+      <c r="L421" s="96">
         <f>F421*(K421-J421)</f>
         <v/>
       </c>
@@ -16923,31 +16885,31 @@
       <c r="C422" s="95" t="n"/>
       <c r="D422" s="91" t="inlineStr">
         <is>
-          <t>上詮(3363)</t>
+          <t>佳必琪(6197)</t>
         </is>
       </c>
       <c r="E422" s="92" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F422" s="92" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G422" s="92" t="n">
-        <v>2580</v>
+        <v>1298</v>
       </c>
       <c r="H422" s="92" t="n">
-        <v>892</v>
+        <v>198</v>
       </c>
       <c r="I422" s="92" t="n">
-        <v>1688</v>
+        <v>1100</v>
       </c>
       <c r="J422" s="93" t="n">
-        <v>921.3200000000001</v>
+        <v>324.6</v>
       </c>
       <c r="K422" s="93" t="n">
-        <v>892</v>
-      </c>
-      <c r="L422" s="94">
+        <v>329.83</v>
+      </c>
+      <c r="L422" s="96">
         <f>F422*(K422-J422)</f>
         <v/>
       </c>
@@ -16991,211 +16953,89 @@
       <c r="A424" s="95" t="n"/>
       <c r="B424" s="95" t="n"/>
       <c r="C424" s="95" t="n"/>
-      <c r="D424" s="91" t="inlineStr">
-        <is>
-          <t>友達(2409)</t>
-        </is>
-      </c>
-      <c r="E424" s="92" t="n">
-        <v>364</v>
-      </c>
-      <c r="F424" s="92" t="n">
-        <v>237</v>
-      </c>
-      <c r="G424" s="92" t="n">
-        <v>986</v>
-      </c>
-      <c r="H424" s="92" t="n">
-        <v>642</v>
-      </c>
-      <c r="I424" s="92" t="n">
-        <v>344</v>
-      </c>
-      <c r="J424" s="93" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="K424" s="93" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="L424" s="96">
-        <f>F424*(K424-J424)</f>
-        <v/>
-      </c>
+      <c r="D424" s="98" t="inlineStr">
+        <is>
+          <t>⚪ 今日漲停僅 4 檔</t>
+        </is>
+      </c>
+      <c r="E424" s="92" t="n"/>
+      <c r="F424" s="92" t="n"/>
+      <c r="G424" s="92" t="n"/>
+      <c r="H424" s="92" t="n"/>
+      <c r="I424" s="92" t="n"/>
+      <c r="J424" s="93" t="n"/>
+      <c r="K424" s="93" t="n"/>
+      <c r="L424" s="96" t="n"/>
     </row>
     <row r="425" ht="16.5" customHeight="1">
       <c r="A425" s="95" t="n"/>
       <c r="B425" s="95" t="n"/>
       <c r="C425" s="95" t="n"/>
-      <c r="D425" s="91" t="inlineStr">
-        <is>
-          <t>創新服務(7828)</t>
-        </is>
-      </c>
-      <c r="E425" s="92" t="n">
-        <v>6</v>
-      </c>
-      <c r="F425" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G425" s="92" t="n">
-        <v>962</v>
-      </c>
-      <c r="H425" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I425" s="92" t="n">
-        <v>962</v>
-      </c>
-      <c r="J425" s="93" t="n">
-        <v>1603.83</v>
-      </c>
-      <c r="K425" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L425" s="96">
-        <f>F425*(K425-J425)</f>
-        <v/>
-      </c>
+      <c r="D425" s="91" t="n"/>
+      <c r="E425" s="92" t="n"/>
+      <c r="F425" s="92" t="n"/>
+      <c r="G425" s="92" t="n"/>
+      <c r="H425" s="92" t="n"/>
+      <c r="I425" s="92" t="n"/>
+      <c r="J425" s="93" t="n"/>
+      <c r="K425" s="93" t="n"/>
+      <c r="L425" s="96" t="n"/>
     </row>
     <row r="426" ht="16.5" customHeight="1">
       <c r="A426" s="95" t="n"/>
       <c r="B426" s="95" t="n"/>
       <c r="C426" s="95" t="n"/>
-      <c r="D426" s="91" t="inlineStr">
-        <is>
-          <t>港建*(3093)</t>
-        </is>
-      </c>
-      <c r="E426" s="92" t="n">
-        <v>150</v>
-      </c>
-      <c r="F426" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G426" s="92" t="n">
-        <v>929</v>
-      </c>
-      <c r="H426" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I426" s="92" t="n">
-        <v>929</v>
-      </c>
-      <c r="J426" s="93" t="n">
-        <v>61.93</v>
-      </c>
-      <c r="K426" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L426" s="96">
-        <f>F426*(K426-J426)</f>
-        <v/>
-      </c>
+      <c r="D426" s="91" t="n"/>
+      <c r="E426" s="92" t="n"/>
+      <c r="F426" s="92" t="n"/>
+      <c r="G426" s="92" t="n"/>
+      <c r="H426" s="92" t="n"/>
+      <c r="I426" s="92" t="n"/>
+      <c r="J426" s="93" t="n"/>
+      <c r="K426" s="93" t="n"/>
+      <c r="L426" s="96" t="n"/>
     </row>
     <row r="427" ht="16.5" customHeight="1">
       <c r="A427" s="95" t="n"/>
       <c r="B427" s="95" t="n"/>
       <c r="C427" s="95" t="n"/>
-      <c r="D427" s="91" t="inlineStr">
-        <is>
-          <t>仁寶(2324)</t>
-        </is>
-      </c>
-      <c r="E427" s="92" t="n">
-        <v>184</v>
-      </c>
-      <c r="F427" s="92" t="n">
-        <v>68</v>
-      </c>
-      <c r="G427" s="92" t="n">
-        <v>762</v>
-      </c>
-      <c r="H427" s="92" t="n">
-        <v>282</v>
-      </c>
-      <c r="I427" s="92" t="n">
-        <v>480</v>
-      </c>
-      <c r="J427" s="93" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="K427" s="93" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="L427" s="96">
-        <f>F427*(K427-J427)</f>
-        <v/>
-      </c>
+      <c r="D427" s="91" t="n"/>
+      <c r="E427" s="92" t="n"/>
+      <c r="F427" s="92" t="n"/>
+      <c r="G427" s="92" t="n"/>
+      <c r="H427" s="92" t="n"/>
+      <c r="I427" s="92" t="n"/>
+      <c r="J427" s="93" t="n"/>
+      <c r="K427" s="93" t="n"/>
+      <c r="L427" s="96" t="n"/>
     </row>
     <row r="428" ht="16.5" customHeight="1">
       <c r="A428" s="95" t="n"/>
       <c r="B428" s="95" t="n"/>
       <c r="C428" s="95" t="n"/>
-      <c r="D428" s="91" t="inlineStr">
-        <is>
-          <t>大量(3167)</t>
-        </is>
-      </c>
-      <c r="E428" s="92" t="n">
-        <v>7</v>
-      </c>
-      <c r="F428" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G428" s="92" t="n">
-        <v>712</v>
-      </c>
-      <c r="H428" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I428" s="92" t="n">
-        <v>712</v>
-      </c>
-      <c r="J428" s="93" t="n">
-        <v>1017.14</v>
-      </c>
-      <c r="K428" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L428" s="96">
-        <f>F428*(K428-J428)</f>
-        <v/>
-      </c>
+      <c r="D428" s="91" t="n"/>
+      <c r="E428" s="92" t="n"/>
+      <c r="F428" s="92" t="n"/>
+      <c r="G428" s="92" t="n"/>
+      <c r="H428" s="92" t="n"/>
+      <c r="I428" s="92" t="n"/>
+      <c r="J428" s="93" t="n"/>
+      <c r="K428" s="93" t="n"/>
+      <c r="L428" s="96" t="n"/>
     </row>
     <row r="429" ht="16.5" customHeight="1">
       <c r="A429" s="95" t="n"/>
       <c r="B429" s="95" t="n"/>
       <c r="C429" s="95" t="n"/>
-      <c r="D429" s="91" t="inlineStr">
-        <is>
-          <t>新纖(1409)</t>
-        </is>
-      </c>
-      <c r="E429" s="92" t="n">
-        <v>106</v>
-      </c>
-      <c r="F429" s="92" t="n">
-        <v>51</v>
-      </c>
-      <c r="G429" s="92" t="n">
-        <v>277</v>
-      </c>
-      <c r="H429" s="92" t="n">
-        <v>133</v>
-      </c>
-      <c r="I429" s="92" t="n">
-        <v>144</v>
-      </c>
-      <c r="J429" s="93" t="n">
-        <v>26.15</v>
-      </c>
-      <c r="K429" s="93" t="n">
-        <v>26.16</v>
-      </c>
-      <c r="L429" s="96">
-        <f>F429*(K429-J429)</f>
-        <v/>
-      </c>
+      <c r="D429" s="91" t="n"/>
+      <c r="E429" s="92" t="n"/>
+      <c r="F429" s="92" t="n"/>
+      <c r="G429" s="92" t="n"/>
+      <c r="H429" s="92" t="n"/>
+      <c r="I429" s="92" t="n"/>
+      <c r="J429" s="93" t="n"/>
+      <c r="K429" s="93" t="n"/>
+      <c r="L429" s="96" t="n"/>
     </row>
     <row r="430" ht="16.5" customHeight="1">
       <c r="A430" s="99" t="inlineStr">

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨+26/5d-190)&quot;;-0&quot; 億 (昨+26/5d-190)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +70億 &quot;&quot;(昨12/5d12)&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.0%&quot; 市-722億 &quot;&quot;(昨20/5d18)&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0%&quot; 市-720億 &quot;&quot;(昨20/5d18)&quot;"/>
     <numFmt numFmtId="168" formatCode="&quot;📅 明日預測 ↕ 中性 &quot;0.0&quot;% 信心 — P/C Ratio 主推 — 3 檔焦點&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00%;[Color10]-0.00%"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
@@ -1818,7 +1818,7 @@
         <v>13</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="H19" s="18" t="n">
-        <v>13571</v>
+        <v>14365</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>10</v>
       </c>
       <c r="N19" s="18" t="n">
-        <v>52338</v>
+        <v>53132</v>
       </c>
     </row>
     <row r="20">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="J22" s="19" t="n">
-        <v>6490</v>
+        <v>7158</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>9</v>
       </c>
       <c r="N22" s="18" t="n">
-        <v>30505</v>
+        <v>31173</v>
       </c>
     </row>
     <row r="23">
@@ -2022,7 +2022,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>張濬安</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="L23" s="19" t="n">
-        <v>1726</v>
+        <v>2461</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>9</v>
       </c>
       <c r="N23" s="18" t="n">
-        <v>21324</v>
+        <v>22879</v>
       </c>
     </row>
     <row r="24">
@@ -2112,27 +2112,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>📌 華碩</t>
+          <t>📌 力積電</t>
         </is>
       </c>
       <c r="E25" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>竹科主力分點</t>
+          <t>張濬安</t>
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>6021</v>
+        <v>4403</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="J25" s="19" t="n">
-        <v>2551</v>
+        <v>2523</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="L25" s="19" t="n">
-        <v>2204</v>
+        <v>2250</v>
       </c>
       <c r="M25" s="20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>16403</v>
+        <v>17167</v>
       </c>
     </row>
     <row r="26">
@@ -2163,27 +2163,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>📌 力積電</t>
+          <t>📌 華碩</t>
         </is>
       </c>
       <c r="E26" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>張濬安</t>
+          <t>竹科主力分點</t>
         </is>
       </c>
       <c r="H26" s="18" t="n">
-        <v>4403</v>
+        <v>6021</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="J26" s="19" t="n">
-        <v>2523</v>
+        <v>2551</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="L26" s="19" t="n">
-        <v>2250</v>
+        <v>2204</v>
       </c>
       <c r="M26" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>16268</v>
+        <v>16403</v>
       </c>
     </row>
     <row r="27">
@@ -2230,19 +2230,19 @@
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>1310</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>強森</t>
         </is>
       </c>
-      <c r="H27" s="18" t="n">
+      <c r="J27" s="19" t="n">
         <v>1004</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>陳族元</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="n">
-        <v>858</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>10</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>5062</v>
+        <v>5513</v>
       </c>
     </row>
     <row r="28">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="E28" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         <v>302</v>
       </c>
       <c r="M28" s="20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N28" s="18" t="n">
-        <v>3056</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="G31" s="196" t="n">
-        <v>-69.29268999999999</v>
+        <v>-67.94410000000001</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="G32" s="198" t="n">
-        <v>0.2066133272140842</v>
+        <v>0.206919138606294</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -2429,11 +2429,11 @@
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>2833870</v>
+        <v>2850916</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 11 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 12 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>11 檔</t>
+          <t>12 檔</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="C72" s="33" t="n">
-        <v>2776908</v>
+        <v>2794292</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>198077</v>
       </c>
       <c r="J72" s="202" t="n">
-        <v>0.2875925512129766</v>
+        <v>0.285803447077483</v>
       </c>
     </row>
     <row r="73">
@@ -3650,7 +3650,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="B86" s="59" t="inlineStr">
         <is>
-          <t>▍ G. 注意股 (資料日 20260630)</t>
+          <t>▍ G. 注意股 (資料日 20260701)</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>1</v>
       </c>
       <c r="E89" s="41" t="n">
-        <v>27.35</v>
+        <v>30.05</v>
       </c>
       <c r="F89" s="41" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>8.960000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3753,276 +3753,276 @@
     <row r="91">
       <c r="B91" s="41" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="C91" s="41" t="inlineStr">
         <is>
-          <t>中纖</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="D91" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E91" s="41" t="n">
-        <v>13.45</v>
+        <v>8.27</v>
       </c>
       <c r="F91" s="41" t="inlineStr">
         <is>
-          <t>56.04</t>
+          <t>-----</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>宇隆</t>
+          <t>榮星</t>
         </is>
       </c>
       <c r="D92" t="n">
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>212</v>
+        <v>22.85</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>25.97</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="41" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="C93" s="41" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>東聯</t>
         </is>
       </c>
       <c r="D93" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E93" s="41" t="n">
-        <v>164.5</v>
+        <v>18.4</v>
       </c>
       <c r="F93" s="41" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>-----</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>凱美</t>
+          <t>中纖</t>
         </is>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>211.5</v>
+        <v>12.4</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>51.67</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="41" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="C95" s="41" t="inlineStr">
         <is>
-          <t>錩新</t>
+          <t>宏旭-KY</t>
         </is>
       </c>
       <c r="D95" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E95" s="41" t="n">
-        <v>37.5</v>
+        <v>62</v>
       </c>
       <c r="F95" s="41" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>24.90</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>453.5</v>
+        <v>169</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>52.43</t>
+          <t>42.46</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="41" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C97" s="41" t="inlineStr">
         <is>
-          <t>百容</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D97" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E97" s="41" t="n">
-        <v>57.1</v>
+        <v>2660</v>
       </c>
       <c r="F97" s="41" t="inlineStr">
         <is>
-          <t>62.07</t>
+          <t>50.30</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>高林</t>
+          <t>矽統</t>
         </is>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>14.55</v>
+        <v>73.5</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>32.33</t>
+          <t>43.24</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="41" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="C99" s="41" t="inlineStr">
         <is>
-          <t>嘉晶</t>
+          <t>凱美</t>
         </is>
       </c>
       <c r="D99" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E99" s="41" t="n">
-        <v>133.5</v>
+        <v>232.5</v>
       </c>
       <c r="F99" s="41" t="inlineStr">
         <is>
-          <t>325.61</t>
+          <t>70.67</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>國碩</t>
         </is>
       </c>
       <c r="D100" t="n">
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>328.5</v>
+        <v>40.2</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>-----</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="41" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="C101" s="41" t="inlineStr">
         <is>
-          <t>大量</t>
+          <t>希華</t>
         </is>
       </c>
       <c r="D101" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E101" s="41" t="n">
-        <v>842</v>
+        <v>79.8</v>
       </c>
       <c r="F101" s="41" t="inlineStr">
         <is>
-          <t>82.07</t>
+          <t>107.84</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="D102" t="n">
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>891</v>
+        <v>333</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>250.99</t>
+          <t>26.08</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
     <row r="122" ht="22" customHeight="1">
       <c r="B122" s="65" t="inlineStr">
         <is>
-          <t>▍ I. 未來 30 天除權息 (有效 260 檔, 已剔除過期)</t>
+          <t>▍ I. 未來 30 天除權息 (有效 306 檔, 已剔除過期)</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="C29" s="70" t="inlineStr">
         <is>
-          <t>-69 億 淨買</t>
+          <t>-68 億 淨買</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="B3" s="98" t="inlineStr">
         <is>
-          <t>大牌分析師 近 50/50 交易日出手 2419 次 (517 檔), 風格分布: 隔日沖近似 38% / 當沖 13% / 留倉 48%, 漲停命中 5% (其中 🔒鎖漲停 4%), 前 5 大集中 24%, 長線部位 58% (32 檔), ⚠️ 處置股部位 14% (40 檔), 📦 連續囤貨 28 檔 (最長 13 天 009816, 皆已停止)。 主軸: 高頻交易/持續進場/📦 連續囤貨。</t>
+          <t>大牌分析師 近 50/50 交易日出手 2419 次 (517 檔), 風格分布: 隔日沖近似 38% / 當沖 13% / 留倉 48%, 漲停命中 5% (其中 🔒鎖漲停 4%), 前 5 大集中 24%, 長線部位 58% (32 檔), ⚠️ 處置股部位 14% (48 檔), 📦 連續囤貨 28 檔 (最長 13 天 009816, 皆已停止)。 主軸: 高頻交易/持續進場/📦 連續囤貨。</t>
         </is>
       </c>
     </row>
@@ -13657,10 +13657,10 @@
         </is>
       </c>
       <c r="E189" s="129" t="n">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F189" s="129" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G189" s="129" t="n">
         <v>11302</v>
@@ -13672,10 +13672,10 @@
         <v>9692</v>
       </c>
       <c r="J189" s="130" t="n">
-        <v>434.69</v>
+        <v>421.71</v>
       </c>
       <c r="K189" s="130" t="n">
-        <v>435.05</v>
+        <v>423.61</v>
       </c>
       <c r="L189" s="220">
         <f>F189*(K189-J189)</f>
@@ -13688,31 +13688,31 @@
       <c r="C190" s="131" t="n"/>
       <c r="D190" s="128" t="inlineStr">
         <is>
-          <t>智邦(2345)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="E190" s="129" t="n">
-        <v>20</v>
+        <v>498</v>
       </c>
       <c r="F190" s="129" t="n">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="G190" s="129" t="n">
-        <v>5230</v>
+        <v>8416</v>
       </c>
       <c r="H190" s="129" t="n">
-        <v>3343</v>
+        <v>2569</v>
       </c>
       <c r="I190" s="129" t="n">
-        <v>1887</v>
+        <v>5847</v>
       </c>
       <c r="J190" s="130" t="n">
-        <v>2615.15</v>
+        <v>169</v>
       </c>
       <c r="K190" s="130" t="n">
-        <v>2571.38</v>
-      </c>
-      <c r="L190" s="219">
+        <v>169</v>
+      </c>
+      <c r="L190" s="220">
         <f>F190*(K190-J190)</f>
         <v/>
       </c>
@@ -13723,29 +13723,29 @@
       <c r="C191" s="131" t="n"/>
       <c r="D191" s="128" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>智邦(2345)</t>
         </is>
       </c>
       <c r="E191" s="129" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F191" s="129" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G191" s="129" t="n">
-        <v>4985</v>
+        <v>5230</v>
       </c>
       <c r="H191" s="129" t="n">
-        <v>4384</v>
+        <v>3343</v>
       </c>
       <c r="I191" s="129" t="n">
-        <v>601</v>
+        <v>1887</v>
       </c>
       <c r="J191" s="130" t="n">
-        <v>4531.73</v>
+        <v>2615.15</v>
       </c>
       <c r="K191" s="130" t="n">
-        <v>4384.4</v>
+        <v>2571.38</v>
       </c>
       <c r="L191" s="219">
         <f>F191*(K191-J191)</f>
@@ -13758,29 +13758,29 @@
       <c r="C192" s="131" t="n"/>
       <c r="D192" s="128" t="inlineStr">
         <is>
-          <t>國巨*(2327)</t>
+          <t>聯發科(2454)</t>
         </is>
       </c>
       <c r="E192" s="129" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F192" s="129" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G192" s="129" t="n">
-        <v>4778</v>
+        <v>4985</v>
       </c>
       <c r="H192" s="129" t="n">
-        <v>2361</v>
+        <v>4384</v>
       </c>
       <c r="I192" s="129" t="n">
-        <v>2417</v>
+        <v>601</v>
       </c>
       <c r="J192" s="130" t="n">
-        <v>1137.57</v>
+        <v>4531.73</v>
       </c>
       <c r="K192" s="130" t="n">
-        <v>1124.14</v>
+        <v>4384.4</v>
       </c>
       <c r="L192" s="219">
         <f>F192*(K192-J192)</f>
@@ -13793,29 +13793,29 @@
       <c r="C193" s="131" t="n"/>
       <c r="D193" s="128" t="inlineStr">
         <is>
-          <t>景碩(3189)</t>
+          <t>國巨*(2327)</t>
         </is>
       </c>
       <c r="E193" s="129" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F193" s="129" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G193" s="129" t="n">
-        <v>4152</v>
+        <v>4778</v>
       </c>
       <c r="H193" s="129" t="n">
-        <v>2110</v>
+        <v>2361</v>
       </c>
       <c r="I193" s="129" t="n">
-        <v>2042</v>
+        <v>2417</v>
       </c>
       <c r="J193" s="130" t="n">
-        <v>883.49</v>
+        <v>1137.57</v>
       </c>
       <c r="K193" s="130" t="n">
-        <v>879.12</v>
+        <v>1124.14</v>
       </c>
       <c r="L193" s="219">
         <f>F193*(K193-J193)</f>
@@ -13828,31 +13828,31 @@
       <c r="C194" s="131" t="n"/>
       <c r="D194" s="128" t="inlineStr">
         <is>
-          <t>群創(3481)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E194" s="129" t="n">
-        <v>538</v>
+        <v>47</v>
       </c>
       <c r="F194" s="129" t="n">
-        <v>461</v>
+        <v>24</v>
       </c>
       <c r="G194" s="129" t="n">
-        <v>3761</v>
+        <v>4152</v>
       </c>
       <c r="H194" s="129" t="n">
-        <v>3227</v>
+        <v>2110</v>
       </c>
       <c r="I194" s="129" t="n">
-        <v>534</v>
+        <v>2042</v>
       </c>
       <c r="J194" s="130" t="n">
-        <v>69.90000000000001</v>
+        <v>883.49</v>
       </c>
       <c r="K194" s="130" t="n">
-        <v>70</v>
-      </c>
-      <c r="L194" s="220">
+        <v>879.12</v>
+      </c>
+      <c r="L194" s="219">
         <f>F194*(K194-J194)</f>
         <v/>
       </c>
@@ -13863,29 +13863,29 @@
       <c r="C195" s="131" t="n"/>
       <c r="D195" s="128" t="inlineStr">
         <is>
-          <t>創見(2451)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E195" s="129" t="n">
-        <v>146</v>
+        <v>486</v>
       </c>
       <c r="F195" s="129" t="n">
-        <v>8</v>
+        <v>259</v>
       </c>
       <c r="G195" s="129" t="n">
-        <v>3703</v>
+        <v>3761</v>
       </c>
       <c r="H195" s="129" t="n">
-        <v>205</v>
+        <v>3227</v>
       </c>
       <c r="I195" s="129" t="n">
-        <v>3498</v>
+        <v>534</v>
       </c>
       <c r="J195" s="130" t="n">
-        <v>253.63</v>
+        <v>77.38</v>
       </c>
       <c r="K195" s="130" t="n">
-        <v>256.5</v>
+        <v>124.59</v>
       </c>
       <c r="L195" s="220">
         <f>F195*(K195-J195)</f>
@@ -13898,31 +13898,31 @@
       <c r="C196" s="131" t="n"/>
       <c r="D196" s="128" t="inlineStr">
         <is>
-          <t>臻鼎-KY(4958)</t>
+          <t>創見(2451)</t>
         </is>
       </c>
       <c r="E196" s="129" t="n">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="F196" s="129" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G196" s="129" t="n">
-        <v>3188</v>
+        <v>3703</v>
       </c>
       <c r="H196" s="129" t="n">
-        <v>1481</v>
+        <v>205</v>
       </c>
       <c r="I196" s="129" t="n">
-        <v>1707</v>
+        <v>3498</v>
       </c>
       <c r="J196" s="130" t="n">
-        <v>601.51</v>
+        <v>250.2</v>
       </c>
       <c r="K196" s="130" t="n">
-        <v>592.28</v>
-      </c>
-      <c r="L196" s="219">
+        <v>256.5</v>
+      </c>
+      <c r="L196" s="220">
         <f>F196*(K196-J196)</f>
         <v/>
       </c>
@@ -13933,31 +13933,31 @@
       <c r="C197" s="131" t="n"/>
       <c r="D197" s="128" t="inlineStr">
         <is>
-          <t>友達(2409)</t>
+          <t>臻鼎-KY(4958)</t>
         </is>
       </c>
       <c r="E197" s="129" t="n">
-        <v>963</v>
+        <v>55</v>
       </c>
       <c r="F197" s="129" t="n">
-        <v>910</v>
+        <v>29</v>
       </c>
       <c r="G197" s="129" t="n">
-        <v>2952</v>
+        <v>3188</v>
       </c>
       <c r="H197" s="129" t="n">
-        <v>2789</v>
+        <v>1481</v>
       </c>
       <c r="I197" s="129" t="n">
-        <v>163</v>
+        <v>1707</v>
       </c>
       <c r="J197" s="130" t="n">
-        <v>30.65</v>
+        <v>579.64</v>
       </c>
       <c r="K197" s="130" t="n">
-        <v>30.65</v>
-      </c>
-      <c r="L197" s="220">
+        <v>510.59</v>
+      </c>
+      <c r="L197" s="219">
         <f>F197*(K197-J197)</f>
         <v/>
       </c>
@@ -13972,10 +13972,10 @@
         </is>
       </c>
       <c r="E198" s="129" t="n">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F198" s="129" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="G198" s="129" t="n">
         <v>2888</v>
@@ -13987,12 +13987,12 @@
         <v>1654</v>
       </c>
       <c r="J198" s="130" t="n">
-        <v>193.83</v>
+        <v>209.28</v>
       </c>
       <c r="K198" s="130" t="n">
-        <v>195.92</v>
-      </c>
-      <c r="L198" s="220">
+        <v>121.01</v>
+      </c>
+      <c r="L198" s="219">
         <f>F198*(K198-J198)</f>
         <v/>
       </c>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -21,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨+26/5d-190)&quot;;-0&quot; 億 (昨+26/5d-190)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +70億 &quot;&quot;(昨12/5d12)&quot;"/>
@@ -35,6 +35,7 @@
     <numFmt numFmtId="174" formatCode="0.0&quot;%&quot;"/>
     <numFmt numFmtId="175" formatCode="0&quot;%&quot;"/>
     <numFmt numFmtId="176" formatCode="#,##0.00;-#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="0&quot; 檔 +69億 &quot;&quot;(昨12/5d12)&quot;"/>
   </numFmts>
   <fonts count="45">
     <font>
@@ -541,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1054,6 +1055,9 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1139,12 +1143,12 @@
     <comment ref="D16" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「陳族元」獨佔比 73.5%
-  • 領頭金額 125,231 萬
-  • 合計淨買 170,333 萬
+領頭大戶「陳族元」獨佔比 73.1%
+  • 領頭金額 122,814 萬
+  • 合計淨買 167,916 萬
   • 大戶數 11 位 (名義共識)
 判讀: 名義 11 位大戶共識,
-實質 1 人下注佔 74%,
+實質 1 人下注佔 73%,
 剩餘 10 位為陪襯小單,
 真共識訊號被稀釋.</t>
       </text>
@@ -1152,9 +1156,9 @@
     <comment ref="D18" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「陳族元」獨佔比 85.3%
-  • 領頭金額 113,167 萬
-  • 合計淨買 132,691 萬
+領頭大戶「陳族元」獨佔比 85.1%
+  • 領頭金額 111,125 萬
+  • 合計淨買 130,648 萬
   • 大戶數 11 位 (名義共識)
 判讀: 名義 11 位大戶共識,
 實質 1 人下注佔 85%,
@@ -1513,7 +1517,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 📌 一般共識 2327 / 4958 / 3189 (Q5 中性, 中性信號)  |  避開 — 除權息 27 檔: 1101, 1101B, 1470 ... | 明日恐處置 1 檔: 2303  |  訊號: 中性但 hot 多 (24 個信號 — 留意)</t>
+          <t>💡 📌 一般共識 2327 / 4958 / 3189 (Q5 中性, 中性信號)  |  避開 — 除權息 27 檔: 1101, 1101B, 1470 ... | 明日恐處置 5 檔: 3189/6213/8021...  |  訊號: 中性但 hot 多 (24 個信號 — 留意)</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1669,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
@@ -1673,7 +1677,7 @@
         </is>
       </c>
       <c r="H16" s="18" t="n">
-        <v>125231</v>
+        <v>122814</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1695,7 +1699,7 @@
         <v>8</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>170333</v>
+        <v>167916</v>
       </c>
     </row>
     <row r="17">
@@ -1732,7 +1736,7 @@
         </is>
       </c>
       <c r="J17" s="19" t="n">
-        <v>27838</v>
+        <v>27775</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1746,7 +1750,7 @@
         <v>8</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>140869</v>
+        <v>140806</v>
       </c>
     </row>
     <row r="18">
@@ -1767,7 +1771,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
@@ -1775,7 +1779,7 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>113168</v>
+        <v>111125</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1797,7 +1801,7 @@
         <v>8</v>
       </c>
       <c r="N18" s="18" t="n">
-        <v>132691</v>
+        <v>130649</v>
       </c>
     </row>
     <row r="19">
@@ -1826,7 +1830,7 @@
         </is>
       </c>
       <c r="H19" s="18" t="n">
-        <v>14365</v>
+        <v>14362</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1848,7 +1852,7 @@
         <v>10</v>
       </c>
       <c r="N19" s="18" t="n">
-        <v>53132</v>
+        <v>53128</v>
       </c>
     </row>
     <row r="20">
@@ -1877,7 +1881,7 @@
         </is>
       </c>
       <c r="H20" s="18" t="n">
-        <v>10887</v>
+        <v>9953</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1899,7 +1903,7 @@
         <v>10</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>49708</v>
+        <v>48774</v>
       </c>
     </row>
     <row r="21">
@@ -1908,49 +1912,49 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>📌 南亞科</t>
+          <t>📌 友達</t>
         </is>
       </c>
       <c r="E21" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
+          <t>張濬安</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>9401</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>陳族元</t>
         </is>
       </c>
-      <c r="H21" s="18" t="n">
-        <v>10443</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>林滄海</t>
-        </is>
-      </c>
       <c r="J21" s="19" t="n">
-        <v>8128</v>
+        <v>7221</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>布哥</t>
+          <t>竹科主力分點</t>
         </is>
       </c>
       <c r="L21" s="19" t="n">
-        <v>5062</v>
+        <v>3786</v>
       </c>
       <c r="M21" s="20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N21" s="18" t="n">
-        <v>39670</v>
+        <v>31236</v>
       </c>
     </row>
     <row r="22">
@@ -1959,49 +1963,49 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>📌 友達</t>
+          <t>📌 南亞科</t>
         </is>
       </c>
       <c r="E22" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>張濬安</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="H22" s="18" t="n">
-        <v>9401</v>
+        <v>8128</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>布哥</t>
         </is>
       </c>
       <c r="J22" s="19" t="n">
-        <v>7158</v>
+        <v>5062</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>竹科主力分點</t>
+          <t>強森</t>
         </is>
       </c>
       <c r="L22" s="19" t="n">
-        <v>3786</v>
+        <v>3597</v>
       </c>
       <c r="M22" s="20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N22" s="18" t="n">
-        <v>31173</v>
+        <v>30627</v>
       </c>
     </row>
     <row r="23">
@@ -2046,13 +2050,13 @@
         </is>
       </c>
       <c r="L23" s="19" t="n">
-        <v>2461</v>
+        <v>2478</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>9</v>
       </c>
       <c r="N23" s="18" t="n">
-        <v>22879</v>
+        <v>22896</v>
       </c>
     </row>
     <row r="24">
@@ -2061,19 +2065,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>📌 群聯</t>
+          <t>📌 力積電</t>
         </is>
       </c>
       <c r="E24" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
@@ -2081,29 +2085,29 @@
         </is>
       </c>
       <c r="H24" s="18" t="n">
-        <v>3930</v>
+        <v>4403</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>竹科主力分點</t>
+          <t>強森</t>
         </is>
       </c>
       <c r="J24" s="19" t="n">
-        <v>2952</v>
+        <v>2523</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>布哥</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="L24" s="19" t="n">
-        <v>2889</v>
+        <v>2250</v>
       </c>
       <c r="M24" s="20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>17237</v>
+        <v>17231</v>
       </c>
     </row>
     <row r="25">
@@ -2112,27 +2116,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>📌 力積電</t>
+          <t>📌 華碩</t>
         </is>
       </c>
       <c r="E25" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>張濬安</t>
+          <t>竹科主力分點</t>
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>4403</v>
+        <v>6021</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2140,7 +2144,7 @@
         </is>
       </c>
       <c r="J25" s="19" t="n">
-        <v>2523</v>
+        <v>2551</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2148,13 +2152,13 @@
         </is>
       </c>
       <c r="L25" s="19" t="n">
-        <v>2250</v>
+        <v>2204</v>
       </c>
       <c r="M25" s="20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>17167</v>
+        <v>17026</v>
       </c>
     </row>
     <row r="26">
@@ -2163,49 +2167,49 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>📌 華碩</t>
+          <t>📌 群聯</t>
         </is>
       </c>
       <c r="E26" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F26" s="16" t="n">
         <v>15</v>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
+          <t>張濬安</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="n">
+        <v>3930</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>竹科主力分點</t>
         </is>
       </c>
-      <c r="H26" s="18" t="n">
-        <v>6021</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>強森</t>
-        </is>
-      </c>
       <c r="J26" s="19" t="n">
-        <v>2551</v>
+        <v>2952</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>布哥</t>
         </is>
       </c>
       <c r="L26" s="19" t="n">
-        <v>2204</v>
+        <v>2889</v>
       </c>
       <c r="M26" s="20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>16403</v>
+        <v>16578</v>
       </c>
     </row>
     <row r="27">
@@ -2234,7 +2238,7 @@
         </is>
       </c>
       <c r="H27" s="18" t="n">
-        <v>1310</v>
+        <v>1334</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2256,7 +2260,7 @@
         <v>10</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>5513</v>
+        <v>5538</v>
       </c>
     </row>
     <row r="28">
@@ -2274,10 +2278,10 @@
         </is>
       </c>
       <c r="E28" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
@@ -2304,10 +2308,10 @@
         <v>302</v>
       </c>
       <c r="M28" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N28" s="18" t="n">
-        <v>3124</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
@@ -2332,7 +2336,7 @@
         </is>
       </c>
       <c r="G31" s="196" t="n">
-        <v>-67.94410000000001</v>
+        <v>-70.77464999999999</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
@@ -2341,7 +2345,7 @@
           <t>Q3 強共識股</t>
         </is>
       </c>
-      <c r="C32" s="197" t="n">
+      <c r="C32" s="222" t="n">
         <v>13</v>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -2350,7 +2354,7 @@
         </is>
       </c>
       <c r="G32" s="198" t="n">
-        <v>0.206919138606294</v>
+        <v>0.2062267155802317</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -2429,11 +2433,11 @@
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>2850916</v>
+        <v>2826495</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2465,7 +2469,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2497,7 +2501,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2621,7 +2625,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>民哥</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2631,12 +2635,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 12 檔新標的 (過去從沒買過)</t>
+          <t>民哥 今日買進 10 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>12 檔</t>
+          <t>10 檔</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2652,7 @@
       </c>
       <c r="C48" s="41" t="inlineStr">
         <is>
-          <t>民哥</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D48" s="41" t="inlineStr">
@@ -2658,7 +2662,7 @@
       </c>
       <c r="E48" s="41" t="inlineStr">
         <is>
-          <t>民哥 今日買進 10 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 10 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F48" s="41" t="inlineStr">
@@ -2943,11 +2947,11 @@
         <v>40</v>
       </c>
       <c r="E61" t="n">
-        <v>4199746</v>
+        <v>4194968</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>陳族元 連續 40 天加碼 2327 (累計 4,199,746 萬)</t>
+          <t>陳族元 連續 40 天加碼 2327 (累計 4,194,968 萬)</t>
         </is>
       </c>
     </row>
@@ -3012,11 +3016,11 @@
         <v>24</v>
       </c>
       <c r="E64" s="41" t="n">
-        <v>2459724</v>
+        <v>2454739</v>
       </c>
       <c r="F64" s="41" t="inlineStr">
         <is>
-          <t>陳族元 連續 24 天加碼 2454 (累計 2,459,724 萬)</t>
+          <t>陳族元 連續 24 天加碼 2454 (累計 2,454,739 萬)</t>
         </is>
       </c>
     </row>
@@ -3058,11 +3062,11 @@
         <v>22</v>
       </c>
       <c r="E66" s="41" t="n">
-        <v>1077017</v>
+        <v>1071058</v>
       </c>
       <c r="F66" s="41" t="inlineStr">
         <is>
-          <t>陳族元 連續 22 天加碼 2408 (累計 1,077,017 萬)</t>
+          <t>陳族元 連續 22 天加碼 2408 (累計 1,071,058 萬)</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3177,7 @@
         </is>
       </c>
       <c r="C72" s="33" t="n">
-        <v>2794292</v>
+        <v>2769537</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3200,7 +3204,7 @@
         <v>198077</v>
       </c>
       <c r="J72" s="202" t="n">
-        <v>0.285803447077483</v>
+        <v>0.2883579763176334</v>
       </c>
     </row>
     <row r="73">
@@ -5080,7 +5084,7 @@
     <row r="26">
       <c r="C26" s="69" t="inlineStr">
         <is>
-          <t>明日恐處置 1 檔 (2303)</t>
+          <t>明日恐處置 5 檔 (3189 / 6213 / 8021 ...)</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5098,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="C29" s="70" t="inlineStr">
         <is>
-          <t>-68 億 淨買</t>
+          <t>-71 億 淨買</t>
         </is>
       </c>
     </row>
@@ -13653,29 +13657,29 @@
       </c>
       <c r="D189" s="128" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="E189" s="129" t="n">
-        <v>268</v>
+        <v>504</v>
       </c>
       <c r="F189" s="129" t="n">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="G189" s="129" t="n">
-        <v>11302</v>
+        <v>8511</v>
       </c>
       <c r="H189" s="129" t="n">
-        <v>1610</v>
+        <v>2574</v>
       </c>
       <c r="I189" s="129" t="n">
-        <v>9692</v>
+        <v>5937</v>
       </c>
       <c r="J189" s="130" t="n">
-        <v>421.71</v>
+        <v>168.87</v>
       </c>
       <c r="K189" s="130" t="n">
-        <v>423.61</v>
+        <v>169.34</v>
       </c>
       <c r="L189" s="220">
         <f>F189*(K189-J189)</f>
@@ -13688,29 +13692,29 @@
       <c r="C190" s="131" t="n"/>
       <c r="D190" s="128" t="inlineStr">
         <is>
-          <t>聯電(2303)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E190" s="129" t="n">
-        <v>498</v>
+        <v>260</v>
       </c>
       <c r="F190" s="129" t="n">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="G190" s="129" t="n">
-        <v>8416</v>
+        <v>5343</v>
       </c>
       <c r="H190" s="129" t="n">
-        <v>2569</v>
+        <v>4694</v>
       </c>
       <c r="I190" s="129" t="n">
-        <v>5847</v>
+        <v>649</v>
       </c>
       <c r="J190" s="130" t="n">
-        <v>169</v>
+        <v>205.51</v>
       </c>
       <c r="K190" s="130" t="n">
-        <v>169</v>
+        <v>1268.51</v>
       </c>
       <c r="L190" s="220">
         <f>F190*(K190-J190)</f>
@@ -13723,31 +13727,31 @@
       <c r="C191" s="131" t="n"/>
       <c r="D191" s="128" t="inlineStr">
         <is>
-          <t>智邦(2345)</t>
+          <t>創見(2451)</t>
         </is>
       </c>
       <c r="E191" s="129" t="n">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="F191" s="129" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G191" s="129" t="n">
-        <v>5230</v>
+        <v>3657</v>
       </c>
       <c r="H191" s="129" t="n">
-        <v>3343</v>
+        <v>200</v>
       </c>
       <c r="I191" s="129" t="n">
-        <v>1887</v>
+        <v>3457</v>
       </c>
       <c r="J191" s="130" t="n">
-        <v>2615.15</v>
+        <v>250.5</v>
       </c>
       <c r="K191" s="130" t="n">
-        <v>2571.38</v>
-      </c>
-      <c r="L191" s="219">
+        <v>250.5</v>
+      </c>
+      <c r="L191" s="220">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -13758,31 +13762,31 @@
       <c r="C192" s="131" t="n"/>
       <c r="D192" s="128" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>大立光(3008)</t>
         </is>
       </c>
       <c r="E192" s="129" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F192" s="129" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G192" s="129" t="n">
-        <v>4985</v>
+        <v>3561</v>
       </c>
       <c r="H192" s="129" t="n">
-        <v>4384</v>
+        <v>1864</v>
       </c>
       <c r="I192" s="129" t="n">
-        <v>601</v>
+        <v>1697</v>
       </c>
       <c r="J192" s="130" t="n">
-        <v>4531.73</v>
+        <v>4451.25</v>
       </c>
       <c r="K192" s="130" t="n">
-        <v>4384.4</v>
-      </c>
-      <c r="L192" s="219">
+        <v>4659</v>
+      </c>
+      <c r="L192" s="220">
         <f>F192*(K192-J192)</f>
         <v/>
       </c>
@@ -13793,29 +13797,29 @@
       <c r="C193" s="131" t="n"/>
       <c r="D193" s="128" t="inlineStr">
         <is>
-          <t>國巨*(2327)</t>
+          <t>欣興(3037)</t>
         </is>
       </c>
       <c r="E193" s="129" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F193" s="129" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G193" s="129" t="n">
-        <v>4778</v>
+        <v>3462</v>
       </c>
       <c r="H193" s="129" t="n">
-        <v>2361</v>
+        <v>1447</v>
       </c>
       <c r="I193" s="129" t="n">
-        <v>2417</v>
+        <v>2015</v>
       </c>
       <c r="J193" s="130" t="n">
-        <v>1137.57</v>
+        <v>1049.24</v>
       </c>
       <c r="K193" s="130" t="n">
-        <v>1124.14</v>
+        <v>1033.79</v>
       </c>
       <c r="L193" s="219">
         <f>F193*(K193-J193)</f>
@@ -13828,31 +13832,31 @@
       <c r="C194" s="131" t="n"/>
       <c r="D194" s="128" t="inlineStr">
         <is>
-          <t>景碩(3189)</t>
+          <t>臻鼎-KY(4958)</t>
         </is>
       </c>
       <c r="E194" s="129" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F194" s="129" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G194" s="129" t="n">
-        <v>4152</v>
+        <v>3419</v>
       </c>
       <c r="H194" s="129" t="n">
-        <v>2110</v>
+        <v>1775</v>
       </c>
       <c r="I194" s="129" t="n">
-        <v>2042</v>
+        <v>1644</v>
       </c>
       <c r="J194" s="130" t="n">
-        <v>883.49</v>
+        <v>599.89</v>
       </c>
       <c r="K194" s="130" t="n">
-        <v>879.12</v>
-      </c>
-      <c r="L194" s="219">
+        <v>612.03</v>
+      </c>
+      <c r="L194" s="220">
         <f>F194*(K194-J194)</f>
         <v/>
       </c>
@@ -13867,27 +13871,27 @@
         </is>
       </c>
       <c r="E195" s="129" t="n">
-        <v>486</v>
+        <v>538</v>
       </c>
       <c r="F195" s="129" t="n">
-        <v>259</v>
+        <v>461</v>
       </c>
       <c r="G195" s="129" t="n">
-        <v>3761</v>
+        <v>3398</v>
       </c>
       <c r="H195" s="129" t="n">
-        <v>3227</v>
+        <v>1797</v>
       </c>
       <c r="I195" s="129" t="n">
-        <v>534</v>
+        <v>1601</v>
       </c>
       <c r="J195" s="130" t="n">
-        <v>77.38</v>
+        <v>63.15</v>
       </c>
       <c r="K195" s="130" t="n">
-        <v>124.59</v>
-      </c>
-      <c r="L195" s="220">
+        <v>38.97</v>
+      </c>
+      <c r="L195" s="219">
         <f>F195*(K195-J195)</f>
         <v/>
       </c>
@@ -13898,29 +13902,29 @@
       <c r="C196" s="131" t="n"/>
       <c r="D196" s="128" t="inlineStr">
         <is>
-          <t>創見(2451)</t>
+          <t>力積電(6770)</t>
         </is>
       </c>
       <c r="E196" s="129" t="n">
-        <v>148</v>
+        <v>364</v>
       </c>
       <c r="F196" s="129" t="n">
-        <v>8</v>
+        <v>234</v>
       </c>
       <c r="G196" s="129" t="n">
-        <v>3703</v>
+        <v>2702</v>
       </c>
       <c r="H196" s="129" t="n">
-        <v>205</v>
+        <v>1739</v>
       </c>
       <c r="I196" s="129" t="n">
-        <v>3498</v>
+        <v>963</v>
       </c>
       <c r="J196" s="130" t="n">
-        <v>250.2</v>
+        <v>74.22</v>
       </c>
       <c r="K196" s="130" t="n">
-        <v>256.5</v>
+        <v>74.31</v>
       </c>
       <c r="L196" s="220">
         <f>F196*(K196-J196)</f>
@@ -13933,31 +13937,31 @@
       <c r="C197" s="131" t="n"/>
       <c r="D197" s="128" t="inlineStr">
         <is>
-          <t>臻鼎-KY(4958)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E197" s="129" t="n">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="F197" s="129" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="G197" s="129" t="n">
-        <v>3188</v>
+        <v>2687</v>
       </c>
       <c r="H197" s="129" t="n">
-        <v>1481</v>
+        <v>1967</v>
       </c>
       <c r="I197" s="129" t="n">
-        <v>1707</v>
+        <v>720</v>
       </c>
       <c r="J197" s="130" t="n">
-        <v>579.64</v>
+        <v>180.36</v>
       </c>
       <c r="K197" s="130" t="n">
-        <v>510.59</v>
-      </c>
-      <c r="L197" s="219">
+        <v>312.25</v>
+      </c>
+      <c r="L197" s="220">
         <f>F197*(K197-J197)</f>
         <v/>
       </c>
@@ -13968,29 +13972,29 @@
       <c r="C198" s="131" t="n"/>
       <c r="D198" s="128" t="inlineStr">
         <is>
-          <t>華邦電(2344)</t>
+          <t>南電(8046)</t>
         </is>
       </c>
       <c r="E198" s="129" t="n">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="F198" s="129" t="n">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="G198" s="129" t="n">
-        <v>2888</v>
+        <v>2373</v>
       </c>
       <c r="H198" s="129" t="n">
-        <v>1234</v>
+        <v>1858</v>
       </c>
       <c r="I198" s="129" t="n">
-        <v>1654</v>
+        <v>515</v>
       </c>
       <c r="J198" s="130" t="n">
-        <v>209.28</v>
+        <v>1186.6</v>
       </c>
       <c r="K198" s="130" t="n">
-        <v>121.01</v>
+        <v>1161.19</v>
       </c>
       <c r="L198" s="219">
         <f>F198*(K198-J198)</f>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -1143,12 +1143,12 @@
     <comment ref="D16" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「陳族元」獨佔比 73.1%
-  • 領頭金額 122,814 萬
-  • 合計淨買 167,916 萬
+領頭大戶「陳族元」獨佔比 73.5%
+  • 領頭金額 125,231 萬
+  • 合計淨買 170,333 萬
   • 大戶數 11 位 (名義共識)
 判讀: 名義 11 位大戶共識,
-實質 1 人下注佔 73%,
+實質 1 人下注佔 74%,
 剩餘 10 位為陪襯小單,
 真共識訊號被稀釋.</t>
       </text>
@@ -1156,9 +1156,9 @@
     <comment ref="D18" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「陳族元」獨佔比 85.1%
-  • 領頭金額 111,125 萬
-  • 合計淨買 130,648 萬
+領頭大戶「陳族元」獨佔比 85.3%
+  • 領頭金額 113,167 萬
+  • 合計淨買 132,691 萬
   • 大戶數 11 位 (名義共識)
 判讀: 名義 11 位大戶共識,
 實質 1 人下注佔 85%,
@@ -1669,7 +1669,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="H16" s="18" t="n">
-        <v>122814</v>
+        <v>125231</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>8</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>167916</v>
+        <v>170333</v>
       </c>
     </row>
     <row r="17">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J17" s="19" t="n">
-        <v>27775</v>
+        <v>27838</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>8</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>140806</v>
+        <v>140869</v>
       </c>
     </row>
     <row r="18">
@@ -1771,7 +1771,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>111125</v>
+        <v>113168</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>8</v>
       </c>
       <c r="N18" s="18" t="n">
-        <v>130649</v>
+        <v>132691</v>
       </c>
     </row>
     <row r="19">
@@ -1822,7 +1822,7 @@
         <v>13</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="H19" s="18" t="n">
-        <v>14362</v>
+        <v>13571</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>10</v>
       </c>
       <c r="N19" s="18" t="n">
-        <v>53128</v>
+        <v>52338</v>
       </c>
     </row>
     <row r="20">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="H20" s="18" t="n">
-        <v>9953</v>
+        <v>10887</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>10</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>48774</v>
+        <v>49708</v>
       </c>
     </row>
     <row r="21">
@@ -1912,49 +1912,49 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>📌 友達</t>
+          <t>📌 南亞科</t>
         </is>
       </c>
       <c r="E21" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>張濬安</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="H21" s="18" t="n">
-        <v>9401</v>
+        <v>10443</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="J21" s="19" t="n">
-        <v>7221</v>
+        <v>8128</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>竹科主力分點</t>
+          <t>布哥</t>
         </is>
       </c>
       <c r="L21" s="19" t="n">
-        <v>3786</v>
+        <v>5062</v>
       </c>
       <c r="M21" s="20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N21" s="18" t="n">
-        <v>31236</v>
+        <v>39670</v>
       </c>
     </row>
     <row r="22">
@@ -1963,49 +1963,49 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>📌 南亞科</t>
+          <t>📌 友達</t>
         </is>
       </c>
       <c r="E22" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>張濬安</t>
         </is>
       </c>
       <c r="H22" s="18" t="n">
-        <v>8128</v>
+        <v>9401</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>布哥</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="J22" s="19" t="n">
-        <v>5062</v>
+        <v>6490</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>強森</t>
+          <t>竹科主力分點</t>
         </is>
       </c>
       <c r="L22" s="19" t="n">
-        <v>3597</v>
+        <v>3786</v>
       </c>
       <c r="M22" s="20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N22" s="18" t="n">
-        <v>30627</v>
+        <v>30505</v>
       </c>
     </row>
     <row r="23">
@@ -2026,7 +2026,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
@@ -2046,17 +2046,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>張濬安</t>
         </is>
       </c>
       <c r="L23" s="19" t="n">
-        <v>2478</v>
+        <v>1726</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>9</v>
       </c>
       <c r="N23" s="18" t="n">
-        <v>22896</v>
+        <v>21324</v>
       </c>
     </row>
     <row r="24">
@@ -2065,19 +2065,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>📌 力積電</t>
+          <t>📌 群聯</t>
         </is>
       </c>
       <c r="E24" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
@@ -2085,29 +2085,29 @@
         </is>
       </c>
       <c r="H24" s="18" t="n">
-        <v>4403</v>
+        <v>3930</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>強森</t>
+          <t>竹科主力分點</t>
         </is>
       </c>
       <c r="J24" s="19" t="n">
-        <v>2523</v>
+        <v>2952</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>布哥</t>
         </is>
       </c>
       <c r="L24" s="19" t="n">
-        <v>2250</v>
+        <v>2889</v>
       </c>
       <c r="M24" s="20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>17231</v>
+        <v>17237</v>
       </c>
     </row>
     <row r="25">
@@ -2128,7 +2128,7 @@
         <v>10</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>7</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>17026</v>
+        <v>16403</v>
       </c>
     </row>
     <row r="26">
@@ -2167,19 +2167,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>📌 群聯</t>
+          <t>📌 力積電</t>
         </is>
       </c>
       <c r="E26" s="15" t="n">
         <v>11</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
@@ -2187,29 +2187,29 @@
         </is>
       </c>
       <c r="H26" s="18" t="n">
-        <v>3930</v>
+        <v>4403</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>竹科主力分點</t>
+          <t>強森</t>
         </is>
       </c>
       <c r="J26" s="19" t="n">
-        <v>2952</v>
+        <v>2523</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>布哥</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="L26" s="19" t="n">
-        <v>2889</v>
+        <v>2250</v>
       </c>
       <c r="M26" s="20" t="n">
         <v>8</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>16578</v>
+        <v>16268</v>
       </c>
     </row>
     <row r="27">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
+          <t>強森</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>1004</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>陳族元</t>
         </is>
       </c>
-      <c r="H27" s="18" t="n">
-        <v>1334</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>強森</t>
-        </is>
-      </c>
       <c r="J27" s="19" t="n">
-        <v>1004</v>
+        <v>858</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>10</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>5538</v>
+        <v>5062</v>
       </c>
     </row>
     <row r="28">
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="G31" s="196" t="n">
-        <v>-70.77464999999999</v>
+        <v>-69.29268999999999</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
@@ -2345,7 +2345,7 @@
           <t>Q3 強共識股</t>
         </is>
       </c>
-      <c r="C32" s="222" t="n">
+      <c r="C32" s="197" t="n">
         <v>13</v>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G32" s="198" t="n">
-        <v>0.2062267155802317</v>
+        <v>0.2064924530775332</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>2826495</v>
+        <v>2833870</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>民哥</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>民哥 今日買進 10 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 11 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>10 檔</t>
+          <t>11 檔</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="C48" s="41" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>民哥</t>
         </is>
       </c>
       <c r="D48" s="41" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="E48" s="41" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 10 檔新標的 (過去從沒買過)</t>
+          <t>民哥 今日買進 10 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F48" s="41" t="inlineStr">
@@ -2947,11 +2947,11 @@
         <v>40</v>
       </c>
       <c r="E61" t="n">
-        <v>4194968</v>
+        <v>4199746</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>陳族元 連續 40 天加碼 2327 (累計 4,194,968 萬)</t>
+          <t>陳族元 連續 40 天加碼 2327 (累計 4,199,746 萬)</t>
         </is>
       </c>
     </row>
@@ -3016,11 +3016,11 @@
         <v>24</v>
       </c>
       <c r="E64" s="41" t="n">
-        <v>2454739</v>
+        <v>2459724</v>
       </c>
       <c r="F64" s="41" t="inlineStr">
         <is>
-          <t>陳族元 連續 24 天加碼 2454 (累計 2,454,739 萬)</t>
+          <t>陳族元 連續 24 天加碼 2454 (累計 2,459,724 萬)</t>
         </is>
       </c>
     </row>
@@ -3062,11 +3062,11 @@
         <v>22</v>
       </c>
       <c r="E66" s="41" t="n">
-        <v>1071058</v>
+        <v>1077017</v>
       </c>
       <c r="F66" s="41" t="inlineStr">
         <is>
-          <t>陳族元 連續 22 天加碼 2408 (累計 1,071,058 萬)</t>
+          <t>陳族元 連續 22 天加碼 2408 (累計 1,077,017 萬)</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="C72" s="33" t="n">
-        <v>2769537</v>
+        <v>2776908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>198077</v>
       </c>
       <c r="J72" s="202" t="n">
-        <v>0.2883579763176334</v>
+        <v>0.2875925512129766</v>
       </c>
     </row>
     <row r="73">
@@ -5098,7 +5098,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="C29" s="70" t="inlineStr">
         <is>
-          <t>-71 億 淨買</t>
+          <t>-69 億 淨買</t>
         </is>
       </c>
     </row>
@@ -13657,29 +13657,29 @@
       </c>
       <c r="D189" s="128" t="inlineStr">
         <is>
-          <t>聯電(2303)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E189" s="129" t="n">
-        <v>504</v>
+        <v>260</v>
       </c>
       <c r="F189" s="129" t="n">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="G189" s="129" t="n">
-        <v>8511</v>
+        <v>11302</v>
       </c>
       <c r="H189" s="129" t="n">
-        <v>2574</v>
+        <v>1610</v>
       </c>
       <c r="I189" s="129" t="n">
-        <v>5937</v>
+        <v>9692</v>
       </c>
       <c r="J189" s="130" t="n">
-        <v>168.87</v>
+        <v>434.69</v>
       </c>
       <c r="K189" s="130" t="n">
-        <v>169.34</v>
+        <v>435.05</v>
       </c>
       <c r="L189" s="220">
         <f>F189*(K189-J189)</f>
@@ -13692,31 +13692,31 @@
       <c r="C190" s="131" t="n"/>
       <c r="D190" s="128" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>智邦(2345)</t>
         </is>
       </c>
       <c r="E190" s="129" t="n">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="F190" s="129" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="G190" s="129" t="n">
-        <v>5343</v>
+        <v>5230</v>
       </c>
       <c r="H190" s="129" t="n">
-        <v>4694</v>
+        <v>3343</v>
       </c>
       <c r="I190" s="129" t="n">
-        <v>649</v>
+        <v>1887</v>
       </c>
       <c r="J190" s="130" t="n">
-        <v>205.51</v>
+        <v>2615.15</v>
       </c>
       <c r="K190" s="130" t="n">
-        <v>1268.51</v>
-      </c>
-      <c r="L190" s="220">
+        <v>2571.38</v>
+      </c>
+      <c r="L190" s="219">
         <f>F190*(K190-J190)</f>
         <v/>
       </c>
@@ -13727,31 +13727,31 @@
       <c r="C191" s="131" t="n"/>
       <c r="D191" s="128" t="inlineStr">
         <is>
-          <t>創見(2451)</t>
+          <t>聯發科(2454)</t>
         </is>
       </c>
       <c r="E191" s="129" t="n">
-        <v>146</v>
+        <v>11</v>
       </c>
       <c r="F191" s="129" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G191" s="129" t="n">
-        <v>3657</v>
+        <v>4985</v>
       </c>
       <c r="H191" s="129" t="n">
-        <v>200</v>
+        <v>4384</v>
       </c>
       <c r="I191" s="129" t="n">
-        <v>3457</v>
+        <v>601</v>
       </c>
       <c r="J191" s="130" t="n">
-        <v>250.5</v>
+        <v>4531.73</v>
       </c>
       <c r="K191" s="130" t="n">
-        <v>250.5</v>
-      </c>
-      <c r="L191" s="220">
+        <v>4384.4</v>
+      </c>
+      <c r="L191" s="219">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -13762,31 +13762,31 @@
       <c r="C192" s="131" t="n"/>
       <c r="D192" s="128" t="inlineStr">
         <is>
-          <t>大立光(3008)</t>
+          <t>國巨*(2327)</t>
         </is>
       </c>
       <c r="E192" s="129" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F192" s="129" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G192" s="129" t="n">
-        <v>3561</v>
+        <v>4778</v>
       </c>
       <c r="H192" s="129" t="n">
-        <v>1864</v>
+        <v>2361</v>
       </c>
       <c r="I192" s="129" t="n">
-        <v>1697</v>
+        <v>2417</v>
       </c>
       <c r="J192" s="130" t="n">
-        <v>4451.25</v>
+        <v>1137.57</v>
       </c>
       <c r="K192" s="130" t="n">
-        <v>4659</v>
-      </c>
-      <c r="L192" s="220">
+        <v>1124.14</v>
+      </c>
+      <c r="L192" s="219">
         <f>F192*(K192-J192)</f>
         <v/>
       </c>
@@ -13797,29 +13797,29 @@
       <c r="C193" s="131" t="n"/>
       <c r="D193" s="128" t="inlineStr">
         <is>
-          <t>欣興(3037)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E193" s="129" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F193" s="129" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G193" s="129" t="n">
-        <v>3462</v>
+        <v>4152</v>
       </c>
       <c r="H193" s="129" t="n">
-        <v>1447</v>
+        <v>2110</v>
       </c>
       <c r="I193" s="129" t="n">
-        <v>2015</v>
+        <v>2042</v>
       </c>
       <c r="J193" s="130" t="n">
-        <v>1049.24</v>
+        <v>883.49</v>
       </c>
       <c r="K193" s="130" t="n">
-        <v>1033.79</v>
+        <v>879.12</v>
       </c>
       <c r="L193" s="219">
         <f>F193*(K193-J193)</f>
@@ -13832,29 +13832,29 @@
       <c r="C194" s="131" t="n"/>
       <c r="D194" s="128" t="inlineStr">
         <is>
-          <t>臻鼎-KY(4958)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E194" s="129" t="n">
-        <v>57</v>
+        <v>538</v>
       </c>
       <c r="F194" s="129" t="n">
-        <v>29</v>
+        <v>461</v>
       </c>
       <c r="G194" s="129" t="n">
-        <v>3419</v>
+        <v>3761</v>
       </c>
       <c r="H194" s="129" t="n">
-        <v>1775</v>
+        <v>3227</v>
       </c>
       <c r="I194" s="129" t="n">
-        <v>1644</v>
+        <v>534</v>
       </c>
       <c r="J194" s="130" t="n">
-        <v>599.89</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K194" s="130" t="n">
-        <v>612.03</v>
+        <v>70</v>
       </c>
       <c r="L194" s="220">
         <f>F194*(K194-J194)</f>
@@ -13867,31 +13867,31 @@
       <c r="C195" s="131" t="n"/>
       <c r="D195" s="128" t="inlineStr">
         <is>
-          <t>群創(3481)</t>
+          <t>創見(2451)</t>
         </is>
       </c>
       <c r="E195" s="129" t="n">
-        <v>538</v>
+        <v>146</v>
       </c>
       <c r="F195" s="129" t="n">
-        <v>461</v>
+        <v>8</v>
       </c>
       <c r="G195" s="129" t="n">
-        <v>3398</v>
+        <v>3703</v>
       </c>
       <c r="H195" s="129" t="n">
-        <v>1797</v>
+        <v>205</v>
       </c>
       <c r="I195" s="129" t="n">
-        <v>1601</v>
+        <v>3498</v>
       </c>
       <c r="J195" s="130" t="n">
-        <v>63.15</v>
+        <v>253.63</v>
       </c>
       <c r="K195" s="130" t="n">
-        <v>38.97</v>
-      </c>
-      <c r="L195" s="219">
+        <v>256.5</v>
+      </c>
+      <c r="L195" s="220">
         <f>F195*(K195-J195)</f>
         <v/>
       </c>
@@ -13902,31 +13902,31 @@
       <c r="C196" s="131" t="n"/>
       <c r="D196" s="128" t="inlineStr">
         <is>
-          <t>力積電(6770)</t>
+          <t>臻鼎-KY(4958)</t>
         </is>
       </c>
       <c r="E196" s="129" t="n">
-        <v>364</v>
+        <v>53</v>
       </c>
       <c r="F196" s="129" t="n">
-        <v>234</v>
+        <v>25</v>
       </c>
       <c r="G196" s="129" t="n">
-        <v>2702</v>
+        <v>3188</v>
       </c>
       <c r="H196" s="129" t="n">
-        <v>1739</v>
+        <v>1481</v>
       </c>
       <c r="I196" s="129" t="n">
-        <v>963</v>
+        <v>1707</v>
       </c>
       <c r="J196" s="130" t="n">
-        <v>74.22</v>
+        <v>601.51</v>
       </c>
       <c r="K196" s="130" t="n">
-        <v>74.31</v>
-      </c>
-      <c r="L196" s="220">
+        <v>592.28</v>
+      </c>
+      <c r="L196" s="219">
         <f>F196*(K196-J196)</f>
         <v/>
       </c>
@@ -13937,29 +13937,29 @@
       <c r="C197" s="131" t="n"/>
       <c r="D197" s="128" t="inlineStr">
         <is>
-          <t>華邦電(2344)</t>
+          <t>友達(2409)</t>
         </is>
       </c>
       <c r="E197" s="129" t="n">
-        <v>149</v>
+        <v>963</v>
       </c>
       <c r="F197" s="129" t="n">
-        <v>63</v>
+        <v>910</v>
       </c>
       <c r="G197" s="129" t="n">
-        <v>2687</v>
+        <v>2952</v>
       </c>
       <c r="H197" s="129" t="n">
-        <v>1967</v>
+        <v>2789</v>
       </c>
       <c r="I197" s="129" t="n">
-        <v>720</v>
+        <v>163</v>
       </c>
       <c r="J197" s="130" t="n">
-        <v>180.36</v>
+        <v>30.65</v>
       </c>
       <c r="K197" s="130" t="n">
-        <v>312.25</v>
+        <v>30.65</v>
       </c>
       <c r="L197" s="220">
         <f>F197*(K197-J197)</f>
@@ -13972,31 +13972,31 @@
       <c r="C198" s="131" t="n"/>
       <c r="D198" s="128" t="inlineStr">
         <is>
-          <t>南電(8046)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E198" s="129" t="n">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="F198" s="129" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="G198" s="129" t="n">
-        <v>2373</v>
+        <v>2888</v>
       </c>
       <c r="H198" s="129" t="n">
-        <v>1858</v>
+        <v>1234</v>
       </c>
       <c r="I198" s="129" t="n">
-        <v>515</v>
+        <v>1654</v>
       </c>
       <c r="J198" s="130" t="n">
-        <v>1186.6</v>
+        <v>193.83</v>
       </c>
       <c r="K198" s="130" t="n">
-        <v>1161.19</v>
-      </c>
-      <c r="L198" s="219">
+        <v>195.92</v>
+      </c>
+      <c r="L198" s="220">
         <f>F198*(K198-J198)</f>
         <v/>
       </c>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -1822,7 +1822,7 @@
         <v>13</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="H19" s="18" t="n">
-        <v>13571</v>
+        <v>14365</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>10</v>
       </c>
       <c r="N19" s="18" t="n">
-        <v>52338</v>
+        <v>53132</v>
       </c>
     </row>
     <row r="20">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="J22" s="19" t="n">
-        <v>6490</v>
+        <v>7158</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>9</v>
       </c>
       <c r="N22" s="18" t="n">
-        <v>30505</v>
+        <v>31173</v>
       </c>
     </row>
     <row r="23">
@@ -2026,7 +2026,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
@@ -2046,17 +2046,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>張濬安</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="L23" s="19" t="n">
-        <v>1726</v>
+        <v>2461</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>9</v>
       </c>
       <c r="N23" s="18" t="n">
-        <v>21324</v>
+        <v>22879</v>
       </c>
     </row>
     <row r="24">
@@ -2116,27 +2116,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>📌 華碩</t>
+          <t>📌 力積電</t>
         </is>
       </c>
       <c r="E25" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>竹科主力分點</t>
+          <t>張濬安</t>
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>6021</v>
+        <v>4403</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="J25" s="19" t="n">
-        <v>2551</v>
+        <v>2523</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="L25" s="19" t="n">
-        <v>2204</v>
+        <v>2250</v>
       </c>
       <c r="M25" s="20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>16403</v>
+        <v>17167</v>
       </c>
     </row>
     <row r="26">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>📌 力積電</t>
+          <t>📌 華碩</t>
         </is>
       </c>
       <c r="E26" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>張濬安</t>
+          <t>竹科主力分點</t>
         </is>
       </c>
       <c r="H26" s="18" t="n">
-        <v>4403</v>
+        <v>6021</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="J26" s="19" t="n">
-        <v>2523</v>
+        <v>2551</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="L26" s="19" t="n">
-        <v>2250</v>
+        <v>2204</v>
       </c>
       <c r="M26" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>16268</v>
+        <v>16403</v>
       </c>
     </row>
     <row r="27">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>1310</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>強森</t>
         </is>
       </c>
-      <c r="H27" s="18" t="n">
+      <c r="J27" s="19" t="n">
         <v>1004</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>陳族元</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="n">
-        <v>858</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>10</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>5062</v>
+        <v>5513</v>
       </c>
     </row>
     <row r="28">
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="E28" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
@@ -2308,10 +2308,10 @@
         <v>302</v>
       </c>
       <c r="M28" s="20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N28" s="18" t="n">
-        <v>3056</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="G31" s="196" t="n">
-        <v>-69.29268999999999</v>
+        <v>-67.94410000000001</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G32" s="198" t="n">
-        <v>0.2064924530775332</v>
+        <v>0.2069969164823522</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -2433,11 +2433,11 @@
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>2833870</v>
+        <v>2850916</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 11 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 12 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>11 檔</t>
+          <t>12 檔</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="C72" s="33" t="n">
-        <v>2776908</v>
+        <v>2794292</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>198077</v>
       </c>
       <c r="J72" s="202" t="n">
-        <v>0.2875925512129766</v>
+        <v>0.285803447077483</v>
       </c>
     </row>
     <row r="73">
@@ -5098,7 +5098,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="C29" s="70" t="inlineStr">
         <is>
-          <t>-69 億 淨買</t>
+          <t>-68 億 淨買</t>
         </is>
       </c>
     </row>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="E189" s="129" t="n">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F189" s="129" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G189" s="129" t="n">
         <v>11302</v>
@@ -13676,10 +13676,10 @@
         <v>9692</v>
       </c>
       <c r="J189" s="130" t="n">
-        <v>434.69</v>
+        <v>421.71</v>
       </c>
       <c r="K189" s="130" t="n">
-        <v>435.05</v>
+        <v>423.61</v>
       </c>
       <c r="L189" s="220">
         <f>F189*(K189-J189)</f>
@@ -13692,31 +13692,31 @@
       <c r="C190" s="131" t="n"/>
       <c r="D190" s="128" t="inlineStr">
         <is>
-          <t>智邦(2345)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="E190" s="129" t="n">
-        <v>20</v>
+        <v>498</v>
       </c>
       <c r="F190" s="129" t="n">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="G190" s="129" t="n">
-        <v>5230</v>
+        <v>8416</v>
       </c>
       <c r="H190" s="129" t="n">
-        <v>3343</v>
+        <v>2569</v>
       </c>
       <c r="I190" s="129" t="n">
-        <v>1887</v>
+        <v>5847</v>
       </c>
       <c r="J190" s="130" t="n">
-        <v>2615.15</v>
+        <v>169</v>
       </c>
       <c r="K190" s="130" t="n">
-        <v>2571.38</v>
-      </c>
-      <c r="L190" s="219">
+        <v>169</v>
+      </c>
+      <c r="L190" s="220">
         <f>F190*(K190-J190)</f>
         <v/>
       </c>
@@ -13727,29 +13727,29 @@
       <c r="C191" s="131" t="n"/>
       <c r="D191" s="128" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>智邦(2345)</t>
         </is>
       </c>
       <c r="E191" s="129" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F191" s="129" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G191" s="129" t="n">
-        <v>4985</v>
+        <v>5230</v>
       </c>
       <c r="H191" s="129" t="n">
-        <v>4384</v>
+        <v>3343</v>
       </c>
       <c r="I191" s="129" t="n">
-        <v>601</v>
+        <v>1887</v>
       </c>
       <c r="J191" s="130" t="n">
-        <v>4531.73</v>
+        <v>2615.15</v>
       </c>
       <c r="K191" s="130" t="n">
-        <v>4384.4</v>
+        <v>2571.38</v>
       </c>
       <c r="L191" s="219">
         <f>F191*(K191-J191)</f>
@@ -13762,29 +13762,29 @@
       <c r="C192" s="131" t="n"/>
       <c r="D192" s="128" t="inlineStr">
         <is>
-          <t>國巨*(2327)</t>
+          <t>聯發科(2454)</t>
         </is>
       </c>
       <c r="E192" s="129" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F192" s="129" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G192" s="129" t="n">
-        <v>4778</v>
+        <v>4985</v>
       </c>
       <c r="H192" s="129" t="n">
-        <v>2361</v>
+        <v>4384</v>
       </c>
       <c r="I192" s="129" t="n">
-        <v>2417</v>
+        <v>601</v>
       </c>
       <c r="J192" s="130" t="n">
-        <v>1137.57</v>
+        <v>4531.73</v>
       </c>
       <c r="K192" s="130" t="n">
-        <v>1124.14</v>
+        <v>4384.4</v>
       </c>
       <c r="L192" s="219">
         <f>F192*(K192-J192)</f>
@@ -13797,29 +13797,29 @@
       <c r="C193" s="131" t="n"/>
       <c r="D193" s="128" t="inlineStr">
         <is>
-          <t>景碩(3189)</t>
+          <t>國巨*(2327)</t>
         </is>
       </c>
       <c r="E193" s="129" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F193" s="129" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G193" s="129" t="n">
-        <v>4152</v>
+        <v>4778</v>
       </c>
       <c r="H193" s="129" t="n">
-        <v>2110</v>
+        <v>2361</v>
       </c>
       <c r="I193" s="129" t="n">
-        <v>2042</v>
+        <v>2417</v>
       </c>
       <c r="J193" s="130" t="n">
-        <v>883.49</v>
+        <v>1137.57</v>
       </c>
       <c r="K193" s="130" t="n">
-        <v>879.12</v>
+        <v>1124.14</v>
       </c>
       <c r="L193" s="219">
         <f>F193*(K193-J193)</f>
@@ -13832,31 +13832,31 @@
       <c r="C194" s="131" t="n"/>
       <c r="D194" s="128" t="inlineStr">
         <is>
-          <t>群創(3481)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E194" s="129" t="n">
-        <v>538</v>
+        <v>47</v>
       </c>
       <c r="F194" s="129" t="n">
-        <v>461</v>
+        <v>24</v>
       </c>
       <c r="G194" s="129" t="n">
-        <v>3761</v>
+        <v>4152</v>
       </c>
       <c r="H194" s="129" t="n">
-        <v>3227</v>
+        <v>2110</v>
       </c>
       <c r="I194" s="129" t="n">
-        <v>534</v>
+        <v>2042</v>
       </c>
       <c r="J194" s="130" t="n">
-        <v>69.90000000000001</v>
+        <v>883.49</v>
       </c>
       <c r="K194" s="130" t="n">
-        <v>70</v>
-      </c>
-      <c r="L194" s="220">
+        <v>879.12</v>
+      </c>
+      <c r="L194" s="219">
         <f>F194*(K194-J194)</f>
         <v/>
       </c>
@@ -13867,29 +13867,29 @@
       <c r="C195" s="131" t="n"/>
       <c r="D195" s="128" t="inlineStr">
         <is>
-          <t>創見(2451)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E195" s="129" t="n">
-        <v>146</v>
+        <v>486</v>
       </c>
       <c r="F195" s="129" t="n">
-        <v>8</v>
+        <v>259</v>
       </c>
       <c r="G195" s="129" t="n">
-        <v>3703</v>
+        <v>3761</v>
       </c>
       <c r="H195" s="129" t="n">
-        <v>205</v>
+        <v>3227</v>
       </c>
       <c r="I195" s="129" t="n">
-        <v>3498</v>
+        <v>534</v>
       </c>
       <c r="J195" s="130" t="n">
-        <v>253.63</v>
+        <v>77.38</v>
       </c>
       <c r="K195" s="130" t="n">
-        <v>256.5</v>
+        <v>124.59</v>
       </c>
       <c r="L195" s="220">
         <f>F195*(K195-J195)</f>
@@ -13902,31 +13902,31 @@
       <c r="C196" s="131" t="n"/>
       <c r="D196" s="128" t="inlineStr">
         <is>
-          <t>臻鼎-KY(4958)</t>
+          <t>創見(2451)</t>
         </is>
       </c>
       <c r="E196" s="129" t="n">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="F196" s="129" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G196" s="129" t="n">
-        <v>3188</v>
+        <v>3703</v>
       </c>
       <c r="H196" s="129" t="n">
-        <v>1481</v>
+        <v>205</v>
       </c>
       <c r="I196" s="129" t="n">
-        <v>1707</v>
+        <v>3498</v>
       </c>
       <c r="J196" s="130" t="n">
-        <v>601.51</v>
+        <v>250.2</v>
       </c>
       <c r="K196" s="130" t="n">
-        <v>592.28</v>
-      </c>
-      <c r="L196" s="219">
+        <v>256.5</v>
+      </c>
+      <c r="L196" s="220">
         <f>F196*(K196-J196)</f>
         <v/>
       </c>
@@ -13937,31 +13937,31 @@
       <c r="C197" s="131" t="n"/>
       <c r="D197" s="128" t="inlineStr">
         <is>
-          <t>友達(2409)</t>
+          <t>臻鼎-KY(4958)</t>
         </is>
       </c>
       <c r="E197" s="129" t="n">
-        <v>963</v>
+        <v>55</v>
       </c>
       <c r="F197" s="129" t="n">
-        <v>910</v>
+        <v>29</v>
       </c>
       <c r="G197" s="129" t="n">
-        <v>2952</v>
+        <v>3188</v>
       </c>
       <c r="H197" s="129" t="n">
-        <v>2789</v>
+        <v>1481</v>
       </c>
       <c r="I197" s="129" t="n">
-        <v>163</v>
+        <v>1707</v>
       </c>
       <c r="J197" s="130" t="n">
-        <v>30.65</v>
+        <v>579.64</v>
       </c>
       <c r="K197" s="130" t="n">
-        <v>30.65</v>
-      </c>
-      <c r="L197" s="220">
+        <v>510.59</v>
+      </c>
+      <c r="L197" s="219">
         <f>F197*(K197-J197)</f>
         <v/>
       </c>
@@ -13976,10 +13976,10 @@
         </is>
       </c>
       <c r="E198" s="129" t="n">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F198" s="129" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="G198" s="129" t="n">
         <v>2888</v>
@@ -13991,12 +13991,12 @@
         <v>1654</v>
       </c>
       <c r="J198" s="130" t="n">
-        <v>193.83</v>
+        <v>209.28</v>
       </c>
       <c r="K198" s="130" t="n">
-        <v>195.92</v>
-      </c>
-      <c r="L198" s="220">
+        <v>121.01</v>
+      </c>
+      <c r="L198" s="219">
         <f>F198*(K198-J198)</f>
         <v/>
       </c>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨+26/5d-190)&quot;;-0&quot; 億 (昨+26/5d-190)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +70億 &quot;&quot;(昨12/5d12)&quot;"/>
@@ -41,8 +41,9 @@
     <numFmt numFmtId="179" formatCode="0&quot; 檔 +105億 &quot;&quot;(昨13/5d12)&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0%&quot; 市-1418億 &quot;&quot;(昨21/5d18)&quot;"/>
     <numFmt numFmtId="181" formatCode="&quot;📅 明日預測 ↑ 偏多 &quot;0.0&quot;% 信心 — P/C Ratio 主推 — 3 檔焦點&quot;"/>
+    <numFmt numFmtId="182" formatCode="0.0%&quot; 市-1416億 &quot;&quot;(昨21/5d18)&quot;"/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="52">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -334,6 +335,12 @@
       <color rgb="FFB45309"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Noto Sans TC"/>
+      <i val="1"/>
+      <color rgb="FF10B981"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="48">
     <fill>
@@ -588,7 +595,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1133,6 +1140,10 @@
     <xf numFmtId="175" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="182" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1556,7 +1567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N135"/>
+  <dimension ref="B2:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1592,7 +1603,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 📌 一般共識 2330 / 2454 / 5483 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 除權息 30 檔: 00939, 00984D, 1452 ... | 明日恐處置 5 檔: 3189/6213/8021...  |  訊號: 強偏多 (Q5 67.1%, hot=24)</t>
+          <t>💡 📌 一般共識 2330 / 2454 / 5483 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 明日恐處置 9 檔: 1447/1617/3055...  |  訊號: 強偏多 (Q5 67.1%, hot=24)</t>
         </is>
       </c>
     </row>
@@ -2275,8 +2286,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G29" s="225" t="n">
-        <v>0.2110509342257378</v>
+      <c r="G29" s="236" t="n">
+        <v>0.2106659514045904</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
@@ -3576,7 +3587,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="B83" s="59" t="inlineStr">
         <is>
-          <t>▍ G. 注意股 (資料日 20260701)</t>
+          <t>▍ G. 注意股 (資料日 20260703)</t>
         </is>
       </c>
     </row>
@@ -3608,755 +3619,769 @@
       </c>
     </row>
     <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>059570</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>強茂凱基5B購03</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="41" t="inlineStr">
-        <is>
-          <t>1435</t>
-        </is>
-      </c>
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>中福</t>
-        </is>
-      </c>
-      <c r="D86" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="41" t="n">
-        <v>30.05</v>
-      </c>
-      <c r="F86" s="41" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>1444</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>力麗</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-----</t>
+      <c r="B85" s="237" t="inlineStr">
+        <is>
+          <t>✅ 今日無新增注意股 (市場無異常波動標的)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260702)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="41" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="C88" s="41" t="inlineStr">
-        <is>
-          <t>力鵬</t>
-        </is>
-      </c>
-      <c r="D88" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="41" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="F88" s="41" t="inlineStr">
-        <is>
-          <t>-----</t>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>借券張數</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>融券張數</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>榮星</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
+          <t>力積電</t>
+        </is>
+      </c>
+      <c r="D89" s="33" t="n">
+        <v>17785</v>
+      </c>
+      <c r="E89" s="33" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F89" s="206" t="n">
+        <v>15.33</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="47" t="inlineStr">
+        <is>
+          <t>🔴 2886</t>
+        </is>
+      </c>
+      <c r="C90" s="41" t="inlineStr">
+        <is>
+          <t>兆豐金</t>
+        </is>
+      </c>
+      <c r="D90" s="62" t="n">
+        <v>14055</v>
+      </c>
+      <c r="E90" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="E89" t="n">
-        <v>22.85</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>25.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="41" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="C90" s="41" t="inlineStr">
-        <is>
-          <t>東聯</t>
-        </is>
-      </c>
-      <c r="D90" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="41" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F90" s="41" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
+      <c r="F90" s="204" t="n">
+        <v>14055</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>中纖</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
+          <t>主動統一台股增長</t>
+        </is>
+      </c>
+      <c r="D91" s="33" t="n">
+        <v>11517</v>
+      </c>
+      <c r="E91" s="33" t="n">
+        <v>514</v>
+      </c>
+      <c r="F91" s="206" t="n">
+        <v>22.41</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="47" t="inlineStr">
+        <is>
+          <t>🔴 2891</t>
+        </is>
+      </c>
+      <c r="C92" s="41" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="D92" s="62" t="n">
+        <v>8917</v>
+      </c>
+      <c r="E92" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="E91" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>51.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="41" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="C92" s="41" t="inlineStr">
-        <is>
-          <t>宏旭-KY</t>
-        </is>
-      </c>
-      <c r="D92" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="41" t="n">
-        <v>62</v>
-      </c>
-      <c r="F92" s="41" t="inlineStr">
-        <is>
-          <t>24.90</t>
-        </is>
+      <c r="F92" s="204" t="n">
+        <v>8917</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" t="n">
-        <v>169</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>42.46</t>
-        </is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="D93" s="33" t="n">
+        <v>6897</v>
+      </c>
+      <c r="E93" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F93" s="206" t="n">
+        <v>287.38</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="41" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C94" s="41" t="inlineStr">
         <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="D94" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="41" t="n">
-        <v>2660</v>
-      </c>
-      <c r="F94" s="41" t="inlineStr">
-        <is>
-          <t>50.30</t>
-        </is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="D94" s="62" t="n">
+        <v>6176</v>
+      </c>
+      <c r="E94" s="62" t="n">
+        <v>103</v>
+      </c>
+      <c r="F94" s="205" t="n">
+        <v>59.96</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>矽統</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="n">
-        <v>73.5</v>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="D95" s="33" t="n">
+        <v>5181</v>
+      </c>
+      <c r="E95" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>43.24</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="41" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="C96" s="41" t="inlineStr">
         <is>
-          <t>凱美</t>
-        </is>
-      </c>
-      <c r="D96" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="41" t="n">
-        <v>232.5</v>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="D96" s="62" t="n">
+        <v>4899</v>
+      </c>
+      <c r="E96" s="62" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="41" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>國碩</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="D97" s="33" t="n">
+        <v>4880</v>
+      </c>
+      <c r="E97" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="47" t="inlineStr">
+        <is>
+          <t>🔴 0056</t>
+        </is>
+      </c>
+      <c r="C98" s="41" t="inlineStr">
+        <is>
+          <t>元大高股息</t>
+        </is>
+      </c>
+      <c r="D98" s="62" t="n">
+        <v>4538</v>
+      </c>
+      <c r="E98" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" s="204" t="n">
+        <v>1134.5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="46" t="inlineStr">
+        <is>
+          <t>🔴 2892</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D99" s="33" t="n">
+        <v>4271</v>
+      </c>
+      <c r="E99" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E97" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="41" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="C98" s="41" t="inlineStr">
-        <is>
-          <t>希華</t>
-        </is>
-      </c>
-      <c r="D98" s="41" t="n">
+      <c r="F99" s="203" t="n">
+        <v>4271</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="47" t="inlineStr">
+        <is>
+          <t>🔴 2412</t>
+        </is>
+      </c>
+      <c r="C100" s="41" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="D100" s="62" t="n">
+        <v>4249</v>
+      </c>
+      <c r="E100" s="62" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" s="204" t="n">
+        <v>2124.5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="46" t="inlineStr">
+        <is>
+          <t>🔴 1101</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="D101" s="33" t="n">
+        <v>4130</v>
+      </c>
+      <c r="E101" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E98" s="41" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="F98" s="41" t="inlineStr">
-        <is>
-          <t>107.84</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>3023</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>信邦</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" t="n">
-        <v>333</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>26.08</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260701)</t>
-        </is>
+      <c r="F101" s="203" t="n">
+        <v>4130</v>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B102" s="41" t="inlineStr">
+        <is>
+          <t>8112</t>
+        </is>
+      </c>
+      <c r="C102" s="41" t="inlineStr">
+        <is>
+          <t>至上</t>
+        </is>
+      </c>
+      <c r="D102" s="62" t="n">
+        <v>4099</v>
+      </c>
+      <c r="E102" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>8422</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>可寧衛*</t>
+        </is>
+      </c>
+      <c r="D103" s="33" t="n">
+        <v>3773</v>
+      </c>
+      <c r="E103" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="B105" s="65" t="inlineStr">
+        <is>
+          <t>▍ I. 未來 30 天除權息 (有效 258 檔, 已剔除過期)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="60" t="inlineStr">
+        <is>
+          <t>除權息日</t>
+        </is>
+      </c>
+      <c r="C106" s="60" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C102" s="12" t="inlineStr">
+      <c r="D106" s="60" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D102" s="12" t="inlineStr">
-        <is>
-          <t>借券張數</t>
-        </is>
-      </c>
-      <c r="E102" s="12" t="inlineStr">
-        <is>
-          <t>融券張數</t>
-        </is>
-      </c>
-      <c r="F102" s="12" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="46" t="inlineStr">
-        <is>
-          <t>🔴 2887</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D103" s="33" t="n">
-        <v>13846</v>
-      </c>
-      <c r="E103" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="F103" s="203" t="n">
-        <v>4615.33</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="41" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C104" s="41" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D104" s="62" t="n">
-        <v>12974</v>
-      </c>
-      <c r="E104" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D105" s="33" t="n">
-        <v>11153</v>
-      </c>
-      <c r="E105" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" s="47" t="inlineStr">
-        <is>
-          <t>🔴 3231</t>
-        </is>
-      </c>
-      <c r="C106" s="41" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="D106" s="62" t="n">
-        <v>11039</v>
-      </c>
-      <c r="E106" s="62" t="n">
-        <v>3</v>
-      </c>
-      <c r="F106" s="204" t="n">
-        <v>3679.67</v>
+      <c r="E106" s="60" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="F106" s="60" t="inlineStr">
+        <is>
+          <t>現金股利</t>
+        </is>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="46" t="inlineStr">
-        <is>
-          <t>🔴 2002</t>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D107" s="33" t="n">
-        <v>8477</v>
-      </c>
-      <c r="E107" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="F107" s="203" t="n">
-        <v>1695.4</v>
+          <t>1455</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>集盛</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="41" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C108" s="41" t="inlineStr">
         <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="D108" s="62" t="n">
-        <v>7892</v>
-      </c>
-      <c r="E108" s="62" t="n">
-        <v>451</v>
-      </c>
-      <c r="F108" s="205" t="n">
-        <v>17.5</v>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="D108" s="41" t="inlineStr">
+        <is>
+          <t>花仙子</t>
+        </is>
+      </c>
+      <c r="E108" s="41" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F108" s="41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>中纖</t>
-        </is>
-      </c>
-      <c r="D109" s="33" t="n">
-        <v>7786</v>
-      </c>
-      <c r="E109" s="33" t="n">
-        <v>437</v>
-      </c>
-      <c r="F109" s="206" t="n">
-        <v>17.82</v>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="47" t="inlineStr">
-        <is>
-          <t>🔴 1101</t>
+      <c r="B110" s="41" t="inlineStr">
+        <is>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C110" s="41" t="inlineStr">
         <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="D110" s="62" t="n">
-        <v>7348</v>
-      </c>
-      <c r="E110" s="62" t="n">
-        <v>2</v>
-      </c>
-      <c r="F110" s="204" t="n">
-        <v>3674</v>
+          <t>2425</t>
+        </is>
+      </c>
+      <c r="D110" s="41" t="inlineStr">
+        <is>
+          <t>承啟</t>
+        </is>
+      </c>
+      <c r="E110" s="41" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F110" s="41" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="46" t="inlineStr">
-        <is>
-          <t>🔴 0056</t>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="D111" s="33" t="n">
-        <v>7238</v>
-      </c>
-      <c r="E111" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="F111" s="203" t="n">
-        <v>1809.5</v>
+          <t>2838A</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>聯邦銀甲特</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>2.630625</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" s="41" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C112" s="41" t="inlineStr">
         <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="D112" s="62" t="n">
-        <v>6334</v>
-      </c>
-      <c r="E112" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>2945</t>
+        </is>
+      </c>
+      <c r="D112" s="41" t="inlineStr">
+        <is>
+          <t>三商家購</t>
+        </is>
+      </c>
+      <c r="E112" s="41" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F112" s="41" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="46" t="inlineStr">
-        <is>
-          <t>🔴 2886</t>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D113" s="33" t="n">
-        <v>6035</v>
-      </c>
-      <c r="E113" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="F113" s="203" t="n">
-        <v>1207</v>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>6.584838</v>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="41" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C114" s="41" t="inlineStr">
         <is>
-          <t>金寶</t>
-        </is>
-      </c>
-      <c r="D114" s="62" t="n">
-        <v>5782</v>
-      </c>
-      <c r="E114" s="62" t="n">
-        <v>74</v>
-      </c>
-      <c r="F114" s="205" t="n">
-        <v>78.14</v>
+          <t>910861</t>
+        </is>
+      </c>
+      <c r="D114" s="41" t="inlineStr">
+        <is>
+          <t>神州-DR</t>
+        </is>
+      </c>
+      <c r="E114" s="41" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F114" s="41" t="n">
+        <v>0.072018</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D115" s="33" t="n">
-        <v>5366</v>
-      </c>
-      <c r="E115" s="33" t="n">
-        <v>278</v>
-      </c>
-      <c r="F115" s="206" t="n">
-        <v>19.3</v>
+          <t>00946</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>群益科技高息成長</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>0.058</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="41" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C116" s="41" t="inlineStr">
         <is>
-          <t>寶成</t>
-        </is>
-      </c>
-      <c r="D116" s="62" t="n">
-        <v>5179</v>
-      </c>
-      <c r="E116" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>00953B</t>
+        </is>
+      </c>
+      <c r="D116" s="41" t="inlineStr">
+        <is>
+          <t>群益優選非投等債</t>
+        </is>
+      </c>
+      <c r="E116" s="41" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F116" s="41" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>瑞軒</t>
-        </is>
-      </c>
-      <c r="D117" s="33" t="n">
-        <v>5112</v>
-      </c>
-      <c r="E117" s="33" t="n">
-        <v>602</v>
-      </c>
-      <c r="F117" s="206" t="n">
-        <v>8.49</v>
-      </c>
-    </row>
-    <row r="119" ht="22" customHeight="1">
-      <c r="B119" s="65" t="inlineStr">
-        <is>
-          <t>▍ I. 未來 30 天除權息 (有效 279 檔, 已剔除過期)</t>
-        </is>
+          <t>00985B</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>群益ESG投等債0-5</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>0.048</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="41" t="inlineStr">
+        <is>
+          <t>20260706</t>
+        </is>
+      </c>
+      <c r="C118" s="41" t="inlineStr">
+        <is>
+          <t>00997A</t>
+        </is>
+      </c>
+      <c r="D118" s="41" t="inlineStr">
+        <is>
+          <t>主動群益美國增長</t>
+        </is>
+      </c>
+      <c r="E118" s="41" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F118" s="41" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>20260706</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>三芳</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="120">
-      <c r="B120" s="60" t="inlineStr">
-        <is>
-          <t>除權息日</t>
-        </is>
-      </c>
-      <c r="C120" s="60" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="D120" s="60" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="E120" s="60" t="inlineStr">
-        <is>
-          <t>類型</t>
-        </is>
-      </c>
-      <c r="F120" s="60" t="inlineStr">
-        <is>
-          <t>現金股利</t>
-        </is>
+      <c r="B120" s="41" t="inlineStr">
+        <is>
+          <t>20260706</t>
+        </is>
+      </c>
+      <c r="C120" s="41" t="inlineStr">
+        <is>
+          <t>2373</t>
+        </is>
+      </c>
+      <c r="D120" s="41" t="inlineStr">
+        <is>
+          <t>震旦行</t>
+        </is>
+      </c>
+      <c r="E120" s="41" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F120" s="41" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="121">
       <c r="B121" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>00939</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>統一台灣高息動能</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4365,370 +4390,19 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="B122" s="41" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C122" s="41" t="inlineStr">
-        <is>
-          <t>00984D</t>
-        </is>
-      </c>
-      <c r="D122" s="41" t="inlineStr">
-        <is>
-          <t>主動聯博全球非投</t>
-        </is>
-      </c>
-      <c r="E122" s="41" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F122" s="41" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>宏益</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="41" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C124" s="41" t="inlineStr">
-        <is>
-          <t>1612</t>
-        </is>
-      </c>
-      <c r="D124" s="41" t="inlineStr">
-        <is>
-          <t>宏泰</t>
-        </is>
-      </c>
-      <c r="E124" s="41" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F124" s="41" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>南光</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="41" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C126" s="41" t="inlineStr">
-        <is>
-          <t>1789</t>
-        </is>
-      </c>
-      <c r="D126" s="41" t="inlineStr">
-        <is>
-          <t>神隆</t>
-        </is>
-      </c>
-      <c r="E126" s="41" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F126" s="41" t="n">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>春源</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="41" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C128" s="41" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="D128" s="41" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="E128" s="41" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F128" s="41" t="n">
-        <v>7.171792</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2354</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>鴻準</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="41" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C130" s="41" t="inlineStr">
-        <is>
-          <t>2433</t>
-        </is>
-      </c>
-      <c r="D130" s="41" t="inlineStr">
-        <is>
-          <t>互盛電</t>
-        </is>
-      </c>
-      <c r="E130" s="41" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F130" s="41" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2462</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>良得電</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" s="41" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C132" s="41" t="inlineStr">
-        <is>
-          <t>2607</t>
-        </is>
-      </c>
-      <c r="D132" s="41" t="inlineStr">
-        <is>
-          <t>榮運</t>
-        </is>
-      </c>
-      <c r="E132" s="41" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F132" s="41" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>2753</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>八方雲集</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F133" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" s="41" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C134" s="41" t="inlineStr">
-        <is>
-          <t>2820</t>
-        </is>
-      </c>
-      <c r="D134" s="41" t="inlineStr">
-        <is>
-          <t>華票</t>
-        </is>
-      </c>
-      <c r="E134" s="41" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F134" s="41" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>3006</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>晶豪科</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F135" t="n">
-        <v>1</v>
+        <v>7.113868</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="G28:I28"/>
     <mergeCell ref="B67:J67"/>
     <mergeCell ref="B9:N9"/>
     <mergeCell ref="B42:J42"/>
     <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B101:J101"/>
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B119:J119"/>
+    <mergeCell ref="B87:J87"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="B4:N4"/>
     <mergeCell ref="B7:N7"/>
@@ -4747,6 +4421,8 @@
     <mergeCell ref="B27:J27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="B56:J56"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B105:J105"/>
     <mergeCell ref="B10:N10"/>
   </mergeCells>
   <conditionalFormatting sqref="N16:N25">
@@ -4821,17 +4497,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D85:D99">
+  <conditionalFormatting sqref="D89:D103">
     <cfRule type="dataBar" priority="9">
-      <dataBar minLength="5" maxLength="90" showValue="1">
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFB300"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D103:D117">
-    <cfRule type="dataBar" priority="10">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4839,8 +4506,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F103:F117">
-    <cfRule type="dataBar" priority="11">
+  <conditionalFormatting sqref="F89:F103">
+    <cfRule type="dataBar" priority="10">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5039,16 +4706,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="69" t="inlineStr">
-        <is>
-          <t>除權息 30 檔 (00939 / 00984D / 1452 ...)</t>
+      <c r="C32" s="71" t="inlineStr">
+        <is>
+          <t>今日無除權息</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="C33" s="69" t="inlineStr">
         <is>
-          <t>明日恐處置 5 檔 (3189 / 6213 / 8021 ...)</t>
+          <t>明日恐處置 9 檔 (1447 / 1617 / 3055 ...)</t>
         </is>
       </c>
     </row>
@@ -11095,7 +10762,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="B3" s="98" t="inlineStr">
         <is>
-          <t>大牌分析師 近 51/51 交易日出手 2465 次 (521 檔), 風格分布: 隔日沖近似 39% / 當沖 13% / 留倉 48%, 漲停命中 5% (其中 🔒鎖漲停 4%), 前 5 大集中 24%, 長線部位 61% (35 檔), ⚠️ 處置股部位 14% (48 檔), 📦 連續囤貨 29 檔 (最長 13 天 009816, 4 檔仍 active)。 主軸: 高頻交易/持續進場/📦 連續囤貨。</t>
+          <t>大牌分析師 近 51/51 交易日出手 2465 次 (521 檔), 風格分布: 隔日沖近似 39% / 當沖 13% / 留倉 48%, 漲停命中 5% (其中 🔒鎖漲停 4%), 前 5 大集中 24%, 長線部位 61% (35 檔), ⚠️ 處置股部位 11% (42 檔), 📦 連續囤貨 29 檔 (最長 13 天 009816, 4 檔仍 active)。 主軸: 高頻交易/持續進場/📦 連續囤貨。</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="19">
+  <numFmts count="20">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨+26/5d-190)&quot;;-0&quot; 億 (昨+26/5d-190)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +70億 &quot;&quot;(昨12/5d12)&quot;"/>
@@ -42,6 +42,7 @@
     <numFmt numFmtId="180" formatCode="0.0%&quot; 市-1418億 &quot;&quot;(昨21/5d18)&quot;"/>
     <numFmt numFmtId="181" formatCode="&quot;📅 明日預測 ↑ 偏多 &quot;0.0&quot;% 信心 — P/C Ratio 主推 — 3 檔焦點&quot;"/>
     <numFmt numFmtId="182" formatCode="0.0%&quot; 市-1416億 &quot;&quot;(昨21/5d18)&quot;"/>
+    <numFmt numFmtId="183" formatCode="0.0%&quot; 市-1417億 &quot;&quot;(昨21/5d18)&quot;"/>
   </numFmts>
   <fonts count="52">
     <font>
@@ -595,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1144,6 +1145,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="183" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2238,13 +2242,13 @@
         </is>
       </c>
       <c r="L25" s="19" t="n">
-        <v>528</v>
+        <v>479</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>7</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>6291</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -2269,7 +2273,7 @@
         </is>
       </c>
       <c r="G28" s="223" t="n">
-        <v>16.67531</v>
+        <v>16.23846</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
@@ -2286,8 +2290,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G29" s="236" t="n">
-        <v>0.2106659514045904</v>
+      <c r="G29" s="238" t="n">
+        <v>0.2107734731758731</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
@@ -2398,11 +2402,11 @@
         </is>
       </c>
       <c r="D36" s="33" t="n">
-        <v>1199489</v>
+        <v>1202887</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2434,7 +2438,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -3147,7 +3151,7 @@
         </is>
       </c>
       <c r="C70" s="33" t="n">
-        <v>1108795</v>
+        <v>1111948</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3174,7 +3178,7 @@
         <v>73050</v>
       </c>
       <c r="J70" s="202" t="n">
-        <v>0.2383021249907783</v>
+        <v>0.2376265538388181</v>
       </c>
     </row>
     <row r="71">
@@ -4729,7 +4733,7 @@
     <row r="36" ht="22" customHeight="1">
       <c r="C36" s="226" t="inlineStr">
         <is>
-          <t>+17 億 淨買</t>
+          <t>+16 億 淨買</t>
         </is>
       </c>
     </row>
@@ -18532,10 +18536,10 @@
         </is>
       </c>
       <c r="E195" s="129" t="n">
-        <v>271</v>
+        <v>147</v>
       </c>
       <c r="F195" s="129" t="n">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="G195" s="129" t="n">
         <v>2924</v>
@@ -18547,12 +18551,12 @@
         <v>1091</v>
       </c>
       <c r="J195" s="130" t="n">
-        <v>107.91</v>
+        <v>198.93</v>
       </c>
       <c r="K195" s="130" t="n">
-        <v>104.74</v>
-      </c>
-      <c r="L195" s="219">
+        <v>458.23</v>
+      </c>
+      <c r="L195" s="220">
         <f>F195*(K195-J195)</f>
         <v/>
       </c>
@@ -18567,10 +18571,10 @@
         </is>
       </c>
       <c r="E196" s="129" t="n">
-        <v>204</v>
+        <v>71</v>
       </c>
       <c r="F196" s="129" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G196" s="129" t="n">
         <v>2793</v>
@@ -18582,12 +18586,12 @@
         <v>2181</v>
       </c>
       <c r="J196" s="130" t="n">
-        <v>136.91</v>
+        <v>393.38</v>
       </c>
       <c r="K196" s="130" t="n">
-        <v>145.74</v>
-      </c>
-      <c r="L196" s="220">
+        <v>139.11</v>
+      </c>
+      <c r="L196" s="219">
         <f>F196*(K196-J196)</f>
         <v/>
       </c>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -1635,7 +1635,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>🟡 跟單實際淨報酬 (扣 0.585% 成本): 淨 hit 116/228 = 51% | 平均 +0.92% | 中位 +0.08% | 累積 +211% — 勉強損益兩平</t>
+          <t>🟡 跟單實際淨報酬 (扣 0.585% 成本): 淨 hit 116/228 = 51% | 平均 +0.92% | 中位 +0.08% | 累積 +210% — 勉強損益兩平</t>
         </is>
       </c>
     </row>
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="L25" s="19" t="n">
-        <v>479</v>
+        <v>528</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>7</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>6242</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="G28" s="223" t="n">
-        <v>16.23846</v>
+        <v>16.67345</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
@@ -2290,8 +2290,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G29" s="238" t="n">
-        <v>0.2107734731758731</v>
+      <c r="G29" s="225" t="n">
+        <v>0.2110515210419748</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
@@ -2402,11 +2402,11 @@
         </is>
       </c>
       <c r="D36" s="33" t="n">
-        <v>1202887</v>
+        <v>1199489</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="C47" s="41" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>民哥</t>
         </is>
       </c>
       <c r="D47" s="41" t="inlineStr">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="E47" s="41" t="inlineStr">
         <is>
-          <t>林滄海 今日買進 6 檔新標的 (過去從沒買過)</t>
+          <t>民哥 今日買進 7 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F47" s="41" t="inlineStr">
         <is>
-          <t>6 檔</t>
+          <t>7 檔</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>民哥</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>民哥 今日買進 6 檔新標的 (過去從沒買過)</t>
+          <t>林滄海 今日買進 6 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="C70" s="33" t="n">
-        <v>1111948</v>
+        <v>1108795</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>73050</v>
       </c>
       <c r="J70" s="202" t="n">
-        <v>0.2376265538388181</v>
+        <v>0.2383021249907783</v>
       </c>
     </row>
     <row r="71">
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="C76" s="33" t="n">
-        <v>132255</v>
+        <v>132292</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>9264</v>
       </c>
       <c r="J76" s="202" t="n">
-        <v>0.3169780476942631</v>
+        <v>0.3168893938328802</v>
       </c>
     </row>
     <row r="77">
@@ -4733,7 +4733,7 @@
     <row r="36" ht="22" customHeight="1">
       <c r="C36" s="226" t="inlineStr">
         <is>
-          <t>+16 億 淨買</t>
+          <t>+17 億 淨買</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
         <v>23.08</v>
       </c>
       <c r="I6" s="212" t="n">
-        <v>-1.7</v>
+        <v>-1.71</v>
       </c>
       <c r="J6" s="71" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>44.44444444444444</v>
       </c>
       <c r="G42" s="208" t="n">
-        <v>1.269722222222222</v>
+        <v>1.263888888888888</v>
       </c>
     </row>
     <row r="43">
@@ -6113,7 +6113,7 @@
     <row r="4" ht="18" customHeight="1">
       <c r="B4" s="88" t="inlineStr">
         <is>
-          <t>歸因分布: 個股弱勢 (跑輸大盤 &gt;2pp): 40 | TAIEX 資料缺, 歸因不全: 38 | TAIEX 整盤跌: 15 | 假共識 (領頭獨佔 ≥50%): 9 | flat close (隔日收 = 今日收, 真實現象): 8 | alpha noise (個股無系統性原因): 3</t>
+          <t>歸因分布: 個股弱勢 (跑輸大盤 &gt;2pp): 39 | TAIEX 資料缺, 歸因不全: 38 | TAIEX 整盤跌: 15 | 假共識 (領頭獨佔 ≥50%): 9 | flat close (隔日收 = 今日收, 真實現象): 8 | alpha noise (個股無系統性原因): 4</t>
         </is>
       </c>
     </row>
@@ -6189,10 +6189,10 @@
         <v>-0.83</v>
       </c>
       <c r="F7" s="215" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="G7" s="216" t="n">
-        <v>-2.77</v>
+        <v>-2.17</v>
       </c>
       <c r="H7" s="213" t="n">
         <v>37.3</v>
@@ -6231,10 +6231,10 @@
         <v>-3.42</v>
       </c>
       <c r="F8" s="215" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="G8" s="216" t="n">
-        <v>-5.36</v>
+        <v>-4.76</v>
       </c>
       <c r="H8" s="213" t="n">
         <v>21.1</v>
@@ -6273,10 +6273,10 @@
         <v>-3.63</v>
       </c>
       <c r="F9" s="215" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="G9" s="216" t="n">
-        <v>-5.57</v>
+        <v>-4.97</v>
       </c>
       <c r="H9" s="213" t="n">
         <v>21.7</v>
@@ -6315,10 +6315,10 @@
         <v>-7.46</v>
       </c>
       <c r="F10" s="215" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="G10" s="216" t="n">
-        <v>-9.4</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="H10" s="235" t="n">
         <v>52.7</v>
@@ -6357,10 +6357,10 @@
         <v>-3.33</v>
       </c>
       <c r="F11" s="215" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="G11" s="216" t="n">
-        <v>-5.27</v>
+        <v>-4.67</v>
       </c>
       <c r="H11" s="213" t="n">
         <v>16.8</v>
@@ -6396,13 +6396,13 @@
         </is>
       </c>
       <c r="E12" s="212" t="n">
-        <v>-6.32</v>
+        <v>-6.53</v>
       </c>
       <c r="F12" s="215" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="G12" s="216" t="n">
-        <v>-8.26</v>
+        <v>-7.87</v>
       </c>
       <c r="H12" s="235" t="n">
         <v>67.30000000000001</v>
@@ -6441,10 +6441,10 @@
         <v>-3.6</v>
       </c>
       <c r="F13" s="215" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="G13" s="216" t="n">
-        <v>-5.54</v>
+        <v>-4.94</v>
       </c>
       <c r="H13" s="213" t="n">
         <v>29.4</v>
@@ -6483,10 +6483,10 @@
         <v>-3.42</v>
       </c>
       <c r="F14" s="215" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="G14" s="216" t="n">
-        <v>-5.36</v>
+        <v>-4.76</v>
       </c>
       <c r="H14" s="235" t="n">
         <v>60.09999999999999</v>
@@ -6525,10 +6525,10 @@
         <v>-0.49</v>
       </c>
       <c r="F15" s="215" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="G15" s="216" t="n">
-        <v>-2.43</v>
+        <v>-1.83</v>
       </c>
       <c r="H15" s="213" t="n">
         <v>20.3</v>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="K15" s="93" t="inlineStr">
         <is>
-          <t>個股弱勢 (跑輸大盤 &gt;2pp)</t>
+          <t>alpha noise (個股無系統性原因)</t>
         </is>
       </c>
     </row>
@@ -6567,10 +6567,10 @@
         <v>-1.32</v>
       </c>
       <c r="F16" s="215" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="G16" s="216" t="n">
-        <v>-3.26</v>
+        <v>-2.66</v>
       </c>
       <c r="H16" s="213" t="n">
         <v>22.7</v>
@@ -18536,10 +18536,10 @@
         </is>
       </c>
       <c r="E195" s="129" t="n">
-        <v>147</v>
+        <v>271</v>
       </c>
       <c r="F195" s="129" t="n">
-        <v>40</v>
+        <v>175</v>
       </c>
       <c r="G195" s="129" t="n">
         <v>2924</v>
@@ -18551,12 +18551,12 @@
         <v>1091</v>
       </c>
       <c r="J195" s="130" t="n">
-        <v>198.93</v>
+        <v>107.91</v>
       </c>
       <c r="K195" s="130" t="n">
-        <v>458.23</v>
-      </c>
-      <c r="L195" s="220">
+        <v>104.74</v>
+      </c>
+      <c r="L195" s="219">
         <f>F195*(K195-J195)</f>
         <v/>
       </c>
@@ -18571,10 +18571,10 @@
         </is>
       </c>
       <c r="E196" s="129" t="n">
-        <v>71</v>
+        <v>204</v>
       </c>
       <c r="F196" s="129" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G196" s="129" t="n">
         <v>2793</v>
@@ -18586,12 +18586,12 @@
         <v>2181</v>
       </c>
       <c r="J196" s="130" t="n">
-        <v>393.38</v>
+        <v>136.91</v>
       </c>
       <c r="K196" s="130" t="n">
-        <v>139.11</v>
-      </c>
-      <c r="L196" s="219">
+        <v>145.74</v>
+      </c>
+      <c r="L196" s="220">
         <f>F196*(K196-J196)</f>
         <v/>
       </c>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -23,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="24">
+  <numFmts count="25">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨+26/5d-190)&quot;;-0&quot; 億 (昨+26/5d-190)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +70億 &quot;&quot;(昨12/5d12)&quot;"/>
@@ -48,6 +48,7 @@
     <numFmt numFmtId="185" formatCode="0&quot; 檔 +90億 &quot;&quot;(昨10/5d12)&quot;"/>
     <numFmt numFmtId="186" formatCode="0.0%&quot; 市-1293億 &quot;&quot;(昨21/5d19)&quot;"/>
     <numFmt numFmtId="187" formatCode="&quot;📅 明日預測 ↑ 偏多 &quot;0.0&quot;% 信心 — 外資現貨 主推 — 3 檔焦點&quot;"/>
+    <numFmt numFmtId="188" formatCode="0.0%&quot; 市-1289億 &quot;&quot;(昨21/5d19)&quot;"/>
   </numFmts>
   <fonts count="52">
     <font>
@@ -601,7 +602,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1165,6 +1166,9 @@
     <xf numFmtId="187" fontId="45" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="188" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1650,7 +1654,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 📌 一般共識 2330 / 2408 / 3711 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 除權息 8 檔: 1455, 1730, 2013 ... | 明日恐處置 9 檔: 1447/1617/3055...  |  訊號: 強偏多 (Q5 95%, hot=21)</t>
+          <t>💡 📌 一般共識 2330 / 2408 / 3711 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 除權息 8 檔: 1455, 1730, 2013 ... | 明日恐處置 3 檔: 1444/1515/1718  |  訊號: 強偏多 (Q5 95%, hot=21)</t>
         </is>
       </c>
     </row>
@@ -2384,8 +2388,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G30" s="241" t="n">
-        <v>0.2258019218974628</v>
+      <c r="G30" s="243" t="n">
+        <v>0.22600318154549</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
@@ -4829,7 +4833,7 @@
     <row r="32">
       <c r="C32" s="69" t="inlineStr">
         <is>
-          <t>明日恐處置 9 檔 (1447 / 1617 / 3055 ...)</t>
+          <t>明日恐處置 3 檔 (1444 / 1515 / 1718)</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -2265,7 +2265,7 @@
         <v>10</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>7</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>16427</v>
+        <v>16143</v>
       </c>
     </row>
     <row r="26">
@@ -2316,7 +2316,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>7</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>8968</v>
+        <v>9114</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="G29" s="239" t="n">
-        <v>62.14276</v>
+        <v>62.21303</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="G30" s="243" t="n">
-        <v>0.22600318154549</v>
+        <v>0.2261998468242964</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="D37" s="33" t="n">
-        <v>1362450</v>
+        <v>1368762</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>張濬安(航海王)</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>張濬安(航海王) 今日買進 11 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 12 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>11 檔</t>
+          <t>12 檔</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C48" s="41" t="inlineStr">
         <is>
-          <t>民哥</t>
+          <t>張濬安(航海王)</t>
         </is>
       </c>
       <c r="D48" s="41" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="E48" s="41" t="inlineStr">
         <is>
-          <t>民哥 今日買進 11 檔新標的 (過去從沒買過)</t>
+          <t>張濬安(航海王) 今日買進 11 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F48" s="41" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>民哥</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 11 檔新標的 (過去從沒買過)</t>
+          <t>民哥 今日買進 11 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3229,77 +3229,77 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="35" t="inlineStr">
+      <c r="B71" s="32" t="inlineStr">
+        <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="C71" s="33" t="n">
+        <v>1315396</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="E71" s="33" t="n">
+        <v>159748</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>禾伸堂(3026)</t>
+        </is>
+      </c>
+      <c r="G71" s="33" t="n">
+        <v>104066</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>晶技(3042)</t>
+        </is>
+      </c>
+      <c r="I71" s="33" t="n">
+        <v>84354</v>
+      </c>
+      <c r="J71" s="202" t="n">
+        <v>0.264686903506806</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="35" t="inlineStr">
         <is>
           <t>張濬安(航海王)</t>
         </is>
       </c>
-      <c r="C71" s="33" t="n">
+      <c r="C72" s="33" t="n">
         <v>1314317</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>南電(8046)</t>
         </is>
       </c>
-      <c r="E71" s="33" t="n">
+      <c r="E72" s="33" t="n">
         <v>166965</v>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>晶技(3042)</t>
         </is>
       </c>
-      <c r="G71" s="33" t="n">
+      <c r="G72" s="33" t="n">
         <v>80144</v>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>台積電(2330)</t>
         </is>
       </c>
-      <c r="I71" s="33" t="n">
+      <c r="I72" s="33" t="n">
         <v>71983</v>
       </c>
-      <c r="J71" s="202" t="n">
+      <c r="J72" s="202" t="n">
         <v>0.2427811762045588</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="32" t="inlineStr">
-        <is>
-          <t>陳族元</t>
-        </is>
-      </c>
-      <c r="C72" s="33" t="n">
-        <v>1310921</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="E72" s="33" t="n">
-        <v>159748</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>禾伸堂(3026)</t>
-        </is>
-      </c>
-      <c r="G72" s="33" t="n">
-        <v>104066</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>晶技(3042)</t>
-        </is>
-      </c>
-      <c r="I72" s="33" t="n">
-        <v>84354</v>
-      </c>
-      <c r="J72" s="202" t="n">
-        <v>0.265590608615045</v>
       </c>
     </row>
     <row r="73">
@@ -18440,7 +18440,7 @@
         </is>
       </c>
       <c r="E189" s="129" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F189" s="129" t="n">
         <v>1</v>
@@ -18455,7 +18455,7 @@
         <v>6586</v>
       </c>
       <c r="J189" s="130" t="n">
-        <v>846.22</v>
+        <v>879.62</v>
       </c>
       <c r="K189" s="130" t="n">
         <v>988</v>
@@ -18475,7 +18475,7 @@
         </is>
       </c>
       <c r="E190" s="129" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F190" s="129" t="n">
         <v>54</v>
@@ -18490,12 +18490,12 @@
         <v>3487</v>
       </c>
       <c r="J190" s="130" t="n">
-        <v>400.68</v>
+        <v>409.32</v>
       </c>
       <c r="K190" s="130" t="n">
         <v>407.96</v>
       </c>
-      <c r="L190" s="220">
+      <c r="L190" s="219">
         <f>F190*(K190-J190)</f>
         <v/>
       </c>
@@ -18580,10 +18580,10 @@
         </is>
       </c>
       <c r="E193" s="129" t="n">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="F193" s="129" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="G193" s="129" t="n">
         <v>2522</v>
@@ -18595,12 +18595,12 @@
         <v>663</v>
       </c>
       <c r="J193" s="130" t="n">
-        <v>184.12</v>
+        <v>336.32</v>
       </c>
       <c r="K193" s="130" t="n">
-        <v>182.29</v>
-      </c>
-      <c r="L193" s="219">
+        <v>344.33</v>
+      </c>
+      <c r="L193" s="220">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -18681,29 +18681,29 @@
       <c r="C196" s="131" t="n"/>
       <c r="D196" s="128" t="inlineStr">
         <is>
-          <t>大立光(3008)</t>
+          <t>晶豪科(3006)</t>
         </is>
       </c>
       <c r="E196" s="129" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F196" s="129" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G196" s="129" t="n">
-        <v>1819</v>
+        <v>1988</v>
       </c>
       <c r="H196" s="129" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="I196" s="129" t="n">
         <v>1819</v>
       </c>
       <c r="J196" s="130" t="n">
-        <v>4548.25</v>
+        <v>211.5</v>
       </c>
       <c r="K196" s="130" t="n">
-        <v>0</v>
+        <v>211.5</v>
       </c>
       <c r="L196" s="220">
         <f>F196*(K196-J196)</f>
@@ -18716,29 +18716,29 @@
       <c r="C197" s="131" t="n"/>
       <c r="D197" s="128" t="inlineStr">
         <is>
-          <t>高力(8996)</t>
+          <t>大立光(3008)</t>
         </is>
       </c>
       <c r="E197" s="129" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F197" s="129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G197" s="129" t="n">
-        <v>1780</v>
+        <v>1819</v>
       </c>
       <c r="H197" s="129" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="I197" s="129" t="n">
-        <v>1506</v>
+        <v>1819</v>
       </c>
       <c r="J197" s="130" t="n">
-        <v>1369.62</v>
+        <v>4548.25</v>
       </c>
       <c r="K197" s="130" t="n">
-        <v>1370</v>
+        <v>0</v>
       </c>
       <c r="L197" s="220">
         <f>F197*(K197-J197)</f>
@@ -18751,29 +18751,29 @@
       <c r="C198" s="131" t="n"/>
       <c r="D198" s="128" t="inlineStr">
         <is>
-          <t>台半(5425)</t>
+          <t>高力(8996)</t>
         </is>
       </c>
       <c r="E198" s="129" t="n">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="F198" s="129" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G198" s="129" t="n">
-        <v>1352</v>
+        <v>1780</v>
       </c>
       <c r="H198" s="129" t="n">
-        <v>207</v>
+        <v>274</v>
       </c>
       <c r="I198" s="129" t="n">
-        <v>1145</v>
+        <v>1506</v>
       </c>
       <c r="J198" s="130" t="n">
-        <v>128.77</v>
+        <v>1369.62</v>
       </c>
       <c r="K198" s="130" t="n">
-        <v>129.31</v>
+        <v>1370</v>
       </c>
       <c r="L198" s="220">
         <f>F198*(K198-J198)</f>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="G30" s="243" t="n">
-        <v>0.2261998468242964</v>
+        <v>0.2260135027650007</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -1654,7 +1654,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 📌 一般共識 2330 / 2408 / 3711 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 除權息 8 檔: 1455, 1730, 2013 ... | 明日恐處置 3 檔: 1444/1515/1718  |  訊號: 強偏多 (Q5 95%, hot=21)</t>
+          <t>💡 📌 一般共識 2330 / 2408 / 3711 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 明日恐處置 3 檔: 1444/1515/1718  |  訊號: 強偏多 (Q5 95%, hot=21)</t>
         </is>
       </c>
     </row>
@@ -2388,8 +2388,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G30" s="243" t="n">
-        <v>0.2260135027650007</v>
+      <c r="G30" s="241" t="n">
+        <v>0.2260558506983937</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
@@ -3712,7 +3712,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="B85" s="59" t="inlineStr">
         <is>
-          <t>▍ G. 注意股 (資料日 20260703)</t>
+          <t>▍ G. 注意股 (資料日 20260704)</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="B107" s="65" t="inlineStr">
         <is>
-          <t>▍ I. 未來 30 天除權息 (有效 258 檔, 已剔除過期)</t>
+          <t>▍ I. 未來 30 天除權息 (有效 266 檔, 已剔除過期)</t>
         </is>
       </c>
     </row>
@@ -4146,17 +4146,17 @@
     <row r="109">
       <c r="B109" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>00946</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>群益科技高息成長</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4165,23 +4165,23 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0.16</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="41" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C110" s="41" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>00953B</t>
         </is>
       </c>
       <c r="D110" s="41" t="inlineStr">
         <is>
-          <t>花仙子</t>
+          <t>群益優選非投等債</t>
         </is>
       </c>
       <c r="E110" s="41" t="inlineStr">
@@ -4190,23 +4190,23 @@
         </is>
       </c>
       <c r="F110" s="41" t="n">
-        <v>3</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>00985B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>中鋼構</t>
+          <t>群益ESG投等債0-5</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4215,23 +4215,23 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2.4</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" s="41" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C112" s="41" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>00997A</t>
         </is>
       </c>
       <c r="D112" s="41" t="inlineStr">
         <is>
-          <t>承啟</t>
+          <t>主動群益美國增長</t>
         </is>
       </c>
       <c r="E112" s="41" t="inlineStr">
@@ -4240,23 +4240,23 @@
         </is>
       </c>
       <c r="F112" s="41" t="n">
-        <v>0.1</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2838A</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>聯邦銀甲特</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4265,23 +4265,23 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2.630625</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="41" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C114" s="41" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="D114" s="41" t="inlineStr">
         <is>
-          <t>三商家購</t>
+          <t>震旦行</t>
         </is>
       </c>
       <c r="E114" s="41" t="inlineStr">
@@ -4290,23 +4290,23 @@
         </is>
       </c>
       <c r="F114" s="41" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4315,23 +4315,23 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>6.584838</v>
+        <v>7.113868</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="41" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C116" s="41" t="inlineStr">
         <is>
-          <t>910861</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="D116" s="41" t="inlineStr">
         <is>
-          <t>神州-DR</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="E116" s="41" t="inlineStr">
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="F116" s="41" t="n">
-        <v>0.072018</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>00946</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>群益科技高息成長</t>
+          <t>匯僑</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0.058</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="118">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="C118" s="41" t="inlineStr">
         <is>
-          <t>00953B</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="D118" s="41" t="inlineStr">
         <is>
-          <t>群益優選非投等債</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="E118" s="41" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="F118" s="41" t="n">
-        <v>0.061</v>
+        <v>1.980153</v>
       </c>
     </row>
     <row r="119">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>00985B</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>群益ESG投等債0-5</t>
+          <t>嘉威</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0.048</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="120">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="C120" s="41" t="inlineStr">
         <is>
-          <t>00997A</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="D120" s="41" t="inlineStr">
         <is>
-          <t>主動群益美國增長</t>
+          <t>合勤控</t>
         </is>
       </c>
       <c r="E120" s="41" t="inlineStr">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="F120" s="41" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="121">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>東明-KY</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="122">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="C122" s="41" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="D122" s="41" t="inlineStr">
         <is>
-          <t>震旦行</t>
+          <t>鈞寶</t>
         </is>
       </c>
       <c r="E122" s="41" t="inlineStr">
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="F122" s="41" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="123">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>7.113868</v>
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
@@ -4824,9 +4824,9 @@
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="69" t="inlineStr">
-        <is>
-          <t>除權息 8 檔 (1455 / 1730 / 2013 ...)</t>
+      <c r="C31" s="71" t="inlineStr">
+        <is>
+          <t>今日無除權息</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="B3" s="98" t="inlineStr">
         <is>
-          <t>大牌分析師 近 52/52 交易日出手 2511 次 (529 檔), 風格分布: 隔日沖近似 39% / 當沖 13% / 留倉 48%, 漲停命中 5% (其中 🔒鎖漲停 4%), 前 5 大集中 25%, 長線部位 63% (37 檔), ⚠️ 處置股部位 11% (43 檔), 📦 連續囤貨 29 檔 (最長 13 天 009816, 2 檔仍 active)。 主軸: 高頻交易/持續進場/📦 連續囤貨。</t>
+          <t>大牌分析師 近 52/52 交易日出手 2511 次 (529 檔), 風格分布: 隔日沖近似 39% / 當沖 13% / 留倉 48%, 漲停命中 5% (其中 🔒鎖漲停 4%), 前 5 大集中 25%, 長線部位 63% (37 檔), ⚠️ 處置股部位 12% (35 檔), 📦 連續囤貨 29 檔 (最長 13 天 009816, 2 檔仍 active)。 主軸: 高頻交易/持續進場/📦 連續囤貨。</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -1687,9 +1687,9 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>🔬 Phase 3.5 多日 alpha (觀察期 n=38): 5 日內擇高 86.8% / +12.78%  |  premium 擇高 92.9% / +15.99% (n=28)  |  premium 持有 3 天 92.9% / +12.16%  — 來源: quad_hit_log × stock_history t+1~t+5</t>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>🚀 Phase 3.5 多日 alpha (正式): 5 日內擇高 72.8% / +8.56%  |  premium 擇高 73.5% / +9.61% (n=83)  |  premium 持有 3 天 75.7% / +6.37%  — 來源: quad_hit_log × stock_history t+1~t+5</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>📌 大牌分析師 歷史 alpha: 全 picks n=1461 hit_1d=48% / hit_3d=51%  |  新標 n=302 hit_3d=49% mean=+0.96%  |  連加 n=69 hit_5d=59% mean=+3.86%</t>
+          <t>📌 大牌分析師 歷史 alpha: 全 picks n=1641 hit_1d=49% / hit_3d=51%  |  新標 n=314 hit_3d=50% mean=+1.07%  |  連加 n=80 hit_5d=57% mean=+3.63%</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
         <v>10</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>7</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>16143</v>
+        <v>16427</v>
       </c>
     </row>
     <row r="26">
@@ -2316,7 +2316,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>7</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>9114</v>
+        <v>8968</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="G29" s="239" t="n">
-        <v>62.21303</v>
+        <v>62.13752</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="G30" s="241" t="n">
-        <v>0.2260558506983937</v>
+        <v>0.2258069783531962</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
@@ -2400,7 +2400,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="28" t="inlineStr">
         <is>
-          <t>✅ 過去 30 天 P/C 命中率: 偏多 18/27 (67%) | 偏空 0/0 (0%) | 整體 18/27 (67%)</t>
+          <t>✅ 過去 30 天 P/C 命中率: 偏多 19/28 (68%) | 偏空 0/0 (0%) | 整體 19/28 (68%)</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="D37" s="33" t="n">
-        <v>1368762</v>
+        <v>1362450</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>張濬安(航海王)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 12 檔新標的 (過去從沒買過)</t>
+          <t>張濬安(航海王) 今日買進 11 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>12 檔</t>
+          <t>11 檔</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C48" s="41" t="inlineStr">
         <is>
-          <t>張濬安(航海王)</t>
+          <t>民哥</t>
         </is>
       </c>
       <c r="D48" s="41" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="E48" s="41" t="inlineStr">
         <is>
-          <t>張濬安(航海王) 今日買進 11 檔新標的 (過去從沒買過)</t>
+          <t>民哥 今日買進 11 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F48" s="41" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>民哥</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>民哥 今日買進 11 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 11 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>大牌分析師 今日買進 8 檔新標的 (過去從沒買過)</t>
+          <t>大牌分析師 今日買進 9 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>8 檔</t>
+          <t>9 檔</t>
         </is>
       </c>
     </row>
@@ -3229,77 +3229,77 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="32" t="inlineStr">
+      <c r="B71" s="35" t="inlineStr">
+        <is>
+          <t>張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="C71" s="33" t="n">
+        <v>1314317</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>南電(8046)</t>
+        </is>
+      </c>
+      <c r="E71" s="33" t="n">
+        <v>166965</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>晶技(3042)</t>
+        </is>
+      </c>
+      <c r="G71" s="33" t="n">
+        <v>80144</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>台積電(2330)</t>
+        </is>
+      </c>
+      <c r="I71" s="33" t="n">
+        <v>71983</v>
+      </c>
+      <c r="J71" s="202" t="n">
+        <v>0.2427811762045588</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="32" t="inlineStr">
         <is>
           <t>陳族元</t>
         </is>
       </c>
-      <c r="C71" s="33" t="n">
-        <v>1315396</v>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="C72" s="33" t="n">
+        <v>1310921</v>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>南亞科(2408)</t>
         </is>
       </c>
-      <c r="E71" s="33" t="n">
+      <c r="E72" s="33" t="n">
         <v>159748</v>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>禾伸堂(3026)</t>
         </is>
       </c>
-      <c r="G71" s="33" t="n">
+      <c r="G72" s="33" t="n">
         <v>104066</v>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>晶技(3042)</t>
         </is>
       </c>
-      <c r="I71" s="33" t="n">
+      <c r="I72" s="33" t="n">
         <v>84354</v>
       </c>
-      <c r="J71" s="202" t="n">
-        <v>0.264686903506806</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="35" t="inlineStr">
-        <is>
-          <t>張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="C72" s="33" t="n">
-        <v>1314317</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>南電(8046)</t>
-        </is>
-      </c>
-      <c r="E72" s="33" t="n">
-        <v>166965</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>晶技(3042)</t>
-        </is>
-      </c>
-      <c r="G72" s="33" t="n">
-        <v>80144</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>台積電(2330)</t>
-        </is>
-      </c>
-      <c r="I72" s="33" t="n">
-        <v>71983</v>
-      </c>
       <c r="J72" s="202" t="n">
-        <v>0.2427811762045588</v>
+        <v>0.265590608615045</v>
       </c>
     </row>
     <row r="73">
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="C82" s="33" t="n">
-        <v>77663</v>
+        <v>77863</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>5947</v>
       </c>
       <c r="J82" s="202" t="n">
-        <v>0.3001381612069598</v>
+        <v>0.2993652987154427</v>
       </c>
     </row>
     <row r="83">
@@ -3712,7 +3712,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="B85" s="59" t="inlineStr">
         <is>
-          <t>▍ G. 注意股 (資料日 20260704)</t>
+          <t>▍ G. 注意股 (資料日 20260706)</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="B107" s="65" t="inlineStr">
         <is>
-          <t>▍ I. 未來 30 天除權息 (有效 266 檔, 已剔除過期)</t>
+          <t>▍ I. 未來 30 天除權息 (有效 270 檔, 已剔除過期)</t>
         </is>
       </c>
     </row>
@@ -10888,21 +10888,21 @@
     <row r="6">
       <c r="B6" s="99" t="inlineStr">
         <is>
-          <t>全部 picks: n=1461  hit_1d=48%  mean_1d=+0.21%  hit_3d=51%  mean_3d=+0.78%  hit_5d=54%  mean_5d=+2.17%</t>
+          <t>全部 picks: n=1641  hit_1d=49%  mean_1d=+0.26%  hit_3d=51%  mean_3d=+0.86%  hit_5d=52%  mean_5d=+1.91%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="99" t="inlineStr">
         <is>
-          <t>新標的: n=302  hit_1d=48%  mean_1d=+0.25%  hit_3d=49%  mean_3d=+0.96%  hit_5d=52%  mean_5d=+2.36%</t>
+          <t>新標的: n=314  hit_1d=48%  mean_1d=+0.21%  hit_3d=50%  mean_3d=+1.07%  hit_5d=52%  mean_5d=+2.33%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="99" t="inlineStr">
         <is>
-          <t>連續加碼: n=69  hit_1d=48%  mean_1d=+0.87%  hit_3d=52%  mean_3d=-3.16%  hit_5d=59%  mean_5d=+3.86%</t>
+          <t>連續加碼: n=80  hit_1d=52%  mean_1d=+1.16%  hit_3d=53%  mean_3d=-2.53%  hit_5d=57%  mean_5d=+3.63%</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="201" t="n">
-        <v>-0.0528</v>
+        <v>-0.0619</v>
       </c>
     </row>
     <row r="16">
@@ -18440,7 +18440,7 @@
         </is>
       </c>
       <c r="E189" s="129" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F189" s="129" t="n">
         <v>1</v>
@@ -18455,7 +18455,7 @@
         <v>6586</v>
       </c>
       <c r="J189" s="130" t="n">
-        <v>879.62</v>
+        <v>846.22</v>
       </c>
       <c r="K189" s="130" t="n">
         <v>988</v>
@@ -18475,7 +18475,7 @@
         </is>
       </c>
       <c r="E190" s="129" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F190" s="129" t="n">
         <v>54</v>
@@ -18490,12 +18490,12 @@
         <v>3487</v>
       </c>
       <c r="J190" s="130" t="n">
-        <v>409.32</v>
+        <v>400.68</v>
       </c>
       <c r="K190" s="130" t="n">
         <v>407.96</v>
       </c>
-      <c r="L190" s="219">
+      <c r="L190" s="220">
         <f>F190*(K190-J190)</f>
         <v/>
       </c>
@@ -18580,10 +18580,10 @@
         </is>
       </c>
       <c r="E193" s="129" t="n">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="F193" s="129" t="n">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="G193" s="129" t="n">
         <v>2522</v>
@@ -18595,12 +18595,12 @@
         <v>663</v>
       </c>
       <c r="J193" s="130" t="n">
-        <v>336.32</v>
+        <v>184.12</v>
       </c>
       <c r="K193" s="130" t="n">
-        <v>344.33</v>
-      </c>
-      <c r="L193" s="220">
+        <v>182.29</v>
+      </c>
+      <c r="L193" s="219">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -18681,29 +18681,29 @@
       <c r="C196" s="131" t="n"/>
       <c r="D196" s="128" t="inlineStr">
         <is>
-          <t>晶豪科(3006)</t>
+          <t>大立光(3008)</t>
         </is>
       </c>
       <c r="E196" s="129" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="F196" s="129" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G196" s="129" t="n">
-        <v>1988</v>
+        <v>1819</v>
       </c>
       <c r="H196" s="129" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="I196" s="129" t="n">
         <v>1819</v>
       </c>
       <c r="J196" s="130" t="n">
-        <v>211.5</v>
+        <v>4548.25</v>
       </c>
       <c r="K196" s="130" t="n">
-        <v>211.5</v>
+        <v>0</v>
       </c>
       <c r="L196" s="220">
         <f>F196*(K196-J196)</f>
@@ -18716,29 +18716,29 @@
       <c r="C197" s="131" t="n"/>
       <c r="D197" s="128" t="inlineStr">
         <is>
-          <t>大立光(3008)</t>
+          <t>高力(8996)</t>
         </is>
       </c>
       <c r="E197" s="129" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F197" s="129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G197" s="129" t="n">
-        <v>1819</v>
+        <v>1780</v>
       </c>
       <c r="H197" s="129" t="n">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="I197" s="129" t="n">
-        <v>1819</v>
+        <v>1506</v>
       </c>
       <c r="J197" s="130" t="n">
-        <v>4548.25</v>
+        <v>1369.62</v>
       </c>
       <c r="K197" s="130" t="n">
-        <v>0</v>
+        <v>1370</v>
       </c>
       <c r="L197" s="220">
         <f>F197*(K197-J197)</f>
@@ -18751,29 +18751,29 @@
       <c r="C198" s="131" t="n"/>
       <c r="D198" s="128" t="inlineStr">
         <is>
-          <t>高力(8996)</t>
+          <t>台半(5425)</t>
         </is>
       </c>
       <c r="E198" s="129" t="n">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="F198" s="129" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G198" s="129" t="n">
-        <v>1780</v>
+        <v>1352</v>
       </c>
       <c r="H198" s="129" t="n">
-        <v>274</v>
+        <v>207</v>
       </c>
       <c r="I198" s="129" t="n">
-        <v>1506</v>
+        <v>1145</v>
       </c>
       <c r="J198" s="130" t="n">
-        <v>1369.62</v>
+        <v>128.77</v>
       </c>
       <c r="K198" s="130" t="n">
-        <v>1370</v>
+        <v>129.31</v>
       </c>
       <c r="L198" s="220">
         <f>F198*(K198-J198)</f>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -1605,7 +1605,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 📌 一般共識 2330 / 2383 / 2308 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 除權息 22 檔: 00946, 00953B, 00985B ... | 明日恐處置 3 檔: 1444/1515/1718  |  訊號: 強偏多 (Q5 95%, hot=19)</t>
+          <t>💡 📌 一般共識 2330 / 2383 / 2308 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 除權息 22 檔: 00946, 00953B, 00985B ... | 明日恐處置 8 檔: 2466/3026/3167...  |  訊號: 強偏多 (Q5 95%, hot=19)</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="G35" s="246" t="n">
-        <v>0.1877375185157214</v>
+        <v>0.1880521603928755</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -5035,7 +5035,7 @@
     <row r="31">
       <c r="C31" s="69" t="inlineStr">
         <is>
-          <t>明日恐處置 3 檔 (1444 / 1515 / 1718)</t>
+          <t>明日恐處置 8 檔 (2466 / 3026 / 3167 ...)</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="G35" s="246" t="n">
-        <v>0.1880521603928755</v>
+        <v>0.1877375185157214</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -24,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="28">
+  <numFmts count="29">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨+26/5d-190)&quot;;-0&quot; 億 (昨+26/5d-190)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +70億 &quot;&quot;(昨12/5d12)&quot;"/>
@@ -53,6 +53,7 @@
     <numFmt numFmtId="189" formatCode="+0&quot; 億 (昨+62/5d-34)&quot;;-0&quot; 億 (昨+62/5d-34)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="190" formatCode="0&quot; 檔 +75億 &quot;&quot;(昨11/5d12)&quot;"/>
     <numFmt numFmtId="191" formatCode="0.0%&quot; 市-1269億 &quot;&quot;(昨23/5d20)&quot;"/>
+    <numFmt numFmtId="192" formatCode="0.0%&quot; 市-1270億 &quot;&quot;(昨23/5d20)&quot;"/>
   </numFmts>
   <fonts count="52">
     <font>
@@ -606,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1182,6 +1183,9 @@
     <xf numFmtId="191" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="192" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2594,8 +2598,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G35" s="246" t="n">
-        <v>0.1877375185157214</v>
+      <c r="G35" s="247" t="n">
+        <v>0.187868889492441</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -24,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="29">
+  <numFmts count="30">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨+26/5d-190)&quot;;-0&quot; 億 (昨+26/5d-190)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +70億 &quot;&quot;(昨12/5d12)&quot;"/>
@@ -54,6 +54,7 @@
     <numFmt numFmtId="190" formatCode="0&quot; 檔 +75億 &quot;&quot;(昨11/5d12)&quot;"/>
     <numFmt numFmtId="191" formatCode="0.0%&quot; 市-1269億 &quot;&quot;(昨23/5d20)&quot;"/>
     <numFmt numFmtId="192" formatCode="0.0%&quot; 市-1270億 &quot;&quot;(昨23/5d20)&quot;"/>
+    <numFmt numFmtId="193" formatCode="0.0%&quot; 市-1274億 &quot;&quot;(昨23/5d20)&quot;"/>
   </numFmts>
   <fonts count="52">
     <font>
@@ -607,7 +608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1186,6 +1187,9 @@
     <xf numFmtId="192" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="193" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2581,7 +2585,7 @@
         </is>
       </c>
       <c r="G34" s="244" t="n">
-        <v>-173.9864</v>
+        <v>-173.97844</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
@@ -2598,8 +2602,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G35" s="247" t="n">
-        <v>0.187868889492441</v>
+      <c r="G35" s="248" t="n">
+        <v>0.1881211267889168</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -2678,7 +2682,7 @@
         </is>
       </c>
       <c r="D41" s="33" t="n">
-        <v>1154176</v>
+        <v>1153606</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2742,7 +2746,7 @@
         </is>
       </c>
       <c r="D43" s="33" t="n">
-        <v>460978</v>
+        <v>460109</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2806,7 +2810,7 @@
         </is>
       </c>
       <c r="D45" s="33" t="n">
-        <v>318848</v>
+        <v>318384</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2897,7 +2901,7 @@
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>張濬安(航海王)</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="D51" s="41" t="inlineStr">
@@ -2907,7 +2911,7 @@
       </c>
       <c r="E51" s="41" t="inlineStr">
         <is>
-          <t>張濬安(航海王) 今日買進 12 檔新標的 (過去從沒買過)</t>
+          <t>林滄海 今日買進 12 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F51" s="41" t="inlineStr">
@@ -2924,7 +2928,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>張濬安(航海王)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2934,12 +2938,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>林滄海 今日買進 12 檔新標的 (過去從沒買過)</t>
+          <t>張濬安(航海王) 今日買進 11 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>12 檔</t>
+          <t>11 檔</t>
         </is>
       </c>
     </row>
@@ -2961,12 +2965,12 @@
       </c>
       <c r="E53" s="41" t="inlineStr">
         <is>
-          <t>迷你哥/松山哥 今日買進 9 檔新標的 (過去從沒買過)</t>
+          <t>迷你哥/松山哥 今日買進 8 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F53" s="41" t="inlineStr">
         <is>
-          <t>9 檔</t>
+          <t>8 檔</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3449,7 @@
         </is>
       </c>
       <c r="C76" s="33" t="n">
-        <v>1044072</v>
+        <v>1043502</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3472,7 +3476,7 @@
         <v>42623</v>
       </c>
       <c r="J76" s="202" t="n">
-        <v>0.2477659349387844</v>
+        <v>0.2479012739888113</v>
       </c>
     </row>
     <row r="77">
@@ -3519,7 +3523,7 @@
         </is>
       </c>
       <c r="C78" s="33" t="n">
-        <v>458228</v>
+        <v>457359</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3546,7 +3550,7 @@
         <v>38253</v>
       </c>
       <c r="J78" s="202" t="n">
-        <v>0.3982710350024518</v>
+        <v>0.3990277657218434</v>
       </c>
     </row>
     <row r="79">
@@ -3593,7 +3597,7 @@
         </is>
       </c>
       <c r="C80" s="33" t="n">
-        <v>294519</v>
+        <v>294055</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3620,7 +3624,7 @@
         <v>15058</v>
       </c>
       <c r="J80" s="202" t="n">
-        <v>0.2139676415094019</v>
+        <v>0.2143051955515865</v>
       </c>
     </row>
     <row r="81">
@@ -3630,7 +3634,7 @@
         </is>
       </c>
       <c r="C81" s="33" t="n">
-        <v>235161</v>
+        <v>234766</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3657,7 +3661,7 @@
         <v>14181</v>
       </c>
       <c r="J81" s="202" t="n">
-        <v>0.1833723208237424</v>
+        <v>0.183680380292759</v>
       </c>
     </row>
     <row r="82">
@@ -3667,7 +3671,7 @@
         </is>
       </c>
       <c r="C82" s="33" t="n">
-        <v>175971</v>
+        <v>175726</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3694,7 +3698,7 @@
         <v>13013</v>
       </c>
       <c r="J82" s="202" t="n">
-        <v>0.2923942976838176</v>
+        <v>0.292801959418548</v>
       </c>
     </row>
     <row r="83">
@@ -3704,7 +3708,7 @@
         </is>
       </c>
       <c r="C83" s="33" t="n">
-        <v>155253</v>
+        <v>155270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3731,7 +3735,7 @@
         <v>9585</v>
       </c>
       <c r="J83" s="202" t="n">
-        <v>0.2588144891335363</v>
+        <v>0.2587864857084157</v>
       </c>
     </row>
     <row r="84">
@@ -3815,7 +3819,7 @@
         </is>
       </c>
       <c r="C86" s="33" t="n">
-        <v>75692</v>
+        <v>75091</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3842,7 +3846,7 @@
         <v>5286</v>
       </c>
       <c r="J86" s="202" t="n">
-        <v>0.2571593149041637</v>
+        <v>0.2592158058678059</v>
       </c>
     </row>
     <row r="87">
@@ -3852,7 +3856,7 @@
         </is>
       </c>
       <c r="C87" s="33" t="n">
-        <v>71734</v>
+        <v>71669</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3879,7 +3883,7 @@
         <v>5158</v>
       </c>
       <c r="J87" s="202" t="n">
-        <v>0.2255496339955474</v>
+        <v>0.225753565334111</v>
       </c>
     </row>
     <row r="88">
@@ -3889,7 +3893,7 @@
         </is>
       </c>
       <c r="C88" s="33" t="n">
-        <v>35719</v>
+        <v>35546</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3916,7 +3920,7 @@
         <v>2724</v>
       </c>
       <c r="J88" s="202" t="n">
-        <v>0.3575563979238173</v>
+        <v>0.3593006245428459</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
@@ -27263,31 +27267,31 @@
       <c r="C416" s="178" t="n"/>
       <c r="D416" s="175" t="inlineStr">
         <is>
-          <t>菱生(2369)</t>
+          <t>聯傑(3094)</t>
         </is>
       </c>
       <c r="E416" s="176" t="n">
-        <v>1893</v>
+        <v>1475</v>
       </c>
       <c r="F416" s="176" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G416" s="176" t="n">
-        <v>8177</v>
+        <v>6328</v>
       </c>
       <c r="H416" s="176" t="n">
-        <v>115</v>
+        <v>4</v>
       </c>
       <c r="I416" s="176" t="n">
-        <v>8062</v>
+        <v>6324</v>
       </c>
       <c r="J416" s="177" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="K416" s="177" t="n">
-        <v>42.74</v>
-      </c>
-      <c r="L416" s="219">
+        <v>43</v>
+      </c>
+      <c r="L416" s="220">
         <f>F416*(K416-J416)</f>
         <v/>
       </c>
@@ -27298,29 +27302,29 @@
       <c r="C417" s="178" t="n"/>
       <c r="D417" s="175" t="inlineStr">
         <is>
-          <t>聯傑(3094)</t>
+          <t>大亞(1609)</t>
         </is>
       </c>
       <c r="E417" s="176" t="n">
-        <v>1475</v>
+        <v>1012</v>
       </c>
       <c r="F417" s="176" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G417" s="176" t="n">
-        <v>6328</v>
+        <v>4427</v>
       </c>
       <c r="H417" s="176" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="I417" s="176" t="n">
-        <v>6324</v>
+        <v>4395</v>
       </c>
       <c r="J417" s="177" t="n">
-        <v>42.9</v>
+        <v>43.75</v>
       </c>
       <c r="K417" s="177" t="n">
-        <v>43</v>
+        <v>45.86</v>
       </c>
       <c r="L417" s="220">
         <f>F417*(K417-J417)</f>
@@ -27333,31 +27337,31 @@
       <c r="C418" s="178" t="n"/>
       <c r="D418" s="175" t="inlineStr">
         <is>
-          <t>大亞(1609)</t>
+          <t>長榮航太(2645)</t>
         </is>
       </c>
       <c r="E418" s="176" t="n">
-        <v>1012</v>
+        <v>63</v>
       </c>
       <c r="F418" s="176" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G418" s="176" t="n">
-        <v>4427</v>
+        <v>1489</v>
       </c>
       <c r="H418" s="176" t="n">
-        <v>32</v>
+        <v>635</v>
       </c>
       <c r="I418" s="176" t="n">
-        <v>4395</v>
+        <v>854</v>
       </c>
       <c r="J418" s="177" t="n">
-        <v>43.75</v>
+        <v>236.33</v>
       </c>
       <c r="K418" s="177" t="n">
-        <v>45.86</v>
-      </c>
-      <c r="L418" s="220">
+        <v>235.3</v>
+      </c>
+      <c r="L418" s="219">
         <f>F418*(K418-J418)</f>
         <v/>
       </c>
@@ -27609,29 +27613,29 @@
       <c r="C425" s="178" t="n"/>
       <c r="D425" s="175" t="inlineStr">
         <is>
-          <t>映泰(2399)</t>
+          <t>廣閎科(6693)</t>
         </is>
       </c>
       <c r="E425" s="176" t="n">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="F425" s="176" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G425" s="176" t="n">
-        <v>869</v>
+        <v>836</v>
       </c>
       <c r="H425" s="176" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="I425" s="176" t="n">
-        <v>721</v>
+        <v>836</v>
       </c>
       <c r="J425" s="177" t="n">
-        <v>55</v>
+        <v>278.8</v>
       </c>
       <c r="K425" s="177" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L425" s="220">
         <f>F425*(K425-J425)</f>
@@ -27642,46 +27646,25 @@
       <c r="A426" s="178" t="n"/>
       <c r="B426" s="178" t="n"/>
       <c r="C426" s="178" t="n"/>
-      <c r="D426" s="175" t="inlineStr">
-        <is>
-          <t>廣閎科(6693)</t>
-        </is>
-      </c>
-      <c r="E426" s="176" t="n">
-        <v>30</v>
-      </c>
-      <c r="F426" s="176" t="n">
-        <v>0</v>
-      </c>
-      <c r="G426" s="176" t="n">
-        <v>836</v>
-      </c>
-      <c r="H426" s="176" t="n">
-        <v>0</v>
-      </c>
-      <c r="I426" s="176" t="n">
-        <v>836</v>
-      </c>
-      <c r="J426" s="177" t="n">
-        <v>278.8</v>
-      </c>
-      <c r="K426" s="177" t="n">
-        <v>0</v>
-      </c>
-      <c r="L426" s="220">
-        <f>F426*(K426-J426)</f>
-        <v/>
-      </c>
+      <c r="D426" s="180" t="inlineStr">
+        <is>
+          <t>⚪ 今日漲停僅 6 檔</t>
+        </is>
+      </c>
+      <c r="E426" s="176" t="n"/>
+      <c r="F426" s="176" t="n"/>
+      <c r="G426" s="176" t="n"/>
+      <c r="H426" s="176" t="n"/>
+      <c r="I426" s="176" t="n"/>
+      <c r="J426" s="177" t="n"/>
+      <c r="K426" s="177" t="n"/>
+      <c r="L426" s="221" t="n"/>
     </row>
     <row r="427" ht="16.5" customHeight="1">
       <c r="A427" s="178" t="n"/>
       <c r="B427" s="178" t="n"/>
       <c r="C427" s="178" t="n"/>
-      <c r="D427" s="180" t="inlineStr">
-        <is>
-          <t>⚪ 今日漲停僅 7 檔</t>
-        </is>
-      </c>
+      <c r="D427" s="175" t="n"/>
       <c r="E427" s="176" t="n"/>
       <c r="F427" s="176" t="n"/>
       <c r="G427" s="176" t="n"/>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -1613,7 +1613,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 📌 一般共識 2330 / 2383 / 2308 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 除權息 22 檔: 00946, 00953B, 00985B ... | 明日恐處置 8 檔: 2466/3026/3167...  |  訊號: 強偏多 (Q5 95%, hot=19)</t>
+          <t>💡 📌 一般共識 2330 / 2383 / 2308 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 明日恐處置 8 檔: 2466/3026/3167...  |  訊號: 強偏多 (Q5 95%, hot=19)</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G34" s="244" t="n">
-        <v>-173.97844</v>
+        <v>-173.99525</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
@@ -2602,8 +2602,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G35" s="248" t="n">
-        <v>0.1881211267889168</v>
+      <c r="G35" s="247" t="n">
+        <v>0.1877312504931147</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -2614,7 +2614,7 @@
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="28" t="inlineStr">
         <is>
-          <t>✅ 過去 30 天 P/C 命中率: 偏多 18/27 (67%) | 偏空 0/0 (0%) | 整體 18/27 (67%)</t>
+          <t>✅ 過去 30 天 P/C 命中率: 偏多 18/28 (64%) | 偏空 0/0 (0%) | 整體 18/28 (64%)</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="D41" s="33" t="n">
-        <v>1153606</v>
+        <v>1154176</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="D43" s="33" t="n">
-        <v>460109</v>
+        <v>460978</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="D45" s="33" t="n">
-        <v>318384</v>
+        <v>318848</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>張濬安(航海王)</t>
         </is>
       </c>
       <c r="D51" s="41" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="E51" s="41" t="inlineStr">
         <is>
-          <t>林滄海 今日買進 12 檔新標的 (過去從沒買過)</t>
+          <t>張濬安(航海王) 今日買進 12 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F51" s="41" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>張濬安(航海王)</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>張濬安(航海王) 今日買進 11 檔新標的 (過去從沒買過)</t>
+          <t>林滄海 今日買進 12 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>11 檔</t>
+          <t>12 檔</t>
         </is>
       </c>
     </row>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E53" s="41" t="inlineStr">
         <is>
-          <t>迷你哥/松山哥 今日買進 8 檔新標的 (過去從沒買過)</t>
+          <t>迷你哥/松山哥 今日買進 9 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F53" s="41" t="inlineStr">
         <is>
-          <t>8 檔</t>
+          <t>9 檔</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tradow</t>
+          <t>民哥</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tradow 今日買進 7 檔新標的 (過去從沒買過)</t>
+          <t>民哥 今日買進 8 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>7 檔</t>
+          <t>8 檔</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C55" s="41" t="inlineStr">
         <is>
-          <t>巨人傑</t>
+          <t>Tradow</t>
         </is>
       </c>
       <c r="D55" s="41" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="E55" s="41" t="inlineStr">
         <is>
-          <t>巨人傑 今日買進 7 檔新標的 (過去從沒買過)</t>
+          <t>Tradow 今日買進 7 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F55" s="41" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>民哥</t>
+          <t>巨人傑</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>民哥 今日買進 7 檔新標的 (過去從沒買過)</t>
+          <t>巨人傑 今日買進 7 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="E57" s="41" t="inlineStr">
         <is>
-          <t>強森 今日買進 6 檔新標的 (過去從沒買過)</t>
+          <t>強森 今日買進 7 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F57" s="41" t="inlineStr">
         <is>
-          <t>6 檔</t>
+          <t>7 檔</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="C76" s="33" t="n">
-        <v>1043502</v>
+        <v>1044072</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>42623</v>
       </c>
       <c r="J76" s="202" t="n">
-        <v>0.2479012739888113</v>
+        <v>0.2477659349387844</v>
       </c>
     </row>
     <row r="77">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="C78" s="33" t="n">
-        <v>457359</v>
+        <v>458228</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>38253</v>
       </c>
       <c r="J78" s="202" t="n">
-        <v>0.3990277657218434</v>
+        <v>0.3982710350024518</v>
       </c>
     </row>
     <row r="79">
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="C80" s="33" t="n">
-        <v>294055</v>
+        <v>294519</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>15058</v>
       </c>
       <c r="J80" s="202" t="n">
-        <v>0.2143051955515865</v>
+        <v>0.2139676415094019</v>
       </c>
     </row>
     <row r="81">
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="C81" s="33" t="n">
-        <v>234766</v>
+        <v>235161</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>14181</v>
       </c>
       <c r="J81" s="202" t="n">
-        <v>0.183680380292759</v>
+        <v>0.1833723208237424</v>
       </c>
     </row>
     <row r="82">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C82" s="33" t="n">
-        <v>175726</v>
+        <v>175971</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>13013</v>
       </c>
       <c r="J82" s="202" t="n">
-        <v>0.292801959418548</v>
+        <v>0.2923942976838176</v>
       </c>
     </row>
     <row r="83">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="C83" s="33" t="n">
-        <v>155270</v>
+        <v>155290</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>9585</v>
       </c>
       <c r="J83" s="202" t="n">
-        <v>0.2587864857084157</v>
+        <v>0.2587519898203623</v>
       </c>
     </row>
     <row r="84">
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="C86" s="33" t="n">
-        <v>75091</v>
+        <v>75692</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>5286</v>
       </c>
       <c r="J86" s="202" t="n">
-        <v>0.2592158058678059</v>
+        <v>0.2571593149041637</v>
       </c>
     </row>
     <row r="87">
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="C87" s="33" t="n">
-        <v>71669</v>
+        <v>71734</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>5158</v>
       </c>
       <c r="J87" s="202" t="n">
-        <v>0.225753565334111</v>
+        <v>0.2255496339955474</v>
       </c>
     </row>
     <row r="88">
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="C88" s="33" t="n">
-        <v>35546</v>
+        <v>35719</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3920,13 +3920,13 @@
         <v>2724</v>
       </c>
       <c r="J88" s="202" t="n">
-        <v>0.3593006245428459</v>
+        <v>0.3575563979238173</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="B90" s="59" t="inlineStr">
         <is>
-          <t>▍ G. 注意股 (資料日 20260706)</t>
+          <t>▍ G. 注意股 (資料日 20260707)</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="B112" s="65" t="inlineStr">
         <is>
-          <t>▍ I. 未來 30 天除權息 (有效 270 檔, 已剔除過期)</t>
+          <t>▍ I. 未來 30 天除權息 (有效 260 檔, 已剔除過期)</t>
         </is>
       </c>
     </row>
@@ -4364,17 +4364,17 @@
     <row r="114">
       <c r="B114" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>00946</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>群益科技高息成長</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4383,23 +4383,23 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0.058</v>
+        <v>1.347149</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="41" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="C115" s="41" t="inlineStr">
         <is>
-          <t>00953B</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="D115" s="41" t="inlineStr">
         <is>
-          <t>群益優選非投等債</t>
+          <t>圓剛</t>
         </is>
       </c>
       <c r="E115" s="41" t="inlineStr">
@@ -4408,23 +4408,23 @@
         </is>
       </c>
       <c r="F115" s="41" t="n">
-        <v>0.061</v>
+        <v>0.250119</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>00985B</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>群益ESG投等債0-5</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4433,23 +4433,23 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0.048</v>
+        <v>24.500215</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="41" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="C117" s="41" t="inlineStr">
         <is>
-          <t>00997A</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="D117" s="41" t="inlineStr">
         <is>
-          <t>主動群益美國增長</t>
+          <t>宏普</t>
         </is>
       </c>
       <c r="E117" s="41" t="inlineStr">
@@ -4458,23 +4458,23 @@
         </is>
       </c>
       <c r="F117" s="41" t="n">
-        <v>0.37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>益登</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4483,23 +4483,23 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="41" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="C119" s="41" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="D119" s="41" t="inlineStr">
         <is>
-          <t>震旦行</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="E119" s="41" t="inlineStr">
@@ -4508,23 +4508,23 @@
         </is>
       </c>
       <c r="F119" s="41" t="n">
-        <v>3.7</v>
+        <v>4.249688</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4533,23 +4533,23 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>7.113868</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="41" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="C121" s="41" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="D121" s="41" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="E121" s="41" t="inlineStr">
@@ -4558,23 +4558,23 @@
         </is>
       </c>
       <c r="F121" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
       <c r="B122" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>匯僑</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4583,23 +4583,23 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="B123" s="41" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="C123" s="41" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="D123" s="41" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>潤泰新</t>
         </is>
       </c>
       <c r="E123" s="41" t="inlineStr">
@@ -4608,48 +4608,48 @@
         </is>
       </c>
       <c r="F123" s="41" t="n">
-        <v>1.980153</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="124">
       <c r="B124" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>嘉威</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>息</t>
+          <t>權息</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0.3</v>
+        <v>1.801172</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" s="41" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="C125" s="41" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="D125" s="41" t="inlineStr">
         <is>
-          <t>合勤控</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="E125" s="41" t="inlineStr">
@@ -4658,23 +4658,23 @@
         </is>
       </c>
       <c r="F125" s="41" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>東明-KY</t>
+          <t>威致</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4683,23 +4683,23 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" s="41" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="C127" s="41" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="D127" s="41" t="inlineStr">
         <is>
-          <t>鈞寶</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="E127" s="41" t="inlineStr">
@@ -4708,23 +4708,23 @@
         </is>
       </c>
       <c r="F127" s="41" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3.5</v>
+        <v>2.608082</v>
       </c>
     </row>
   </sheetData>
@@ -5034,9 +5034,9 @@
       </c>
     </row>
     <row r="30">
-      <c r="C30" s="69" t="inlineStr">
-        <is>
-          <t>除權息 22 檔 (00946 / 00953B / 00985B ...)</t>
+      <c r="C30" s="71" t="inlineStr">
+        <is>
+          <t>今日無除權息</t>
         </is>
       </c>
     </row>
@@ -11090,7 +11090,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="B3" s="98" t="inlineStr">
         <is>
-          <t>大牌分析師 近 53/53 交易日出手 2561 次 (532 檔), 風格分布: 隔日沖近似 39% / 當沖 13% / 留倉 48%, 漲停命中 4% (其中 🔒鎖漲停 4%), 前 5 大集中 24%, 長線部位 62% (38 檔), ⚠️ 處置股部位 12% (36 檔), 📦 連續囤貨 29 檔 (最長 13 天 009816, 皆已停止)。 主軸: 高頻交易/持續進場/📦 連續囤貨。</t>
+          <t>大牌分析師 近 53/53 交易日出手 2561 次 (532 檔), 風格分布: 隔日沖近似 39% / 當沖 13% / 留倉 48%, 漲停命中 4% (其中 🔒鎖漲停 4%), 前 5 大集中 24%, 長線部位 62% (38 檔), ⚠️ 處置股部位 11% (34 檔), 📦 連續囤貨 29 檔 (最長 13 天 009816, 皆已停止)。 主軸: 高頻交易/持續進場/📦 連續囤貨。</t>
         </is>
       </c>
     </row>
@@ -27267,31 +27267,31 @@
       <c r="C416" s="178" t="n"/>
       <c r="D416" s="175" t="inlineStr">
         <is>
-          <t>聯傑(3094)</t>
+          <t>菱生(2369)</t>
         </is>
       </c>
       <c r="E416" s="176" t="n">
-        <v>1475</v>
+        <v>1893</v>
       </c>
       <c r="F416" s="176" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G416" s="176" t="n">
-        <v>6328</v>
+        <v>8177</v>
       </c>
       <c r="H416" s="176" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="I416" s="176" t="n">
-        <v>6324</v>
+        <v>8062</v>
       </c>
       <c r="J416" s="177" t="n">
-        <v>42.9</v>
+        <v>43.2</v>
       </c>
       <c r="K416" s="177" t="n">
-        <v>43</v>
-      </c>
-      <c r="L416" s="220">
+        <v>42.74</v>
+      </c>
+      <c r="L416" s="219">
         <f>F416*(K416-J416)</f>
         <v/>
       </c>
@@ -27302,29 +27302,29 @@
       <c r="C417" s="178" t="n"/>
       <c r="D417" s="175" t="inlineStr">
         <is>
-          <t>大亞(1609)</t>
+          <t>聯傑(3094)</t>
         </is>
       </c>
       <c r="E417" s="176" t="n">
-        <v>1012</v>
+        <v>1475</v>
       </c>
       <c r="F417" s="176" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G417" s="176" t="n">
-        <v>4427</v>
+        <v>6328</v>
       </c>
       <c r="H417" s="176" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="I417" s="176" t="n">
-        <v>4395</v>
+        <v>6324</v>
       </c>
       <c r="J417" s="177" t="n">
-        <v>43.75</v>
+        <v>42.9</v>
       </c>
       <c r="K417" s="177" t="n">
-        <v>45.86</v>
+        <v>43</v>
       </c>
       <c r="L417" s="220">
         <f>F417*(K417-J417)</f>
@@ -27337,31 +27337,31 @@
       <c r="C418" s="178" t="n"/>
       <c r="D418" s="175" t="inlineStr">
         <is>
-          <t>長榮航太(2645)</t>
+          <t>大亞(1609)</t>
         </is>
       </c>
       <c r="E418" s="176" t="n">
-        <v>63</v>
+        <v>1012</v>
       </c>
       <c r="F418" s="176" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G418" s="176" t="n">
-        <v>1489</v>
+        <v>4427</v>
       </c>
       <c r="H418" s="176" t="n">
-        <v>635</v>
+        <v>32</v>
       </c>
       <c r="I418" s="176" t="n">
-        <v>854</v>
+        <v>4395</v>
       </c>
       <c r="J418" s="177" t="n">
-        <v>236.33</v>
+        <v>43.75</v>
       </c>
       <c r="K418" s="177" t="n">
-        <v>235.3</v>
-      </c>
-      <c r="L418" s="219">
+        <v>45.86</v>
+      </c>
+      <c r="L418" s="220">
         <f>F418*(K418-J418)</f>
         <v/>
       </c>
@@ -27613,29 +27613,29 @@
       <c r="C425" s="178" t="n"/>
       <c r="D425" s="175" t="inlineStr">
         <is>
-          <t>廣閎科(6693)</t>
+          <t>映泰(2399)</t>
         </is>
       </c>
       <c r="E425" s="176" t="n">
-        <v>30</v>
+        <v>158</v>
       </c>
       <c r="F425" s="176" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G425" s="176" t="n">
-        <v>836</v>
+        <v>869</v>
       </c>
       <c r="H425" s="176" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="I425" s="176" t="n">
-        <v>836</v>
+        <v>721</v>
       </c>
       <c r="J425" s="177" t="n">
-        <v>278.8</v>
+        <v>55</v>
       </c>
       <c r="K425" s="177" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L425" s="220">
         <f>F425*(K425-J425)</f>
@@ -27646,25 +27646,46 @@
       <c r="A426" s="178" t="n"/>
       <c r="B426" s="178" t="n"/>
       <c r="C426" s="178" t="n"/>
-      <c r="D426" s="180" t="inlineStr">
-        <is>
-          <t>⚪ 今日漲停僅 6 檔</t>
-        </is>
-      </c>
-      <c r="E426" s="176" t="n"/>
-      <c r="F426" s="176" t="n"/>
-      <c r="G426" s="176" t="n"/>
-      <c r="H426" s="176" t="n"/>
-      <c r="I426" s="176" t="n"/>
-      <c r="J426" s="177" t="n"/>
-      <c r="K426" s="177" t="n"/>
-      <c r="L426" s="221" t="n"/>
+      <c r="D426" s="175" t="inlineStr">
+        <is>
+          <t>廣閎科(6693)</t>
+        </is>
+      </c>
+      <c r="E426" s="176" t="n">
+        <v>30</v>
+      </c>
+      <c r="F426" s="176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G426" s="176" t="n">
+        <v>836</v>
+      </c>
+      <c r="H426" s="176" t="n">
+        <v>0</v>
+      </c>
+      <c r="I426" s="176" t="n">
+        <v>836</v>
+      </c>
+      <c r="J426" s="177" t="n">
+        <v>278.8</v>
+      </c>
+      <c r="K426" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L426" s="220">
+        <f>F426*(K426-J426)</f>
+        <v/>
+      </c>
     </row>
     <row r="427" ht="16.5" customHeight="1">
       <c r="A427" s="178" t="n"/>
       <c r="B427" s="178" t="n"/>
       <c r="C427" s="178" t="n"/>
-      <c r="D427" s="175" t="n"/>
+      <c r="D427" s="180" t="inlineStr">
+        <is>
+          <t>⚪ 今日漲停僅 7 檔</t>
+        </is>
+      </c>
       <c r="E427" s="176" t="n"/>
       <c r="F427" s="176" t="n"/>
       <c r="G427" s="176" t="n"/>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -1656,7 +1656,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 🎯 quad 進場 (78.9% alpha): 2308 / 6770 / 2330 +6  |  避開 — 除權息 7 檔: 1465, 1527, 2367 ... | 明日恐處置 6 檔: 3374/4542/4556...  |  訊號: 強偏多 (Q5 81.7%, hot=21)</t>
+          <t>💡 🎯 quad 進場 (78.9% alpha): 2308 / 6770 / 2330 +6  |  避開 — 除權息 7 檔: 1465, 1527, 2367 ... | 明日恐處置 1 檔: 3362  |  訊號: 強偏多 (Q5 81.7%, hot=21)</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
     <row r="37">
       <c r="C37" s="71" t="inlineStr">
         <is>
-          <t>明日恐處置 6 檔 (3374 / 4542 / 4556 ...)</t>
+          <t>明日恐處置 1 檔 (3362)</t>
         </is>
       </c>
     </row>
@@ -30436,7 +30436,7 @@
     <row r="485" ht="16.5" customHeight="1">
       <c r="A485" s="204" t="inlineStr">
         <is>
-          <t>ⓘ histock top-buyer 資料 fetched @ 2026-08-03 21:34 TW | 0/23 success</t>
+          <t>ⓘ histock top-buyer 資料 fetched @ 2026-08-03 22:55 TW | 0/23 success</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -21,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨-64/5d-140)&quot;;-0&quot; 億 (昨-64/5d-140)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +122億 &quot;&quot;(昨5/5d9)&quot;"/>
@@ -35,6 +35,8 @@
     <numFmt numFmtId="174" formatCode="0.0&quot;%&quot;"/>
     <numFmt numFmtId="175" formatCode="0&quot;%&quot;"/>
     <numFmt numFmtId="176" formatCode="#,##0.00;-#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="0&quot; 檔 +120億 &quot;&quot;(昨5/5d9)&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0%&quot; 市-960億 &quot;&quot;(昨15/5d16)&quot;"/>
   </numFmts>
   <fonts count="53">
     <font>
@@ -341,7 +343,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="49">
+  <fills count="50">
     <fill>
       <patternFill/>
     </fill>
@@ -585,6 +587,12 @@
         <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -598,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1145,6 +1153,24 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1230,12 +1256,12 @@
     <comment ref="D19" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「張濬安(航海王)」獨佔比 83.1%
+領頭大戶「張濬安(航海王)」獨佔比 84.0%
   • 領頭金額 104,611 萬
-  • 合計淨買 125,848 萬
+  • 合計淨買 124,595 萬
   • 大戶數 12 位 (名義共識)
 判讀: 名義 12 位大戶共識,
-實質 1 人下注佔 83%,
+實質 1 人下注佔 84%,
 剩餘 11 位為陪襯小單,
 真共識訊號被稀釋.</t>
       </text>
@@ -1243,9 +1269,9 @@
     <comment ref="D20" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「陳族元」獨佔比 56.8%
-  • 領頭金額 55,828 萬
-  • 合計淨買 98,358 萬
+領頭大戶「陳族元」獨佔比 56.7%
+  • 領頭金額 55,645 萬
+  • 合計淨買 98,174 萬
   • 大戶數 13 位 (名義共識)
 判讀: 名義 13 位大戶共識,
 實質 1 人下注佔 57%,
@@ -1269,12 +1295,12 @@
     <comment ref="D22" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「陳族元」獨佔比 57.9%
-  • 領頭金額 24,657 萬
-  • 合計淨買 42,552 萬
+領頭大戶「陳族元」獨佔比 58.8%
+  • 領頭金額 25,491 萬
+  • 合計淨買 43,385 萬
   • 大戶數 11 位 (名義共識)
 判讀: 名義 11 位大戶共識,
-實質 1 人下注佔 58%,
+實質 1 人下注佔 59%,
 剩餘 10 位為陪襯小單,
 真共識訊號被稀釋.</t>
       </text>
@@ -1295,12 +1321,12 @@
     <comment ref="D24" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「陳律師」獨佔比 53.6%
+領頭大戶「陳律師」獨佔比 56.6%
   • 領頭金額 15,283 萬
-  • 合計淨買 28,538 萬
+  • 合計淨買 27,020 萬
   • 大戶數 12 位 (名義共識)
 判讀: 名義 12 位大戶共識,
-實質 1 人下注佔 54%,
+實質 1 人下注佔 57%,
 剩餘 11 位為陪襯小單,
 真共識訊號被稀釋.</t>
       </text>
@@ -1816,7 +1842,7 @@
         </is>
       </c>
       <c r="H16" s="17" t="n">
-        <v>193024</v>
+        <v>175305</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1838,7 +1864,7 @@
         <v>9</v>
       </c>
       <c r="N16" s="17" t="n">
-        <v>441946</v>
+        <v>424227</v>
       </c>
     </row>
     <row r="17">
@@ -1867,7 +1893,7 @@
         </is>
       </c>
       <c r="H17" s="17" t="n">
-        <v>85501</v>
+        <v>85215</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1889,7 +1915,7 @@
         <v>9</v>
       </c>
       <c r="N17" s="17" t="n">
-        <v>193870</v>
+        <v>193584</v>
       </c>
     </row>
     <row r="18">
@@ -1926,7 +1952,7 @@
         </is>
       </c>
       <c r="J18" s="18" t="n">
-        <v>52121</v>
+        <v>53420</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1940,7 +1966,7 @@
         <v>10</v>
       </c>
       <c r="N18" s="17" t="n">
-        <v>184850</v>
+        <v>186148</v>
       </c>
     </row>
     <row r="19">
@@ -1981,17 +2007,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="L19" s="18" t="n">
-        <v>3583</v>
+        <v>3049</v>
       </c>
       <c r="M19" s="19" t="n">
         <v>9</v>
       </c>
       <c r="N19" s="17" t="n">
-        <v>125848</v>
+        <v>124595</v>
       </c>
     </row>
     <row r="20">
@@ -2020,7 +2046,7 @@
         </is>
       </c>
       <c r="H20" s="17" t="n">
-        <v>55829</v>
+        <v>55645</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2042,7 +2068,7 @@
         <v>10</v>
       </c>
       <c r="N20" s="17" t="n">
-        <v>98358</v>
+        <v>98174</v>
       </c>
     </row>
     <row r="21">
@@ -2114,7 +2140,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
@@ -2122,7 +2148,7 @@
         </is>
       </c>
       <c r="H22" s="17" t="n">
-        <v>24658</v>
+        <v>25491</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2144,7 +2170,7 @@
         <v>8</v>
       </c>
       <c r="N22" s="17" t="n">
-        <v>42552</v>
+        <v>43386</v>
       </c>
     </row>
     <row r="23">
@@ -2236,17 +2262,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>張濬安</t>
         </is>
       </c>
       <c r="L24" s="18" t="n">
-        <v>2399</v>
+        <v>1747</v>
       </c>
       <c r="M24" s="19" t="n">
         <v>9</v>
       </c>
       <c r="N24" s="17" t="n">
-        <v>28538</v>
+        <v>27020</v>
       </c>
     </row>
     <row r="25">
@@ -2322,7 +2348,7 @@
         </is>
       </c>
       <c r="G28" s="208" t="n">
-        <v>123.7623</v>
+        <v>121.3232</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
@@ -2331,7 +2357,7 @@
           <t>Q3 強共識股</t>
         </is>
       </c>
-      <c r="C29" s="209" t="n">
+      <c r="C29" s="238" t="n">
         <v>10</v>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -2339,8 +2365,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G29" s="210" t="n">
-        <v>0.2294531048392597</v>
+      <c r="G29" s="239" t="n">
+        <v>0.2281411777835858</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
@@ -2419,11 +2445,11 @@
         </is>
       </c>
       <c r="D35" s="33" t="n">
-        <v>1633313</v>
+        <v>1589585</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2435,7 +2461,7 @@
         </is>
       </c>
       <c r="H35" s="33" t="n">
-        <v>441946</v>
+        <v>424227</v>
       </c>
       <c r="I35" s="212" t="n">
         <v>-0.0227</v>
@@ -2455,7 +2481,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2487,7 +2513,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2499,7 +2525,7 @@
         </is>
       </c>
       <c r="H37" s="33" t="n">
-        <v>231618</v>
+        <v>231704</v>
       </c>
       <c r="I37" s="213" t="n">
         <v>0.0495</v>
@@ -2519,7 +2545,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2531,7 +2557,7 @@
         </is>
       </c>
       <c r="H38" s="33" t="n">
-        <v>193870</v>
+        <v>193584</v>
       </c>
       <c r="I38" s="213" t="n">
         <v>0.0345</v>
@@ -2551,7 +2577,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2563,7 +2589,7 @@
         </is>
       </c>
       <c r="H39" s="33" t="n">
-        <v>184850</v>
+        <v>186148</v>
       </c>
       <c r="I39" s="212" t="n">
         <v>-0.0248</v>
@@ -2979,11 +3005,11 @@
         <v>48</v>
       </c>
       <c r="E60" t="n">
-        <v>5512941</v>
+        <v>5495856</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>陳族元 連續 48 天加碼 2330 (累計 5,512,941 萬)</t>
+          <t>陳族元 連續 48 天加碼 2330 (累計 5,495,856 萬)</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3166,7 @@
         </is>
       </c>
       <c r="C68" s="33" t="n">
-        <v>1490209</v>
+        <v>1448081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3148,7 +3174,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>200755</v>
+        <v>183670</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3164,10 +3190,10 @@
         </is>
       </c>
       <c r="I68" s="33" t="n">
-        <v>127764</v>
+        <v>127776</v>
       </c>
       <c r="J68" s="214" t="n">
-        <v>0.3132101774207987</v>
+        <v>0.3105319337520347</v>
       </c>
     </row>
     <row r="69">
@@ -5074,7 +5100,7 @@
     <row r="40" ht="22" customHeight="1">
       <c r="C40" s="75" t="inlineStr">
         <is>
-          <t>+124 億 淨買</t>
+          <t>+121 億 淨買</t>
         </is>
       </c>
     </row>
@@ -12240,7 +12266,7 @@
     <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="110" t="inlineStr">
         <is>
-          <t>⚠️ 本 Excel 無 top-buyer highlight — histock 資料仍是 T-1 (需等到當日盤後晚間 update, 23 次) | attempted=23, success=0</t>
+          <t>⚠️ 部分 top-buyer highlight 缺 (histock: 17/23 = 73% success | fetch_fail=6 stale=0 empty=0)</t>
         </is>
       </c>
       <c r="B1" s="111" t="n"/>
@@ -19431,29 +19457,29 @@
       </c>
       <c r="D190" s="137" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>致茂(2360)</t>
         </is>
       </c>
       <c r="E190" s="138" t="n">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="F190" s="138" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G190" s="138" t="n">
-        <v>19834</v>
+        <v>4080</v>
       </c>
       <c r="H190" s="138" t="n">
-        <v>876</v>
+        <v>3246</v>
       </c>
       <c r="I190" s="138" t="n">
-        <v>18958</v>
+        <v>834</v>
       </c>
       <c r="J190" s="139" t="n">
-        <v>2389.67</v>
+        <v>1942.62</v>
       </c>
       <c r="K190" s="139" t="n">
-        <v>2190.25</v>
+        <v>1909.41</v>
       </c>
       <c r="L190" s="236">
         <f>F190*(K190-J190)</f>
@@ -19466,31 +19492,31 @@
       <c r="C191" s="140" t="n"/>
       <c r="D191" s="137" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="E191" s="138" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F191" s="138" t="n">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G191" s="138" t="n">
-        <v>12447</v>
+        <v>3892</v>
       </c>
       <c r="H191" s="138" t="n">
-        <v>1912</v>
+        <v>1098</v>
       </c>
       <c r="I191" s="138" t="n">
-        <v>10535</v>
+        <v>2794</v>
       </c>
       <c r="J191" s="139" t="n">
-        <v>379.49</v>
+        <v>119.74</v>
       </c>
       <c r="K191" s="139" t="n">
-        <v>398.33</v>
-      </c>
-      <c r="L191" s="235">
+        <v>119.39</v>
+      </c>
+      <c r="L191" s="236">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -19501,29 +19527,29 @@
       <c r="C192" s="140" t="n"/>
       <c r="D192" s="137" t="inlineStr">
         <is>
-          <t>光寶科(2301)</t>
+          <t>台積電(2330)</t>
         </is>
       </c>
       <c r="E192" s="138" t="n">
-        <v>323</v>
+        <v>12</v>
       </c>
       <c r="F192" s="138" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G192" s="138" t="n">
-        <v>7413</v>
+        <v>2749</v>
       </c>
       <c r="H192" s="138" t="n">
-        <v>77</v>
+        <v>1510</v>
       </c>
       <c r="I192" s="138" t="n">
-        <v>7336</v>
+        <v>1239</v>
       </c>
       <c r="J192" s="139" t="n">
-        <v>229.5</v>
+        <v>2291.08</v>
       </c>
       <c r="K192" s="139" t="n">
-        <v>257</v>
+        <v>2517</v>
       </c>
       <c r="L192" s="235">
         <f>F192*(K192-J192)</f>
@@ -19536,29 +19562,29 @@
       <c r="C193" s="140" t="n"/>
       <c r="D193" s="137" t="inlineStr">
         <is>
-          <t>臻鼎-KY(4958)</t>
+          <t>台達電(2308)</t>
         </is>
       </c>
       <c r="E193" s="138" t="n">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="F193" s="138" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G193" s="138" t="n">
-        <v>3748</v>
+        <v>2672</v>
       </c>
       <c r="H193" s="138" t="n">
-        <v>1172</v>
+        <v>1617</v>
       </c>
       <c r="I193" s="138" t="n">
-        <v>2576</v>
+        <v>1055</v>
       </c>
       <c r="J193" s="139" t="n">
-        <v>430.8</v>
+        <v>1571.59</v>
       </c>
       <c r="K193" s="139" t="n">
-        <v>433.96</v>
+        <v>1617.3</v>
       </c>
       <c r="L193" s="235">
         <f>F193*(K193-J193)</f>
@@ -19571,31 +19597,31 @@
       <c r="C194" s="140" t="n"/>
       <c r="D194" s="137" t="inlineStr">
         <is>
-          <t>金像電(2368)</t>
+          <t>臻鼎-KY(4958)</t>
         </is>
       </c>
       <c r="E194" s="138" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="F194" s="138" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G194" s="138" t="n">
-        <v>3358</v>
+        <v>2445</v>
       </c>
       <c r="H194" s="138" t="n">
-        <v>87</v>
+        <v>1121</v>
       </c>
       <c r="I194" s="138" t="n">
-        <v>3271</v>
+        <v>1324</v>
       </c>
       <c r="J194" s="139" t="n">
-        <v>861</v>
+        <v>436.55</v>
       </c>
       <c r="K194" s="139" t="n">
-        <v>872</v>
-      </c>
-      <c r="L194" s="235">
+        <v>431.31</v>
+      </c>
+      <c r="L194" s="236">
         <f>F194*(K194-J194)</f>
         <v/>
       </c>
@@ -19606,29 +19632,29 @@
       <c r="C195" s="140" t="n"/>
       <c r="D195" s="137" t="inlineStr">
         <is>
-          <t>旺宏(2337)</t>
+          <t>穩懋(3105)</t>
         </is>
       </c>
       <c r="E195" s="138" t="n">
-        <v>238</v>
+        <v>76</v>
       </c>
       <c r="F195" s="138" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G195" s="138" t="n">
-        <v>2574</v>
+        <v>2383</v>
       </c>
       <c r="H195" s="138" t="n">
-        <v>351</v>
+        <v>1576</v>
       </c>
       <c r="I195" s="138" t="n">
-        <v>2223</v>
+        <v>807</v>
       </c>
       <c r="J195" s="139" t="n">
-        <v>108.13</v>
+        <v>313.61</v>
       </c>
       <c r="K195" s="139" t="n">
-        <v>109.59</v>
+        <v>315.12</v>
       </c>
       <c r="L195" s="235">
         <f>F195*(K195-J195)</f>
@@ -19641,31 +19667,31 @@
       <c r="C196" s="140" t="n"/>
       <c r="D196" s="137" t="inlineStr">
         <is>
-          <t>亞翔(6139)</t>
+          <t>南亞(1303)</t>
         </is>
       </c>
       <c r="E196" s="138" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="F196" s="138" t="n">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="G196" s="138" t="n">
-        <v>2266</v>
+        <v>1959</v>
       </c>
       <c r="H196" s="138" t="n">
-        <v>619</v>
+        <v>1466</v>
       </c>
       <c r="I196" s="138" t="n">
-        <v>1647</v>
+        <v>493</v>
       </c>
       <c r="J196" s="139" t="n">
-        <v>755.23</v>
+        <v>170.38</v>
       </c>
       <c r="K196" s="139" t="n">
-        <v>773.75</v>
-      </c>
-      <c r="L196" s="235">
+        <v>168.54</v>
+      </c>
+      <c r="L196" s="236">
         <f>F196*(K196-J196)</f>
         <v/>
       </c>
@@ -19676,29 +19702,29 @@
       <c r="C197" s="140" t="n"/>
       <c r="D197" s="137" t="inlineStr">
         <is>
-          <t>聯電(2303)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E197" s="138" t="n">
-        <v>191</v>
+        <v>430</v>
       </c>
       <c r="F197" s="138" t="n">
-        <v>64</v>
+        <v>275</v>
       </c>
       <c r="G197" s="138" t="n">
-        <v>2266</v>
+        <v>1939</v>
       </c>
       <c r="H197" s="138" t="n">
-        <v>771</v>
+        <v>1262</v>
       </c>
       <c r="I197" s="138" t="n">
-        <v>1495</v>
+        <v>677</v>
       </c>
       <c r="J197" s="139" t="n">
-        <v>118.62</v>
+        <v>45.09</v>
       </c>
       <c r="K197" s="139" t="n">
-        <v>120.5</v>
+        <v>45.9</v>
       </c>
       <c r="L197" s="235">
         <f>F197*(K197-J197)</f>
@@ -19711,29 +19737,29 @@
       <c r="C198" s="140" t="n"/>
       <c r="D198" s="137" t="inlineStr">
         <is>
-          <t>力積電(6770)</t>
+          <t>世芯-KY(3661)</t>
         </is>
       </c>
       <c r="E198" s="138" t="n">
-        <v>369</v>
+        <v>5</v>
       </c>
       <c r="F198" s="138" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G198" s="138" t="n">
-        <v>2023</v>
+        <v>1601</v>
       </c>
       <c r="H198" s="138" t="n">
-        <v>88</v>
+        <v>1290</v>
       </c>
       <c r="I198" s="138" t="n">
-        <v>1935</v>
+        <v>311</v>
       </c>
       <c r="J198" s="139" t="n">
-        <v>54.82</v>
+        <v>3201.2</v>
       </c>
       <c r="K198" s="139" t="n">
-        <v>55.19</v>
+        <v>3226.25</v>
       </c>
       <c r="L198" s="235">
         <f>F198*(K198-J198)</f>
@@ -19746,29 +19772,29 @@
       <c r="C199" s="140" t="n"/>
       <c r="D199" s="137" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>台光電(2383)</t>
         </is>
       </c>
       <c r="E199" s="138" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="F199" s="138" t="n">
         <v>1</v>
       </c>
       <c r="G199" s="138" t="n">
-        <v>1974</v>
+        <v>1572</v>
       </c>
       <c r="H199" s="138" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I199" s="138" t="n">
-        <v>1974</v>
+        <v>1552</v>
       </c>
       <c r="J199" s="139" t="n">
-        <v>205.66</v>
+        <v>5239</v>
       </c>
       <c r="K199" s="139" t="n">
-        <v>4</v>
+        <v>204</v>
       </c>
       <c r="L199" s="236">
         <f>F199*(K199-J199)</f>
@@ -30436,7 +30462,7 @@
     <row r="485" ht="16.5" customHeight="1">
       <c r="A485" s="204" t="inlineStr">
         <is>
-          <t>ⓘ histock top-buyer 資料 fetched @ 2026-08-03 22:55 TW | 0/23 success</t>
+          <t>ⓘ histock top-buyer 資料 fetched @ 2026-08-04 01:49 TW | 17/23 success</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -2273,8 +2273,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G28" s="248" t="n">
-        <v>0.1824037584120599</v>
+      <c r="G28" s="246" t="n">
+        <v>0.1827575179330782</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -30521,7 +30521,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-08-04 22:09 TW | 24/24 success | 來源: 富邦24/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-08-04 22:56 TW | 24/24 success | 來源: 富邦24/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -30521,7 +30521,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-08-04 22:56 TW | 24/24 success | 來源: 富邦24/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-08-05 00:02 TW | 24/24 success | 來源: 富邦24/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="19">
+  <numFmts count="20">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨-64/5d-140)&quot;;-0&quot; 億 (昨-64/5d-140)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +122億 &quot;&quot;(昨5/5d9)&quot;"/>
@@ -42,6 +42,7 @@
     <numFmt numFmtId="180" formatCode="0&quot; 檔 +78億 &quot;&quot;(昨10/5d9)&quot;"/>
     <numFmt numFmtId="181" formatCode="0.0%&quot; 市-1302億 &quot;&quot;(昨23/5d18)&quot;"/>
     <numFmt numFmtId="182" formatCode="0.0%&quot; 市-1297億 &quot;&quot;(昨23/5d18)&quot;"/>
+    <numFmt numFmtId="183" formatCode="0.0%&quot; 市-1301億 &quot;&quot;(昨23/5d18)&quot;"/>
   </numFmts>
   <fonts count="54">
     <font>
@@ -617,7 +618,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="250">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1195,6 +1196,9 @@
     <xf numFmtId="182" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="183" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2201,23 +2205,23 @@
         <v>10</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>293</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>陳律師</t>
         </is>
       </c>
-      <c r="H24" s="17" t="n">
+      <c r="J24" s="18" t="n">
         <v>272</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>陳族元</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="n">
-        <v>223</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2231,7 +2235,7 @@
         <v>7</v>
       </c>
       <c r="N24" s="17" t="n">
-        <v>1203</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -2256,7 +2260,7 @@
         </is>
       </c>
       <c r="G27" s="244" t="n">
-        <v>-90.55685</v>
+        <v>-89.31316</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
@@ -2273,8 +2277,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G28" s="246" t="n">
-        <v>0.1827575179330782</v>
+      <c r="G28" s="249" t="n">
+        <v>0.1832270153711584</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -2385,11 +2389,11 @@
         </is>
       </c>
       <c r="D35" s="33" t="n">
-        <v>1407222</v>
+        <v>1423998</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2421,7 +2425,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -3063,7 +3067,7 @@
         </is>
       </c>
       <c r="C66" s="33" t="n">
-        <v>1370793</v>
+        <v>1385934</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3079,7 +3083,7 @@
         </is>
       </c>
       <c r="G66" s="33" t="n">
-        <v>110105</v>
+        <v>118606</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3090,7 +3094,7 @@
         <v>97103</v>
       </c>
       <c r="J66" s="214" t="n">
-        <v>0.3376421531186692</v>
+        <v>0.3400869954532483</v>
       </c>
     </row>
     <row r="67">
@@ -5000,7 +5004,7 @@
     <row r="33" ht="22" customHeight="1">
       <c r="C33" s="247" t="inlineStr">
         <is>
-          <t>-91 億 淨買</t>
+          <t>-89 億 淨買</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19548,7 @@
         </is>
       </c>
       <c r="E191" s="138" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F191" s="138" t="n">
         <v>1</v>
@@ -19559,7 +19563,7 @@
         <v>12434</v>
       </c>
       <c r="J191" s="139" t="n">
-        <v>1019.34</v>
+        <v>1027.77</v>
       </c>
       <c r="K191" s="139" t="n">
         <v>25</v>
@@ -19614,10 +19618,10 @@
         </is>
       </c>
       <c r="E193" s="138" t="n">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F193" s="138" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G193" s="138" t="n">
         <v>10447</v>
@@ -19629,12 +19633,12 @@
         <v>4615</v>
       </c>
       <c r="J193" s="139" t="n">
-        <v>414.58</v>
+        <v>435.31</v>
       </c>
       <c r="K193" s="139" t="n">
-        <v>428.85</v>
-      </c>
-      <c r="L193" s="235">
+        <v>435.25</v>
+      </c>
+      <c r="L193" s="236">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -19645,31 +19649,31 @@
       <c r="C194" s="140" t="n"/>
       <c r="D194" s="137" t="inlineStr">
         <is>
-          <t>貿聯-KY(3665)</t>
+          <t>欣興(3037)</t>
         </is>
       </c>
       <c r="E194" s="138" t="n">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="F194" s="138" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G194" s="138" t="n">
-        <v>4752</v>
+        <v>8501</v>
       </c>
       <c r="H194" s="138" t="n">
-        <v>54</v>
+        <v>3049</v>
       </c>
       <c r="I194" s="138" t="n">
-        <v>4698</v>
+        <v>5452</v>
       </c>
       <c r="J194" s="139" t="n">
-        <v>2263.1</v>
+        <v>924</v>
       </c>
       <c r="K194" s="139" t="n">
-        <v>538</v>
-      </c>
-      <c r="L194" s="236">
+        <v>924</v>
+      </c>
+      <c r="L194" s="235">
         <f>F194*(K194-J194)</f>
         <v/>
       </c>
@@ -19680,29 +19684,29 @@
       <c r="C195" s="140" t="n"/>
       <c r="D195" s="137" t="inlineStr">
         <is>
-          <t>國巨*(2327)</t>
+          <t>貿聯-KY(3665)</t>
         </is>
       </c>
       <c r="E195" s="138" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="F195" s="138" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="G195" s="138" t="n">
-        <v>3676</v>
+        <v>4752</v>
       </c>
       <c r="H195" s="138" t="n">
-        <v>2996</v>
+        <v>54</v>
       </c>
       <c r="I195" s="138" t="n">
-        <v>680</v>
+        <v>4698</v>
       </c>
       <c r="J195" s="139" t="n">
-        <v>565.5700000000001</v>
+        <v>2263.1</v>
       </c>
       <c r="K195" s="139" t="n">
-        <v>565.1900000000001</v>
+        <v>538</v>
       </c>
       <c r="L195" s="236">
         <f>F195*(K195-J195)</f>
@@ -19715,31 +19719,31 @@
       <c r="C196" s="140" t="n"/>
       <c r="D196" s="137" t="inlineStr">
         <is>
-          <t>日月光投控(3711)</t>
+          <t>國巨*(2327)</t>
         </is>
       </c>
       <c r="E196" s="138" t="n">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="F196" s="138" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="G196" s="138" t="n">
-        <v>2813</v>
+        <v>3676</v>
       </c>
       <c r="H196" s="138" t="n">
-        <v>233</v>
+        <v>2996</v>
       </c>
       <c r="I196" s="138" t="n">
-        <v>2580</v>
+        <v>680</v>
       </c>
       <c r="J196" s="139" t="n">
-        <v>585.98</v>
+        <v>266.39</v>
       </c>
       <c r="K196" s="139" t="n">
-        <v>582</v>
-      </c>
-      <c r="L196" s="236">
+        <v>507.71</v>
+      </c>
+      <c r="L196" s="235">
         <f>F196*(K196-J196)</f>
         <v/>
       </c>
@@ -19750,29 +19754,29 @@
       <c r="C197" s="140" t="n"/>
       <c r="D197" s="137" t="inlineStr">
         <is>
-          <t>南亞(1303)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="E197" s="138" t="n">
-        <v>141</v>
+        <v>244</v>
       </c>
       <c r="F197" s="138" t="n">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="G197" s="138" t="n">
-        <v>2410</v>
+        <v>2891</v>
       </c>
       <c r="H197" s="138" t="n">
-        <v>1457</v>
+        <v>557</v>
       </c>
       <c r="I197" s="138" t="n">
-        <v>953</v>
+        <v>2334</v>
       </c>
       <c r="J197" s="139" t="n">
-        <v>170.89</v>
+        <v>118.5</v>
       </c>
       <c r="K197" s="139" t="n">
-        <v>171.36</v>
+        <v>118.51</v>
       </c>
       <c r="L197" s="235">
         <f>F197*(K197-J197)</f>
@@ -19785,31 +19789,31 @@
       <c r="C198" s="140" t="n"/>
       <c r="D198" s="137" t="inlineStr">
         <is>
-          <t>勤誠(8210)</t>
+          <t>日月光投控(3711)</t>
         </is>
       </c>
       <c r="E198" s="138" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F198" s="138" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G198" s="138" t="n">
-        <v>2256</v>
+        <v>2813</v>
       </c>
       <c r="H198" s="138" t="n">
-        <v>574</v>
+        <v>233</v>
       </c>
       <c r="I198" s="138" t="n">
-        <v>1682</v>
+        <v>2580</v>
       </c>
       <c r="J198" s="139" t="n">
-        <v>1127.9</v>
+        <v>585.98</v>
       </c>
       <c r="K198" s="139" t="n">
-        <v>1147.4</v>
-      </c>
-      <c r="L198" s="235">
+        <v>582</v>
+      </c>
+      <c r="L198" s="236">
         <f>F198*(K198-J198)</f>
         <v/>
       </c>
@@ -30521,7 +30525,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-08-05 00:02 TW | 24/24 success | 來源: 富邦24/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-08-05 00:46 TW | 24/24 success | 來源: 富邦24/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="20">
+  <numFmts count="21">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨-64/5d-140)&quot;;-0&quot; 億 (昨-64/5d-140)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +122億 &quot;&quot;(昨5/5d9)&quot;"/>
@@ -43,6 +43,7 @@
     <numFmt numFmtId="181" formatCode="0.0%&quot; 市-1302億 &quot;&quot;(昨23/5d18)&quot;"/>
     <numFmt numFmtId="182" formatCode="0.0%&quot; 市-1297億 &quot;&quot;(昨23/5d18)&quot;"/>
     <numFmt numFmtId="183" formatCode="0.0%&quot; 市-1301億 &quot;&quot;(昨23/5d18)&quot;"/>
+    <numFmt numFmtId="184" formatCode="0.0%&quot; 市-1295億 &quot;&quot;(昨23/5d18)&quot;"/>
   </numFmts>
   <fonts count="54">
     <font>
@@ -618,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="251">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1199,6 +1200,9 @@
     <xf numFmtId="183" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="184" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2260,7 +2264,7 @@
         </is>
       </c>
       <c r="G27" s="244" t="n">
-        <v>-89.31316</v>
+        <v>-89.41092999999999</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
@@ -2277,8 +2281,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G28" s="249" t="n">
-        <v>0.1832270153711584</v>
+      <c r="G28" s="250" t="n">
+        <v>0.1827521554957778</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -2357,7 +2361,7 @@
         </is>
       </c>
       <c r="D34" s="33" t="n">
-        <v>1453099</v>
+        <v>1452482</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2389,7 +2393,7 @@
         </is>
       </c>
       <c r="D35" s="33" t="n">
-        <v>1423998</v>
+        <v>1423818</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -3067,7 +3071,7 @@
         </is>
       </c>
       <c r="C66" s="33" t="n">
-        <v>1385934</v>
+        <v>1385755</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3094,7 +3098,7 @@
         <v>97103</v>
       </c>
       <c r="J66" s="214" t="n">
-        <v>0.3400869954532483</v>
+        <v>0.3401311213304923</v>
       </c>
     </row>
     <row r="67">
@@ -3104,7 +3108,7 @@
         </is>
       </c>
       <c r="C67" s="33" t="n">
-        <v>1231906</v>
+        <v>1231370</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3131,7 +3135,7 @@
         <v>69680</v>
       </c>
       <c r="J67" s="214" t="n">
-        <v>0.2423758990033248</v>
+        <v>0.2424814416011698</v>
       </c>
     </row>
     <row r="68">
@@ -3474,7 +3478,7 @@
         </is>
       </c>
       <c r="C77" s="33" t="n">
-        <v>38408</v>
+        <v>38131</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3501,7 +3505,7 @@
         <v>3386</v>
       </c>
       <c r="J77" s="214" t="n">
-        <v>0.3562154210656495</v>
+        <v>0.3588040302742622</v>
       </c>
     </row>
     <row r="78">
@@ -28128,33 +28132,33 @@
       <c r="A417" s="187" t="n"/>
       <c r="B417" s="187" t="n"/>
       <c r="C417" s="187" t="n"/>
-      <c r="D417" s="240" t="inlineStr">
-        <is>
-          <t>明遠精密(7704)</t>
-        </is>
-      </c>
-      <c r="E417" s="241" t="n">
-        <v>58</v>
-      </c>
-      <c r="F417" s="241" t="n">
+      <c r="D417" s="184" t="inlineStr">
+        <is>
+          <t>合晶(6182)</t>
+        </is>
+      </c>
+      <c r="E417" s="185" t="n">
+        <v>31</v>
+      </c>
+      <c r="F417" s="185" t="n">
+        <v>1</v>
+      </c>
+      <c r="G417" s="185" t="n">
+        <v>296</v>
+      </c>
+      <c r="H417" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="G417" s="241" t="n">
-        <v>353</v>
-      </c>
-      <c r="H417" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="I417" s="241" t="n">
-        <v>353</v>
-      </c>
-      <c r="J417" s="242" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="K417" s="242" t="n">
-        <v>0</v>
-      </c>
-      <c r="L417" s="243">
+      <c r="I417" s="185" t="n">
+        <v>296</v>
+      </c>
+      <c r="J417" s="186" t="n">
+        <v>95.52</v>
+      </c>
+      <c r="K417" s="186" t="n">
+        <v>5</v>
+      </c>
+      <c r="L417" s="236">
         <f>F417*(K417-J417)</f>
         <v/>
       </c>
@@ -28165,31 +28169,31 @@
       <c r="C418" s="187" t="n"/>
       <c r="D418" s="184" t="inlineStr">
         <is>
-          <t>合晶(6182)</t>
+          <t>閎康(3587)</t>
         </is>
       </c>
       <c r="E418" s="185" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F418" s="185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G418" s="185" t="n">
-        <v>296</v>
+        <v>252</v>
       </c>
       <c r="H418" s="185" t="n">
         <v>0</v>
       </c>
       <c r="I418" s="185" t="n">
-        <v>296</v>
+        <v>252</v>
       </c>
       <c r="J418" s="186" t="n">
-        <v>95.52</v>
+        <v>251.5</v>
       </c>
       <c r="K418" s="186" t="n">
-        <v>5</v>
-      </c>
-      <c r="L418" s="236">
+        <v>0</v>
+      </c>
+      <c r="L418" s="235">
         <f>F418*(K418-J418)</f>
         <v/>
       </c>
@@ -30525,7 +30529,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-08-05 00:46 TW | 24/24 success | 來源: 富邦24/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-08-05 01:43 TW | 23/23 success | 來源: 富邦23/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="G30" s="251" t="n">
-        <v>-187.38063</v>
+        <v>-187.36154</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="G31" s="253" t="n">
-        <v>0.1593232770364576</v>
+        <v>0.1593540390485123</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="D40" s="33" t="n">
-        <v>380258</v>
+        <v>380239</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="D41" s="33" t="n">
-        <v>375000</v>
+        <v>374969</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>陳律師</t>
+          <t>蔣承翰</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>陳律師 今日買進 6 檔新標的 (過去從沒買過)</t>
+          <t>蔣承翰 今日買進 5 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>6 檔</t>
+          <t>5 檔</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C49" s="41" t="inlineStr">
         <is>
-          <t>蔣承翰</t>
+          <t>陳律師</t>
         </is>
       </c>
       <c r="D49" s="41" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E49" s="41" t="inlineStr">
         <is>
-          <t>蔣承翰 今日買進 5 檔新標的 (過去從沒買過)</t>
+          <t>陳律師 今日買進 5 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F49" s="41" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>強森</t>
+          <t>Tradow</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>強森 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>Tradow 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>4 檔</t>
+          <t>3 檔</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>張濬安(航海王)</t>
         </is>
       </c>
       <c r="D51" s="41" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E51" s="41" t="inlineStr">
         <is>
-          <t>林滄海 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>張濬安(航海王) 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F51" s="41" t="inlineStr">
         <is>
-          <t>4 檔</t>
+          <t>3 檔</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>強森</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>強森 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>4 檔</t>
+          <t>3 檔</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="C53" s="41" t="inlineStr">
         <is>
-          <t>Tradow</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="D53" s="41" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="E53" s="41" t="inlineStr">
         <is>
-          <t>Tradow 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>林滄海 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F53" s="41" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>張濬安(航海王)</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>張濬安(航海王) 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="C70" s="33" t="n">
-        <v>310124</v>
+        <v>310105</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>16869</v>
       </c>
       <c r="J70" s="214" t="n">
-        <v>0.2019043344261217</v>
+        <v>0.2019167701262476</v>
       </c>
     </row>
     <row r="71">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="C71" s="33" t="n">
-        <v>280810</v>
+        <v>280769</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>20725</v>
       </c>
       <c r="J71" s="214" t="n">
-        <v>0.3446970277002737</v>
+        <v>0.344746749106917</v>
       </c>
     </row>
     <row r="72">
@@ -28263,31 +28263,31 @@
       <c r="C417" s="187" t="n"/>
       <c r="D417" s="240" t="inlineStr">
         <is>
-          <t>亞泰金屬(6727)</t>
+          <t>前鼎(4908)</t>
         </is>
       </c>
       <c r="E417" s="241" t="n">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="F417" s="241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G417" s="241" t="n">
-        <v>4233</v>
+        <v>2714</v>
       </c>
       <c r="H417" s="241" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I417" s="241" t="n">
-        <v>4224</v>
+        <v>2714</v>
       </c>
       <c r="J417" s="242" t="n">
-        <v>406.98</v>
+        <v>165.5</v>
       </c>
       <c r="K417" s="242" t="n">
-        <v>88</v>
-      </c>
-      <c r="L417" s="255">
+        <v>0</v>
+      </c>
+      <c r="L417" s="243">
         <f>F417*(K417-J417)</f>
         <v/>
       </c>
@@ -28296,33 +28296,33 @@
       <c r="A418" s="187" t="n"/>
       <c r="B418" s="187" t="n"/>
       <c r="C418" s="187" t="n"/>
-      <c r="D418" s="240" t="inlineStr">
-        <is>
-          <t>前鼎(4908)</t>
-        </is>
-      </c>
-      <c r="E418" s="241" t="n">
-        <v>164</v>
-      </c>
-      <c r="F418" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="G418" s="241" t="n">
-        <v>2714</v>
-      </c>
-      <c r="H418" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="I418" s="241" t="n">
-        <v>2714</v>
-      </c>
-      <c r="J418" s="242" t="n">
-        <v>165.5</v>
-      </c>
-      <c r="K418" s="242" t="n">
-        <v>0</v>
-      </c>
-      <c r="L418" s="243">
+      <c r="D418" s="184" t="inlineStr">
+        <is>
+          <t>聯亞(3081)</t>
+        </is>
+      </c>
+      <c r="E418" s="185" t="n">
+        <v>10</v>
+      </c>
+      <c r="F418" s="185" t="n">
+        <v>1</v>
+      </c>
+      <c r="G418" s="185" t="n">
+        <v>2168</v>
+      </c>
+      <c r="H418" s="185" t="n">
+        <v>231</v>
+      </c>
+      <c r="I418" s="185" t="n">
+        <v>1937</v>
+      </c>
+      <c r="J418" s="186" t="n">
+        <v>2167.6</v>
+      </c>
+      <c r="K418" s="186" t="n">
+        <v>2309</v>
+      </c>
+      <c r="L418" s="235">
         <f>F418*(K418-J418)</f>
         <v/>
       </c>
@@ -30574,7 +30574,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-08-05 21:40 TW | 19/19 success | 來源: 富邦19/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-08-05 22:57 TW | 18/18 success | 來源: 富邦18/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="G30" s="251" t="n">
-        <v>-187.36154</v>
+        <v>-187.38063</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="G31" s="253" t="n">
-        <v>0.1593540390485123</v>
+        <v>0.1590669231384998</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="D40" s="33" t="n">
-        <v>380239</v>
+        <v>380258</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="D41" s="33" t="n">
-        <v>374969</v>
+        <v>375000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>蔣承翰</t>
+          <t>陳律師</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>蔣承翰 今日買進 5 檔新標的 (過去從沒買過)</t>
+          <t>陳律師 今日買進 6 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>5 檔</t>
+          <t>6 檔</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C49" s="41" t="inlineStr">
         <is>
-          <t>陳律師</t>
+          <t>蔣承翰</t>
         </is>
       </c>
       <c r="D49" s="41" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E49" s="41" t="inlineStr">
         <is>
-          <t>陳律師 今日買進 5 檔新標的 (過去從沒買過)</t>
+          <t>蔣承翰 今日買進 5 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F49" s="41" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tradow</t>
+          <t>強森</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tradow 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>強森 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3 檔</t>
+          <t>4 檔</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>張濬安(航海王)</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="D51" s="41" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E51" s="41" t="inlineStr">
         <is>
-          <t>張濬安(航海王) 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>林滄海 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F51" s="41" t="inlineStr">
         <is>
-          <t>3 檔</t>
+          <t>4 檔</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>強森</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>強森 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>3 檔</t>
+          <t>4 檔</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="C53" s="41" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>Tradow</t>
         </is>
       </c>
       <c r="D53" s="41" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="E53" s="41" t="inlineStr">
         <is>
-          <t>林滄海 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>Tradow 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F53" s="41" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>張濬安(航海王)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>張濬安(航海王) 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="C70" s="33" t="n">
-        <v>310105</v>
+        <v>310124</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>16869</v>
       </c>
       <c r="J70" s="214" t="n">
-        <v>0.2019167701262476</v>
+        <v>0.2019043344261217</v>
       </c>
     </row>
     <row r="71">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="C71" s="33" t="n">
-        <v>280769</v>
+        <v>280810</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>20725</v>
       </c>
       <c r="J71" s="214" t="n">
-        <v>0.344746749106917</v>
+        <v>0.3446970277002737</v>
       </c>
     </row>
     <row r="72">
@@ -28263,31 +28263,31 @@
       <c r="C417" s="187" t="n"/>
       <c r="D417" s="240" t="inlineStr">
         <is>
-          <t>前鼎(4908)</t>
+          <t>亞泰金屬(6727)</t>
         </is>
       </c>
       <c r="E417" s="241" t="n">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="F417" s="241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G417" s="241" t="n">
-        <v>2714</v>
+        <v>4233</v>
       </c>
       <c r="H417" s="241" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I417" s="241" t="n">
-        <v>2714</v>
+        <v>4224</v>
       </c>
       <c r="J417" s="242" t="n">
-        <v>165.5</v>
+        <v>406.98</v>
       </c>
       <c r="K417" s="242" t="n">
-        <v>0</v>
-      </c>
-      <c r="L417" s="243">
+        <v>88</v>
+      </c>
+      <c r="L417" s="255">
         <f>F417*(K417-J417)</f>
         <v/>
       </c>
@@ -28296,33 +28296,33 @@
       <c r="A418" s="187" t="n"/>
       <c r="B418" s="187" t="n"/>
       <c r="C418" s="187" t="n"/>
-      <c r="D418" s="184" t="inlineStr">
-        <is>
-          <t>聯亞(3081)</t>
-        </is>
-      </c>
-      <c r="E418" s="185" t="n">
-        <v>10</v>
-      </c>
-      <c r="F418" s="185" t="n">
-        <v>1</v>
-      </c>
-      <c r="G418" s="185" t="n">
-        <v>2168</v>
-      </c>
-      <c r="H418" s="185" t="n">
-        <v>231</v>
-      </c>
-      <c r="I418" s="185" t="n">
-        <v>1937</v>
-      </c>
-      <c r="J418" s="186" t="n">
-        <v>2167.6</v>
-      </c>
-      <c r="K418" s="186" t="n">
-        <v>2309</v>
-      </c>
-      <c r="L418" s="235">
+      <c r="D418" s="240" t="inlineStr">
+        <is>
+          <t>前鼎(4908)</t>
+        </is>
+      </c>
+      <c r="E418" s="241" t="n">
+        <v>164</v>
+      </c>
+      <c r="F418" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G418" s="241" t="n">
+        <v>2714</v>
+      </c>
+      <c r="H418" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="I418" s="241" t="n">
+        <v>2714</v>
+      </c>
+      <c r="J418" s="242" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="K418" s="242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L418" s="243">
         <f>F418*(K418-J418)</f>
         <v/>
       </c>
@@ -30574,7 +30574,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-08-05 22:57 TW | 18/18 success | 來源: 富邦18/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-08-05 23:55 TW | 19/19 success | 來源: 富邦19/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -23,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="24">
+  <numFmts count="25">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨-64/5d-140)&quot;;-0&quot; 億 (昨-64/5d-140)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +122億 &quot;&quot;(昨5/5d9)&quot;"/>
@@ -48,6 +48,7 @@
     <numFmt numFmtId="185" formatCode="+0&quot; 億 (昨-89/5d-59)&quot;;-0&quot; 億 (昨-89/5d-59)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="186" formatCode="0&quot; 檔 +63億 &quot;&quot;(昨9/5d8)&quot;"/>
     <numFmt numFmtId="187" formatCode="0.0%&quot; 市-478億 &quot;&quot;(昨18/5d18)&quot;"/>
+    <numFmt numFmtId="188" formatCode="0.0%&quot; 市-475億 &quot;&quot;(昨18/5d18)&quot;"/>
   </numFmts>
   <fonts count="54">
     <font>
@@ -623,7 +624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="256">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1220,6 +1221,9 @@
     <xf numFmtId="176" fontId="5" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="188" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1305,12 +1309,12 @@
     <comment ref="D16" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「張濬安(航海王)」獨佔比 60.9%
+領頭大戶「張濬安(航海王)」獨佔比 60.3%
   • 領頭金額 136,742 萬
-  • 合計淨買 224,645 萬
+  • 合計淨買 226,692 萬
   • 大戶數 10 位 (名義共識)
 判讀: 名義 10 位大戶共識,
-實質 1 人下注佔 61%,
+實質 1 人下注佔 60%,
 剩餘 9 位為陪襯小單,
 真共識訊號被稀釋.</t>
       </text>
@@ -1831,7 +1835,7 @@
         <v>10</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
@@ -1847,7 +1851,7 @@
         </is>
       </c>
       <c r="J16" s="18" t="n">
-        <v>56060</v>
+        <v>58107</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1861,7 +1865,7 @@
         <v>7</v>
       </c>
       <c r="N16" s="17" t="n">
-        <v>224645</v>
+        <v>226692</v>
       </c>
     </row>
     <row r="17">
@@ -2239,7 +2243,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
@@ -2247,7 +2251,7 @@
         </is>
       </c>
       <c r="H24" s="17" t="n">
-        <v>5060</v>
+        <v>4888</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2269,7 +2273,7 @@
         <v>8</v>
       </c>
       <c r="N24" s="17" t="n">
-        <v>19002</v>
+        <v>18830</v>
       </c>
     </row>
     <row r="25">
@@ -2392,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
@@ -2422,7 +2426,7 @@
         <v>7</v>
       </c>
       <c r="N27" s="17" t="n">
-        <v>7730</v>
+        <v>7848</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -2447,7 +2451,7 @@
         </is>
       </c>
       <c r="G30" s="251" t="n">
-        <v>-187.38063</v>
+        <v>-183.99805</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
@@ -2464,8 +2468,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G31" s="253" t="n">
-        <v>0.1590669231384998</v>
+      <c r="G31" s="256" t="n">
+        <v>0.1595358900128013</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -2548,7 +2552,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2576,11 +2580,11 @@
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>1489607</v>
+        <v>1509116</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2592,7 +2596,7 @@
         </is>
       </c>
       <c r="H38" s="33" t="n">
-        <v>224645</v>
+        <v>226692</v>
       </c>
       <c r="I38" s="213" t="n">
         <v>0.0206</v>
@@ -2844,22 +2848,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>強森</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>強森 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 5 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>4 檔</t>
+          <t>5 檔</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2875,7 @@
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>強森</t>
         </is>
       </c>
       <c r="D51" s="41" t="inlineStr">
@@ -2881,7 +2885,7 @@
       </c>
       <c r="E51" s="41" t="inlineStr">
         <is>
-          <t>林滄海 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>強森 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F51" s="41" t="inlineStr">
@@ -2898,7 +2902,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2908,7 +2912,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>林滄海 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3218,7 +3222,7 @@
         </is>
       </c>
       <c r="C67" s="33" t="n">
-        <v>1371660</v>
+        <v>1389992</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3245,7 +3249,7 @@
         <v>124487</v>
       </c>
       <c r="J67" s="214" t="n">
-        <v>0.3274504853571938</v>
+        <v>0.3231317667636168</v>
       </c>
     </row>
     <row r="68">
@@ -5137,7 +5141,7 @@
     <row r="36" ht="22" customHeight="1">
       <c r="C36" s="247" t="inlineStr">
         <is>
-          <t>-187 億 淨買</t>
+          <t>-184 億 淨買</t>
         </is>
       </c>
     </row>
@@ -19642,31 +19646,31 @@
       <c r="C190" s="140" t="n"/>
       <c r="D190" s="137" t="inlineStr">
         <is>
-          <t>聯電(2303)</t>
+          <t>南亞(1303)</t>
         </is>
       </c>
       <c r="E190" s="138" t="n">
-        <v>696</v>
+        <v>752</v>
       </c>
       <c r="F190" s="138" t="n">
-        <v>133</v>
+        <v>726</v>
       </c>
       <c r="G190" s="138" t="n">
-        <v>8692</v>
+        <v>13310</v>
       </c>
       <c r="H190" s="138" t="n">
-        <v>1658</v>
+        <v>12850</v>
       </c>
       <c r="I190" s="138" t="n">
-        <v>7034</v>
+        <v>460</v>
       </c>
       <c r="J190" s="139" t="n">
-        <v>124.89</v>
+        <v>177</v>
       </c>
       <c r="K190" s="139" t="n">
-        <v>124.67</v>
-      </c>
-      <c r="L190" s="236">
+        <v>177</v>
+      </c>
+      <c r="L190" s="235">
         <f>F190*(K190-J190)</f>
         <v/>
       </c>
@@ -19677,31 +19681,31 @@
       <c r="C191" s="140" t="n"/>
       <c r="D191" s="137" t="inlineStr">
         <is>
-          <t>高力(8996)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="E191" s="138" t="n">
-        <v>79</v>
+        <v>712</v>
       </c>
       <c r="F191" s="138" t="n">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="G191" s="138" t="n">
-        <v>8310</v>
+        <v>8692</v>
       </c>
       <c r="H191" s="138" t="n">
-        <v>3634</v>
+        <v>1658</v>
       </c>
       <c r="I191" s="138" t="n">
-        <v>4676</v>
+        <v>7034</v>
       </c>
       <c r="J191" s="139" t="n">
-        <v>1051.9</v>
+        <v>122.08</v>
       </c>
       <c r="K191" s="139" t="n">
-        <v>1068.76</v>
-      </c>
-      <c r="L191" s="235">
+        <v>121.92</v>
+      </c>
+      <c r="L191" s="236">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -19712,29 +19716,29 @@
       <c r="C192" s="140" t="n"/>
       <c r="D192" s="137" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>高力(8996)</t>
         </is>
       </c>
       <c r="E192" s="138" t="n">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="F192" s="138" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="G192" s="138" t="n">
-        <v>7916</v>
+        <v>8310</v>
       </c>
       <c r="H192" s="138" t="n">
-        <v>1500</v>
+        <v>3634</v>
       </c>
       <c r="I192" s="138" t="n">
-        <v>6416</v>
+        <v>4676</v>
       </c>
       <c r="J192" s="139" t="n">
-        <v>224.89</v>
+        <v>1038.75</v>
       </c>
       <c r="K192" s="139" t="n">
-        <v>220.56</v>
+        <v>1038.23</v>
       </c>
       <c r="L192" s="236">
         <f>F192*(K192-J192)</f>
@@ -19747,31 +19751,31 @@
       <c r="C193" s="140" t="n"/>
       <c r="D193" s="137" t="inlineStr">
         <is>
-          <t>旺宏(2337)</t>
+          <t>文曄(3036)</t>
         </is>
       </c>
       <c r="E193" s="138" t="n">
-        <v>500</v>
+        <v>352</v>
       </c>
       <c r="F193" s="138" t="n">
-        <v>259</v>
+        <v>67</v>
       </c>
       <c r="G193" s="138" t="n">
-        <v>6135</v>
+        <v>7916</v>
       </c>
       <c r="H193" s="138" t="n">
-        <v>3188</v>
+        <v>1500</v>
       </c>
       <c r="I193" s="138" t="n">
-        <v>2947</v>
+        <v>6416</v>
       </c>
       <c r="J193" s="139" t="n">
-        <v>122.71</v>
+        <v>224.89</v>
       </c>
       <c r="K193" s="139" t="n">
-        <v>123.09</v>
-      </c>
-      <c r="L193" s="235">
+        <v>223.85</v>
+      </c>
+      <c r="L193" s="236">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -19782,29 +19786,29 @@
       <c r="C194" s="140" t="n"/>
       <c r="D194" s="137" t="inlineStr">
         <is>
-          <t>強茂(2481)</t>
+          <t>旺宏(2337)</t>
         </is>
       </c>
       <c r="E194" s="138" t="n">
-        <v>332</v>
+        <v>130</v>
       </c>
       <c r="F194" s="138" t="n">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="G194" s="138" t="n">
-        <v>4589</v>
+        <v>6135</v>
       </c>
       <c r="H194" s="138" t="n">
-        <v>245</v>
+        <v>3188</v>
       </c>
       <c r="I194" s="138" t="n">
-        <v>4344</v>
+        <v>2947</v>
       </c>
       <c r="J194" s="139" t="n">
-        <v>138.22</v>
+        <v>471.95</v>
       </c>
       <c r="K194" s="139" t="n">
-        <v>136.33</v>
+        <v>419.49</v>
       </c>
       <c r="L194" s="236">
         <f>F194*(K194-J194)</f>
@@ -19817,29 +19821,29 @@
       <c r="C195" s="140" t="n"/>
       <c r="D195" s="137" t="inlineStr">
         <is>
-          <t>華邦電(2344)</t>
+          <t>強茂(2481)</t>
         </is>
       </c>
       <c r="E195" s="138" t="n">
-        <v>185</v>
+        <v>342</v>
       </c>
       <c r="F195" s="138" t="n">
-        <v>164</v>
+        <v>18</v>
       </c>
       <c r="G195" s="138" t="n">
-        <v>3120</v>
+        <v>4589</v>
       </c>
       <c r="H195" s="138" t="n">
-        <v>2775</v>
+        <v>245</v>
       </c>
       <c r="I195" s="138" t="n">
-        <v>345</v>
+        <v>4344</v>
       </c>
       <c r="J195" s="139" t="n">
-        <v>168.64</v>
+        <v>134.18</v>
       </c>
       <c r="K195" s="139" t="n">
-        <v>169.2</v>
+        <v>136.33</v>
       </c>
       <c r="L195" s="235">
         <f>F195*(K195-J195)</f>
@@ -19852,29 +19856,29 @@
       <c r="C196" s="140" t="n"/>
       <c r="D196" s="137" t="inlineStr">
         <is>
-          <t>環球晶(6488)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E196" s="138" t="n">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="F196" s="138" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="G196" s="138" t="n">
-        <v>2363</v>
+        <v>4494</v>
       </c>
       <c r="H196" s="138" t="n">
-        <v>1169</v>
+        <v>2448</v>
       </c>
       <c r="I196" s="138" t="n">
-        <v>1194</v>
+        <v>2046</v>
       </c>
       <c r="J196" s="139" t="n">
-        <v>875.22</v>
+        <v>445</v>
       </c>
       <c r="K196" s="139" t="n">
-        <v>899.38</v>
+        <v>445</v>
       </c>
       <c r="L196" s="235">
         <f>F196*(K196-J196)</f>
@@ -19887,29 +19891,29 @@
       <c r="C197" s="140" t="n"/>
       <c r="D197" s="137" t="inlineStr">
         <is>
-          <t>群創(3481)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E197" s="138" t="n">
-        <v>403</v>
+        <v>185</v>
       </c>
       <c r="F197" s="138" t="n">
-        <v>367</v>
+        <v>164</v>
       </c>
       <c r="G197" s="138" t="n">
-        <v>1926</v>
+        <v>3120</v>
       </c>
       <c r="H197" s="138" t="n">
-        <v>1754</v>
+        <v>2775</v>
       </c>
       <c r="I197" s="138" t="n">
-        <v>172</v>
+        <v>345</v>
       </c>
       <c r="J197" s="139" t="n">
-        <v>47.8</v>
+        <v>168.64</v>
       </c>
       <c r="K197" s="139" t="n">
-        <v>47.8</v>
+        <v>169.2</v>
       </c>
       <c r="L197" s="235">
         <f>F197*(K197-J197)</f>
@@ -19922,29 +19926,29 @@
       <c r="C198" s="140" t="n"/>
       <c r="D198" s="137" t="inlineStr">
         <is>
-          <t>力成(6239)</t>
+          <t>環球晶(6488)</t>
         </is>
       </c>
       <c r="E198" s="138" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="F198" s="138" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="G198" s="138" t="n">
-        <v>1909</v>
+        <v>2363</v>
       </c>
       <c r="H198" s="138" t="n">
-        <v>1678</v>
+        <v>1169</v>
       </c>
       <c r="I198" s="138" t="n">
-        <v>231</v>
+        <v>1194</v>
       </c>
       <c r="J198" s="139" t="n">
-        <v>258</v>
+        <v>875.22</v>
       </c>
       <c r="K198" s="139" t="n">
-        <v>258.12</v>
+        <v>899.38</v>
       </c>
       <c r="L198" s="235">
         <f>F198*(K198-J198)</f>
@@ -30574,7 +30578,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-08-05 23:55 TW | 19/19 success | 來源: 富邦19/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-08-06 00:38 TW | 19/19 success | 來源: 富邦19/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -1309,12 +1309,12 @@
     <comment ref="D16" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「張濬安(航海王)」獨佔比 60.3%
+領頭大戶「張濬安(航海王)」獨佔比 60.9%
   • 領頭金額 136,742 萬
-  • 合計淨買 226,692 萬
+  • 合計淨買 224,645 萬
   • 大戶數 10 位 (名義共識)
 判讀: 名義 10 位大戶共識,
-實質 1 人下注佔 60%,
+實質 1 人下注佔 61%,
 剩餘 9 位為陪襯小單,
 真共識訊號被稀釋.</t>
       </text>
@@ -1835,7 +1835,7 @@
         <v>10</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="J16" s="18" t="n">
-        <v>58107</v>
+        <v>56060</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>7</v>
       </c>
       <c r="N16" s="17" t="n">
-        <v>226692</v>
+        <v>224645</v>
       </c>
     </row>
     <row r="17">
@@ -2243,7 +2243,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="H24" s="17" t="n">
-        <v>4888</v>
+        <v>5060</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>8</v>
       </c>
       <c r="N24" s="17" t="n">
-        <v>18830</v>
+        <v>19002</v>
       </c>
     </row>
     <row r="25">
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>7</v>
       </c>
       <c r="N27" s="17" t="n">
-        <v>7848</v>
+        <v>7730</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="G30" s="251" t="n">
-        <v>-183.99805</v>
+        <v>-187.38063</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
@@ -2468,8 +2468,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G31" s="256" t="n">
-        <v>0.1595358900128013</v>
+      <c r="G31" s="253" t="n">
+        <v>0.1590669231384998</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2580,11 +2580,11 @@
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>1509116</v>
+        <v>1489607</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H38" s="33" t="n">
-        <v>226692</v>
+        <v>224645</v>
       </c>
       <c r="I38" s="213" t="n">
         <v>0.0206</v>
@@ -2848,22 +2848,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>強森</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 5 檔新標的 (過去從沒買過)</t>
+          <t>強森 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5 檔</t>
+          <t>4 檔</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>強森</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="D51" s="41" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="E51" s="41" t="inlineStr">
         <is>
-          <t>強森 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>林滄海 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F51" s="41" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>林滄海 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="C67" s="33" t="n">
-        <v>1389992</v>
+        <v>1371660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>124487</v>
       </c>
       <c r="J67" s="214" t="n">
-        <v>0.3231317667636168</v>
+        <v>0.3274504853571938</v>
       </c>
     </row>
     <row r="68">
@@ -5141,7 +5141,7 @@
     <row r="36" ht="22" customHeight="1">
       <c r="C36" s="247" t="inlineStr">
         <is>
-          <t>-184 億 淨買</t>
+          <t>-187 億 淨買</t>
         </is>
       </c>
     </row>
@@ -19646,31 +19646,31 @@
       <c r="C190" s="140" t="n"/>
       <c r="D190" s="137" t="inlineStr">
         <is>
-          <t>南亞(1303)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="E190" s="138" t="n">
-        <v>752</v>
+        <v>696</v>
       </c>
       <c r="F190" s="138" t="n">
-        <v>726</v>
+        <v>133</v>
       </c>
       <c r="G190" s="138" t="n">
-        <v>13310</v>
+        <v>8692</v>
       </c>
       <c r="H190" s="138" t="n">
-        <v>12850</v>
+        <v>1658</v>
       </c>
       <c r="I190" s="138" t="n">
-        <v>460</v>
+        <v>7034</v>
       </c>
       <c r="J190" s="139" t="n">
-        <v>177</v>
+        <v>124.89</v>
       </c>
       <c r="K190" s="139" t="n">
-        <v>177</v>
-      </c>
-      <c r="L190" s="235">
+        <v>124.67</v>
+      </c>
+      <c r="L190" s="236">
         <f>F190*(K190-J190)</f>
         <v/>
       </c>
@@ -19681,31 +19681,31 @@
       <c r="C191" s="140" t="n"/>
       <c r="D191" s="137" t="inlineStr">
         <is>
-          <t>聯電(2303)</t>
+          <t>高力(8996)</t>
         </is>
       </c>
       <c r="E191" s="138" t="n">
-        <v>712</v>
+        <v>79</v>
       </c>
       <c r="F191" s="138" t="n">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="G191" s="138" t="n">
-        <v>8692</v>
+        <v>8310</v>
       </c>
       <c r="H191" s="138" t="n">
-        <v>1658</v>
+        <v>3634</v>
       </c>
       <c r="I191" s="138" t="n">
-        <v>7034</v>
+        <v>4676</v>
       </c>
       <c r="J191" s="139" t="n">
-        <v>122.08</v>
+        <v>1051.9</v>
       </c>
       <c r="K191" s="139" t="n">
-        <v>121.92</v>
-      </c>
-      <c r="L191" s="236">
+        <v>1068.76</v>
+      </c>
+      <c r="L191" s="235">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -19716,29 +19716,29 @@
       <c r="C192" s="140" t="n"/>
       <c r="D192" s="137" t="inlineStr">
         <is>
-          <t>高力(8996)</t>
+          <t>文曄(3036)</t>
         </is>
       </c>
       <c r="E192" s="138" t="n">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="F192" s="138" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="G192" s="138" t="n">
-        <v>8310</v>
+        <v>7916</v>
       </c>
       <c r="H192" s="138" t="n">
-        <v>3634</v>
+        <v>1500</v>
       </c>
       <c r="I192" s="138" t="n">
-        <v>4676</v>
+        <v>6416</v>
       </c>
       <c r="J192" s="139" t="n">
-        <v>1038.75</v>
+        <v>224.89</v>
       </c>
       <c r="K192" s="139" t="n">
-        <v>1038.23</v>
+        <v>220.56</v>
       </c>
       <c r="L192" s="236">
         <f>F192*(K192-J192)</f>
@@ -19751,31 +19751,31 @@
       <c r="C193" s="140" t="n"/>
       <c r="D193" s="137" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>旺宏(2337)</t>
         </is>
       </c>
       <c r="E193" s="138" t="n">
-        <v>352</v>
+        <v>500</v>
       </c>
       <c r="F193" s="138" t="n">
-        <v>67</v>
+        <v>259</v>
       </c>
       <c r="G193" s="138" t="n">
-        <v>7916</v>
+        <v>6135</v>
       </c>
       <c r="H193" s="138" t="n">
-        <v>1500</v>
+        <v>3188</v>
       </c>
       <c r="I193" s="138" t="n">
-        <v>6416</v>
+        <v>2947</v>
       </c>
       <c r="J193" s="139" t="n">
-        <v>224.89</v>
+        <v>122.71</v>
       </c>
       <c r="K193" s="139" t="n">
-        <v>223.85</v>
-      </c>
-      <c r="L193" s="236">
+        <v>123.09</v>
+      </c>
+      <c r="L193" s="235">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -19786,29 +19786,29 @@
       <c r="C194" s="140" t="n"/>
       <c r="D194" s="137" t="inlineStr">
         <is>
-          <t>旺宏(2337)</t>
+          <t>強茂(2481)</t>
         </is>
       </c>
       <c r="E194" s="138" t="n">
-        <v>130</v>
+        <v>332</v>
       </c>
       <c r="F194" s="138" t="n">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="G194" s="138" t="n">
-        <v>6135</v>
+        <v>4589</v>
       </c>
       <c r="H194" s="138" t="n">
-        <v>3188</v>
+        <v>245</v>
       </c>
       <c r="I194" s="138" t="n">
-        <v>2947</v>
+        <v>4344</v>
       </c>
       <c r="J194" s="139" t="n">
-        <v>471.95</v>
+        <v>138.22</v>
       </c>
       <c r="K194" s="139" t="n">
-        <v>419.49</v>
+        <v>136.33</v>
       </c>
       <c r="L194" s="236">
         <f>F194*(K194-J194)</f>
@@ -19821,29 +19821,29 @@
       <c r="C195" s="140" t="n"/>
       <c r="D195" s="137" t="inlineStr">
         <is>
-          <t>強茂(2481)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E195" s="138" t="n">
-        <v>342</v>
+        <v>185</v>
       </c>
       <c r="F195" s="138" t="n">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="G195" s="138" t="n">
-        <v>4589</v>
+        <v>3120</v>
       </c>
       <c r="H195" s="138" t="n">
-        <v>245</v>
+        <v>2775</v>
       </c>
       <c r="I195" s="138" t="n">
-        <v>4344</v>
+        <v>345</v>
       </c>
       <c r="J195" s="139" t="n">
-        <v>134.18</v>
+        <v>168.64</v>
       </c>
       <c r="K195" s="139" t="n">
-        <v>136.33</v>
+        <v>169.2</v>
       </c>
       <c r="L195" s="235">
         <f>F195*(K195-J195)</f>
@@ -19856,29 +19856,29 @@
       <c r="C196" s="140" t="n"/>
       <c r="D196" s="137" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>環球晶(6488)</t>
         </is>
       </c>
       <c r="E196" s="138" t="n">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="F196" s="138" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="G196" s="138" t="n">
-        <v>4494</v>
+        <v>2363</v>
       </c>
       <c r="H196" s="138" t="n">
-        <v>2448</v>
+        <v>1169</v>
       </c>
       <c r="I196" s="138" t="n">
-        <v>2046</v>
+        <v>1194</v>
       </c>
       <c r="J196" s="139" t="n">
-        <v>445</v>
+        <v>875.22</v>
       </c>
       <c r="K196" s="139" t="n">
-        <v>445</v>
+        <v>899.38</v>
       </c>
       <c r="L196" s="235">
         <f>F196*(K196-J196)</f>
@@ -19891,29 +19891,29 @@
       <c r="C197" s="140" t="n"/>
       <c r="D197" s="137" t="inlineStr">
         <is>
-          <t>華邦電(2344)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E197" s="138" t="n">
-        <v>185</v>
+        <v>403</v>
       </c>
       <c r="F197" s="138" t="n">
-        <v>164</v>
+        <v>367</v>
       </c>
       <c r="G197" s="138" t="n">
-        <v>3120</v>
+        <v>1926</v>
       </c>
       <c r="H197" s="138" t="n">
-        <v>2775</v>
+        <v>1754</v>
       </c>
       <c r="I197" s="138" t="n">
-        <v>345</v>
+        <v>172</v>
       </c>
       <c r="J197" s="139" t="n">
-        <v>168.64</v>
+        <v>47.8</v>
       </c>
       <c r="K197" s="139" t="n">
-        <v>169.2</v>
+        <v>47.8</v>
       </c>
       <c r="L197" s="235">
         <f>F197*(K197-J197)</f>
@@ -19926,29 +19926,29 @@
       <c r="C198" s="140" t="n"/>
       <c r="D198" s="137" t="inlineStr">
         <is>
-          <t>環球晶(6488)</t>
+          <t>力成(6239)</t>
         </is>
       </c>
       <c r="E198" s="138" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="F198" s="138" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="G198" s="138" t="n">
-        <v>2363</v>
+        <v>1909</v>
       </c>
       <c r="H198" s="138" t="n">
-        <v>1169</v>
+        <v>1678</v>
       </c>
       <c r="I198" s="138" t="n">
-        <v>1194</v>
+        <v>231</v>
       </c>
       <c r="J198" s="139" t="n">
-        <v>875.22</v>
+        <v>258</v>
       </c>
       <c r="K198" s="139" t="n">
-        <v>899.38</v>
+        <v>258.12</v>
       </c>
       <c r="L198" s="235">
         <f>F198*(K198-J198)</f>
@@ -30578,7 +30578,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-08-06 00:38 TW | 19/19 success | 來源: 富邦19/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-08-06 01:29 TW | 19/19 success | 來源: 富邦19/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -1765,7 +1765,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 📌 一般共識 2330 / 6274 / 2308 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 除權息 11 檔: 1419, 1439, 1713 ...  |  訊號: 強偏多 (Q5 82.1%, hot=13)</t>
+          <t>💡 📌 一般共識 2330 / 6274 / 2308 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 除權息 11 檔: 1419, 1439, 1713 ... | 明日恐處置 6 檔: 2059/2455/3037...  |  訊號: 強偏多 (Q5 82.1%, hot=13)</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
@@ -2298,13 +2298,13 @@
         </is>
       </c>
       <c r="L23" s="18" t="n">
-        <v>4686</v>
+        <v>5216</v>
       </c>
       <c r="M23" s="19" t="n">
         <v>8</v>
       </c>
       <c r="N23" s="17" t="n">
-        <v>33041</v>
+        <v>33571</v>
       </c>
     </row>
     <row r="24">
@@ -2529,23 +2529,23 @@
         <v>11</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>2206</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>張濬安</t>
         </is>
       </c>
-      <c r="H28" s="17" t="n">
+      <c r="J28" s="18" t="n">
         <v>1680</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>陳族元</t>
-        </is>
-      </c>
-      <c r="J28" s="18" t="n">
-        <v>1647</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>8</v>
       </c>
       <c r="N28" s="17" t="n">
-        <v>10228</v>
+        <v>10788</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="G31" s="257" t="n">
-        <v>-70.58412</v>
+        <v>-70.38218000000001</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="G32" s="259" t="n">
-        <v>0.1847289431673657</v>
+        <v>0.1849776296801424</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -2681,11 +2681,11 @@
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>1333527</v>
+        <v>1341606</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="C65" s="33" t="n">
-        <v>1259132</v>
+        <v>1264701</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>82320</v>
       </c>
       <c r="J65" s="214" t="n">
-        <v>0.3663949529663974</v>
+        <v>0.3647815356802178</v>
       </c>
     </row>
     <row r="66">
@@ -3741,7 +3741,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="B79" s="59" t="inlineStr">
         <is>
-          <t>▍ G. 注意股 (資料日 20260805)</t>
+          <t>▍ G. 注意股 (資料日 20260806)</t>
         </is>
       </c>
     </row>
@@ -3775,19 +3775,19 @@
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>039038</t>
+          <t>039037</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>富鼎統一6A購01</t>
+          <t>富鼎統一5A購01</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3798,19 +3798,19 @@
     <row r="82">
       <c r="B82" s="41" t="inlineStr">
         <is>
-          <t>053859</t>
+          <t>039038</t>
         </is>
       </c>
       <c r="C82" s="41" t="inlineStr">
         <is>
-          <t>強茂統一61購02</t>
+          <t>富鼎統一6A購01</t>
         </is>
       </c>
       <c r="D82" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E82" s="41" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="F82" s="41" t="inlineStr">
         <is>
@@ -3821,19 +3821,19 @@
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t>059816</t>
+          <t>040616</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>台虹凱基5A購02</t>
+          <t>華新科統一5A購01</t>
         </is>
       </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.14</v>
+        <v>6</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3844,19 +3844,19 @@
     <row r="84">
       <c r="B84" s="41" t="inlineStr">
         <is>
-          <t>068822</t>
+          <t>053859</t>
         </is>
       </c>
       <c r="C84" s="41" t="inlineStr">
         <is>
-          <t>富鼎統一69購01</t>
+          <t>強茂統一61購02</t>
         </is>
       </c>
       <c r="D84" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E84" s="41" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="F84" s="41" t="inlineStr">
         <is>
@@ -3867,19 +3867,19 @@
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t>071559</t>
+          <t>057151</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>強茂統一63購03</t>
+          <t>永光統一61購03</t>
         </is>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>0.64</v>
+        <v>0.9</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3890,230 +3890,230 @@
     <row r="86">
       <c r="B86" s="41" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>057514</t>
         </is>
       </c>
       <c r="C86" s="41" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>強茂統一63購01</t>
         </is>
       </c>
       <c r="D86" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E86" s="41" t="n">
-        <v>1510</v>
+        <v>1.5</v>
       </c>
       <c r="F86" s="41" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>-----</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>059570</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>強茂凱基5B購03</t>
         </is>
       </c>
       <c r="D87" t="n">
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>9470</v>
+        <v>13.5</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>83.47</t>
+          <t>-----</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="41" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>063447</t>
         </is>
       </c>
       <c r="C88" s="41" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>國巨統一74購01</t>
         </is>
       </c>
       <c r="D88" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E88" s="41" t="n">
-        <v>940</v>
+        <v>2.79</v>
       </c>
       <c r="F88" s="41" t="inlineStr">
         <is>
-          <t>42.44</t>
+          <t>-----</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>064658</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>群創群益5A購04</t>
         </is>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>5245</v>
+        <v>13</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>82.02</t>
+          <t>-----</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="41" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>068822</t>
         </is>
       </c>
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>富鼎統一69購01</t>
         </is>
       </c>
       <c r="D90" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E90" s="41" t="n">
-        <v>4000</v>
+        <v>0.79</v>
       </c>
       <c r="F90" s="41" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>-----</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>072318</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>富鼎台新61購01</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>388</v>
+        <v>1.1</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>95.10</t>
+          <t>-----</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="41" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>希華</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="D92" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E92" s="41" t="n">
-        <v>70.5</v>
+        <v>10100</v>
       </c>
       <c r="F92" s="41" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>55.68</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="D93" t="n">
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>969</v>
+        <v>252.5</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>64.51</t>
+          <t>29.53</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="41" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C94" s="41" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D94" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E94" s="41" t="n">
-        <v>828</v>
+        <v>2410</v>
       </c>
       <c r="F94" s="41" t="inlineStr">
         <is>
-          <t>233.24</t>
+          <t>45.57</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D95" t="n">
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>4390</v>
+        <v>5305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>112.54</t>
+          <t>82.96</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="B115" s="67" t="inlineStr">
         <is>
-          <t>▍ I. 未來 30 天除權息 (有效 99 檔, 已剔除過期)</t>
+          <t>▍ I. 未來 30 天除權息 (有效 110 檔, 已剔除過期)</t>
         </is>
       </c>
     </row>
@@ -5210,9 +5210,9 @@
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="73" t="inlineStr">
-        <is>
-          <t>今日無處置股</t>
+      <c r="C33" s="71" t="inlineStr">
+        <is>
+          <t>明日恐處置 6 檔 (2059 / 2455 / 3037 ...)</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
     <row r="36" ht="22" customHeight="1">
       <c r="C36" s="247" t="inlineStr">
         <is>
-          <t>-71 億 淨買</t>
+          <t>-70 億 淨買</t>
         </is>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="B3" s="106" t="inlineStr">
         <is>
-          <t>大牌分析師 近 75/75 交易日出手 3579 次 (600 檔), 風格分布: 隔日沖近似 32% / 當沖 14% / 留倉 54%, 漲停命中 4% (其中 🔒鎖漲停 3%), 前 5 大集中 24%, 長線部位 73% (67 檔), ⚠️ 處置股部位 11% (25 檔), 📦 連續囤貨 38 檔 (最長 13 天 009816, 3 檔仍 active)。 主軸: 📈 長線持有/高頻交易/持續進場/📦 連續囤貨。</t>
+          <t>大牌分析師 近 75/75 交易日出手 3579 次 (600 檔), 風格分布: 隔日沖近似 32% / 當沖 14% / 留倉 54%, 漲停命中 4% (其中 🔒鎖漲停 3%), 前 5 大集中 24%, 長線部位 73% (67 檔), ⚠️ 處置股部位 14% (41 檔), 📦 連續囤貨 38 檔 (最長 13 天 009816, 3 檔仍 active)。 主軸: 📈 長線持有/高頻交易/持續進場/📦 連續囤貨。</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19451,7 @@
         </is>
       </c>
       <c r="E189" s="138" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F189" s="138" t="n">
         <v>5</v>
@@ -19466,7 +19466,7 @@
         <v>7646</v>
       </c>
       <c r="J189" s="139" t="n">
-        <v>991.9299999999999</v>
+        <v>979.98</v>
       </c>
       <c r="K189" s="139" t="n">
         <v>976.6</v>
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="E191" s="138" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F191" s="138" t="n">
         <v>11</v>
@@ -19536,12 +19536,12 @@
         <v>4617</v>
       </c>
       <c r="J191" s="139" t="n">
-        <v>228.67</v>
+        <v>233.05</v>
       </c>
       <c r="K191" s="139" t="n">
         <v>230.73</v>
       </c>
-      <c r="L191" s="235">
+      <c r="L191" s="236">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -19657,29 +19657,29 @@
       <c r="C195" s="140" t="n"/>
       <c r="D195" s="137" t="inlineStr">
         <is>
-          <t>景碩(3189)</t>
+          <t>力積電(6770)</t>
         </is>
       </c>
       <c r="E195" s="138" t="n">
-        <v>30</v>
+        <v>393</v>
       </c>
       <c r="F195" s="138" t="n">
-        <v>22</v>
+        <v>309</v>
       </c>
       <c r="G195" s="138" t="n">
-        <v>2566</v>
+        <v>2617</v>
       </c>
       <c r="H195" s="138" t="n">
-        <v>1917</v>
+        <v>2058</v>
       </c>
       <c r="I195" s="138" t="n">
-        <v>649</v>
+        <v>559</v>
       </c>
       <c r="J195" s="139" t="n">
-        <v>855.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K195" s="139" t="n">
-        <v>871.3200000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L195" s="235">
         <f>F195*(K195-J195)</f>
@@ -19692,29 +19692,29 @@
       <c r="C196" s="140" t="n"/>
       <c r="D196" s="137" t="inlineStr">
         <is>
-          <t>欣興(3037)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E196" s="138" t="n">
+        <v>30</v>
+      </c>
+      <c r="F196" s="138" t="n">
         <v>22</v>
       </c>
-      <c r="F196" s="138" t="n">
-        <v>19</v>
-      </c>
       <c r="G196" s="138" t="n">
-        <v>2108</v>
+        <v>2566</v>
       </c>
       <c r="H196" s="138" t="n">
-        <v>1833</v>
+        <v>1917</v>
       </c>
       <c r="I196" s="138" t="n">
-        <v>275</v>
+        <v>649</v>
       </c>
       <c r="J196" s="139" t="n">
-        <v>958.27</v>
+        <v>855.4</v>
       </c>
       <c r="K196" s="139" t="n">
-        <v>964.84</v>
+        <v>871.3200000000001</v>
       </c>
       <c r="L196" s="235">
         <f>F196*(K196-J196)</f>
@@ -19727,29 +19727,29 @@
       <c r="C197" s="140" t="n"/>
       <c r="D197" s="137" t="inlineStr">
         <is>
-          <t>穩懋(3105)</t>
+          <t>欣興(3037)</t>
         </is>
       </c>
       <c r="E197" s="138" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F197" s="138" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="G197" s="138" t="n">
-        <v>2099</v>
+        <v>2108</v>
       </c>
       <c r="H197" s="138" t="n">
-        <v>1795</v>
+        <v>1833</v>
       </c>
       <c r="I197" s="138" t="n">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="J197" s="139" t="n">
-        <v>381.58</v>
+        <v>958.27</v>
       </c>
       <c r="K197" s="139" t="n">
-        <v>381.85</v>
+        <v>964.84</v>
       </c>
       <c r="L197" s="235">
         <f>F197*(K197-J197)</f>
@@ -19762,29 +19762,29 @@
       <c r="C198" s="140" t="n"/>
       <c r="D198" s="137" t="inlineStr">
         <is>
-          <t>國巨*(2327)</t>
+          <t>穩懋(3105)</t>
         </is>
       </c>
       <c r="E198" s="138" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="F198" s="138" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G198" s="138" t="n">
-        <v>1766</v>
+        <v>2099</v>
       </c>
       <c r="H198" s="138" t="n">
-        <v>1280</v>
+        <v>1795</v>
       </c>
       <c r="I198" s="138" t="n">
-        <v>486</v>
+        <v>304</v>
       </c>
       <c r="J198" s="139" t="n">
-        <v>569.6799999999999</v>
+        <v>381.58</v>
       </c>
       <c r="K198" s="139" t="n">
-        <v>581.95</v>
+        <v>381.85</v>
       </c>
       <c r="L198" s="235">
         <f>F198*(K198-J198)</f>
@@ -30271,7 +30271,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-08-06 21:36 TW | 11/11 success | 來源: 富邦11/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-08-06 22:57 TW | 11/11 success | 來源: 富邦11/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -30271,7 +30271,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-08-06 22:57 TW | 11/11 success | 來源: 富邦11/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-08-06 23:52 TW | 11/11 success | 來源: 富邦11/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -21,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨-177/5d-99)&quot;;-0&quot; 億 (昨-177/5d-99)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +63億 &quot;&quot;(昨15/5d11)&quot;"/>
@@ -35,6 +35,7 @@
     <numFmt numFmtId="174" formatCode="0.0&quot;%&quot;"/>
     <numFmt numFmtId="175" formatCode="0&quot;%&quot;"/>
     <numFmt numFmtId="176" formatCode="#,##0.00;-#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="0.0%&quot; 市-709億 &quot;&quot;(昨11/5d18)&quot;"/>
   </numFmts>
   <fonts count="50">
     <font>
@@ -581,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1141,6 +1142,9 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2288,7 +2292,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
@@ -2300,25 +2304,25 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="n">
+        <v>3239</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>強森</t>
         </is>
       </c>
-      <c r="J26" s="18" t="n">
+      <c r="L26" s="18" t="n">
         <v>1871</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>竹科主力分點</t>
-        </is>
-      </c>
-      <c r="L26" s="18" t="n">
-        <v>1292</v>
       </c>
       <c r="M26" s="19" t="n">
         <v>7</v>
       </c>
       <c r="N26" s="17" t="n">
-        <v>13312</v>
+        <v>15707</v>
       </c>
     </row>
     <row r="27">
@@ -2394,7 +2398,7 @@
         </is>
       </c>
       <c r="G30" s="208" t="n">
-        <v>-23.49664</v>
+        <v>-23.14886</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
@@ -2411,8 +2415,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G31" s="210" t="n">
-        <v>0.2096115874434546</v>
+      <c r="G31" s="241" t="n">
+        <v>0.2093086161180469</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -2495,7 +2499,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2523,11 +2527,11 @@
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>1479730</v>
+        <v>1485604</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2539,7 +2543,7 @@
         </is>
       </c>
       <c r="H38" s="33" t="n">
-        <v>234024</v>
+        <v>234593</v>
       </c>
       <c r="I38" s="212" t="n">
         <v>0.0271</v>
@@ -2683,22 +2687,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>巨人傑</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>巨人傑 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 5 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3 檔</t>
+          <t>5 檔</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2714,7 @@
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
-          <t>布哥/n_nchang</t>
+          <t>巨人傑</t>
         </is>
       </c>
       <c r="D47" s="40" t="inlineStr">
@@ -2720,7 +2724,7 @@
       </c>
       <c r="E47" s="40" t="inlineStr">
         <is>
-          <t>布哥/n_nchang 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>巨人傑 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F47" s="40" t="inlineStr">
@@ -2737,7 +2741,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>布哥/n_nchang</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2747,7 +2751,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>林滄海 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>布哥/n_nchang 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2764,7 +2768,7 @@
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="D49" s="40" t="inlineStr">
@@ -2774,7 +2778,7 @@
       </c>
       <c r="E49" s="40" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>林滄海 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F49" s="40" t="inlineStr">
@@ -3078,7 +3082,7 @@
         </is>
       </c>
       <c r="C64" s="33" t="n">
-        <v>1437897</v>
+        <v>1443898</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3105,7 +3109,7 @@
         <v>94068</v>
       </c>
       <c r="J64" s="213" t="n">
-        <v>0.2265536339678389</v>
+        <v>0.2256120673385749</v>
       </c>
     </row>
     <row r="65">
@@ -17562,10 +17566,10 @@
         </is>
       </c>
       <c r="E189" s="133" t="n">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F189" s="133" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G189" s="133" t="n">
         <v>28712</v>
@@ -17577,12 +17581,12 @@
         <v>19306</v>
       </c>
       <c r="J189" s="134" t="n">
-        <v>944.46</v>
+        <v>969.99</v>
       </c>
       <c r="K189" s="134" t="n">
-        <v>959.85</v>
-      </c>
-      <c r="L189" s="237">
+        <v>969.74</v>
+      </c>
+      <c r="L189" s="236">
         <f>F189*(K189-J189)</f>
         <v/>
       </c>
@@ -17597,7 +17601,7 @@
         </is>
       </c>
       <c r="E190" s="133" t="n">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F190" s="133" t="n">
         <v>3</v>
@@ -17612,7 +17616,7 @@
         <v>19547</v>
       </c>
       <c r="J190" s="134" t="n">
-        <v>1185.88</v>
+        <v>1222.26</v>
       </c>
       <c r="K190" s="134" t="n">
         <v>1251.67</v>
@@ -17635,7 +17639,7 @@
         <v>60</v>
       </c>
       <c r="F191" s="133" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G191" s="133" t="n">
         <v>8188</v>
@@ -17650,9 +17654,9 @@
         <v>1364.62</v>
       </c>
       <c r="K191" s="134" t="n">
-        <v>1287.14</v>
-      </c>
-      <c r="L191" s="236">
+        <v>1386.15</v>
+      </c>
+      <c r="L191" s="237">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -17702,10 +17706,10 @@
         </is>
       </c>
       <c r="E193" s="133" t="n">
-        <v>164</v>
+        <v>87</v>
       </c>
       <c r="F193" s="133" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="G193" s="133" t="n">
         <v>3867</v>
@@ -17717,12 +17721,12 @@
         <v>2029</v>
       </c>
       <c r="J193" s="134" t="n">
-        <v>235.79</v>
+        <v>444.47</v>
       </c>
       <c r="K193" s="134" t="n">
-        <v>238.74</v>
-      </c>
-      <c r="L193" s="237">
+        <v>353.52</v>
+      </c>
+      <c r="L193" s="236">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -17772,10 +17776,10 @@
         </is>
       </c>
       <c r="E195" s="133" t="n">
-        <v>56</v>
+        <v>211</v>
       </c>
       <c r="F195" s="133" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="G195" s="133" t="n">
         <v>2893</v>
@@ -17787,12 +17791,12 @@
         <v>1662</v>
       </c>
       <c r="J195" s="134" t="n">
-        <v>516.59</v>
+        <v>137.1</v>
       </c>
       <c r="K195" s="134" t="n">
-        <v>512.92</v>
-      </c>
-      <c r="L195" s="236">
+        <v>236.73</v>
+      </c>
+      <c r="L195" s="237">
         <f>F195*(K195-J195)</f>
         <v/>
       </c>
@@ -17838,31 +17842,31 @@
       <c r="C197" s="135" t="n"/>
       <c r="D197" s="132" t="inlineStr">
         <is>
-          <t>金居(8358)</t>
+          <t>晶豪科(3006)</t>
         </is>
       </c>
       <c r="E197" s="133" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="F197" s="133" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G197" s="133" t="n">
-        <v>2096</v>
+        <v>2423</v>
       </c>
       <c r="H197" s="133" t="n">
-        <v>490</v>
+        <v>28</v>
       </c>
       <c r="I197" s="133" t="n">
-        <v>1606</v>
+        <v>2395</v>
       </c>
       <c r="J197" s="134" t="n">
-        <v>523.9</v>
+        <v>278.51</v>
       </c>
       <c r="K197" s="134" t="n">
-        <v>544.89</v>
-      </c>
-      <c r="L197" s="237">
+        <v>278</v>
+      </c>
+      <c r="L197" s="236">
         <f>F197*(K197-J197)</f>
         <v/>
       </c>
@@ -17873,31 +17877,31 @@
       <c r="C198" s="135" t="n"/>
       <c r="D198" s="132" t="inlineStr">
         <is>
-          <t>頎邦(6147)</t>
+          <t>金居(8358)</t>
         </is>
       </c>
       <c r="E198" s="133" t="n">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="F198" s="133" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G198" s="133" t="n">
-        <v>2072</v>
+        <v>2096</v>
       </c>
       <c r="H198" s="133" t="n">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="I198" s="133" t="n">
-        <v>1632</v>
+        <v>1606</v>
       </c>
       <c r="J198" s="134" t="n">
-        <v>183.37</v>
+        <v>523.9</v>
       </c>
       <c r="K198" s="134" t="n">
-        <v>183.25</v>
-      </c>
-      <c r="L198" s="236">
+        <v>544.89</v>
+      </c>
+      <c r="L198" s="237">
         <f>F198*(K198-J198)</f>
         <v/>
       </c>
@@ -28504,7 +28508,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-01 21:38 TW | 17/17 success | 來源: 富邦17/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-01 22:59 TW | 17/17 success | 來源: 富邦17/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -21,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="16">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨-177/5d-99)&quot;;-0&quot; 億 (昨-177/5d-99)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +63億 &quot;&quot;(昨15/5d11)&quot;"/>
@@ -36,6 +36,8 @@
     <numFmt numFmtId="175" formatCode="0&quot;%&quot;"/>
     <numFmt numFmtId="176" formatCode="#,##0.00;-#,##0.00"/>
     <numFmt numFmtId="177" formatCode="0.0%&quot; 市-709億 &quot;&quot;(昨11/5d18)&quot;"/>
+    <numFmt numFmtId="178" formatCode="0&quot; 檔 +64億 &quot;&quot;(昨15/5d11)&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.0%&quot; 市-704億 &quot;&quot;(昨11/5d18)&quot;"/>
   </numFmts>
   <fonts count="50">
     <font>
@@ -582,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1145,6 +1147,12 @@
     <xf numFmtId="177" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="178" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1230,12 +1238,12 @@
     <comment ref="D17" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「陳族元」獨佔比 63.4%
-  • 領頭金額 78,702 萬
-  • 合計淨買 124,157 萬
+領頭大戶「陳族元」獨佔比 63.6%
+  • 領頭金額 79,367 萬
+  • 合計淨買 124,822 萬
   • 大戶數 10 位 (名義共識)
 判讀: 名義 10 位大戶共識,
-實質 1 人下注佔 63%,
+實質 1 人下注佔 64%,
 剩餘 9 位為陪襯小單,
 真共識訊號被稀釋.</t>
       </text>
@@ -1256,9 +1264,9 @@
     <comment ref="D20" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「張濬安(航海王)」獨佔比 53.6%
+領頭大戶「張濬安(航海王)」獨佔比 54.3%
   • 領頭金額 24,904 萬
-  • 合計淨買 46,428 萬
+  • 合計淨買 45,905 萬
   • 大戶數 11 位 (名義共識)
 判讀: 名義 11 位大戶共識,
 實質 1 人下注佔 54%,
@@ -1786,33 +1794,33 @@
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>26403</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>張濬安</t>
         </is>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="J16" s="18" t="n">
         <v>21508</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>陳律師</t>
         </is>
       </c>
-      <c r="J16" s="18" t="n">
+      <c r="L16" s="18" t="n">
         <v>21175</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>陳族元</t>
-        </is>
-      </c>
-      <c r="L16" s="18" t="n">
-        <v>19716</v>
       </c>
       <c r="M16" s="19" t="n">
         <v>9</v>
       </c>
       <c r="N16" s="17" t="n">
-        <v>152902</v>
+        <v>159590</v>
       </c>
     </row>
     <row r="17">
@@ -1841,7 +1849,7 @@
         </is>
       </c>
       <c r="H17" s="17" t="n">
-        <v>78703</v>
+        <v>79368</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1863,7 +1871,7 @@
         <v>7</v>
       </c>
       <c r="N17" s="17" t="n">
-        <v>124158</v>
+        <v>124823</v>
       </c>
     </row>
     <row r="18">
@@ -1892,7 +1900,7 @@
         </is>
       </c>
       <c r="H18" s="17" t="n">
-        <v>13887</v>
+        <v>13145</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1914,7 +1922,7 @@
         <v>10</v>
       </c>
       <c r="N18" s="17" t="n">
-        <v>78294</v>
+        <v>77551</v>
       </c>
     </row>
     <row r="19">
@@ -1986,7 +1994,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
@@ -2010,13 +2018,13 @@
         </is>
       </c>
       <c r="L20" s="18" t="n">
-        <v>4004</v>
+        <v>3481</v>
       </c>
       <c r="M20" s="19" t="n">
         <v>8</v>
       </c>
       <c r="N20" s="17" t="n">
-        <v>46428</v>
+        <v>45905</v>
       </c>
     </row>
     <row r="21">
@@ -2041,33 +2049,33 @@
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
+          <t>強森</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>6655</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>張濬安</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>6323</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>陳族元</t>
         </is>
       </c>
-      <c r="H21" s="17" t="n">
-        <v>7366</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>強森</t>
-        </is>
-      </c>
-      <c r="J21" s="18" t="n">
-        <v>6655</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>張濬安</t>
-        </is>
-      </c>
       <c r="L21" s="18" t="n">
-        <v>6323</v>
+        <v>6188</v>
       </c>
       <c r="M21" s="19" t="n">
         <v>9</v>
       </c>
       <c r="N21" s="17" t="n">
-        <v>34034</v>
+        <v>32855</v>
       </c>
     </row>
     <row r="22">
@@ -2112,13 +2120,13 @@
         </is>
       </c>
       <c r="L22" s="18" t="n">
-        <v>4993</v>
+        <v>4908</v>
       </c>
       <c r="M22" s="19" t="n">
         <v>10</v>
       </c>
       <c r="N22" s="17" t="n">
-        <v>32312</v>
+        <v>32227</v>
       </c>
     </row>
     <row r="23">
@@ -2198,7 +2206,7 @@
         </is>
       </c>
       <c r="H24" s="17" t="n">
-        <v>9943</v>
+        <v>8801</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2220,7 +2228,7 @@
         <v>7</v>
       </c>
       <c r="N24" s="17" t="n">
-        <v>28819</v>
+        <v>27677</v>
       </c>
     </row>
     <row r="25">
@@ -2238,10 +2246,10 @@
         </is>
       </c>
       <c r="E25" s="14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
@@ -2268,10 +2276,10 @@
         <v>1491</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N25" s="17" t="n">
-        <v>20948</v>
+        <v>21402</v>
       </c>
     </row>
     <row r="26">
@@ -2308,7 +2316,7 @@
         </is>
       </c>
       <c r="J26" s="18" t="n">
-        <v>3239</v>
+        <v>3291</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2322,7 +2330,7 @@
         <v>7</v>
       </c>
       <c r="N26" s="17" t="n">
-        <v>15707</v>
+        <v>15758</v>
       </c>
     </row>
     <row r="27">
@@ -2351,7 +2359,7 @@
         </is>
       </c>
       <c r="H27" s="17" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2373,7 +2381,7 @@
         <v>7</v>
       </c>
       <c r="N27" s="17" t="n">
-        <v>2601</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -2398,7 +2406,7 @@
         </is>
       </c>
       <c r="G30" s="208" t="n">
-        <v>-23.14886</v>
+        <v>-18.87241</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
@@ -2407,7 +2415,7 @@
           <t>Q3 強共識股</t>
         </is>
       </c>
-      <c r="C31" s="209" t="n">
+      <c r="C31" s="242" t="n">
         <v>12</v>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -2415,8 +2423,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G31" s="241" t="n">
-        <v>0.2093086161180469</v>
+      <c r="G31" s="243" t="n">
+        <v>0.2093965494893468</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -2527,11 +2535,11 @@
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>1485604</v>
+        <v>1489239</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2543,7 +2551,7 @@
         </is>
       </c>
       <c r="H38" s="33" t="n">
-        <v>234593</v>
+        <v>234608</v>
       </c>
       <c r="I38" s="212" t="n">
         <v>0.0271</v>
@@ -2692,17 +2700,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 5 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>5 檔</t>
+          <t>4 檔</t>
         </is>
       </c>
     </row>
@@ -2907,11 +2915,11 @@
         <v>31</v>
       </c>
       <c r="E56" t="n">
-        <v>1341522</v>
+        <v>1344709</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>陳族元 連續 31 天加碼 3008 (累計 1,341,522 萬)</t>
+          <t>陳族元 連續 31 天加碼 3008 (累計 1,344,709 萬)</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3090,7 @@
         </is>
       </c>
       <c r="C64" s="33" t="n">
-        <v>1443898</v>
+        <v>1447590</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3090,7 +3098,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>123706</v>
+        <v>124513</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3098,7 +3106,7 @@
         </is>
       </c>
       <c r="G64" s="33" t="n">
-        <v>107986</v>
+        <v>108644</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3109,7 +3117,7 @@
         <v>94068</v>
       </c>
       <c r="J64" s="213" t="n">
-        <v>0.2256120673385749</v>
+        <v>0.2260477669617202</v>
       </c>
     </row>
     <row r="65">
@@ -5003,7 +5011,7 @@
     <row r="36" ht="22" customHeight="1">
       <c r="C36" s="70" t="inlineStr">
         <is>
-          <t>-23 億 淨買</t>
+          <t>-19 億 淨買</t>
         </is>
       </c>
     </row>
@@ -17566,27 +17574,27 @@
         </is>
       </c>
       <c r="E189" s="133" t="n">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F189" s="133" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G189" s="133" t="n">
-        <v>28712</v>
+        <v>29518</v>
       </c>
       <c r="H189" s="133" t="n">
-        <v>9406</v>
+        <v>9516</v>
       </c>
       <c r="I189" s="133" t="n">
-        <v>19306</v>
+        <v>20002</v>
       </c>
       <c r="J189" s="134" t="n">
-        <v>969.99</v>
+        <v>971</v>
       </c>
       <c r="K189" s="134" t="n">
-        <v>969.74</v>
-      </c>
-      <c r="L189" s="236">
+        <v>971</v>
+      </c>
+      <c r="L189" s="237">
         <f>F189*(K189-J189)</f>
         <v/>
       </c>
@@ -17601,25 +17609,25 @@
         </is>
       </c>
       <c r="E190" s="133" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F190" s="133" t="n">
         <v>3</v>
       </c>
       <c r="G190" s="133" t="n">
-        <v>19923</v>
+        <v>20580</v>
       </c>
       <c r="H190" s="133" t="n">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="I190" s="133" t="n">
-        <v>19547</v>
+        <v>20212</v>
       </c>
       <c r="J190" s="134" t="n">
-        <v>1222.26</v>
+        <v>1225</v>
       </c>
       <c r="K190" s="134" t="n">
-        <v>1251.67</v>
+        <v>1225</v>
       </c>
       <c r="L190" s="237">
         <f>F190*(K190-J190)</f>
@@ -17632,29 +17640,29 @@
       <c r="C191" s="135" t="n"/>
       <c r="D191" s="132" t="inlineStr">
         <is>
-          <t>雙鴻(3324)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E191" s="133" t="n">
-        <v>60</v>
+        <v>214</v>
       </c>
       <c r="F191" s="133" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="G191" s="133" t="n">
-        <v>8188</v>
+        <v>11069</v>
       </c>
       <c r="H191" s="133" t="n">
-        <v>1802</v>
+        <v>2719</v>
       </c>
       <c r="I191" s="133" t="n">
-        <v>6386</v>
+        <v>8350</v>
       </c>
       <c r="J191" s="134" t="n">
-        <v>1364.62</v>
+        <v>517.22</v>
       </c>
       <c r="K191" s="134" t="n">
-        <v>1386.15</v>
+        <v>522.9400000000001</v>
       </c>
       <c r="L191" s="237">
         <f>F191*(K191-J191)</f>
@@ -17667,31 +17675,31 @@
       <c r="C192" s="135" t="n"/>
       <c r="D192" s="132" t="inlineStr">
         <is>
-          <t>智邦(2345)</t>
+          <t>雙鴻(3324)</t>
         </is>
       </c>
       <c r="E192" s="133" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="F192" s="133" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G192" s="133" t="n">
-        <v>4268</v>
+        <v>8250</v>
       </c>
       <c r="H192" s="133" t="n">
-        <v>25</v>
+        <v>1925</v>
       </c>
       <c r="I192" s="133" t="n">
-        <v>4243</v>
+        <v>6325</v>
       </c>
       <c r="J192" s="134" t="n">
-        <v>2246.47</v>
+        <v>1375</v>
       </c>
       <c r="K192" s="134" t="n">
-        <v>252</v>
-      </c>
-      <c r="L192" s="236">
+        <v>1375</v>
+      </c>
+      <c r="L192" s="237">
         <f>F192*(K192-J192)</f>
         <v/>
       </c>
@@ -17702,31 +17710,31 @@
       <c r="C193" s="135" t="n"/>
       <c r="D193" s="132" t="inlineStr">
         <is>
-          <t>南亞(1303)</t>
+          <t>金居(8358)</t>
         </is>
       </c>
       <c r="E193" s="133" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F193" s="133" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="G193" s="133" t="n">
-        <v>3867</v>
+        <v>4058</v>
       </c>
       <c r="H193" s="133" t="n">
-        <v>1838</v>
+        <v>3595</v>
       </c>
       <c r="I193" s="133" t="n">
-        <v>2029</v>
+        <v>463</v>
       </c>
       <c r="J193" s="134" t="n">
-        <v>444.47</v>
+        <v>527.04</v>
       </c>
       <c r="K193" s="134" t="n">
-        <v>353.52</v>
-      </c>
-      <c r="L193" s="236">
+        <v>528.6900000000001</v>
+      </c>
+      <c r="L193" s="237">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -17737,29 +17745,29 @@
       <c r="C194" s="135" t="n"/>
       <c r="D194" s="132" t="inlineStr">
         <is>
-          <t>緯穎(6669)</t>
+          <t>台虹(8039)</t>
         </is>
       </c>
       <c r="E194" s="133" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="F194" s="133" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G194" s="133" t="n">
-        <v>3825</v>
+        <v>3430</v>
       </c>
       <c r="H194" s="133" t="n">
-        <v>3271</v>
+        <v>1959</v>
       </c>
       <c r="I194" s="133" t="n">
-        <v>554</v>
+        <v>1471</v>
       </c>
       <c r="J194" s="134" t="n">
-        <v>7649.2</v>
+        <v>623.58</v>
       </c>
       <c r="K194" s="134" t="n">
-        <v>8177.75</v>
+        <v>1088.33</v>
       </c>
       <c r="L194" s="237">
         <f>F194*(K194-J194)</f>
@@ -17772,29 +17780,29 @@
       <c r="C195" s="135" t="n"/>
       <c r="D195" s="132" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>旺矽(6223)</t>
         </is>
       </c>
       <c r="E195" s="133" t="n">
-        <v>211</v>
+        <v>6</v>
       </c>
       <c r="F195" s="133" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="G195" s="133" t="n">
-        <v>2893</v>
+        <v>3243</v>
       </c>
       <c r="H195" s="133" t="n">
-        <v>1231</v>
+        <v>635</v>
       </c>
       <c r="I195" s="133" t="n">
-        <v>1662</v>
+        <v>2608</v>
       </c>
       <c r="J195" s="134" t="n">
-        <v>137.1</v>
+        <v>5404.33</v>
       </c>
       <c r="K195" s="134" t="n">
-        <v>236.73</v>
+        <v>6354</v>
       </c>
       <c r="L195" s="237">
         <f>F195*(K195-J195)</f>
@@ -17807,29 +17815,29 @@
       <c r="C196" s="135" t="n"/>
       <c r="D196" s="132" t="inlineStr">
         <is>
-          <t>大量(3167)</t>
+          <t>大立光(3008)</t>
         </is>
       </c>
       <c r="E196" s="133" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F196" s="133" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G196" s="133" t="n">
-        <v>2657</v>
+        <v>3187</v>
       </c>
       <c r="H196" s="133" t="n">
-        <v>1678</v>
+        <v>208</v>
       </c>
       <c r="I196" s="133" t="n">
-        <v>979</v>
+        <v>2979</v>
       </c>
       <c r="J196" s="134" t="n">
-        <v>805.09</v>
+        <v>7966.75</v>
       </c>
       <c r="K196" s="134" t="n">
-        <v>798.86</v>
+        <v>2081</v>
       </c>
       <c r="L196" s="236">
         <f>F196*(K196-J196)</f>
@@ -17846,27 +17854,27 @@
         </is>
       </c>
       <c r="E197" s="133" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F197" s="133" t="n">
         <v>1</v>
       </c>
       <c r="G197" s="133" t="n">
-        <v>2423</v>
+        <v>2475</v>
       </c>
       <c r="H197" s="133" t="n">
         <v>28</v>
       </c>
       <c r="I197" s="133" t="n">
-        <v>2395</v>
+        <v>2447</v>
       </c>
       <c r="J197" s="134" t="n">
-        <v>278.51</v>
+        <v>278.04</v>
       </c>
       <c r="K197" s="134" t="n">
-        <v>278</v>
-      </c>
-      <c r="L197" s="236">
+        <v>282</v>
+      </c>
+      <c r="L197" s="237">
         <f>F197*(K197-J197)</f>
         <v/>
       </c>
@@ -17877,29 +17885,29 @@
       <c r="C198" s="135" t="n"/>
       <c r="D198" s="132" t="inlineStr">
         <is>
-          <t>金居(8358)</t>
+          <t>聯亞(3081)</t>
         </is>
       </c>
       <c r="E198" s="133" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="F198" s="133" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G198" s="133" t="n">
-        <v>2096</v>
+        <v>2470</v>
       </c>
       <c r="H198" s="133" t="n">
-        <v>490</v>
+        <v>393</v>
       </c>
       <c r="I198" s="133" t="n">
-        <v>1606</v>
+        <v>2077</v>
       </c>
       <c r="J198" s="134" t="n">
-        <v>523.9</v>
+        <v>3528.29</v>
       </c>
       <c r="K198" s="134" t="n">
-        <v>544.89</v>
+        <v>3926</v>
       </c>
       <c r="L198" s="237">
         <f>F198*(K198-J198)</f>
@@ -28508,7 +28516,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-01 22:59 TW | 17/17 success | 來源: 富邦17/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-02 01:42 TW | 17/17 success | 來源: 富邦17/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -1238,12 +1238,12 @@
     <comment ref="D17" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「陳族元」獨佔比 63.6%
-  • 領頭金額 79,367 萬
-  • 合計淨買 124,822 萬
+領頭大戶「陳族元」獨佔比 63.4%
+  • 領頭金額 78,702 萬
+  • 合計淨買 124,157 萬
   • 大戶數 10 位 (名義共識)
 判讀: 名義 10 位大戶共識,
-實質 1 人下注佔 64%,
+實質 1 人下注佔 63%,
 剩餘 9 位為陪襯小單,
 真共識訊號被稀釋.</t>
       </text>
@@ -1264,9 +1264,9 @@
     <comment ref="D20" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「張濬安(航海王)」獨佔比 54.3%
+領頭大戶「張濬安(航海王)」獨佔比 53.6%
   • 領頭金額 24,904 萬
-  • 合計淨買 45,905 萬
+  • 合計淨買 46,428 萬
   • 大戶數 11 位 (名義共識)
 判讀: 名義 11 位大戶共識,
 實質 1 人下注佔 54%,
@@ -1794,33 +1794,33 @@
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
+          <t>張濬安</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>21508</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>陳律師</t>
+        </is>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>21175</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>陳族元</t>
         </is>
       </c>
-      <c r="H16" s="17" t="n">
-        <v>26403</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>張濬安</t>
-        </is>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>21508</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>陳律師</t>
-        </is>
-      </c>
       <c r="L16" s="18" t="n">
-        <v>21175</v>
+        <v>19716</v>
       </c>
       <c r="M16" s="19" t="n">
         <v>9</v>
       </c>
       <c r="N16" s="17" t="n">
-        <v>159590</v>
+        <v>152902</v>
       </c>
     </row>
     <row r="17">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="H17" s="17" t="n">
-        <v>79368</v>
+        <v>78703</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>7</v>
       </c>
       <c r="N17" s="17" t="n">
-        <v>124823</v>
+        <v>124158</v>
       </c>
     </row>
     <row r="18">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="H18" s="17" t="n">
-        <v>13145</v>
+        <v>13887</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>10</v>
       </c>
       <c r="N18" s="17" t="n">
-        <v>77551</v>
+        <v>78294</v>
       </c>
     </row>
     <row r="19">
@@ -1994,7 +1994,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="L20" s="18" t="n">
-        <v>3481</v>
+        <v>4004</v>
       </c>
       <c r="M20" s="19" t="n">
         <v>8</v>
       </c>
       <c r="N20" s="17" t="n">
-        <v>45905</v>
+        <v>46428</v>
       </c>
     </row>
     <row r="21">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>7366</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>強森</t>
         </is>
       </c>
-      <c r="H21" s="17" t="n">
+      <c r="J21" s="18" t="n">
         <v>6655</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>張濬安</t>
         </is>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="L21" s="18" t="n">
         <v>6323</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>陳族元</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="n">
-        <v>6188</v>
       </c>
       <c r="M21" s="19" t="n">
         <v>9</v>
       </c>
       <c r="N21" s="17" t="n">
-        <v>32855</v>
+        <v>34034</v>
       </c>
     </row>
     <row r="22">
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="L22" s="18" t="n">
-        <v>4908</v>
+        <v>4993</v>
       </c>
       <c r="M22" s="19" t="n">
         <v>10</v>
       </c>
       <c r="N22" s="17" t="n">
-        <v>32227</v>
+        <v>32312</v>
       </c>
     </row>
     <row r="23">
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="H24" s="17" t="n">
-        <v>8801</v>
+        <v>9943</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>7</v>
       </c>
       <c r="N24" s="17" t="n">
-        <v>27677</v>
+        <v>28819</v>
       </c>
     </row>
     <row r="25">
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="E25" s="14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
@@ -2276,10 +2276,10 @@
         <v>1491</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N25" s="17" t="n">
-        <v>21402</v>
+        <v>20948</v>
       </c>
     </row>
     <row r="26">
@@ -2300,7 +2300,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
@@ -2312,25 +2312,25 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>強森</t>
         </is>
       </c>
       <c r="J26" s="18" t="n">
-        <v>3291</v>
+        <v>1871</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>強森</t>
+          <t>竹科主力分點</t>
         </is>
       </c>
       <c r="L26" s="18" t="n">
-        <v>1871</v>
+        <v>1292</v>
       </c>
       <c r="M26" s="19" t="n">
         <v>7</v>
       </c>
       <c r="N26" s="17" t="n">
-        <v>15758</v>
+        <v>13312</v>
       </c>
     </row>
     <row r="27">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H27" s="17" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>7</v>
       </c>
       <c r="N27" s="17" t="n">
-        <v>2600</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="G30" s="208" t="n">
-        <v>-18.87241</v>
+        <v>-23.49664</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
@@ -2415,7 +2415,7 @@
           <t>Q3 強共識股</t>
         </is>
       </c>
-      <c r="C31" s="242" t="n">
+      <c r="C31" s="209" t="n">
         <v>12</v>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -2423,8 +2423,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G31" s="243" t="n">
-        <v>0.2093965494893468</v>
+      <c r="G31" s="210" t="n">
+        <v>0.2092273806982912</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2535,11 +2535,11 @@
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>1489239</v>
+        <v>1479730</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="H38" s="33" t="n">
-        <v>234608</v>
+        <v>234024</v>
       </c>
       <c r="I38" s="212" t="n">
         <v>0.0271</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>巨人傑</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>巨人傑 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>4 檔</t>
+          <t>3 檔</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
-          <t>巨人傑</t>
+          <t>布哥/n_nchang</t>
         </is>
       </c>
       <c r="D47" s="40" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="E47" s="40" t="inlineStr">
         <is>
-          <t>巨人傑 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>布哥/n_nchang 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F47" s="40" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>布哥/n_nchang</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>布哥/n_nchang 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>林滄海 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D49" s="40" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E49" s="40" t="inlineStr">
         <is>
-          <t>林滄海 今日買進 3 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 3 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F49" s="40" t="inlineStr">
@@ -2915,11 +2915,11 @@
         <v>31</v>
       </c>
       <c r="E56" t="n">
-        <v>1344709</v>
+        <v>1341522</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>陳族元 連續 31 天加碼 3008 (累計 1,344,709 萬)</t>
+          <t>陳族元 連續 31 天加碼 3008 (累計 1,341,522 萬)</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="C64" s="33" t="n">
-        <v>1447590</v>
+        <v>1437897</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>124513</v>
+        <v>123706</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="G64" s="33" t="n">
-        <v>108644</v>
+        <v>107986</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>94068</v>
       </c>
       <c r="J64" s="213" t="n">
-        <v>0.2260477669617202</v>
+        <v>0.2265536339678389</v>
       </c>
     </row>
     <row r="65">
@@ -5011,7 +5011,7 @@
     <row r="36" ht="22" customHeight="1">
       <c r="C36" s="70" t="inlineStr">
         <is>
-          <t>-19 億 淨買</t>
+          <t>-23 億 淨買</t>
         </is>
       </c>
     </row>
@@ -17580,19 +17580,19 @@
         <v>98</v>
       </c>
       <c r="G189" s="133" t="n">
-        <v>29518</v>
+        <v>28712</v>
       </c>
       <c r="H189" s="133" t="n">
-        <v>9516</v>
+        <v>9406</v>
       </c>
       <c r="I189" s="133" t="n">
-        <v>20002</v>
+        <v>19306</v>
       </c>
       <c r="J189" s="134" t="n">
-        <v>971</v>
+        <v>944.46</v>
       </c>
       <c r="K189" s="134" t="n">
-        <v>971</v>
+        <v>959.85</v>
       </c>
       <c r="L189" s="237">
         <f>F189*(K189-J189)</f>
@@ -17615,19 +17615,19 @@
         <v>3</v>
       </c>
       <c r="G190" s="133" t="n">
-        <v>20580</v>
+        <v>19923</v>
       </c>
       <c r="H190" s="133" t="n">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="I190" s="133" t="n">
-        <v>20212</v>
+        <v>19547</v>
       </c>
       <c r="J190" s="134" t="n">
-        <v>1225</v>
+        <v>1185.88</v>
       </c>
       <c r="K190" s="134" t="n">
-        <v>1225</v>
+        <v>1251.67</v>
       </c>
       <c r="L190" s="237">
         <f>F190*(K190-J190)</f>
@@ -17640,31 +17640,31 @@
       <c r="C191" s="135" t="n"/>
       <c r="D191" s="132" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>雙鴻(3324)</t>
         </is>
       </c>
       <c r="E191" s="133" t="n">
-        <v>214</v>
+        <v>60</v>
       </c>
       <c r="F191" s="133" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="G191" s="133" t="n">
-        <v>11069</v>
+        <v>8188</v>
       </c>
       <c r="H191" s="133" t="n">
-        <v>2719</v>
+        <v>1802</v>
       </c>
       <c r="I191" s="133" t="n">
-        <v>8350</v>
+        <v>6386</v>
       </c>
       <c r="J191" s="134" t="n">
-        <v>517.22</v>
+        <v>1364.62</v>
       </c>
       <c r="K191" s="134" t="n">
-        <v>522.9400000000001</v>
-      </c>
-      <c r="L191" s="237">
+        <v>1287.14</v>
+      </c>
+      <c r="L191" s="236">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -17675,31 +17675,31 @@
       <c r="C192" s="135" t="n"/>
       <c r="D192" s="132" t="inlineStr">
         <is>
-          <t>雙鴻(3324)</t>
+          <t>智邦(2345)</t>
         </is>
       </c>
       <c r="E192" s="133" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F192" s="133" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G192" s="133" t="n">
-        <v>8250</v>
+        <v>4268</v>
       </c>
       <c r="H192" s="133" t="n">
-        <v>1925</v>
+        <v>25</v>
       </c>
       <c r="I192" s="133" t="n">
-        <v>6325</v>
+        <v>4243</v>
       </c>
       <c r="J192" s="134" t="n">
-        <v>1375</v>
+        <v>2246.47</v>
       </c>
       <c r="K192" s="134" t="n">
-        <v>1375</v>
-      </c>
-      <c r="L192" s="237">
+        <v>252</v>
+      </c>
+      <c r="L192" s="236">
         <f>F192*(K192-J192)</f>
         <v/>
       </c>
@@ -17710,29 +17710,29 @@
       <c r="C193" s="135" t="n"/>
       <c r="D193" s="132" t="inlineStr">
         <is>
-          <t>金居(8358)</t>
+          <t>南亞(1303)</t>
         </is>
       </c>
       <c r="E193" s="133" t="n">
+        <v>164</v>
+      </c>
+      <c r="F193" s="133" t="n">
         <v>77</v>
       </c>
-      <c r="F193" s="133" t="n">
-        <v>68</v>
-      </c>
       <c r="G193" s="133" t="n">
-        <v>4058</v>
+        <v>3867</v>
       </c>
       <c r="H193" s="133" t="n">
-        <v>3595</v>
+        <v>1838</v>
       </c>
       <c r="I193" s="133" t="n">
-        <v>463</v>
+        <v>2029</v>
       </c>
       <c r="J193" s="134" t="n">
-        <v>527.04</v>
+        <v>235.79</v>
       </c>
       <c r="K193" s="134" t="n">
-        <v>528.6900000000001</v>
+        <v>238.74</v>
       </c>
       <c r="L193" s="237">
         <f>F193*(K193-J193)</f>
@@ -17745,29 +17745,29 @@
       <c r="C194" s="135" t="n"/>
       <c r="D194" s="132" t="inlineStr">
         <is>
-          <t>台虹(8039)</t>
+          <t>緯穎(6669)</t>
         </is>
       </c>
       <c r="E194" s="133" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="F194" s="133" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G194" s="133" t="n">
-        <v>3430</v>
+        <v>3825</v>
       </c>
       <c r="H194" s="133" t="n">
-        <v>1959</v>
+        <v>3271</v>
       </c>
       <c r="I194" s="133" t="n">
-        <v>1471</v>
+        <v>554</v>
       </c>
       <c r="J194" s="134" t="n">
-        <v>623.58</v>
+        <v>7649.2</v>
       </c>
       <c r="K194" s="134" t="n">
-        <v>1088.33</v>
+        <v>8177.75</v>
       </c>
       <c r="L194" s="237">
         <f>F194*(K194-J194)</f>
@@ -17780,31 +17780,31 @@
       <c r="C195" s="135" t="n"/>
       <c r="D195" s="132" t="inlineStr">
         <is>
-          <t>旺矽(6223)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E195" s="133" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="F195" s="133" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G195" s="133" t="n">
-        <v>3243</v>
+        <v>2893</v>
       </c>
       <c r="H195" s="133" t="n">
-        <v>635</v>
+        <v>1231</v>
       </c>
       <c r="I195" s="133" t="n">
-        <v>2608</v>
+        <v>1662</v>
       </c>
       <c r="J195" s="134" t="n">
-        <v>5404.33</v>
+        <v>516.59</v>
       </c>
       <c r="K195" s="134" t="n">
-        <v>6354</v>
-      </c>
-      <c r="L195" s="237">
+        <v>512.92</v>
+      </c>
+      <c r="L195" s="236">
         <f>F195*(K195-J195)</f>
         <v/>
       </c>
@@ -17815,29 +17815,29 @@
       <c r="C196" s="135" t="n"/>
       <c r="D196" s="132" t="inlineStr">
         <is>
-          <t>大立光(3008)</t>
+          <t>大量(3167)</t>
         </is>
       </c>
       <c r="E196" s="133" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F196" s="133" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G196" s="133" t="n">
-        <v>3187</v>
+        <v>2657</v>
       </c>
       <c r="H196" s="133" t="n">
-        <v>208</v>
+        <v>1678</v>
       </c>
       <c r="I196" s="133" t="n">
-        <v>2979</v>
+        <v>979</v>
       </c>
       <c r="J196" s="134" t="n">
-        <v>7966.75</v>
+        <v>805.09</v>
       </c>
       <c r="K196" s="134" t="n">
-        <v>2081</v>
+        <v>798.86</v>
       </c>
       <c r="L196" s="236">
         <f>F196*(K196-J196)</f>
@@ -17850,29 +17850,29 @@
       <c r="C197" s="135" t="n"/>
       <c r="D197" s="132" t="inlineStr">
         <is>
-          <t>晶豪科(3006)</t>
+          <t>金居(8358)</t>
         </is>
       </c>
       <c r="E197" s="133" t="n">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="F197" s="133" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G197" s="133" t="n">
-        <v>2475</v>
+        <v>2096</v>
       </c>
       <c r="H197" s="133" t="n">
-        <v>28</v>
+        <v>490</v>
       </c>
       <c r="I197" s="133" t="n">
-        <v>2447</v>
+        <v>1606</v>
       </c>
       <c r="J197" s="134" t="n">
-        <v>278.04</v>
+        <v>523.9</v>
       </c>
       <c r="K197" s="134" t="n">
-        <v>282</v>
+        <v>544.89</v>
       </c>
       <c r="L197" s="237">
         <f>F197*(K197-J197)</f>
@@ -17885,31 +17885,31 @@
       <c r="C198" s="135" t="n"/>
       <c r="D198" s="132" t="inlineStr">
         <is>
-          <t>聯亞(3081)</t>
+          <t>頎邦(6147)</t>
         </is>
       </c>
       <c r="E198" s="133" t="n">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="F198" s="133" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G198" s="133" t="n">
-        <v>2470</v>
+        <v>2072</v>
       </c>
       <c r="H198" s="133" t="n">
-        <v>393</v>
+        <v>440</v>
       </c>
       <c r="I198" s="133" t="n">
-        <v>2077</v>
+        <v>1632</v>
       </c>
       <c r="J198" s="134" t="n">
-        <v>3528.29</v>
+        <v>183.37</v>
       </c>
       <c r="K198" s="134" t="n">
-        <v>3926</v>
-      </c>
-      <c r="L198" s="237">
+        <v>183.25</v>
+      </c>
+      <c r="L198" s="236">
         <f>F198*(K198-J198)</f>
         <v/>
       </c>
@@ -28516,7 +28516,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-02 01:42 TW | 17/17 success | 來源: 富邦17/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-02 02:15 TW | 17/17 success | 來源: 富邦17/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="G31" s="210" t="n">
-        <v>0.2092273806982912</v>
+        <v>0.2096115874434546</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -28516,7 +28516,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-02 02:15 TW | 17/17 success | 來源: 富邦17/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-02 03:12 TW | 17/17 success | 來源: 富邦17/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="20">
+  <numFmts count="22">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨-177/5d-99)&quot;;-0&quot; 億 (昨-177/5d-99)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +63億 &quot;&quot;(昨15/5d11)&quot;"/>
@@ -43,6 +43,8 @@
     <numFmt numFmtId="181" formatCode="0&quot; 檔 +120億 &quot;&quot;(昨12/5d11)&quot;"/>
     <numFmt numFmtId="182" formatCode="0.0%&quot; 市-1611億 &quot;&quot;(昨21/5d19)&quot;"/>
     <numFmt numFmtId="183" formatCode="&quot;📅 明日預測 ↕ 中性 &quot;0.0&quot;% 信心 — P/C Ratio 主推 — 3 檔焦點&quot;"/>
+    <numFmt numFmtId="184" formatCode="0&quot; 檔 +121億 &quot;&quot;(昨12/5d11)&quot;"/>
+    <numFmt numFmtId="185" formatCode="0.0%&quot; 市-1608億 &quot;&quot;(昨21/5d19)&quot;"/>
   </numFmts>
   <fonts count="53">
     <font>
@@ -613,7 +615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="254">
+  <cellXfs count="256">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1206,6 +1208,12 @@
     <xf numFmtId="0" fontId="51" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="184" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1655,7 +1663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N142"/>
+  <dimension ref="B2:N141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1891,10 +1899,10 @@
         </is>
       </c>
       <c r="E17" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G17" s="16" t="inlineStr">
         <is>
@@ -1921,10 +1929,10 @@
         <v>40732</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N17" s="17" t="n">
-        <v>256864</v>
+        <v>268406</v>
       </c>
     </row>
     <row r="18">
@@ -2659,23 +2667,23 @@
         <v>10</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>2382</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>強森</t>
         </is>
       </c>
-      <c r="H32" s="17" t="n">
+      <c r="J32" s="18" t="n">
         <v>1370</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>陳族元</t>
-        </is>
-      </c>
-      <c r="J32" s="18" t="n">
-        <v>949</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2689,7 +2697,7 @@
         <v>7</v>
       </c>
       <c r="N32" s="17" t="n">
-        <v>5185</v>
+        <v>6618</v>
       </c>
     </row>
     <row r="33">
@@ -2758,10 +2766,10 @@
         </is>
       </c>
       <c r="E34" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
@@ -2788,10 +2796,10 @@
         <v>132</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N34" s="17" t="n">
-        <v>1608</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -2816,7 +2824,7 @@
         </is>
       </c>
       <c r="G37" s="244" t="n">
-        <v>-151.23464</v>
+        <v>-148.32073</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
@@ -2825,7 +2833,7 @@
           <t>Q3 強共識股</t>
         </is>
       </c>
-      <c r="C38" s="245" t="n">
+      <c r="C38" s="254" t="n">
         <v>19</v>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -2833,8 +2841,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G38" s="246" t="n">
-        <v>0.2027315599898919</v>
+      <c r="G38" s="255" t="n">
+        <v>0.2035157242394799</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
@@ -2917,7 +2925,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2945,11 +2953,11 @@
         </is>
       </c>
       <c r="D45" s="33" t="n">
-        <v>929828</v>
+        <v>951729</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2961,7 +2969,7 @@
         </is>
       </c>
       <c r="H45" s="33" t="n">
-        <v>256864</v>
+        <v>268406</v>
       </c>
       <c r="I45" s="234" t="n">
         <v>-0.009300000000000001</v>
@@ -2981,7 +2989,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -3013,7 +3021,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -3045,7 +3053,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -3213,22 +3221,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>Tradow</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 5 檔新標的 (過去從沒買過)</t>
+          <t>Tradow 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>5 檔</t>
+          <t>4 檔</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3248,7 @@
       </c>
       <c r="C58" s="40" t="inlineStr">
         <is>
-          <t>Tradow</t>
+          <t>竹科主力分點</t>
         </is>
       </c>
       <c r="D58" s="40" t="inlineStr">
@@ -3250,7 +3258,7 @@
       </c>
       <c r="E58" s="40" t="inlineStr">
         <is>
-          <t>Tradow 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>竹科主力分點 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F58" s="40" t="inlineStr">
@@ -3267,7 +3275,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>竹科主力分點</t>
+          <t>蔣承翰</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3277,7 +3285,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>竹科主力分點 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>蔣承翰 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3294,7 +3302,7 @@
       </c>
       <c r="C60" s="40" t="inlineStr">
         <is>
-          <t>蔣承翰</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D60" s="40" t="inlineStr">
@@ -3304,7 +3312,7 @@
       </c>
       <c r="E60" s="40" t="inlineStr">
         <is>
-          <t>蔣承翰 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F60" s="40" t="inlineStr">
@@ -3648,7 +3656,7 @@
         </is>
       </c>
       <c r="C77" s="33" t="n">
-        <v>877076</v>
+        <v>900821</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3675,7 +3683,7 @@
         <v>76726</v>
       </c>
       <c r="J77" s="213" t="n">
-        <v>0.2905248472737998</v>
+        <v>0.28286672585709</v>
       </c>
     </row>
     <row r="78">
@@ -4088,7 +4096,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="B90" s="57" t="inlineStr">
         <is>
-          <t>▍ G. 注意股 (資料日 20260901)</t>
+          <t>▍ G. 注意股 (資料日 20260902)</t>
         </is>
       </c>
     </row>
@@ -4122,19 +4130,19 @@
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t>047757</t>
+          <t>066185</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>南電中信5C購02</t>
+          <t>聯發科元大64購05</t>
         </is>
       </c>
       <c r="D92" t="n">
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>25.5</v>
+        <v>1.64</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4145,19 +4153,19 @@
     <row r="93">
       <c r="B93" s="40" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>069544</t>
         </is>
       </c>
       <c r="C93" s="40" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>立隆電元大5B購05</t>
         </is>
       </c>
       <c r="D93" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E93" s="40" t="n">
-        <v>15.65</v>
+        <v>0.14</v>
       </c>
       <c r="F93" s="40" t="inlineStr">
         <is>
@@ -4168,69 +4176,69 @@
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>鼎元</t>
         </is>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>1225</v>
+        <v>104.5</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>43.97</t>
+          <t>1045.00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="40" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="C95" s="40" t="inlineStr">
         <is>
-          <t>鼎元</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="D95" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E95" s="40" t="n">
-        <v>107.5</v>
+        <v>542</v>
       </c>
       <c r="F95" s="40" t="inlineStr">
         <is>
-          <t>1075.00</t>
+          <t>132.84</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>冠西電</t>
         </is>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>524</v>
+        <v>104</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>128.43</t>
+          <t>66.24</t>
         </is>
       </c>
     </row>
@@ -4249,980 +4257,957 @@
         <v>1</v>
       </c>
       <c r="E97" s="40" t="n">
-        <v>7580</v>
+        <v>7810</v>
       </c>
       <c r="F97" s="40" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>41.54</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>971</v>
+        <v>1050</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>64.65</t>
+          <t>28.41</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="40" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="C99" s="40" t="inlineStr">
         <is>
-          <t>蔚華科</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="D99" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E99" s="40" t="n">
-        <v>129.5</v>
+        <v>602</v>
       </c>
       <c r="F99" s="40" t="inlineStr">
         <is>
-          <t>-----</t>
+          <t>122.11</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="D100" t="n">
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>874</v>
+        <v>34.15</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>162.15</t>
+          <t>-----</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="40" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="C101" s="40" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="D101" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E101" s="40" t="n">
-        <v>1005</v>
+        <v>92.2</v>
       </c>
       <c r="F101" s="40" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>40.09</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="D102" t="n">
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>625</v>
+        <v>331</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>126.77</t>
+          <t>41.07</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="40" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="C103" s="40" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="D103" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E103" s="40" t="n">
-        <v>81.90000000000001</v>
+        <v>313.5</v>
       </c>
       <c r="F103" s="40" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>99.52</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="D104" t="n">
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>34</v>
+        <v>45.95</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-----</t>
+          <t>13.32</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" s="40" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>911608</t>
         </is>
       </c>
       <c r="C105" s="40" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>明輝-DR</t>
         </is>
       </c>
       <c r="D105" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E105" s="40" t="n">
-        <v>7800</v>
+        <v>2.72</v>
       </c>
       <c r="F105" s="40" t="inlineStr">
         <is>
-          <t>25.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" t="n">
-        <v>2285</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>48.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="22" customHeight="1">
-      <c r="B108" s="4" t="inlineStr">
+          <t>-----</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260902)</t>
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>借券張數</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>融券張數</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+    </row>
     <row r="109">
-      <c r="B109" s="12" t="inlineStr">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>00685L</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>群益臺灣加權正2</t>
+        </is>
+      </c>
+      <c r="D109" s="33" t="n">
+        <v>30217</v>
+      </c>
+      <c r="E109" s="33" t="n">
+        <v>521</v>
+      </c>
+      <c r="F109" s="215" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="40" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C110" s="40" t="inlineStr">
+        <is>
+          <t>台新新光金</t>
+        </is>
+      </c>
+      <c r="D110" s="60" t="n">
+        <v>16341</v>
+      </c>
+      <c r="E110" s="60" t="n">
+        <v>69</v>
+      </c>
+      <c r="F110" s="216" t="n">
+        <v>236.83</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>00712</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>復華富時不動產</t>
+        </is>
+      </c>
+      <c r="D111" s="33" t="n">
+        <v>7743</v>
+      </c>
+      <c r="E111" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="40" t="inlineStr">
+        <is>
+          <t>00673R</t>
+        </is>
+      </c>
+      <c r="C112" s="40" t="inlineStr">
+        <is>
+          <t>期元大S&amp;P原油反1</t>
+        </is>
+      </c>
+      <c r="D112" s="60" t="n">
+        <v>6645</v>
+      </c>
+      <c r="E112" s="60" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F112" s="216" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="D113" s="33" t="n">
+        <v>6239</v>
+      </c>
+      <c r="E113" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="F113" s="215" t="n">
+        <v>129.98</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="40" t="inlineStr">
+        <is>
+          <t>00918</t>
+        </is>
+      </c>
+      <c r="C114" s="40" t="inlineStr">
+        <is>
+          <t>大華優利高填息30</t>
+        </is>
+      </c>
+      <c r="D114" s="60" t="n">
+        <v>6004</v>
+      </c>
+      <c r="E114" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2801</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>彰銀</t>
+        </is>
+      </c>
+      <c r="D115" s="33" t="n">
+        <v>4623</v>
+      </c>
+      <c r="E115" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="F115" s="215" t="n">
+        <v>420.27</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="40" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="C116" s="40" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="D116" s="60" t="n">
+        <v>4265</v>
+      </c>
+      <c r="E116" s="60" t="n">
+        <v>324</v>
+      </c>
+      <c r="F116" s="216" t="n">
+        <v>13.16</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>00919</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>群益台灣精選高息</t>
+        </is>
+      </c>
+      <c r="D117" s="33" t="n">
+        <v>4195</v>
+      </c>
+      <c r="E117" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F117" s="215" t="n">
+        <v>599.29</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="40" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="C118" s="40" t="inlineStr">
+        <is>
+          <t>和桐</t>
+        </is>
+      </c>
+      <c r="D118" s="60" t="n">
+        <v>4177</v>
+      </c>
+      <c r="E118" s="60" t="n">
+        <v>104</v>
+      </c>
+      <c r="F118" s="216" t="n">
+        <v>40.16</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="D119" s="33" t="n">
+        <v>4078</v>
+      </c>
+      <c r="E119" s="33" t="n">
+        <v>53</v>
+      </c>
+      <c r="F119" s="215" t="n">
+        <v>76.94</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="40" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C120" s="40" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D120" s="60" t="n">
+        <v>4043</v>
+      </c>
+      <c r="E120" s="60" t="n">
+        <v>17</v>
+      </c>
+      <c r="F120" s="216" t="n">
+        <v>237.82</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="43" t="inlineStr">
+        <is>
+          <t>🔴 2002</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>中鋼</t>
+        </is>
+      </c>
+      <c r="D121" s="33" t="n">
+        <v>3921</v>
+      </c>
+      <c r="E121" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F121" s="252" t="n">
+        <v>1960.5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="40" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="C122" s="40" t="inlineStr">
+        <is>
+          <t>主動統一升級50</t>
+        </is>
+      </c>
+      <c r="D122" s="60" t="n">
+        <v>3651</v>
+      </c>
+      <c r="E122" s="60" t="n">
+        <v>165</v>
+      </c>
+      <c r="F122" s="216" t="n">
+        <v>22.13</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="D123" s="33" t="n">
+        <v>3364</v>
+      </c>
+      <c r="E123" s="33" t="n">
+        <v>47</v>
+      </c>
+      <c r="F123" s="215" t="n">
+        <v>71.56999999999999</v>
+      </c>
+    </row>
+    <row r="125" ht="22" customHeight="1">
+      <c r="B125" s="62" t="inlineStr">
+        <is>
+          <t>▍ I. 未來 30 天除權息 (有效 91 檔, 已剔除過期)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="58" t="inlineStr">
+        <is>
+          <t>除權息日</t>
+        </is>
+      </c>
+      <c r="C126" s="58" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C109" s="12" t="inlineStr">
+      <c r="D126" s="58" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D109" s="12" t="inlineStr">
-        <is>
-          <t>借券張數</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="inlineStr">
-        <is>
-          <t>融券張數</t>
-        </is>
-      </c>
-      <c r="F109" s="12" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="D110" s="33" t="n">
-        <v>30217</v>
-      </c>
-      <c r="E110" s="33" t="n">
-        <v>521</v>
-      </c>
-      <c r="F110" s="215" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="40" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C111" s="40" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D111" s="60" t="n">
-        <v>16341</v>
-      </c>
-      <c r="E111" s="60" t="n">
-        <v>69</v>
-      </c>
-      <c r="F111" s="216" t="n">
-        <v>236.83</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>00712</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>復華富時不動產</t>
-        </is>
-      </c>
-      <c r="D112" s="33" t="n">
-        <v>7743</v>
-      </c>
-      <c r="E112" s="33" t="n">
+      <c r="E126" s="58" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="F126" s="58" t="inlineStr">
+        <is>
+          <t>現金股利</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>00406A</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>主動中信台灣收益</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>0.138</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="40" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C128" s="40" t="inlineStr">
+        <is>
+          <t>00946</t>
+        </is>
+      </c>
+      <c r="D128" s="40" t="inlineStr">
+        <is>
+          <t>群益科技高息成長</t>
+        </is>
+      </c>
+      <c r="E128" s="40" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F128" s="40" t="n">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>00953B</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>群益優選非投等債</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>0.067</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="40" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C130" s="40" t="inlineStr">
+        <is>
+          <t>00985B</t>
+        </is>
+      </c>
+      <c r="D130" s="40" t="inlineStr">
+        <is>
+          <t>群益ESG投等債0-5</t>
+        </is>
+      </c>
+      <c r="E130" s="40" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F130" s="40" t="n">
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2464</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>盟立</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>0.471403</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="40" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C132" s="40" t="inlineStr">
+        <is>
+          <t>2845</t>
+        </is>
+      </c>
+      <c r="D132" s="40" t="inlineStr">
+        <is>
+          <t>遠東銀</t>
+        </is>
+      </c>
+      <c r="E132" s="40" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F132" s="40" t="n">
+        <v>0.514</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2923</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>鼎固-KY</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="40" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C134" s="40" t="inlineStr">
+        <is>
+          <t>3013</t>
+        </is>
+      </c>
+      <c r="D134" s="40" t="inlineStr">
+        <is>
+          <t>晟銘電</t>
+        </is>
+      </c>
+      <c r="E134" s="40" t="inlineStr">
+        <is>
+          <t>權</t>
+        </is>
+      </c>
+      <c r="F134" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="B113" s="40" t="inlineStr">
-        <is>
-          <t>00673R</t>
-        </is>
-      </c>
-      <c r="C113" s="40" t="inlineStr">
-        <is>
-          <t>期元大S&amp;P原油反1</t>
-        </is>
-      </c>
-      <c r="D113" s="60" t="n">
-        <v>6645</v>
-      </c>
-      <c r="E113" s="60" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F113" s="216" t="n">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D114" s="33" t="n">
-        <v>6239</v>
-      </c>
-      <c r="E114" s="33" t="n">
-        <v>48</v>
-      </c>
-      <c r="F114" s="215" t="n">
-        <v>129.98</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="40" t="inlineStr">
-        <is>
-          <t>00918</t>
-        </is>
-      </c>
-      <c r="C115" s="40" t="inlineStr">
-        <is>
-          <t>大華優利高填息30</t>
-        </is>
-      </c>
-      <c r="D115" s="60" t="n">
-        <v>6004</v>
-      </c>
-      <c r="E115" s="60" t="n">
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>3346</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>麗清</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="40" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C136" s="40" t="inlineStr">
+        <is>
+          <t>4438</t>
+        </is>
+      </c>
+      <c r="D136" s="40" t="inlineStr">
+        <is>
+          <t>廣越</t>
+        </is>
+      </c>
+      <c r="E136" s="40" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F136" s="40" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>22.996187</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="40" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C138" s="40" t="inlineStr">
+        <is>
+          <t>6426</t>
+        </is>
+      </c>
+      <c r="D138" s="40" t="inlineStr">
+        <is>
+          <t>統新</t>
+        </is>
+      </c>
+      <c r="E138" s="40" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F138" s="40" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>權</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="D116" s="33" t="n">
-        <v>4623</v>
-      </c>
-      <c r="E116" s="33" t="n">
-        <v>11</v>
-      </c>
-      <c r="F116" s="215" t="n">
-        <v>420.27</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="40" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="C117" s="40" t="inlineStr">
-        <is>
-          <t>群創</t>
-        </is>
-      </c>
-      <c r="D117" s="60" t="n">
-        <v>4265</v>
-      </c>
-      <c r="E117" s="60" t="n">
-        <v>324</v>
-      </c>
-      <c r="F117" s="216" t="n">
-        <v>13.16</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>00919</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>群益台灣精選高息</t>
-        </is>
-      </c>
-      <c r="D118" s="33" t="n">
-        <v>4195</v>
-      </c>
-      <c r="E118" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="F118" s="215" t="n">
-        <v>599.29</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="40" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
-      </c>
-      <c r="C119" s="40" t="inlineStr">
-        <is>
-          <t>和桐</t>
-        </is>
-      </c>
-      <c r="D119" s="60" t="n">
-        <v>4177</v>
-      </c>
-      <c r="E119" s="60" t="n">
-        <v>104</v>
-      </c>
-      <c r="F119" s="216" t="n">
-        <v>40.16</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="D120" s="33" t="n">
-        <v>4078</v>
-      </c>
-      <c r="E120" s="33" t="n">
-        <v>53</v>
-      </c>
-      <c r="F120" s="215" t="n">
-        <v>76.94</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" s="40" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="C121" s="40" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D121" s="60" t="n">
-        <v>4043</v>
-      </c>
-      <c r="E121" s="60" t="n">
-        <v>17</v>
-      </c>
-      <c r="F121" s="216" t="n">
-        <v>237.82</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="B122" s="43" t="inlineStr">
-        <is>
-          <t>🔴 2002</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D122" s="33" t="n">
-        <v>3921</v>
-      </c>
-      <c r="E122" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F122" s="252" t="n">
-        <v>1960.5</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" s="40" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="C123" s="40" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="D123" s="60" t="n">
-        <v>3651</v>
-      </c>
-      <c r="E123" s="60" t="n">
-        <v>165</v>
-      </c>
-      <c r="F123" s="216" t="n">
-        <v>22.13</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D124" s="33" t="n">
-        <v>3364</v>
-      </c>
-      <c r="E124" s="33" t="n">
-        <v>47</v>
-      </c>
-      <c r="F124" s="215" t="n">
-        <v>71.56999999999999</v>
-      </c>
-    </row>
-    <row r="126" ht="22" customHeight="1">
-      <c r="B126" s="62" t="inlineStr">
-        <is>
-          <t>▍ I. 未來 30 天除權息 (有效 84 檔, 已剔除過期)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="58" t="inlineStr">
-        <is>
-          <t>除權息日</t>
-        </is>
-      </c>
-      <c r="C127" s="58" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="D127" s="58" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="E127" s="58" t="inlineStr">
-        <is>
-          <t>類型</t>
-        </is>
-      </c>
-      <c r="F127" s="58" t="inlineStr">
-        <is>
-          <t>現金股利</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" t="inlineStr">
+    </row>
+    <row r="140">
+      <c r="B140" s="40" t="inlineStr">
         <is>
           <t>20260902</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
+      <c r="C140" s="40" t="inlineStr">
+        <is>
+          <t>6753</t>
+        </is>
+      </c>
+      <c r="D140" s="40" t="inlineStr">
+        <is>
+          <t>龍德造船</t>
+        </is>
+      </c>
+      <c r="E140" s="40" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F128" t="n">
-        <v>0.138</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="B129" s="40" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C129" s="40" t="inlineStr">
-        <is>
-          <t>00946</t>
-        </is>
-      </c>
-      <c r="D129" s="40" t="inlineStr">
-        <is>
-          <t>群益科技高息成長</t>
-        </is>
-      </c>
-      <c r="E129" s="40" t="inlineStr">
+      <c r="F140" s="40" t="n">
+        <v>1.249351</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>20260903</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>味王</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F129" s="40" t="n">
-        <v>0.058</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>00953B</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>群益優選非投等債</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F130" t="n">
-        <v>0.067</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="B131" s="40" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C131" s="40" t="inlineStr">
-        <is>
-          <t>00985B</t>
-        </is>
-      </c>
-      <c r="D131" s="40" t="inlineStr">
-        <is>
-          <t>群益ESG投等債0-5</t>
-        </is>
-      </c>
-      <c r="E131" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F131" s="40" t="n">
-        <v>0.053</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2464</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>盟立</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>權息</t>
-        </is>
-      </c>
-      <c r="F132" t="n">
-        <v>0.471403</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" s="40" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C133" s="40" t="inlineStr">
-        <is>
-          <t>2845</t>
-        </is>
-      </c>
-      <c r="D133" s="40" t="inlineStr">
-        <is>
-          <t>遠東銀</t>
-        </is>
-      </c>
-      <c r="E133" s="40" t="inlineStr">
-        <is>
-          <t>權息</t>
-        </is>
-      </c>
-      <c r="F133" s="40" t="n">
-        <v>0.514</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>2923</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>鼎固-KY</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F134" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" s="40" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C135" s="40" t="inlineStr">
-        <is>
-          <t>3013</t>
-        </is>
-      </c>
-      <c r="D135" s="40" t="inlineStr">
-        <is>
-          <t>晟銘電</t>
-        </is>
-      </c>
-      <c r="E135" s="40" t="inlineStr">
-        <is>
-          <t>權</t>
-        </is>
-      </c>
-      <c r="F135" s="40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>3346</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>麗清</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F136" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="B137" s="40" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C137" s="40" t="inlineStr">
-        <is>
-          <t>4438</t>
-        </is>
-      </c>
-      <c r="D137" s="40" t="inlineStr">
-        <is>
-          <t>廣越</t>
-        </is>
-      </c>
-      <c r="E137" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F137" s="40" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>亞翔</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F138" t="n">
-        <v>22.996187</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="B139" s="40" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C139" s="40" t="inlineStr">
-        <is>
-          <t>6426</t>
-        </is>
-      </c>
-      <c r="D139" s="40" t="inlineStr">
-        <is>
-          <t>統新</t>
-        </is>
-      </c>
-      <c r="E139" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F139" s="40" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>權</t>
-        </is>
-      </c>
-      <c r="F140" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="B141" s="40" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="C141" s="40" t="inlineStr">
-        <is>
-          <t>6753</t>
-        </is>
-      </c>
-      <c r="D141" s="40" t="inlineStr">
-        <is>
-          <t>龍德造船</t>
-        </is>
-      </c>
-      <c r="E141" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F141" s="40" t="n">
-        <v>1.249351</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>20260903</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>味王</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F142" t="n">
+      <c r="F141" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5231,9 +5216,9 @@
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="B9:N9"/>
     <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B107:J107"/>
     <mergeCell ref="B40:N40"/>
     <mergeCell ref="B4:N4"/>
-    <mergeCell ref="B108:J108"/>
     <mergeCell ref="B65:J65"/>
     <mergeCell ref="B7:N7"/>
     <mergeCell ref="B3:N3"/>
@@ -5242,7 +5227,6 @@
     <mergeCell ref="B51:J51"/>
     <mergeCell ref="B36:J36"/>
     <mergeCell ref="B12:N12"/>
-    <mergeCell ref="B126:J126"/>
     <mergeCell ref="B39:N39"/>
     <mergeCell ref="B11:N11"/>
     <mergeCell ref="B42:E42"/>
@@ -5251,6 +5235,7 @@
     <mergeCell ref="B14:N14"/>
     <mergeCell ref="B90:J90"/>
     <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B125:J125"/>
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="B13:N13"/>
@@ -5329,7 +5314,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D92:D106">
+  <conditionalFormatting sqref="D92:D105">
     <cfRule type="dataBar" priority="9">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -5338,7 +5323,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D110:D124">
+  <conditionalFormatting sqref="D109:D123">
     <cfRule type="dataBar" priority="10">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -5347,7 +5332,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F110:F124">
+  <conditionalFormatting sqref="F109:F123">
     <cfRule type="dataBar" priority="11">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -5416,7 +5401,7 @@
     <row r="9">
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>② 聯發科 (2454) · 10 大戶</t>
+          <t>② 聯發科 (2454) · 11 大戶</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5513,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="C29" s="70" t="inlineStr">
         <is>
-          <t>-151 億 淨買</t>
+          <t>-148 億 淨買</t>
         </is>
       </c>
     </row>
@@ -18455,29 +18440,29 @@
       </c>
       <c r="D189" s="132" t="inlineStr">
         <is>
-          <t>全新(2455)</t>
+          <t>聯發科(2454)</t>
         </is>
       </c>
       <c r="E189" s="133" t="n">
-        <v>276</v>
+        <v>50</v>
       </c>
       <c r="F189" s="133" t="n">
-        <v>245</v>
+        <v>23</v>
       </c>
       <c r="G189" s="133" t="n">
-        <v>14958</v>
+        <v>21375</v>
       </c>
       <c r="H189" s="133" t="n">
-        <v>13291</v>
+        <v>9832</v>
       </c>
       <c r="I189" s="133" t="n">
-        <v>1667</v>
+        <v>11543</v>
       </c>
       <c r="J189" s="134" t="n">
-        <v>541.97</v>
+        <v>4275</v>
       </c>
       <c r="K189" s="134" t="n">
-        <v>542.49</v>
+        <v>4275</v>
       </c>
       <c r="L189" s="237">
         <f>F189*(K189-J189)</f>
@@ -18490,29 +18475,29 @@
       <c r="C190" s="135" t="n"/>
       <c r="D190" s="132" t="inlineStr">
         <is>
-          <t>華星光(4979)</t>
+          <t>全新(2455)</t>
         </is>
       </c>
       <c r="E190" s="133" t="n">
-        <v>90</v>
+        <v>276</v>
       </c>
       <c r="F190" s="133" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="G190" s="133" t="n">
-        <v>5539</v>
+        <v>14958</v>
       </c>
       <c r="H190" s="133" t="n">
-        <v>0</v>
+        <v>13291</v>
       </c>
       <c r="I190" s="133" t="n">
-        <v>5539</v>
+        <v>1667</v>
       </c>
       <c r="J190" s="134" t="n">
-        <v>615.4</v>
+        <v>541.97</v>
       </c>
       <c r="K190" s="134" t="n">
-        <v>0</v>
+        <v>542.49</v>
       </c>
       <c r="L190" s="237">
         <f>F190*(K190-J190)</f>
@@ -18525,29 +18510,29 @@
       <c r="C191" s="135" t="n"/>
       <c r="D191" s="132" t="inlineStr">
         <is>
-          <t>禾伸堂(3026)</t>
+          <t>華星光(4979)</t>
         </is>
       </c>
       <c r="E191" s="133" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="F191" s="133" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G191" s="133" t="n">
-        <v>4669</v>
+        <v>5539</v>
       </c>
       <c r="H191" s="133" t="n">
-        <v>1652</v>
+        <v>0</v>
       </c>
       <c r="I191" s="133" t="n">
-        <v>3017</v>
+        <v>5539</v>
       </c>
       <c r="J191" s="134" t="n">
-        <v>686.62</v>
+        <v>622.3099999999999</v>
       </c>
       <c r="K191" s="134" t="n">
-        <v>688.33</v>
+        <v>0</v>
       </c>
       <c r="L191" s="237">
         <f>F191*(K191-J191)</f>
@@ -18560,29 +18545,29 @@
       <c r="C192" s="135" t="n"/>
       <c r="D192" s="132" t="inlineStr">
         <is>
-          <t>台光電(2383)</t>
+          <t>禾伸堂(3026)</t>
         </is>
       </c>
       <c r="E192" s="133" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="F192" s="133" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G192" s="133" t="n">
-        <v>4447</v>
+        <v>4669</v>
       </c>
       <c r="H192" s="133" t="n">
-        <v>0</v>
+        <v>1652</v>
       </c>
       <c r="I192" s="133" t="n">
-        <v>4447</v>
+        <v>3017</v>
       </c>
       <c r="J192" s="134" t="n">
-        <v>5559.12</v>
+        <v>686.62</v>
       </c>
       <c r="K192" s="134" t="n">
-        <v>0</v>
+        <v>688.33</v>
       </c>
       <c r="L192" s="237">
         <f>F192*(K192-J192)</f>
@@ -18595,29 +18580,29 @@
       <c r="C193" s="135" t="n"/>
       <c r="D193" s="132" t="inlineStr">
         <is>
-          <t>南亞(1303)</t>
+          <t>台光電(2383)</t>
         </is>
       </c>
       <c r="E193" s="133" t="n">
-        <v>170</v>
+        <v>8</v>
       </c>
       <c r="F193" s="133" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="G193" s="133" t="n">
-        <v>4045</v>
+        <v>4447</v>
       </c>
       <c r="H193" s="133" t="n">
-        <v>3405</v>
+        <v>0</v>
       </c>
       <c r="I193" s="133" t="n">
-        <v>640</v>
+        <v>4447</v>
       </c>
       <c r="J193" s="134" t="n">
-        <v>237.96</v>
+        <v>5559.12</v>
       </c>
       <c r="K193" s="134" t="n">
-        <v>238.12</v>
+        <v>0</v>
       </c>
       <c r="L193" s="237">
         <f>F193*(K193-J193)</f>
@@ -18630,31 +18615,31 @@
       <c r="C194" s="135" t="n"/>
       <c r="D194" s="132" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>南亞(1303)</t>
         </is>
       </c>
       <c r="E194" s="133" t="n">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="F194" s="133" t="n">
-        <v>2</v>
+        <v>143</v>
       </c>
       <c r="G194" s="133" t="n">
-        <v>3933</v>
+        <v>4045</v>
       </c>
       <c r="H194" s="133" t="n">
-        <v>363</v>
+        <v>3405</v>
       </c>
       <c r="I194" s="133" t="n">
-        <v>3570</v>
+        <v>640</v>
       </c>
       <c r="J194" s="134" t="n">
-        <v>2458.12</v>
+        <v>237.96</v>
       </c>
       <c r="K194" s="134" t="n">
-        <v>1814</v>
-      </c>
-      <c r="L194" s="236">
+        <v>238.12</v>
+      </c>
+      <c r="L194" s="237">
         <f>F194*(K194-J194)</f>
         <v/>
       </c>
@@ -18665,31 +18650,31 @@
       <c r="C195" s="135" t="n"/>
       <c r="D195" s="132" t="inlineStr">
         <is>
-          <t>台燿(6274)</t>
+          <t>台積電(2330)</t>
         </is>
       </c>
       <c r="E195" s="133" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F195" s="133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G195" s="133" t="n">
-        <v>3635</v>
+        <v>3933</v>
       </c>
       <c r="H195" s="133" t="n">
-        <v>188</v>
+        <v>363</v>
       </c>
       <c r="I195" s="133" t="n">
-        <v>3447</v>
+        <v>3570</v>
       </c>
       <c r="J195" s="134" t="n">
-        <v>1398.04</v>
+        <v>2458.12</v>
       </c>
       <c r="K195" s="134" t="n">
-        <v>1878</v>
-      </c>
-      <c r="L195" s="237">
+        <v>1814</v>
+      </c>
+      <c r="L195" s="236">
         <f>F195*(K195-J195)</f>
         <v/>
       </c>
@@ -18700,29 +18685,29 @@
       <c r="C196" s="135" t="n"/>
       <c r="D196" s="132" t="inlineStr">
         <is>
-          <t>穩懋(3105)</t>
+          <t>台燿(6274)</t>
         </is>
       </c>
       <c r="E196" s="133" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="F196" s="133" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="G196" s="133" t="n">
-        <v>3365</v>
+        <v>3635</v>
       </c>
       <c r="H196" s="133" t="n">
-        <v>1713</v>
+        <v>188</v>
       </c>
       <c r="I196" s="133" t="n">
-        <v>1652</v>
+        <v>3447</v>
       </c>
       <c r="J196" s="134" t="n">
-        <v>467.4</v>
+        <v>1398.04</v>
       </c>
       <c r="K196" s="134" t="n">
-        <v>475.83</v>
+        <v>1878</v>
       </c>
       <c r="L196" s="237">
         <f>F196*(K196-J196)</f>
@@ -18735,29 +18720,29 @@
       <c r="C197" s="135" t="n"/>
       <c r="D197" s="132" t="inlineStr">
         <is>
-          <t>光寶科(2301)</t>
+          <t>穩懋(3105)</t>
         </is>
       </c>
       <c r="E197" s="133" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F197" s="133" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G197" s="133" t="n">
-        <v>2832</v>
+        <v>3365</v>
       </c>
       <c r="H197" s="133" t="n">
-        <v>918</v>
+        <v>1713</v>
       </c>
       <c r="I197" s="133" t="n">
-        <v>1914</v>
+        <v>1652</v>
       </c>
       <c r="J197" s="134" t="n">
-        <v>314.68</v>
+        <v>467.4</v>
       </c>
       <c r="K197" s="134" t="n">
-        <v>316.52</v>
+        <v>475.83</v>
       </c>
       <c r="L197" s="237">
         <f>F197*(K197-J197)</f>
@@ -18770,31 +18755,31 @@
       <c r="C198" s="135" t="n"/>
       <c r="D198" s="132" t="inlineStr">
         <is>
-          <t>欣興(3037)</t>
+          <t>光寶科(2301)</t>
         </is>
       </c>
       <c r="E198" s="133" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="F198" s="133" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G198" s="133" t="n">
-        <v>2550</v>
+        <v>2832</v>
       </c>
       <c r="H198" s="133" t="n">
-        <v>1919</v>
+        <v>918</v>
       </c>
       <c r="I198" s="133" t="n">
-        <v>631</v>
+        <v>1914</v>
       </c>
       <c r="J198" s="134" t="n">
-        <v>980.65</v>
+        <v>314.68</v>
       </c>
       <c r="K198" s="134" t="n">
-        <v>959.6</v>
-      </c>
-      <c r="L198" s="236">
+        <v>316.52</v>
+      </c>
+      <c r="L198" s="237">
         <f>F198*(K198-J198)</f>
         <v/>
       </c>
@@ -29258,7 +29243,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-02 21:38 TW | 9/9 success | 來源: 富邦9/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-02 22:56 TW | 9/9 success | 來源: 富邦9/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -29243,7 +29243,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-02 22:56 TW | 9/9 success | 來源: 富邦9/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-03 01:30 TW | 9/9 success | 來源: 富邦9/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -29243,7 +29243,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-03 01:30 TW | 9/9 success | 來源: 富邦9/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-03 02:19 TW | 9/9 success | 來源: 富邦9/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="22">
+  <numFmts count="23">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨-177/5d-99)&quot;;-0&quot; 億 (昨-177/5d-99)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +63億 &quot;&quot;(昨15/5d11)&quot;"/>
@@ -45,6 +45,7 @@
     <numFmt numFmtId="183" formatCode="&quot;📅 明日預測 ↕ 中性 &quot;0.0&quot;% 信心 — P/C Ratio 主推 — 3 檔焦點&quot;"/>
     <numFmt numFmtId="184" formatCode="0&quot; 檔 +121億 &quot;&quot;(昨12/5d11)&quot;"/>
     <numFmt numFmtId="185" formatCode="0.0%&quot; 市-1608億 &quot;&quot;(昨21/5d19)&quot;"/>
+    <numFmt numFmtId="186" formatCode="0.0%&quot; 市-1614億 &quot;&quot;(昨21/5d19)&quot;"/>
   </numFmts>
   <fonts count="53">
     <font>
@@ -615,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="256">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1214,6 +1215,9 @@
     <xf numFmtId="185" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="186" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1899,10 +1903,10 @@
         </is>
       </c>
       <c r="E17" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G17" s="16" t="inlineStr">
         <is>
@@ -1929,10 +1933,10 @@
         <v>40732</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N17" s="17" t="n">
-        <v>268406</v>
+        <v>256864</v>
       </c>
     </row>
     <row r="18">
@@ -2667,23 +2671,23 @@
         <v>10</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
+          <t>強森</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>1370</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>陳族元</t>
         </is>
       </c>
-      <c r="H32" s="17" t="n">
-        <v>2382</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>強森</t>
-        </is>
-      </c>
       <c r="J32" s="18" t="n">
-        <v>1370</v>
+        <v>949</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2697,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="N32" s="17" t="n">
-        <v>6618</v>
+        <v>5185</v>
       </c>
     </row>
     <row r="33">
@@ -2766,10 +2770,10 @@
         </is>
       </c>
       <c r="E34" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
@@ -2796,10 +2800,10 @@
         <v>132</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N34" s="17" t="n">
-        <v>1667</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -2824,7 +2828,7 @@
         </is>
       </c>
       <c r="G37" s="244" t="n">
-        <v>-148.32073</v>
+        <v>-151.23464</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
@@ -2833,7 +2837,7 @@
           <t>Q3 強共識股</t>
         </is>
       </c>
-      <c r="C38" s="254" t="n">
+      <c r="C38" s="245" t="n">
         <v>19</v>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -2841,8 +2845,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G38" s="255" t="n">
-        <v>0.2035157242394799</v>
+      <c r="G38" s="256" t="n">
+        <v>0.2029313523982471</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
@@ -2925,7 +2929,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2953,11 +2957,11 @@
         </is>
       </c>
       <c r="D45" s="33" t="n">
-        <v>951729</v>
+        <v>929828</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2969,7 +2973,7 @@
         </is>
       </c>
       <c r="H45" s="33" t="n">
-        <v>268406</v>
+        <v>256864</v>
       </c>
       <c r="I45" s="234" t="n">
         <v>-0.009300000000000001</v>
@@ -2989,7 +2993,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -3021,7 +3025,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -3053,7 +3057,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -3221,22 +3225,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tradow</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tradow 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>陳族元 今日買進 5 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>4 檔</t>
+          <t>5 檔</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3252,7 @@
       </c>
       <c r="C58" s="40" t="inlineStr">
         <is>
-          <t>竹科主力分點</t>
+          <t>Tradow</t>
         </is>
       </c>
       <c r="D58" s="40" t="inlineStr">
@@ -3258,7 +3262,7 @@
       </c>
       <c r="E58" s="40" t="inlineStr">
         <is>
-          <t>竹科主力分點 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>Tradow 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F58" s="40" t="inlineStr">
@@ -3275,7 +3279,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>蔣承翰</t>
+          <t>竹科主力分點</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3285,7 +3289,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>蔣承翰 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>竹科主力分點 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3302,7 +3306,7 @@
       </c>
       <c r="C60" s="40" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>蔣承翰</t>
         </is>
       </c>
       <c r="D60" s="40" t="inlineStr">
@@ -3312,7 +3316,7 @@
       </c>
       <c r="E60" s="40" t="inlineStr">
         <is>
-          <t>陳族元 今日買進 4 檔新標的 (過去從沒買過)</t>
+          <t>蔣承翰 今日買進 4 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
       <c r="F60" s="40" t="inlineStr">
@@ -3656,7 +3660,7 @@
         </is>
       </c>
       <c r="C77" s="33" t="n">
-        <v>900821</v>
+        <v>877076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3683,7 +3687,7 @@
         <v>76726</v>
       </c>
       <c r="J77" s="213" t="n">
-        <v>0.28286672585709</v>
+        <v>0.2905248472737998</v>
       </c>
     </row>
     <row r="78">
@@ -5401,7 +5405,7 @@
     <row r="9">
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>② 聯發科 (2454) · 11 大戶</t>
+          <t>② 聯發科 (2454) · 10 大戶</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5517,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="C29" s="70" t="inlineStr">
         <is>
-          <t>-148 億 淨買</t>
+          <t>-151 億 淨買</t>
         </is>
       </c>
     </row>
@@ -18440,29 +18444,29 @@
       </c>
       <c r="D189" s="132" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>全新(2455)</t>
         </is>
       </c>
       <c r="E189" s="133" t="n">
-        <v>50</v>
+        <v>276</v>
       </c>
       <c r="F189" s="133" t="n">
-        <v>23</v>
+        <v>245</v>
       </c>
       <c r="G189" s="133" t="n">
-        <v>21375</v>
+        <v>14958</v>
       </c>
       <c r="H189" s="133" t="n">
-        <v>9832</v>
+        <v>13291</v>
       </c>
       <c r="I189" s="133" t="n">
-        <v>11543</v>
+        <v>1667</v>
       </c>
       <c r="J189" s="134" t="n">
-        <v>4275</v>
+        <v>541.97</v>
       </c>
       <c r="K189" s="134" t="n">
-        <v>4275</v>
+        <v>542.49</v>
       </c>
       <c r="L189" s="237">
         <f>F189*(K189-J189)</f>
@@ -18475,29 +18479,29 @@
       <c r="C190" s="135" t="n"/>
       <c r="D190" s="132" t="inlineStr">
         <is>
-          <t>全新(2455)</t>
+          <t>華星光(4979)</t>
         </is>
       </c>
       <c r="E190" s="133" t="n">
-        <v>276</v>
+        <v>90</v>
       </c>
       <c r="F190" s="133" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="G190" s="133" t="n">
-        <v>14958</v>
+        <v>5539</v>
       </c>
       <c r="H190" s="133" t="n">
-        <v>13291</v>
+        <v>0</v>
       </c>
       <c r="I190" s="133" t="n">
-        <v>1667</v>
+        <v>5539</v>
       </c>
       <c r="J190" s="134" t="n">
-        <v>541.97</v>
+        <v>615.4</v>
       </c>
       <c r="K190" s="134" t="n">
-        <v>542.49</v>
+        <v>0</v>
       </c>
       <c r="L190" s="237">
         <f>F190*(K190-J190)</f>
@@ -18510,29 +18514,29 @@
       <c r="C191" s="135" t="n"/>
       <c r="D191" s="132" t="inlineStr">
         <is>
-          <t>華星光(4979)</t>
+          <t>禾伸堂(3026)</t>
         </is>
       </c>
       <c r="E191" s="133" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="F191" s="133" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G191" s="133" t="n">
-        <v>5539</v>
+        <v>4669</v>
       </c>
       <c r="H191" s="133" t="n">
-        <v>0</v>
+        <v>1652</v>
       </c>
       <c r="I191" s="133" t="n">
-        <v>5539</v>
+        <v>3017</v>
       </c>
       <c r="J191" s="134" t="n">
-        <v>622.3099999999999</v>
+        <v>686.62</v>
       </c>
       <c r="K191" s="134" t="n">
-        <v>0</v>
+        <v>688.33</v>
       </c>
       <c r="L191" s="237">
         <f>F191*(K191-J191)</f>
@@ -18545,29 +18549,29 @@
       <c r="C192" s="135" t="n"/>
       <c r="D192" s="132" t="inlineStr">
         <is>
-          <t>禾伸堂(3026)</t>
+          <t>台光電(2383)</t>
         </is>
       </c>
       <c r="E192" s="133" t="n">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="F192" s="133" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G192" s="133" t="n">
-        <v>4669</v>
+        <v>4447</v>
       </c>
       <c r="H192" s="133" t="n">
-        <v>1652</v>
+        <v>0</v>
       </c>
       <c r="I192" s="133" t="n">
-        <v>3017</v>
+        <v>4447</v>
       </c>
       <c r="J192" s="134" t="n">
-        <v>686.62</v>
+        <v>5559.12</v>
       </c>
       <c r="K192" s="134" t="n">
-        <v>688.33</v>
+        <v>0</v>
       </c>
       <c r="L192" s="237">
         <f>F192*(K192-J192)</f>
@@ -18580,29 +18584,29 @@
       <c r="C193" s="135" t="n"/>
       <c r="D193" s="132" t="inlineStr">
         <is>
-          <t>台光電(2383)</t>
+          <t>南亞(1303)</t>
         </is>
       </c>
       <c r="E193" s="133" t="n">
-        <v>8</v>
+        <v>170</v>
       </c>
       <c r="F193" s="133" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="G193" s="133" t="n">
-        <v>4447</v>
+        <v>4045</v>
       </c>
       <c r="H193" s="133" t="n">
-        <v>0</v>
+        <v>3405</v>
       </c>
       <c r="I193" s="133" t="n">
-        <v>4447</v>
+        <v>640</v>
       </c>
       <c r="J193" s="134" t="n">
-        <v>5559.12</v>
+        <v>237.96</v>
       </c>
       <c r="K193" s="134" t="n">
-        <v>0</v>
+        <v>238.12</v>
       </c>
       <c r="L193" s="237">
         <f>F193*(K193-J193)</f>
@@ -18615,31 +18619,31 @@
       <c r="C194" s="135" t="n"/>
       <c r="D194" s="132" t="inlineStr">
         <is>
-          <t>南亞(1303)</t>
+          <t>台積電(2330)</t>
         </is>
       </c>
       <c r="E194" s="133" t="n">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c r="F194" s="133" t="n">
-        <v>143</v>
+        <v>2</v>
       </c>
       <c r="G194" s="133" t="n">
-        <v>4045</v>
+        <v>3933</v>
       </c>
       <c r="H194" s="133" t="n">
-        <v>3405</v>
+        <v>363</v>
       </c>
       <c r="I194" s="133" t="n">
-        <v>640</v>
+        <v>3570</v>
       </c>
       <c r="J194" s="134" t="n">
-        <v>237.96</v>
+        <v>2458.12</v>
       </c>
       <c r="K194" s="134" t="n">
-        <v>238.12</v>
-      </c>
-      <c r="L194" s="237">
+        <v>1814</v>
+      </c>
+      <c r="L194" s="236">
         <f>F194*(K194-J194)</f>
         <v/>
       </c>
@@ -18650,31 +18654,31 @@
       <c r="C195" s="135" t="n"/>
       <c r="D195" s="132" t="inlineStr">
         <is>
-          <t>台積電(2330)</t>
+          <t>台燿(6274)</t>
         </is>
       </c>
       <c r="E195" s="133" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F195" s="133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G195" s="133" t="n">
-        <v>3933</v>
+        <v>3635</v>
       </c>
       <c r="H195" s="133" t="n">
-        <v>363</v>
+        <v>188</v>
       </c>
       <c r="I195" s="133" t="n">
-        <v>3570</v>
+        <v>3447</v>
       </c>
       <c r="J195" s="134" t="n">
-        <v>2458.12</v>
+        <v>1398.04</v>
       </c>
       <c r="K195" s="134" t="n">
-        <v>1814</v>
-      </c>
-      <c r="L195" s="236">
+        <v>1878</v>
+      </c>
+      <c r="L195" s="237">
         <f>F195*(K195-J195)</f>
         <v/>
       </c>
@@ -18685,29 +18689,29 @@
       <c r="C196" s="135" t="n"/>
       <c r="D196" s="132" t="inlineStr">
         <is>
-          <t>台燿(6274)</t>
+          <t>穩懋(3105)</t>
         </is>
       </c>
       <c r="E196" s="133" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="F196" s="133" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="G196" s="133" t="n">
-        <v>3635</v>
+        <v>3365</v>
       </c>
       <c r="H196" s="133" t="n">
-        <v>188</v>
+        <v>1713</v>
       </c>
       <c r="I196" s="133" t="n">
-        <v>3447</v>
+        <v>1652</v>
       </c>
       <c r="J196" s="134" t="n">
-        <v>1398.04</v>
+        <v>467.4</v>
       </c>
       <c r="K196" s="134" t="n">
-        <v>1878</v>
+        <v>475.83</v>
       </c>
       <c r="L196" s="237">
         <f>F196*(K196-J196)</f>
@@ -18720,29 +18724,29 @@
       <c r="C197" s="135" t="n"/>
       <c r="D197" s="132" t="inlineStr">
         <is>
-          <t>穩懋(3105)</t>
+          <t>光寶科(2301)</t>
         </is>
       </c>
       <c r="E197" s="133" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F197" s="133" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G197" s="133" t="n">
-        <v>3365</v>
+        <v>2832</v>
       </c>
       <c r="H197" s="133" t="n">
-        <v>1713</v>
+        <v>918</v>
       </c>
       <c r="I197" s="133" t="n">
-        <v>1652</v>
+        <v>1914</v>
       </c>
       <c r="J197" s="134" t="n">
-        <v>467.4</v>
+        <v>314.68</v>
       </c>
       <c r="K197" s="134" t="n">
-        <v>475.83</v>
+        <v>316.52</v>
       </c>
       <c r="L197" s="237">
         <f>F197*(K197-J197)</f>
@@ -18755,31 +18759,31 @@
       <c r="C198" s="135" t="n"/>
       <c r="D198" s="132" t="inlineStr">
         <is>
-          <t>光寶科(2301)</t>
+          <t>欣興(3037)</t>
         </is>
       </c>
       <c r="E198" s="133" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="F198" s="133" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G198" s="133" t="n">
-        <v>2832</v>
+        <v>2550</v>
       </c>
       <c r="H198" s="133" t="n">
-        <v>918</v>
+        <v>1919</v>
       </c>
       <c r="I198" s="133" t="n">
-        <v>1914</v>
+        <v>631</v>
       </c>
       <c r="J198" s="134" t="n">
-        <v>314.68</v>
+        <v>980.65</v>
       </c>
       <c r="K198" s="134" t="n">
-        <v>316.52</v>
-      </c>
-      <c r="L198" s="237">
+        <v>959.6</v>
+      </c>
+      <c r="L198" s="236">
         <f>F198*(K198-J198)</f>
         <v/>
       </c>
@@ -29243,7 +29247,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-03 02:19 TW | 9/9 success | 來源: 富邦9/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-03 03:16 TW | 9/9 success | 來源: 富邦9/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -2027,7 +2027,7 @@
         <v>13</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>10</v>
       </c>
       <c r="N20" s="17" t="n">
-        <v>38483</v>
+        <v>39193</v>
       </c>
     </row>
     <row r="21">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="G32" s="257" t="n">
-        <v>-199.32547</v>
+        <v>-199.54917</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G33" s="259" t="n">
-        <v>0.1702456257638463</v>
+        <v>0.1707376082472423</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2670,11 +2670,11 @@
         </is>
       </c>
       <c r="D40" s="33" t="n">
-        <v>870535</v>
+        <v>881453</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="C66" s="33" t="n">
-        <v>809114</v>
+        <v>819686</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>40121</v>
       </c>
       <c r="J66" s="213" t="n">
-        <v>0.2024861026965552</v>
+        <v>0.199874464124067</v>
       </c>
     </row>
     <row r="67">
@@ -5098,7 +5098,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="C29" s="70" t="inlineStr">
         <is>
-          <t>-199 億 淨買</t>
+          <t>-200 億 淨買</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17570,7 @@
         </is>
       </c>
       <c r="E189" s="133" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F189" s="133" t="n">
         <v>4</v>
@@ -17585,7 +17585,7 @@
         <v>36163</v>
       </c>
       <c r="J189" s="134" t="n">
-        <v>1344.34</v>
+        <v>1349.28</v>
       </c>
       <c r="K189" s="134" t="n">
         <v>1342.5</v>
@@ -17605,10 +17605,10 @@
         </is>
       </c>
       <c r="E190" s="133" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F190" s="133" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G190" s="133" t="n">
         <v>6900</v>
@@ -17620,10 +17620,10 @@
         <v>5108</v>
       </c>
       <c r="J190" s="134" t="n">
-        <v>425.9</v>
+        <v>413.15</v>
       </c>
       <c r="K190" s="134" t="n">
-        <v>448.05</v>
+        <v>416.79</v>
       </c>
       <c r="L190" s="237">
         <f>F190*(K190-J190)</f>
@@ -17640,7 +17640,7 @@
         </is>
       </c>
       <c r="E191" s="133" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F191" s="133" t="n">
         <v>15</v>
@@ -17655,7 +17655,7 @@
         <v>5017</v>
       </c>
       <c r="J191" s="134" t="n">
-        <v>478.7</v>
+        <v>470.85</v>
       </c>
       <c r="K191" s="134" t="n">
         <v>484.53</v>
@@ -17710,10 +17710,10 @@
         </is>
       </c>
       <c r="E193" s="133" t="n">
-        <v>101</v>
+        <v>195</v>
       </c>
       <c r="F193" s="133" t="n">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="G193" s="133" t="n">
         <v>4975</v>
@@ -17725,12 +17725,12 @@
         <v>2627</v>
       </c>
       <c r="J193" s="134" t="n">
-        <v>492.6</v>
+        <v>255.14</v>
       </c>
       <c r="K193" s="134" t="n">
-        <v>521.67</v>
-      </c>
-      <c r="L193" s="237">
+        <v>194.01</v>
+      </c>
+      <c r="L193" s="236">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -17745,10 +17745,10 @@
         </is>
       </c>
       <c r="E194" s="133" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F194" s="133" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G194" s="133" t="n">
         <v>4190</v>
@@ -17760,12 +17760,12 @@
         <v>3002</v>
       </c>
       <c r="J194" s="134" t="n">
-        <v>654.66</v>
+        <v>634.8200000000001</v>
       </c>
       <c r="K194" s="134" t="n">
-        <v>698.53</v>
-      </c>
-      <c r="L194" s="237">
+        <v>625</v>
+      </c>
+      <c r="L194" s="236">
         <f>F194*(K194-J194)</f>
         <v/>
       </c>
@@ -17780,10 +17780,10 @@
         </is>
       </c>
       <c r="E195" s="133" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F195" s="133" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G195" s="133" t="n">
         <v>3951</v>
@@ -17795,10 +17795,10 @@
         <v>2153</v>
       </c>
       <c r="J195" s="134" t="n">
-        <v>1067.78</v>
+        <v>940.67</v>
       </c>
       <c r="K195" s="134" t="n">
-        <v>1057.65</v>
+        <v>899</v>
       </c>
       <c r="L195" s="236">
         <f>F195*(K195-J195)</f>
@@ -17881,29 +17881,29 @@
       <c r="C198" s="135" t="n"/>
       <c r="D198" s="132" t="inlineStr">
         <is>
-          <t>富喬(1815)</t>
+          <t>晶豪科(3006)</t>
         </is>
       </c>
       <c r="E198" s="133" t="n">
-        <v>237</v>
+        <v>111</v>
       </c>
       <c r="F198" s="133" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="G198" s="133" t="n">
-        <v>2864</v>
+        <v>3075</v>
       </c>
       <c r="H198" s="133" t="n">
-        <v>441</v>
+        <v>2493</v>
       </c>
       <c r="I198" s="133" t="n">
-        <v>2423</v>
+        <v>582</v>
       </c>
       <c r="J198" s="134" t="n">
-        <v>120.84</v>
+        <v>277</v>
       </c>
       <c r="K198" s="134" t="n">
-        <v>126</v>
+        <v>277</v>
       </c>
       <c r="L198" s="237">
         <f>F198*(K198-J198)</f>
@@ -28138,7 +28138,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-03 21:37 TW | 1/1 success | 來源: 富邦1/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-03 22:54 TW | 1/1 success | 來源: 富邦1/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -52,7 +52,7 @@
     <numFmt numFmtId="189" formatCode="0.0%&quot; 市-1215億 &quot;&quot;(昨20/5d18)&quot;"/>
     <numFmt numFmtId="190" formatCode="&quot;📅 明日預測 ↓ 偏空 &quot;0.0&quot;% 信心 — P/C Ratio 主推 — 1 檔焦點&quot;"/>
   </numFmts>
-  <fonts count="54">
+  <fonts count="55">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -362,6 +362,12 @@
       <color rgb="FF059669"/>
       <sz val="16"/>
     </font>
+    <font>
+      <name val="Noto Sans TC"/>
+      <i val="1"/>
+      <color rgb="FF10B981"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="51">
     <fill>
@@ -633,7 +639,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="262">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1248,6 +1254,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1635,7 +1642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N131"/>
+  <dimension ref="B2:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1671,7 +1678,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 📌 一般共識 2408 / 6669 / 8046 (Q5 偏空, 中性信號)  |  避開 — 除權息 4 檔: 1203, 3661, 7780 ... | 明日恐處置 3 檔: 3625/4304/4971  |  訊號: 強偏空 (Q5 10%, hot=14)</t>
+          <t>💡 📌 一般共識 2408 / 6669 / 8046 (Q5 偏空, 中性信號)  |  避開 — 明日恐處置 3 檔: 3625/4304/4971  |  訊號: 強偏空 (Q5 10%, hot=14)</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2566,7 @@
         </is>
       </c>
       <c r="G33" s="259" t="n">
-        <v>0.1707376082472423</v>
+        <v>0.1706536496408914</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
@@ -3690,7 +3697,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="B80" s="57" t="inlineStr">
         <is>
-          <t>▍ G. 注意股 (資料日 20260902)</t>
+          <t>▍ G. 注意股 (資料日 20260904)</t>
         </is>
       </c>
     </row>
@@ -3722,1108 +3729,794 @@
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>066185</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>聯發科元大64購05</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="40" t="inlineStr">
-        <is>
-          <t>069544</t>
-        </is>
-      </c>
-      <c r="C83" s="40" t="inlineStr">
-        <is>
-          <t>立隆電元大5B購05</t>
-        </is>
-      </c>
-      <c r="D83" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="40" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F83" s="40" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2426</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>鼎元</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" t="n">
-        <v>104.5</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>1045.00</t>
+      <c r="B82" s="262" t="inlineStr">
+        <is>
+          <t>✅ 今日無新增注意股 (市場無異常波動標的)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260903)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="40" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
-      </c>
-      <c r="C85" s="40" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="D85" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="40" t="n">
-        <v>542</v>
-      </c>
-      <c r="F85" s="40" t="inlineStr">
-        <is>
-          <t>132.84</t>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>借券張數</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>融券張數</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>冠西電</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" t="n">
-        <v>104</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>66.24</t>
-        </is>
+          <t>台新新光金</t>
+        </is>
+      </c>
+      <c r="D86" s="33" t="n">
+        <v>15554</v>
+      </c>
+      <c r="E86" s="33" t="n">
+        <v>107</v>
+      </c>
+      <c r="F86" s="215" t="n">
+        <v>145.36</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="40" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="C87" s="40" t="inlineStr">
         <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="D87" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="40" t="n">
-        <v>7810</v>
-      </c>
-      <c r="F87" s="40" t="inlineStr">
-        <is>
-          <t>41.54</t>
-        </is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="D87" s="60" t="n">
+        <v>10700</v>
+      </c>
+      <c r="E87" s="60" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F87" s="216" t="n">
+        <v>2.23</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" t="n">
-        <v>1050</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>28.41</t>
-        </is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D88" s="33" t="n">
+        <v>7573</v>
+      </c>
+      <c r="E88" s="33" t="n">
+        <v>1609</v>
+      </c>
+      <c r="F88" s="215" t="n">
+        <v>4.71</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="40" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="C89" s="40" t="inlineStr">
         <is>
-          <t>聯鈞</t>
-        </is>
-      </c>
-      <c r="D89" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="40" t="n">
-        <v>602</v>
-      </c>
-      <c r="F89" s="40" t="inlineStr">
-        <is>
-          <t>122.11</t>
-        </is>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="D89" s="60" t="n">
+        <v>6933</v>
+      </c>
+      <c r="E89" s="60" t="n">
+        <v>52</v>
+      </c>
+      <c r="F89" s="216" t="n">
+        <v>133.33</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>光鼎</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" t="n">
-        <v>34.15</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
+          <t>力積電</t>
+        </is>
+      </c>
+      <c r="D90" s="33" t="n">
+        <v>6755</v>
+      </c>
+      <c r="E90" s="33" t="n">
+        <v>269</v>
+      </c>
+      <c r="F90" s="215" t="n">
+        <v>25.11</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="40" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C91" s="40" t="inlineStr">
         <is>
-          <t>天二科技</t>
-        </is>
-      </c>
-      <c r="D91" s="40" t="n">
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D91" s="60" t="n">
+        <v>5779</v>
+      </c>
+      <c r="E91" s="60" t="n">
+        <v>26</v>
+      </c>
+      <c r="F91" s="216" t="n">
+        <v>222.27</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="43" t="inlineStr">
+        <is>
+          <t>🔴 00918</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>大華優利高填息30</t>
+        </is>
+      </c>
+      <c r="D92" s="33" t="n">
+        <v>4933</v>
+      </c>
+      <c r="E92" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E91" s="40" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="F91" s="40" t="inlineStr">
-        <is>
-          <t>40.09</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>6933</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AMAX-KY</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>331</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>41.07</t>
-        </is>
+      <c r="F92" s="252" t="n">
+        <v>4933</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="40" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="C93" s="40" t="inlineStr">
         <is>
-          <t>台虹</t>
-        </is>
-      </c>
-      <c r="D93" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="40" t="n">
-        <v>313.5</v>
-      </c>
-      <c r="F93" s="40" t="inlineStr">
-        <is>
-          <t>99.52</t>
-        </is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="D93" s="60" t="n">
+        <v>4673</v>
+      </c>
+      <c r="E93" s="60" t="n">
+        <v>18</v>
+      </c>
+      <c r="F93" s="216" t="n">
+        <v>259.61</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>00685L</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>山林水</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" t="n">
-        <v>45.95</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>13.32</t>
-        </is>
+          <t>群益臺灣加權正2</t>
+        </is>
+      </c>
+      <c r="D94" s="33" t="n">
+        <v>3808</v>
+      </c>
+      <c r="E94" s="33" t="n">
+        <v>1685</v>
+      </c>
+      <c r="F94" s="215" t="n">
+        <v>2.26</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="40" t="inlineStr">
         <is>
-          <t>911608</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="C95" s="40" t="inlineStr">
         <is>
-          <t>明輝-DR</t>
-        </is>
-      </c>
-      <c r="D95" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="40" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="F95" s="40" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="22" customHeight="1">
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260903)</t>
-        </is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="D95" s="60" t="n">
+        <v>3247</v>
+      </c>
+      <c r="E95" s="60" t="n">
+        <v>493</v>
+      </c>
+      <c r="F95" s="216" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D96" s="33" t="n">
+        <v>3236</v>
+      </c>
+      <c r="E96" s="33" t="n">
+        <v>131</v>
+      </c>
+      <c r="F96" s="215" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="40" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="C97" s="40" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="D97" s="60" t="n">
+        <v>3177</v>
+      </c>
+      <c r="E97" s="60" t="n">
+        <v>113</v>
+      </c>
+      <c r="F97" s="216" t="n">
+        <v>28.12</v>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>主動統一台股增長</t>
+        </is>
+      </c>
+      <c r="D98" s="33" t="n">
+        <v>2866</v>
+      </c>
+      <c r="E98" s="33" t="n">
+        <v>184</v>
+      </c>
+      <c r="F98" s="215" t="n">
+        <v>15.58</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="44" t="inlineStr">
+        <is>
+          <t>🔴 1718</t>
+        </is>
+      </c>
+      <c r="C99" s="40" t="inlineStr">
+        <is>
+          <t>中纖</t>
+        </is>
+      </c>
+      <c r="D99" s="60" t="n">
+        <v>2794</v>
+      </c>
+      <c r="E99" s="60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" s="217" t="n">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2426</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>鼎元</t>
+        </is>
+      </c>
+      <c r="D100" s="33" t="n">
+        <v>2695</v>
+      </c>
+      <c r="E100" s="33" t="n">
+        <v>456</v>
+      </c>
+      <c r="F100" s="215" t="n">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="B102" s="62" t="inlineStr">
+        <is>
+          <t>▍ I. 未來 30 天除權息 (有效 74 檔, 已剔除過期)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="58" t="inlineStr">
+        <is>
+          <t>除權息日</t>
+        </is>
+      </c>
+      <c r="C103" s="58" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C98" s="12" t="inlineStr">
+      <c r="D103" s="58" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D98" s="12" t="inlineStr">
-        <is>
-          <t>借券張數</t>
-        </is>
-      </c>
-      <c r="E98" s="12" t="inlineStr">
-        <is>
-          <t>融券張數</t>
-        </is>
-      </c>
-      <c r="F98" s="12" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D99" s="33" t="n">
-        <v>15554</v>
-      </c>
-      <c r="E99" s="33" t="n">
-        <v>107</v>
-      </c>
-      <c r="F99" s="215" t="n">
-        <v>145.36</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="40" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="C100" s="40" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="D100" s="60" t="n">
-        <v>10700</v>
-      </c>
-      <c r="E100" s="60" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F100" s="216" t="n">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="D101" s="33" t="n">
-        <v>7573</v>
-      </c>
-      <c r="E101" s="33" t="n">
-        <v>1609</v>
-      </c>
-      <c r="F101" s="215" t="n">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="40" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C102" s="40" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D102" s="60" t="n">
-        <v>6933</v>
-      </c>
-      <c r="E102" s="60" t="n">
-        <v>52</v>
-      </c>
-      <c r="F102" s="216" t="n">
-        <v>133.33</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="D103" s="33" t="n">
-        <v>6755</v>
-      </c>
-      <c r="E103" s="33" t="n">
-        <v>269</v>
-      </c>
-      <c r="F103" s="215" t="n">
-        <v>25.11</v>
+      <c r="E103" s="58" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="F103" s="58" t="inlineStr">
+        <is>
+          <t>現金股利</t>
+        </is>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="40" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="C104" s="40" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="D104" s="60" t="n">
-        <v>5779</v>
-      </c>
-      <c r="E104" s="60" t="n">
-        <v>26</v>
-      </c>
-      <c r="F104" s="216" t="n">
-        <v>222.27</v>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>主動國泰動能高息</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="43" t="inlineStr">
-        <is>
-          <t>🔴 00918</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>大華優利高填息30</t>
-        </is>
-      </c>
-      <c r="D105" s="33" t="n">
-        <v>4933</v>
-      </c>
-      <c r="E105" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="252" t="n">
-        <v>4933</v>
+      <c r="B105" s="40" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C105" s="40" t="inlineStr">
+        <is>
+          <t>01010T</t>
+        </is>
+      </c>
+      <c r="D105" s="40" t="inlineStr">
+        <is>
+          <t>京城樂富R1</t>
+        </is>
+      </c>
+      <c r="E105" s="40" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F105" s="40" t="n">
+        <v>0.09872</v>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="40" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C106" s="40" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D106" s="60" t="n">
-        <v>4673</v>
-      </c>
-      <c r="E106" s="60" t="n">
-        <v>18</v>
-      </c>
-      <c r="F106" s="216" t="n">
-        <v>259.61</v>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>聚隆</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="107">
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="D107" s="33" t="n">
-        <v>3808</v>
-      </c>
-      <c r="E107" s="33" t="n">
-        <v>1685</v>
-      </c>
-      <c r="F107" s="215" t="n">
-        <v>2.26</v>
+      <c r="B107" s="40" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C107" s="40" t="inlineStr">
+        <is>
+          <t>6533</t>
+        </is>
+      </c>
+      <c r="D107" s="40" t="inlineStr">
+        <is>
+          <t>晶心科</t>
+        </is>
+      </c>
+      <c r="E107" s="40" t="inlineStr">
+        <is>
+          <t>權</t>
+        </is>
+      </c>
+      <c r="F107" s="40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="40" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="C108" s="40" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="D108" s="60" t="n">
-        <v>3247</v>
-      </c>
-      <c r="E108" s="60" t="n">
-        <v>493</v>
-      </c>
-      <c r="F108" s="216" t="n">
-        <v>6.59</v>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>00940</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>元大台灣價值高息</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
       </c>
     </row>
     <row r="109">
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D109" s="33" t="n">
-        <v>3236</v>
-      </c>
-      <c r="E109" s="33" t="n">
-        <v>131</v>
-      </c>
-      <c r="F109" s="215" t="n">
-        <v>24.7</v>
+      <c r="B109" s="40" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C109" s="40" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="D109" s="40" t="inlineStr">
+        <is>
+          <t>瑞昱</t>
+        </is>
+      </c>
+      <c r="E109" s="40" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F109" s="40" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="40" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="C110" s="40" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="D110" s="60" t="n">
-        <v>3177</v>
-      </c>
-      <c r="E110" s="60" t="n">
-        <v>113</v>
-      </c>
-      <c r="F110" s="216" t="n">
-        <v>28.12</v>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2442</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>新美齊</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>2.031861</v>
       </c>
     </row>
     <row r="111">
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="D111" s="33" t="n">
-        <v>2866</v>
-      </c>
-      <c r="E111" s="33" t="n">
-        <v>184</v>
-      </c>
-      <c r="F111" s="215" t="n">
-        <v>15.58</v>
+      <c r="B111" s="40" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C111" s="40" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="D111" s="40" t="inlineStr">
+        <is>
+          <t>第一店</t>
+        </is>
+      </c>
+      <c r="E111" s="40" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F111" s="40" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="112">
-      <c r="B112" s="44" t="inlineStr">
-        <is>
-          <t>🔴 1718</t>
-        </is>
-      </c>
-      <c r="C112" s="40" t="inlineStr">
-        <is>
-          <t>中纖</t>
-        </is>
-      </c>
-      <c r="D112" s="60" t="n">
-        <v>2794</v>
-      </c>
-      <c r="E112" s="60" t="n">
-        <v>2</v>
-      </c>
-      <c r="F112" s="217" t="n">
-        <v>1397</v>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>弘憶股</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="113">
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2426</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>鼎元</t>
-        </is>
-      </c>
-      <c r="D113" s="33" t="n">
-        <v>2695</v>
-      </c>
-      <c r="E113" s="33" t="n">
-        <v>456</v>
-      </c>
-      <c r="F113" s="215" t="n">
-        <v>5.91</v>
-      </c>
-    </row>
-    <row r="115" ht="22" customHeight="1">
-      <c r="B115" s="62" t="inlineStr">
-        <is>
-          <t>▍ I. 未來 30 天除權息 (有效 77 檔, 已剔除過期)</t>
-        </is>
+      <c r="B113" s="40" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C113" s="40" t="inlineStr">
+        <is>
+          <t>3622</t>
+        </is>
+      </c>
+      <c r="D113" s="40" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="E113" s="40" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F113" s="40" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>8473</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>山林水</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>0.782345</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="40" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C115" s="40" t="inlineStr">
+        <is>
+          <t>9933</t>
+        </is>
+      </c>
+      <c r="D115" s="40" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="E115" s="40" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F115" s="40" t="n">
+        <v>0.763056</v>
       </c>
     </row>
     <row r="116">
-      <c r="B116" s="58" t="inlineStr">
-        <is>
-          <t>除權息日</t>
-        </is>
-      </c>
-      <c r="C116" s="58" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="D116" s="58" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="E116" s="58" t="inlineStr">
-        <is>
-          <t>類型</t>
-        </is>
-      </c>
-      <c r="F116" s="58" t="inlineStr">
-        <is>
-          <t>現金股利</t>
-        </is>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>三地開發</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="117">
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>20260903</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>味王</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
+      <c r="B117" s="40" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C117" s="40" t="inlineStr">
+        <is>
+          <t>3059</t>
+        </is>
+      </c>
+      <c r="D117" s="40" t="inlineStr">
+        <is>
+          <t>華晶科</t>
+        </is>
+      </c>
+      <c r="E117" s="40" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F117" t="n">
-        <v>1</v>
+      <c r="F117" s="40" t="n">
+        <v>0.998614</v>
       </c>
     </row>
     <row r="118">
-      <c r="B118" s="40" t="inlineStr">
-        <is>
-          <t>20260903</t>
-        </is>
-      </c>
-      <c r="C118" s="40" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="D118" s="40" t="inlineStr">
-        <is>
-          <t>世芯-KY</t>
-        </is>
-      </c>
-      <c r="E118" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F118" s="40" t="n">
-        <v>32.551656</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>20260903</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>7780</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>大研生醫*</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>0.116588</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" s="40" t="inlineStr">
-        <is>
-          <t>20260903</t>
-        </is>
-      </c>
-      <c r="C120" s="40" t="inlineStr">
-        <is>
-          <t>8466</t>
-        </is>
-      </c>
-      <c r="D120" s="40" t="inlineStr">
-        <is>
-          <t>美吉吉-KY</t>
-        </is>
-      </c>
-      <c r="E120" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F120" s="40" t="n">
-        <v>0.301938</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="B122" s="40" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="C122" s="40" t="inlineStr">
-        <is>
-          <t>01010T</t>
-        </is>
-      </c>
-      <c r="D122" s="40" t="inlineStr">
-        <is>
-          <t>京城樂富R1</t>
-        </is>
-      </c>
-      <c r="E122" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F122" s="40" t="n">
-        <v>0.09872</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>1466</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>聚隆</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="40" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="C124" s="40" t="inlineStr">
-        <is>
-          <t>6533</t>
-        </is>
-      </c>
-      <c r="D124" s="40" t="inlineStr">
-        <is>
-          <t>晶心科</t>
-        </is>
-      </c>
-      <c r="E124" s="40" t="inlineStr">
-        <is>
-          <t>權</t>
-        </is>
-      </c>
-      <c r="F124" s="40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>00940</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>元大台灣價值高息</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="40" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C126" s="40" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="D126" s="40" t="inlineStr">
-        <is>
-          <t>瑞昱</t>
-        </is>
-      </c>
-      <c r="E126" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F126" s="40" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2442</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>新美齊</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>神達</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
         <is>
           <t>權息</t>
         </is>
       </c>
-      <c r="F127" t="n">
-        <v>2.031861</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="40" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C128" s="40" t="inlineStr">
-        <is>
-          <t>2706</t>
-        </is>
-      </c>
-      <c r="D128" s="40" t="inlineStr">
-        <is>
-          <t>第一店</t>
-        </is>
-      </c>
-      <c r="E128" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F128" s="40" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>3312</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>弘憶股</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="40" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C130" s="40" t="inlineStr">
-        <is>
-          <t>3622</t>
-        </is>
-      </c>
-      <c r="D130" s="40" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="E130" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F130" s="40" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>8473</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>山林水</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>權息</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>0.782345</v>
+      <c r="F118" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="B9:N9"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F37:I37"/>
     <mergeCell ref="G33:I33"/>
     <mergeCell ref="B35:N35"/>
     <mergeCell ref="B4:N4"/>
+    <mergeCell ref="B84:J84"/>
     <mergeCell ref="B7:N7"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="B64:J64"/>
+    <mergeCell ref="B82:F82"/>
     <mergeCell ref="G32:I32"/>
     <mergeCell ref="B80:J80"/>
     <mergeCell ref="B12:N12"/>
     <mergeCell ref="B11:N11"/>
-    <mergeCell ref="B97:J97"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B54:J54"/>
     <mergeCell ref="B14:N14"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B115:J115"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B102:J102"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="B10:N10"/>
@@ -4900,17 +4593,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D82:D95">
+  <conditionalFormatting sqref="D86:D100">
     <cfRule type="dataBar" priority="9">
-      <dataBar minLength="5" maxLength="90" showValue="1">
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFB300"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D99:D113">
-    <cfRule type="dataBar" priority="10">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4918,8 +4602,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F99:F113">
-    <cfRule type="dataBar" priority="11">
+  <conditionalFormatting sqref="F86:F100">
+    <cfRule type="dataBar" priority="10">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5075,9 +4759,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="66" t="inlineStr">
-        <is>
-          <t>除權息 4 檔 (1203 / 3661 / 7780 ...)</t>
+      <c r="C25" s="68" t="inlineStr">
+        <is>
+          <t>今日無除權息</t>
         </is>
       </c>
     </row>
@@ -28138,7 +27822,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-03 22:54 TW | 1/1 success | 來源: 富邦1/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-04 01:22 TW | 1/1 success | 來源: 富邦1/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -2034,7 +2034,7 @@
         <v>13</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>10</v>
       </c>
       <c r="N20" s="17" t="n">
-        <v>39193</v>
+        <v>38483</v>
       </c>
     </row>
     <row r="21">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="G32" s="257" t="n">
-        <v>-199.54917</v>
+        <v>-199.32547</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="G33" s="259" t="n">
-        <v>0.1706536496408914</v>
+        <v>0.170329424857283</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2677,11 +2677,11 @@
         </is>
       </c>
       <c r="D40" s="33" t="n">
-        <v>881453</v>
+        <v>870535</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="C66" s="33" t="n">
-        <v>819686</v>
+        <v>809114</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>40121</v>
       </c>
       <c r="J66" s="213" t="n">
-        <v>0.199874464124067</v>
+        <v>0.2024861026965552</v>
       </c>
     </row>
     <row r="67">
@@ -4782,7 +4782,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="C29" s="70" t="inlineStr">
         <is>
-          <t>-200 億 淨買</t>
+          <t>-199 億 淨買</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
         </is>
       </c>
       <c r="E189" s="133" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F189" s="133" t="n">
         <v>4</v>
@@ -17269,7 +17269,7 @@
         <v>36163</v>
       </c>
       <c r="J189" s="134" t="n">
-        <v>1349.28</v>
+        <v>1344.34</v>
       </c>
       <c r="K189" s="134" t="n">
         <v>1342.5</v>
@@ -17289,10 +17289,10 @@
         </is>
       </c>
       <c r="E190" s="133" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F190" s="133" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G190" s="133" t="n">
         <v>6900</v>
@@ -17304,10 +17304,10 @@
         <v>5108</v>
       </c>
       <c r="J190" s="134" t="n">
-        <v>413.15</v>
+        <v>425.9</v>
       </c>
       <c r="K190" s="134" t="n">
-        <v>416.79</v>
+        <v>448.05</v>
       </c>
       <c r="L190" s="237">
         <f>F190*(K190-J190)</f>
@@ -17324,7 +17324,7 @@
         </is>
       </c>
       <c r="E191" s="133" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F191" s="133" t="n">
         <v>15</v>
@@ -17339,7 +17339,7 @@
         <v>5017</v>
       </c>
       <c r="J191" s="134" t="n">
-        <v>470.85</v>
+        <v>478.7</v>
       </c>
       <c r="K191" s="134" t="n">
         <v>484.53</v>
@@ -17394,10 +17394,10 @@
         </is>
       </c>
       <c r="E193" s="133" t="n">
-        <v>195</v>
+        <v>101</v>
       </c>
       <c r="F193" s="133" t="n">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="G193" s="133" t="n">
         <v>4975</v>
@@ -17409,12 +17409,12 @@
         <v>2627</v>
       </c>
       <c r="J193" s="134" t="n">
-        <v>255.14</v>
+        <v>492.6</v>
       </c>
       <c r="K193" s="134" t="n">
-        <v>194.01</v>
-      </c>
-      <c r="L193" s="236">
+        <v>521.67</v>
+      </c>
+      <c r="L193" s="237">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -17429,10 +17429,10 @@
         </is>
       </c>
       <c r="E194" s="133" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F194" s="133" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G194" s="133" t="n">
         <v>4190</v>
@@ -17444,12 +17444,12 @@
         <v>3002</v>
       </c>
       <c r="J194" s="134" t="n">
-        <v>634.8200000000001</v>
+        <v>654.66</v>
       </c>
       <c r="K194" s="134" t="n">
-        <v>625</v>
-      </c>
-      <c r="L194" s="236">
+        <v>698.53</v>
+      </c>
+      <c r="L194" s="237">
         <f>F194*(K194-J194)</f>
         <v/>
       </c>
@@ -17464,10 +17464,10 @@
         </is>
       </c>
       <c r="E195" s="133" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F195" s="133" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G195" s="133" t="n">
         <v>3951</v>
@@ -17479,10 +17479,10 @@
         <v>2153</v>
       </c>
       <c r="J195" s="134" t="n">
-        <v>940.67</v>
+        <v>1067.78</v>
       </c>
       <c r="K195" s="134" t="n">
-        <v>899</v>
+        <v>1057.65</v>
       </c>
       <c r="L195" s="236">
         <f>F195*(K195-J195)</f>
@@ -17565,29 +17565,29 @@
       <c r="C198" s="135" t="n"/>
       <c r="D198" s="132" t="inlineStr">
         <is>
-          <t>晶豪科(3006)</t>
+          <t>富喬(1815)</t>
         </is>
       </c>
       <c r="E198" s="133" t="n">
-        <v>111</v>
+        <v>237</v>
       </c>
       <c r="F198" s="133" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="G198" s="133" t="n">
-        <v>3075</v>
+        <v>2864</v>
       </c>
       <c r="H198" s="133" t="n">
-        <v>2493</v>
+        <v>441</v>
       </c>
       <c r="I198" s="133" t="n">
-        <v>582</v>
+        <v>2423</v>
       </c>
       <c r="J198" s="134" t="n">
-        <v>277</v>
+        <v>120.84</v>
       </c>
       <c r="K198" s="134" t="n">
-        <v>277</v>
+        <v>126</v>
       </c>
       <c r="L198" s="237">
         <f>F198*(K198-J198)</f>
@@ -27822,7 +27822,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-04 01:22 TW | 1/1 success | 來源: 富邦1/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-04 02:18 TW | 1/1 success | 來源: 富邦1/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -27822,7 +27822,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-04 02:18 TW | 1/1 success | 來源: 富邦1/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-04 03:12 TW | 1/1 success | 來源: 富邦1/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -24,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="30">
+  <numFmts count="31">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨-177/5d-99)&quot;;-0&quot; 億 (昨-177/5d-99)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +63億 &quot;&quot;(昨15/5d11)&quot;"/>
@@ -55,6 +55,7 @@
     <numFmt numFmtId="191" formatCode="+0&quot; 億 (昨-199/5d-122)&quot;;-0&quot; 億 (昨-199/5d-122)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="192" formatCode="0&quot; 檔 +36億 &quot;&quot;(昨14/5d13)&quot;"/>
     <numFmt numFmtId="193" formatCode="0.0%&quot; 市-444億 &quot;&quot;(昨17/5d18)&quot;"/>
+    <numFmt numFmtId="194" formatCode="0.0%&quot; 市-446億 &quot;&quot;(昨17/5d18)&quot;"/>
   </numFmts>
   <fonts count="55">
     <font>
@@ -643,7 +644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="266">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1268,6 +1269,9 @@
     <xf numFmtId="193" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="194" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2576,8 +2580,8 @@
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G32" s="265" t="n">
-        <v>0.1701493816780536</v>
+      <c r="G32" s="266" t="n">
+        <v>0.1700160365736953</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -9516,7 +9520,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="B3" s="101" t="inlineStr">
         <is>
-          <t>大牌分析師 近 96/96 交易日出手 4599 次 (649 檔), 風格分布: 隔日沖近似 34% / 當沖 14% / 留倉 52%, 漲停命中 3% (其中 🔒鎖漲停 2%), 前 5 大集中 19%, 長線部位 76% (100 檔), ⚠️ 處置股部位 7% (20 檔), 📦 連續囤貨 52 檔 (最長 13 天 009816, 3 檔仍 active)。 主軸: 📈 長線持有/高頻交易/持續進場/📦 連續囤貨。</t>
+          <t>大牌分析師 近 96/96 交易日出手 4599 次 (649 檔), 風格分布: 隔日沖近似 34% / 當沖 14% / 留倉 52%, 漲停命中 3% (其中 🔒鎖漲停 2%), 前 5 大集中 19%, 長線部位 76% (100 檔), ⚠️ 處置股部位 9% (20 檔), 📦 連續囤貨 52 檔 (最長 13 天 009816, 3 檔仍 active)。 主軸: 📈 長線持有/高頻交易/持續進場/📦 連續囤貨。</t>
         </is>
       </c>
     </row>
@@ -28039,7 +28043,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-04 21:38 TW | 17/17 success | 來源: 富邦17/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-05 01:12 TW | 17/17 success | 來源: 富邦17/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -24,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="31">
+  <numFmts count="32">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨-177/5d-99)&quot;;-0&quot; 億 (昨-177/5d-99)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +63億 &quot;&quot;(昨15/5d11)&quot;"/>
@@ -56,6 +56,7 @@
     <numFmt numFmtId="192" formatCode="0&quot; 檔 +36億 &quot;&quot;(昨14/5d13)&quot;"/>
     <numFmt numFmtId="193" formatCode="0.0%&quot; 市-444億 &quot;&quot;(昨17/5d18)&quot;"/>
     <numFmt numFmtId="194" formatCode="0.0%&quot; 市-446億 &quot;&quot;(昨17/5d18)&quot;"/>
+    <numFmt numFmtId="195" formatCode="0&quot; 檔 +34億 &quot;&quot;(昨14/5d13)&quot;"/>
   </numFmts>
   <fonts count="55">
     <font>
@@ -644,7 +645,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="268">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1272,6 +1273,9 @@
     <xf numFmtId="194" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="195" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1357,12 +1361,12 @@
     <comment ref="D17" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「張濬安(航海王)」獨佔比 77.7%
+領頭大戶「張濬安(航海王)」獨佔比 76.8%
   • 領頭金額 41,002 萬
-  • 合計淨買 52,762 萬
+  • 合計淨買 53,394 萬
   • 大戶數 11 位 (名義共識)
 判讀: 名義 11 位大戶共識,
-實質 1 人下注佔 78%,
+實質 1 人下注佔 77%,
 剩餘 10 位為陪襯小單,
 真共識訊號被稀釋.</t>
       </text>
@@ -1370,9 +1374,9 @@
     <comment ref="D20" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「陳族元」獨佔比 58.4%
-  • 領頭金額 17,734 萬
-  • 合計淨買 30,374 萬
+領頭大戶「陳族元」獨佔比 58.3%
+  • 領頭金額 17,640 萬
+  • 合計淨買 30,280 萬
   • 大戶數 11 位 (名義共識)
 判讀: 名義 11 位大戶共識,
 實質 1 人下注佔 58%,
@@ -1380,7 +1384,7 @@
 真共識訊號被稀釋.</t>
       </text>
     </comment>
-    <comment ref="D26" authorId="0" shapeId="0">
+    <comment ref="D24" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
 領頭大戶「陳族元」獨佔比 56.2%
@@ -1398,8 +1402,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ConsensusTbl_15" displayName="ConsensusTbl_15" ref="B15:N28" headerRowCount="1">
-  <autoFilter ref="B15:N28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ConsensusTbl_15" displayName="ConsensusTbl_15" ref="B15:N27" headerRowCount="1">
+  <autoFilter ref="B15:N27"/>
   <tableColumns count="13">
     <tableColumn id="2" name="#"/>
     <tableColumn id="3" name="代號"/>
@@ -1708,7 +1712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N121"/>
+  <dimension ref="B2:N120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1737,14 +1741,14 @@
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>🎯 13 強共識 / Q5 ↑ 偏多 81.7% / E 9 異常 / F 7 長期 / J 0 集中 / H 1 借券壓力</t>
+          <t>🎯 12 強共識 / Q5 ↑ 偏多 81.7% / E 9 異常 / F 7 長期 / J 0 集中 / H 1 借券壓力</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 📌 一般共識 4958 / 6669 / 3037 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 明日恐處置 3 檔: 3625/4304/4971  |  訊號: 強偏多 (Q5 81.7%, hot=17)</t>
+          <t>💡 📌 一般共識 4958 / 6669 / 6147 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 明日恐處置 3 檔: 3625/4304/4971  |  訊號: 強偏多 (Q5 81.7%, hot=17)</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1797,7 @@
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>📊 今日共識集中產業 (top 3): 半導體業 4 (31%)  |  電子零組件業 3 (23%)  |  光電業 2 (15%)</t>
+          <t>📊 今日共識集中產業 (top 3): 半導體業 4 (33%)  |  電子零組件業 3 (25%)  |  光電業 1 (8%)</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1900,7 @@
         <v>10</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
@@ -1904,7 +1908,7 @@
         </is>
       </c>
       <c r="H16" s="17" t="n">
-        <v>27429</v>
+        <v>27059</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1926,7 +1930,7 @@
         <v>7</v>
       </c>
       <c r="N16" s="17" t="n">
-        <v>58753</v>
+        <v>58382</v>
       </c>
     </row>
     <row r="17">
@@ -1977,7 +1981,7 @@
         <v>8</v>
       </c>
       <c r="N17" s="17" t="n">
-        <v>52763</v>
+        <v>53394</v>
       </c>
     </row>
     <row r="18">
@@ -1986,49 +1990,49 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="E18" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
+          <t>張濬安</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>11651</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>林滄海</t>
         </is>
       </c>
-      <c r="H18" s="17" t="n">
-        <v>14768</v>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" s="18" t="n">
+        <v>9997</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>陳族元</t>
         </is>
       </c>
-      <c r="J18" s="18" t="n">
-        <v>5998</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>蔣承翰</t>
-        </is>
-      </c>
       <c r="L18" s="18" t="n">
-        <v>3591</v>
+        <v>3348</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N18" s="17" t="n">
-        <v>38924</v>
+        <v>36271</v>
       </c>
     </row>
     <row r="19">
@@ -2037,49 +2041,49 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="E19" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>張濬安</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="H19" s="17" t="n">
-        <v>11651</v>
+        <v>14768</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>蔣承翰</t>
         </is>
       </c>
       <c r="J19" s="18" t="n">
-        <v>9997</v>
+        <v>3591</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>強森</t>
         </is>
       </c>
       <c r="L19" s="18" t="n">
-        <v>3348</v>
+        <v>3486</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N19" s="17" t="n">
-        <v>36271</v>
+        <v>34729</v>
       </c>
     </row>
     <row r="20">
@@ -2108,7 +2112,7 @@
         </is>
       </c>
       <c r="H20" s="17" t="n">
-        <v>17734</v>
+        <v>17640</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2130,7 +2134,7 @@
         <v>8</v>
       </c>
       <c r="N20" s="17" t="n">
-        <v>30374</v>
+        <v>30281</v>
       </c>
     </row>
     <row r="21">
@@ -2167,7 +2171,7 @@
         </is>
       </c>
       <c r="J21" s="18" t="n">
-        <v>7373</v>
+        <v>6871</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2181,7 +2185,7 @@
         <v>9</v>
       </c>
       <c r="N21" s="17" t="n">
-        <v>29364</v>
+        <v>28861</v>
       </c>
     </row>
     <row r="22">
@@ -2261,7 +2265,7 @@
         </is>
       </c>
       <c r="H23" s="17" t="n">
-        <v>10229</v>
+        <v>10129</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2283,7 +2287,7 @@
         <v>8</v>
       </c>
       <c r="N23" s="17" t="n">
-        <v>24754</v>
+        <v>24653</v>
       </c>
     </row>
     <row r="24">
@@ -2292,49 +2296,49 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6442</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>📌 光聖</t>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>📌 🔁 ⚠️ 南亞</t>
         </is>
       </c>
       <c r="E24" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>8414</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>林滄海</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>1604</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>張濬安</t>
         </is>
       </c>
-      <c r="H24" s="17" t="n">
-        <v>5042</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>陳族元</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="n">
-        <v>3035</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>林滄海</t>
-        </is>
-      </c>
       <c r="L24" s="18" t="n">
-        <v>2187</v>
+        <v>948</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N24" s="17" t="n">
-        <v>16004</v>
+        <v>14970</v>
       </c>
     </row>
     <row r="25">
@@ -2343,35 +2347,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>📌 玉晶光</t>
+          <t>📌 光聖</t>
         </is>
       </c>
       <c r="E25" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>巨人傑</t>
+          <t>張濬安</t>
         </is>
       </c>
       <c r="H25" s="17" t="n">
-        <v>4031</v>
+        <v>5042</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>蔣承翰</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="J25" s="18" t="n">
-        <v>3815</v>
+        <v>2187</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2379,13 +2383,13 @@
         </is>
       </c>
       <c r="L25" s="18" t="n">
-        <v>3054</v>
+        <v>1782</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N25" s="17" t="n">
-        <v>15740</v>
+        <v>14391</v>
       </c>
     </row>
     <row r="26">
@@ -2394,49 +2398,49 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>📌 🔁 ⚠️ 南亞</t>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>📌 🔁 金像電</t>
         </is>
       </c>
       <c r="E26" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>竹科主力分點</t>
         </is>
       </c>
       <c r="H26" s="17" t="n">
-        <v>8414</v>
+        <v>1862</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>陳律師</t>
         </is>
       </c>
       <c r="J26" s="18" t="n">
-        <v>1604</v>
+        <v>1613</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>張濬安</t>
+          <t>蔣承翰</t>
         </is>
       </c>
       <c r="L26" s="18" t="n">
-        <v>948</v>
+        <v>1597</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N26" s="17" t="n">
-        <v>14970</v>
+        <v>10995</v>
       </c>
     </row>
     <row r="27">
@@ -2445,19 +2449,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>📌 🔁 金像電</t>
+          <t>📌 友達</t>
         </is>
       </c>
       <c r="E27" s="14" t="n">
         <v>10</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
@@ -2465,2186 +2469,2138 @@
         </is>
       </c>
       <c r="H27" s="17" t="n">
-        <v>1862</v>
+        <v>1821</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>陳律師</t>
+          <t>張濬安</t>
         </is>
       </c>
       <c r="J27" s="18" t="n">
-        <v>1613</v>
+        <v>767</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>蔣承翰</t>
+          <t>強森</t>
         </is>
       </c>
       <c r="L27" s="18" t="n">
-        <v>1597</v>
+        <v>690</v>
       </c>
       <c r="M27" s="19" t="n">
         <v>7</v>
       </c>
       <c r="N27" s="17" t="n">
-        <v>10314</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="n">
-        <v>13</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>📌 友達</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>竹科主力分點</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="n">
-        <v>1821</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>張濬安</t>
-        </is>
-      </c>
-      <c r="J28" s="18" t="n">
-        <v>767</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>強森</t>
-        </is>
-      </c>
-      <c r="L28" s="18" t="n">
-        <v>690</v>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="N28" s="17" t="n">
         <v>4868</v>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="21" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>▍ A. 追蹤池摘要 (10 秒判讀今日 13 位大戶在做什麼)</t>
         </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Q1 活躍率</t>
+        </is>
+      </c>
+      <c r="C30" s="207" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>Q2 淨買差</t>
+        </is>
+      </c>
+      <c r="G30" s="263" t="n">
+        <v>-54.26411</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>Q1 活躍率</t>
-        </is>
-      </c>
-      <c r="C31" s="207" t="n">
+          <t>Q3 強共識股</t>
+        </is>
+      </c>
+      <c r="C31" s="267" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>Q4 追蹤佔比</t>
+        </is>
+      </c>
+      <c r="G31" s="265" t="n">
+        <v>0.1698439376702703</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="211" t="n">
+        <v>81.7</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>✅ 過去 30 天 P/C 命中率: 偏多 13/21 (62%) | 偏空 1/2 (50%) | 整體 14/23 (61%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="29" t="inlineStr">
+        <is>
+          <t>▍ B. Top 5 高手(按今日總買金額)</t>
+        </is>
+      </c>
+      <c r="F35" s="30" t="inlineStr">
+        <is>
+          <t>▍ C. Top 5 熱門個股(按今日淨買金額)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D36" s="31" t="inlineStr">
+        <is>
+          <t>買進(萬元)</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>佔比%</t>
+        </is>
+      </c>
+      <c r="F36" s="31" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="G36" s="31" t="inlineStr">
+        <is>
+          <t>個股</t>
+        </is>
+      </c>
+      <c r="H36" s="31" t="inlineStr">
+        <is>
+          <t>淨買(萬元)</t>
+        </is>
+      </c>
+      <c r="I36" s="31" t="inlineStr">
+        <is>
+          <t>漲跌%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="22" t="inlineStr">
-        <is>
-          <t>Q2 淨買差</t>
-        </is>
-      </c>
-      <c r="G31" s="263" t="n">
-        <v>-55.80669</v>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>Q3 強共識股</t>
-        </is>
-      </c>
-      <c r="C32" s="264" t="n">
-        <v>13</v>
-      </c>
-      <c r="F32" s="22" t="inlineStr">
-        <is>
-          <t>Q4 追蹤佔比</t>
-        </is>
-      </c>
-      <c r="G32" s="266" t="n">
-        <v>0.1700160365736953</v>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="211" t="n">
-        <v>81.7</v>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="28" t="inlineStr">
-        <is>
-          <t>✅ 過去 30 天 P/C 命中率: 偏多 13/21 (62%) | 偏空 1/2 (50%) | 整體 14/23 (61%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="29" t="inlineStr">
-        <is>
-          <t>▍ B. Top 5 高手(按今日總買金額)</t>
-        </is>
-      </c>
-      <c r="F36" s="30" t="inlineStr">
-        <is>
-          <t>▍ C. Top 5 熱門個股(按今日淨買金額)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="31" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C37" s="31" t="inlineStr">
-        <is>
-          <t>Master</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="inlineStr">
-        <is>
-          <t>買進(萬元)</t>
-        </is>
-      </c>
-      <c r="E37" s="31" t="inlineStr">
-        <is>
-          <t>佔比%</t>
-        </is>
-      </c>
-      <c r="F37" s="31" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="G37" s="31" t="inlineStr">
-        <is>
-          <t>個股</t>
-        </is>
-      </c>
-      <c r="H37" s="31" t="inlineStr">
-        <is>
-          <t>淨買(萬元)</t>
-        </is>
-      </c>
-      <c r="I37" s="31" t="inlineStr">
-        <is>
-          <t>漲跌%</t>
-        </is>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="D37" s="33" t="n">
+        <v>1389219</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>32.6%</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>國巨*(2327)</t>
+        </is>
+      </c>
+      <c r="H37" s="33" t="n">
+        <v>286383</v>
+      </c>
+      <c r="I37" s="212" t="n">
+        <v>0.0998</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="32" t="inlineStr">
-        <is>
-          <t>張濬安(航海王)</t>
+        <v>2</v>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>1389219</v>
+        <v>934039</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>國巨*(2327)</t>
+          <t>聯發科(2454)</t>
         </is>
       </c>
       <c r="H38" s="33" t="n">
-        <v>286383</v>
+        <v>155997</v>
       </c>
       <c r="I38" s="212" t="n">
-        <v>0.0998</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>2</v>
-      </c>
-      <c r="C39" s="35" t="inlineStr">
-        <is>
-          <t>陳族元</t>
+        <v>3</v>
+      </c>
+      <c r="C39" s="36" t="inlineStr">
+        <is>
+          <t>陳律師</t>
         </is>
       </c>
       <c r="D39" s="33" t="n">
-        <v>936333</v>
+        <v>502119</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="H39" s="33" t="n">
-        <v>155997</v>
+        <v>141896</v>
       </c>
       <c r="I39" s="212" t="n">
-        <v>0.0173</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>3</v>
-      </c>
-      <c r="C40" s="36" t="inlineStr">
-        <is>
-          <t>陳律師</t>
+        <v>4</v>
+      </c>
+      <c r="C40" s="38" t="inlineStr">
+        <is>
+          <t>蔣承翰</t>
         </is>
       </c>
       <c r="D40" s="33" t="n">
-        <v>502119</v>
+        <v>394648</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40" s="16" t="inlineStr">
         <is>
-          <t>聯電(2303)</t>
+          <t>華星光(4979)</t>
         </is>
       </c>
       <c r="H40" s="33" t="n">
-        <v>142050</v>
+        <v>129805</v>
       </c>
       <c r="I40" s="212" t="n">
-        <v>0.04</v>
+        <v>0.09970000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C41" s="38" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="C41" s="37" t="inlineStr">
+        <is>
+          <t>林滄海</t>
+        </is>
+      </c>
+      <c r="D41" s="33" t="n">
+        <v>314114</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>7.4%</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>大立光(3008)</t>
+        </is>
+      </c>
+      <c r="H41" s="33" t="n">
+        <v>60676</v>
+      </c>
+      <c r="I41" s="212" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="39" t="inlineStr">
+        <is>
+          <t>▍ E. 異常行為警報 (z&gt;2σ 量爆 + 新標的進場)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>嚴重度</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>金額/檔數</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>巨人傑</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>巨人傑 今日買進 7 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>7 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="40" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C47" s="40" t="inlineStr">
+        <is>
+          <t>張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="D47" s="40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E47" s="40" t="inlineStr">
+        <is>
+          <t>張濬安(航海王) 今日買進 5 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F47" s="40" t="inlineStr">
+        <is>
+          <t>5 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>強森</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>強森 今日買進 4 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>4 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="40" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C49" s="40" t="inlineStr">
         <is>
           <t>蔣承翰</t>
         </is>
       </c>
-      <c r="D41" s="33" t="n">
-        <v>394648</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>9.3%</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>4</v>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="D49" s="40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E49" s="40" t="inlineStr">
+        <is>
+          <t>蔣承翰 今日買進 4 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
+        <is>
+          <t>4 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>迷你哥/松山哥</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>迷你哥/松山哥 今日買進 4 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>4 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="40" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C51" s="40" t="inlineStr">
+        <is>
+          <t>Tradow</t>
+        </is>
+      </c>
+      <c r="D51" s="40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E51" s="40" t="inlineStr">
+        <is>
+          <t>Tradow 今日買進 3 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F51" s="40" t="inlineStr">
+        <is>
+          <t>3 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>林滄海</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>林滄海 今日買進 3 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>3 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="40" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C53" s="40" t="inlineStr">
+        <is>
+          <t>竹科主力分點</t>
+        </is>
+      </c>
+      <c r="D53" s="40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E53" s="40" t="inlineStr">
+        <is>
+          <t>竹科主力分點 今日買進 3 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F53" s="40" t="inlineStr">
+        <is>
+          <t>3 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>陳律師</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>陳律師 今日買進 3 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="B56" s="41" t="inlineStr">
+        <is>
+          <t>▍ F. 跨日連續囤貨 Top 30 (按連續天數排序)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="42" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="C57" s="42" t="inlineStr">
+        <is>
+          <t>股票代號</t>
+        </is>
+      </c>
+      <c r="D57" s="42" t="inlineStr">
+        <is>
+          <t>連續天數</t>
+        </is>
+      </c>
+      <c r="E57" s="42" t="inlineStr">
+        <is>
+          <t>累計買金額(萬)</t>
+        </is>
+      </c>
+      <c r="F57" s="42" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>🔴 陳族元</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="D58" s="43" t="n">
+        <v>34</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1361455</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>陳族元 連續 34 天加碼 3008 (累計 1,361,455 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="40" t="inlineStr">
+        <is>
+          <t>🔴 強森</t>
+        </is>
+      </c>
+      <c r="C59" s="40" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="D59" s="44" t="n">
+        <v>25</v>
+      </c>
+      <c r="E59" s="40" t="n">
+        <v>137179</v>
+      </c>
+      <c r="F59" s="40" t="inlineStr">
+        <is>
+          <t>強森 連續 25 天加碼 8299 (累計 137,179 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>🔴 陳族元</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="D60" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="E60" t="n">
+        <v>387681</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>陳族元 連續 22 天加碼 6274 (累計 387,681 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="40" t="inlineStr">
+        <is>
+          <t>🔴 林滄海</t>
+        </is>
+      </c>
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="D61" s="44" t="n">
+        <v>22</v>
+      </c>
+      <c r="E61" s="40" t="n">
+        <v>201046</v>
+      </c>
+      <c r="F61" s="40" t="inlineStr">
+        <is>
+          <t>林滄海 連續 22 天加碼 6274 (累計 201,046 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>🔴 強森</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D62" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="E62" t="n">
+        <v>134261</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>強森 連續 22 天加碼 6669 (累計 134,261 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="40" t="inlineStr">
+        <is>
+          <t>🔴 張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="C63" s="40" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="D63" s="44" t="n">
+        <v>19</v>
+      </c>
+      <c r="E63" s="40" t="n">
+        <v>643501</v>
+      </c>
+      <c r="F63" s="40" t="inlineStr">
+        <is>
+          <t>張濬安(航海王) 連續 19 天加碼 3008 (累計 643,501 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>🔴 張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="D64" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="E64" t="n">
+        <v>136155</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>張濬安(航海王) 連續 19 天加碼 3481 (累計 136,155 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="B66" s="45" t="inlineStr">
+        <is>
+          <t>▍ J. Master × Top 3 個股 cross-table (今日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="46" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="C67" s="46" t="inlineStr">
+        <is>
+          <t>今日總買(萬)</t>
+        </is>
+      </c>
+      <c r="D67" s="46" t="inlineStr">
+        <is>
+          <t>Top1 個股</t>
+        </is>
+      </c>
+      <c r="E67" s="46" t="inlineStr">
+        <is>
+          <t>Top1 金額</t>
+        </is>
+      </c>
+      <c r="F67" s="46" t="inlineStr">
+        <is>
+          <t>Top2 個股</t>
+        </is>
+      </c>
+      <c r="G67" s="46" t="inlineStr">
+        <is>
+          <t>Top2 金額</t>
+        </is>
+      </c>
+      <c r="H67" s="46" t="inlineStr">
+        <is>
+          <t>Top3 個股</t>
+        </is>
+      </c>
+      <c r="I67" s="46" t="inlineStr">
+        <is>
+          <t>Top3 金額</t>
+        </is>
+      </c>
+      <c r="J67" s="46" t="inlineStr">
+        <is>
+          <t>Top3 合計%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="32" t="inlineStr">
+        <is>
+          <t>張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="C68" s="33" t="n">
+        <v>1228191</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>國巨*(2327)</t>
+        </is>
+      </c>
+      <c r="E68" s="33" t="n">
+        <v>148470</v>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>華星光(4979)</t>
         </is>
       </c>
-      <c r="H41" s="33" t="n">
-        <v>129805</v>
-      </c>
-      <c r="I41" s="212" t="n">
-        <v>0.09970000000000001</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="n">
-        <v>5</v>
-      </c>
-      <c r="C42" s="37" t="inlineStr">
+      <c r="G68" s="33" t="n">
+        <v>141533</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>聯發科(2454)</t>
+        </is>
+      </c>
+      <c r="I68" s="33" t="n">
+        <v>127234</v>
+      </c>
+      <c r="J68" s="213" t="n">
+        <v>0.3397173858845687</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="35" t="inlineStr">
+        <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="C69" s="33" t="n">
+        <v>898008</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>國巨*(2327)</t>
+        </is>
+      </c>
+      <c r="E69" s="33" t="n">
+        <v>96132</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="G69" s="33" t="n">
+        <v>68872</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>聯發科(2454)</t>
+        </is>
+      </c>
+      <c r="I69" s="33" t="n">
+        <v>61967</v>
+      </c>
+      <c r="J69" s="213" t="n">
+        <v>0.2527497809317713</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="36" t="inlineStr">
+        <is>
+          <t>陳律師</t>
+        </is>
+      </c>
+      <c r="C70" s="33" t="n">
+        <v>493661</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>國巨*(2327)</t>
+        </is>
+      </c>
+      <c r="E70" s="33" t="n">
+        <v>90023</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="G70" s="33" t="n">
+        <v>36673</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>緯創(3231)</t>
+        </is>
+      </c>
+      <c r="I70" s="33" t="n">
+        <v>26538</v>
+      </c>
+      <c r="J70" s="213" t="n">
+        <v>0.3104046969912735</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="38" t="inlineStr">
+        <is>
+          <t>蔣承翰</t>
+        </is>
+      </c>
+      <c r="C71" s="33" t="n">
+        <v>388255</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>騰輝電子-KY(6672)</t>
+        </is>
+      </c>
+      <c r="E71" s="33" t="n">
+        <v>91120</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>信昌電(6173)</t>
+        </is>
+      </c>
+      <c r="G71" s="33" t="n">
+        <v>39473</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>國巨*(2327)</t>
+        </is>
+      </c>
+      <c r="I71" s="33" t="n">
+        <v>28060</v>
+      </c>
+      <c r="J71" s="213" t="n">
+        <v>0.4086306098075158</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="37" t="inlineStr">
         <is>
           <t>林滄海</t>
         </is>
       </c>
-      <c r="D42" s="33" t="n">
-        <v>314114</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>7.4%</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>5</v>
-      </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>大量(3167)</t>
-        </is>
-      </c>
-      <c r="H42" s="33" t="n">
-        <v>60112</v>
-      </c>
-      <c r="I42" s="212" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="B45" s="39" t="inlineStr">
-        <is>
-          <t>▍ E. 異常行為警報 (z&gt;2σ 量爆 + 新標的進場)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="12" t="inlineStr">
+      <c r="C72" s="33" t="n">
+        <v>293349</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="E72" s="33" t="n">
+        <v>37190</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>欣興(3037)</t>
+        </is>
+      </c>
+      <c r="G72" s="33" t="n">
+        <v>18130</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>聯發科(2454)</t>
+        </is>
+      </c>
+      <c r="I72" s="33" t="n">
+        <v>17740</v>
+      </c>
+      <c r="J72" s="213" t="n">
+        <v>0.2490541995313439</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="50" t="inlineStr">
+        <is>
+          <t>強森</t>
+        </is>
+      </c>
+      <c r="C73" s="33" t="n">
+        <v>208780</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>聯發科(2454)</t>
+        </is>
+      </c>
+      <c r="E73" s="33" t="n">
+        <v>30118</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>欣興(3037)</t>
+        </is>
+      </c>
+      <c r="G73" s="33" t="n">
+        <v>11073</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="I73" s="33" t="n">
+        <v>10534</v>
+      </c>
+      <c r="J73" s="213" t="n">
+        <v>0.2477469149402913</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="51" t="inlineStr">
+        <is>
+          <t>竹科主力分點</t>
+        </is>
+      </c>
+      <c r="C74" s="33" t="n">
+        <v>110642</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="E74" s="33" t="n">
+        <v>10533</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>創意(3443)</t>
+        </is>
+      </c>
+      <c r="G74" s="33" t="n">
+        <v>10450</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>京元電子(2449)</t>
+        </is>
+      </c>
+      <c r="I74" s="33" t="n">
+        <v>7335</v>
+      </c>
+      <c r="J74" s="213" t="n">
+        <v>0.255935821723797</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="52" t="inlineStr">
+        <is>
+          <t>民哥</t>
+        </is>
+      </c>
+      <c r="C75" s="33" t="n">
+        <v>98683</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="E75" s="33" t="n">
+        <v>12393</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>大立光(3008)</t>
+        </is>
+      </c>
+      <c r="G75" s="33" t="n">
+        <v>10122</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>奇鋐(3017)</t>
+        </is>
+      </c>
+      <c r="I75" s="33" t="n">
+        <v>7578</v>
+      </c>
+      <c r="J75" s="213" t="n">
+        <v>0.304947240313204</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="48" t="inlineStr">
+        <is>
+          <t>巨人傑</t>
+        </is>
+      </c>
+      <c r="C76" s="33" t="n">
+        <v>72100</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>大立光(3008)</t>
+        </is>
+      </c>
+      <c r="E76" s="33" t="n">
+        <v>9273</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>聯亞(3081)</t>
+        </is>
+      </c>
+      <c r="G76" s="33" t="n">
+        <v>5468</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>雙鴻(3324)</t>
+        </is>
+      </c>
+      <c r="I76" s="33" t="n">
+        <v>4319</v>
+      </c>
+      <c r="J76" s="213" t="n">
+        <v>0.2643644044876498</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="53" t="inlineStr">
+        <is>
+          <t>布哥/n_nchang</t>
+        </is>
+      </c>
+      <c r="C77" s="33" t="n">
+        <v>54675</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>大立光(3008)</t>
+        </is>
+      </c>
+      <c r="E77" s="33" t="n">
+        <v>5930</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="G77" s="33" t="n">
+        <v>5130</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>玉晶光(3406)</t>
+        </is>
+      </c>
+      <c r="I77" s="33" t="n">
+        <v>4106</v>
+      </c>
+      <c r="J77" s="213" t="n">
+        <v>0.2773790580704161</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="55" t="inlineStr">
+        <is>
+          <t>Tradow</t>
+        </is>
+      </c>
+      <c r="C78" s="33" t="n">
+        <v>51582</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>華通(2313)</t>
+        </is>
+      </c>
+      <c r="E78" s="33" t="n">
+        <v>4996</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>創新服務(7828)</t>
+        </is>
+      </c>
+      <c r="G78" s="33" t="n">
+        <v>4084</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>昇達科(3491)</t>
+        </is>
+      </c>
+      <c r="I78" s="33" t="n">
+        <v>4015</v>
+      </c>
+      <c r="J78" s="213" t="n">
+        <v>0.2538787981008769</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="54" t="inlineStr">
+        <is>
+          <t>大牌分析師</t>
+        </is>
+      </c>
+      <c r="C79" s="33" t="n">
+        <v>48883</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>上詮(3363)</t>
+        </is>
+      </c>
+      <c r="E79" s="33" t="n">
+        <v>5242</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>強茂(2481)</t>
+        </is>
+      </c>
+      <c r="G79" s="33" t="n">
+        <v>4055</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>全新(2455)</t>
+        </is>
+      </c>
+      <c r="I79" s="33" t="n">
+        <v>3413</v>
+      </c>
+      <c r="J79" s="213" t="n">
+        <v>0.2600029048775349</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="56" t="inlineStr">
+        <is>
+          <t>迷你哥/松山哥</t>
+        </is>
+      </c>
+      <c r="C80" s="33" t="n">
+        <v>32928</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>強茂(2481)</t>
+        </is>
+      </c>
+      <c r="E80" s="33" t="n">
+        <v>4696</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>聯發科(2454)</t>
+        </is>
+      </c>
+      <c r="G80" s="33" t="n">
+        <v>4398</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="I80" s="33" t="n">
+        <v>3956</v>
+      </c>
+      <c r="J80" s="213" t="n">
+        <v>0.3962913360240279</v>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="B82" s="57" t="inlineStr">
+        <is>
+          <t>▍ G. 注意股 (資料日 20260905)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="58" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C83" s="58" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D83" s="58" t="inlineStr">
+        <is>
+          <t>累計次數</t>
+        </is>
+      </c>
+      <c r="E83" s="58" t="inlineStr">
+        <is>
+          <t>收盤價</t>
+        </is>
+      </c>
+      <c r="F83" s="58" t="inlineStr">
+        <is>
+          <t>本益比</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="262" t="inlineStr">
+        <is>
+          <t>✅ 今日無新增注意股 (市場無異常波動標的)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260904)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>借券張數</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>融券張數</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>台新新光金</t>
+        </is>
+      </c>
+      <c r="D88" s="33" t="n">
+        <v>11010</v>
+      </c>
+      <c r="E88" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="F88" s="215" t="n">
+        <v>200.18</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="40" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="C89" s="40" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="D89" s="60" t="n">
+        <v>7788</v>
+      </c>
+      <c r="E89" s="60" t="n">
+        <v>25</v>
+      </c>
+      <c r="F89" s="216" t="n">
+        <v>311.52</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="D90" s="33" t="n">
+        <v>6429</v>
+      </c>
+      <c r="E90" s="33" t="n">
+        <v>91</v>
+      </c>
+      <c r="F90" s="215" t="n">
+        <v>70.65000000000001</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="40" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="C91" s="40" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="D91" s="60" t="n">
+        <v>5267</v>
+      </c>
+      <c r="E91" s="60" t="n">
+        <v>482</v>
+      </c>
+      <c r="F91" s="216" t="n">
+        <v>10.93</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="D92" s="33" t="n">
+        <v>5042</v>
+      </c>
+      <c r="E92" s="33" t="n">
+        <v>315</v>
+      </c>
+      <c r="F92" s="215" t="n">
+        <v>16.01</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="40" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="C93" s="40" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="D93" s="60" t="n">
+        <v>4941</v>
+      </c>
+      <c r="E93" s="60" t="n">
+        <v>95</v>
+      </c>
+      <c r="F93" s="216" t="n">
+        <v>52.01</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>6770</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>力積電</t>
+        </is>
+      </c>
+      <c r="D94" s="33" t="n">
+        <v>4064</v>
+      </c>
+      <c r="E94" s="33" t="n">
+        <v>315</v>
+      </c>
+      <c r="F94" s="215" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="40" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C95" s="40" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D95" s="60" t="n">
+        <v>3827</v>
+      </c>
+      <c r="E95" s="60" t="n">
+        <v>88</v>
+      </c>
+      <c r="F95" s="216" t="n">
+        <v>43.49</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="D96" s="33" t="n">
+        <v>3520</v>
+      </c>
+      <c r="E96" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="F96" s="215" t="n">
+        <v>135.38</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="40" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="C97" s="40" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="D97" s="60" t="n">
+        <v>3459</v>
+      </c>
+      <c r="E97" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="F97" s="216" t="n">
+        <v>432.38</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D98" s="33" t="n">
+        <v>2964</v>
+      </c>
+      <c r="E98" s="33" t="n">
+        <v>84</v>
+      </c>
+      <c r="F98" s="215" t="n">
+        <v>35.29</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="40" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C99" s="40" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D99" s="60" t="n">
+        <v>2817</v>
+      </c>
+      <c r="E99" s="60" t="n">
+        <v>66</v>
+      </c>
+      <c r="F99" s="216" t="n">
+        <v>42.68</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="43" t="inlineStr">
+        <is>
+          <t>🔴 2801</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>彰銀</t>
+        </is>
+      </c>
+      <c r="D100" s="33" t="n">
+        <v>2621</v>
+      </c>
+      <c r="E100" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" s="252" t="n">
+        <v>1310.5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="40" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C101" s="40" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D101" s="60" t="n">
+        <v>2478</v>
+      </c>
+      <c r="E101" s="60" t="n">
+        <v>45</v>
+      </c>
+      <c r="F101" s="216" t="n">
+        <v>55.07</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D102" s="33" t="n">
+        <v>2397</v>
+      </c>
+      <c r="E102" s="33" t="n">
+        <v>188</v>
+      </c>
+      <c r="F102" s="215" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="B104" s="62" t="inlineStr">
+        <is>
+          <t>▍ I. 未來 30 天除權息 (有效 74 檔, 已剔除過期)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="58" t="inlineStr">
+        <is>
+          <t>除權息日</t>
+        </is>
+      </c>
+      <c r="C105" s="58" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="D105" s="58" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="E105" s="58" t="inlineStr">
         <is>
           <t>類型</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>Master</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>嚴重度</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>說明</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>金額/檔數</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>巨人傑</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>巨人傑 今日買進 7 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>7 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="40" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C48" s="40" t="inlineStr">
-        <is>
-          <t>張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="D48" s="40" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E48" s="40" t="inlineStr">
-        <is>
-          <t>張濬安(航海王) 今日買進 5 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F48" s="40" t="inlineStr">
-        <is>
-          <t>5 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>強森</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>強森 今日買進 4 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>4 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="40" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C50" s="40" t="inlineStr">
-        <is>
-          <t>蔣承翰</t>
-        </is>
-      </c>
-      <c r="D50" s="40" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E50" s="40" t="inlineStr">
-        <is>
-          <t>蔣承翰 今日買進 4 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F50" s="40" t="inlineStr">
-        <is>
-          <t>4 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>迷你哥/松山哥</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>迷你哥/松山哥 今日買進 4 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>4 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="40" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C52" s="40" t="inlineStr">
-        <is>
-          <t>Tradow</t>
-        </is>
-      </c>
-      <c r="D52" s="40" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E52" s="40" t="inlineStr">
-        <is>
-          <t>Tradow 今日買進 3 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F52" s="40" t="inlineStr">
-        <is>
-          <t>3 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>林滄海</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>林滄海 今日買進 3 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>3 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="40" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C54" s="40" t="inlineStr">
-        <is>
-          <t>竹科主力分點</t>
-        </is>
-      </c>
-      <c r="D54" s="40" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E54" s="40" t="inlineStr">
-        <is>
-          <t>竹科主力分點 今日買進 3 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F54" s="40" t="inlineStr">
-        <is>
-          <t>3 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>陳律師</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>陳律師 今日買進 3 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>3 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="B57" s="41" t="inlineStr">
-        <is>
-          <t>▍ F. 跨日連續囤貨 Top 30 (按連續天數排序)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="42" t="inlineStr">
-        <is>
-          <t>Master</t>
-        </is>
-      </c>
-      <c r="C58" s="42" t="inlineStr">
-        <is>
-          <t>股票代號</t>
-        </is>
-      </c>
-      <c r="D58" s="42" t="inlineStr">
-        <is>
-          <t>連續天數</t>
-        </is>
-      </c>
-      <c r="E58" s="42" t="inlineStr">
-        <is>
-          <t>累計買金額(萬)</t>
-        </is>
-      </c>
-      <c r="F58" s="42" t="inlineStr">
-        <is>
-          <t>說明</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>🔴 陳族元</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="D59" s="43" t="n">
-        <v>34</v>
-      </c>
-      <c r="E59" t="n">
-        <v>1360617</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>陳族元 連續 34 天加碼 3008 (累計 1,360,617 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="40" t="inlineStr">
-        <is>
-          <t>🔴 強森</t>
-        </is>
-      </c>
-      <c r="C60" s="40" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
-      </c>
-      <c r="D60" s="44" t="n">
+      <c r="F105" s="58" t="inlineStr">
+        <is>
+          <t>現金股利</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>主動國泰動能高息</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="40" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C107" s="40" t="inlineStr">
+        <is>
+          <t>01010T</t>
+        </is>
+      </c>
+      <c r="D107" s="40" t="inlineStr">
+        <is>
+          <t>京城樂富R1</t>
+        </is>
+      </c>
+      <c r="E107" s="40" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F107" s="40" t="n">
+        <v>0.09872</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>聚隆</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="40" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C109" s="40" t="inlineStr">
+        <is>
+          <t>6533</t>
+        </is>
+      </c>
+      <c r="D109" s="40" t="inlineStr">
+        <is>
+          <t>晶心科</t>
+        </is>
+      </c>
+      <c r="E109" s="40" t="inlineStr">
+        <is>
+          <t>權</t>
+        </is>
+      </c>
+      <c r="F109" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>00940</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>元大台灣價值高息</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="40" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C111" s="40" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="D111" s="40" t="inlineStr">
+        <is>
+          <t>瑞昱</t>
+        </is>
+      </c>
+      <c r="E111" s="40" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F111" s="40" t="n">
         <v>25</v>
       </c>
-      <c r="E60" s="40" t="n">
-        <v>137179</v>
-      </c>
-      <c r="F60" s="40" t="inlineStr">
-        <is>
-          <t>強森 連續 25 天加碼 8299 (累計 137,179 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>🔴 陳族元</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="D61" s="43" t="n">
-        <v>22</v>
-      </c>
-      <c r="E61" t="n">
-        <v>388436</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>陳族元 連續 22 天加碼 6274 (累計 388,436 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="40" t="inlineStr">
-        <is>
-          <t>🔴 林滄海</t>
-        </is>
-      </c>
-      <c r="C62" s="40" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="D62" s="44" t="n">
-        <v>22</v>
-      </c>
-      <c r="E62" s="40" t="n">
-        <v>201046</v>
-      </c>
-      <c r="F62" s="40" t="inlineStr">
-        <is>
-          <t>林滄海 連續 22 天加碼 6274 (累計 201,046 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>🔴 強森</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="D63" s="43" t="n">
-        <v>22</v>
-      </c>
-      <c r="E63" t="n">
-        <v>134261</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>強森 連續 22 天加碼 6669 (累計 134,261 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="40" t="inlineStr">
-        <is>
-          <t>🔴 張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="C64" s="40" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="D64" s="44" t="n">
-        <v>19</v>
-      </c>
-      <c r="E64" s="40" t="n">
-        <v>643501</v>
-      </c>
-      <c r="F64" s="40" t="inlineStr">
-        <is>
-          <t>張濬安(航海王) 連續 19 天加碼 3008 (累計 643,501 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>🔴 張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="D65" s="43" t="n">
-        <v>19</v>
-      </c>
-      <c r="E65" t="n">
-        <v>136155</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>張濬安(航海王) 連續 19 天加碼 3481 (累計 136,155 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="B67" s="45" t="inlineStr">
-        <is>
-          <t>▍ J. Master × Top 3 個股 cross-table (今日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="46" t="inlineStr">
-        <is>
-          <t>Master</t>
-        </is>
-      </c>
-      <c r="C68" s="46" t="inlineStr">
-        <is>
-          <t>今日總買(萬)</t>
-        </is>
-      </c>
-      <c r="D68" s="46" t="inlineStr">
-        <is>
-          <t>Top1 個股</t>
-        </is>
-      </c>
-      <c r="E68" s="46" t="inlineStr">
-        <is>
-          <t>Top1 金額</t>
-        </is>
-      </c>
-      <c r="F68" s="46" t="inlineStr">
-        <is>
-          <t>Top2 個股</t>
-        </is>
-      </c>
-      <c r="G68" s="46" t="inlineStr">
-        <is>
-          <t>Top2 金額</t>
-        </is>
-      </c>
-      <c r="H68" s="46" t="inlineStr">
-        <is>
-          <t>Top3 個股</t>
-        </is>
-      </c>
-      <c r="I68" s="46" t="inlineStr">
-        <is>
-          <t>Top3 金額</t>
-        </is>
-      </c>
-      <c r="J68" s="46" t="inlineStr">
-        <is>
-          <t>Top3 合計%</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="32" t="inlineStr">
-        <is>
-          <t>張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="C69" s="33" t="n">
-        <v>1228191</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>國巨*(2327)</t>
-        </is>
-      </c>
-      <c r="E69" s="33" t="n">
-        <v>148470</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>華星光(4979)</t>
-        </is>
-      </c>
-      <c r="G69" s="33" t="n">
-        <v>141533</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>聯發科(2454)</t>
-        </is>
-      </c>
-      <c r="I69" s="33" t="n">
-        <v>127234</v>
-      </c>
-      <c r="J69" s="213" t="n">
-        <v>0.3397173858845687</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="35" t="inlineStr">
-        <is>
-          <t>陳族元</t>
-        </is>
-      </c>
-      <c r="C70" s="33" t="n">
-        <v>900302</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>國巨*(2327)</t>
-        </is>
-      </c>
-      <c r="E70" s="33" t="n">
-        <v>96132</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>聯電(2303)</t>
-        </is>
-      </c>
-      <c r="G70" s="33" t="n">
-        <v>68843</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>聯發科(2454)</t>
-        </is>
-      </c>
-      <c r="I70" s="33" t="n">
-        <v>61967</v>
-      </c>
-      <c r="J70" s="213" t="n">
-        <v>0.252074192881944</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="36" t="inlineStr">
-        <is>
-          <t>陳律師</t>
-        </is>
-      </c>
-      <c r="C71" s="33" t="n">
-        <v>493661</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>國巨*(2327)</t>
-        </is>
-      </c>
-      <c r="E71" s="33" t="n">
-        <v>90023</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="G71" s="33" t="n">
-        <v>36673</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>緯創(3231)</t>
-        </is>
-      </c>
-      <c r="I71" s="33" t="n">
-        <v>26538</v>
-      </c>
-      <c r="J71" s="213" t="n">
-        <v>0.3104046969912735</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="38" t="inlineStr">
-        <is>
-          <t>蔣承翰</t>
-        </is>
-      </c>
-      <c r="C72" s="33" t="n">
-        <v>388255</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>騰輝電子-KY(6672)</t>
-        </is>
-      </c>
-      <c r="E72" s="33" t="n">
-        <v>91120</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>信昌電(6173)</t>
-        </is>
-      </c>
-      <c r="G72" s="33" t="n">
-        <v>39473</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>國巨*(2327)</t>
-        </is>
-      </c>
-      <c r="I72" s="33" t="n">
-        <v>28060</v>
-      </c>
-      <c r="J72" s="213" t="n">
-        <v>0.4086306098075158</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="37" t="inlineStr">
-        <is>
-          <t>林滄海</t>
-        </is>
-      </c>
-      <c r="C73" s="33" t="n">
-        <v>293349</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>聯電(2303)</t>
-        </is>
-      </c>
-      <c r="E73" s="33" t="n">
-        <v>37190</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>欣興(3037)</t>
-        </is>
-      </c>
-      <c r="G73" s="33" t="n">
-        <v>18130</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>聯發科(2454)</t>
-        </is>
-      </c>
-      <c r="I73" s="33" t="n">
-        <v>17740</v>
-      </c>
-      <c r="J73" s="213" t="n">
-        <v>0.2490541995313439</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="50" t="inlineStr">
-        <is>
-          <t>強森</t>
-        </is>
-      </c>
-      <c r="C74" s="33" t="n">
-        <v>208780</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>聯發科(2454)</t>
-        </is>
-      </c>
-      <c r="E74" s="33" t="n">
-        <v>30118</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>欣興(3037)</t>
-        </is>
-      </c>
-      <c r="G74" s="33" t="n">
-        <v>11073</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="I74" s="33" t="n">
-        <v>10534</v>
-      </c>
-      <c r="J74" s="213" t="n">
-        <v>0.2477469149402913</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="51" t="inlineStr">
-        <is>
-          <t>竹科主力分點</t>
-        </is>
-      </c>
-      <c r="C75" s="33" t="n">
-        <v>110642</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="E75" s="33" t="n">
-        <v>10533</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>創意(3443)</t>
-        </is>
-      </c>
-      <c r="G75" s="33" t="n">
-        <v>10450</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>京元電子(2449)</t>
-        </is>
-      </c>
-      <c r="I75" s="33" t="n">
-        <v>7335</v>
-      </c>
-      <c r="J75" s="213" t="n">
-        <v>0.255935821723797</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="52" t="inlineStr">
-        <is>
-          <t>民哥</t>
-        </is>
-      </c>
-      <c r="C76" s="33" t="n">
-        <v>98683</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="E76" s="33" t="n">
-        <v>12393</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>大立光(3008)</t>
-        </is>
-      </c>
-      <c r="G76" s="33" t="n">
-        <v>10122</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>奇鋐(3017)</t>
-        </is>
-      </c>
-      <c r="I76" s="33" t="n">
-        <v>7578</v>
-      </c>
-      <c r="J76" s="213" t="n">
-        <v>0.304947240313204</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="48" t="inlineStr">
-        <is>
-          <t>巨人傑</t>
-        </is>
-      </c>
-      <c r="C77" s="33" t="n">
-        <v>72100</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>大立光(3008)</t>
-        </is>
-      </c>
-      <c r="E77" s="33" t="n">
-        <v>9273</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>聯亞(3081)</t>
-        </is>
-      </c>
-      <c r="G77" s="33" t="n">
-        <v>5468</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>雙鴻(3324)</t>
-        </is>
-      </c>
-      <c r="I77" s="33" t="n">
-        <v>4319</v>
-      </c>
-      <c r="J77" s="213" t="n">
-        <v>0.2643644044876498</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="53" t="inlineStr">
-        <is>
-          <t>布哥/n_nchang</t>
-        </is>
-      </c>
-      <c r="C78" s="33" t="n">
-        <v>54675</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>大立光(3008)</t>
-        </is>
-      </c>
-      <c r="E78" s="33" t="n">
-        <v>5930</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="G78" s="33" t="n">
-        <v>5130</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>玉晶光(3406)</t>
-        </is>
-      </c>
-      <c r="I78" s="33" t="n">
-        <v>4106</v>
-      </c>
-      <c r="J78" s="213" t="n">
-        <v>0.2773790580704161</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="55" t="inlineStr">
-        <is>
-          <t>Tradow</t>
-        </is>
-      </c>
-      <c r="C79" s="33" t="n">
-        <v>51582</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>華通(2313)</t>
-        </is>
-      </c>
-      <c r="E79" s="33" t="n">
-        <v>4996</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>創新服務(7828)</t>
-        </is>
-      </c>
-      <c r="G79" s="33" t="n">
-        <v>4084</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>昇達科(3491)</t>
-        </is>
-      </c>
-      <c r="I79" s="33" t="n">
-        <v>4015</v>
-      </c>
-      <c r="J79" s="213" t="n">
-        <v>0.2538787981008769</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="54" t="inlineStr">
-        <is>
-          <t>大牌分析師</t>
-        </is>
-      </c>
-      <c r="C80" s="33" t="n">
-        <v>48883</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>上詮(3363)</t>
-        </is>
-      </c>
-      <c r="E80" s="33" t="n">
-        <v>5242</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>強茂(2481)</t>
-        </is>
-      </c>
-      <c r="G80" s="33" t="n">
-        <v>4055</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>全新(2455)</t>
-        </is>
-      </c>
-      <c r="I80" s="33" t="n">
-        <v>3413</v>
-      </c>
-      <c r="J80" s="213" t="n">
-        <v>0.2600029048775349</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="56" t="inlineStr">
-        <is>
-          <t>迷你哥/松山哥</t>
-        </is>
-      </c>
-      <c r="C81" s="33" t="n">
-        <v>32928</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>強茂(2481)</t>
-        </is>
-      </c>
-      <c r="E81" s="33" t="n">
-        <v>4696</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>聯發科(2454)</t>
-        </is>
-      </c>
-      <c r="G81" s="33" t="n">
-        <v>4398</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="I81" s="33" t="n">
-        <v>3956</v>
-      </c>
-      <c r="J81" s="213" t="n">
-        <v>0.3962913360240279</v>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="1">
-      <c r="B83" s="57" t="inlineStr">
-        <is>
-          <t>▍ G. 注意股 (資料日 20260904)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="58" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C84" s="58" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D84" s="58" t="inlineStr">
-        <is>
-          <t>累計次數</t>
-        </is>
-      </c>
-      <c r="E84" s="58" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F84" s="58" t="inlineStr">
-        <is>
-          <t>本益比</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="262" t="inlineStr">
-        <is>
-          <t>✅ 今日無新增注意股 (市場無異常波動標的)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260904)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="12" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C88" s="12" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t>借券張數</t>
-        </is>
-      </c>
-      <c r="E88" s="12" t="inlineStr">
-        <is>
-          <t>融券張數</t>
-        </is>
-      </c>
-      <c r="F88" s="12" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D89" s="33" t="n">
-        <v>11010</v>
-      </c>
-      <c r="E89" s="33" t="n">
-        <v>55</v>
-      </c>
-      <c r="F89" s="215" t="n">
-        <v>200.18</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="40" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C90" s="40" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D90" s="60" t="n">
-        <v>7788</v>
-      </c>
-      <c r="E90" s="60" t="n">
-        <v>25</v>
-      </c>
-      <c r="F90" s="216" t="n">
-        <v>311.52</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2481</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>強茂</t>
-        </is>
-      </c>
-      <c r="D91" s="33" t="n">
-        <v>6429</v>
-      </c>
-      <c r="E91" s="33" t="n">
-        <v>91</v>
-      </c>
-      <c r="F91" s="215" t="n">
-        <v>70.65000000000001</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="40" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="C92" s="40" t="inlineStr">
-        <is>
-          <t>群創</t>
-        </is>
-      </c>
-      <c r="D92" s="60" t="n">
-        <v>5267</v>
-      </c>
-      <c r="E92" s="60" t="n">
-        <v>482</v>
-      </c>
-      <c r="F92" s="216" t="n">
-        <v>10.93</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="D93" s="33" t="n">
-        <v>5042</v>
-      </c>
-      <c r="E93" s="33" t="n">
-        <v>315</v>
-      </c>
-      <c r="F93" s="215" t="n">
-        <v>16.01</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="40" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="C94" s="40" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-      <c r="D94" s="60" t="n">
-        <v>4941</v>
-      </c>
-      <c r="E94" s="60" t="n">
-        <v>95</v>
-      </c>
-      <c r="F94" s="216" t="n">
-        <v>52.01</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="D95" s="33" t="n">
-        <v>4064</v>
-      </c>
-      <c r="E95" s="33" t="n">
-        <v>315</v>
-      </c>
-      <c r="F95" s="215" t="n">
-        <v>12.9</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="40" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C96" s="40" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D96" s="60" t="n">
-        <v>3827</v>
-      </c>
-      <c r="E96" s="60" t="n">
-        <v>88</v>
-      </c>
-      <c r="F96" s="216" t="n">
-        <v>43.49</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D97" s="33" t="n">
-        <v>3520</v>
-      </c>
-      <c r="E97" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="F97" s="215" t="n">
-        <v>135.38</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="40" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C98" s="40" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D98" s="60" t="n">
-        <v>3459</v>
-      </c>
-      <c r="E98" s="60" t="n">
-        <v>8</v>
-      </c>
-      <c r="F98" s="216" t="n">
-        <v>432.38</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D99" s="33" t="n">
-        <v>2964</v>
-      </c>
-      <c r="E99" s="33" t="n">
-        <v>84</v>
-      </c>
-      <c r="F99" s="215" t="n">
-        <v>35.29</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="40" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="C100" s="40" t="inlineStr">
-        <is>
-          <t>富邦金</t>
-        </is>
-      </c>
-      <c r="D100" s="60" t="n">
-        <v>2817</v>
-      </c>
-      <c r="E100" s="60" t="n">
-        <v>66</v>
-      </c>
-      <c r="F100" s="216" t="n">
-        <v>42.68</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="43" t="inlineStr">
-        <is>
-          <t>🔴 2801</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="D101" s="33" t="n">
-        <v>2621</v>
-      </c>
-      <c r="E101" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F101" s="252" t="n">
-        <v>1310.5</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="40" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="C102" s="40" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="D102" s="60" t="n">
-        <v>2478</v>
-      </c>
-      <c r="E102" s="60" t="n">
-        <v>45</v>
-      </c>
-      <c r="F102" s="216" t="n">
-        <v>55.07</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="D103" s="33" t="n">
-        <v>2397</v>
-      </c>
-      <c r="E103" s="33" t="n">
-        <v>188</v>
-      </c>
-      <c r="F103" s="215" t="n">
-        <v>12.75</v>
-      </c>
-    </row>
-    <row r="105" ht="22" customHeight="1">
-      <c r="B105" s="62" t="inlineStr">
-        <is>
-          <t>▍ I. 未來 30 天除權息 (有效 74 檔, 已剔除過期)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" s="58" t="inlineStr">
-        <is>
-          <t>除權息日</t>
-        </is>
-      </c>
-      <c r="C106" s="58" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="D106" s="58" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="E106" s="58" t="inlineStr">
-        <is>
-          <t>類型</t>
-        </is>
-      </c>
-      <c r="F106" s="58" t="inlineStr">
-        <is>
-          <t>現金股利</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2442</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>新美齊</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>2.031861</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="40" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C113" s="40" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="D113" s="40" t="inlineStr">
+        <is>
+          <t>第一店</t>
+        </is>
+      </c>
+      <c r="E113" s="40" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F107" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" s="40" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="C108" s="40" t="inlineStr">
-        <is>
-          <t>01010T</t>
-        </is>
-      </c>
-      <c r="D108" s="40" t="inlineStr">
-        <is>
-          <t>京城樂富R1</t>
-        </is>
-      </c>
-      <c r="E108" s="40" t="inlineStr">
+      <c r="F113" s="40" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>弘憶股</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F108" s="40" t="n">
-        <v>0.09872</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>1466</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>聚隆</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
+      <c r="F114" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="40" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C115" s="40" t="inlineStr">
+        <is>
+          <t>3622</t>
+        </is>
+      </c>
+      <c r="D115" s="40" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="E115" s="40" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F109" t="n">
+      <c r="F115" s="40" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>8473</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>山林水</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>0.782345</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="40" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C117" s="40" t="inlineStr">
+        <is>
+          <t>9933</t>
+        </is>
+      </c>
+      <c r="D117" s="40" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="E117" s="40" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F117" s="40" t="n">
+        <v>0.763056</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>三地開發</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="110">
-      <c r="B110" s="40" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="C110" s="40" t="inlineStr">
-        <is>
-          <t>6533</t>
-        </is>
-      </c>
-      <c r="D110" s="40" t="inlineStr">
-        <is>
-          <t>晶心科</t>
-        </is>
-      </c>
-      <c r="E110" s="40" t="inlineStr">
-        <is>
-          <t>權</t>
-        </is>
-      </c>
-      <c r="F110" s="40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>00940</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>元大台灣價值高息</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
+    <row r="119">
+      <c r="B119" s="40" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C119" s="40" t="inlineStr">
+        <is>
+          <t>3059</t>
+        </is>
+      </c>
+      <c r="D119" s="40" t="inlineStr">
+        <is>
+          <t>華晶科</t>
+        </is>
+      </c>
+      <c r="E119" s="40" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="40" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C112" s="40" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="D112" s="40" t="inlineStr">
-        <is>
-          <t>瑞昱</t>
-        </is>
-      </c>
-      <c r="E112" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F112" s="40" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2442</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>新美齊</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
+      <c r="F119" s="40" t="n">
+        <v>0.998614</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>神達</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
         <is>
           <t>權息</t>
         </is>
       </c>
-      <c r="F113" t="n">
-        <v>2.031861</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="B114" s="40" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C114" s="40" t="inlineStr">
-        <is>
-          <t>2706</t>
-        </is>
-      </c>
-      <c r="D114" s="40" t="inlineStr">
-        <is>
-          <t>第一店</t>
-        </is>
-      </c>
-      <c r="E114" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F114" s="40" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>3312</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>弘憶股</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" s="40" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C116" s="40" t="inlineStr">
-        <is>
-          <t>3622</t>
-        </is>
-      </c>
-      <c r="D116" s="40" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="E116" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F116" s="40" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>8473</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>山林水</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>權息</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>0.782345</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="40" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C118" s="40" t="inlineStr">
-        <is>
-          <t>9933</t>
-        </is>
-      </c>
-      <c r="D118" s="40" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="E118" s="40" t="inlineStr">
-        <is>
-          <t>權息</t>
-        </is>
-      </c>
-      <c r="F118" s="40" t="n">
-        <v>0.763056</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>1438</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>三地開發</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>權息</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" s="40" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="C120" s="40" t="inlineStr">
-        <is>
-          <t>3059</t>
-        </is>
-      </c>
-      <c r="D120" s="40" t="inlineStr">
-        <is>
-          <t>華晶科</t>
-        </is>
-      </c>
-      <c r="E120" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F120" s="40" t="n">
-        <v>0.998614</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>3706</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>神達</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>權息</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
+      <c r="F120" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B67:J67"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="B9:N9"/>
-    <mergeCell ref="B57:J57"/>
     <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B44:J44"/>
+    <mergeCell ref="B82:J82"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B4:N4"/>
     <mergeCell ref="B7:N7"/>
-    <mergeCell ref="B83:J83"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="B45:J45"/>
+    <mergeCell ref="B104:J104"/>
+    <mergeCell ref="B86:J86"/>
     <mergeCell ref="G31:I31"/>
     <mergeCell ref="B12:N12"/>
     <mergeCell ref="B11:N11"/>
+    <mergeCell ref="B84:F84"/>
     <mergeCell ref="B2:N2"/>
-    <mergeCell ref="F36:I36"/>
     <mergeCell ref="B14:N14"/>
-    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="B8:N8"/>
+    <mergeCell ref="B66:J66"/>
     <mergeCell ref="B13:N13"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B105:J105"/>
-    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B56:J56"/>
     <mergeCell ref="B10:N10"/>
   </mergeCells>
-  <conditionalFormatting sqref="N16:N28">
+  <conditionalFormatting sqref="N16:N27">
     <cfRule type="dataBar" priority="1">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4653,7 +4609,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E16:E28">
+  <conditionalFormatting sqref="E16:E27">
     <cfRule type="dataBar" priority="2">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4662,7 +4618,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D38:D42">
+  <conditionalFormatting sqref="D37:D41">
     <cfRule type="dataBar" priority="3">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4671,7 +4627,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H38:H42">
+  <conditionalFormatting sqref="H37:H41">
     <cfRule type="dataBar" priority="4">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4680,7 +4636,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D59:D65">
+  <conditionalFormatting sqref="D58:D64">
     <cfRule type="dataBar" priority="5">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4689,7 +4645,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E59:E65">
+  <conditionalFormatting sqref="E58:E64">
     <cfRule type="dataBar" priority="6">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4698,7 +4654,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C69:C81">
+  <conditionalFormatting sqref="C68:C80">
     <cfRule type="dataBar" priority="7">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4707,7 +4663,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J69:J81">
+  <conditionalFormatting sqref="J68:J80">
     <cfRule type="dataBar" priority="8">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4716,7 +4672,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D89:D103">
+  <conditionalFormatting sqref="D88:D102">
     <cfRule type="dataBar" priority="9">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4725,7 +4681,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F89:F103">
+  <conditionalFormatting sqref="F88:F102">
     <cfRule type="dataBar" priority="10">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4748,7 +4704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:C36"/>
+  <dimension ref="C2:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="2" max="2"/>
@@ -4801,14 +4757,14 @@
     <row r="10">
       <c r="C10" s="66" t="inlineStr">
         <is>
-          <t>③ 欣興 (3037) · 10 大戶</t>
+          <t>③ 頎邦 (6147) · 11 大戶</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="66" t="inlineStr">
         <is>
-          <t>④ 頎邦 (6147) · 11 大戶</t>
+          <t>④ 欣興 (3037) · 10 大戶</t>
         </is>
       </c>
     </row>
@@ -4829,21 +4785,21 @@
     <row r="15">
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>半導體業 · 4 檔 (31%)</t>
+          <t>半導體業 · 4 檔 (33%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="C16" s="66" t="inlineStr">
         <is>
-          <t>電子零組件業 · 3 檔 (23%)</t>
+          <t>電子零組件業 · 3 檔 (25%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="66" t="inlineStr">
         <is>
-          <t>光電業 · 2 檔 (15%)</t>
+          <t>電腦及週邊設備業 · 1 檔 (8%)</t>
         </is>
       </c>
     </row>
@@ -4899,54 +4855,47 @@
     <row r="27">
       <c r="C27" s="69" t="inlineStr">
         <is>
-          <t>⚠️ 玉晶光 (3406) · 10 大戶</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="69" t="inlineStr">
-        <is>
           <t>⚠️ 友達 (2409) · 10 大戶</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="C29" s="64" t="inlineStr">
+        <is>
+          <t>🚫 今日避開</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="C30" s="64" t="inlineStr">
-        <is>
-          <t>🚫 今日避開</t>
+      <c r="C30" s="68" t="inlineStr">
+        <is>
+          <t>今日無除權息</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="68" t="inlineStr">
-        <is>
-          <t>今日無除權息</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" s="66" t="inlineStr">
+      <c r="C31" s="66" t="inlineStr">
         <is>
           <t>明日恐處置 3 檔 (3625 / 4304 / 4971)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="C34" s="64" t="inlineStr">
+    <row r="33">
+      <c r="C33" s="64" t="inlineStr">
         <is>
           <t>📊 追蹤池方向</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="C35" s="70" t="inlineStr">
-        <is>
-          <t>-56 億 淨買</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" s="68" t="inlineStr">
+    <row r="34" ht="22" customHeight="1">
+      <c r="C34" s="70" t="inlineStr">
+        <is>
+          <t>-54 億 淨買</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" s="68" t="inlineStr">
         <is>
           <t>比昨 -199 反彈 / 比 5d -122 偏強</t>
         </is>
@@ -17086,19 +17035,19 @@
         <v>30</v>
       </c>
       <c r="G189" s="133" t="n">
-        <v>10886</v>
+        <v>10106</v>
       </c>
       <c r="H189" s="133" t="n">
-        <v>934</v>
+        <v>3506</v>
       </c>
       <c r="I189" s="133" t="n">
-        <v>9952</v>
+        <v>6600</v>
       </c>
       <c r="J189" s="134" t="n">
-        <v>310.15</v>
+        <v>287.91</v>
       </c>
       <c r="K189" s="134" t="n">
-        <v>311.4</v>
+        <v>1168.57</v>
       </c>
       <c r="L189" s="237">
         <f>F189*(K189-J189)</f>
@@ -17121,16 +17070,16 @@
         <v>0</v>
       </c>
       <c r="G190" s="133" t="n">
-        <v>9549</v>
+        <v>9301</v>
       </c>
       <c r="H190" s="133" t="n">
         <v>0</v>
       </c>
       <c r="I190" s="133" t="n">
-        <v>9549</v>
+        <v>9301</v>
       </c>
       <c r="J190" s="134" t="n">
-        <v>1344.94</v>
+        <v>1310</v>
       </c>
       <c r="K190" s="134" t="n">
         <v>0</v>
@@ -17146,31 +17095,31 @@
       <c r="C191" s="135" t="n"/>
       <c r="D191" s="132" t="inlineStr">
         <is>
-          <t>欣興(3037)</t>
+          <t>台光電(2383)</t>
         </is>
       </c>
       <c r="E191" s="133" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F191" s="133" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G191" s="133" t="n">
-        <v>6166</v>
+        <v>4866</v>
       </c>
       <c r="H191" s="133" t="n">
-        <v>971</v>
+        <v>3215</v>
       </c>
       <c r="I191" s="133" t="n">
-        <v>5195</v>
+        <v>1651</v>
       </c>
       <c r="J191" s="134" t="n">
-        <v>880.87</v>
+        <v>5406.11</v>
       </c>
       <c r="K191" s="134" t="n">
-        <v>882.91</v>
-      </c>
-      <c r="L191" s="237">
+        <v>5358.33</v>
+      </c>
+      <c r="L191" s="236">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -17191,21 +17140,21 @@
         <v>41</v>
       </c>
       <c r="G192" s="133" t="n">
-        <v>4583</v>
+        <v>4494</v>
       </c>
       <c r="H192" s="133" t="n">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="I192" s="133" t="n">
-        <v>3723</v>
+        <v>3629</v>
       </c>
       <c r="J192" s="134" t="n">
-        <v>215.15</v>
+        <v>211</v>
       </c>
       <c r="K192" s="134" t="n">
-        <v>209.63</v>
-      </c>
-      <c r="L192" s="236">
+        <v>211</v>
+      </c>
+      <c r="L192" s="237">
         <f>F192*(K192-J192)</f>
         <v/>
       </c>
@@ -17216,31 +17165,31 @@
       <c r="C193" s="135" t="n"/>
       <c r="D193" s="132" t="inlineStr">
         <is>
-          <t>南亞科(2408)</t>
+          <t>晶豪科(3006)</t>
         </is>
       </c>
       <c r="E193" s="133" t="n">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="F193" s="133" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G193" s="133" t="n">
-        <v>3486</v>
+        <v>2977</v>
       </c>
       <c r="H193" s="133" t="n">
-        <v>3006</v>
+        <v>1868</v>
       </c>
       <c r="I193" s="133" t="n">
-        <v>480</v>
+        <v>1109</v>
       </c>
       <c r="J193" s="134" t="n">
-        <v>497.94</v>
+        <v>278.25</v>
       </c>
       <c r="K193" s="134" t="n">
-        <v>492.87</v>
-      </c>
-      <c r="L193" s="236">
+        <v>278.85</v>
+      </c>
+      <c r="L193" s="237">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -17251,29 +17200,29 @@
       <c r="C194" s="135" t="n"/>
       <c r="D194" s="132" t="inlineStr">
         <is>
-          <t>南電(8046)</t>
+          <t>欣興(3037)</t>
         </is>
       </c>
       <c r="E194" s="133" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="F194" s="133" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G194" s="133" t="n">
-        <v>3331</v>
+        <v>2625</v>
       </c>
       <c r="H194" s="133" t="n">
-        <v>1491</v>
+        <v>1625</v>
       </c>
       <c r="I194" s="133" t="n">
-        <v>1840</v>
+        <v>1000</v>
       </c>
       <c r="J194" s="134" t="n">
-        <v>1040.88</v>
+        <v>374.99</v>
       </c>
       <c r="K194" s="134" t="n">
-        <v>1065.07</v>
+        <v>1477.09</v>
       </c>
       <c r="L194" s="237">
         <f>F194*(K194-J194)</f>
@@ -17286,29 +17235,29 @@
       <c r="C195" s="135" t="n"/>
       <c r="D195" s="132" t="inlineStr">
         <is>
-          <t>強茂(2481)</t>
+          <t>金像電(2368)</t>
         </is>
       </c>
       <c r="E195" s="133" t="n">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="F195" s="133" t="n">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="G195" s="133" t="n">
-        <v>2982</v>
+        <v>1944</v>
       </c>
       <c r="H195" s="133" t="n">
-        <v>2128</v>
+        <v>1263</v>
       </c>
       <c r="I195" s="133" t="n">
-        <v>854</v>
+        <v>681</v>
       </c>
       <c r="J195" s="134" t="n">
-        <v>154.51</v>
+        <v>1022.89</v>
       </c>
       <c r="K195" s="134" t="n">
-        <v>156.49</v>
+        <v>1052.42</v>
       </c>
       <c r="L195" s="237">
         <f>F195*(K195-J195)</f>
@@ -17321,29 +17270,29 @@
       <c r="C196" s="135" t="n"/>
       <c r="D196" s="132" t="inlineStr">
         <is>
-          <t>光聖(6442)</t>
+          <t>永擎(7711)</t>
         </is>
       </c>
       <c r="E196" s="133" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F196" s="133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G196" s="133" t="n">
-        <v>2148</v>
+        <v>1821</v>
       </c>
       <c r="H196" s="133" t="n">
-        <v>535</v>
+        <v>22</v>
       </c>
       <c r="I196" s="133" t="n">
-        <v>1613</v>
+        <v>1799</v>
       </c>
       <c r="J196" s="134" t="n">
-        <v>1789.92</v>
+        <v>628.03</v>
       </c>
       <c r="K196" s="134" t="n">
-        <v>1783</v>
+        <v>221</v>
       </c>
       <c r="L196" s="236">
         <f>F196*(K196-J196)</f>
@@ -17356,31 +17305,31 @@
       <c r="C197" s="135" t="n"/>
       <c r="D197" s="132" t="inlineStr">
         <is>
-          <t>奇鋐(3017)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E197" s="133" t="n">
-        <v>6</v>
+        <v>225</v>
       </c>
       <c r="F197" s="133" t="n">
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="G197" s="133" t="n">
-        <v>2132</v>
+        <v>1677</v>
       </c>
       <c r="H197" s="133" t="n">
-        <v>486</v>
+        <v>971</v>
       </c>
       <c r="I197" s="133" t="n">
-        <v>1646</v>
+        <v>706</v>
       </c>
       <c r="J197" s="134" t="n">
-        <v>3553.33</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="K197" s="134" t="n">
-        <v>4860</v>
-      </c>
-      <c r="L197" s="237">
+        <v>57.81</v>
+      </c>
+      <c r="L197" s="236">
         <f>F197*(K197-J197)</f>
         <v/>
       </c>
@@ -17391,29 +17340,29 @@
       <c r="C198" s="135" t="n"/>
       <c r="D198" s="132" t="inlineStr">
         <is>
-          <t>玉晶光(3406)</t>
+          <t>一詮(2486)</t>
         </is>
       </c>
       <c r="E198" s="133" t="n">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="F198" s="133" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G198" s="133" t="n">
-        <v>1738</v>
+        <v>1483</v>
       </c>
       <c r="H198" s="133" t="n">
-        <v>0</v>
+        <v>1135</v>
       </c>
       <c r="I198" s="133" t="n">
-        <v>1738</v>
+        <v>348</v>
       </c>
       <c r="J198" s="134" t="n">
-        <v>1086.19</v>
+        <v>255.72</v>
       </c>
       <c r="K198" s="134" t="n">
-        <v>0</v>
+        <v>257.86</v>
       </c>
       <c r="L198" s="237">
         <f>F198*(K198-J198)</f>
@@ -28043,7 +27992,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-05 01:12 TW | 17/17 success | 來源: 富邦17/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-05 02:06 TW | 17/17 success | 來源: 富邦17/histock0</t>
         </is>
       </c>
     </row>

--- a/data/reports/latest.xlsx
+++ b/data/reports/latest.xlsx
@@ -24,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="32">
+  <numFmts count="33">
     <numFmt numFmtId="164" formatCode="0%&quot; (13/13 ・昨100/5d100)&quot;"/>
     <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨-177/5d-99)&quot;;-0&quot; 億 (昨-177/5d-99)&quot;;0&quot; 億&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; 檔 +63億 &quot;&quot;(昨15/5d11)&quot;"/>
@@ -57,6 +57,7 @@
     <numFmt numFmtId="193" formatCode="0.0%&quot; 市-444億 &quot;&quot;(昨17/5d18)&quot;"/>
     <numFmt numFmtId="194" formatCode="0.0%&quot; 市-446億 &quot;&quot;(昨17/5d18)&quot;"/>
     <numFmt numFmtId="195" formatCode="0&quot; 檔 +34億 &quot;&quot;(昨14/5d13)&quot;"/>
+    <numFmt numFmtId="196" formatCode="0.0%&quot; 市-447億 &quot;&quot;(昨17/5d18)&quot;"/>
   </numFmts>
   <fonts count="55">
     <font>
@@ -645,7 +646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="268">
+  <cellXfs count="269">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1276,6 +1277,9 @@
     <xf numFmtId="195" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="196" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1361,12 +1365,12 @@
     <comment ref="D17" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「張濬安(航海王)」獨佔比 76.8%
+領頭大戶「張濬安(航海王)」獨佔比 77.7%
   • 領頭金額 41,002 萬
-  • 合計淨買 53,394 萬
+  • 合計淨買 52,762 萬
   • 大戶數 11 位 (名義共識)
 判讀: 名義 11 位大戶共識,
-實質 1 人下注佔 77%,
+實質 1 人下注佔 78%,
 剩餘 10 位為陪襯小單,
 真共識訊號被稀釋.</t>
       </text>
@@ -1374,9 +1378,9 @@
     <comment ref="D20" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
-領頭大戶「陳族元」獨佔比 58.3%
-  • 領頭金額 17,640 萬
-  • 合計淨買 30,280 萬
+領頭大戶「陳族元」獨佔比 58.4%
+  • 領頭金額 17,734 萬
+  • 合計淨買 30,374 萬
   • 大戶數 11 位 (名義共識)
 判讀: 名義 11 位大戶共識,
 實質 1 人下注佔 58%,
@@ -1384,7 +1388,7 @@
 真共識訊號被稀釋.</t>
       </text>
     </comment>
-    <comment ref="D24" authorId="0" shapeId="0">
+    <comment ref="D26" authorId="0" shapeId="0">
       <text>
         <t>⚠️ 假共識警示
 領頭大戶「陳族元」獨佔比 56.2%
@@ -1402,8 +1406,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ConsensusTbl_15" displayName="ConsensusTbl_15" ref="B15:N27" headerRowCount="1">
-  <autoFilter ref="B15:N27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ConsensusTbl_15" displayName="ConsensusTbl_15" ref="B15:N28" headerRowCount="1">
+  <autoFilter ref="B15:N28"/>
   <tableColumns count="13">
     <tableColumn id="2" name="#"/>
     <tableColumn id="3" name="代號"/>
@@ -1712,7 +1716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N120"/>
+  <dimension ref="B2:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1741,14 +1745,14 @@
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>🎯 12 強共識 / Q5 ↑ 偏多 81.7% / E 9 異常 / F 7 長期 / J 0 集中 / H 1 借券壓力</t>
+          <t>🎯 13 強共識 / Q5 ↑ 偏多 81.7% / E 9 異常 / F 7 長期 / J 0 集中 / H 1 借券壓力</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 📌 一般共識 4958 / 6669 / 6147 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 明日恐處置 3 檔: 3625/4304/4971  |  訊號: 強偏多 (Q5 81.7%, hot=17)</t>
+          <t>💡 📌 一般共識 4958 / 6669 / 3037 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 明日恐處置 3 檔: 3625/4304/4971  |  訊號: 強偏多 (Q5 81.7%, hot=17)</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1801,7 @@
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>📊 今日共識集中產業 (top 3): 半導體業 4 (33%)  |  電子零組件業 3 (25%)  |  光電業 1 (8%)</t>
+          <t>📊 今日共識集中產業 (top 3): 半導體業 4 (31%)  |  電子零組件業 3 (23%)  |  光電業 2 (15%)</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1904,7 @@
         <v>10</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
@@ -1908,7 +1912,7 @@
         </is>
       </c>
       <c r="H16" s="17" t="n">
-        <v>27059</v>
+        <v>27429</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1930,7 +1934,7 @@
         <v>7</v>
       </c>
       <c r="N16" s="17" t="n">
-        <v>58382</v>
+        <v>58753</v>
       </c>
     </row>
     <row r="17">
@@ -1981,7 +1985,7 @@
         <v>8</v>
       </c>
       <c r="N17" s="17" t="n">
-        <v>53394</v>
+        <v>52763</v>
       </c>
     </row>
     <row r="18">
@@ -1990,49 +1994,49 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="E18" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>張濬安</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="H18" s="17" t="n">
-        <v>11651</v>
+        <v>14768</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="J18" s="18" t="n">
-        <v>9997</v>
+        <v>5998</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>陳族元</t>
+          <t>蔣承翰</t>
         </is>
       </c>
       <c r="L18" s="18" t="n">
-        <v>3348</v>
+        <v>3591</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N18" s="17" t="n">
-        <v>36271</v>
+        <v>38924</v>
       </c>
     </row>
     <row r="19">
@@ -2041,49 +2045,49 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="E19" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
+          <t>張濬安</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>11651</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>林滄海</t>
         </is>
       </c>
-      <c r="H19" s="17" t="n">
-        <v>14768</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>蔣承翰</t>
-        </is>
-      </c>
       <c r="J19" s="18" t="n">
-        <v>3591</v>
+        <v>9997</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>強森</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="L19" s="18" t="n">
-        <v>3486</v>
+        <v>3348</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N19" s="17" t="n">
-        <v>34729</v>
+        <v>36271</v>
       </c>
     </row>
     <row r="20">
@@ -2112,7 +2116,7 @@
         </is>
       </c>
       <c r="H20" s="17" t="n">
-        <v>17640</v>
+        <v>17734</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2134,7 +2138,7 @@
         <v>8</v>
       </c>
       <c r="N20" s="17" t="n">
-        <v>30281</v>
+        <v>30374</v>
       </c>
     </row>
     <row r="21">
@@ -2171,7 +2175,7 @@
         </is>
       </c>
       <c r="J21" s="18" t="n">
-        <v>6871</v>
+        <v>7373</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2185,7 +2189,7 @@
         <v>9</v>
       </c>
       <c r="N21" s="17" t="n">
-        <v>28861</v>
+        <v>29364</v>
       </c>
     </row>
     <row r="22">
@@ -2265,7 +2269,7 @@
         </is>
       </c>
       <c r="H23" s="17" t="n">
-        <v>10129</v>
+        <v>10229</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2287,7 +2291,7 @@
         <v>8</v>
       </c>
       <c r="N23" s="17" t="n">
-        <v>24653</v>
+        <v>24754</v>
       </c>
     </row>
     <row r="24">
@@ -2296,49 +2300,49 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>📌 🔁 ⚠️ 南亞</t>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>📌 光聖</t>
         </is>
       </c>
       <c r="E24" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
+          <t>張濬安</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>5042</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>陳族元</t>
         </is>
       </c>
-      <c r="H24" s="17" t="n">
-        <v>8414</v>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" s="18" t="n">
+        <v>3035</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>林滄海</t>
         </is>
       </c>
-      <c r="J24" s="18" t="n">
-        <v>1604</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>張濬安</t>
-        </is>
-      </c>
       <c r="L24" s="18" t="n">
-        <v>948</v>
+        <v>2187</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N24" s="17" t="n">
-        <v>14970</v>
+        <v>16004</v>
       </c>
     </row>
     <row r="25">
@@ -2347,35 +2351,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>📌 光聖</t>
+          <t>📌 玉晶光</t>
         </is>
       </c>
       <c r="E25" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>張濬安</t>
+          <t>巨人傑</t>
         </is>
       </c>
       <c r="H25" s="17" t="n">
-        <v>5042</v>
+        <v>4031</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>林滄海</t>
+          <t>蔣承翰</t>
         </is>
       </c>
       <c r="J25" s="18" t="n">
-        <v>2187</v>
+        <v>3815</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2383,13 +2387,13 @@
         </is>
       </c>
       <c r="L25" s="18" t="n">
-        <v>1782</v>
+        <v>3054</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N25" s="17" t="n">
-        <v>14391</v>
+        <v>15740</v>
       </c>
     </row>
     <row r="26">
@@ -2398,49 +2402,49 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>📌 🔁 金像電</t>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>📌 🔁 ⚠️ 南亞</t>
         </is>
       </c>
       <c r="E26" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>竹科主力分點</t>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="H26" s="17" t="n">
-        <v>1862</v>
+        <v>8414</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>陳律師</t>
+          <t>林滄海</t>
         </is>
       </c>
       <c r="J26" s="18" t="n">
-        <v>1613</v>
+        <v>1604</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>蔣承翰</t>
+          <t>張濬安</t>
         </is>
       </c>
       <c r="L26" s="18" t="n">
-        <v>1597</v>
+        <v>948</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N26" s="17" t="n">
-        <v>10995</v>
+        <v>14970</v>
       </c>
     </row>
     <row r="27">
@@ -2449,19 +2453,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>📌 友達</t>
+          <t>📌 🔁 金像電</t>
         </is>
       </c>
       <c r="E27" s="14" t="n">
         <v>10</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
@@ -2469,2138 +2473,2189 @@
         </is>
       </c>
       <c r="H27" s="17" t="n">
-        <v>1821</v>
+        <v>1862</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>張濬安</t>
+          <t>陳律師</t>
         </is>
       </c>
       <c r="J27" s="18" t="n">
-        <v>767</v>
+        <v>1613</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>強森</t>
+          <t>蔣承翰</t>
         </is>
       </c>
       <c r="L27" s="18" t="n">
-        <v>690</v>
+        <v>1597</v>
       </c>
       <c r="M27" s="19" t="n">
         <v>7</v>
       </c>
       <c r="N27" s="17" t="n">
+        <v>10314</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>13</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>📌 友達</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>竹科主力分點</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>1821</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>張濬安</t>
+        </is>
+      </c>
+      <c r="J28" s="18" t="n">
+        <v>767</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>強森</t>
+        </is>
+      </c>
+      <c r="L28" s="18" t="n">
+        <v>690</v>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="N28" s="17" t="n">
         <v>4868</v>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="21" t="inlineStr">
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>▍ A. 追蹤池摘要 (10 秒判讀今日 13 位大戶在做什麼)</t>
         </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="B30" s="22" t="inlineStr">
-        <is>
-          <t>Q1 活躍率</t>
-        </is>
-      </c>
-      <c r="C30" s="207" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="22" t="inlineStr">
-        <is>
-          <t>Q2 淨買差</t>
-        </is>
-      </c>
-      <c r="G30" s="263" t="n">
-        <v>-54.26411</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="B31" s="22" t="inlineStr">
         <is>
+          <t>Q1 活躍率</t>
+        </is>
+      </c>
+      <c r="C31" s="207" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>Q2 淨買差</t>
+        </is>
+      </c>
+      <c r="G31" s="263" t="n">
+        <v>-55.80669</v>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="B32" s="22" t="inlineStr">
+        <is>
           <t>Q3 強共識股</t>
         </is>
       </c>
-      <c r="C31" s="267" t="n">
-        <v>12</v>
-      </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="C32" s="264" t="n">
+        <v>13</v>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G31" s="265" t="n">
-        <v>0.1698439376702703</v>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="211" t="n">
+      <c r="G32" s="268" t="n">
+        <v>0.1700004655337603</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="211" t="n">
         <v>81.7</v>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="28" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>✅ 過去 30 天 P/C 命中率: 偏多 13/21 (62%) | 偏空 1/2 (50%) | 整體 14/23 (61%)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="29" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <t>▍ B. Top 5 高手(按今日總買金額)</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
+      <c r="F36" s="30" t="inlineStr">
         <is>
           <t>▍ C. Top 5 熱門個股(按今日淨買金額)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="31" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C36" s="31" t="inlineStr">
+      <c r="C37" s="31" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D36" s="31" t="inlineStr">
+      <c r="D37" s="31" t="inlineStr">
         <is>
           <t>買進(萬元)</t>
         </is>
       </c>
-      <c r="E36" s="31" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>佔比%</t>
         </is>
       </c>
-      <c r="F36" s="31" t="inlineStr">
+      <c r="F37" s="31" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="G36" s="31" t="inlineStr">
+      <c r="G37" s="31" t="inlineStr">
         <is>
           <t>個股</t>
         </is>
       </c>
-      <c r="H36" s="31" t="inlineStr">
+      <c r="H37" s="31" t="inlineStr">
         <is>
           <t>淨買(萬元)</t>
         </is>
       </c>
-      <c r="I36" s="31" t="inlineStr">
+      <c r="I37" s="31" t="inlineStr">
         <is>
           <t>漲跌%</t>
         </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="32" t="inlineStr">
-        <is>
-          <t>張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="D37" s="33" t="n">
-        <v>1389219</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>32.6%</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>國巨*(2327)</t>
-        </is>
-      </c>
-      <c r="H37" s="33" t="n">
-        <v>286383</v>
-      </c>
-      <c r="I37" s="212" t="n">
-        <v>0.0998</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>2</v>
-      </c>
-      <c r="C38" s="35" t="inlineStr">
-        <is>
-          <t>陳族元</t>
+        <v>1</v>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>張濬安(航海王)</t>
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>934039</v>
+        <v>1389219</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>聯發科(2454)</t>
+          <t>國巨*(2327)</t>
         </is>
       </c>
       <c r="H38" s="33" t="n">
-        <v>155997</v>
+        <v>286383</v>
       </c>
       <c r="I38" s="212" t="n">
-        <v>0.0173</v>
+        <v>0.0998</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>3</v>
-      </c>
-      <c r="C39" s="36" t="inlineStr">
-        <is>
-          <t>陳律師</t>
+        <v>2</v>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>陳族元</t>
         </is>
       </c>
       <c r="D39" s="33" t="n">
-        <v>502119</v>
+        <v>936333</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>聯電(2303)</t>
+          <t>聯發科(2454)</t>
         </is>
       </c>
       <c r="H39" s="33" t="n">
-        <v>141896</v>
+        <v>155997</v>
       </c>
       <c r="I39" s="212" t="n">
-        <v>0.04</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>4</v>
-      </c>
-      <c r="C40" s="38" t="inlineStr">
-        <is>
-          <t>蔣承翰</t>
+        <v>3</v>
+      </c>
+      <c r="C40" s="36" t="inlineStr">
+        <is>
+          <t>陳律師</t>
         </is>
       </c>
       <c r="D40" s="33" t="n">
-        <v>394648</v>
+        <v>502119</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" s="16" t="inlineStr">
         <is>
-          <t>華星光(4979)</t>
+          <t>聯電(2303)</t>
         </is>
       </c>
       <c r="H40" s="33" t="n">
-        <v>129805</v>
+        <v>142050</v>
       </c>
       <c r="I40" s="212" t="n">
-        <v>0.09970000000000001</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="38" t="inlineStr">
+        <is>
+          <t>蔣承翰</t>
+        </is>
+      </c>
+      <c r="D41" s="33" t="n">
+        <v>394648</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>9.3%</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>華星光(4979)</t>
+        </is>
+      </c>
+      <c r="H41" s="33" t="n">
+        <v>129805</v>
+      </c>
+      <c r="I41" s="212" t="n">
+        <v>0.09970000000000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
         <v>5</v>
       </c>
-      <c r="C41" s="37" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
         <is>
           <t>林滄海</t>
         </is>
       </c>
-      <c r="D41" s="33" t="n">
+      <c r="D42" s="33" t="n">
         <v>314114</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>7.4%</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="F42" t="n">
         <v>5</v>
       </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>大量(3167)</t>
+        </is>
+      </c>
+      <c r="H42" s="33" t="n">
+        <v>60112</v>
+      </c>
+      <c r="I42" s="212" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="B45" s="39" t="inlineStr">
+        <is>
+          <t>▍ E. 異常行為警報 (z&gt;2σ 量爆 + 新標的進場)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>嚴重度</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>金額/檔數</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>巨人傑</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>巨人傑 今日買進 7 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>7 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="40" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C48" s="40" t="inlineStr">
+        <is>
+          <t>張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="D48" s="40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E48" s="40" t="inlineStr">
+        <is>
+          <t>張濬安(航海王) 今日買進 5 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F48" s="40" t="inlineStr">
+        <is>
+          <t>5 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>強森</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>強森 今日買進 4 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="40" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C50" s="40" t="inlineStr">
+        <is>
+          <t>蔣承翰</t>
+        </is>
+      </c>
+      <c r="D50" s="40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E50" s="40" t="inlineStr">
+        <is>
+          <t>蔣承翰 今日買進 4 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F50" s="40" t="inlineStr">
+        <is>
+          <t>4 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>迷你哥/松山哥</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>迷你哥/松山哥 今日買進 4 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="40" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C52" s="40" t="inlineStr">
+        <is>
+          <t>Tradow</t>
+        </is>
+      </c>
+      <c r="D52" s="40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E52" s="40" t="inlineStr">
+        <is>
+          <t>Tradow 今日買進 3 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F52" s="40" t="inlineStr">
+        <is>
+          <t>3 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>林滄海</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>林滄海 今日買進 3 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>3 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="40" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C54" s="40" t="inlineStr">
+        <is>
+          <t>竹科主力分點</t>
+        </is>
+      </c>
+      <c r="D54" s="40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E54" s="40" t="inlineStr">
+        <is>
+          <t>竹科主力分點 今日買進 3 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F54" s="40" t="inlineStr">
+        <is>
+          <t>3 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>陳律師</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>陳律師 今日買進 3 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="B57" s="41" t="inlineStr">
+        <is>
+          <t>▍ F. 跨日連續囤貨 Top 30 (按連續天數排序)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="42" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="C58" s="42" t="inlineStr">
+        <is>
+          <t>股票代號</t>
+        </is>
+      </c>
+      <c r="D58" s="42" t="inlineStr">
+        <is>
+          <t>連續天數</t>
+        </is>
+      </c>
+      <c r="E58" s="42" t="inlineStr">
+        <is>
+          <t>累計買金額(萬)</t>
+        </is>
+      </c>
+      <c r="F58" s="42" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>🔴 陳族元</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="D59" s="43" t="n">
+        <v>34</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1360617</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>陳族元 連續 34 天加碼 3008 (累計 1,360,617 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="40" t="inlineStr">
+        <is>
+          <t>🔴 強森</t>
+        </is>
+      </c>
+      <c r="C60" s="40" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="D60" s="44" t="n">
+        <v>25</v>
+      </c>
+      <c r="E60" s="40" t="n">
+        <v>137179</v>
+      </c>
+      <c r="F60" s="40" t="inlineStr">
+        <is>
+          <t>強森 連續 25 天加碼 8299 (累計 137,179 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>🔴 陳族元</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="D61" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="E61" t="n">
+        <v>388436</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>陳族元 連續 22 天加碼 6274 (累計 388,436 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="40" t="inlineStr">
+        <is>
+          <t>🔴 林滄海</t>
+        </is>
+      </c>
+      <c r="C62" s="40" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="D62" s="44" t="n">
+        <v>22</v>
+      </c>
+      <c r="E62" s="40" t="n">
+        <v>201046</v>
+      </c>
+      <c r="F62" s="40" t="inlineStr">
+        <is>
+          <t>林滄海 連續 22 天加碼 6274 (累計 201,046 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>🔴 強森</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D63" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="E63" t="n">
+        <v>134261</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>強森 連續 22 天加碼 6669 (累計 134,261 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="40" t="inlineStr">
+        <is>
+          <t>🔴 張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="C64" s="40" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="D64" s="44" t="n">
+        <v>19</v>
+      </c>
+      <c r="E64" s="40" t="n">
+        <v>643501</v>
+      </c>
+      <c r="F64" s="40" t="inlineStr">
+        <is>
+          <t>張濬安(航海王) 連續 19 天加碼 3008 (累計 643,501 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>🔴 張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="D65" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="E65" t="n">
+        <v>136155</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>張濬安(航海王) 連續 19 天加碼 3481 (累計 136,155 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="B67" s="45" t="inlineStr">
+        <is>
+          <t>▍ J. Master × Top 3 個股 cross-table (今日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="46" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="C68" s="46" t="inlineStr">
+        <is>
+          <t>今日總買(萬)</t>
+        </is>
+      </c>
+      <c r="D68" s="46" t="inlineStr">
+        <is>
+          <t>Top1 個股</t>
+        </is>
+      </c>
+      <c r="E68" s="46" t="inlineStr">
+        <is>
+          <t>Top1 金額</t>
+        </is>
+      </c>
+      <c r="F68" s="46" t="inlineStr">
+        <is>
+          <t>Top2 個股</t>
+        </is>
+      </c>
+      <c r="G68" s="46" t="inlineStr">
+        <is>
+          <t>Top2 金額</t>
+        </is>
+      </c>
+      <c r="H68" s="46" t="inlineStr">
+        <is>
+          <t>Top3 個股</t>
+        </is>
+      </c>
+      <c r="I68" s="46" t="inlineStr">
+        <is>
+          <t>Top3 金額</t>
+        </is>
+      </c>
+      <c r="J68" s="46" t="inlineStr">
+        <is>
+          <t>Top3 合計%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="32" t="inlineStr">
+        <is>
+          <t>張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="C69" s="33" t="n">
+        <v>1228191</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>國巨*(2327)</t>
+        </is>
+      </c>
+      <c r="E69" s="33" t="n">
+        <v>148470</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>華星光(4979)</t>
+        </is>
+      </c>
+      <c r="G69" s="33" t="n">
+        <v>141533</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>聯發科(2454)</t>
+        </is>
+      </c>
+      <c r="I69" s="33" t="n">
+        <v>127234</v>
+      </c>
+      <c r="J69" s="213" t="n">
+        <v>0.3397173858845687</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="35" t="inlineStr">
+        <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="C70" s="33" t="n">
+        <v>900302</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>國巨*(2327)</t>
+        </is>
+      </c>
+      <c r="E70" s="33" t="n">
+        <v>96132</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="G70" s="33" t="n">
+        <v>68843</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>聯發科(2454)</t>
+        </is>
+      </c>
+      <c r="I70" s="33" t="n">
+        <v>61967</v>
+      </c>
+      <c r="J70" s="213" t="n">
+        <v>0.252074192881944</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="36" t="inlineStr">
+        <is>
+          <t>陳律師</t>
+        </is>
+      </c>
+      <c r="C71" s="33" t="n">
+        <v>493661</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>國巨*(2327)</t>
+        </is>
+      </c>
+      <c r="E71" s="33" t="n">
+        <v>90023</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="G71" s="33" t="n">
+        <v>36673</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>緯創(3231)</t>
+        </is>
+      </c>
+      <c r="I71" s="33" t="n">
+        <v>26538</v>
+      </c>
+      <c r="J71" s="213" t="n">
+        <v>0.3104046969912735</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="38" t="inlineStr">
+        <is>
+          <t>蔣承翰</t>
+        </is>
+      </c>
+      <c r="C72" s="33" t="n">
+        <v>388255</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>騰輝電子-KY(6672)</t>
+        </is>
+      </c>
+      <c r="E72" s="33" t="n">
+        <v>91120</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>信昌電(6173)</t>
+        </is>
+      </c>
+      <c r="G72" s="33" t="n">
+        <v>39473</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>國巨*(2327)</t>
+        </is>
+      </c>
+      <c r="I72" s="33" t="n">
+        <v>28060</v>
+      </c>
+      <c r="J72" s="213" t="n">
+        <v>0.4086306098075158</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="37" t="inlineStr">
+        <is>
+          <t>林滄海</t>
+        </is>
+      </c>
+      <c r="C73" s="33" t="n">
+        <v>293349</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="E73" s="33" t="n">
+        <v>37190</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>欣興(3037)</t>
+        </is>
+      </c>
+      <c r="G73" s="33" t="n">
+        <v>18130</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>聯發科(2454)</t>
+        </is>
+      </c>
+      <c r="I73" s="33" t="n">
+        <v>17740</v>
+      </c>
+      <c r="J73" s="213" t="n">
+        <v>0.2490541995313439</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="50" t="inlineStr">
+        <is>
+          <t>強森</t>
+        </is>
+      </c>
+      <c r="C74" s="33" t="n">
+        <v>208780</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>聯發科(2454)</t>
+        </is>
+      </c>
+      <c r="E74" s="33" t="n">
+        <v>30118</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>欣興(3037)</t>
+        </is>
+      </c>
+      <c r="G74" s="33" t="n">
+        <v>11073</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="I74" s="33" t="n">
+        <v>10534</v>
+      </c>
+      <c r="J74" s="213" t="n">
+        <v>0.2477469149402913</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="51" t="inlineStr">
+        <is>
+          <t>竹科主力分點</t>
+        </is>
+      </c>
+      <c r="C75" s="33" t="n">
+        <v>110642</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="E75" s="33" t="n">
+        <v>10533</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>創意(3443)</t>
+        </is>
+      </c>
+      <c r="G75" s="33" t="n">
+        <v>10450</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>京元電子(2449)</t>
+        </is>
+      </c>
+      <c r="I75" s="33" t="n">
+        <v>7335</v>
+      </c>
+      <c r="J75" s="213" t="n">
+        <v>0.255935821723797</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="52" t="inlineStr">
+        <is>
+          <t>民哥</t>
+        </is>
+      </c>
+      <c r="C76" s="33" t="n">
+        <v>98683</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="E76" s="33" t="n">
+        <v>12393</v>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>大立光(3008)</t>
         </is>
       </c>
-      <c r="H41" s="33" t="n">
-        <v>60676</v>
-      </c>
-      <c r="I41" s="212" t="n">
-        <v>0.035</v>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="39" t="inlineStr">
-        <is>
-          <t>▍ E. 異常行為警報 (z&gt;2σ 量爆 + 新標的進場)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="12" t="inlineStr">
+      <c r="G76" s="33" t="n">
+        <v>10122</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>奇鋐(3017)</t>
+        </is>
+      </c>
+      <c r="I76" s="33" t="n">
+        <v>7578</v>
+      </c>
+      <c r="J76" s="213" t="n">
+        <v>0.304947240313204</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="48" t="inlineStr">
+        <is>
+          <t>巨人傑</t>
+        </is>
+      </c>
+      <c r="C77" s="33" t="n">
+        <v>72100</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>大立光(3008)</t>
+        </is>
+      </c>
+      <c r="E77" s="33" t="n">
+        <v>9273</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>聯亞(3081)</t>
+        </is>
+      </c>
+      <c r="G77" s="33" t="n">
+        <v>5468</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>雙鴻(3324)</t>
+        </is>
+      </c>
+      <c r="I77" s="33" t="n">
+        <v>4319</v>
+      </c>
+      <c r="J77" s="213" t="n">
+        <v>0.2643644044876498</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="53" t="inlineStr">
+        <is>
+          <t>布哥/n_nchang</t>
+        </is>
+      </c>
+      <c r="C78" s="33" t="n">
+        <v>54675</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>大立光(3008)</t>
+        </is>
+      </c>
+      <c r="E78" s="33" t="n">
+        <v>5930</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="G78" s="33" t="n">
+        <v>5130</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>玉晶光(3406)</t>
+        </is>
+      </c>
+      <c r="I78" s="33" t="n">
+        <v>4106</v>
+      </c>
+      <c r="J78" s="213" t="n">
+        <v>0.2773790580704161</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="55" t="inlineStr">
+        <is>
+          <t>Tradow</t>
+        </is>
+      </c>
+      <c r="C79" s="33" t="n">
+        <v>51582</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>華通(2313)</t>
+        </is>
+      </c>
+      <c r="E79" s="33" t="n">
+        <v>4996</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>創新服務(7828)</t>
+        </is>
+      </c>
+      <c r="G79" s="33" t="n">
+        <v>4084</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>昇達科(3491)</t>
+        </is>
+      </c>
+      <c r="I79" s="33" t="n">
+        <v>4015</v>
+      </c>
+      <c r="J79" s="213" t="n">
+        <v>0.2538787981008769</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="54" t="inlineStr">
+        <is>
+          <t>大牌分析師</t>
+        </is>
+      </c>
+      <c r="C80" s="33" t="n">
+        <v>48883</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>上詮(3363)</t>
+        </is>
+      </c>
+      <c r="E80" s="33" t="n">
+        <v>5242</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>強茂(2481)</t>
+        </is>
+      </c>
+      <c r="G80" s="33" t="n">
+        <v>4055</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>全新(2455)</t>
+        </is>
+      </c>
+      <c r="I80" s="33" t="n">
+        <v>3413</v>
+      </c>
+      <c r="J80" s="213" t="n">
+        <v>0.2600029048775349</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="56" t="inlineStr">
+        <is>
+          <t>迷你哥/松山哥</t>
+        </is>
+      </c>
+      <c r="C81" s="33" t="n">
+        <v>32928</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>強茂(2481)</t>
+        </is>
+      </c>
+      <c r="E81" s="33" t="n">
+        <v>4696</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>聯發科(2454)</t>
+        </is>
+      </c>
+      <c r="G81" s="33" t="n">
+        <v>4398</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>南亞科(2408)</t>
+        </is>
+      </c>
+      <c r="I81" s="33" t="n">
+        <v>3956</v>
+      </c>
+      <c r="J81" s="213" t="n">
+        <v>0.3962913360240279</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="B83" s="57" t="inlineStr">
+        <is>
+          <t>▍ G. 注意股 (資料日 20260905)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="58" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C84" s="58" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D84" s="58" t="inlineStr">
+        <is>
+          <t>累計次數</t>
+        </is>
+      </c>
+      <c r="E84" s="58" t="inlineStr">
+        <is>
+          <t>收盤價</t>
+        </is>
+      </c>
+      <c r="F84" s="58" t="inlineStr">
+        <is>
+          <t>本益比</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="262" t="inlineStr">
+        <is>
+          <t>✅ 今日無新增注意股 (市場無異常波動標的)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260904)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>借券張數</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>融券張數</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>台新新光金</t>
+        </is>
+      </c>
+      <c r="D89" s="33" t="n">
+        <v>11010</v>
+      </c>
+      <c r="E89" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="F89" s="215" t="n">
+        <v>200.18</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="40" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="C90" s="40" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="D90" s="60" t="n">
+        <v>7788</v>
+      </c>
+      <c r="E90" s="60" t="n">
+        <v>25</v>
+      </c>
+      <c r="F90" s="216" t="n">
+        <v>311.52</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="D91" s="33" t="n">
+        <v>6429</v>
+      </c>
+      <c r="E91" s="33" t="n">
+        <v>91</v>
+      </c>
+      <c r="F91" s="215" t="n">
+        <v>70.65000000000001</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="40" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="C92" s="40" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="D92" s="60" t="n">
+        <v>5267</v>
+      </c>
+      <c r="E92" s="60" t="n">
+        <v>482</v>
+      </c>
+      <c r="F92" s="216" t="n">
+        <v>10.93</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="D93" s="33" t="n">
+        <v>5042</v>
+      </c>
+      <c r="E93" s="33" t="n">
+        <v>315</v>
+      </c>
+      <c r="F93" s="215" t="n">
+        <v>16.01</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="40" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="C94" s="40" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="D94" s="60" t="n">
+        <v>4941</v>
+      </c>
+      <c r="E94" s="60" t="n">
+        <v>95</v>
+      </c>
+      <c r="F94" s="216" t="n">
+        <v>52.01</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>6770</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>力積電</t>
+        </is>
+      </c>
+      <c r="D95" s="33" t="n">
+        <v>4064</v>
+      </c>
+      <c r="E95" s="33" t="n">
+        <v>315</v>
+      </c>
+      <c r="F95" s="215" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="40" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C96" s="40" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D96" s="60" t="n">
+        <v>3827</v>
+      </c>
+      <c r="E96" s="60" t="n">
+        <v>88</v>
+      </c>
+      <c r="F96" s="216" t="n">
+        <v>43.49</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="D97" s="33" t="n">
+        <v>3520</v>
+      </c>
+      <c r="E97" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="F97" s="215" t="n">
+        <v>135.38</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="40" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="C98" s="40" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="D98" s="60" t="n">
+        <v>3459</v>
+      </c>
+      <c r="E98" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="F98" s="216" t="n">
+        <v>432.38</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D99" s="33" t="n">
+        <v>2964</v>
+      </c>
+      <c r="E99" s="33" t="n">
+        <v>84</v>
+      </c>
+      <c r="F99" s="215" t="n">
+        <v>35.29</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="40" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C100" s="40" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D100" s="60" t="n">
+        <v>2817</v>
+      </c>
+      <c r="E100" s="60" t="n">
+        <v>66</v>
+      </c>
+      <c r="F100" s="216" t="n">
+        <v>42.68</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="43" t="inlineStr">
+        <is>
+          <t>🔴 2801</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>彰銀</t>
+        </is>
+      </c>
+      <c r="D101" s="33" t="n">
+        <v>2621</v>
+      </c>
+      <c r="E101" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" s="252" t="n">
+        <v>1310.5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="40" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C102" s="40" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D102" s="60" t="n">
+        <v>2478</v>
+      </c>
+      <c r="E102" s="60" t="n">
+        <v>45</v>
+      </c>
+      <c r="F102" s="216" t="n">
+        <v>55.07</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D103" s="33" t="n">
+        <v>2397</v>
+      </c>
+      <c r="E103" s="33" t="n">
+        <v>188</v>
+      </c>
+      <c r="F103" s="215" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="B105" s="62" t="inlineStr">
+        <is>
+          <t>▍ I. 未來 30 天除權息 (有效 74 檔, 已剔除過期)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="58" t="inlineStr">
+        <is>
+          <t>除權息日</t>
+        </is>
+      </c>
+      <c r="C106" s="58" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="D106" s="58" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="E106" s="58" t="inlineStr">
         <is>
           <t>類型</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>Master</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>嚴重度</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>說明</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>金額/檔數</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>巨人傑</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>巨人傑 今日買進 7 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>7 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="40" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C47" s="40" t="inlineStr">
-        <is>
-          <t>張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="D47" s="40" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E47" s="40" t="inlineStr">
-        <is>
-          <t>張濬安(航海王) 今日買進 5 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F47" s="40" t="inlineStr">
-        <is>
-          <t>5 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>強森</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>強森 今日買進 4 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>4 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="40" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C49" s="40" t="inlineStr">
-        <is>
-          <t>蔣承翰</t>
-        </is>
-      </c>
-      <c r="D49" s="40" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E49" s="40" t="inlineStr">
-        <is>
-          <t>蔣承翰 今日買進 4 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F49" s="40" t="inlineStr">
-        <is>
-          <t>4 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>迷你哥/松山哥</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>迷你哥/松山哥 今日買進 4 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>4 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="40" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C51" s="40" t="inlineStr">
-        <is>
-          <t>Tradow</t>
-        </is>
-      </c>
-      <c r="D51" s="40" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E51" s="40" t="inlineStr">
-        <is>
-          <t>Tradow 今日買進 3 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F51" s="40" t="inlineStr">
-        <is>
-          <t>3 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>林滄海</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>林滄海 今日買進 3 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>3 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="40" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C53" s="40" t="inlineStr">
-        <is>
-          <t>竹科主力分點</t>
-        </is>
-      </c>
-      <c r="D53" s="40" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E53" s="40" t="inlineStr">
-        <is>
-          <t>竹科主力分點 今日買進 3 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F53" s="40" t="inlineStr">
-        <is>
-          <t>3 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>陳律師</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>陳律師 今日買進 3 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>3 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="B56" s="41" t="inlineStr">
-        <is>
-          <t>▍ F. 跨日連續囤貨 Top 30 (按連續天數排序)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="42" t="inlineStr">
-        <is>
-          <t>Master</t>
-        </is>
-      </c>
-      <c r="C57" s="42" t="inlineStr">
-        <is>
-          <t>股票代號</t>
-        </is>
-      </c>
-      <c r="D57" s="42" t="inlineStr">
-        <is>
-          <t>連續天數</t>
-        </is>
-      </c>
-      <c r="E57" s="42" t="inlineStr">
-        <is>
-          <t>累計買金額(萬)</t>
-        </is>
-      </c>
-      <c r="F57" s="42" t="inlineStr">
-        <is>
-          <t>說明</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>🔴 陳族元</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="D58" s="43" t="n">
-        <v>34</v>
-      </c>
-      <c r="E58" t="n">
-        <v>1361455</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>陳族元 連續 34 天加碼 3008 (累計 1,361,455 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="40" t="inlineStr">
-        <is>
-          <t>🔴 強森</t>
-        </is>
-      </c>
-      <c r="C59" s="40" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
-      </c>
-      <c r="D59" s="44" t="n">
+      <c r="F106" s="58" t="inlineStr">
+        <is>
+          <t>現金股利</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>主動國泰動能高息</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="40" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C108" s="40" t="inlineStr">
+        <is>
+          <t>01010T</t>
+        </is>
+      </c>
+      <c r="D108" s="40" t="inlineStr">
+        <is>
+          <t>京城樂富R1</t>
+        </is>
+      </c>
+      <c r="E108" s="40" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F108" s="40" t="n">
+        <v>0.09872</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>聚隆</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="40" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C110" s="40" t="inlineStr">
+        <is>
+          <t>6533</t>
+        </is>
+      </c>
+      <c r="D110" s="40" t="inlineStr">
+        <is>
+          <t>晶心科</t>
+        </is>
+      </c>
+      <c r="E110" s="40" t="inlineStr">
+        <is>
+          <t>權</t>
+        </is>
+      </c>
+      <c r="F110" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>00940</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>元大台灣價值高息</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="40" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C112" s="40" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="D112" s="40" t="inlineStr">
+        <is>
+          <t>瑞昱</t>
+        </is>
+      </c>
+      <c r="E112" s="40" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F112" s="40" t="n">
         <v>25</v>
       </c>
-      <c r="E59" s="40" t="n">
-        <v>137179</v>
-      </c>
-      <c r="F59" s="40" t="inlineStr">
-        <is>
-          <t>強森 連續 25 天加碼 8299 (累計 137,179 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>🔴 陳族元</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="D60" s="43" t="n">
-        <v>22</v>
-      </c>
-      <c r="E60" t="n">
-        <v>387681</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>陳族元 連續 22 天加碼 6274 (累計 387,681 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="40" t="inlineStr">
-        <is>
-          <t>🔴 林滄海</t>
-        </is>
-      </c>
-      <c r="C61" s="40" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="D61" s="44" t="n">
-        <v>22</v>
-      </c>
-      <c r="E61" s="40" t="n">
-        <v>201046</v>
-      </c>
-      <c r="F61" s="40" t="inlineStr">
-        <is>
-          <t>林滄海 連續 22 天加碼 6274 (累計 201,046 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>🔴 強森</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="D62" s="43" t="n">
-        <v>22</v>
-      </c>
-      <c r="E62" t="n">
-        <v>134261</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>強森 連續 22 天加碼 6669 (累計 134,261 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="40" t="inlineStr">
-        <is>
-          <t>🔴 張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="C63" s="40" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="D63" s="44" t="n">
-        <v>19</v>
-      </c>
-      <c r="E63" s="40" t="n">
-        <v>643501</v>
-      </c>
-      <c r="F63" s="40" t="inlineStr">
-        <is>
-          <t>張濬安(航海王) 連續 19 天加碼 3008 (累計 643,501 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>🔴 張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="D64" s="43" t="n">
-        <v>19</v>
-      </c>
-      <c r="E64" t="n">
-        <v>136155</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>張濬安(航海王) 連續 19 天加碼 3481 (累計 136,155 萬)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="B66" s="45" t="inlineStr">
-        <is>
-          <t>▍ J. Master × Top 3 個股 cross-table (今日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="46" t="inlineStr">
-        <is>
-          <t>Master</t>
-        </is>
-      </c>
-      <c r="C67" s="46" t="inlineStr">
-        <is>
-          <t>今日總買(萬)</t>
-        </is>
-      </c>
-      <c r="D67" s="46" t="inlineStr">
-        <is>
-          <t>Top1 個股</t>
-        </is>
-      </c>
-      <c r="E67" s="46" t="inlineStr">
-        <is>
-          <t>Top1 金額</t>
-        </is>
-      </c>
-      <c r="F67" s="46" t="inlineStr">
-        <is>
-          <t>Top2 個股</t>
-        </is>
-      </c>
-      <c r="G67" s="46" t="inlineStr">
-        <is>
-          <t>Top2 金額</t>
-        </is>
-      </c>
-      <c r="H67" s="46" t="inlineStr">
-        <is>
-          <t>Top3 個股</t>
-        </is>
-      </c>
-      <c r="I67" s="46" t="inlineStr">
-        <is>
-          <t>Top3 金額</t>
-        </is>
-      </c>
-      <c r="J67" s="46" t="inlineStr">
-        <is>
-          <t>Top3 合計%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="32" t="inlineStr">
-        <is>
-          <t>張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="C68" s="33" t="n">
-        <v>1228191</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>國巨*(2327)</t>
-        </is>
-      </c>
-      <c r="E68" s="33" t="n">
-        <v>148470</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>華星光(4979)</t>
-        </is>
-      </c>
-      <c r="G68" s="33" t="n">
-        <v>141533</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>聯發科(2454)</t>
-        </is>
-      </c>
-      <c r="I68" s="33" t="n">
-        <v>127234</v>
-      </c>
-      <c r="J68" s="213" t="n">
-        <v>0.3397173858845687</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="35" t="inlineStr">
-        <is>
-          <t>陳族元</t>
-        </is>
-      </c>
-      <c r="C69" s="33" t="n">
-        <v>898008</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>國巨*(2327)</t>
-        </is>
-      </c>
-      <c r="E69" s="33" t="n">
-        <v>96132</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>聯電(2303)</t>
-        </is>
-      </c>
-      <c r="G69" s="33" t="n">
-        <v>68872</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>聯發科(2454)</t>
-        </is>
-      </c>
-      <c r="I69" s="33" t="n">
-        <v>61967</v>
-      </c>
-      <c r="J69" s="213" t="n">
-        <v>0.2527497809317713</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="36" t="inlineStr">
-        <is>
-          <t>陳律師</t>
-        </is>
-      </c>
-      <c r="C70" s="33" t="n">
-        <v>493661</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>國巨*(2327)</t>
-        </is>
-      </c>
-      <c r="E70" s="33" t="n">
-        <v>90023</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="G70" s="33" t="n">
-        <v>36673</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>緯創(3231)</t>
-        </is>
-      </c>
-      <c r="I70" s="33" t="n">
-        <v>26538</v>
-      </c>
-      <c r="J70" s="213" t="n">
-        <v>0.3104046969912735</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="38" t="inlineStr">
-        <is>
-          <t>蔣承翰</t>
-        </is>
-      </c>
-      <c r="C71" s="33" t="n">
-        <v>388255</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>騰輝電子-KY(6672)</t>
-        </is>
-      </c>
-      <c r="E71" s="33" t="n">
-        <v>91120</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>信昌電(6173)</t>
-        </is>
-      </c>
-      <c r="G71" s="33" t="n">
-        <v>39473</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>國巨*(2327)</t>
-        </is>
-      </c>
-      <c r="I71" s="33" t="n">
-        <v>28060</v>
-      </c>
-      <c r="J71" s="213" t="n">
-        <v>0.4086306098075158</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="37" t="inlineStr">
-        <is>
-          <t>林滄海</t>
-        </is>
-      </c>
-      <c r="C72" s="33" t="n">
-        <v>293349</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>聯電(2303)</t>
-        </is>
-      </c>
-      <c r="E72" s="33" t="n">
-        <v>37190</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>欣興(3037)</t>
-        </is>
-      </c>
-      <c r="G72" s="33" t="n">
-        <v>18130</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>聯發科(2454)</t>
-        </is>
-      </c>
-      <c r="I72" s="33" t="n">
-        <v>17740</v>
-      </c>
-      <c r="J72" s="213" t="n">
-        <v>0.2490541995313439</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="50" t="inlineStr">
-        <is>
-          <t>強森</t>
-        </is>
-      </c>
-      <c r="C73" s="33" t="n">
-        <v>208780</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>聯發科(2454)</t>
-        </is>
-      </c>
-      <c r="E73" s="33" t="n">
-        <v>30118</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>欣興(3037)</t>
-        </is>
-      </c>
-      <c r="G73" s="33" t="n">
-        <v>11073</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="I73" s="33" t="n">
-        <v>10534</v>
-      </c>
-      <c r="J73" s="213" t="n">
-        <v>0.2477469149402913</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="51" t="inlineStr">
-        <is>
-          <t>竹科主力分點</t>
-        </is>
-      </c>
-      <c r="C74" s="33" t="n">
-        <v>110642</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="E74" s="33" t="n">
-        <v>10533</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>創意(3443)</t>
-        </is>
-      </c>
-      <c r="G74" s="33" t="n">
-        <v>10450</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>京元電子(2449)</t>
-        </is>
-      </c>
-      <c r="I74" s="33" t="n">
-        <v>7335</v>
-      </c>
-      <c r="J74" s="213" t="n">
-        <v>0.255935821723797</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="52" t="inlineStr">
-        <is>
-          <t>民哥</t>
-        </is>
-      </c>
-      <c r="C75" s="33" t="n">
-        <v>98683</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="E75" s="33" t="n">
-        <v>12393</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>大立光(3008)</t>
-        </is>
-      </c>
-      <c r="G75" s="33" t="n">
-        <v>10122</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>奇鋐(3017)</t>
-        </is>
-      </c>
-      <c r="I75" s="33" t="n">
-        <v>7578</v>
-      </c>
-      <c r="J75" s="213" t="n">
-        <v>0.304947240313204</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="48" t="inlineStr">
-        <is>
-          <t>巨人傑</t>
-        </is>
-      </c>
-      <c r="C76" s="33" t="n">
-        <v>72100</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>大立光(3008)</t>
-        </is>
-      </c>
-      <c r="E76" s="33" t="n">
-        <v>9273</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>聯亞(3081)</t>
-        </is>
-      </c>
-      <c r="G76" s="33" t="n">
-        <v>5468</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>雙鴻(3324)</t>
-        </is>
-      </c>
-      <c r="I76" s="33" t="n">
-        <v>4319</v>
-      </c>
-      <c r="J76" s="213" t="n">
-        <v>0.2643644044876498</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="53" t="inlineStr">
-        <is>
-          <t>布哥/n_nchang</t>
-        </is>
-      </c>
-      <c r="C77" s="33" t="n">
-        <v>54675</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>大立光(3008)</t>
-        </is>
-      </c>
-      <c r="E77" s="33" t="n">
-        <v>5930</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="G77" s="33" t="n">
-        <v>5130</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>玉晶光(3406)</t>
-        </is>
-      </c>
-      <c r="I77" s="33" t="n">
-        <v>4106</v>
-      </c>
-      <c r="J77" s="213" t="n">
-        <v>0.2773790580704161</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="55" t="inlineStr">
-        <is>
-          <t>Tradow</t>
-        </is>
-      </c>
-      <c r="C78" s="33" t="n">
-        <v>51582</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>華通(2313)</t>
-        </is>
-      </c>
-      <c r="E78" s="33" t="n">
-        <v>4996</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>創新服務(7828)</t>
-        </is>
-      </c>
-      <c r="G78" s="33" t="n">
-        <v>4084</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>昇達科(3491)</t>
-        </is>
-      </c>
-      <c r="I78" s="33" t="n">
-        <v>4015</v>
-      </c>
-      <c r="J78" s="213" t="n">
-        <v>0.2538787981008769</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="54" t="inlineStr">
-        <is>
-          <t>大牌分析師</t>
-        </is>
-      </c>
-      <c r="C79" s="33" t="n">
-        <v>48883</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>上詮(3363)</t>
-        </is>
-      </c>
-      <c r="E79" s="33" t="n">
-        <v>5242</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>強茂(2481)</t>
-        </is>
-      </c>
-      <c r="G79" s="33" t="n">
-        <v>4055</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>全新(2455)</t>
-        </is>
-      </c>
-      <c r="I79" s="33" t="n">
-        <v>3413</v>
-      </c>
-      <c r="J79" s="213" t="n">
-        <v>0.2600029048775349</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="56" t="inlineStr">
-        <is>
-          <t>迷你哥/松山哥</t>
-        </is>
-      </c>
-      <c r="C80" s="33" t="n">
-        <v>32928</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>強茂(2481)</t>
-        </is>
-      </c>
-      <c r="E80" s="33" t="n">
-        <v>4696</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>聯發科(2454)</t>
-        </is>
-      </c>
-      <c r="G80" s="33" t="n">
-        <v>4398</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>南亞科(2408)</t>
-        </is>
-      </c>
-      <c r="I80" s="33" t="n">
-        <v>3956</v>
-      </c>
-      <c r="J80" s="213" t="n">
-        <v>0.3962913360240279</v>
-      </c>
-    </row>
-    <row r="82" ht="22" customHeight="1">
-      <c r="B82" s="57" t="inlineStr">
-        <is>
-          <t>▍ G. 注意股 (資料日 20260905)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="58" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C83" s="58" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D83" s="58" t="inlineStr">
-        <is>
-          <t>累計次數</t>
-        </is>
-      </c>
-      <c r="E83" s="58" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F83" s="58" t="inlineStr">
-        <is>
-          <t>本益比</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="262" t="inlineStr">
-        <is>
-          <t>✅ 今日無新增注意股 (市場無異常波動標的)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260904)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C87" s="12" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>借券張數</t>
-        </is>
-      </c>
-      <c r="E87" s="12" t="inlineStr">
-        <is>
-          <t>融券張數</t>
-        </is>
-      </c>
-      <c r="F87" s="12" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D88" s="33" t="n">
-        <v>11010</v>
-      </c>
-      <c r="E88" s="33" t="n">
-        <v>55</v>
-      </c>
-      <c r="F88" s="215" t="n">
-        <v>200.18</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="40" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C89" s="40" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D89" s="60" t="n">
-        <v>7788</v>
-      </c>
-      <c r="E89" s="60" t="n">
-        <v>25</v>
-      </c>
-      <c r="F89" s="216" t="n">
-        <v>311.52</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2481</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>強茂</t>
-        </is>
-      </c>
-      <c r="D90" s="33" t="n">
-        <v>6429</v>
-      </c>
-      <c r="E90" s="33" t="n">
-        <v>91</v>
-      </c>
-      <c r="F90" s="215" t="n">
-        <v>70.65000000000001</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="40" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="C91" s="40" t="inlineStr">
-        <is>
-          <t>群創</t>
-        </is>
-      </c>
-      <c r="D91" s="60" t="n">
-        <v>5267</v>
-      </c>
-      <c r="E91" s="60" t="n">
-        <v>482</v>
-      </c>
-      <c r="F91" s="216" t="n">
-        <v>10.93</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="D92" s="33" t="n">
-        <v>5042</v>
-      </c>
-      <c r="E92" s="33" t="n">
-        <v>315</v>
-      </c>
-      <c r="F92" s="215" t="n">
-        <v>16.01</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="40" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="C93" s="40" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-      <c r="D93" s="60" t="n">
-        <v>4941</v>
-      </c>
-      <c r="E93" s="60" t="n">
-        <v>95</v>
-      </c>
-      <c r="F93" s="216" t="n">
-        <v>52.01</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="D94" s="33" t="n">
-        <v>4064</v>
-      </c>
-      <c r="E94" s="33" t="n">
-        <v>315</v>
-      </c>
-      <c r="F94" s="215" t="n">
-        <v>12.9</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="40" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C95" s="40" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D95" s="60" t="n">
-        <v>3827</v>
-      </c>
-      <c r="E95" s="60" t="n">
-        <v>88</v>
-      </c>
-      <c r="F95" s="216" t="n">
-        <v>43.49</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D96" s="33" t="n">
-        <v>3520</v>
-      </c>
-      <c r="E96" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="F96" s="215" t="n">
-        <v>135.38</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="40" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C97" s="40" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D97" s="60" t="n">
-        <v>3459</v>
-      </c>
-      <c r="E97" s="60" t="n">
-        <v>8</v>
-      </c>
-      <c r="F97" s="216" t="n">
-        <v>432.38</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D98" s="33" t="n">
-        <v>2964</v>
-      </c>
-      <c r="E98" s="33" t="n">
-        <v>84</v>
-      </c>
-      <c r="F98" s="215" t="n">
-        <v>35.29</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="40" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="C99" s="40" t="inlineStr">
-        <is>
-          <t>富邦金</t>
-        </is>
-      </c>
-      <c r="D99" s="60" t="n">
-        <v>2817</v>
-      </c>
-      <c r="E99" s="60" t="n">
-        <v>66</v>
-      </c>
-      <c r="F99" s="216" t="n">
-        <v>42.68</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="43" t="inlineStr">
-        <is>
-          <t>🔴 2801</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="D100" s="33" t="n">
-        <v>2621</v>
-      </c>
-      <c r="E100" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F100" s="252" t="n">
-        <v>1310.5</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="40" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="C101" s="40" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="D101" s="60" t="n">
-        <v>2478</v>
-      </c>
-      <c r="E101" s="60" t="n">
-        <v>45</v>
-      </c>
-      <c r="F101" s="216" t="n">
-        <v>55.07</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="D102" s="33" t="n">
-        <v>2397</v>
-      </c>
-      <c r="E102" s="33" t="n">
-        <v>188</v>
-      </c>
-      <c r="F102" s="215" t="n">
-        <v>12.75</v>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="1">
-      <c r="B104" s="62" t="inlineStr">
-        <is>
-          <t>▍ I. 未來 30 天除權息 (有效 74 檔, 已剔除過期)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="58" t="inlineStr">
-        <is>
-          <t>除權息日</t>
-        </is>
-      </c>
-      <c r="C105" s="58" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="D105" s="58" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="E105" s="58" t="inlineStr">
-        <is>
-          <t>類型</t>
-        </is>
-      </c>
-      <c r="F105" s="58" t="inlineStr">
-        <is>
-          <t>現金股利</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2442</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>新美齊</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>2.031861</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="40" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C114" s="40" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="D114" s="40" t="inlineStr">
+        <is>
+          <t>第一店</t>
+        </is>
+      </c>
+      <c r="E114" s="40" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F106" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="40" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="C107" s="40" t="inlineStr">
-        <is>
-          <t>01010T</t>
-        </is>
-      </c>
-      <c r="D107" s="40" t="inlineStr">
-        <is>
-          <t>京城樂富R1</t>
-        </is>
-      </c>
-      <c r="E107" s="40" t="inlineStr">
+      <c r="F114" s="40" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>弘憶股</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F107" s="40" t="n">
-        <v>0.09872</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>1466</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>聚隆</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
+      <c r="F115" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="40" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C116" s="40" t="inlineStr">
+        <is>
+          <t>3622</t>
+        </is>
+      </c>
+      <c r="D116" s="40" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="E116" s="40" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F108" t="n">
+      <c r="F116" s="40" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>8473</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>山林水</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>0.782345</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="40" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C118" s="40" t="inlineStr">
+        <is>
+          <t>9933</t>
+        </is>
+      </c>
+      <c r="D118" s="40" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="E118" s="40" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F118" s="40" t="n">
+        <v>0.763056</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>三地開發</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="109">
-      <c r="B109" s="40" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="C109" s="40" t="inlineStr">
-        <is>
-          <t>6533</t>
-        </is>
-      </c>
-      <c r="D109" s="40" t="inlineStr">
-        <is>
-          <t>晶心科</t>
-        </is>
-      </c>
-      <c r="E109" s="40" t="inlineStr">
-        <is>
-          <t>權</t>
-        </is>
-      </c>
-      <c r="F109" s="40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>00940</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>元大台灣價值高息</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
+    <row r="120">
+      <c r="B120" s="40" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C120" s="40" t="inlineStr">
+        <is>
+          <t>3059</t>
+        </is>
+      </c>
+      <c r="D120" s="40" t="inlineStr">
+        <is>
+          <t>華晶科</t>
+        </is>
+      </c>
+      <c r="E120" s="40" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F110" t="n">
-        <v>0.055</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="40" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C111" s="40" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="D111" s="40" t="inlineStr">
-        <is>
-          <t>瑞昱</t>
-        </is>
-      </c>
-      <c r="E111" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F111" s="40" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2442</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>新美齊</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
+      <c r="F120" s="40" t="n">
+        <v>0.998614</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>神達</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
         <is>
           <t>權息</t>
         </is>
       </c>
-      <c r="F112" t="n">
-        <v>2.031861</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="B113" s="40" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C113" s="40" t="inlineStr">
-        <is>
-          <t>2706</t>
-        </is>
-      </c>
-      <c r="D113" s="40" t="inlineStr">
-        <is>
-          <t>第一店</t>
-        </is>
-      </c>
-      <c r="E113" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F113" s="40" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>3312</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>弘憶股</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="40" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C115" s="40" t="inlineStr">
-        <is>
-          <t>3622</t>
-        </is>
-      </c>
-      <c r="D115" s="40" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="E115" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F115" s="40" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>8473</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>山林水</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>權息</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>0.782345</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="40" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="C117" s="40" t="inlineStr">
-        <is>
-          <t>9933</t>
-        </is>
-      </c>
-      <c r="D117" s="40" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="E117" s="40" t="inlineStr">
-        <is>
-          <t>權息</t>
-        </is>
-      </c>
-      <c r="F117" s="40" t="n">
-        <v>0.763056</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>1438</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>三地開發</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>權息</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="40" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="C119" s="40" t="inlineStr">
-        <is>
-          <t>3059</t>
-        </is>
-      </c>
-      <c r="D119" s="40" t="inlineStr">
-        <is>
-          <t>華晶科</t>
-        </is>
-      </c>
-      <c r="E119" s="40" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F119" s="40" t="n">
-        <v>0.998614</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3706</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>神達</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>權息</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
+      <c r="F121" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B67:J67"/>
     <mergeCell ref="B9:N9"/>
+    <mergeCell ref="B57:J57"/>
     <mergeCell ref="B33:N33"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B44:J44"/>
-    <mergeCell ref="B82:J82"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B32:N32"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B87:J87"/>
     <mergeCell ref="B4:N4"/>
     <mergeCell ref="B7:N7"/>
+    <mergeCell ref="B83:J83"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B104:J104"/>
-    <mergeCell ref="B86:J86"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="B45:J45"/>
     <mergeCell ref="G31:I31"/>
     <mergeCell ref="B12:N12"/>
     <mergeCell ref="B11:N11"/>
-    <mergeCell ref="B84:F84"/>
     <mergeCell ref="B2:N2"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="B14:N14"/>
-    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="C32:D32"/>
     <mergeCell ref="B8:N8"/>
-    <mergeCell ref="B66:J66"/>
     <mergeCell ref="B13:N13"/>
-    <mergeCell ref="B56:J56"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B105:J105"/>
+    <mergeCell ref="B34:N34"/>
     <mergeCell ref="B10:N10"/>
   </mergeCells>
-  <conditionalFormatting sqref="N16:N27">
+  <conditionalFormatting sqref="N16:N28">
     <cfRule type="dataBar" priority="1">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4609,7 +4664,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E16:E27">
+  <conditionalFormatting sqref="E16:E28">
     <cfRule type="dataBar" priority="2">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4618,7 +4673,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D37:D41">
+  <conditionalFormatting sqref="D38:D42">
     <cfRule type="dataBar" priority="3">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4627,7 +4682,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H37:H41">
+  <conditionalFormatting sqref="H38:H42">
     <cfRule type="dataBar" priority="4">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4636,7 +4691,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D58:D64">
+  <conditionalFormatting sqref="D59:D65">
     <cfRule type="dataBar" priority="5">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4645,7 +4700,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E58:E64">
+  <conditionalFormatting sqref="E59:E65">
     <cfRule type="dataBar" priority="6">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4654,7 +4709,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C68:C80">
+  <conditionalFormatting sqref="C69:C81">
     <cfRule type="dataBar" priority="7">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4663,7 +4718,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J68:J80">
+  <conditionalFormatting sqref="J69:J81">
     <cfRule type="dataBar" priority="8">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4672,7 +4727,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D88:D102">
+  <conditionalFormatting sqref="D89:D103">
     <cfRule type="dataBar" priority="9">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4681,7 +4736,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F88:F102">
+  <conditionalFormatting sqref="F89:F103">
     <cfRule type="dataBar" priority="10">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -4704,7 +4759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:C35"/>
+  <dimension ref="C2:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="2" max="2"/>
@@ -4757,14 +4812,14 @@
     <row r="10">
       <c r="C10" s="66" t="inlineStr">
         <is>
-          <t>③ 頎邦 (6147) · 11 大戶</t>
+          <t>③ 欣興 (3037) · 10 大戶</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="66" t="inlineStr">
         <is>
-          <t>④ 欣興 (3037) · 10 大戶</t>
+          <t>④ 頎邦 (6147) · 11 大戶</t>
         </is>
       </c>
     </row>
@@ -4785,21 +4840,21 @@
     <row r="15">
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>半導體業 · 4 檔 (33%)</t>
+          <t>半導體業 · 4 檔 (31%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="C16" s="66" t="inlineStr">
         <is>
-          <t>電子零組件業 · 3 檔 (25%)</t>
+          <t>電子零組件業 · 3 檔 (23%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="66" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業 · 1 檔 (8%)</t>
+          <t>光電業 · 2 檔 (15%)</t>
         </is>
       </c>
     </row>
@@ -4855,47 +4910,54 @@
     <row r="27">
       <c r="C27" s="69" t="inlineStr">
         <is>
+          <t>⚠️ 玉晶光 (3406) · 10 大戶</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="69" t="inlineStr">
+        <is>
           <t>⚠️ 友達 (2409) · 10 大戶</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="C29" s="64" t="inlineStr">
+    <row r="30">
+      <c r="C30" s="64" t="inlineStr">
         <is>
           <t>🚫 今日避開</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="C30" s="68" t="inlineStr">
+    <row r="31">
+      <c r="C31" s="68" t="inlineStr">
         <is>
           <t>今日無除權息</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="C31" s="66" t="inlineStr">
+    <row r="32">
+      <c r="C32" s="66" t="inlineStr">
         <is>
           <t>明日恐處置 3 檔 (3625 / 4304 / 4971)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="C33" s="64" t="inlineStr">
+    <row r="34">
+      <c r="C34" s="64" t="inlineStr">
         <is>
           <t>📊 追蹤池方向</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="C34" s="70" t="inlineStr">
-        <is>
-          <t>-54 億 淨買</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" s="68" t="inlineStr">
+    <row r="35" ht="22" customHeight="1">
+      <c r="C35" s="70" t="inlineStr">
+        <is>
+          <t>-56 億 淨買</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" s="68" t="inlineStr">
         <is>
           <t>比昨 -199 反彈 / 比 5d -122 偏強</t>
         </is>
@@ -17035,19 +17097,19 @@
         <v>30</v>
       </c>
       <c r="G189" s="133" t="n">
-        <v>10106</v>
+        <v>10886</v>
       </c>
       <c r="H189" s="133" t="n">
-        <v>3506</v>
+        <v>934</v>
       </c>
       <c r="I189" s="133" t="n">
-        <v>6600</v>
+        <v>9952</v>
       </c>
       <c r="J189" s="134" t="n">
-        <v>287.91</v>
+        <v>310.15</v>
       </c>
       <c r="K189" s="134" t="n">
-        <v>1168.57</v>
+        <v>311.4</v>
       </c>
       <c r="L189" s="237">
         <f>F189*(K189-J189)</f>
@@ -17070,16 +17132,16 @@
         <v>0</v>
       </c>
       <c r="G190" s="133" t="n">
-        <v>9301</v>
+        <v>9549</v>
       </c>
       <c r="H190" s="133" t="n">
         <v>0</v>
       </c>
       <c r="I190" s="133" t="n">
-        <v>9301</v>
+        <v>9549</v>
       </c>
       <c r="J190" s="134" t="n">
-        <v>1310</v>
+        <v>1344.94</v>
       </c>
       <c r="K190" s="134" t="n">
         <v>0</v>
@@ -17095,31 +17157,31 @@
       <c r="C191" s="135" t="n"/>
       <c r="D191" s="132" t="inlineStr">
         <is>
-          <t>台光電(2383)</t>
+          <t>欣興(3037)</t>
         </is>
       </c>
       <c r="E191" s="133" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="F191" s="133" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G191" s="133" t="n">
-        <v>4866</v>
+        <v>6166</v>
       </c>
       <c r="H191" s="133" t="n">
-        <v>3215</v>
+        <v>971</v>
       </c>
       <c r="I191" s="133" t="n">
-        <v>1651</v>
+        <v>5195</v>
       </c>
       <c r="J191" s="134" t="n">
-        <v>5406.11</v>
+        <v>880.87</v>
       </c>
       <c r="K191" s="134" t="n">
-        <v>5358.33</v>
-      </c>
-      <c r="L191" s="236">
+        <v>882.91</v>
+      </c>
+      <c r="L191" s="237">
         <f>F191*(K191-J191)</f>
         <v/>
       </c>
@@ -17140,21 +17202,21 @@
         <v>41</v>
       </c>
       <c r="G192" s="133" t="n">
-        <v>4494</v>
+        <v>4583</v>
       </c>
       <c r="H192" s="133" t="n">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="I192" s="133" t="n">
-        <v>3629</v>
+        <v>3723</v>
       </c>
       <c r="J192" s="134" t="n">
-        <v>211</v>
+        <v>215.15</v>
       </c>
       <c r="K192" s="134" t="n">
-        <v>211</v>
-      </c>
-      <c r="L192" s="237">
+        <v>209.63</v>
+      </c>
+      <c r="L192" s="236">
         <f>F192*(K192-J192)</f>
         <v/>
       </c>
@@ -17165,31 +17227,31 @@
       <c r="C193" s="135" t="n"/>
       <c r="D193" s="132" t="inlineStr">
         <is>
-          <t>晶豪科(3006)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E193" s="133" t="n">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="F193" s="133" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G193" s="133" t="n">
-        <v>2977</v>
+        <v>3486</v>
       </c>
       <c r="H193" s="133" t="n">
-        <v>1868</v>
+        <v>3006</v>
       </c>
       <c r="I193" s="133" t="n">
-        <v>1109</v>
+        <v>480</v>
       </c>
       <c r="J193" s="134" t="n">
-        <v>278.25</v>
+        <v>497.94</v>
       </c>
       <c r="K193" s="134" t="n">
-        <v>278.85</v>
-      </c>
-      <c r="L193" s="237">
+        <v>492.87</v>
+      </c>
+      <c r="L193" s="236">
         <f>F193*(K193-J193)</f>
         <v/>
       </c>
@@ -17200,29 +17262,29 @@
       <c r="C194" s="135" t="n"/>
       <c r="D194" s="132" t="inlineStr">
         <is>
-          <t>欣興(3037)</t>
+          <t>南電(8046)</t>
         </is>
       </c>
       <c r="E194" s="133" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F194" s="133" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G194" s="133" t="n">
-        <v>2625</v>
+        <v>3331</v>
       </c>
       <c r="H194" s="133" t="n">
-        <v>1625</v>
+        <v>1491</v>
       </c>
       <c r="I194" s="133" t="n">
-        <v>1000</v>
+        <v>1840</v>
       </c>
       <c r="J194" s="134" t="n">
-        <v>374.99</v>
+        <v>1040.88</v>
       </c>
       <c r="K194" s="134" t="n">
-        <v>1477.09</v>
+        <v>1065.07</v>
       </c>
       <c r="L194" s="237">
         <f>F194*(K194-J194)</f>
@@ -17235,29 +17297,29 @@
       <c r="C195" s="135" t="n"/>
       <c r="D195" s="132" t="inlineStr">
         <is>
-          <t>金像電(2368)</t>
+          <t>強茂(2481)</t>
         </is>
       </c>
       <c r="E195" s="133" t="n">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="F195" s="133" t="n">
-        <v>12</v>
+        <v>136</v>
       </c>
       <c r="G195" s="133" t="n">
-        <v>1944</v>
+        <v>2982</v>
       </c>
       <c r="H195" s="133" t="n">
-        <v>1263</v>
+        <v>2128</v>
       </c>
       <c r="I195" s="133" t="n">
-        <v>681</v>
+        <v>854</v>
       </c>
       <c r="J195" s="134" t="n">
-        <v>1022.89</v>
+        <v>154.51</v>
       </c>
       <c r="K195" s="134" t="n">
-        <v>1052.42</v>
+        <v>156.49</v>
       </c>
       <c r="L195" s="237">
         <f>F195*(K195-J195)</f>
@@ -17270,29 +17332,29 @@
       <c r="C196" s="135" t="n"/>
       <c r="D196" s="132" t="inlineStr">
         <is>
-          <t>永擎(7711)</t>
+          <t>光聖(6442)</t>
         </is>
       </c>
       <c r="E196" s="133" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F196" s="133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G196" s="133" t="n">
-        <v>1821</v>
+        <v>2148</v>
       </c>
       <c r="H196" s="133" t="n">
-        <v>22</v>
+        <v>535</v>
       </c>
       <c r="I196" s="133" t="n">
-        <v>1799</v>
+        <v>1613</v>
       </c>
       <c r="J196" s="134" t="n">
-        <v>628.03</v>
+        <v>1789.92</v>
       </c>
       <c r="K196" s="134" t="n">
-        <v>221</v>
+        <v>1783</v>
       </c>
       <c r="L196" s="236">
         <f>F196*(K196-J196)</f>
@@ -17305,31 +17367,31 @@
       <c r="C197" s="135" t="n"/>
       <c r="D197" s="132" t="inlineStr">
         <is>
-          <t>群創(3481)</t>
+          <t>奇鋐(3017)</t>
         </is>
       </c>
       <c r="E197" s="133" t="n">
-        <v>225</v>
+        <v>6</v>
       </c>
       <c r="F197" s="133" t="n">
-        <v>168</v>
+        <v>1</v>
       </c>
       <c r="G197" s="133" t="n">
-        <v>1677</v>
+        <v>2132</v>
       </c>
       <c r="H197" s="133" t="n">
-        <v>971</v>
+        <v>486</v>
       </c>
       <c r="I197" s="133" t="n">
-        <v>706</v>
+        <v>1646</v>
       </c>
       <c r="J197" s="134" t="n">
-        <v>74.54000000000001</v>
+        <v>3553.33</v>
       </c>
       <c r="K197" s="134" t="n">
-        <v>57.81</v>
-      </c>
-      <c r="L197" s="236">
+        <v>4860</v>
+      </c>
+      <c r="L197" s="237">
         <f>F197*(K197-J197)</f>
         <v/>
       </c>
@@ -17340,29 +17402,29 @@
       <c r="C198" s="135" t="n"/>
       <c r="D198" s="132" t="inlineStr">
         <is>
-          <t>一詮(2486)</t>
+          <t>玉晶光(3406)</t>
         </is>
       </c>
       <c r="E198" s="133" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="F198" s="133" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G198" s="133" t="n">
-        <v>1483</v>
+        <v>1738</v>
       </c>
       <c r="H198" s="133" t="n">
-        <v>1135</v>
+        <v>0</v>
       </c>
       <c r="I198" s="133" t="n">
-        <v>348</v>
+        <v>1738</v>
       </c>
       <c r="J198" s="134" t="n">
-        <v>255.72</v>
+        <v>1086.19</v>
       </c>
       <c r="K198" s="134" t="n">
-        <v>257.86</v>
+        <v>0</v>
       </c>
       <c r="L198" s="237">
         <f>F198*(K198-J198)</f>
@@ -27992,7 +28054,7 @@
     <row r="484" ht="16.5" customHeight="1">
       <c r="A484" s="204" t="inlineStr">
         <is>
-          <t>ⓘ top-buyer 資料 fetched @ 2026-09-05 02:06 TW | 17/17 success | 來源: 富邦17/histock0</t>
+          <t>ⓘ top-buyer 資料 fetched @ 2026-09-05 02:59 TW | 17/17 success | 來源: 富邦17/histock0</t>
         </is>
       </c>
     </row>
